--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,31 +502,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.7</v>
+        <v>113.55</v>
       </c>
       <c r="D2" t="n">
-        <v>114.73</v>
+        <v>114.61</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.03</v>
+        <v>-1.06</v>
       </c>
       <c r="F2" t="n">
         <v>115.2</v>
       </c>
       <c r="G2" t="n">
-        <v>114.91</v>
+        <v>114.77</v>
       </c>
       <c r="H2" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="I2" t="n">
-        <v>113.6</v>
+        <v>113.3</v>
       </c>
       <c r="J2" t="n">
-        <v>111.48</v>
+        <v>111.36</v>
       </c>
       <c r="K2" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="3">
@@ -554,31 +554,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.85</v>
+        <v>129.59</v>
       </c>
       <c r="D3" t="n">
-        <v>130.66</v>
+        <v>130.81</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.22</v>
       </c>
       <c r="F3" t="n">
         <v>130.95</v>
       </c>
       <c r="G3" t="n">
-        <v>129.54</v>
+        <v>129.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="n">
-        <v>129.35</v>
+        <v>129.08</v>
       </c>
       <c r="J3" t="n">
-        <v>125</v>
+        <v>125.15</v>
       </c>
       <c r="K3" t="n">
-        <v>4.35</v>
+        <v>3.93</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.62</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="4">
@@ -606,31 +606,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5642.5</v>
+        <v>5696.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5674.03</v>
+        <v>5685.62</v>
       </c>
       <c r="E4" t="n">
-        <v>-31.53</v>
+        <v>10.88</v>
       </c>
       <c r="F4" t="n">
-        <v>5665.5</v>
+        <v>5696.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5594.42</v>
+        <v>5606.71</v>
       </c>
       <c r="H4" t="n">
-        <v>71.08</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>5556</v>
       </c>
       <c r="J4" t="n">
-        <v>5488.99</v>
+        <v>5500.49</v>
       </c>
       <c r="K4" t="n">
-        <v>67.01000000000001</v>
+        <v>55.51</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="5">
@@ -658,31 +658,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1454.1</v>
+        <v>1458.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1465.63</v>
+        <v>1465.83</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.53</v>
+        <v>-7.03</v>
       </c>
       <c r="F5" t="n">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="G5" t="n">
-        <v>1416.09</v>
+        <v>1416.3</v>
       </c>
       <c r="H5" t="n">
-        <v>43.91</v>
+        <v>46.7</v>
       </c>
       <c r="I5" t="n">
         <v>1443.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1413.03</v>
+        <v>1413.23</v>
       </c>
       <c r="K5" t="n">
-        <v>30.47</v>
+        <v>30.27</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="6">
@@ -710,31 +710,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>364.4</v>
+        <v>366</v>
       </c>
       <c r="D6" t="n">
-        <v>367.82</v>
+        <v>367.11</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.42</v>
+        <v>-1.11</v>
       </c>
       <c r="F6" t="n">
         <v>372.3</v>
       </c>
       <c r="G6" t="n">
-        <v>369.66</v>
+        <v>368.91</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>3.39</v>
       </c>
       <c r="I6" t="n">
-        <v>364.1</v>
+        <v>363.6</v>
       </c>
       <c r="J6" t="n">
-        <v>356.89</v>
+        <v>356.16</v>
       </c>
       <c r="K6" t="n">
-        <v>7.21</v>
+        <v>7.44</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -762,31 +762,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12165</v>
+        <v>12190</v>
       </c>
       <c r="D7" t="n">
-        <v>12247.2</v>
+        <v>12252.24</v>
       </c>
       <c r="E7" t="n">
-        <v>-82.2</v>
+        <v>-62.24</v>
       </c>
       <c r="F7" t="n">
         <v>12239</v>
       </c>
       <c r="G7" t="n">
-        <v>12453.04</v>
+        <v>12458.04</v>
       </c>
       <c r="H7" t="n">
-        <v>-214.04</v>
+        <v>-219.04</v>
       </c>
       <c r="I7" t="n">
         <v>11970</v>
       </c>
       <c r="J7" t="n">
-        <v>12055.35</v>
+        <v>12060.74</v>
       </c>
       <c r="K7" t="n">
-        <v>-85.34999999999999</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="8">
@@ -814,31 +814,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4629.5</v>
+        <v>4645</v>
       </c>
       <c r="D8" t="n">
-        <v>4660.39</v>
+        <v>4668.05</v>
       </c>
       <c r="E8" t="n">
-        <v>-30.89</v>
+        <v>-23.05</v>
       </c>
       <c r="F8" t="n">
         <v>4673.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4662.53</v>
+        <v>4670.81</v>
       </c>
       <c r="H8" t="n">
-        <v>10.87</v>
+        <v>2.59</v>
       </c>
       <c r="I8" t="n">
         <v>4603.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4527.18</v>
+        <v>4534.78</v>
       </c>
       <c r="K8" t="n">
-        <v>76.12</v>
+        <v>68.52</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="9">
@@ -869,28 +869,28 @@
         <v>2760</v>
       </c>
       <c r="D9" t="n">
-        <v>2780.06</v>
+        <v>2781.07</v>
       </c>
       <c r="E9" t="n">
-        <v>-20.06</v>
+        <v>-21.07</v>
       </c>
       <c r="F9" t="n">
         <v>2787</v>
       </c>
       <c r="G9" t="n">
-        <v>2779.48</v>
+        <v>2780.66</v>
       </c>
       <c r="H9" t="n">
-        <v>7.52</v>
+        <v>6.34</v>
       </c>
       <c r="I9" t="n">
         <v>2748.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2686.92</v>
+        <v>2687.92</v>
       </c>
       <c r="K9" t="n">
-        <v>61.78</v>
+        <v>60.78</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="10">
@@ -918,31 +918,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>737.55</v>
+        <v>741.05</v>
       </c>
       <c r="D10" t="n">
-        <v>747.73</v>
+        <v>743.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.18</v>
+        <v>-2.45</v>
       </c>
       <c r="F10" t="n">
         <v>752.9</v>
       </c>
       <c r="G10" t="n">
-        <v>735.01</v>
+        <v>729.87</v>
       </c>
       <c r="H10" t="n">
-        <v>17.89</v>
+        <v>23.03</v>
       </c>
       <c r="I10" t="n">
-        <v>737.45</v>
+        <v>733.95</v>
       </c>
       <c r="J10" t="n">
-        <v>723.83</v>
+        <v>719.63</v>
       </c>
       <c r="K10" t="n">
-        <v>13.62</v>
+        <v>14.32</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="11">
@@ -970,31 +970,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D11" t="n">
-        <v>1202.34</v>
+        <v>1200.53</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.34</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>1194.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1218.66</v>
+        <v>1215.78</v>
       </c>
       <c r="H11" t="n">
-        <v>-23.96</v>
+        <v>-21.08</v>
       </c>
       <c r="I11" t="n">
         <v>1163.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1176.91</v>
+        <v>1174.1</v>
       </c>
       <c r="K11" t="n">
-        <v>-13.61</v>
+        <v>-10.8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="12">
@@ -1022,35 +1022,35 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>612.25</v>
+        <v>603</v>
       </c>
       <c r="D12" t="n">
-        <v>612.96</v>
+        <v>617.05</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.71</v>
+        <v>-14.05</v>
       </c>
       <c r="F12" t="n">
         <v>632.5</v>
       </c>
       <c r="G12" t="n">
-        <v>595.73</v>
+        <v>600.51</v>
       </c>
       <c r="H12" t="n">
-        <v>36.77</v>
+        <v>31.99</v>
       </c>
       <c r="I12" t="n">
         <v>602.6</v>
       </c>
       <c r="J12" t="n">
-        <v>582.35</v>
+        <v>586.4</v>
       </c>
       <c r="K12" t="n">
-        <v>20.25</v>
+        <v>16.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.12</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="13">
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8007</v>
+        <v>7986.5</v>
       </c>
       <c r="D13" t="n">
-        <v>8063.5</v>
+        <v>8074.08</v>
       </c>
       <c r="E13" t="n">
-        <v>-56.5</v>
+        <v>-87.58</v>
       </c>
       <c r="F13" t="n">
-        <v>8018</v>
+        <v>8019</v>
       </c>
       <c r="G13" t="n">
-        <v>8157.7</v>
+        <v>8167.83</v>
       </c>
       <c r="H13" t="n">
-        <v>-139.7</v>
+        <v>-148.83</v>
       </c>
       <c r="I13" t="n">
         <v>7905.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7877.72</v>
+        <v>7887.48</v>
       </c>
       <c r="K13" t="n">
-        <v>27.78</v>
+        <v>18.02</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="14">
@@ -1126,31 +1126,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2122.7</v>
+        <v>2099</v>
       </c>
       <c r="D14" t="n">
-        <v>2132.93</v>
+        <v>2138.37</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.23</v>
+        <v>-39.37</v>
       </c>
       <c r="F14" t="n">
         <v>2143.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2017.79</v>
+        <v>2024.27</v>
       </c>
       <c r="H14" t="n">
-        <v>126.11</v>
+        <v>119.63</v>
       </c>
       <c r="I14" t="n">
         <v>2055.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2033.95</v>
+        <v>2039.35</v>
       </c>
       <c r="K14" t="n">
-        <v>21.75</v>
+        <v>16.35</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.48</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="15">
@@ -1178,31 +1178,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1661.1</v>
+        <v>1650</v>
       </c>
       <c r="D15" t="n">
-        <v>1669.45</v>
+        <v>1674.09</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.35</v>
+        <v>-24.09</v>
       </c>
       <c r="F15" t="n">
         <v>1664.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1685.36</v>
+        <v>1690.45</v>
       </c>
       <c r="H15" t="n">
-        <v>-20.56</v>
+        <v>-25.65</v>
       </c>
       <c r="I15" t="n">
-        <v>1647.7</v>
+        <v>1639</v>
       </c>
       <c r="J15" t="n">
-        <v>1627.4</v>
+        <v>1632.32</v>
       </c>
       <c r="K15" t="n">
-        <v>20.3</v>
+        <v>6.68</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
@@ -1230,31 +1230,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>311.25</v>
+        <v>310.35</v>
       </c>
       <c r="D16" t="n">
-        <v>313.19</v>
+        <v>313.84</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.94</v>
+        <v>-3.49</v>
       </c>
       <c r="F16" t="n">
         <v>314.65</v>
       </c>
       <c r="G16" t="n">
-        <v>317.06</v>
+        <v>317.77</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.41</v>
+        <v>-3.12</v>
       </c>
       <c r="I16" t="n">
-        <v>310.25</v>
+        <v>309.5</v>
       </c>
       <c r="J16" t="n">
-        <v>306.18</v>
+        <v>306.87</v>
       </c>
       <c r="K16" t="n">
-        <v>4.07</v>
+        <v>2.63</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="17">
@@ -1282,31 +1282,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14349</v>
+        <v>14310</v>
       </c>
       <c r="D17" t="n">
-        <v>14409.36</v>
+        <v>14462.78</v>
       </c>
       <c r="E17" t="n">
-        <v>-60.36</v>
+        <v>-152.78</v>
       </c>
       <c r="F17" t="n">
-        <v>14367</v>
+        <v>14395</v>
       </c>
       <c r="G17" t="n">
-        <v>14685.71</v>
+        <v>14747.67</v>
       </c>
       <c r="H17" t="n">
-        <v>-318.71</v>
+        <v>-352.67</v>
       </c>
       <c r="I17" t="n">
         <v>14023</v>
       </c>
       <c r="J17" t="n">
-        <v>14185.38</v>
+        <v>14245.49</v>
       </c>
       <c r="K17" t="n">
-        <v>-162.38</v>
+        <v>-222.49</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="18">
@@ -1334,31 +1334,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1780.5</v>
+        <v>1777</v>
       </c>
       <c r="D18" t="n">
-        <v>1801.88</v>
+        <v>1806.47</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.38</v>
+        <v>-29.47</v>
       </c>
       <c r="F18" t="n">
         <v>1788</v>
       </c>
       <c r="G18" t="n">
-        <v>1837.43</v>
+        <v>1842.09</v>
       </c>
       <c r="H18" t="n">
-        <v>-49.43</v>
+        <v>-54.09</v>
       </c>
       <c r="I18" t="n">
         <v>1745.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1775.22</v>
+        <v>1779.76</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.12</v>
+        <v>-34.66</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -1472,31 +1472,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24531.6</v>
+        <v>24624.65</v>
       </c>
       <c r="D2" t="n">
-        <v>24523.85</v>
+        <v>24533.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7.75</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>24677.6</v>
       </c>
       <c r="G2" t="n">
-        <v>24628.49</v>
+        <v>24637.91</v>
       </c>
       <c r="H2" t="n">
-        <v>49.11</v>
+        <v>39.69</v>
       </c>
       <c r="I2" t="n">
-        <v>24508.45</v>
+        <v>24497.95</v>
       </c>
       <c r="J2" t="n">
-        <v>24468.34</v>
+        <v>24468.76</v>
       </c>
       <c r="K2" t="n">
-        <v>40.11</v>
+        <v>29.19</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="3">
@@ -1524,31 +1524,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57542.15</v>
+        <v>57739.95</v>
       </c>
       <c r="D3" t="n">
-        <v>57552.2</v>
+        <v>57541.8</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.05</v>
+        <v>198.15</v>
       </c>
       <c r="F3" t="n">
         <v>57931.85</v>
       </c>
       <c r="G3" t="n">
-        <v>57810.11</v>
+        <v>57818.39</v>
       </c>
       <c r="H3" t="n">
-        <v>121.74</v>
+        <v>113.46</v>
       </c>
       <c r="I3" t="n">
-        <v>57492.15</v>
+        <v>57456.35</v>
       </c>
       <c r="J3" t="n">
-        <v>57416.01</v>
+        <v>57378.69</v>
       </c>
       <c r="K3" t="n">
-        <v>76.14</v>
+        <v>77.66</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.02</v>
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -1662,35 +1662,35 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.7</v>
+        <v>113.55</v>
       </c>
       <c r="D2" t="n">
-        <v>116.64</v>
+        <v>116.52</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.94</v>
+        <v>-2.97</v>
       </c>
       <c r="F2" t="n">
         <v>115.2</v>
       </c>
       <c r="G2" t="n">
-        <v>116.54</v>
+        <v>116.42</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.34</v>
+        <v>-1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>113.6</v>
+        <v>113.3</v>
       </c>
       <c r="J2" t="n">
-        <v>112.45</v>
+        <v>112.33</v>
       </c>
       <c r="K2" t="n">
-        <v>1.15</v>
+        <v>0.97</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
@@ -1714,35 +1714,35 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.85</v>
+        <v>129.59</v>
       </c>
       <c r="D3" t="n">
-        <v>135.5</v>
+        <v>135.65</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.65</v>
+        <v>-6.06</v>
       </c>
       <c r="F3" t="n">
         <v>130.95</v>
       </c>
       <c r="G3" t="n">
-        <v>135.28</v>
+        <v>135.43</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.33</v>
+        <v>-4.48</v>
       </c>
       <c r="I3" t="n">
-        <v>129.35</v>
+        <v>129.08</v>
       </c>
       <c r="J3" t="n">
-        <v>126.13</v>
+        <v>126.28</v>
       </c>
       <c r="K3" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.17</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="4">
@@ -1766,31 +1766,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5645.5</v>
+        <v>5696.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5793.54</v>
+        <v>5805.08</v>
       </c>
       <c r="E4" t="n">
-        <v>-148.04</v>
+        <v>-108.58</v>
       </c>
       <c r="F4" t="n">
-        <v>5665.5</v>
+        <v>5696.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5787.71</v>
+        <v>5799.25</v>
       </c>
       <c r="H4" t="n">
-        <v>-122.21</v>
+        <v>-102.75</v>
       </c>
       <c r="I4" t="n">
         <v>5556</v>
       </c>
       <c r="J4" t="n">
-        <v>5542.68</v>
+        <v>5554.22</v>
       </c>
       <c r="K4" t="n">
-        <v>13.32</v>
+        <v>1.78</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1799,11 +1799,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="5">
@@ -1818,31 +1818,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1454.4</v>
+        <v>1458.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1501.5</v>
+        <v>1501.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-47.1</v>
+        <v>-42.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="G5" t="n">
-        <v>1499.8</v>
+        <v>1500</v>
       </c>
       <c r="H5" t="n">
-        <v>-39.8</v>
+        <v>-37</v>
       </c>
       <c r="I5" t="n">
         <v>1443.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1428.1</v>
+        <v>1428.3</v>
       </c>
       <c r="K5" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="6">
@@ -1870,31 +1870,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>364.35</v>
+        <v>366</v>
       </c>
       <c r="D6" t="n">
-        <v>375.9</v>
+        <v>375.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-11.55</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>372.3</v>
       </c>
       <c r="G6" t="n">
-        <v>375.51</v>
+        <v>374.81</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.21</v>
+        <v>-2.51</v>
       </c>
       <c r="I6" t="n">
-        <v>364.1</v>
+        <v>363.6</v>
       </c>
       <c r="J6" t="n">
-        <v>359.06</v>
+        <v>358.36</v>
       </c>
       <c r="K6" t="n">
-        <v>5.04</v>
+        <v>5.24</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="7">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12165</v>
+        <v>12190</v>
       </c>
       <c r="D7" t="n">
-        <v>12442.88</v>
+        <v>12447.9</v>
       </c>
       <c r="E7" t="n">
-        <v>-277.88</v>
+        <v>-257.9</v>
       </c>
       <c r="F7" t="n">
         <v>12239</v>
       </c>
       <c r="G7" t="n">
-        <v>12432.78</v>
+        <v>12437.8</v>
       </c>
       <c r="H7" t="n">
-        <v>-193.78</v>
+        <v>-198.8</v>
       </c>
       <c r="I7" t="n">
         <v>11970</v>
       </c>
       <c r="J7" t="n">
-        <v>12008.51</v>
+        <v>12013.53</v>
       </c>
       <c r="K7" t="n">
-        <v>-38.51</v>
+        <v>-43.53</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="8">
@@ -1974,31 +1974,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4629.9</v>
+        <v>4645</v>
       </c>
       <c r="D8" t="n">
-        <v>4738.99</v>
+        <v>4746.62</v>
       </c>
       <c r="E8" t="n">
-        <v>-109.09</v>
+        <v>-101.62</v>
       </c>
       <c r="F8" t="n">
         <v>4673.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4734.98</v>
+        <v>4742.61</v>
       </c>
       <c r="H8" t="n">
-        <v>-61.58</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>4603.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4566.58</v>
+        <v>4574.21</v>
       </c>
       <c r="K8" t="n">
-        <v>36.72</v>
+        <v>29.09</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="9">
@@ -2026,31 +2026,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2759.2</v>
+        <v>2760</v>
       </c>
       <c r="D9" t="n">
-        <v>2841.21</v>
+        <v>2842.21</v>
       </c>
       <c r="E9" t="n">
-        <v>-82.01000000000001</v>
+        <v>-82.20999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>2787</v>
       </c>
       <c r="G9" t="n">
-        <v>2838.25</v>
+        <v>2839.25</v>
       </c>
       <c r="H9" t="n">
-        <v>-51.25</v>
+        <v>-52.25</v>
       </c>
       <c r="I9" t="n">
         <v>2748.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2713.84</v>
+        <v>2714.84</v>
       </c>
       <c r="K9" t="n">
-        <v>34.86</v>
+        <v>33.86</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2078,31 +2078,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>737.55</v>
+        <v>741.05</v>
       </c>
       <c r="D10" t="n">
-        <v>762.97</v>
+        <v>758.76</v>
       </c>
       <c r="E10" t="n">
-        <v>-25.42</v>
+        <v>-17.71</v>
       </c>
       <c r="F10" t="n">
         <v>752.9</v>
       </c>
       <c r="G10" t="n">
-        <v>762.22</v>
+        <v>758.01</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.32</v>
+        <v>-5.11</v>
       </c>
       <c r="I10" t="n">
-        <v>737.45</v>
+        <v>733.95</v>
       </c>
       <c r="J10" t="n">
-        <v>730.79</v>
+        <v>726.58</v>
       </c>
       <c r="K10" t="n">
-        <v>6.66</v>
+        <v>7.37</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2111,11 +2111,11 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.33</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11">
@@ -2130,31 +2130,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D11" t="n">
-        <v>1239.18</v>
+        <v>1237.38</v>
       </c>
       <c r="E11" t="n">
-        <v>-48.18</v>
+        <v>-45.38</v>
       </c>
       <c r="F11" t="n">
         <v>1194.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1237.49</v>
+        <v>1235.68</v>
       </c>
       <c r="H11" t="n">
-        <v>-42.79</v>
+        <v>-40.98</v>
       </c>
       <c r="I11" t="n">
         <v>1163.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1166.21</v>
+        <v>1164.4</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.91</v>
+        <v>-1.1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.89</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="12">
@@ -2182,44 +2182,44 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>612.25</v>
+        <v>603</v>
       </c>
       <c r="D12" t="n">
-        <v>636.95</v>
+        <v>641</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.7</v>
+        <v>-38</v>
       </c>
       <c r="F12" t="n">
         <v>632.5</v>
       </c>
       <c r="G12" t="n">
-        <v>635.87</v>
+        <v>639.9299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.37</v>
+        <v>-7.43</v>
       </c>
       <c r="I12" t="n">
         <v>602.6</v>
       </c>
       <c r="J12" t="n">
-        <v>590.8099999999999</v>
+        <v>594.87</v>
       </c>
       <c r="K12" t="n">
-        <v>11.79</v>
+        <v>7.73</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.88</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="13">
@@ -2234,31 +2234,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8010</v>
+        <v>7986.5</v>
       </c>
       <c r="D13" t="n">
-        <v>8222.07</v>
+        <v>8232.610000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-212.07</v>
+        <v>-246.11</v>
       </c>
       <c r="F13" t="n">
-        <v>8018</v>
+        <v>8019</v>
       </c>
       <c r="G13" t="n">
-        <v>8214.23</v>
+        <v>8224.77</v>
       </c>
       <c r="H13" t="n">
-        <v>-196.23</v>
+        <v>-205.77</v>
       </c>
       <c r="I13" t="n">
         <v>7905.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7884.93</v>
+        <v>7895.47</v>
       </c>
       <c r="K13" t="n">
-        <v>20.57</v>
+        <v>10.03</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="14">
@@ -2286,31 +2286,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2123.5</v>
+        <v>2099</v>
       </c>
       <c r="D14" t="n">
-        <v>2208.49</v>
+        <v>2213.9</v>
       </c>
       <c r="E14" t="n">
-        <v>-84.98999999999999</v>
+        <v>-114.9</v>
       </c>
       <c r="F14" t="n">
         <v>2143.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2205.07</v>
+        <v>2210.48</v>
       </c>
       <c r="H14" t="n">
-        <v>-61.17</v>
+        <v>-66.58</v>
       </c>
       <c r="I14" t="n">
         <v>2055.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2061.5</v>
+        <v>2066.91</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.8</v>
+        <v>-11.21</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="15">
@@ -2338,31 +2338,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1661.3</v>
+        <v>1650</v>
       </c>
       <c r="D15" t="n">
-        <v>1718.66</v>
+        <v>1723.27</v>
       </c>
       <c r="E15" t="n">
-        <v>-57.36</v>
+        <v>-73.27</v>
       </c>
       <c r="F15" t="n">
         <v>1664.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1716.38</v>
+        <v>1720.99</v>
       </c>
       <c r="H15" t="n">
-        <v>-51.58</v>
+        <v>-56.19</v>
       </c>
       <c r="I15" t="n">
-        <v>1647.7</v>
+        <v>1639</v>
       </c>
       <c r="J15" t="n">
-        <v>1620.69</v>
+        <v>1625.3</v>
       </c>
       <c r="K15" t="n">
-        <v>27.01</v>
+        <v>13.7</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.34</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="16">
@@ -2390,31 +2390,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>311.5</v>
+        <v>310.35</v>
       </c>
       <c r="D16" t="n">
-        <v>324.67</v>
+        <v>325.32</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.17</v>
+        <v>-14.97</v>
       </c>
       <c r="F16" t="n">
         <v>314.65</v>
       </c>
       <c r="G16" t="n">
-        <v>324.15</v>
+        <v>324.8</v>
       </c>
       <c r="H16" t="n">
-        <v>-9.5</v>
+        <v>-10.15</v>
       </c>
       <c r="I16" t="n">
-        <v>310.25</v>
+        <v>309.5</v>
       </c>
       <c r="J16" t="n">
-        <v>302.42</v>
+        <v>303.06</v>
       </c>
       <c r="K16" t="n">
-        <v>7.83</v>
+        <v>6.44</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.06</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="17">
@@ -2442,31 +2442,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14349</v>
+        <v>14310</v>
       </c>
       <c r="D17" t="n">
-        <v>14929.34</v>
+        <v>14982.51</v>
       </c>
       <c r="E17" t="n">
-        <v>-580.34</v>
+        <v>-672.51</v>
       </c>
       <c r="F17" t="n">
-        <v>14367</v>
+        <v>14395</v>
       </c>
       <c r="G17" t="n">
-        <v>14905.87</v>
+        <v>14959.04</v>
       </c>
       <c r="H17" t="n">
-        <v>-538.87</v>
+        <v>-564.04</v>
       </c>
       <c r="I17" t="n">
         <v>14023</v>
       </c>
       <c r="J17" t="n">
-        <v>13919.92</v>
+        <v>13973.09</v>
       </c>
       <c r="K17" t="n">
-        <v>103.08</v>
+        <v>49.91</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="18">
@@ -2494,35 +2494,35 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1780.5</v>
+        <v>1777</v>
       </c>
       <c r="D18" t="n">
-        <v>1856.14</v>
+        <v>1859.55</v>
       </c>
       <c r="E18" t="n">
-        <v>-75.64</v>
+        <v>-82.55</v>
       </c>
       <c r="F18" t="n">
         <v>1788</v>
       </c>
       <c r="G18" t="n">
-        <v>1853.23</v>
+        <v>1856.64</v>
       </c>
       <c r="H18" t="n">
-        <v>-65.23</v>
+        <v>-68.64</v>
       </c>
       <c r="I18" t="n">
         <v>1745.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1731.03</v>
+        <v>1734.44</v>
       </c>
       <c r="K18" t="n">
-        <v>14.07</v>
+        <v>10.66</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.08</v>
+        <v>4.44</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,28 +505,28 @@
         <v>113.55</v>
       </c>
       <c r="D2" t="n">
-        <v>114.61</v>
+        <v>113.4</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.06</v>
+        <v>0.15</v>
       </c>
       <c r="F2" t="n">
         <v>115.2</v>
       </c>
       <c r="G2" t="n">
-        <v>114.77</v>
+        <v>113.67</v>
       </c>
       <c r="H2" t="n">
-        <v>0.43</v>
+        <v>1.53</v>
       </c>
       <c r="I2" t="n">
         <v>113.3</v>
       </c>
       <c r="J2" t="n">
-        <v>111.36</v>
+        <v>112.1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.94</v>
+        <v>1.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.92</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3">
@@ -557,28 +557,28 @@
         <v>129.59</v>
       </c>
       <c r="D3" t="n">
-        <v>130.81</v>
+        <v>129.41</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.22</v>
+        <v>0.18</v>
       </c>
       <c r="F3" t="n">
         <v>130.95</v>
       </c>
       <c r="G3" t="n">
-        <v>129.7</v>
+        <v>129.41</v>
       </c>
       <c r="H3" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="I3" t="n">
         <v>129.08</v>
       </c>
       <c r="J3" t="n">
-        <v>125.15</v>
+        <v>125.97</v>
       </c>
       <c r="K3" t="n">
-        <v>3.93</v>
+        <v>3.11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.93</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="4">
@@ -609,32 +609,32 @@
         <v>5696.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5685.62</v>
+        <v>5753.04</v>
       </c>
       <c r="E4" t="n">
-        <v>10.88</v>
+        <v>-56.54</v>
       </c>
       <c r="F4" t="n">
         <v>5696.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5606.71</v>
+        <v>5753.04</v>
       </c>
       <c r="H4" t="n">
-        <v>89.79000000000001</v>
+        <v>-56.54</v>
       </c>
       <c r="I4" t="n">
         <v>5556</v>
       </c>
       <c r="J4" t="n">
-        <v>5500.49</v>
+        <v>5603.74</v>
       </c>
       <c r="K4" t="n">
-        <v>55.51</v>
+        <v>-47.74</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.19</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -661,28 +661,28 @@
         <v>1458.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1465.83</v>
+        <v>1463.41</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.03</v>
+        <v>-4.61</v>
       </c>
       <c r="F5" t="n">
         <v>1463</v>
       </c>
       <c r="G5" t="n">
-        <v>1416.3</v>
+        <v>1463.41</v>
       </c>
       <c r="H5" t="n">
-        <v>46.7</v>
+        <v>-0.41</v>
       </c>
       <c r="I5" t="n">
         <v>1443.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1413.23</v>
+        <v>1429.22</v>
       </c>
       <c r="K5" t="n">
-        <v>30.27</v>
+        <v>14.28</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6">
@@ -713,28 +713,28 @@
         <v>366</v>
       </c>
       <c r="D6" t="n">
-        <v>367.11</v>
+        <v>367.82</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.11</v>
+        <v>-1.82</v>
       </c>
       <c r="F6" t="n">
         <v>372.3</v>
       </c>
       <c r="G6" t="n">
-        <v>368.91</v>
+        <v>367.82</v>
       </c>
       <c r="H6" t="n">
-        <v>3.39</v>
+        <v>4.48</v>
       </c>
       <c r="I6" t="n">
         <v>363.6</v>
       </c>
       <c r="J6" t="n">
-        <v>356.16</v>
+        <v>359.75</v>
       </c>
       <c r="K6" t="n">
-        <v>7.44</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.3</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="7">
@@ -765,28 +765,28 @@
         <v>12190</v>
       </c>
       <c r="D7" t="n">
-        <v>12252.24</v>
+        <v>12225.1</v>
       </c>
       <c r="E7" t="n">
-        <v>-62.24</v>
+        <v>-35.1</v>
       </c>
       <c r="F7" t="n">
         <v>12239</v>
       </c>
       <c r="G7" t="n">
-        <v>12458.04</v>
+        <v>12390.22</v>
       </c>
       <c r="H7" t="n">
-        <v>-219.04</v>
+        <v>-151.22</v>
       </c>
       <c r="I7" t="n">
         <v>11970</v>
       </c>
       <c r="J7" t="n">
-        <v>12060.74</v>
+        <v>12190</v>
       </c>
       <c r="K7" t="n">
-        <v>-90.73999999999999</v>
+        <v>-220</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="8">
@@ -817,28 +817,28 @@
         <v>4645</v>
       </c>
       <c r="D8" t="n">
-        <v>4668.05</v>
+        <v>4659.03</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.05</v>
+        <v>-14.03</v>
       </c>
       <c r="F8" t="n">
         <v>4673.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4670.81</v>
+        <v>4659.03</v>
       </c>
       <c r="H8" t="n">
-        <v>2.59</v>
+        <v>14.37</v>
       </c>
       <c r="I8" t="n">
         <v>4603.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4534.78</v>
+        <v>4585.31</v>
       </c>
       <c r="K8" t="n">
-        <v>68.52</v>
+        <v>17.99</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -869,28 +869,28 @@
         <v>2760</v>
       </c>
       <c r="D9" t="n">
-        <v>2781.07</v>
+        <v>2760.99</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.07</v>
+        <v>-0.99</v>
       </c>
       <c r="F9" t="n">
         <v>2787</v>
       </c>
       <c r="G9" t="n">
-        <v>2780.66</v>
+        <v>2760.99</v>
       </c>
       <c r="H9" t="n">
-        <v>6.34</v>
+        <v>26.01</v>
       </c>
       <c r="I9" t="n">
         <v>2748.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2687.92</v>
+        <v>2710.51</v>
       </c>
       <c r="K9" t="n">
-        <v>60.78</v>
+        <v>38.19</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.76</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10">
@@ -921,28 +921,28 @@
         <v>741.05</v>
       </c>
       <c r="D10" t="n">
-        <v>743.5</v>
+        <v>744.51</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.45</v>
+        <v>-3.46</v>
       </c>
       <c r="F10" t="n">
         <v>752.9</v>
       </c>
       <c r="G10" t="n">
-        <v>729.87</v>
+        <v>744.51</v>
       </c>
       <c r="H10" t="n">
-        <v>23.03</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>733.95</v>
       </c>
       <c r="J10" t="n">
-        <v>719.63</v>
+        <v>728.89</v>
       </c>
       <c r="K10" t="n">
-        <v>14.32</v>
+        <v>5.06</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="11">
@@ -973,32 +973,32 @@
         <v>1192</v>
       </c>
       <c r="D11" t="n">
-        <v>1200.53</v>
+        <v>1193.36</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.529999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="F11" t="n">
         <v>1194.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1215.78</v>
+        <v>1215.66</v>
       </c>
       <c r="H11" t="n">
-        <v>-21.08</v>
+        <v>-20.96</v>
       </c>
       <c r="I11" t="n">
         <v>1163.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1174.1</v>
+        <v>1192</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.8</v>
+        <v>-28.7</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.71</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -1025,32 +1025,32 @@
         <v>603</v>
       </c>
       <c r="D12" t="n">
-        <v>617.05</v>
+        <v>593.98</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.05</v>
+        <v>9.02</v>
       </c>
       <c r="F12" t="n">
         <v>632.5</v>
       </c>
       <c r="G12" t="n">
-        <v>600.51</v>
+        <v>593.98</v>
       </c>
       <c r="H12" t="n">
-        <v>31.99</v>
+        <v>38.52</v>
       </c>
       <c r="I12" t="n">
         <v>602.6</v>
       </c>
       <c r="J12" t="n">
-        <v>586.4</v>
+        <v>581.89</v>
       </c>
       <c r="K12" t="n">
-        <v>16.2</v>
+        <v>20.71</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="13">
@@ -1077,28 +1077,28 @@
         <v>7986.5</v>
       </c>
       <c r="D13" t="n">
-        <v>8074.08</v>
+        <v>7963.04</v>
       </c>
       <c r="E13" t="n">
-        <v>-87.58</v>
+        <v>23.46</v>
       </c>
       <c r="F13" t="n">
         <v>8019</v>
       </c>
       <c r="G13" t="n">
-        <v>8167.83</v>
+        <v>8076.38</v>
       </c>
       <c r="H13" t="n">
-        <v>-148.83</v>
+        <v>-57.38</v>
       </c>
       <c r="I13" t="n">
         <v>7905.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7887.48</v>
+        <v>7927.02</v>
       </c>
       <c r="K13" t="n">
-        <v>18.02</v>
+        <v>-21.52</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="14">
@@ -1129,28 +1129,28 @@
         <v>2099</v>
       </c>
       <c r="D14" t="n">
-        <v>2138.37</v>
+        <v>2076.84</v>
       </c>
       <c r="E14" t="n">
-        <v>-39.37</v>
+        <v>22.16</v>
       </c>
       <c r="F14" t="n">
         <v>2143.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2024.27</v>
+        <v>2076.84</v>
       </c>
       <c r="H14" t="n">
-        <v>119.63</v>
+        <v>67.06</v>
       </c>
       <c r="I14" t="n">
         <v>2055.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2039.35</v>
+        <v>2033.15</v>
       </c>
       <c r="K14" t="n">
-        <v>16.35</v>
+        <v>22.55</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="15">
@@ -1181,32 +1181,32 @@
         <v>1650</v>
       </c>
       <c r="D15" t="n">
-        <v>1674.09</v>
+        <v>1639.27</v>
       </c>
       <c r="E15" t="n">
-        <v>-24.09</v>
+        <v>10.73</v>
       </c>
       <c r="F15" t="n">
         <v>1664.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1690.45</v>
+        <v>1678.63</v>
       </c>
       <c r="H15" t="n">
-        <v>-25.65</v>
+        <v>-13.83</v>
       </c>
       <c r="I15" t="n">
         <v>1639</v>
       </c>
       <c r="J15" t="n">
-        <v>1632.32</v>
+        <v>1647.94</v>
       </c>
       <c r="K15" t="n">
-        <v>6.68</v>
+        <v>-8.94</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="16">
@@ -1233,28 +1233,28 @@
         <v>310.35</v>
       </c>
       <c r="D16" t="n">
-        <v>313.84</v>
+        <v>309.35</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.49</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>314.65</v>
       </c>
       <c r="G16" t="n">
-        <v>317.77</v>
+        <v>314.06</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.12</v>
+        <v>0.59</v>
       </c>
       <c r="I16" t="n">
         <v>309.5</v>
       </c>
       <c r="J16" t="n">
-        <v>306.87</v>
+        <v>308.27</v>
       </c>
       <c r="K16" t="n">
-        <v>2.63</v>
+        <v>1.23</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.11</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="17">
@@ -1285,28 +1285,28 @@
         <v>14310</v>
       </c>
       <c r="D17" t="n">
-        <v>14462.78</v>
+        <v>14272.16</v>
       </c>
       <c r="E17" t="n">
-        <v>-152.78</v>
+        <v>37.84</v>
       </c>
       <c r="F17" t="n">
         <v>14395</v>
       </c>
       <c r="G17" t="n">
-        <v>14747.67</v>
+        <v>14581.96</v>
       </c>
       <c r="H17" t="n">
-        <v>-352.67</v>
+        <v>-186.96</v>
       </c>
       <c r="I17" t="n">
         <v>14023</v>
       </c>
       <c r="J17" t="n">
-        <v>14245.49</v>
+        <v>14310</v>
       </c>
       <c r="K17" t="n">
-        <v>-222.49</v>
+        <v>-287</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.06</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="18">
@@ -1337,28 +1337,28 @@
         <v>1777</v>
       </c>
       <c r="D18" t="n">
-        <v>1806.47</v>
+        <v>1771.87</v>
       </c>
       <c r="E18" t="n">
-        <v>-29.47</v>
+        <v>5.13</v>
       </c>
       <c r="F18" t="n">
         <v>1788</v>
       </c>
       <c r="G18" t="n">
-        <v>1842.09</v>
+        <v>1821.67</v>
       </c>
       <c r="H18" t="n">
-        <v>-54.09</v>
+        <v>-33.67</v>
       </c>
       <c r="I18" t="n">
         <v>1745.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1779.76</v>
+        <v>1777</v>
       </c>
       <c r="K18" t="n">
-        <v>-34.66</v>
+        <v>-31.9</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -1475,28 +1475,28 @@
         <v>24624.65</v>
       </c>
       <c r="D2" t="n">
-        <v>24533.5</v>
+        <v>24624.65</v>
       </c>
       <c r="E2" t="n">
-        <v>91.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>24677.6</v>
       </c>
       <c r="G2" t="n">
-        <v>24637.91</v>
+        <v>24702.19</v>
       </c>
       <c r="H2" t="n">
-        <v>39.69</v>
+        <v>-24.59</v>
       </c>
       <c r="I2" t="n">
         <v>24497.95</v>
       </c>
       <c r="J2" t="n">
-        <v>24468.76</v>
+        <v>24522.54</v>
       </c>
       <c r="K2" t="n">
-        <v>29.19</v>
+        <v>-24.59</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1527,28 +1527,28 @@
         <v>57739.95</v>
       </c>
       <c r="D3" t="n">
-        <v>57541.8</v>
+        <v>57739.95</v>
       </c>
       <c r="E3" t="n">
-        <v>198.15</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>57931.85</v>
       </c>
       <c r="G3" t="n">
-        <v>57818.39</v>
+        <v>57962.41</v>
       </c>
       <c r="H3" t="n">
-        <v>113.46</v>
+        <v>-30.56</v>
       </c>
       <c r="I3" t="n">
         <v>57456.35</v>
       </c>
       <c r="J3" t="n">
-        <v>57378.69</v>
+        <v>57486.91</v>
       </c>
       <c r="K3" t="n">
-        <v>77.66</v>
+        <v>-30.56</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1665,41 +1665,41 @@
         <v>113.55</v>
       </c>
       <c r="D2" t="n">
-        <v>116.52</v>
+        <v>115.27</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.97</v>
+        <v>-1.72</v>
       </c>
       <c r="F2" t="n">
         <v>115.2</v>
       </c>
       <c r="G2" t="n">
-        <v>116.42</v>
+        <v>115.29</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.22</v>
+        <v>-0.09</v>
       </c>
       <c r="I2" t="n">
         <v>113.3</v>
       </c>
       <c r="J2" t="n">
-        <v>112.33</v>
+        <v>113.06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.97</v>
+        <v>0.24</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="3">
@@ -1717,32 +1717,32 @@
         <v>129.59</v>
       </c>
       <c r="D3" t="n">
-        <v>135.65</v>
+        <v>134.19</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.06</v>
+        <v>-4.6</v>
       </c>
       <c r="F3" t="n">
         <v>130.95</v>
       </c>
       <c r="G3" t="n">
-        <v>135.43</v>
+        <v>134.12</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.48</v>
+        <v>-3.17</v>
       </c>
       <c r="I3" t="n">
         <v>129.08</v>
       </c>
       <c r="J3" t="n">
-        <v>126.28</v>
+        <v>127.09</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>1.99</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.47</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="4">
@@ -1769,41 +1769,41 @@
         <v>5696.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5805.08</v>
+        <v>5868.87</v>
       </c>
       <c r="E4" t="n">
-        <v>-108.58</v>
+        <v>-172.37</v>
       </c>
       <c r="F4" t="n">
         <v>5696.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5799.25</v>
+        <v>5803.79</v>
       </c>
       <c r="H4" t="n">
-        <v>-102.75</v>
+        <v>-107.29</v>
       </c>
       <c r="I4" t="n">
         <v>5556</v>
       </c>
       <c r="J4" t="n">
-        <v>5554.22</v>
+        <v>5656.56</v>
       </c>
       <c r="K4" t="n">
-        <v>1.78</v>
+        <v>-100.56</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.87</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5">
@@ -1821,28 +1821,28 @@
         <v>1458.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1501.7</v>
+        <v>1498.87</v>
       </c>
       <c r="E5" t="n">
-        <v>-42.9</v>
+        <v>-40.07</v>
       </c>
       <c r="F5" t="n">
         <v>1463</v>
       </c>
       <c r="G5" t="n">
-        <v>1500</v>
+        <v>1492.01</v>
       </c>
       <c r="H5" t="n">
-        <v>-37</v>
+        <v>-29.01</v>
       </c>
       <c r="I5" t="n">
         <v>1443.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1428.3</v>
+        <v>1444.19</v>
       </c>
       <c r="K5" t="n">
-        <v>15.2</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="6">
@@ -1873,28 +1873,28 @@
         <v>366</v>
       </c>
       <c r="D6" t="n">
-        <v>375.2</v>
+        <v>375.63</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>372.3</v>
       </c>
       <c r="G6" t="n">
-        <v>374.81</v>
+        <v>373.29</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.51</v>
+        <v>-0.99</v>
       </c>
       <c r="I6" t="n">
         <v>363.6</v>
       </c>
       <c r="J6" t="n">
-        <v>358.36</v>
+        <v>363.13</v>
       </c>
       <c r="K6" t="n">
-        <v>5.24</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="7">
@@ -1925,28 +1925,28 @@
         <v>12190</v>
       </c>
       <c r="D7" t="n">
-        <v>12447.9</v>
+        <v>12417.77</v>
       </c>
       <c r="E7" t="n">
-        <v>-257.9</v>
+        <v>-227.77</v>
       </c>
       <c r="F7" t="n">
         <v>12239</v>
       </c>
       <c r="G7" t="n">
-        <v>12437.8</v>
+        <v>12368.43</v>
       </c>
       <c r="H7" t="n">
-        <v>-198.8</v>
+        <v>-129.43</v>
       </c>
       <c r="I7" t="n">
         <v>11970</v>
       </c>
       <c r="J7" t="n">
-        <v>12013.53</v>
+        <v>12143.54</v>
       </c>
       <c r="K7" t="n">
-        <v>-43.53</v>
+        <v>-173.54</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="8">
@@ -1977,28 +1977,28 @@
         <v>4645</v>
       </c>
       <c r="D8" t="n">
-        <v>4746.62</v>
+        <v>4736.45</v>
       </c>
       <c r="E8" t="n">
-        <v>-101.62</v>
+        <v>-91.45</v>
       </c>
       <c r="F8" t="n">
         <v>4673.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4742.61</v>
+        <v>4716.81</v>
       </c>
       <c r="H8" t="n">
-        <v>-69.20999999999999</v>
+        <v>-43.41</v>
       </c>
       <c r="I8" t="n">
         <v>4603.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4574.21</v>
+        <v>4624.39</v>
       </c>
       <c r="K8" t="n">
-        <v>29.09</v>
+        <v>-21.09</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="9">
@@ -2029,28 +2029,28 @@
         <v>2760</v>
       </c>
       <c r="D9" t="n">
-        <v>2842.21</v>
+        <v>2821.25</v>
       </c>
       <c r="E9" t="n">
-        <v>-82.20999999999999</v>
+        <v>-61.25</v>
       </c>
       <c r="F9" t="n">
         <v>2787</v>
       </c>
       <c r="G9" t="n">
-        <v>2839.25</v>
+        <v>2816.47</v>
       </c>
       <c r="H9" t="n">
-        <v>-52.25</v>
+        <v>-29.47</v>
       </c>
       <c r="I9" t="n">
         <v>2748.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2714.84</v>
+        <v>2737.23</v>
       </c>
       <c r="K9" t="n">
-        <v>33.86</v>
+        <v>11.47</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2059,11 +2059,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.89</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
@@ -2081,28 +2081,28 @@
         <v>741.05</v>
       </c>
       <c r="D10" t="n">
-        <v>758.76</v>
+        <v>759.6</v>
       </c>
       <c r="E10" t="n">
-        <v>-17.71</v>
+        <v>-18.55</v>
       </c>
       <c r="F10" t="n">
         <v>752.9</v>
       </c>
       <c r="G10" t="n">
-        <v>758.01</v>
+        <v>755.09</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.11</v>
+        <v>-2.19</v>
       </c>
       <c r="I10" t="n">
         <v>733.95</v>
       </c>
       <c r="J10" t="n">
-        <v>726.58</v>
+        <v>735.79</v>
       </c>
       <c r="K10" t="n">
-        <v>7.37</v>
+        <v>-1.84</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="11">
@@ -2133,28 +2133,28 @@
         <v>1192</v>
       </c>
       <c r="D11" t="n">
-        <v>1237.38</v>
+        <v>1229.59</v>
       </c>
       <c r="E11" t="n">
-        <v>-45.38</v>
+        <v>-37.59</v>
       </c>
       <c r="F11" t="n">
         <v>1194.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1235.68</v>
+        <v>1226.52</v>
       </c>
       <c r="H11" t="n">
-        <v>-40.98</v>
+        <v>-31.82</v>
       </c>
       <c r="I11" t="n">
         <v>1163.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1164.4</v>
+        <v>1174.45</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1</v>
+        <v>-11.15</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.67</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="12">
@@ -2185,41 +2185,41 @@
         <v>603</v>
       </c>
       <c r="D12" t="n">
-        <v>641</v>
+        <v>617.36</v>
       </c>
       <c r="E12" t="n">
-        <v>-38</v>
+        <v>-14.36</v>
       </c>
       <c r="F12" t="n">
         <v>632.5</v>
       </c>
       <c r="G12" t="n">
-        <v>639.9299999999999</v>
+        <v>625.47</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.43</v>
+        <v>7.03</v>
       </c>
       <c r="I12" t="n">
         <v>602.6</v>
       </c>
       <c r="J12" t="n">
-        <v>594.87</v>
+        <v>590.3</v>
       </c>
       <c r="K12" t="n">
-        <v>7.73</v>
+        <v>12.3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.93</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="13">
@@ -2237,28 +2237,28 @@
         <v>7986.5</v>
       </c>
       <c r="D13" t="n">
-        <v>8232.610000000001</v>
+        <v>8118.77</v>
       </c>
       <c r="E13" t="n">
-        <v>-246.11</v>
+        <v>-132.27</v>
       </c>
       <c r="F13" t="n">
         <v>8019</v>
       </c>
       <c r="G13" t="n">
-        <v>8224.77</v>
+        <v>8132.49</v>
       </c>
       <c r="H13" t="n">
-        <v>-205.77</v>
+        <v>-113.49</v>
       </c>
       <c r="I13" t="n">
         <v>7905.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7895.47</v>
+        <v>7933.88</v>
       </c>
       <c r="K13" t="n">
-        <v>10.03</v>
+        <v>-28.38</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2267,11 +2267,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.99</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="14">
@@ -2289,28 +2289,28 @@
         <v>2099</v>
       </c>
       <c r="D14" t="n">
-        <v>2213.9</v>
+        <v>2150.77</v>
       </c>
       <c r="E14" t="n">
-        <v>-114.9</v>
+        <v>-51.77</v>
       </c>
       <c r="F14" t="n">
         <v>2143.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2210.48</v>
+        <v>2169.69</v>
       </c>
       <c r="H14" t="n">
-        <v>-66.58</v>
+        <v>-25.79</v>
       </c>
       <c r="I14" t="n">
         <v>2055.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2066.91</v>
+        <v>2060.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.21</v>
+        <v>-4.83</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2319,11 +2319,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.19</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="15">
@@ -2341,28 +2341,28 @@
         <v>1650</v>
       </c>
       <c r="D15" t="n">
-        <v>1723.27</v>
+        <v>1684.47</v>
       </c>
       <c r="E15" t="n">
-        <v>-73.27</v>
+        <v>-34.47</v>
       </c>
       <c r="F15" t="n">
         <v>1664.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1720.99</v>
+        <v>1692.85</v>
       </c>
       <c r="H15" t="n">
-        <v>-56.19</v>
+        <v>-28.05</v>
       </c>
       <c r="I15" t="n">
         <v>1639</v>
       </c>
       <c r="J15" t="n">
-        <v>1625.3</v>
+        <v>1629.46</v>
       </c>
       <c r="K15" t="n">
-        <v>13.7</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.25</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="16">
@@ -2393,28 +2393,28 @@
         <v>310.35</v>
       </c>
       <c r="D16" t="n">
-        <v>325.32</v>
+        <v>320.66</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.97</v>
+        <v>-10.31</v>
       </c>
       <c r="F16" t="n">
         <v>314.65</v>
       </c>
       <c r="G16" t="n">
-        <v>324.8</v>
+        <v>321.09</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.15</v>
+        <v>-6.44</v>
       </c>
       <c r="I16" t="n">
         <v>309.5</v>
       </c>
       <c r="J16" t="n">
-        <v>303.06</v>
+        <v>304.44</v>
       </c>
       <c r="K16" t="n">
-        <v>6.44</v>
+        <v>5.06</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="17">
@@ -2445,28 +2445,28 @@
         <v>14310</v>
       </c>
       <c r="D17" t="n">
-        <v>14982.51</v>
+        <v>14784.44</v>
       </c>
       <c r="E17" t="n">
-        <v>-672.51</v>
+        <v>-474.44</v>
       </c>
       <c r="F17" t="n">
         <v>14395</v>
       </c>
       <c r="G17" t="n">
-        <v>14959.04</v>
+        <v>14795.97</v>
       </c>
       <c r="H17" t="n">
-        <v>-564.04</v>
+        <v>-400.97</v>
       </c>
       <c r="I17" t="n">
         <v>14023</v>
       </c>
       <c r="J17" t="n">
-        <v>13973.09</v>
+        <v>14044.68</v>
       </c>
       <c r="K17" t="n">
-        <v>49.91</v>
+        <v>-21.68</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.49</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="18">
@@ -2497,28 +2497,28 @@
         <v>1777</v>
       </c>
       <c r="D18" t="n">
-        <v>1859.55</v>
+        <v>1825.11</v>
       </c>
       <c r="E18" t="n">
-        <v>-82.55</v>
+        <v>-48.11</v>
       </c>
       <c r="F18" t="n">
         <v>1788</v>
       </c>
       <c r="G18" t="n">
-        <v>1856.64</v>
+        <v>1837.21</v>
       </c>
       <c r="H18" t="n">
-        <v>-68.64</v>
+        <v>-49.21</v>
       </c>
       <c r="I18" t="n">
         <v>1745.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1734.44</v>
+        <v>1744.15</v>
       </c>
       <c r="K18" t="n">
-        <v>10.66</v>
+        <v>0.95</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.44</v>
+        <v>2.64</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,6 +1372,1254 @@
       </c>
       <c r="N18" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5598.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5680.14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.64</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5695.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5680.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5586</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5543.73</v>
+      </c>
+      <c r="K19" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4934</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4749.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>184.53</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4749.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>200.53</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4685.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4635.08</v>
+      </c>
+      <c r="K20" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>128</v>
+      </c>
+      <c r="D21" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>130.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>127.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>124.36</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5486.56</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-12.56</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5572</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5486.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5465</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5334.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="D23" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="F23" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>113.07</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3414</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3436.39</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-22.39</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3449</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3436.39</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3410</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3348.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F25" t="n">
+        <v>522</v>
+      </c>
+      <c r="G25" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="I25" t="n">
+        <v>510</v>
+      </c>
+      <c r="J25" t="n">
+        <v>500.09</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F26" t="n">
+        <v>367</v>
+      </c>
+      <c r="G26" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I26" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12099</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12088.83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12204</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12195.97</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11999.72</v>
+      </c>
+      <c r="K27" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1474</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1486.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1488.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1486.61</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1446.53</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2731.16</v>
+      </c>
+      <c r="E29" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2763.74</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2718.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>733.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>732.24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F30" t="n">
+        <v>743.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>732.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>732</v>
+      </c>
+      <c r="J30" t="n">
+        <v>722.0700000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1232.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1216.11</v>
+      </c>
+      <c r="E31" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1257</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1216.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1199.92</v>
+      </c>
+      <c r="K31" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>799.45</v>
+      </c>
+      <c r="D32" t="n">
+        <v>800.16</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F32" t="n">
+        <v>814.55</v>
+      </c>
+      <c r="G32" t="n">
+        <v>812.45</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>798.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>799.45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1187.15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1187.15</v>
+      </c>
+      <c r="H33" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1160.63</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5330</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5326.11</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5424</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5414.12</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5315</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5328.45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-13.45</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2084.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2111.77</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2103</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2111.77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2068.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2062.42</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>609</v>
+      </c>
+      <c r="D36" t="n">
+        <v>605.35</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F36" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>605.35</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I36" t="n">
+        <v>597</v>
+      </c>
+      <c r="J36" t="n">
+        <v>593.99</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7935</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7824.85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8081.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7896.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7935</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2095</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2059.92</v>
+      </c>
+      <c r="E38" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2059.92</v>
+      </c>
+      <c r="H38" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2072.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2025.82</v>
+      </c>
+      <c r="K38" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1606.52</v>
+      </c>
+      <c r="E39" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1670</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1662.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1631</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1635</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13967.07</v>
+      </c>
+      <c r="E40" t="n">
+        <v>232.93</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14445</v>
+      </c>
+      <c r="G40" t="n">
+        <v>14320.44</v>
+      </c>
+      <c r="H40" t="n">
+        <v>124.56</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14137</v>
+      </c>
+      <c r="J40" t="n">
+        <v>14090.25</v>
+      </c>
+      <c r="K40" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>317.34</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F41" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="I41" t="n">
+        <v>310</v>
+      </c>
+      <c r="J41" t="n">
+        <v>316.14</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1750.26</v>
+      </c>
+      <c r="E42" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1813.9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1801.51</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1772.85</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
@@ -1385,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,6 +2810,110 @@
       </c>
       <c r="N3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24627.95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24629.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24677.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24669.59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24604.15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24596.69</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>58007.95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>58020.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-12.65</v>
+      </c>
+      <c r="F5" t="n">
+        <v>58076.85</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58160.06</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-83.20999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>57714.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>57797.91</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-83.20999999999999</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -1575,7 +2927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2534,6 +3886,1254 @@
         <v>2.64</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ALKEM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5598.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5811.79</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-213.29</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5695.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5837.57</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-142.07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5586</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5600.34</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-14.34</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4934</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4827.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4816.52</v>
+      </c>
+      <c r="H20" t="n">
+        <v>133.48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4685.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4674.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IEX (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>128</v>
+      </c>
+      <c r="D21" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>130.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>131.92</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>127.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>125.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5678.92</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-204.92</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5572</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5647.99</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-75.98999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5465</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5382.19</v>
+      </c>
+      <c r="K22" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="D23" t="n">
+        <v>116.74</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>116.08</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="I23" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>114.04</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3414</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3526.98</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-112.98</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3449</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3494.05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-45.05</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3410</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3378.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>525.8200000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-14.32</v>
+      </c>
+      <c r="F25" t="n">
+        <v>522</v>
+      </c>
+      <c r="G25" t="n">
+        <v>524.05</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="I25" t="n">
+        <v>510</v>
+      </c>
+      <c r="J25" t="n">
+        <v>505.75</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RECLTD (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="F26" t="n">
+        <v>367</v>
+      </c>
+      <c r="G26" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>360.68</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12099</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12290.28</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-191.28</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12204</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12270.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-66.25</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>12059.11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-48.11</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1474</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1522.37</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-48.37</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1488.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1505.31</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-17.21</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1461.16</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2755</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2791.35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2808.18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-20.18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2735.07</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INDHOTEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>733.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>747.74</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="F30" t="n">
+        <v>743.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>747.45</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="I30" t="n">
+        <v>732</v>
+      </c>
+      <c r="J30" t="n">
+        <v>729.0700000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1232.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1254.29</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-22.19</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1257</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1266.93</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-9.93</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1214.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAMS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>799.45</v>
+      </c>
+      <c r="D32" t="n">
+        <v>823.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-23.95</v>
+      </c>
+      <c r="F32" t="n">
+        <v>814.55</v>
+      </c>
+      <c r="G32" t="n">
+        <v>820.25</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>798.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>789.55</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1223.58</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-37.58</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1218.74</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-21.74</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1169.9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>11</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5330</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5475.84</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-145.84</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5424</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5463.93</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-39.93</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5315</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5267.72</v>
+      </c>
+      <c r="K34" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2084.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2160.62</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-76.12</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2103</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2126.93</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-23.93</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2068.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2067.75</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>609</v>
+      </c>
+      <c r="D36" t="n">
+        <v>628.78</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-19.78</v>
+      </c>
+      <c r="F36" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>630.48</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-14.28</v>
+      </c>
+      <c r="I36" t="n">
+        <v>597</v>
+      </c>
+      <c r="J36" t="n">
+        <v>597.17</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7935</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7979.16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-44.16</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8073.04</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-29.04</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7896.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7889.17</v>
+      </c>
+      <c r="K37" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GODREJPROP (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2095</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2139.15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-44.15</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2168.43</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-59.43</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2072.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2054.64</v>
+      </c>
+      <c r="K38" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1650.09</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-15.09</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1670</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1674.53</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1631</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1617.08</v>
+      </c>
+      <c r="K39" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14418.18</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-218.18</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14445</v>
+      </c>
+      <c r="G40" t="n">
+        <v>14613.75</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-168.75</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14137</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13990.58</v>
+      </c>
+      <c r="K40" t="n">
+        <v>146.42</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="F41" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>326.02</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="I41" t="n">
+        <v>310</v>
+      </c>
+      <c r="J41" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1814.05</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-36.05</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1813.9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1836.87</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-22.97</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1746.38</v>
+      </c>
+      <c r="K42" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>128</v>
+        <v>5459.5</v>
       </c>
       <c r="D21" t="n">
-        <v>126.34</v>
+        <v>5490.58</v>
       </c>
       <c r="E21" t="n">
-        <v>1.66</v>
+        <v>-31.08</v>
       </c>
       <c r="F21" t="n">
-        <v>130.32</v>
+        <v>5572</v>
       </c>
       <c r="G21" t="n">
-        <v>126.34</v>
+        <v>5490.58</v>
       </c>
       <c r="H21" t="n">
-        <v>3.98</v>
+        <v>81.42</v>
       </c>
       <c r="I21" t="n">
-        <v>127.74</v>
+        <v>5459.5</v>
       </c>
       <c r="J21" t="n">
-        <v>124.36</v>
+        <v>5302.29</v>
       </c>
       <c r="K21" t="n">
-        <v>3.38</v>
+        <v>157.21</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22">
@@ -1538,39 +1538,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5474</v>
+        <v>128.83</v>
       </c>
       <c r="D22" t="n">
-        <v>5486.56</v>
+        <v>131.57</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.56</v>
+        <v>-2.74</v>
       </c>
       <c r="F22" t="n">
-        <v>5572</v>
+        <v>130.32</v>
       </c>
       <c r="G22" t="n">
-        <v>5486.56</v>
+        <v>131.57</v>
       </c>
       <c r="H22" t="n">
-        <v>85.44</v>
+        <v>-1.25</v>
       </c>
       <c r="I22" t="n">
-        <v>5465</v>
+        <v>127.74</v>
       </c>
       <c r="J22" t="n">
-        <v>5334.6</v>
+        <v>124.83</v>
       </c>
       <c r="K22" t="n">
-        <v>130.4</v>
+        <v>2.91</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.23</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="23">
@@ -1594,31 +1594,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>114.44</v>
+        <v>114.3</v>
       </c>
       <c r="D23" t="n">
-        <v>114.81</v>
+        <v>114.84</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.37</v>
+        <v>-0.54</v>
       </c>
       <c r="F23" t="n">
         <v>114.85</v>
       </c>
       <c r="G23" t="n">
-        <v>114.81</v>
+        <v>114.84</v>
       </c>
       <c r="H23" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I23" t="n">
         <v>113.2</v>
       </c>
       <c r="J23" t="n">
-        <v>113.07</v>
+        <v>112.6</v>
       </c>
       <c r="K23" t="n">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="24">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3414</v>
+        <v>3406</v>
       </c>
       <c r="D24" t="n">
-        <v>3436.39</v>
+        <v>3410.87</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.39</v>
+        <v>-4.87</v>
       </c>
       <c r="F24" t="n">
         <v>3449</v>
       </c>
       <c r="G24" t="n">
-        <v>3436.39</v>
+        <v>3416.49</v>
       </c>
       <c r="H24" t="n">
-        <v>12.61</v>
+        <v>32.51</v>
       </c>
       <c r="I24" t="n">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="J24" t="n">
-        <v>3348.98</v>
+        <v>3329.27</v>
       </c>
       <c r="K24" t="n">
-        <v>61.02</v>
+        <v>76.73</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.65</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="25">
@@ -1698,31 +1698,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>511.5</v>
+        <v>512</v>
       </c>
       <c r="D25" t="n">
-        <v>511.75</v>
+        <v>515.85</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.25</v>
+        <v>-3.85</v>
       </c>
       <c r="F25" t="n">
         <v>522</v>
       </c>
       <c r="G25" t="n">
-        <v>511.75</v>
+        <v>515.85</v>
       </c>
       <c r="H25" t="n">
-        <v>10.25</v>
+        <v>6.15</v>
       </c>
       <c r="I25" t="n">
         <v>510</v>
       </c>
       <c r="J25" t="n">
-        <v>500.09</v>
+        <v>499.14</v>
       </c>
       <c r="K25" t="n">
-        <v>9.91</v>
+        <v>10.86</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="26">
@@ -1750,31 +1750,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>363.3</v>
+        <v>361.5</v>
       </c>
       <c r="D26" t="n">
-        <v>363.46</v>
+        <v>364.23</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.16</v>
+        <v>-2.73</v>
       </c>
       <c r="F26" t="n">
         <v>367</v>
       </c>
       <c r="G26" t="n">
-        <v>363.46</v>
+        <v>364.23</v>
       </c>
       <c r="H26" t="n">
-        <v>3.54</v>
+        <v>2.77</v>
       </c>
       <c r="I26" t="n">
-        <v>361.6</v>
+        <v>361.5</v>
       </c>
       <c r="J26" t="n">
-        <v>357.14</v>
+        <v>354.29</v>
       </c>
       <c r="K26" t="n">
-        <v>4.46</v>
+        <v>7.21</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.04</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12099</v>
+        <v>12075</v>
       </c>
       <c r="D27" t="n">
-        <v>12088.83</v>
+        <v>12181.82</v>
       </c>
       <c r="E27" t="n">
-        <v>10.17</v>
+        <v>-106.82</v>
       </c>
       <c r="F27" t="n">
         <v>12204</v>
       </c>
       <c r="G27" t="n">
-        <v>12195.97</v>
+        <v>12246.74</v>
       </c>
       <c r="H27" t="n">
-        <v>8.029999999999999</v>
+        <v>-42.74</v>
       </c>
       <c r="I27" t="n">
         <v>12011</v>
       </c>
       <c r="J27" t="n">
-        <v>11999.72</v>
+        <v>11938.81</v>
       </c>
       <c r="K27" t="n">
-        <v>11.28</v>
+        <v>72.19</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.08</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="28">
@@ -1854,31 +1854,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="D28" t="n">
-        <v>1486.61</v>
+        <v>1476.19</v>
       </c>
       <c r="E28" t="n">
-        <v>-12.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F28" t="n">
         <v>1488.1</v>
       </c>
       <c r="G28" t="n">
-        <v>1486.61</v>
+        <v>1483.21</v>
       </c>
       <c r="H28" t="n">
-        <v>1.49</v>
+        <v>4.89</v>
       </c>
       <c r="I28" t="n">
         <v>1461</v>
       </c>
       <c r="J28" t="n">
-        <v>1446.53</v>
+        <v>1445.41</v>
       </c>
       <c r="K28" t="n">
-        <v>14.47</v>
+        <v>15.59</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29">
@@ -1909,28 +1909,28 @@
         <v>2755</v>
       </c>
       <c r="D29" t="n">
-        <v>2731.16</v>
+        <v>2801.28</v>
       </c>
       <c r="E29" t="n">
-        <v>23.84</v>
+        <v>-46.28</v>
       </c>
       <c r="F29" t="n">
         <v>2788</v>
       </c>
       <c r="G29" t="n">
-        <v>2763.74</v>
+        <v>2801.28</v>
       </c>
       <c r="H29" t="n">
-        <v>24.26</v>
+        <v>-13.28</v>
       </c>
       <c r="I29" t="n">
         <v>2741.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2718.8</v>
+        <v>2710.9</v>
       </c>
       <c r="K29" t="n">
-        <v>22.8</v>
+        <v>30.7</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.87</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="30">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>733.9</v>
+        <v>736</v>
       </c>
       <c r="D30" t="n">
-        <v>732.24</v>
+        <v>743.5700000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.66</v>
+        <v>-7.57</v>
       </c>
       <c r="F30" t="n">
         <v>743.8</v>
       </c>
       <c r="G30" t="n">
-        <v>732.9</v>
+        <v>743.5700000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>10.9</v>
+        <v>0.23</v>
       </c>
       <c r="I30" t="n">
         <v>732</v>
       </c>
       <c r="J30" t="n">
-        <v>722.0700000000001</v>
+        <v>722.08</v>
       </c>
       <c r="K30" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.23</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="31">
@@ -2006,35 +2006,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1232.1</v>
+        <v>799.45</v>
       </c>
       <c r="D31" t="n">
-        <v>1216.11</v>
+        <v>805.13</v>
       </c>
       <c r="E31" t="n">
-        <v>15.99</v>
+        <v>-5.68</v>
       </c>
       <c r="F31" t="n">
-        <v>1257</v>
+        <v>814.55</v>
       </c>
       <c r="G31" t="n">
-        <v>1216.32</v>
+        <v>817.6</v>
       </c>
       <c r="H31" t="n">
-        <v>40.68</v>
+        <v>-3.05</v>
       </c>
       <c r="I31" t="n">
-        <v>1229.5</v>
+        <v>798.25</v>
       </c>
       <c r="J31" t="n">
-        <v>1199.92</v>
+        <v>797.28</v>
       </c>
       <c r="K31" t="n">
-        <v>29.58</v>
+        <v>0.97</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="32">
@@ -2058,35 +2058,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>799.45</v>
+        <v>1186</v>
       </c>
       <c r="D32" t="n">
-        <v>800.16</v>
+        <v>1194.33</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.71</v>
+        <v>-8.33</v>
       </c>
       <c r="F32" t="n">
-        <v>814.55</v>
+        <v>1197</v>
       </c>
       <c r="G32" t="n">
-        <v>812.45</v>
+        <v>1194.33</v>
       </c>
       <c r="H32" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="I32" t="n">
-        <v>798.25</v>
+        <v>1180.9</v>
       </c>
       <c r="J32" t="n">
-        <v>799.45</v>
+        <v>1157.27</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.2</v>
+        <v>23.63</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -2110,35 +2110,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1186</v>
+        <v>5318.5</v>
       </c>
       <c r="D33" t="n">
-        <v>1187.15</v>
+        <v>5364.96</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.15</v>
+        <v>-46.46</v>
       </c>
       <c r="F33" t="n">
-        <v>1197</v>
+        <v>5424</v>
       </c>
       <c r="G33" t="n">
-        <v>1187.15</v>
+        <v>5434.76</v>
       </c>
       <c r="H33" t="n">
-        <v>9.85</v>
+        <v>-10.76</v>
       </c>
       <c r="I33" t="n">
-        <v>1180.9</v>
+        <v>5315</v>
       </c>
       <c r="J33" t="n">
-        <v>1160.63</v>
+        <v>5299.51</v>
       </c>
       <c r="K33" t="n">
-        <v>20.27</v>
+        <v>15.49</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.1</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="34">
@@ -2162,35 +2162,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5330</v>
+        <v>1240</v>
       </c>
       <c r="D34" t="n">
-        <v>5326.11</v>
+        <v>1266.36</v>
       </c>
       <c r="E34" t="n">
-        <v>3.89</v>
+        <v>-26.36</v>
       </c>
       <c r="F34" t="n">
-        <v>5424</v>
+        <v>1257</v>
       </c>
       <c r="G34" t="n">
-        <v>5414.12</v>
+        <v>1266.36</v>
       </c>
       <c r="H34" t="n">
-        <v>9.880000000000001</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>5315</v>
+        <v>1229.5</v>
       </c>
       <c r="J34" t="n">
-        <v>5328.45</v>
+        <v>1204.38</v>
       </c>
       <c r="K34" t="n">
-        <v>-13.45</v>
+        <v>25.12</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="35">
@@ -2218,31 +2218,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2084.5</v>
+        <v>2086</v>
       </c>
       <c r="D35" t="n">
-        <v>2111.77</v>
+        <v>2075.54</v>
       </c>
       <c r="E35" t="n">
-        <v>-27.27</v>
+        <v>10.46</v>
       </c>
       <c r="F35" t="n">
         <v>2103</v>
       </c>
       <c r="G35" t="n">
-        <v>2111.77</v>
+        <v>2111.58</v>
       </c>
       <c r="H35" t="n">
-        <v>-8.77</v>
+        <v>-8.58</v>
       </c>
       <c r="I35" t="n">
         <v>2068.6</v>
       </c>
       <c r="J35" t="n">
-        <v>2062.42</v>
+        <v>2058.35</v>
       </c>
       <c r="K35" t="n">
-        <v>6.18</v>
+        <v>10.25</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -2270,31 +2270,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>609</v>
+        <v>609.75</v>
       </c>
       <c r="D36" t="n">
-        <v>605.35</v>
+        <v>617.3200000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>3.65</v>
+        <v>-7.57</v>
       </c>
       <c r="F36" t="n">
         <v>616.2</v>
       </c>
       <c r="G36" t="n">
-        <v>605.35</v>
+        <v>617.3200000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>10.85</v>
+        <v>-1.12</v>
       </c>
       <c r="I36" t="n">
         <v>597</v>
       </c>
       <c r="J36" t="n">
-        <v>593.99</v>
+        <v>591.96</v>
       </c>
       <c r="K36" t="n">
-        <v>3.01</v>
+        <v>5.04</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.6</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="37">
@@ -2322,31 +2322,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7935</v>
+        <v>7967.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7824.85</v>
+        <v>8149.04</v>
       </c>
       <c r="E37" t="n">
-        <v>110.15</v>
+        <v>-181.54</v>
       </c>
       <c r="F37" t="n">
         <v>8044</v>
       </c>
       <c r="G37" t="n">
-        <v>8081.8</v>
+        <v>8168.44</v>
       </c>
       <c r="H37" t="n">
-        <v>-37.8</v>
+        <v>-124.44</v>
       </c>
       <c r="I37" t="n">
         <v>7896.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7935</v>
+        <v>7966.09</v>
       </c>
       <c r="K37" t="n">
-        <v>-38.5</v>
+        <v>-69.59</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="38">
@@ -2374,31 +2374,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2095</v>
+        <v>2081.9</v>
       </c>
       <c r="D38" t="n">
-        <v>2059.92</v>
+        <v>2134.3</v>
       </c>
       <c r="E38" t="n">
-        <v>35.08</v>
+        <v>-52.4</v>
       </c>
       <c r="F38" t="n">
         <v>2109</v>
       </c>
       <c r="G38" t="n">
-        <v>2059.92</v>
+        <v>2134.3</v>
       </c>
       <c r="H38" t="n">
-        <v>49.08</v>
+        <v>-25.3</v>
       </c>
       <c r="I38" t="n">
         <v>2072.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2025.82</v>
+        <v>2006.73</v>
       </c>
       <c r="K38" t="n">
-        <v>46.38</v>
+        <v>65.47</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.7</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="39">
@@ -2426,31 +2426,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1635</v>
+        <v>1632.2</v>
       </c>
       <c r="D39" t="n">
-        <v>1606.52</v>
+        <v>1674.43</v>
       </c>
       <c r="E39" t="n">
-        <v>28.48</v>
+        <v>-42.23</v>
       </c>
       <c r="F39" t="n">
         <v>1670</v>
       </c>
       <c r="G39" t="n">
-        <v>1662.3</v>
+        <v>1674.43</v>
       </c>
       <c r="H39" t="n">
-        <v>7.7</v>
+        <v>-4.43</v>
       </c>
       <c r="I39" t="n">
         <v>1631</v>
       </c>
       <c r="J39" t="n">
-        <v>1635</v>
+        <v>1627.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-4</v>
+        <v>3.16</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.77</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="40">
@@ -2481,28 +2481,28 @@
         <v>14200</v>
       </c>
       <c r="D40" t="n">
-        <v>13967.07</v>
+        <v>14552.35</v>
       </c>
       <c r="E40" t="n">
-        <v>232.93</v>
+        <v>-352.35</v>
       </c>
       <c r="F40" t="n">
         <v>14445</v>
       </c>
       <c r="G40" t="n">
-        <v>14320.44</v>
+        <v>14552.35</v>
       </c>
       <c r="H40" t="n">
-        <v>124.56</v>
+        <v>-107.35</v>
       </c>
       <c r="I40" t="n">
         <v>14137</v>
       </c>
       <c r="J40" t="n">
-        <v>14090.25</v>
+        <v>14049.2</v>
       </c>
       <c r="K40" t="n">
-        <v>46.75</v>
+        <v>87.8</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="41">
@@ -2530,31 +2530,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>316.5</v>
+        <v>316.25</v>
       </c>
       <c r="D41" t="n">
-        <v>317.34</v>
+        <v>317.64</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.84</v>
+        <v>-1.39</v>
       </c>
       <c r="F41" t="n">
         <v>319.7</v>
       </c>
       <c r="G41" t="n">
-        <v>321.23</v>
+        <v>322.58</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.53</v>
+        <v>-2.88</v>
       </c>
       <c r="I41" t="n">
         <v>310</v>
       </c>
       <c r="J41" t="n">
-        <v>316.14</v>
+        <v>314.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.14</v>
+        <v>-4.55</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="42">
@@ -2582,35 +2582,35 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1778</v>
+        <v>1772.8</v>
       </c>
       <c r="D42" t="n">
-        <v>1750.26</v>
+        <v>1815.3</v>
       </c>
       <c r="E42" t="n">
-        <v>27.74</v>
+        <v>-42.5</v>
       </c>
       <c r="F42" t="n">
         <v>1813.9</v>
       </c>
       <c r="G42" t="n">
-        <v>1801.51</v>
+        <v>1815.3</v>
       </c>
       <c r="H42" t="n">
-        <v>12.39</v>
+        <v>-1.4</v>
       </c>
       <c r="I42" t="n">
         <v>1757.9</v>
       </c>
       <c r="J42" t="n">
-        <v>1772.85</v>
+        <v>1760.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-14.95</v>
+        <v>-2.74</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.58</v>
+        <v>2.34</v>
       </c>
     </row>
   </sheetData>
@@ -2824,31 +2824,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24627.95</v>
+        <v>24636</v>
       </c>
       <c r="D4" t="n">
-        <v>24629.4</v>
+        <v>24636</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>24677.05</v>
       </c>
       <c r="G4" t="n">
-        <v>24669.59</v>
+        <v>24673.99</v>
       </c>
       <c r="H4" t="n">
-        <v>7.46</v>
+        <v>3.06</v>
       </c>
       <c r="I4" t="n">
         <v>24604.15</v>
       </c>
       <c r="J4" t="n">
-        <v>24596.69</v>
+        <v>24601.09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.46</v>
+        <v>3.06</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2876,31 +2876,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>58007.95</v>
+        <v>58063.65</v>
       </c>
       <c r="D5" t="n">
-        <v>58020.6</v>
+        <v>58063.65</v>
       </c>
       <c r="E5" t="n">
-        <v>-12.65</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>58076.85</v>
       </c>
       <c r="G5" t="n">
-        <v>58160.06</v>
+        <v>58188.76</v>
       </c>
       <c r="H5" t="n">
-        <v>-83.20999999999999</v>
+        <v>-111.91</v>
       </c>
       <c r="I5" t="n">
         <v>57714.7</v>
       </c>
       <c r="J5" t="n">
-        <v>57797.91</v>
+        <v>57826.61</v>
       </c>
       <c r="K5" t="n">
-        <v>-83.20999999999999</v>
+        <v>-111.91</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3998,48 +3998,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IEX (AUG-2026 FUT)</t>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>128</v>
+        <v>5459.5</v>
       </c>
       <c r="D21" t="n">
-        <v>130.6</v>
+        <v>5683.65</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6</v>
+        <v>-224.15</v>
       </c>
       <c r="F21" t="n">
-        <v>130.32</v>
+        <v>5572</v>
       </c>
       <c r="G21" t="n">
-        <v>131.92</v>
+        <v>5669.3</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6</v>
+        <v>-97.3</v>
       </c>
       <c r="I21" t="n">
-        <v>127.74</v>
+        <v>5459.5</v>
       </c>
       <c r="J21" t="n">
-        <v>125.98</v>
+        <v>5351.87</v>
       </c>
       <c r="K21" t="n">
-        <v>1.76</v>
+        <v>107.63</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.99</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="22">
@@ -4050,39 +4050,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PERSISTENT (AUG-2026 FUT)</t>
+          <t>IEX (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5474</v>
+        <v>128.83</v>
       </c>
       <c r="D22" t="n">
-        <v>5678.92</v>
+        <v>135.98</v>
       </c>
       <c r="E22" t="n">
-        <v>-204.92</v>
+        <v>-7.15</v>
       </c>
       <c r="F22" t="n">
-        <v>5572</v>
+        <v>130.32</v>
       </c>
       <c r="G22" t="n">
-        <v>5647.99</v>
+        <v>133.58</v>
       </c>
       <c r="H22" t="n">
-        <v>-75.98999999999999</v>
+        <v>-3.26</v>
       </c>
       <c r="I22" t="n">
-        <v>5465</v>
+        <v>127.74</v>
       </c>
       <c r="J22" t="n">
-        <v>5382.19</v>
+        <v>126.45</v>
       </c>
       <c r="K22" t="n">
-        <v>82.81</v>
+        <v>1.29</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.61</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="23">
@@ -4106,31 +4106,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>114.44</v>
+        <v>114.3</v>
       </c>
       <c r="D23" t="n">
-        <v>116.74</v>
+        <v>116.78</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3</v>
+        <v>-2.48</v>
       </c>
       <c r="F23" t="n">
         <v>114.85</v>
       </c>
       <c r="G23" t="n">
-        <v>116.08</v>
+        <v>116.68</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.23</v>
+        <v>-1.83</v>
       </c>
       <c r="I23" t="n">
         <v>113.2</v>
       </c>
       <c r="J23" t="n">
-        <v>114.04</v>
+        <v>113.57</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.84</v>
+        <v>-0.37</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="24">
@@ -4158,31 +4158,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3414</v>
+        <v>3406</v>
       </c>
       <c r="D24" t="n">
-        <v>3526.98</v>
+        <v>3501.02</v>
       </c>
       <c r="E24" t="n">
-        <v>-112.98</v>
+        <v>-95.02</v>
       </c>
       <c r="F24" t="n">
         <v>3449</v>
       </c>
       <c r="G24" t="n">
-        <v>3494.05</v>
+        <v>3508.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-45.05</v>
+        <v>-59.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="J24" t="n">
-        <v>3378.5</v>
+        <v>3360.57</v>
       </c>
       <c r="K24" t="n">
-        <v>31.5</v>
+        <v>45.43</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="25">
@@ -4210,31 +4210,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>511.5</v>
+        <v>512</v>
       </c>
       <c r="D25" t="n">
-        <v>525.8200000000001</v>
+        <v>530.01</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.32</v>
+        <v>-18.01</v>
       </c>
       <c r="F25" t="n">
         <v>522</v>
       </c>
       <c r="G25" t="n">
-        <v>524.05</v>
+        <v>527.87</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.05</v>
+        <v>-5.87</v>
       </c>
       <c r="I25" t="n">
         <v>510</v>
       </c>
       <c r="J25" t="n">
-        <v>505.75</v>
+        <v>504.78</v>
       </c>
       <c r="K25" t="n">
-        <v>4.25</v>
+        <v>5.22</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -4243,11 +4243,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="26">
@@ -4262,31 +4262,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>363.3</v>
+        <v>361.5</v>
       </c>
       <c r="D26" t="n">
-        <v>371.45</v>
+        <v>372.3</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.15</v>
+        <v>-10.8</v>
       </c>
       <c r="F26" t="n">
         <v>367</v>
       </c>
       <c r="G26" t="n">
-        <v>370.3</v>
+        <v>370.85</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.3</v>
+        <v>-3.85</v>
       </c>
       <c r="I26" t="n">
-        <v>361.6</v>
+        <v>361.5</v>
       </c>
       <c r="J26" t="n">
-        <v>360.68</v>
+        <v>357.81</v>
       </c>
       <c r="K26" t="n">
-        <v>0.92</v>
+        <v>3.69</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -4295,11 +4295,11 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.19</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -4314,31 +4314,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12099</v>
+        <v>12075</v>
       </c>
       <c r="D27" t="n">
-        <v>12290.28</v>
+        <v>12385.33</v>
       </c>
       <c r="E27" t="n">
-        <v>-191.28</v>
+        <v>-310.33</v>
       </c>
       <c r="F27" t="n">
         <v>12204</v>
       </c>
       <c r="G27" t="n">
-        <v>12270.25</v>
+        <v>12324.05</v>
       </c>
       <c r="H27" t="n">
-        <v>-66.25</v>
+        <v>-120.05</v>
       </c>
       <c r="I27" t="n">
         <v>12011</v>
       </c>
       <c r="J27" t="n">
-        <v>12059.11</v>
+        <v>11999.75</v>
       </c>
       <c r="K27" t="n">
-        <v>-48.11</v>
+        <v>11.25</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -4347,11 +4347,11 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.56</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="28">
@@ -4366,31 +4366,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="D28" t="n">
-        <v>1522.37</v>
+        <v>1511.61</v>
       </c>
       <c r="E28" t="n">
-        <v>-48.37</v>
+        <v>-34.61</v>
       </c>
       <c r="F28" t="n">
         <v>1488.1</v>
       </c>
       <c r="G28" t="n">
-        <v>1505.31</v>
+        <v>1517.85</v>
       </c>
       <c r="H28" t="n">
-        <v>-17.21</v>
+        <v>-29.75</v>
       </c>
       <c r="I28" t="n">
         <v>1461</v>
       </c>
       <c r="J28" t="n">
-        <v>1461.16</v>
+        <v>1459.93</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.16</v>
+        <v>1.07</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -4399,11 +4399,11 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.18</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="29">
@@ -4421,28 +4421,28 @@
         <v>2755</v>
       </c>
       <c r="D29" t="n">
-        <v>2791.35</v>
+        <v>2863.02</v>
       </c>
       <c r="E29" t="n">
-        <v>-36.35</v>
+        <v>-108.02</v>
       </c>
       <c r="F29" t="n">
         <v>2788</v>
       </c>
       <c r="G29" t="n">
-        <v>2808.18</v>
+        <v>2825.99</v>
       </c>
       <c r="H29" t="n">
-        <v>-20.18</v>
+        <v>-37.99</v>
       </c>
       <c r="I29" t="n">
         <v>2741.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2735.07</v>
+        <v>2727.1</v>
       </c>
       <c r="K29" t="n">
-        <v>6.53</v>
+        <v>14.5</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -4451,11 +4451,11 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.3</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="30">
@@ -4470,31 +4470,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>733.9</v>
+        <v>736</v>
       </c>
       <c r="D30" t="n">
-        <v>747.74</v>
+        <v>759.25</v>
       </c>
       <c r="E30" t="n">
-        <v>-13.84</v>
+        <v>-23.25</v>
       </c>
       <c r="F30" t="n">
         <v>743.8</v>
       </c>
       <c r="G30" t="n">
-        <v>747.45</v>
+        <v>754.29</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.65</v>
+        <v>-10.49</v>
       </c>
       <c r="I30" t="n">
         <v>732</v>
       </c>
       <c r="J30" t="n">
-        <v>729.0700000000001</v>
+        <v>729.0599999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4503,11 +4503,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="31">
@@ -4518,35 +4518,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAUKRI (AUG-2026 FUT)</t>
+          <t>CAMS (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1232.1</v>
+        <v>799.45</v>
       </c>
       <c r="D31" t="n">
-        <v>1254.29</v>
+        <v>828.51</v>
       </c>
       <c r="E31" t="n">
-        <v>-22.19</v>
+        <v>-29.06</v>
       </c>
       <c r="F31" t="n">
-        <v>1257</v>
+        <v>814.55</v>
       </c>
       <c r="G31" t="n">
-        <v>1266.93</v>
+        <v>825.45</v>
       </c>
       <c r="H31" t="n">
-        <v>-9.93</v>
+        <v>-10.9</v>
       </c>
       <c r="I31" t="n">
-        <v>1229.5</v>
+        <v>798.25</v>
       </c>
       <c r="J31" t="n">
-        <v>1214.75</v>
+        <v>787.25</v>
       </c>
       <c r="K31" t="n">
-        <v>14.75</v>
+        <v>11</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4555,11 +4555,11 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.77</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="32">
@@ -4570,35 +4570,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAMS (AUG-2026 FUT)</t>
+          <t>360ONE (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>799.45</v>
+        <v>1186</v>
       </c>
       <c r="D32" t="n">
-        <v>823.4</v>
+        <v>1230.98</v>
       </c>
       <c r="E32" t="n">
-        <v>-23.95</v>
+        <v>-44.98</v>
       </c>
       <c r="F32" t="n">
-        <v>814.55</v>
+        <v>1197</v>
       </c>
       <c r="G32" t="n">
-        <v>820.25</v>
+        <v>1226.47</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.7</v>
+        <v>-29.47</v>
       </c>
       <c r="I32" t="n">
-        <v>798.25</v>
+        <v>1180.9</v>
       </c>
       <c r="J32" t="n">
-        <v>789.55</v>
+        <v>1166.49</v>
       </c>
       <c r="K32" t="n">
-        <v>8.699999999999999</v>
+        <v>14.41</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="33">
@@ -4622,35 +4622,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>360ONE (AUG-2026 FUT)</t>
+          <t>INDIGO (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1186</v>
+        <v>5318.5</v>
       </c>
       <c r="D33" t="n">
-        <v>1223.58</v>
+        <v>5516.17</v>
       </c>
       <c r="E33" t="n">
-        <v>-37.58</v>
+        <v>-197.67</v>
       </c>
       <c r="F33" t="n">
-        <v>1197</v>
+        <v>5424</v>
       </c>
       <c r="G33" t="n">
-        <v>1218.74</v>
+        <v>5487.08</v>
       </c>
       <c r="H33" t="n">
-        <v>-21.74</v>
+        <v>-63.08</v>
       </c>
       <c r="I33" t="n">
-        <v>1180.9</v>
+        <v>5315</v>
       </c>
       <c r="J33" t="n">
-        <v>1169.9</v>
+        <v>5240.78</v>
       </c>
       <c r="K33" t="n">
-        <v>11</v>
+        <v>74.22</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.07</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="34">
@@ -4674,35 +4674,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INDIGO (AUG-2026 FUT)</t>
+          <t>NAUKRI (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5330</v>
+        <v>1240</v>
       </c>
       <c r="D34" t="n">
-        <v>5475.84</v>
+        <v>1305.82</v>
       </c>
       <c r="E34" t="n">
-        <v>-145.84</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>5424</v>
+        <v>1257</v>
       </c>
       <c r="G34" t="n">
-        <v>5463.93</v>
+        <v>1282.86</v>
       </c>
       <c r="H34" t="n">
-        <v>-39.93</v>
+        <v>-25.86</v>
       </c>
       <c r="I34" t="n">
-        <v>5315</v>
+        <v>1229.5</v>
       </c>
       <c r="J34" t="n">
-        <v>5267.72</v>
+        <v>1219.19</v>
       </c>
       <c r="K34" t="n">
-        <v>47.28</v>
+        <v>10.31</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4711,11 +4711,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.66</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="35">
@@ -4730,31 +4730,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2084.5</v>
+        <v>2086</v>
       </c>
       <c r="D35" t="n">
-        <v>2160.62</v>
+        <v>2123.52</v>
       </c>
       <c r="E35" t="n">
-        <v>-76.12</v>
+        <v>-37.52</v>
       </c>
       <c r="F35" t="n">
         <v>2103</v>
       </c>
       <c r="G35" t="n">
-        <v>2126.93</v>
+        <v>2141.91</v>
       </c>
       <c r="H35" t="n">
-        <v>-23.93</v>
+        <v>-38.91</v>
       </c>
       <c r="I35" t="n">
         <v>2068.6</v>
       </c>
       <c r="J35" t="n">
-        <v>2067.75</v>
+        <v>2063.24</v>
       </c>
       <c r="K35" t="n">
-        <v>0.85</v>
+        <v>5.36</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4763,11 +4763,11 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>3.52</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="36">
@@ -4782,31 +4782,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>609</v>
+        <v>609.75</v>
       </c>
       <c r="D36" t="n">
-        <v>628.78</v>
+        <v>641.22</v>
       </c>
       <c r="E36" t="n">
-        <v>-19.78</v>
+        <v>-31.47</v>
       </c>
       <c r="F36" t="n">
         <v>616.2</v>
       </c>
       <c r="G36" t="n">
-        <v>630.48</v>
+        <v>634.23</v>
       </c>
       <c r="H36" t="n">
-        <v>-14.28</v>
+        <v>-18.03</v>
       </c>
       <c r="I36" t="n">
         <v>597</v>
       </c>
       <c r="J36" t="n">
-        <v>597.17</v>
+        <v>595.17</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.17</v>
+        <v>1.83</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.15</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="37">
@@ -4834,31 +4834,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7935</v>
+        <v>7967.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7979.16</v>
+        <v>8306.77</v>
       </c>
       <c r="E37" t="n">
-        <v>-44.16</v>
+        <v>-339.27</v>
       </c>
       <c r="F37" t="n">
         <v>8044</v>
       </c>
       <c r="G37" t="n">
-        <v>8073.04</v>
+        <v>8156.72</v>
       </c>
       <c r="H37" t="n">
-        <v>-29.04</v>
+        <v>-112.72</v>
       </c>
       <c r="I37" t="n">
         <v>7896.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7889.17</v>
+        <v>7899</v>
       </c>
       <c r="K37" t="n">
-        <v>7.33</v>
+        <v>-2.5</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4867,11 +4867,11 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.55</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="38">
@@ -4886,31 +4886,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2095</v>
+        <v>2081.9</v>
       </c>
       <c r="D38" t="n">
-        <v>2139.15</v>
+        <v>2216.97</v>
       </c>
       <c r="E38" t="n">
-        <v>-44.15</v>
+        <v>-135.07</v>
       </c>
       <c r="F38" t="n">
         <v>2109</v>
       </c>
       <c r="G38" t="n">
-        <v>2168.43</v>
+        <v>2169.08</v>
       </c>
       <c r="H38" t="n">
-        <v>-59.43</v>
+        <v>-60.08</v>
       </c>
       <c r="I38" t="n">
         <v>2072.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2054.64</v>
+        <v>2035.43</v>
       </c>
       <c r="K38" t="n">
-        <v>17.56</v>
+        <v>36.77</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4919,11 +4919,11 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="39">
@@ -4938,44 +4938,44 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1635</v>
+        <v>1632.2</v>
       </c>
       <c r="D39" t="n">
-        <v>1650.09</v>
+        <v>1719.93</v>
       </c>
       <c r="E39" t="n">
-        <v>-15.09</v>
+        <v>-87.73</v>
       </c>
       <c r="F39" t="n">
         <v>1670</v>
       </c>
       <c r="G39" t="n">
-        <v>1674.53</v>
+        <v>1682.35</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.53</v>
+        <v>-12.35</v>
       </c>
       <c r="I39" t="n">
         <v>1631</v>
       </c>
       <c r="J39" t="n">
-        <v>1617.08</v>
+        <v>1609.54</v>
       </c>
       <c r="K39" t="n">
-        <v>13.92</v>
+        <v>21.46</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.91</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="40">
@@ -4993,28 +4993,28 @@
         <v>14200</v>
       </c>
       <c r="D40" t="n">
-        <v>14418.18</v>
+        <v>15022.36</v>
       </c>
       <c r="E40" t="n">
-        <v>-218.18</v>
+        <v>-822.36</v>
       </c>
       <c r="F40" t="n">
         <v>14445</v>
       </c>
       <c r="G40" t="n">
-        <v>14613.75</v>
+        <v>14706.41</v>
       </c>
       <c r="H40" t="n">
-        <v>-168.75</v>
+        <v>-261.41</v>
       </c>
       <c r="I40" t="n">
         <v>14137</v>
       </c>
       <c r="J40" t="n">
-        <v>13990.58</v>
+        <v>13949.83</v>
       </c>
       <c r="K40" t="n">
-        <v>146.42</v>
+        <v>187.17</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5023,11 +5023,11 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.51</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="41">
@@ -5042,31 +5042,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>316.5</v>
+        <v>316.25</v>
       </c>
       <c r="D41" t="n">
-        <v>327.91</v>
+        <v>328.23</v>
       </c>
       <c r="E41" t="n">
-        <v>-11.41</v>
+        <v>-11.98</v>
       </c>
       <c r="F41" t="n">
         <v>319.7</v>
       </c>
       <c r="G41" t="n">
-        <v>326.02</v>
+        <v>327.54</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.32</v>
+        <v>-7.84</v>
       </c>
       <c r="I41" t="n">
         <v>310</v>
       </c>
       <c r="J41" t="n">
-        <v>311.6</v>
+        <v>310.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.6</v>
+        <v>-0.14</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="42">
@@ -5094,44 +5094,44 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1778</v>
+        <v>1772.8</v>
       </c>
       <c r="D42" t="n">
-        <v>1814.05</v>
+        <v>1881.68</v>
       </c>
       <c r="E42" t="n">
-        <v>-36.05</v>
+        <v>-108.88</v>
       </c>
       <c r="F42" t="n">
         <v>1813.9</v>
       </c>
       <c r="G42" t="n">
-        <v>1836.87</v>
+        <v>1843.31</v>
       </c>
       <c r="H42" t="n">
-        <v>-22.97</v>
+        <v>-29.41</v>
       </c>
       <c r="I42" t="n">
         <v>1757.9</v>
       </c>
       <c r="J42" t="n">
-        <v>1746.38</v>
+        <v>1736.04</v>
       </c>
       <c r="K42" t="n">
-        <v>11.52</v>
+        <v>21.86</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.99</v>
+        <v>5.79</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12075</v>
+        <v>12190</v>
       </c>
       <c r="D27" t="n">
         <v>12181.82</v>
       </c>
       <c r="E27" t="n">
-        <v>-106.82</v>
+        <v>8.18</v>
       </c>
       <c r="F27" t="n">
-        <v>12204</v>
+        <v>12239</v>
       </c>
       <c r="G27" t="n">
         <v>12246.74</v>
       </c>
       <c r="H27" t="n">
-        <v>-42.74</v>
+        <v>-7.74</v>
       </c>
       <c r="I27" t="n">
-        <v>12011</v>
+        <v>11970</v>
       </c>
       <c r="J27" t="n">
         <v>11938.81</v>
       </c>
       <c r="K27" t="n">
-        <v>72.19</v>
+        <v>31.19</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.88</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2227,22 +2227,22 @@
         <v>10.46</v>
       </c>
       <c r="F35" t="n">
-        <v>2103</v>
+        <v>2118.5</v>
       </c>
       <c r="G35" t="n">
         <v>2111.58</v>
       </c>
       <c r="H35" t="n">
-        <v>-8.58</v>
+        <v>6.92</v>
       </c>
       <c r="I35" t="n">
-        <v>2068.6</v>
+        <v>2076.1</v>
       </c>
       <c r="J35" t="n">
         <v>2058.35</v>
       </c>
       <c r="K35" t="n">
-        <v>10.25</v>
+        <v>17.75</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2322,31 +2322,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7967.5</v>
+        <v>7986.5</v>
       </c>
       <c r="D37" t="n">
         <v>8149.04</v>
       </c>
       <c r="E37" t="n">
-        <v>-181.54</v>
+        <v>-162.54</v>
       </c>
       <c r="F37" t="n">
-        <v>8044</v>
+        <v>8019</v>
       </c>
       <c r="G37" t="n">
         <v>8168.44</v>
       </c>
       <c r="H37" t="n">
-        <v>-124.44</v>
+        <v>-149.44</v>
       </c>
       <c r="I37" t="n">
-        <v>7896.5</v>
+        <v>7905.5</v>
       </c>
       <c r="J37" t="n">
         <v>7966.09</v>
       </c>
       <c r="K37" t="n">
-        <v>-69.59</v>
+        <v>-60.59</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="38">
@@ -2426,31 +2426,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1632.2</v>
+        <v>1650</v>
       </c>
       <c r="D39" t="n">
         <v>1674.43</v>
       </c>
       <c r="E39" t="n">
-        <v>-42.23</v>
+        <v>-24.43</v>
       </c>
       <c r="F39" t="n">
-        <v>1670</v>
+        <v>1664.8</v>
       </c>
       <c r="G39" t="n">
         <v>1674.43</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.43</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="J39" t="n">
         <v>1627.84</v>
       </c>
       <c r="K39" t="n">
-        <v>3.16</v>
+        <v>11.16</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.52</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="40">
@@ -2478,31 +2478,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14200</v>
+        <v>14310</v>
       </c>
       <c r="D40" t="n">
         <v>14552.35</v>
       </c>
       <c r="E40" t="n">
-        <v>-352.35</v>
+        <v>-242.35</v>
       </c>
       <c r="F40" t="n">
-        <v>14445</v>
+        <v>14395</v>
       </c>
       <c r="G40" t="n">
         <v>14552.35</v>
       </c>
       <c r="H40" t="n">
-        <v>-107.35</v>
+        <v>-157.35</v>
       </c>
       <c r="I40" t="n">
-        <v>14137</v>
+        <v>14023</v>
       </c>
       <c r="J40" t="n">
         <v>14049.2</v>
       </c>
       <c r="K40" t="n">
-        <v>87.8</v>
+        <v>-26.2</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="41">
@@ -2824,31 +2824,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24636</v>
+        <v>24624.65</v>
       </c>
       <c r="D4" t="n">
         <v>24636</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-11.35</v>
       </c>
       <c r="F4" t="n">
-        <v>24677.05</v>
+        <v>24677.6</v>
       </c>
       <c r="G4" t="n">
         <v>24673.99</v>
       </c>
       <c r="H4" t="n">
-        <v>3.06</v>
+        <v>3.61</v>
       </c>
       <c r="I4" t="n">
-        <v>24604.15</v>
+        <v>24497.95</v>
       </c>
       <c r="J4" t="n">
         <v>24601.09</v>
       </c>
       <c r="K4" t="n">
-        <v>3.06</v>
+        <v>-103.14</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
@@ -2876,31 +2876,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>58063.65</v>
+        <v>57739.95</v>
       </c>
       <c r="D5" t="n">
         <v>58063.65</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-323.7</v>
       </c>
       <c r="F5" t="n">
-        <v>58076.85</v>
+        <v>57931.85</v>
       </c>
       <c r="G5" t="n">
         <v>58188.76</v>
       </c>
       <c r="H5" t="n">
-        <v>-111.91</v>
+        <v>-256.91</v>
       </c>
       <c r="I5" t="n">
-        <v>57714.7</v>
+        <v>57456.35</v>
       </c>
       <c r="J5" t="n">
         <v>57826.61</v>
       </c>
       <c r="K5" t="n">
-        <v>-111.91</v>
+        <v>-370.26</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4314,31 +4314,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12075</v>
+        <v>12190</v>
       </c>
       <c r="D27" t="n">
         <v>12385.33</v>
       </c>
       <c r="E27" t="n">
-        <v>-310.33</v>
+        <v>-195.33</v>
       </c>
       <c r="F27" t="n">
-        <v>12204</v>
+        <v>12239</v>
       </c>
       <c r="G27" t="n">
         <v>12324.05</v>
       </c>
       <c r="H27" t="n">
-        <v>-120.05</v>
+        <v>-85.05</v>
       </c>
       <c r="I27" t="n">
-        <v>12011</v>
+        <v>11970</v>
       </c>
       <c r="J27" t="n">
         <v>11999.75</v>
       </c>
       <c r="K27" t="n">
-        <v>11.25</v>
+        <v>-29.75</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -4347,11 +4347,11 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.51</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="28">
@@ -4739,22 +4739,22 @@
         <v>-37.52</v>
       </c>
       <c r="F35" t="n">
-        <v>2103</v>
+        <v>2118.5</v>
       </c>
       <c r="G35" t="n">
         <v>2141.91</v>
       </c>
       <c r="H35" t="n">
-        <v>-38.91</v>
+        <v>-23.41</v>
       </c>
       <c r="I35" t="n">
-        <v>2068.6</v>
+        <v>2076.1</v>
       </c>
       <c r="J35" t="n">
         <v>2063.24</v>
       </c>
       <c r="K35" t="n">
-        <v>5.36</v>
+        <v>12.86</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4834,31 +4834,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7967.5</v>
+        <v>7986.5</v>
       </c>
       <c r="D37" t="n">
         <v>8306.77</v>
       </c>
       <c r="E37" t="n">
-        <v>-339.27</v>
+        <v>-320.27</v>
       </c>
       <c r="F37" t="n">
-        <v>8044</v>
+        <v>8019</v>
       </c>
       <c r="G37" t="n">
         <v>8156.72</v>
       </c>
       <c r="H37" t="n">
-        <v>-112.72</v>
+        <v>-137.72</v>
       </c>
       <c r="I37" t="n">
-        <v>7896.5</v>
+        <v>7905.5</v>
       </c>
       <c r="J37" t="n">
         <v>7899</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.5</v>
+        <v>6.5</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.08</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="38">
@@ -4938,31 +4938,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1632.2</v>
+        <v>1650</v>
       </c>
       <c r="D39" t="n">
         <v>1719.93</v>
       </c>
       <c r="E39" t="n">
-        <v>-87.73</v>
+        <v>-69.93000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1670</v>
+        <v>1664.8</v>
       </c>
       <c r="G39" t="n">
         <v>1682.35</v>
       </c>
       <c r="H39" t="n">
-        <v>-12.35</v>
+        <v>-17.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="J39" t="n">
         <v>1609.54</v>
       </c>
       <c r="K39" t="n">
-        <v>21.46</v>
+        <v>29.46</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="40">
@@ -4990,31 +4990,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14200</v>
+        <v>14310</v>
       </c>
       <c r="D40" t="n">
         <v>15022.36</v>
       </c>
       <c r="E40" t="n">
-        <v>-822.36</v>
+        <v>-712.36</v>
       </c>
       <c r="F40" t="n">
-        <v>14445</v>
+        <v>14395</v>
       </c>
       <c r="G40" t="n">
         <v>14706.41</v>
       </c>
       <c r="H40" t="n">
-        <v>-261.41</v>
+        <v>-311.41</v>
       </c>
       <c r="I40" t="n">
-        <v>14137</v>
+        <v>14023</v>
       </c>
       <c r="J40" t="n">
         <v>13949.83</v>
       </c>
       <c r="K40" t="n">
-        <v>187.17</v>
+        <v>73.17</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.47</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="41">

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2620,6 +2620,1150 @@
       </c>
       <c r="N42" t="n">
         <v>2.34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5475</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5487.56</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-12.56</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5594</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5487.56</v>
+      </c>
+      <c r="H43" t="n">
+        <v>106.44</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5448.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5382.37</v>
+      </c>
+      <c r="K43" t="n">
+        <v>66.13</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>276.72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F44" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>277.41</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="I44" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>275.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5620</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5542.31</v>
+      </c>
+      <c r="E45" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5647.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5631.66</v>
+      </c>
+      <c r="H45" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5506</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5543.83</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-37.83</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="D46" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F46" t="n">
+        <v>115.37</v>
+      </c>
+      <c r="G46" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I46" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>505.2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>505.44</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>513.9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>505.44</v>
+      </c>
+      <c r="H47" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>505.2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>493.14</v>
+      </c>
+      <c r="K47" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>12105</v>
+      </c>
+      <c r="D48" t="n">
+        <v>12210.02</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-105.02</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12105</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12256.51</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-151.51</v>
+      </c>
+      <c r="I48" t="n">
+        <v>11970</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12069.81</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-99.81</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1463.8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1476.32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-12.52</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1476.32</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1462.1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1435.23</v>
+      </c>
+      <c r="K49" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2008.9</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2035.18</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-26.28</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2035.18</v>
+      </c>
+      <c r="H50" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1971.08</v>
+      </c>
+      <c r="K50" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3502</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3524.97</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-22.97</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3504.9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3526.89</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-21.99</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3402.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3472.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-70.40000000000001</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>367</v>
+      </c>
+      <c r="D52" t="n">
+        <v>367.17</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F52" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="G52" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="I52" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2735</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2711.34</v>
+      </c>
+      <c r="E53" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2755</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2748.63</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2695</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2706.05</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>788.2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>801.05</v>
+      </c>
+      <c r="G54" t="n">
+        <v>788.2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="I54" t="n">
+        <v>778.05</v>
+      </c>
+      <c r="J54" t="n">
+        <v>774.46</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1168.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1169.23</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1192.8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1170.66</v>
+      </c>
+      <c r="H55" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1151</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1152.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1225.3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1209.39</v>
+      </c>
+      <c r="E56" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1244</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1222.15</v>
+      </c>
+      <c r="H56" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1222.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1202.88</v>
+      </c>
+      <c r="K56" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5333</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5329.11</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5367.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5348.56</v>
+      </c>
+      <c r="H57" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5281</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5265.31</v>
+      </c>
+      <c r="K57" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2070</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2035.33</v>
+      </c>
+      <c r="E58" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2108.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2035.33</v>
+      </c>
+      <c r="H58" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2062.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2001.43</v>
+      </c>
+      <c r="K58" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8020</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7948.47</v>
+      </c>
+      <c r="E59" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8067.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8169.85</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-102.35</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7920</v>
+      </c>
+      <c r="J59" t="n">
+        <v>8020</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1624.03</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1681.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1653.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1634.3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1628.55</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>630.65</v>
+      </c>
+      <c r="D61" t="n">
+        <v>627.91</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F61" t="n">
+        <v>643.95</v>
+      </c>
+      <c r="G61" t="n">
+        <v>627.91</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="I61" t="n">
+        <v>602.45</v>
+      </c>
+      <c r="J61" t="n">
+        <v>616.61</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-14.16</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>315</v>
+      </c>
+      <c r="D62" t="n">
+        <v>316.13</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="F62" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="I62" t="n">
+        <v>313.15</v>
+      </c>
+      <c r="J62" t="n">
+        <v>314.24</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14075.28</v>
+      </c>
+      <c r="E63" t="n">
+        <v>124.72</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14294</v>
+      </c>
+      <c r="G63" t="n">
+        <v>14183.21</v>
+      </c>
+      <c r="H63" t="n">
+        <v>110.79</v>
+      </c>
+      <c r="I63" t="n">
+        <v>14050</v>
+      </c>
+      <c r="J63" t="n">
+        <v>13960.38</v>
+      </c>
+      <c r="K63" t="n">
+        <v>89.62</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1776</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1748.3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1809</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1781.99</v>
+      </c>
+      <c r="H64" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1765.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1754.28</v>
+      </c>
+      <c r="K64" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
@@ -2633,7 +3777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2914,6 +4058,110 @@
       </c>
       <c r="N5" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24570.65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24570.65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24630.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24626.45</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24522.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24518.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>57746.45</v>
+      </c>
+      <c r="D7" t="n">
+        <v>57746.45</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>57994.45</v>
+      </c>
+      <c r="G7" t="n">
+        <v>57931.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>57686.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>57623.85</v>
+      </c>
+      <c r="K7" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2927,7 +4175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5134,6 +6382,1150 @@
         <v>5.79</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5475</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5677.02</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-202.02</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5594</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5640.02</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-46.02</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5448.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5381.65</v>
+      </c>
+      <c r="K43" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>283.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="F44" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>285.89</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="I44" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>278.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ALKEM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5620</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5653.65</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-33.65</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5647.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5711.72</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-64.22</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5506</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5583.57</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-77.56999999999999</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="D46" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="F46" t="n">
+        <v>115.37</v>
+      </c>
+      <c r="G46" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="I46" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>505.2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>519.85</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="F47" t="n">
+        <v>513.9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>517.52</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="I47" t="n">
+        <v>505.2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>498.8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>12105</v>
+      </c>
+      <c r="D48" t="n">
+        <v>12416.6</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-311.6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12105</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12265.83</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-160.83</v>
+      </c>
+      <c r="I48" t="n">
+        <v>11970</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12054.64</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-84.64</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1463.8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1511.85</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-48.05</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-16.27</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1462.1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1450.05</v>
+      </c>
+      <c r="K49" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2008.9</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2082.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-73.8</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2047.97</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1991.07</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3502</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3613.19</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-111.19</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3504.9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3575.71</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-70.81</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3402.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3466.64</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-64.54000000000001</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RECLTD (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>367</v>
+      </c>
+      <c r="D52" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="F52" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="G52" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I52" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>364.49</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2735</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2772.22</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-37.22</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2755</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2785.84</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2695</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2712.52</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-17.52</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAMS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>811.22</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-23.72</v>
+      </c>
+      <c r="F54" t="n">
+        <v>801.05</v>
+      </c>
+      <c r="G54" t="n">
+        <v>807.23</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="I54" t="n">
+        <v>778.05</v>
+      </c>
+      <c r="J54" t="n">
+        <v>777.15</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1168.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1202.9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-34.8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1192.8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1196.89</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1151</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1153.1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1225.3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1246.47</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-21.17</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1244</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1257.71</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-13.71</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1222.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1207.88</v>
+      </c>
+      <c r="K56" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5333</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5480.42</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-147.42</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5367.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5462.44</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-94.94</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5281</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5266.02</v>
+      </c>
+      <c r="K57" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GODREJPROP (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2070</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2112.71</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-42.71</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2108.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2139.3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2062.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2029.42</v>
+      </c>
+      <c r="K58" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8020</v>
+      </c>
+      <c r="D59" t="n">
+        <v>8077.81</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-57.81</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8067.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8146.78</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-79.28</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7920</v>
+      </c>
+      <c r="J59" t="n">
+        <v>7971.16</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-51.16</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1664.69</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-29.69</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1681.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1669.43</v>
+      </c>
+      <c r="H60" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1634.3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1618.47</v>
+      </c>
+      <c r="K60" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>630.65</v>
+      </c>
+      <c r="D61" t="n">
+        <v>651.03</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-20.38</v>
+      </c>
+      <c r="F61" t="n">
+        <v>643.95</v>
+      </c>
+      <c r="G61" t="n">
+        <v>651.05</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>602.45</v>
+      </c>
+      <c r="J61" t="n">
+        <v>618.8200000000001</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-16.37</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>315</v>
+      </c>
+      <c r="D62" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>324.54</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="I62" t="n">
+        <v>313.15</v>
+      </c>
+      <c r="J62" t="n">
+        <v>309.59</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>14200</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14520.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-320.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14294</v>
+      </c>
+      <c r="G63" t="n">
+        <v>14588.91</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-294.91</v>
+      </c>
+      <c r="I63" t="n">
+        <v>14050</v>
+      </c>
+      <c r="J63" t="n">
+        <v>13987.78</v>
+      </c>
+      <c r="K63" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1776</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1811.04</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-35.04</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1809</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1831.84</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-22.84</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1765.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1743.95</v>
+      </c>
+      <c r="K64" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -2634,31 +2634,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5475</v>
+        <v>5459.5</v>
       </c>
       <c r="D43" t="n">
         <v>5487.56</v>
       </c>
       <c r="E43" t="n">
-        <v>-12.56</v>
+        <v>-28.06</v>
       </c>
       <c r="F43" t="n">
-        <v>5594</v>
+        <v>5572</v>
       </c>
       <c r="G43" t="n">
         <v>5487.56</v>
       </c>
       <c r="H43" t="n">
-        <v>106.44</v>
+        <v>84.44</v>
       </c>
       <c r="I43" t="n">
-        <v>5448.5</v>
+        <v>5459.5</v>
       </c>
       <c r="J43" t="n">
         <v>5382.37</v>
       </c>
       <c r="K43" t="n">
-        <v>66.13</v>
+        <v>77.13</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="44">
@@ -2686,31 +2686,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>280.6</v>
+        <v>276.95</v>
       </c>
       <c r="D44" t="n">
         <v>276.72</v>
       </c>
       <c r="E44" t="n">
-        <v>3.88</v>
+        <v>0.23</v>
       </c>
       <c r="F44" t="n">
-        <v>280.6</v>
+        <v>282.8</v>
       </c>
       <c r="G44" t="n">
         <v>277.41</v>
       </c>
       <c r="H44" t="n">
-        <v>3.19</v>
+        <v>5.39</v>
       </c>
       <c r="I44" t="n">
-        <v>275.4</v>
+        <v>276.95</v>
       </c>
       <c r="J44" t="n">
         <v>275.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.08</v>
+        <v>1.47</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.4</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="45">
@@ -2738,31 +2738,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5620</v>
+        <v>5587.5</v>
       </c>
       <c r="D45" t="n">
         <v>5542.31</v>
       </c>
       <c r="E45" t="n">
-        <v>77.69</v>
+        <v>45.19</v>
       </c>
       <c r="F45" t="n">
-        <v>5647.5</v>
+        <v>5685.32</v>
       </c>
       <c r="G45" t="n">
         <v>5631.66</v>
       </c>
       <c r="H45" t="n">
-        <v>15.84</v>
+        <v>53.66</v>
       </c>
       <c r="I45" t="n">
-        <v>5506</v>
+        <v>5576.02</v>
       </c>
       <c r="J45" t="n">
         <v>5543.83</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.83</v>
+        <v>32.19</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.4</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="46">
@@ -2790,31 +2790,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>114.81</v>
+        <v>114.3</v>
       </c>
       <c r="D46" t="n">
         <v>115.19</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.38</v>
+        <v>-0.89</v>
       </c>
       <c r="F46" t="n">
-        <v>115.37</v>
+        <v>114.85</v>
       </c>
       <c r="G46" t="n">
         <v>115.19</v>
       </c>
       <c r="H46" t="n">
-        <v>0.18</v>
+        <v>-0.34</v>
       </c>
       <c r="I46" t="n">
-        <v>113.6</v>
+        <v>113.2</v>
       </c>
       <c r="J46" t="n">
         <v>113.39</v>
       </c>
       <c r="K46" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.33</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="47">
@@ -2842,31 +2842,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>505.2</v>
+        <v>512</v>
       </c>
       <c r="D47" t="n">
         <v>505.44</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.24</v>
+        <v>6.56</v>
       </c>
       <c r="F47" t="n">
-        <v>513.9</v>
+        <v>522</v>
       </c>
       <c r="G47" t="n">
         <v>505.44</v>
       </c>
       <c r="H47" t="n">
-        <v>8.460000000000001</v>
+        <v>16.56</v>
       </c>
       <c r="I47" t="n">
-        <v>505.2</v>
+        <v>510</v>
       </c>
       <c r="J47" t="n">
         <v>493.14</v>
       </c>
       <c r="K47" t="n">
-        <v>12.06</v>
+        <v>16.86</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.05</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="48">
@@ -2894,31 +2894,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12105</v>
+        <v>12075</v>
       </c>
       <c r="D48" t="n">
         <v>12210.02</v>
       </c>
       <c r="E48" t="n">
-        <v>-105.02</v>
+        <v>-135.02</v>
       </c>
       <c r="F48" t="n">
-        <v>12105</v>
+        <v>12204</v>
       </c>
       <c r="G48" t="n">
         <v>12256.51</v>
       </c>
       <c r="H48" t="n">
-        <v>-151.51</v>
+        <v>-52.51</v>
       </c>
       <c r="I48" t="n">
-        <v>11970</v>
+        <v>12011</v>
       </c>
       <c r="J48" t="n">
         <v>12069.81</v>
       </c>
       <c r="K48" t="n">
-        <v>-99.81</v>
+        <v>-58.81</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="49">
@@ -2946,31 +2946,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1463.8</v>
+        <v>1477</v>
       </c>
       <c r="D49" t="n">
         <v>1476.32</v>
       </c>
       <c r="E49" t="n">
-        <v>-12.52</v>
+        <v>0.68</v>
       </c>
       <c r="F49" t="n">
-        <v>1477</v>
+        <v>1488.1</v>
       </c>
       <c r="G49" t="n">
         <v>1476.32</v>
       </c>
       <c r="H49" t="n">
-        <v>0.68</v>
+        <v>11.78</v>
       </c>
       <c r="I49" t="n">
-        <v>1462.1</v>
+        <v>1461</v>
       </c>
       <c r="J49" t="n">
         <v>1435.23</v>
       </c>
       <c r="K49" t="n">
-        <v>26.87</v>
+        <v>25.77</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="50">
@@ -2998,31 +2998,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2008.9</v>
+        <v>2086</v>
       </c>
       <c r="D50" t="n">
         <v>2035.18</v>
       </c>
       <c r="E50" t="n">
-        <v>-26.28</v>
+        <v>50.82</v>
       </c>
       <c r="F50" t="n">
-        <v>2050</v>
+        <v>2103</v>
       </c>
       <c r="G50" t="n">
         <v>2035.18</v>
       </c>
       <c r="H50" t="n">
-        <v>14.82</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>1988</v>
+        <v>2068.6</v>
       </c>
       <c r="J50" t="n">
         <v>1971.08</v>
       </c>
       <c r="K50" t="n">
-        <v>16.92</v>
+        <v>97.52</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="51">
@@ -3050,31 +3050,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3502</v>
+        <v>3406</v>
       </c>
       <c r="D51" t="n">
         <v>3524.97</v>
       </c>
       <c r="E51" t="n">
-        <v>-22.97</v>
+        <v>-118.97</v>
       </c>
       <c r="F51" t="n">
-        <v>3504.9</v>
+        <v>3449</v>
       </c>
       <c r="G51" t="n">
         <v>3526.89</v>
       </c>
       <c r="H51" t="n">
-        <v>-21.99</v>
+        <v>-77.89</v>
       </c>
       <c r="I51" t="n">
-        <v>3402.1</v>
+        <v>3406</v>
       </c>
       <c r="J51" t="n">
         <v>3472.5</v>
       </c>
       <c r="K51" t="n">
-        <v>-70.40000000000001</v>
+        <v>-66.5</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3083,11 +3083,11 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0.65</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="52">
@@ -3102,22 +3102,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>367</v>
+        <v>361.5</v>
       </c>
       <c r="D52" t="n">
         <v>367.17</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.17</v>
+        <v>-5.67</v>
       </c>
       <c r="F52" t="n">
-        <v>368.7</v>
+        <v>367</v>
       </c>
       <c r="G52" t="n">
         <v>369.86</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.16</v>
+        <v>-2.86</v>
       </c>
       <c r="I52" t="n">
         <v>361.5</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.05</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="53">
@@ -3154,31 +3154,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2735</v>
+        <v>2755</v>
       </c>
       <c r="D53" t="n">
         <v>2711.34</v>
       </c>
       <c r="E53" t="n">
-        <v>23.66</v>
+        <v>43.66</v>
       </c>
       <c r="F53" t="n">
-        <v>2755</v>
+        <v>2788</v>
       </c>
       <c r="G53" t="n">
         <v>2748.63</v>
       </c>
       <c r="H53" t="n">
-        <v>6.37</v>
+        <v>39.37</v>
       </c>
       <c r="I53" t="n">
-        <v>2695</v>
+        <v>2741.6</v>
       </c>
       <c r="J53" t="n">
         <v>2706.05</v>
       </c>
       <c r="K53" t="n">
-        <v>-11.05</v>
+        <v>35.55</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.87</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="54">
@@ -3206,31 +3206,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>787.5</v>
+        <v>799.45</v>
       </c>
       <c r="D54" t="n">
         <v>788.2</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.7</v>
+        <v>11.25</v>
       </c>
       <c r="F54" t="n">
-        <v>801.05</v>
+        <v>814.55</v>
       </c>
       <c r="G54" t="n">
         <v>788.2</v>
       </c>
       <c r="H54" t="n">
-        <v>12.85</v>
+        <v>26.35</v>
       </c>
       <c r="I54" t="n">
-        <v>778.05</v>
+        <v>798.25</v>
       </c>
       <c r="J54" t="n">
         <v>774.46</v>
       </c>
       <c r="K54" t="n">
-        <v>3.59</v>
+        <v>23.79</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.09</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="55">
@@ -3258,31 +3258,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1168.1</v>
+        <v>1186</v>
       </c>
       <c r="D55" t="n">
         <v>1169.23</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.13</v>
+        <v>16.77</v>
       </c>
       <c r="F55" t="n">
-        <v>1192.8</v>
+        <v>1197</v>
       </c>
       <c r="G55" t="n">
         <v>1170.66</v>
       </c>
       <c r="H55" t="n">
-        <v>22.14</v>
+        <v>26.34</v>
       </c>
       <c r="I55" t="n">
-        <v>1151</v>
+        <v>1180.9</v>
       </c>
       <c r="J55" t="n">
         <v>1152.4</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.4</v>
+        <v>28.5</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="56">
@@ -3310,31 +3310,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1225.3</v>
+        <v>1240</v>
       </c>
       <c r="D56" t="n">
         <v>1209.39</v>
       </c>
       <c r="E56" t="n">
-        <v>15.91</v>
+        <v>30.61</v>
       </c>
       <c r="F56" t="n">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="G56" t="n">
         <v>1222.15</v>
       </c>
       <c r="H56" t="n">
-        <v>21.85</v>
+        <v>34.85</v>
       </c>
       <c r="I56" t="n">
-        <v>1222.6</v>
+        <v>1229.5</v>
       </c>
       <c r="J56" t="n">
         <v>1202.88</v>
       </c>
       <c r="K56" t="n">
-        <v>19.72</v>
+        <v>26.62</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3343,11 +3343,11 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.32</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="57">
@@ -3362,31 +3362,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5333</v>
+        <v>5318.5</v>
       </c>
       <c r="D57" t="n">
         <v>5329.11</v>
       </c>
       <c r="E57" t="n">
-        <v>3.89</v>
+        <v>-10.61</v>
       </c>
       <c r="F57" t="n">
-        <v>5367.5</v>
+        <v>5424</v>
       </c>
       <c r="G57" t="n">
         <v>5348.56</v>
       </c>
       <c r="H57" t="n">
-        <v>18.94</v>
+        <v>75.44</v>
       </c>
       <c r="I57" t="n">
-        <v>5281</v>
+        <v>5315</v>
       </c>
       <c r="J57" t="n">
         <v>5265.31</v>
       </c>
       <c r="K57" t="n">
-        <v>15.69</v>
+        <v>49.69</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -3414,31 +3414,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2070</v>
+        <v>2081.9</v>
       </c>
       <c r="D58" t="n">
         <v>2035.33</v>
       </c>
       <c r="E58" t="n">
-        <v>34.67</v>
+        <v>46.57</v>
       </c>
       <c r="F58" t="n">
-        <v>2108.6</v>
+        <v>2109</v>
       </c>
       <c r="G58" t="n">
         <v>2035.33</v>
       </c>
       <c r="H58" t="n">
-        <v>73.27</v>
+        <v>73.67</v>
       </c>
       <c r="I58" t="n">
-        <v>2062.3</v>
+        <v>2072.2</v>
       </c>
       <c r="J58" t="n">
         <v>2001.43</v>
       </c>
       <c r="K58" t="n">
-        <v>60.87</v>
+        <v>70.77</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="59">
@@ -3466,31 +3466,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8020</v>
+        <v>7967.5</v>
       </c>
       <c r="D59" t="n">
         <v>7948.47</v>
       </c>
       <c r="E59" t="n">
-        <v>71.53</v>
+        <v>19.03</v>
       </c>
       <c r="F59" t="n">
-        <v>8067.5</v>
+        <v>8044</v>
       </c>
       <c r="G59" t="n">
         <v>8169.85</v>
       </c>
       <c r="H59" t="n">
-        <v>-102.35</v>
+        <v>-125.85</v>
       </c>
       <c r="I59" t="n">
-        <v>7920</v>
+        <v>7896.5</v>
       </c>
       <c r="J59" t="n">
         <v>8020</v>
       </c>
       <c r="K59" t="n">
-        <v>-100</v>
+        <v>-123.5</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.9</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="60">
@@ -3518,31 +3518,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1635</v>
+        <v>1632.2</v>
       </c>
       <c r="D60" t="n">
         <v>1624.03</v>
       </c>
       <c r="E60" t="n">
-        <v>10.97</v>
+        <v>8.17</v>
       </c>
       <c r="F60" t="n">
-        <v>1681.5</v>
+        <v>1670</v>
       </c>
       <c r="G60" t="n">
         <v>1653.8</v>
       </c>
       <c r="H60" t="n">
-        <v>27.7</v>
+        <v>16.2</v>
       </c>
       <c r="I60" t="n">
-        <v>1634.3</v>
+        <v>1631</v>
       </c>
       <c r="J60" t="n">
         <v>1628.55</v>
       </c>
       <c r="K60" t="n">
-        <v>5.75</v>
+        <v>2.45</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61">
@@ -3570,31 +3570,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>630.65</v>
+        <v>609.75</v>
       </c>
       <c r="D61" t="n">
         <v>627.91</v>
       </c>
       <c r="E61" t="n">
-        <v>2.74</v>
+        <v>-18.16</v>
       </c>
       <c r="F61" t="n">
-        <v>643.95</v>
+        <v>616.2</v>
       </c>
       <c r="G61" t="n">
         <v>627.91</v>
       </c>
       <c r="H61" t="n">
-        <v>16.04</v>
+        <v>-11.71</v>
       </c>
       <c r="I61" t="n">
-        <v>602.45</v>
+        <v>597</v>
       </c>
       <c r="J61" t="n">
         <v>616.61</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.16</v>
+        <v>-19.61</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0.44</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="62">
@@ -3622,31 +3622,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>315</v>
+        <v>316.25</v>
       </c>
       <c r="D62" t="n">
         <v>316.13</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.13</v>
+        <v>0.12</v>
       </c>
       <c r="F62" t="n">
-        <v>316.9</v>
+        <v>319.7</v>
       </c>
       <c r="G62" t="n">
         <v>319.09</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.19</v>
+        <v>0.61</v>
       </c>
       <c r="I62" t="n">
-        <v>313.15</v>
+        <v>310</v>
       </c>
       <c r="J62" t="n">
         <v>314.24</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.09</v>
+        <v>-4.24</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.36</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="63">
@@ -3683,22 +3683,22 @@
         <v>124.72</v>
       </c>
       <c r="F63" t="n">
-        <v>14294</v>
+        <v>14445</v>
       </c>
       <c r="G63" t="n">
         <v>14183.21</v>
       </c>
       <c r="H63" t="n">
-        <v>110.79</v>
+        <v>261.79</v>
       </c>
       <c r="I63" t="n">
-        <v>14050</v>
+        <v>14137</v>
       </c>
       <c r="J63" t="n">
         <v>13960.38</v>
       </c>
       <c r="K63" t="n">
-        <v>89.62</v>
+        <v>176.62</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3726,31 +3726,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1776</v>
+        <v>1772.8</v>
       </c>
       <c r="D64" t="n">
         <v>1748.3</v>
       </c>
       <c r="E64" t="n">
-        <v>27.7</v>
+        <v>24.5</v>
       </c>
       <c r="F64" t="n">
-        <v>1809</v>
+        <v>1813.9</v>
       </c>
       <c r="G64" t="n">
         <v>1781.99</v>
       </c>
       <c r="H64" t="n">
-        <v>27.01</v>
+        <v>31.91</v>
       </c>
       <c r="I64" t="n">
-        <v>1765.5</v>
+        <v>1757.9</v>
       </c>
       <c r="J64" t="n">
         <v>1754.28</v>
       </c>
       <c r="K64" t="n">
-        <v>11.22</v>
+        <v>3.62</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -4072,31 +4072,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24570.65</v>
+        <v>24636</v>
       </c>
       <c r="D6" t="n">
         <v>24570.65</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>24630.4</v>
+        <v>24677.05</v>
       </c>
       <c r="G6" t="n">
         <v>24626.45</v>
       </c>
       <c r="H6" t="n">
-        <v>3.95</v>
+        <v>50.6</v>
       </c>
       <c r="I6" t="n">
-        <v>24522.75</v>
+        <v>24604.15</v>
       </c>
       <c r="J6" t="n">
         <v>24518.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -4124,31 +4124,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57746.45</v>
+        <v>58063.65</v>
       </c>
       <c r="D7" t="n">
         <v>57746.45</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>317.2</v>
       </c>
       <c r="F7" t="n">
-        <v>57994.45</v>
+        <v>58076.85</v>
       </c>
       <c r="G7" t="n">
         <v>57931.75</v>
       </c>
       <c r="H7" t="n">
-        <v>62.7</v>
+        <v>145.1</v>
       </c>
       <c r="I7" t="n">
-        <v>57686.55</v>
+        <v>57714.7</v>
       </c>
       <c r="J7" t="n">
         <v>57623.85</v>
       </c>
       <c r="K7" t="n">
-        <v>62.7</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -6394,31 +6394,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5475</v>
+        <v>5459.5</v>
       </c>
       <c r="D43" t="n">
         <v>5677.02</v>
       </c>
       <c r="E43" t="n">
-        <v>-202.02</v>
+        <v>-217.52</v>
       </c>
       <c r="F43" t="n">
-        <v>5594</v>
+        <v>5572</v>
       </c>
       <c r="G43" t="n">
         <v>5640.02</v>
       </c>
       <c r="H43" t="n">
-        <v>-46.02</v>
+        <v>-68.02</v>
       </c>
       <c r="I43" t="n">
-        <v>5448.5</v>
+        <v>5459.5</v>
       </c>
       <c r="J43" t="n">
         <v>5381.65</v>
       </c>
       <c r="K43" t="n">
-        <v>66.84999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.56</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="44">
@@ -6446,31 +6446,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>280.6</v>
+        <v>276.95</v>
       </c>
       <c r="D44" t="n">
         <v>283.01</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.41</v>
+        <v>-6.06</v>
       </c>
       <c r="F44" t="n">
-        <v>280.6</v>
+        <v>282.8</v>
       </c>
       <c r="G44" t="n">
         <v>285.89</v>
       </c>
       <c r="H44" t="n">
-        <v>-5.29</v>
+        <v>-3.09</v>
       </c>
       <c r="I44" t="n">
-        <v>275.4</v>
+        <v>276.95</v>
       </c>
       <c r="J44" t="n">
         <v>278.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.85</v>
+        <v>-1.3</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0.85</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="45">
@@ -6498,31 +6498,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5620</v>
+        <v>5587.5</v>
       </c>
       <c r="D45" t="n">
         <v>5653.65</v>
       </c>
       <c r="E45" t="n">
-        <v>-33.65</v>
+        <v>-66.15000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>5647.5</v>
+        <v>5685.32</v>
       </c>
       <c r="G45" t="n">
         <v>5711.72</v>
       </c>
       <c r="H45" t="n">
-        <v>-64.22</v>
+        <v>-26.4</v>
       </c>
       <c r="I45" t="n">
-        <v>5506</v>
+        <v>5576.02</v>
       </c>
       <c r="J45" t="n">
         <v>5583.57</v>
       </c>
       <c r="K45" t="n">
-        <v>-77.56999999999999</v>
+        <v>-7.55</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="46">
@@ -6550,31 +6550,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>114.81</v>
+        <v>114.3</v>
       </c>
       <c r="D46" t="n">
         <v>117.12</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.31</v>
+        <v>-2.82</v>
       </c>
       <c r="F46" t="n">
-        <v>115.37</v>
+        <v>114.85</v>
       </c>
       <c r="G46" t="n">
         <v>116.32</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.95</v>
+        <v>-1.47</v>
       </c>
       <c r="I46" t="n">
-        <v>113.6</v>
+        <v>113.2</v>
       </c>
       <c r="J46" t="n">
         <v>114.35</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.75</v>
+        <v>-1.15</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="47">
@@ -6602,31 +6602,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>505.2</v>
+        <v>512</v>
       </c>
       <c r="D47" t="n">
         <v>519.85</v>
       </c>
       <c r="E47" t="n">
-        <v>-14.65</v>
+        <v>-7.85</v>
       </c>
       <c r="F47" t="n">
-        <v>513.9</v>
+        <v>522</v>
       </c>
       <c r="G47" t="n">
         <v>517.52</v>
       </c>
       <c r="H47" t="n">
-        <v>-3.62</v>
+        <v>4.48</v>
       </c>
       <c r="I47" t="n">
-        <v>505.2</v>
+        <v>510</v>
       </c>
       <c r="J47" t="n">
         <v>498.8</v>
       </c>
       <c r="K47" t="n">
-        <v>6.4</v>
+        <v>11.2</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6635,11 +6635,11 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.82</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="48">
@@ -6654,31 +6654,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12105</v>
+        <v>12075</v>
       </c>
       <c r="D48" t="n">
         <v>12416.6</v>
       </c>
       <c r="E48" t="n">
-        <v>-311.6</v>
+        <v>-341.6</v>
       </c>
       <c r="F48" t="n">
-        <v>12105</v>
+        <v>12204</v>
       </c>
       <c r="G48" t="n">
         <v>12265.83</v>
       </c>
       <c r="H48" t="n">
-        <v>-160.83</v>
+        <v>-61.83</v>
       </c>
       <c r="I48" t="n">
-        <v>11970</v>
+        <v>12011</v>
       </c>
       <c r="J48" t="n">
         <v>12054.64</v>
       </c>
       <c r="K48" t="n">
-        <v>-84.64</v>
+        <v>-43.64</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="49">
@@ -6706,31 +6706,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1463.8</v>
+        <v>1477</v>
       </c>
       <c r="D49" t="n">
         <v>1511.85</v>
       </c>
       <c r="E49" t="n">
-        <v>-48.05</v>
+        <v>-34.85</v>
       </c>
       <c r="F49" t="n">
-        <v>1477</v>
+        <v>1488.1</v>
       </c>
       <c r="G49" t="n">
         <v>1493.27</v>
       </c>
       <c r="H49" t="n">
-        <v>-16.27</v>
+        <v>-5.17</v>
       </c>
       <c r="I49" t="n">
-        <v>1462.1</v>
+        <v>1461</v>
       </c>
       <c r="J49" t="n">
         <v>1450.05</v>
       </c>
       <c r="K49" t="n">
-        <v>12.05</v>
+        <v>10.95</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -6739,11 +6739,11 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="50">
@@ -6758,31 +6758,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2008.9</v>
+        <v>2086</v>
       </c>
       <c r="D50" t="n">
         <v>2082.7</v>
       </c>
       <c r="E50" t="n">
-        <v>-73.8</v>
+        <v>3.3</v>
       </c>
       <c r="F50" t="n">
-        <v>2050</v>
+        <v>2103</v>
       </c>
       <c r="G50" t="n">
         <v>2047.97</v>
       </c>
       <c r="H50" t="n">
-        <v>2.03</v>
+        <v>55.03</v>
       </c>
       <c r="I50" t="n">
-        <v>1988</v>
+        <v>2068.6</v>
       </c>
       <c r="J50" t="n">
         <v>1991.07</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.07</v>
+        <v>77.53</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -6791,11 +6791,11 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.54</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="51">
@@ -6810,31 +6810,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3502</v>
+        <v>3406</v>
       </c>
       <c r="D51" t="n">
         <v>3613.19</v>
       </c>
       <c r="E51" t="n">
-        <v>-111.19</v>
+        <v>-207.19</v>
       </c>
       <c r="F51" t="n">
-        <v>3504.9</v>
+        <v>3449</v>
       </c>
       <c r="G51" t="n">
         <v>3575.71</v>
       </c>
       <c r="H51" t="n">
-        <v>-70.81</v>
+        <v>-126.71</v>
       </c>
       <c r="I51" t="n">
-        <v>3402.1</v>
+        <v>3406</v>
       </c>
       <c r="J51" t="n">
         <v>3466.64</v>
       </c>
       <c r="K51" t="n">
-        <v>-64.54000000000001</v>
+        <v>-60.64</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3.08</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="52">
@@ -6862,22 +6862,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>367</v>
+        <v>361.5</v>
       </c>
       <c r="D52" t="n">
         <v>374.73</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.73</v>
+        <v>-13.23</v>
       </c>
       <c r="F52" t="n">
-        <v>368.7</v>
+        <v>367</v>
       </c>
       <c r="G52" t="n">
         <v>373.17</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.47</v>
+        <v>-6.17</v>
       </c>
       <c r="I52" t="n">
         <v>361.5</v>
@@ -6895,11 +6895,11 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.06</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="53">
@@ -6914,31 +6914,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2735</v>
+        <v>2755</v>
       </c>
       <c r="D53" t="n">
         <v>2772.22</v>
       </c>
       <c r="E53" t="n">
-        <v>-37.22</v>
+        <v>-17.22</v>
       </c>
       <c r="F53" t="n">
-        <v>2755</v>
+        <v>2788</v>
       </c>
       <c r="G53" t="n">
         <v>2785.84</v>
       </c>
       <c r="H53" t="n">
-        <v>-30.84</v>
+        <v>2.16</v>
       </c>
       <c r="I53" t="n">
-        <v>2695</v>
+        <v>2741.6</v>
       </c>
       <c r="J53" t="n">
         <v>2712.52</v>
       </c>
       <c r="K53" t="n">
-        <v>-17.52</v>
+        <v>29.08</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.34</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="54">
@@ -6966,31 +6966,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>787.5</v>
+        <v>799.45</v>
       </c>
       <c r="D54" t="n">
         <v>811.22</v>
       </c>
       <c r="E54" t="n">
-        <v>-23.72</v>
+        <v>-11.77</v>
       </c>
       <c r="F54" t="n">
-        <v>801.05</v>
+        <v>814.55</v>
       </c>
       <c r="G54" t="n">
         <v>807.23</v>
       </c>
       <c r="H54" t="n">
-        <v>-6.18</v>
+        <v>7.32</v>
       </c>
       <c r="I54" t="n">
-        <v>778.05</v>
+        <v>798.25</v>
       </c>
       <c r="J54" t="n">
         <v>777.15</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9</v>
+        <v>21.1</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -6999,11 +6999,11 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="55">
@@ -7018,31 +7018,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1168.1</v>
+        <v>1186</v>
       </c>
       <c r="D55" t="n">
         <v>1202.9</v>
       </c>
       <c r="E55" t="n">
-        <v>-34.8</v>
+        <v>-16.9</v>
       </c>
       <c r="F55" t="n">
-        <v>1192.8</v>
+        <v>1197</v>
       </c>
       <c r="G55" t="n">
         <v>1196.89</v>
       </c>
       <c r="H55" t="n">
-        <v>-4.09</v>
+        <v>0.11</v>
       </c>
       <c r="I55" t="n">
-        <v>1151</v>
+        <v>1180.9</v>
       </c>
       <c r="J55" t="n">
         <v>1153.1</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.1</v>
+        <v>27.8</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.89</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="56">
@@ -7070,31 +7070,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1225.3</v>
+        <v>1240</v>
       </c>
       <c r="D56" t="n">
         <v>1246.47</v>
       </c>
       <c r="E56" t="n">
-        <v>-21.17</v>
+        <v>-6.47</v>
       </c>
       <c r="F56" t="n">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="G56" t="n">
         <v>1257.71</v>
       </c>
       <c r="H56" t="n">
-        <v>-13.71</v>
+        <v>-0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>1222.6</v>
+        <v>1229.5</v>
       </c>
       <c r="J56" t="n">
         <v>1207.88</v>
       </c>
       <c r="K56" t="n">
-        <v>14.72</v>
+        <v>21.62</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="57">
@@ -7122,31 +7122,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5333</v>
+        <v>5318.5</v>
       </c>
       <c r="D57" t="n">
         <v>5480.42</v>
       </c>
       <c r="E57" t="n">
-        <v>-147.42</v>
+        <v>-161.92</v>
       </c>
       <c r="F57" t="n">
-        <v>5367.5</v>
+        <v>5424</v>
       </c>
       <c r="G57" t="n">
         <v>5462.44</v>
       </c>
       <c r="H57" t="n">
-        <v>-94.94</v>
+        <v>-38.44</v>
       </c>
       <c r="I57" t="n">
-        <v>5281</v>
+        <v>5315</v>
       </c>
       <c r="J57" t="n">
         <v>5266.02</v>
       </c>
       <c r="K57" t="n">
-        <v>14.98</v>
+        <v>48.98</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="58">
@@ -7174,31 +7174,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2070</v>
+        <v>2081.9</v>
       </c>
       <c r="D58" t="n">
         <v>2112.71</v>
       </c>
       <c r="E58" t="n">
-        <v>-42.71</v>
+        <v>-30.81</v>
       </c>
       <c r="F58" t="n">
-        <v>2108.6</v>
+        <v>2109</v>
       </c>
       <c r="G58" t="n">
         <v>2139.3</v>
       </c>
       <c r="H58" t="n">
-        <v>-30.7</v>
+        <v>-30.3</v>
       </c>
       <c r="I58" t="n">
-        <v>2062.3</v>
+        <v>2072.2</v>
       </c>
       <c r="J58" t="n">
         <v>2029.42</v>
       </c>
       <c r="K58" t="n">
-        <v>32.88</v>
+        <v>42.78</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="59">
@@ -7226,31 +7226,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8020</v>
+        <v>7967.5</v>
       </c>
       <c r="D59" t="n">
         <v>8077.81</v>
       </c>
       <c r="E59" t="n">
-        <v>-57.81</v>
+        <v>-110.31</v>
       </c>
       <c r="F59" t="n">
-        <v>8067.5</v>
+        <v>8044</v>
       </c>
       <c r="G59" t="n">
         <v>8146.78</v>
       </c>
       <c r="H59" t="n">
-        <v>-79.28</v>
+        <v>-102.78</v>
       </c>
       <c r="I59" t="n">
-        <v>7920</v>
+        <v>7896.5</v>
       </c>
       <c r="J59" t="n">
         <v>7971.16</v>
       </c>
       <c r="K59" t="n">
-        <v>-51.16</v>
+        <v>-74.66</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.72</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="60">
@@ -7278,31 +7278,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1635</v>
+        <v>1632.2</v>
       </c>
       <c r="D60" t="n">
         <v>1664.69</v>
       </c>
       <c r="E60" t="n">
-        <v>-29.69</v>
+        <v>-32.49</v>
       </c>
       <c r="F60" t="n">
-        <v>1681.5</v>
+        <v>1670</v>
       </c>
       <c r="G60" t="n">
         <v>1669.43</v>
       </c>
       <c r="H60" t="n">
-        <v>12.07</v>
+        <v>0.57</v>
       </c>
       <c r="I60" t="n">
-        <v>1634.3</v>
+        <v>1631</v>
       </c>
       <c r="J60" t="n">
         <v>1618.47</v>
       </c>
       <c r="K60" t="n">
-        <v>15.83</v>
+        <v>12.53</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="61">
@@ -7330,31 +7330,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>630.65</v>
+        <v>609.75</v>
       </c>
       <c r="D61" t="n">
         <v>651.03</v>
       </c>
       <c r="E61" t="n">
-        <v>-20.38</v>
+        <v>-41.28</v>
       </c>
       <c r="F61" t="n">
-        <v>643.95</v>
+        <v>616.2</v>
       </c>
       <c r="G61" t="n">
         <v>651.05</v>
       </c>
       <c r="H61" t="n">
-        <v>-7.1</v>
+        <v>-34.85</v>
       </c>
       <c r="I61" t="n">
-        <v>602.45</v>
+        <v>597</v>
       </c>
       <c r="J61" t="n">
         <v>618.8200000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.37</v>
+        <v>-21.82</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3.13</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="62">
@@ -7382,31 +7382,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>315</v>
+        <v>316.25</v>
       </c>
       <c r="D62" t="n">
         <v>327.1</v>
       </c>
       <c r="E62" t="n">
-        <v>-12.1</v>
+        <v>-10.85</v>
       </c>
       <c r="F62" t="n">
-        <v>316.9</v>
+        <v>319.7</v>
       </c>
       <c r="G62" t="n">
         <v>324.54</v>
       </c>
       <c r="H62" t="n">
-        <v>-7.64</v>
+        <v>-4.84</v>
       </c>
       <c r="I62" t="n">
-        <v>313.15</v>
+        <v>310</v>
       </c>
       <c r="J62" t="n">
         <v>309.59</v>
       </c>
       <c r="K62" t="n">
-        <v>3.56</v>
+        <v>0.41</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="63">
@@ -7443,22 +7443,22 @@
         <v>-320.75</v>
       </c>
       <c r="F63" t="n">
-        <v>14294</v>
+        <v>14445</v>
       </c>
       <c r="G63" t="n">
         <v>14588.91</v>
       </c>
       <c r="H63" t="n">
-        <v>-294.91</v>
+        <v>-143.91</v>
       </c>
       <c r="I63" t="n">
-        <v>14050</v>
+        <v>14137</v>
       </c>
       <c r="J63" t="n">
         <v>13987.78</v>
       </c>
       <c r="K63" t="n">
-        <v>62.22</v>
+        <v>149.22</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -7486,31 +7486,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1776</v>
+        <v>1772.8</v>
       </c>
       <c r="D64" t="n">
         <v>1811.04</v>
       </c>
       <c r="E64" t="n">
-        <v>-35.04</v>
+        <v>-38.24</v>
       </c>
       <c r="F64" t="n">
-        <v>1809</v>
+        <v>1813.9</v>
       </c>
       <c r="G64" t="n">
         <v>1831.84</v>
       </c>
       <c r="H64" t="n">
-        <v>-22.84</v>
+        <v>-17.94</v>
       </c>
       <c r="I64" t="n">
-        <v>1765.5</v>
+        <v>1757.9</v>
       </c>
       <c r="J64" t="n">
         <v>1743.95</v>
       </c>
       <c r="K64" t="n">
-        <v>21.55</v>
+        <v>13.95</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3764,6 +3764,1202 @@
       </c>
       <c r="N64" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4075.67</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4171.64</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-91.64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4025.8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4039.37</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-13.57</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3425.49</v>
+      </c>
+      <c r="E66" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3534.6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3518.57</v>
+      </c>
+      <c r="H66" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3491.1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3423.59</v>
+      </c>
+      <c r="K66" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>113.53</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F67" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="G67" t="n">
+        <v>114.68</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I67" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>111.89</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5489.59</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-15.59</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5543.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5564.29</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-20.79</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5425</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5386.73</v>
+      </c>
+      <c r="K68" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1661.44</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1665.9</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1680.86</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1630.8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1627.71</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5333.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5365.47</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-31.97</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5355</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5428.65</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-73.65000000000001</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5297</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5255.68</v>
+      </c>
+      <c r="K70" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1467.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1480.12</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-12.42</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1483.7</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1483.16</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1462</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1435.54</v>
+      </c>
+      <c r="K71" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1850.04</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-40.04</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1822.6</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1850.04</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-27.44</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1783.1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1779.32</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2816.63</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-66.63</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2761.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2816.63</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-55.13</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2713.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2713.72</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1282</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1337.1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1298.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1337.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-38.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1236.7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1282</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-45.3</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>621.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>608.64</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>630.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>635.02</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I75" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>614.85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="D76" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F76" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="G76" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="I76" t="n">
+        <v>179.94</v>
+      </c>
+      <c r="J76" t="n">
+        <v>181.03</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7975</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8058.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-83.01000000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8024</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8202.75</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-178.75</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7938</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7944.32</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1940.93</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1959</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1991.14</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-32.14</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1935</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1928.16</v>
+      </c>
+      <c r="K78" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>789.45</v>
+      </c>
+      <c r="D79" t="n">
+        <v>807.13</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-17.68</v>
+      </c>
+      <c r="F79" t="n">
+        <v>798.4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>807.13</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-8.73</v>
+      </c>
+      <c r="I79" t="n">
+        <v>780.05</v>
+      </c>
+      <c r="J79" t="n">
+        <v>776.51</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>280</v>
+      </c>
+      <c r="D80" t="n">
+        <v>282.47</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="F80" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>282.47</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="I80" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>273.61</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>12038</v>
+      </c>
+      <c r="D81" t="n">
+        <v>12000.09</v>
+      </c>
+      <c r="E81" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12124</v>
+      </c>
+      <c r="G81" t="n">
+        <v>12345.48</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-221.48</v>
+      </c>
+      <c r="I81" t="n">
+        <v>11921</v>
+      </c>
+      <c r="J81" t="n">
+        <v>11955.31</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-34.31</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1175.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1201.99</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-26.39</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1201.99</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-12.09</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1161.7</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1148.12</v>
+      </c>
+      <c r="K82" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2108.4</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2173.9</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-65.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2173.9</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-53.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2057.6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2031.51</v>
+      </c>
+      <c r="K83" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="D84" t="n">
+        <v>312.85</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="G84" t="n">
+        <v>317.62</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="I84" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>307.57</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2021.3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2088.35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-67.05</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2037.1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2088.35</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-51.25</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1992.6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1968.33</v>
+      </c>
+      <c r="K85" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>14115</v>
+      </c>
+      <c r="D86" t="n">
+        <v>14353.98</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-238.98</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14271</v>
+      </c>
+      <c r="G86" t="n">
+        <v>14353.98</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-82.98</v>
+      </c>
+      <c r="I86" t="n">
+        <v>14001</v>
+      </c>
+      <c r="J86" t="n">
+        <v>13803.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="D87" t="n">
+        <v>512.49</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-10.59</v>
+      </c>
+      <c r="F87" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>512.49</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I87" t="n">
+        <v>498.25</v>
+      </c>
+      <c r="J87" t="n">
+        <v>487.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>
@@ -3777,7 +4973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4162,6 +5358,110 @@
       </c>
       <c r="N7" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24620.95</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24632.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24511.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24522.95</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="D9" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>58015.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>57959.29</v>
+      </c>
+      <c r="H9" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="I9" t="n">
+        <v>57527.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57471.19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4175,7 +5475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7526,6 +8826,1202 @@
         <v>2.11</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4129.22</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-49.22</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4168.72</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-88.72</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4025.8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4050.23</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-24.43</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3513.87</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3534.6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3636.64</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-102.04</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3491.1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3458.88</v>
+      </c>
+      <c r="K66" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1914.32</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-104.32</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1822.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1887.25</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-64.65000000000001</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1783.1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1768.3</v>
+      </c>
+      <c r="K67" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F68" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="G68" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I68" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>112.68</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5682.41</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-208.41</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5543.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5709.63</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-166.13</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5425</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5346.37</v>
+      </c>
+      <c r="K69" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1703.12</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-63.12</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1665.9</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1694.65</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-28.75</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1630.8</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1613.75</v>
+      </c>
+      <c r="K70" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5333.5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5509.7</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-176.2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5355</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5520.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-165.5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>5297</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5241.17</v>
+      </c>
+      <c r="K71" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1467.7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1511.8</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-44.1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1483.7</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1511.37</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-27.67</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1462</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1448.15</v>
+      </c>
+      <c r="K72" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2879.42</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-129.42</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2761.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2834.2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-72.7</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2713.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2711.59</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1282</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1362.46</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-80.45999999999999</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1298.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1328.71</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-30.21</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1236.7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1258.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-21.78</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>621.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>632.96</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-11.16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>630.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>651.47</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-20.72</v>
+      </c>
+      <c r="I75" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>605.11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CAMS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>789.45</v>
+      </c>
+      <c r="D76" t="n">
+        <v>829.51</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-40.06</v>
+      </c>
+      <c r="F76" t="n">
+        <v>798.4</v>
+      </c>
+      <c r="G76" t="n">
+        <v>817.78</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-19.38</v>
+      </c>
+      <c r="I76" t="n">
+        <v>780.05</v>
+      </c>
+      <c r="J76" t="n">
+        <v>775.3</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="D77" t="n">
+        <v>185.51</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="F77" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="G77" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I77" t="n">
+        <v>179.94</v>
+      </c>
+      <c r="J77" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12038</v>
+      </c>
+      <c r="D78" t="n">
+        <v>12179.11</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-141.11</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12124</v>
+      </c>
+      <c r="G78" t="n">
+        <v>12320.53</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-196.53</v>
+      </c>
+      <c r="I78" t="n">
+        <v>11921</v>
+      </c>
+      <c r="J78" t="n">
+        <v>11934.56</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-13.56</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1175.6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1236.99</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-61.39</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1219.36</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-29.46</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1161.7</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1153.35</v>
+      </c>
+      <c r="K79" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>7975</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8215.84</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-240.84</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8024</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8198.24</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-174.24</v>
+      </c>
+      <c r="I80" t="n">
+        <v>7938</v>
+      </c>
+      <c r="J80" t="n">
+        <v>7879.34</v>
+      </c>
+      <c r="K80" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1970.16</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-27.16</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1959</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1988.85</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-29.85</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1935</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1926.11</v>
+      </c>
+      <c r="K81" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GODREJPROP (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2108.4</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2252.16</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-143.76</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2200.95</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-80.95</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2057.6</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2057.89</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2021.3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2141.48</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-120.18</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2037.1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2089.35</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-52.25</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1992.6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1988.44</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>280</v>
+      </c>
+      <c r="D84" t="n">
+        <v>288.68</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="F84" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="I84" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>276.16</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="D85" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-13.35</v>
+      </c>
+      <c r="F85" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="G85" t="n">
+        <v>323.38</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="I85" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>303.19</v>
+      </c>
+      <c r="K85" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>14115</v>
+      </c>
+      <c r="D86" t="n">
+        <v>14784.36</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-669.36</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14271</v>
+      </c>
+      <c r="G86" t="n">
+        <v>14652.3</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-381.3</v>
+      </c>
+      <c r="I86" t="n">
+        <v>14001</v>
+      </c>
+      <c r="J86" t="n">
+        <v>13838.77</v>
+      </c>
+      <c r="K86" t="n">
+        <v>162.23</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="D87" t="n">
+        <v>526.34</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-24.44</v>
+      </c>
+      <c r="F87" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>519.58</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="I87" t="n">
+        <v>498.25</v>
+      </c>
+      <c r="J87" t="n">
+        <v>493.15</v>
+      </c>
+      <c r="K87" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -3778,31 +3778,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4080</v>
+        <v>4056</v>
       </c>
       <c r="D65" t="n">
         <v>4075.67</v>
       </c>
       <c r="E65" t="n">
-        <v>4.33</v>
+        <v>-19.67</v>
       </c>
       <c r="F65" t="n">
-        <v>4080</v>
+        <v>4062</v>
       </c>
       <c r="G65" t="n">
         <v>4171.64</v>
       </c>
       <c r="H65" t="n">
-        <v>-91.64</v>
+        <v>-109.64</v>
       </c>
       <c r="I65" t="n">
-        <v>4025.8</v>
+        <v>4030</v>
       </c>
       <c r="J65" t="n">
         <v>4039.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-13.57</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="66">
@@ -3830,31 +3830,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3517</v>
+        <v>3502</v>
       </c>
       <c r="D66" t="n">
         <v>3425.49</v>
       </c>
       <c r="E66" t="n">
-        <v>91.51000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>3534.6</v>
+        <v>3504.9</v>
       </c>
       <c r="G66" t="n">
         <v>3518.57</v>
       </c>
       <c r="H66" t="n">
-        <v>16.03</v>
+        <v>-13.67</v>
       </c>
       <c r="I66" t="n">
-        <v>3491.1</v>
+        <v>3402.1</v>
       </c>
       <c r="J66" t="n">
         <v>3423.59</v>
       </c>
       <c r="K66" t="n">
-        <v>67.51000000000001</v>
+        <v>-21.49</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.67</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="67">
@@ -3882,31 +3882,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>113.5</v>
+        <v>114.81</v>
       </c>
       <c r="D67" t="n">
         <v>113.53</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.03</v>
+        <v>1.28</v>
       </c>
       <c r="F67" t="n">
-        <v>115.19</v>
+        <v>115.37</v>
       </c>
       <c r="G67" t="n">
         <v>114.68</v>
       </c>
       <c r="H67" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>113.2</v>
+        <v>113.6</v>
       </c>
       <c r="J67" t="n">
         <v>111.89</v>
       </c>
       <c r="K67" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.03</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="68">
@@ -3934,31 +3934,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="D68" t="n">
         <v>5489.59</v>
       </c>
       <c r="E68" t="n">
-        <v>-15.59</v>
+        <v>-14.59</v>
       </c>
       <c r="F68" t="n">
-        <v>5543.5</v>
+        <v>5594</v>
       </c>
       <c r="G68" t="n">
         <v>5564.29</v>
       </c>
       <c r="H68" t="n">
-        <v>-20.79</v>
+        <v>29.71</v>
       </c>
       <c r="I68" t="n">
-        <v>5425</v>
+        <v>5448.5</v>
       </c>
       <c r="J68" t="n">
         <v>5386.73</v>
       </c>
       <c r="K68" t="n">
-        <v>38.27</v>
+        <v>61.77</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="69">
@@ -3986,31 +3986,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D69" t="n">
         <v>1661.44</v>
       </c>
       <c r="E69" t="n">
-        <v>-21.44</v>
+        <v>-26.44</v>
       </c>
       <c r="F69" t="n">
-        <v>1665.9</v>
+        <v>1681.5</v>
       </c>
       <c r="G69" t="n">
         <v>1680.86</v>
       </c>
       <c r="H69" t="n">
-        <v>-14.96</v>
+        <v>0.64</v>
       </c>
       <c r="I69" t="n">
-        <v>1630.8</v>
+        <v>1634.3</v>
       </c>
       <c r="J69" t="n">
         <v>1627.71</v>
       </c>
       <c r="K69" t="n">
-        <v>3.09</v>
+        <v>6.59</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="70">
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5333.5</v>
+        <v>5333</v>
       </c>
       <c r="D70" t="n">
         <v>5365.47</v>
       </c>
       <c r="E70" t="n">
-        <v>-31.97</v>
+        <v>-32.47</v>
       </c>
       <c r="F70" t="n">
-        <v>5355</v>
+        <v>5367.5</v>
       </c>
       <c r="G70" t="n">
         <v>5428.65</v>
       </c>
       <c r="H70" t="n">
-        <v>-73.65000000000001</v>
+        <v>-61.15</v>
       </c>
       <c r="I70" t="n">
-        <v>5297</v>
+        <v>5281</v>
       </c>
       <c r="J70" t="n">
         <v>5255.68</v>
       </c>
       <c r="K70" t="n">
-        <v>41.32</v>
+        <v>25.32</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="71">
@@ -4090,31 +4090,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1467.7</v>
+        <v>1463.8</v>
       </c>
       <c r="D71" t="n">
         <v>1480.12</v>
       </c>
       <c r="E71" t="n">
-        <v>-12.42</v>
+        <v>-16.32</v>
       </c>
       <c r="F71" t="n">
-        <v>1483.7</v>
+        <v>1477</v>
       </c>
       <c r="G71" t="n">
         <v>1483.16</v>
       </c>
       <c r="H71" t="n">
-        <v>0.54</v>
+        <v>-6.16</v>
       </c>
       <c r="I71" t="n">
-        <v>1462</v>
+        <v>1462.1</v>
       </c>
       <c r="J71" t="n">
         <v>1435.54</v>
       </c>
       <c r="K71" t="n">
-        <v>26.46</v>
+        <v>26.56</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="72">
@@ -4142,31 +4142,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1810</v>
+        <v>1776</v>
       </c>
       <c r="D72" t="n">
         <v>1850.04</v>
       </c>
       <c r="E72" t="n">
-        <v>-40.04</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>1822.6</v>
+        <v>1809</v>
       </c>
       <c r="G72" t="n">
         <v>1850.04</v>
       </c>
       <c r="H72" t="n">
-        <v>-27.44</v>
+        <v>-41.04</v>
       </c>
       <c r="I72" t="n">
-        <v>1783.1</v>
+        <v>1765.5</v>
       </c>
       <c r="J72" t="n">
         <v>1779.32</v>
       </c>
       <c r="K72" t="n">
-        <v>3.78</v>
+        <v>-13.82</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -4194,31 +4194,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2750</v>
+        <v>2735</v>
       </c>
       <c r="D73" t="n">
         <v>2816.63</v>
       </c>
       <c r="E73" t="n">
-        <v>-66.63</v>
+        <v>-81.63</v>
       </c>
       <c r="F73" t="n">
-        <v>2761.5</v>
+        <v>2755</v>
       </c>
       <c r="G73" t="n">
         <v>2816.63</v>
       </c>
       <c r="H73" t="n">
-        <v>-55.13</v>
+        <v>-61.63</v>
       </c>
       <c r="I73" t="n">
-        <v>2713.5</v>
+        <v>2695</v>
       </c>
       <c r="J73" t="n">
         <v>2713.72</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.22</v>
+        <v>-18.72</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="74">
@@ -4246,31 +4246,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1282</v>
+        <v>1225.3</v>
       </c>
       <c r="D74" t="n">
         <v>1337.1</v>
       </c>
       <c r="E74" t="n">
-        <v>-55.1</v>
+        <v>-111.8</v>
       </c>
       <c r="F74" t="n">
-        <v>1298.5</v>
+        <v>1244</v>
       </c>
       <c r="G74" t="n">
         <v>1337.1</v>
       </c>
       <c r="H74" t="n">
-        <v>-38.6</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>1236.7</v>
+        <v>1222.6</v>
       </c>
       <c r="J74" t="n">
         <v>1282</v>
       </c>
       <c r="K74" t="n">
-        <v>-45.3</v>
+        <v>-59.4</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>4.12</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -4298,31 +4298,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>621.8</v>
+        <v>630.65</v>
       </c>
       <c r="D75" t="n">
         <v>608.64</v>
       </c>
       <c r="E75" t="n">
-        <v>13.16</v>
+        <v>22.01</v>
       </c>
       <c r="F75" t="n">
-        <v>630.75</v>
+        <v>643.95</v>
       </c>
       <c r="G75" t="n">
         <v>635.02</v>
       </c>
       <c r="H75" t="n">
-        <v>-4.27</v>
+        <v>8.93</v>
       </c>
       <c r="I75" t="n">
-        <v>610.6</v>
+        <v>602.45</v>
       </c>
       <c r="J75" t="n">
         <v>614.85</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.25</v>
+        <v>-12.4</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4331,11 +4331,11 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.16</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="76">
@@ -4350,31 +4350,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>181.14</v>
+        <v>183.6</v>
       </c>
       <c r="D76" t="n">
         <v>181.4</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.26</v>
+        <v>2.2</v>
       </c>
       <c r="F76" t="n">
-        <v>185.74</v>
+        <v>184.9</v>
       </c>
       <c r="G76" t="n">
         <v>186.9</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.16</v>
+        <v>-2</v>
       </c>
       <c r="I76" t="n">
-        <v>179.94</v>
+        <v>180</v>
       </c>
       <c r="J76" t="n">
         <v>181.03</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.09</v>
+        <v>-1.03</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.14</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="77">
@@ -4402,31 +4402,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7975</v>
+        <v>8020</v>
       </c>
       <c r="D77" t="n">
         <v>8058.01</v>
       </c>
       <c r="E77" t="n">
-        <v>-83.01000000000001</v>
+        <v>-38.01</v>
       </c>
       <c r="F77" t="n">
-        <v>8024</v>
+        <v>8067.5</v>
       </c>
       <c r="G77" t="n">
         <v>8202.75</v>
       </c>
       <c r="H77" t="n">
-        <v>-178.75</v>
+        <v>-135.25</v>
       </c>
       <c r="I77" t="n">
-        <v>7938</v>
+        <v>7920</v>
       </c>
       <c r="J77" t="n">
         <v>7944.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.32</v>
+        <v>-24.32</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.03</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="78">
@@ -4454,31 +4454,31 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1943</v>
+        <v>1959.9</v>
       </c>
       <c r="D78" t="n">
         <v>1940.93</v>
       </c>
       <c r="E78" t="n">
-        <v>2.07</v>
+        <v>18.97</v>
       </c>
       <c r="F78" t="n">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="G78" t="n">
         <v>1991.14</v>
       </c>
       <c r="H78" t="n">
-        <v>-32.14</v>
+        <v>-30.14</v>
       </c>
       <c r="I78" t="n">
-        <v>1935</v>
+        <v>1938.3</v>
       </c>
       <c r="J78" t="n">
         <v>1928.16</v>
       </c>
       <c r="K78" t="n">
-        <v>6.84</v>
+        <v>10.14</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="79">
@@ -4506,31 +4506,31 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>789.45</v>
+        <v>787.5</v>
       </c>
       <c r="D79" t="n">
         <v>807.13</v>
       </c>
       <c r="E79" t="n">
-        <v>-17.68</v>
+        <v>-19.63</v>
       </c>
       <c r="F79" t="n">
-        <v>798.4</v>
+        <v>801.05</v>
       </c>
       <c r="G79" t="n">
         <v>807.13</v>
       </c>
       <c r="H79" t="n">
-        <v>-8.73</v>
+        <v>-6.08</v>
       </c>
       <c r="I79" t="n">
-        <v>780.05</v>
+        <v>778.05</v>
       </c>
       <c r="J79" t="n">
         <v>776.51</v>
       </c>
       <c r="K79" t="n">
-        <v>3.54</v>
+        <v>1.54</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="80">
@@ -4558,13 +4558,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>280</v>
+        <v>280.6</v>
       </c>
       <c r="D80" t="n">
         <v>282.47</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.47</v>
+        <v>-1.87</v>
       </c>
       <c r="F80" t="n">
         <v>280.6</v>
@@ -4576,13 +4576,13 @@
         <v>-1.87</v>
       </c>
       <c r="I80" t="n">
-        <v>275.5</v>
+        <v>275.4</v>
       </c>
       <c r="J80" t="n">
         <v>273.61</v>
       </c>
       <c r="K80" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="81">
@@ -4610,31 +4610,31 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12038</v>
+        <v>12105</v>
       </c>
       <c r="D81" t="n">
         <v>12000.09</v>
       </c>
       <c r="E81" t="n">
-        <v>37.91</v>
+        <v>104.91</v>
       </c>
       <c r="F81" t="n">
-        <v>12124</v>
+        <v>12105</v>
       </c>
       <c r="G81" t="n">
         <v>12345.48</v>
       </c>
       <c r="H81" t="n">
-        <v>-221.48</v>
+        <v>-240.48</v>
       </c>
       <c r="I81" t="n">
-        <v>11921</v>
+        <v>11970</v>
       </c>
       <c r="J81" t="n">
         <v>11955.31</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.31</v>
+        <v>14.69</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="82">
@@ -4662,31 +4662,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1175.6</v>
+        <v>1168.1</v>
       </c>
       <c r="D82" t="n">
         <v>1201.99</v>
       </c>
       <c r="E82" t="n">
-        <v>-26.39</v>
+        <v>-33.89</v>
       </c>
       <c r="F82" t="n">
-        <v>1189.9</v>
+        <v>1192.8</v>
       </c>
       <c r="G82" t="n">
         <v>1201.99</v>
       </c>
       <c r="H82" t="n">
-        <v>-12.09</v>
+        <v>-9.19</v>
       </c>
       <c r="I82" t="n">
-        <v>1161.7</v>
+        <v>1151</v>
       </c>
       <c r="J82" t="n">
         <v>1148.12</v>
       </c>
       <c r="K82" t="n">
-        <v>13.58</v>
+        <v>2.88</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="83">
@@ -4714,31 +4714,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2108.4</v>
+        <v>2070</v>
       </c>
       <c r="D83" t="n">
         <v>2173.9</v>
       </c>
       <c r="E83" t="n">
-        <v>-65.5</v>
+        <v>-103.9</v>
       </c>
       <c r="F83" t="n">
-        <v>2120</v>
+        <v>2108.6</v>
       </c>
       <c r="G83" t="n">
         <v>2173.9</v>
       </c>
       <c r="H83" t="n">
-        <v>-53.9</v>
+        <v>-65.3</v>
       </c>
       <c r="I83" t="n">
-        <v>2057.6</v>
+        <v>2062.3</v>
       </c>
       <c r="J83" t="n">
         <v>2031.51</v>
       </c>
       <c r="K83" t="n">
-        <v>26.09</v>
+        <v>30.79</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>3.01</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="84">
@@ -4766,31 +4766,31 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>310.25</v>
+        <v>315</v>
       </c>
       <c r="D84" t="n">
         <v>312.85</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.6</v>
+        <v>2.15</v>
       </c>
       <c r="F84" t="n">
-        <v>316.25</v>
+        <v>316.9</v>
       </c>
       <c r="G84" t="n">
         <v>317.62</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.37</v>
+        <v>-0.72</v>
       </c>
       <c r="I84" t="n">
-        <v>309.5</v>
+        <v>313.15</v>
       </c>
       <c r="J84" t="n">
         <v>307.57</v>
       </c>
       <c r="K84" t="n">
-        <v>1.93</v>
+        <v>5.58</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -4818,31 +4818,31 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2021.3</v>
+        <v>2008.9</v>
       </c>
       <c r="D85" t="n">
         <v>2088.35</v>
       </c>
       <c r="E85" t="n">
-        <v>-67.05</v>
+        <v>-79.45</v>
       </c>
       <c r="F85" t="n">
-        <v>2037.1</v>
+        <v>2050</v>
       </c>
       <c r="G85" t="n">
         <v>2088.35</v>
       </c>
       <c r="H85" t="n">
-        <v>-51.25</v>
+        <v>-38.35</v>
       </c>
       <c r="I85" t="n">
-        <v>1992.6</v>
+        <v>1988</v>
       </c>
       <c r="J85" t="n">
         <v>1968.33</v>
       </c>
       <c r="K85" t="n">
-        <v>24.27</v>
+        <v>19.67</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="86">
@@ -4870,31 +4870,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>14115</v>
+        <v>14200</v>
       </c>
       <c r="D86" t="n">
         <v>14353.98</v>
       </c>
       <c r="E86" t="n">
-        <v>-238.98</v>
+        <v>-153.98</v>
       </c>
       <c r="F86" t="n">
-        <v>14271</v>
+        <v>14294</v>
       </c>
       <c r="G86" t="n">
         <v>14353.98</v>
       </c>
       <c r="H86" t="n">
-        <v>-82.98</v>
+        <v>-59.98</v>
       </c>
       <c r="I86" t="n">
-        <v>14001</v>
+        <v>14050</v>
       </c>
       <c r="J86" t="n">
         <v>13803.1</v>
       </c>
       <c r="K86" t="n">
-        <v>197.9</v>
+        <v>246.9</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="87">
@@ -4922,31 +4922,31 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>501.9</v>
+        <v>505.2</v>
       </c>
       <c r="D87" t="n">
         <v>512.49</v>
       </c>
       <c r="E87" t="n">
-        <v>-10.59</v>
+        <v>-7.29</v>
       </c>
       <c r="F87" t="n">
-        <v>507.4</v>
+        <v>513.9</v>
       </c>
       <c r="G87" t="n">
         <v>512.49</v>
       </c>
       <c r="H87" t="n">
-        <v>-5.09</v>
+        <v>1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>498.25</v>
+        <v>505.2</v>
       </c>
       <c r="J87" t="n">
         <v>487.96</v>
       </c>
       <c r="K87" t="n">
-        <v>10.29</v>
+        <v>17.24</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -5372,31 +5372,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24583.8</v>
+        <v>24570.65</v>
       </c>
       <c r="D8" t="n">
         <v>24583.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-13.15</v>
       </c>
       <c r="F8" t="n">
-        <v>24620.95</v>
+        <v>24630.4</v>
       </c>
       <c r="G8" t="n">
         <v>24632.8</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.85</v>
+        <v>-2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>24511.1</v>
+        <v>24522.75</v>
       </c>
       <c r="J8" t="n">
         <v>24522.95</v>
       </c>
       <c r="K8" t="n">
-        <v>-11.85</v>
+        <v>-0.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -5424,31 +5424,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57686.95</v>
+        <v>57746.45</v>
       </c>
       <c r="D9" t="n">
         <v>57686.95</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="F9" t="n">
-        <v>58015.85</v>
+        <v>57994.45</v>
       </c>
       <c r="G9" t="n">
         <v>57959.29</v>
       </c>
       <c r="H9" t="n">
-        <v>56.56</v>
+        <v>35.16</v>
       </c>
       <c r="I9" t="n">
-        <v>57527.75</v>
+        <v>57686.55</v>
       </c>
       <c r="J9" t="n">
         <v>57471.19</v>
       </c>
       <c r="K9" t="n">
-        <v>56.56</v>
+        <v>215.36</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -8838,31 +8838,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4080</v>
+        <v>4056</v>
       </c>
       <c r="D65" t="n">
         <v>4129.22</v>
       </c>
       <c r="E65" t="n">
-        <v>-49.22</v>
+        <v>-73.22</v>
       </c>
       <c r="F65" t="n">
-        <v>4080</v>
+        <v>4062</v>
       </c>
       <c r="G65" t="n">
         <v>4168.72</v>
       </c>
       <c r="H65" t="n">
-        <v>-88.72</v>
+        <v>-106.72</v>
       </c>
       <c r="I65" t="n">
-        <v>4025.8</v>
+        <v>4030</v>
       </c>
       <c r="J65" t="n">
         <v>4050.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-24.43</v>
+        <v>-20.23</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.19</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="66">
@@ -8890,31 +8890,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3517</v>
+        <v>3502</v>
       </c>
       <c r="D66" t="n">
         <v>3513.87</v>
       </c>
       <c r="E66" t="n">
-        <v>3.13</v>
+        <v>-11.87</v>
       </c>
       <c r="F66" t="n">
-        <v>3534.6</v>
+        <v>3504.9</v>
       </c>
       <c r="G66" t="n">
         <v>3636.64</v>
       </c>
       <c r="H66" t="n">
-        <v>-102.04</v>
+        <v>-131.74</v>
       </c>
       <c r="I66" t="n">
-        <v>3491.1</v>
+        <v>3402.1</v>
       </c>
       <c r="J66" t="n">
         <v>3458.88</v>
       </c>
       <c r="K66" t="n">
-        <v>32.22</v>
+        <v>-56.78</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="67">
@@ -8942,31 +8942,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1810</v>
+        <v>1776</v>
       </c>
       <c r="D67" t="n">
         <v>1914.32</v>
       </c>
       <c r="E67" t="n">
-        <v>-104.32</v>
+        <v>-138.32</v>
       </c>
       <c r="F67" t="n">
-        <v>1822.6</v>
+        <v>1809</v>
       </c>
       <c r="G67" t="n">
         <v>1887.25</v>
       </c>
       <c r="H67" t="n">
-        <v>-64.65000000000001</v>
+        <v>-78.25</v>
       </c>
       <c r="I67" t="n">
-        <v>1783.1</v>
+        <v>1765.5</v>
       </c>
       <c r="J67" t="n">
         <v>1768.3</v>
       </c>
       <c r="K67" t="n">
-        <v>14.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5.45</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="68">
@@ -8994,31 +8994,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>113.5</v>
+        <v>114.81</v>
       </c>
       <c r="D68" t="n">
         <v>114.99</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.49</v>
+        <v>-0.18</v>
       </c>
       <c r="F68" t="n">
-        <v>115.19</v>
+        <v>115.37</v>
       </c>
       <c r="G68" t="n">
         <v>115.95</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.76</v>
+        <v>-0.58</v>
       </c>
       <c r="I68" t="n">
-        <v>113.2</v>
+        <v>113.6</v>
       </c>
       <c r="J68" t="n">
         <v>112.68</v>
       </c>
       <c r="K68" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.3</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="69">
@@ -9046,31 +9046,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="D69" t="n">
         <v>5682.41</v>
       </c>
       <c r="E69" t="n">
-        <v>-208.41</v>
+        <v>-207.41</v>
       </c>
       <c r="F69" t="n">
-        <v>5543.5</v>
+        <v>5594</v>
       </c>
       <c r="G69" t="n">
         <v>5709.63</v>
       </c>
       <c r="H69" t="n">
-        <v>-166.13</v>
+        <v>-115.63</v>
       </c>
       <c r="I69" t="n">
-        <v>5425</v>
+        <v>5448.5</v>
       </c>
       <c r="J69" t="n">
         <v>5346.37</v>
       </c>
       <c r="K69" t="n">
-        <v>78.63</v>
+        <v>102.13</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="70">
@@ -9098,31 +9098,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D70" t="n">
         <v>1703.12</v>
       </c>
       <c r="E70" t="n">
-        <v>-63.12</v>
+        <v>-68.12</v>
       </c>
       <c r="F70" t="n">
-        <v>1665.9</v>
+        <v>1681.5</v>
       </c>
       <c r="G70" t="n">
         <v>1694.65</v>
       </c>
       <c r="H70" t="n">
-        <v>-28.75</v>
+        <v>-13.15</v>
       </c>
       <c r="I70" t="n">
-        <v>1630.8</v>
+        <v>1634.3</v>
       </c>
       <c r="J70" t="n">
         <v>1613.75</v>
       </c>
       <c r="K70" t="n">
-        <v>17.05</v>
+        <v>20.55</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -9150,31 +9150,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5333.5</v>
+        <v>5333</v>
       </c>
       <c r="D71" t="n">
         <v>5509.7</v>
       </c>
       <c r="E71" t="n">
-        <v>-176.2</v>
+        <v>-176.7</v>
       </c>
       <c r="F71" t="n">
-        <v>5355</v>
+        <v>5367.5</v>
       </c>
       <c r="G71" t="n">
         <v>5520.5</v>
       </c>
       <c r="H71" t="n">
-        <v>-165.5</v>
+        <v>-153</v>
       </c>
       <c r="I71" t="n">
-        <v>5297</v>
+        <v>5281</v>
       </c>
       <c r="J71" t="n">
         <v>5241.17</v>
       </c>
       <c r="K71" t="n">
-        <v>55.83</v>
+        <v>39.83</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="72">
@@ -9202,31 +9202,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1467.7</v>
+        <v>1463.8</v>
       </c>
       <c r="D72" t="n">
         <v>1511.8</v>
       </c>
       <c r="E72" t="n">
-        <v>-44.1</v>
+        <v>-48</v>
       </c>
       <c r="F72" t="n">
-        <v>1483.7</v>
+        <v>1477</v>
       </c>
       <c r="G72" t="n">
         <v>1511.37</v>
       </c>
       <c r="H72" t="n">
-        <v>-27.67</v>
+        <v>-34.37</v>
       </c>
       <c r="I72" t="n">
-        <v>1462</v>
+        <v>1462.1</v>
       </c>
       <c r="J72" t="n">
         <v>1448.15</v>
       </c>
       <c r="K72" t="n">
-        <v>13.85</v>
+        <v>13.95</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="73">
@@ -9254,31 +9254,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2750</v>
+        <v>2735</v>
       </c>
       <c r="D73" t="n">
         <v>2879.42</v>
       </c>
       <c r="E73" t="n">
-        <v>-129.42</v>
+        <v>-144.42</v>
       </c>
       <c r="F73" t="n">
-        <v>2761.5</v>
+        <v>2755</v>
       </c>
       <c r="G73" t="n">
         <v>2834.2</v>
       </c>
       <c r="H73" t="n">
-        <v>-72.7</v>
+        <v>-79.2</v>
       </c>
       <c r="I73" t="n">
-        <v>2713.5</v>
+        <v>2695</v>
       </c>
       <c r="J73" t="n">
         <v>2711.59</v>
       </c>
       <c r="K73" t="n">
-        <v>1.91</v>
+        <v>-16.59</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>4.49</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="74">
@@ -9306,31 +9306,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1282</v>
+        <v>1225.3</v>
       </c>
       <c r="D74" t="n">
         <v>1362.46</v>
       </c>
       <c r="E74" t="n">
-        <v>-80.45999999999999</v>
+        <v>-137.16</v>
       </c>
       <c r="F74" t="n">
-        <v>1298.5</v>
+        <v>1244</v>
       </c>
       <c r="G74" t="n">
         <v>1328.71</v>
       </c>
       <c r="H74" t="n">
-        <v>-30.21</v>
+        <v>-84.70999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>1236.7</v>
+        <v>1222.6</v>
       </c>
       <c r="J74" t="n">
         <v>1258.48</v>
       </c>
       <c r="K74" t="n">
-        <v>-21.78</v>
+        <v>-35.88</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>5.91</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="75">
@@ -9358,31 +9358,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>621.8</v>
+        <v>630.65</v>
       </c>
       <c r="D75" t="n">
         <v>632.96</v>
       </c>
       <c r="E75" t="n">
-        <v>-11.16</v>
+        <v>-2.31</v>
       </c>
       <c r="F75" t="n">
-        <v>630.75</v>
+        <v>643.95</v>
       </c>
       <c r="G75" t="n">
         <v>651.47</v>
       </c>
       <c r="H75" t="n">
-        <v>-20.72</v>
+        <v>-7.52</v>
       </c>
       <c r="I75" t="n">
-        <v>610.6</v>
+        <v>602.45</v>
       </c>
       <c r="J75" t="n">
         <v>605.11</v>
       </c>
       <c r="K75" t="n">
-        <v>5.49</v>
+        <v>-2.66</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.76</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="76">
@@ -9410,31 +9410,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>789.45</v>
+        <v>787.5</v>
       </c>
       <c r="D76" t="n">
         <v>829.51</v>
       </c>
       <c r="E76" t="n">
-        <v>-40.06</v>
+        <v>-42.01</v>
       </c>
       <c r="F76" t="n">
-        <v>798.4</v>
+        <v>801.05</v>
       </c>
       <c r="G76" t="n">
         <v>817.78</v>
       </c>
       <c r="H76" t="n">
-        <v>-19.38</v>
+        <v>-16.73</v>
       </c>
       <c r="I76" t="n">
-        <v>780.05</v>
+        <v>778.05</v>
       </c>
       <c r="J76" t="n">
         <v>775.3</v>
       </c>
       <c r="K76" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>4.83</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="77">
@@ -9462,31 +9462,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>181.14</v>
+        <v>183.6</v>
       </c>
       <c r="D77" t="n">
         <v>185.51</v>
       </c>
       <c r="E77" t="n">
-        <v>-4.37</v>
+        <v>-1.91</v>
       </c>
       <c r="F77" t="n">
-        <v>185.74</v>
+        <v>184.9</v>
       </c>
       <c r="G77" t="n">
         <v>187.2</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.46</v>
+        <v>-2.3</v>
       </c>
       <c r="I77" t="n">
-        <v>179.94</v>
+        <v>180</v>
       </c>
       <c r="J77" t="n">
         <v>178.23</v>
       </c>
       <c r="K77" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.36</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="78">
@@ -9514,31 +9514,31 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12038</v>
+        <v>12105</v>
       </c>
       <c r="D78" t="n">
         <v>12179.11</v>
       </c>
       <c r="E78" t="n">
-        <v>-141.11</v>
+        <v>-74.11</v>
       </c>
       <c r="F78" t="n">
-        <v>12124</v>
+        <v>12105</v>
       </c>
       <c r="G78" t="n">
         <v>12320.53</v>
       </c>
       <c r="H78" t="n">
-        <v>-196.53</v>
+        <v>-215.53</v>
       </c>
       <c r="I78" t="n">
-        <v>11921</v>
+        <v>11970</v>
       </c>
       <c r="J78" t="n">
         <v>11934.56</v>
       </c>
       <c r="K78" t="n">
-        <v>-13.56</v>
+        <v>35.44</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.16</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="79">
@@ -9566,31 +9566,31 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1175.6</v>
+        <v>1168.1</v>
       </c>
       <c r="D79" t="n">
         <v>1236.99</v>
       </c>
       <c r="E79" t="n">
-        <v>-61.39</v>
+        <v>-68.89</v>
       </c>
       <c r="F79" t="n">
-        <v>1189.9</v>
+        <v>1192.8</v>
       </c>
       <c r="G79" t="n">
         <v>1219.36</v>
       </c>
       <c r="H79" t="n">
-        <v>-29.46</v>
+        <v>-26.56</v>
       </c>
       <c r="I79" t="n">
-        <v>1161.7</v>
+        <v>1151</v>
       </c>
       <c r="J79" t="n">
         <v>1153.35</v>
       </c>
       <c r="K79" t="n">
-        <v>8.35</v>
+        <v>-2.35</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>4.96</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="80">
@@ -9618,31 +9618,31 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7975</v>
+        <v>8020</v>
       </c>
       <c r="D80" t="n">
         <v>8215.84</v>
       </c>
       <c r="E80" t="n">
-        <v>-240.84</v>
+        <v>-195.84</v>
       </c>
       <c r="F80" t="n">
-        <v>8024</v>
+        <v>8067.5</v>
       </c>
       <c r="G80" t="n">
         <v>8198.24</v>
       </c>
       <c r="H80" t="n">
-        <v>-174.24</v>
+        <v>-130.74</v>
       </c>
       <c r="I80" t="n">
-        <v>7938</v>
+        <v>7920</v>
       </c>
       <c r="J80" t="n">
         <v>7879.34</v>
       </c>
       <c r="K80" t="n">
-        <v>58.66</v>
+        <v>40.66</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="81">
@@ -9670,31 +9670,31 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1943</v>
+        <v>1959.9</v>
       </c>
       <c r="D81" t="n">
         <v>1970.16</v>
       </c>
       <c r="E81" t="n">
-        <v>-27.16</v>
+        <v>-10.26</v>
       </c>
       <c r="F81" t="n">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="G81" t="n">
         <v>1988.85</v>
       </c>
       <c r="H81" t="n">
-        <v>-29.85</v>
+        <v>-27.85</v>
       </c>
       <c r="I81" t="n">
-        <v>1935</v>
+        <v>1938.3</v>
       </c>
       <c r="J81" t="n">
         <v>1926.11</v>
       </c>
       <c r="K81" t="n">
-        <v>8.890000000000001</v>
+        <v>12.19</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.38</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="82">
@@ -9722,31 +9722,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2108.4</v>
+        <v>2070</v>
       </c>
       <c r="D82" t="n">
         <v>2252.16</v>
       </c>
       <c r="E82" t="n">
-        <v>-143.76</v>
+        <v>-182.16</v>
       </c>
       <c r="F82" t="n">
-        <v>2120</v>
+        <v>2108.6</v>
       </c>
       <c r="G82" t="n">
         <v>2200.95</v>
       </c>
       <c r="H82" t="n">
-        <v>-80.95</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>2057.6</v>
+        <v>2062.3</v>
       </c>
       <c r="J82" t="n">
         <v>2057.89</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.29</v>
+        <v>4.41</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>6.38</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="83">
@@ -9774,31 +9774,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2021.3</v>
+        <v>2008.9</v>
       </c>
       <c r="D83" t="n">
         <v>2141.48</v>
       </c>
       <c r="E83" t="n">
-        <v>-120.18</v>
+        <v>-132.58</v>
       </c>
       <c r="F83" t="n">
-        <v>2037.1</v>
+        <v>2050</v>
       </c>
       <c r="G83" t="n">
         <v>2089.35</v>
       </c>
       <c r="H83" t="n">
-        <v>-52.25</v>
+        <v>-39.35</v>
       </c>
       <c r="I83" t="n">
-        <v>1992.6</v>
+        <v>1988</v>
       </c>
       <c r="J83" t="n">
         <v>1988.44</v>
       </c>
       <c r="K83" t="n">
-        <v>4.16</v>
+        <v>-0.44</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>5.61</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="84">
@@ -9826,13 +9826,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>280</v>
+        <v>280.6</v>
       </c>
       <c r="D84" t="n">
         <v>288.68</v>
       </c>
       <c r="E84" t="n">
-        <v>-8.68</v>
+        <v>-8.08</v>
       </c>
       <c r="F84" t="n">
         <v>280.6</v>
@@ -9844,13 +9844,13 @@
         <v>-7.88</v>
       </c>
       <c r="I84" t="n">
-        <v>275.5</v>
+        <v>275.4</v>
       </c>
       <c r="J84" t="n">
         <v>276.16</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.66</v>
+        <v>-0.76</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="85">
@@ -9878,31 +9878,31 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>310.25</v>
+        <v>315</v>
       </c>
       <c r="D85" t="n">
         <v>323.6</v>
       </c>
       <c r="E85" t="n">
-        <v>-13.35</v>
+        <v>-8.6</v>
       </c>
       <c r="F85" t="n">
-        <v>316.25</v>
+        <v>316.9</v>
       </c>
       <c r="G85" t="n">
         <v>323.38</v>
       </c>
       <c r="H85" t="n">
-        <v>-7.13</v>
+        <v>-6.48</v>
       </c>
       <c r="I85" t="n">
-        <v>309.5</v>
+        <v>313.15</v>
       </c>
       <c r="J85" t="n">
         <v>303.19</v>
       </c>
       <c r="K85" t="n">
-        <v>6.31</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>4.13</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="86">
@@ -9930,31 +9930,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>14115</v>
+        <v>14200</v>
       </c>
       <c r="D86" t="n">
         <v>14784.36</v>
       </c>
       <c r="E86" t="n">
-        <v>-669.36</v>
+        <v>-584.36</v>
       </c>
       <c r="F86" t="n">
-        <v>14271</v>
+        <v>14294</v>
       </c>
       <c r="G86" t="n">
         <v>14652.3</v>
       </c>
       <c r="H86" t="n">
-        <v>-381.3</v>
+        <v>-358.3</v>
       </c>
       <c r="I86" t="n">
-        <v>14001</v>
+        <v>14050</v>
       </c>
       <c r="J86" t="n">
         <v>13838.77</v>
       </c>
       <c r="K86" t="n">
-        <v>162.23</v>
+        <v>211.23</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="87">
@@ -9982,31 +9982,31 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>501.9</v>
+        <v>505.2</v>
       </c>
       <c r="D87" t="n">
         <v>526.34</v>
       </c>
       <c r="E87" t="n">
-        <v>-24.44</v>
+        <v>-21.14</v>
       </c>
       <c r="F87" t="n">
-        <v>507.4</v>
+        <v>513.9</v>
       </c>
       <c r="G87" t="n">
         <v>519.58</v>
       </c>
       <c r="H87" t="n">
-        <v>-12.18</v>
+        <v>-5.68</v>
       </c>
       <c r="I87" t="n">
-        <v>498.25</v>
+        <v>505.2</v>
       </c>
       <c r="J87" t="n">
         <v>493.15</v>
       </c>
       <c r="K87" t="n">
-        <v>5.1</v>
+        <v>12.05</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>4.64</v>
+        <v>4.02</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4960,6 +4960,1150 @@
       </c>
       <c r="N87" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>114.03</v>
+      </c>
+      <c r="D88" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F88" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G88" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="I88" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>112.08</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5865.5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>5786.78</v>
+      </c>
+      <c r="E89" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5937</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5786.78</v>
+      </c>
+      <c r="H89" t="n">
+        <v>150.22</v>
+      </c>
+      <c r="I89" t="n">
+        <v>5803.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>5685.21</v>
+      </c>
+      <c r="K89" t="n">
+        <v>118.29</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5536</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5565.45</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-29.45</v>
+      </c>
+      <c r="F90" t="n">
+        <v>5544</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5565.45</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-21.45</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5430.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5454.18</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-23.68</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>318</v>
+      </c>
+      <c r="D91" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="F91" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="I91" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8025.94</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-25.94</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8110</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8025.94</v>
+      </c>
+      <c r="H92" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="I92" t="n">
+        <v>7955</v>
+      </c>
+      <c r="J92" t="n">
+        <v>7857.46</v>
+      </c>
+      <c r="K92" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1257.89</v>
+      </c>
+      <c r="E93" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1287.36</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1267</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1265.88</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1633.2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1660.3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1663.74</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1636.14</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="F95" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="G95" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="I95" t="n">
+        <v>179.88</v>
+      </c>
+      <c r="J95" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1760.17</v>
+      </c>
+      <c r="E96" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1836</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1792.28</v>
+      </c>
+      <c r="H96" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1809.8</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1760.84</v>
+      </c>
+      <c r="K96" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1256.26</v>
+      </c>
+      <c r="E97" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1391</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1356.17</v>
+      </c>
+      <c r="H97" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1332.95</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-41.85</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11780</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11978.02</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-198.02</v>
+      </c>
+      <c r="F98" t="n">
+        <v>12061</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11978.02</v>
+      </c>
+      <c r="H98" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I98" t="n">
+        <v>11720</v>
+      </c>
+      <c r="J98" t="n">
+        <v>11592.49</v>
+      </c>
+      <c r="K98" t="n">
+        <v>127.51</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5284</v>
+      </c>
+      <c r="D99" t="n">
+        <v>5294.05</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-10.05</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5330</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5294.05</v>
+      </c>
+      <c r="H99" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5217.5</v>
+      </c>
+      <c r="J99" t="n">
+        <v>5178.33</v>
+      </c>
+      <c r="K99" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4037.4</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4050.04</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-12.64</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4075.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4060.6</v>
+      </c>
+      <c r="H100" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I100" t="n">
+        <v>4028.5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4004.16</v>
+      </c>
+      <c r="K100" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2735.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2677.47</v>
+      </c>
+      <c r="E101" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2747.6</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2749.07</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2702.76</v>
+      </c>
+      <c r="K101" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>3460.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3565.7</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-105.6</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3514.6</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3565.7</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3455.1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>3358.06</v>
+      </c>
+      <c r="K102" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>616</v>
+      </c>
+      <c r="D103" t="n">
+        <v>643.38</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-27.38</v>
+      </c>
+      <c r="F103" t="n">
+        <v>627</v>
+      </c>
+      <c r="G103" t="n">
+        <v>643.38</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-16.38</v>
+      </c>
+      <c r="I103" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>594.71</v>
+      </c>
+      <c r="K103" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1458.43</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1469.8</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1458.71</v>
+      </c>
+      <c r="H104" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1457.2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1433.73</v>
+      </c>
+      <c r="K104" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>512</v>
+      </c>
+      <c r="D105" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F105" t="n">
+        <v>512</v>
+      </c>
+      <c r="G105" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I105" t="n">
+        <v>498.75</v>
+      </c>
+      <c r="J105" t="n">
+        <v>496.52</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>788</v>
+      </c>
+      <c r="D106" t="n">
+        <v>774.98</v>
+      </c>
+      <c r="E106" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F106" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>793.28</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="I106" t="n">
+        <v>784.05</v>
+      </c>
+      <c r="J106" t="n">
+        <v>779.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1144.15</v>
+      </c>
+      <c r="E107" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1176.7</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="H107" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1147.8</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1150.17</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1970.34</v>
+      </c>
+      <c r="E108" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2043.9</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2015.42</v>
+      </c>
+      <c r="H108" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1980.53</v>
+      </c>
+      <c r="K108" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>14023</v>
+      </c>
+      <c r="D109" t="n">
+        <v>13983.51</v>
+      </c>
+      <c r="E109" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="F109" t="n">
+        <v>14198</v>
+      </c>
+      <c r="G109" t="n">
+        <v>13983.51</v>
+      </c>
+      <c r="H109" t="n">
+        <v>214.49</v>
+      </c>
+      <c r="I109" t="n">
+        <v>14011</v>
+      </c>
+      <c r="J109" t="n">
+        <v>13569.36</v>
+      </c>
+      <c r="K109" t="n">
+        <v>441.64</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -4973,7 +6117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5462,6 +6606,110 @@
       </c>
       <c r="N9" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24576.85</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24555.95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24429.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24408.35</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>57607.25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>57649.64</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-42.39</v>
+      </c>
+      <c r="I11" t="n">
+        <v>57158.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>57200.49</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-42.39</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5475,7 +6723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10022,6 +11270,1150 @@
         <v>4.02</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5865.5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>5942.75</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-77.25</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5937</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5961.19</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-24.19</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5803.5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5745.52</v>
+      </c>
+      <c r="K88" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>114.03</v>
+      </c>
+      <c r="D89" t="n">
+        <v>117.73</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="F89" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>114.37</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I89" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5536</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5756.99</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-220.99</v>
+      </c>
+      <c r="F90" t="n">
+        <v>5544</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5665.61</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-121.61</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5430.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5392.75</v>
+      </c>
+      <c r="K90" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1288.55</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-13.55</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1292.67</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1267</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1251.31</v>
+      </c>
+      <c r="K91" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1821.49</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1836</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1862.32</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-26.32</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1809.8</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1771.37</v>
+      </c>
+      <c r="K92" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1669.93</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-26.93</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1660.3</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1666.17</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1612.18</v>
+      </c>
+      <c r="K93" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>318</v>
+      </c>
+      <c r="D94" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-15.72</v>
+      </c>
+      <c r="F94" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="I94" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>309.87</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>190.82</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="F95" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="G95" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I95" t="n">
+        <v>179.88</v>
+      </c>
+      <c r="J95" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D96" t="n">
+        <v>8177.27</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-177.27</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8110</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8068.89</v>
+      </c>
+      <c r="H96" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7955</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7883.41</v>
+      </c>
+      <c r="K96" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1292.75</v>
+      </c>
+      <c r="E97" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1391</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1384.9</v>
+      </c>
+      <c r="H97" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-39</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11780</v>
+      </c>
+      <c r="D98" t="n">
+        <v>12160.68</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-380.68</v>
+      </c>
+      <c r="F98" t="n">
+        <v>12061</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11841.03</v>
+      </c>
+      <c r="H98" t="n">
+        <v>219.97</v>
+      </c>
+      <c r="I98" t="n">
+        <v>11720</v>
+      </c>
+      <c r="J98" t="n">
+        <v>11639.18</v>
+      </c>
+      <c r="K98" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5284</v>
+      </c>
+      <c r="D99" t="n">
+        <v>5434.61</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-150.61</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5330</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5368.18</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-38.18</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5217.5</v>
+      </c>
+      <c r="J99" t="n">
+        <v>5177.46</v>
+      </c>
+      <c r="K99" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>616</v>
+      </c>
+      <c r="D100" t="n">
+        <v>669.85</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-53.85</v>
+      </c>
+      <c r="F100" t="n">
+        <v>627</v>
+      </c>
+      <c r="G100" t="n">
+        <v>634.36</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="I100" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>597.0700000000001</v>
+      </c>
+      <c r="K100" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2735.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2738.31</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2747.6</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2769.11</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-21.51</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2687.95</v>
+      </c>
+      <c r="K101" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>4037.4</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4104.98</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-67.58</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4075.5</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4051.84</v>
+      </c>
+      <c r="H102" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="I102" t="n">
+        <v>4028.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>3994.08</v>
+      </c>
+      <c r="K102" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3460.1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3657.22</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-197.12</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3514.6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3512.32</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3455.1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>3392.55</v>
+      </c>
+      <c r="K103" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2019.29</v>
+      </c>
+      <c r="E104" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2043.9</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2061.07</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-17.17</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1993.54</v>
+      </c>
+      <c r="K104" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1489.04</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-26.04</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1469.8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1478.57</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1457.2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1439.41</v>
+      </c>
+      <c r="K105" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>512</v>
+      </c>
+      <c r="D106" t="n">
+        <v>522.21</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="F106" t="n">
+        <v>512</v>
+      </c>
+      <c r="G106" t="n">
+        <v>520.1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>498.75</v>
+      </c>
+      <c r="J106" t="n">
+        <v>501.73</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CAMS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>788</v>
+      </c>
+      <c r="D107" t="n">
+        <v>796.34</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-8.34</v>
+      </c>
+      <c r="F107" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>801.3099999999999</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="I107" t="n">
+        <v>784.05</v>
+      </c>
+      <c r="J107" t="n">
+        <v>771.53</v>
+      </c>
+      <c r="K107" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1178.26</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-10.26</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1176.7</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1190.23</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-13.53</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1147.8</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1141.68</v>
+      </c>
+      <c r="K108" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>14023</v>
+      </c>
+      <c r="D109" t="n">
+        <v>14383.7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-360.7</v>
+      </c>
+      <c r="F109" t="n">
+        <v>14198</v>
+      </c>
+      <c r="G109" t="n">
+        <v>14273.99</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-75.98999999999999</v>
+      </c>
+      <c r="I109" t="n">
+        <v>14011</v>
+      </c>
+      <c r="J109" t="n">
+        <v>13719.2</v>
+      </c>
+      <c r="K109" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -4974,31 +4974,31 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>114.03</v>
+        <v>113.5</v>
       </c>
       <c r="D88" t="n">
         <v>116.24</v>
       </c>
       <c r="E88" t="n">
-        <v>-2.21</v>
+        <v>-2.74</v>
       </c>
       <c r="F88" t="n">
-        <v>114.3</v>
+        <v>115.19</v>
       </c>
       <c r="G88" t="n">
         <v>116.24</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.94</v>
+        <v>-1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>112.3</v>
+        <v>113.2</v>
       </c>
       <c r="J88" t="n">
         <v>112.08</v>
       </c>
       <c r="K88" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="89">
@@ -5026,31 +5026,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5865.5</v>
+        <v>5860</v>
       </c>
       <c r="D89" t="n">
         <v>5786.78</v>
       </c>
       <c r="E89" t="n">
-        <v>78.72</v>
+        <v>73.22</v>
       </c>
       <c r="F89" t="n">
-        <v>5937</v>
+        <v>5933</v>
       </c>
       <c r="G89" t="n">
         <v>5786.78</v>
       </c>
       <c r="H89" t="n">
-        <v>150.22</v>
+        <v>146.22</v>
       </c>
       <c r="I89" t="n">
-        <v>5803.5</v>
+        <v>5756.5</v>
       </c>
       <c r="J89" t="n">
         <v>5685.21</v>
       </c>
       <c r="K89" t="n">
-        <v>118.29</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="90">
@@ -5078,31 +5078,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5536</v>
+        <v>5474</v>
       </c>
       <c r="D90" t="n">
         <v>5565.45</v>
       </c>
       <c r="E90" t="n">
-        <v>-29.45</v>
+        <v>-91.45</v>
       </c>
       <c r="F90" t="n">
-        <v>5544</v>
+        <v>5543.5</v>
       </c>
       <c r="G90" t="n">
         <v>5565.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-21.45</v>
+        <v>-21.95</v>
       </c>
       <c r="I90" t="n">
-        <v>5430.5</v>
+        <v>5425</v>
       </c>
       <c r="J90" t="n">
         <v>5454.18</v>
       </c>
       <c r="K90" t="n">
-        <v>-23.68</v>
+        <v>-29.18</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0.53</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="91">
@@ -5130,31 +5130,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>318</v>
+        <v>310.25</v>
       </c>
       <c r="D91" t="n">
         <v>322.74</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.74</v>
+        <v>-12.49</v>
       </c>
       <c r="F91" t="n">
-        <v>318.5</v>
+        <v>316.25</v>
       </c>
       <c r="G91" t="n">
         <v>322.74</v>
       </c>
       <c r="H91" t="n">
-        <v>-4.24</v>
+        <v>-6.49</v>
       </c>
       <c r="I91" t="n">
-        <v>306.2</v>
+        <v>309.5</v>
       </c>
       <c r="J91" t="n">
         <v>315.93</v>
       </c>
       <c r="K91" t="n">
-        <v>-9.73</v>
+        <v>-6.43</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5163,11 +5163,11 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.47</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="92">
@@ -5182,31 +5182,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8000</v>
+        <v>7975</v>
       </c>
       <c r="D92" t="n">
         <v>8025.94</v>
       </c>
       <c r="E92" t="n">
-        <v>-25.94</v>
+        <v>-50.94</v>
       </c>
       <c r="F92" t="n">
-        <v>8110</v>
+        <v>8024</v>
       </c>
       <c r="G92" t="n">
         <v>8025.94</v>
       </c>
       <c r="H92" t="n">
-        <v>84.06</v>
+        <v>-1.94</v>
       </c>
       <c r="I92" t="n">
-        <v>7955</v>
+        <v>7938</v>
       </c>
       <c r="J92" t="n">
         <v>7857.46</v>
       </c>
       <c r="K92" t="n">
-        <v>97.54000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="93">
@@ -5234,31 +5234,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="D93" t="n">
         <v>1257.89</v>
       </c>
       <c r="E93" t="n">
-        <v>17.11</v>
+        <v>30.11</v>
       </c>
       <c r="F93" t="n">
-        <v>1291.1</v>
+        <v>1298.3</v>
       </c>
       <c r="G93" t="n">
         <v>1287.36</v>
       </c>
       <c r="H93" t="n">
-        <v>3.74</v>
+        <v>10.94</v>
       </c>
       <c r="I93" t="n">
-        <v>1267</v>
+        <v>1280.7</v>
       </c>
       <c r="J93" t="n">
         <v>1265.88</v>
       </c>
       <c r="K93" t="n">
-        <v>1.12</v>
+        <v>14.82</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.36</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="94">
@@ -5286,31 +5286,31 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D94" t="n">
         <v>1633.2</v>
       </c>
       <c r="E94" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="F94" t="n">
-        <v>1660.3</v>
+        <v>1665.9</v>
       </c>
       <c r="G94" t="n">
         <v>1663.74</v>
       </c>
       <c r="H94" t="n">
-        <v>-3.44</v>
+        <v>2.16</v>
       </c>
       <c r="I94" t="n">
-        <v>1640</v>
+        <v>1630.8</v>
       </c>
       <c r="J94" t="n">
         <v>1636.14</v>
       </c>
       <c r="K94" t="n">
-        <v>3.86</v>
+        <v>-5.34</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="95">
@@ -5338,31 +5338,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>182.5</v>
+        <v>181.14</v>
       </c>
       <c r="D95" t="n">
         <v>186.19</v>
       </c>
       <c r="E95" t="n">
-        <v>-3.69</v>
+        <v>-5.05</v>
       </c>
       <c r="F95" t="n">
-        <v>184.85</v>
+        <v>185.74</v>
       </c>
       <c r="G95" t="n">
         <v>186.19</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.34</v>
+        <v>-0.45</v>
       </c>
       <c r="I95" t="n">
-        <v>179.88</v>
+        <v>179.94</v>
       </c>
       <c r="J95" t="n">
         <v>179.98</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.98</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="96">
@@ -5390,31 +5390,31 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1819</v>
+        <v>1810</v>
       </c>
       <c r="D96" t="n">
         <v>1760.17</v>
       </c>
       <c r="E96" t="n">
-        <v>58.83</v>
+        <v>49.83</v>
       </c>
       <c r="F96" t="n">
-        <v>1836</v>
+        <v>1822.6</v>
       </c>
       <c r="G96" t="n">
         <v>1792.28</v>
       </c>
       <c r="H96" t="n">
-        <v>43.72</v>
+        <v>30.32</v>
       </c>
       <c r="I96" t="n">
-        <v>1809.8</v>
+        <v>1783.1</v>
       </c>
       <c r="J96" t="n">
         <v>1760.84</v>
       </c>
       <c r="K96" t="n">
-        <v>48.96</v>
+        <v>22.26</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="97">
@@ -5442,31 +5442,31 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1360</v>
+        <v>1282</v>
       </c>
       <c r="D97" t="n">
         <v>1256.26</v>
       </c>
       <c r="E97" t="n">
-        <v>103.74</v>
+        <v>25.74</v>
       </c>
       <c r="F97" t="n">
-        <v>1391</v>
+        <v>1298.5</v>
       </c>
       <c r="G97" t="n">
         <v>1356.17</v>
       </c>
       <c r="H97" t="n">
-        <v>34.83</v>
+        <v>-57.67</v>
       </c>
       <c r="I97" t="n">
-        <v>1291.1</v>
+        <v>1236.7</v>
       </c>
       <c r="J97" t="n">
         <v>1332.95</v>
       </c>
       <c r="K97" t="n">
-        <v>-41.85</v>
+        <v>-96.25</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5475,11 +5475,11 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>8.26</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="98">
@@ -5494,31 +5494,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11780</v>
+        <v>12038</v>
       </c>
       <c r="D98" t="n">
         <v>11978.02</v>
       </c>
       <c r="E98" t="n">
-        <v>-198.02</v>
+        <v>59.98</v>
       </c>
       <c r="F98" t="n">
-        <v>12061</v>
+        <v>12124</v>
       </c>
       <c r="G98" t="n">
         <v>11978.02</v>
       </c>
       <c r="H98" t="n">
-        <v>82.98</v>
+        <v>145.98</v>
       </c>
       <c r="I98" t="n">
-        <v>11720</v>
+        <v>11921</v>
       </c>
       <c r="J98" t="n">
         <v>11592.49</v>
       </c>
       <c r="K98" t="n">
-        <v>127.51</v>
+        <v>328.51</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99">
@@ -5546,31 +5546,31 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5284</v>
+        <v>5333.5</v>
       </c>
       <c r="D99" t="n">
         <v>5294.05</v>
       </c>
       <c r="E99" t="n">
-        <v>-10.05</v>
+        <v>39.45</v>
       </c>
       <c r="F99" t="n">
-        <v>5330</v>
+        <v>5355</v>
       </c>
       <c r="G99" t="n">
         <v>5294.05</v>
       </c>
       <c r="H99" t="n">
-        <v>35.95</v>
+        <v>60.95</v>
       </c>
       <c r="I99" t="n">
-        <v>5217.5</v>
+        <v>5297</v>
       </c>
       <c r="J99" t="n">
         <v>5178.33</v>
       </c>
       <c r="K99" t="n">
-        <v>39.17</v>
+        <v>118.67</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="100">
@@ -5598,31 +5598,31 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4037.4</v>
+        <v>4080</v>
       </c>
       <c r="D100" t="n">
         <v>4050.04</v>
       </c>
       <c r="E100" t="n">
-        <v>-12.64</v>
+        <v>29.96</v>
       </c>
       <c r="F100" t="n">
-        <v>4075.5</v>
+        <v>4080</v>
       </c>
       <c r="G100" t="n">
         <v>4060.6</v>
       </c>
       <c r="H100" t="n">
-        <v>14.9</v>
+        <v>19.4</v>
       </c>
       <c r="I100" t="n">
-        <v>4028.5</v>
+        <v>4025.8</v>
       </c>
       <c r="J100" t="n">
         <v>4004.16</v>
       </c>
       <c r="K100" t="n">
-        <v>24.34</v>
+        <v>21.64</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0.31</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="101">
@@ -5650,31 +5650,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2735.5</v>
+        <v>2750</v>
       </c>
       <c r="D101" t="n">
         <v>2677.47</v>
       </c>
       <c r="E101" t="n">
-        <v>58.03</v>
+        <v>72.53</v>
       </c>
       <c r="F101" t="n">
-        <v>2747.6</v>
+        <v>2761.5</v>
       </c>
       <c r="G101" t="n">
         <v>2749.07</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.47</v>
+        <v>12.43</v>
       </c>
       <c r="I101" t="n">
-        <v>2720</v>
+        <v>2713.5</v>
       </c>
       <c r="J101" t="n">
         <v>2702.76</v>
       </c>
       <c r="K101" t="n">
-        <v>17.24</v>
+        <v>10.74</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="102">
@@ -5702,31 +5702,31 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3460.1</v>
+        <v>3517</v>
       </c>
       <c r="D102" t="n">
         <v>3565.7</v>
       </c>
       <c r="E102" t="n">
-        <v>-105.6</v>
+        <v>-48.7</v>
       </c>
       <c r="F102" t="n">
-        <v>3514.6</v>
+        <v>3534.6</v>
       </c>
       <c r="G102" t="n">
         <v>3565.7</v>
       </c>
       <c r="H102" t="n">
-        <v>-51.1</v>
+        <v>-31.1</v>
       </c>
       <c r="I102" t="n">
-        <v>3455.1</v>
+        <v>3491.1</v>
       </c>
       <c r="J102" t="n">
         <v>3358.06</v>
       </c>
       <c r="K102" t="n">
-        <v>97.04000000000001</v>
+        <v>133.04</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.96</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="103">
@@ -5754,31 +5754,31 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>616</v>
+        <v>621.8</v>
       </c>
       <c r="D103" t="n">
         <v>643.38</v>
       </c>
       <c r="E103" t="n">
-        <v>-27.38</v>
+        <v>-21.58</v>
       </c>
       <c r="F103" t="n">
-        <v>627</v>
+        <v>630.75</v>
       </c>
       <c r="G103" t="n">
         <v>643.38</v>
       </c>
       <c r="H103" t="n">
-        <v>-16.38</v>
+        <v>-12.63</v>
       </c>
       <c r="I103" t="n">
-        <v>613.1</v>
+        <v>610.6</v>
       </c>
       <c r="J103" t="n">
         <v>594.71</v>
       </c>
       <c r="K103" t="n">
-        <v>18.39</v>
+        <v>15.89</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>4.26</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="104">
@@ -5806,31 +5806,31 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1463</v>
+        <v>1467.7</v>
       </c>
       <c r="D104" t="n">
         <v>1458.43</v>
       </c>
       <c r="E104" t="n">
-        <v>4.57</v>
+        <v>9.27</v>
       </c>
       <c r="F104" t="n">
-        <v>1469.8</v>
+        <v>1483.7</v>
       </c>
       <c r="G104" t="n">
         <v>1458.71</v>
       </c>
       <c r="H104" t="n">
-        <v>11.09</v>
+        <v>24.99</v>
       </c>
       <c r="I104" t="n">
-        <v>1457.2</v>
+        <v>1462</v>
       </c>
       <c r="J104" t="n">
         <v>1433.73</v>
       </c>
       <c r="K104" t="n">
-        <v>23.47</v>
+        <v>28.27</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="105">
@@ -5858,31 +5858,31 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>512</v>
+        <v>501.9</v>
       </c>
       <c r="D105" t="n">
         <v>508.76</v>
       </c>
       <c r="E105" t="n">
-        <v>3.24</v>
+        <v>-6.86</v>
       </c>
       <c r="F105" t="n">
-        <v>512</v>
+        <v>507.4</v>
       </c>
       <c r="G105" t="n">
         <v>508.76</v>
       </c>
       <c r="H105" t="n">
-        <v>3.24</v>
+        <v>-1.36</v>
       </c>
       <c r="I105" t="n">
-        <v>498.75</v>
+        <v>498.25</v>
       </c>
       <c r="J105" t="n">
         <v>496.52</v>
       </c>
       <c r="K105" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="106">
@@ -5910,31 +5910,31 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>788</v>
+        <v>789.45</v>
       </c>
       <c r="D106" t="n">
         <v>774.98</v>
       </c>
       <c r="E106" t="n">
-        <v>13.02</v>
+        <v>14.47</v>
       </c>
       <c r="F106" t="n">
-        <v>796.5</v>
+        <v>798.4</v>
       </c>
       <c r="G106" t="n">
         <v>793.28</v>
       </c>
       <c r="H106" t="n">
-        <v>3.22</v>
+        <v>5.12</v>
       </c>
       <c r="I106" t="n">
-        <v>784.05</v>
+        <v>780.05</v>
       </c>
       <c r="J106" t="n">
         <v>779.96</v>
       </c>
       <c r="K106" t="n">
-        <v>4.09</v>
+        <v>0.09</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="107">
@@ -5962,31 +5962,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1168</v>
+        <v>1175.6</v>
       </c>
       <c r="D107" t="n">
         <v>1144.15</v>
       </c>
       <c r="E107" t="n">
-        <v>23.85</v>
+        <v>31.45</v>
       </c>
       <c r="F107" t="n">
-        <v>1176.7</v>
+        <v>1189.9</v>
       </c>
       <c r="G107" t="n">
         <v>1170.01</v>
       </c>
       <c r="H107" t="n">
-        <v>6.69</v>
+        <v>19.89</v>
       </c>
       <c r="I107" t="n">
-        <v>1147.8</v>
+        <v>1161.7</v>
       </c>
       <c r="J107" t="n">
         <v>1150.17</v>
       </c>
       <c r="K107" t="n">
-        <v>-2.37</v>
+        <v>11.53</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="108">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2032</v>
+        <v>2021.3</v>
       </c>
       <c r="D108" t="n">
         <v>1970.34</v>
       </c>
       <c r="E108" t="n">
-        <v>61.66</v>
+        <v>50.96</v>
       </c>
       <c r="F108" t="n">
-        <v>2043.9</v>
+        <v>2037.1</v>
       </c>
       <c r="G108" t="n">
         <v>2015.42</v>
       </c>
       <c r="H108" t="n">
-        <v>28.48</v>
+        <v>21.68</v>
       </c>
       <c r="I108" t="n">
-        <v>2012</v>
+        <v>1992.6</v>
       </c>
       <c r="J108" t="n">
         <v>1980.53</v>
       </c>
       <c r="K108" t="n">
-        <v>31.47</v>
+        <v>12.07</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3.13</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="109">
@@ -6066,31 +6066,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>14023</v>
+        <v>14115</v>
       </c>
       <c r="D109" t="n">
         <v>13983.51</v>
       </c>
       <c r="E109" t="n">
-        <v>39.49</v>
+        <v>131.49</v>
       </c>
       <c r="F109" t="n">
-        <v>14198</v>
+        <v>14271</v>
       </c>
       <c r="G109" t="n">
         <v>13983.51</v>
       </c>
       <c r="H109" t="n">
-        <v>214.49</v>
+        <v>287.49</v>
       </c>
       <c r="I109" t="n">
-        <v>14011</v>
+        <v>14001</v>
       </c>
       <c r="J109" t="n">
         <v>13569.36</v>
       </c>
       <c r="K109" t="n">
-        <v>441.64</v>
+        <v>431.64</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0.28</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6620,31 +6620,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24471.7</v>
+        <v>24583.8</v>
       </c>
       <c r="D10" t="n">
         <v>24471.7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>112.1</v>
       </c>
       <c r="F10" t="n">
-        <v>24576.85</v>
+        <v>24620.95</v>
       </c>
       <c r="G10" t="n">
         <v>24555.95</v>
       </c>
       <c r="H10" t="n">
-        <v>20.9</v>
+        <v>65</v>
       </c>
       <c r="I10" t="n">
-        <v>24429.25</v>
+        <v>24511.1</v>
       </c>
       <c r="J10" t="n">
         <v>24408.35</v>
       </c>
       <c r="K10" t="n">
-        <v>20.9</v>
+        <v>102.75</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="11">
@@ -6672,31 +6672,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57446.25</v>
+        <v>57686.95</v>
       </c>
       <c r="D11" t="n">
         <v>57446.25</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>240.7</v>
       </c>
       <c r="F11" t="n">
-        <v>57607.25</v>
+        <v>58015.85</v>
       </c>
       <c r="G11" t="n">
         <v>57649.64</v>
       </c>
       <c r="H11" t="n">
-        <v>-42.39</v>
+        <v>366.21</v>
       </c>
       <c r="I11" t="n">
-        <v>57158.1</v>
+        <v>57527.75</v>
       </c>
       <c r="J11" t="n">
         <v>57200.49</v>
       </c>
       <c r="K11" t="n">
-        <v>-42.39</v>
+        <v>327.26</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -11282,31 +11282,31 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5865.5</v>
+        <v>5860</v>
       </c>
       <c r="D88" t="n">
         <v>5942.75</v>
       </c>
       <c r="E88" t="n">
-        <v>-77.25</v>
+        <v>-82.75</v>
       </c>
       <c r="F88" t="n">
-        <v>5937</v>
+        <v>5933</v>
       </c>
       <c r="G88" t="n">
         <v>5961.19</v>
       </c>
       <c r="H88" t="n">
-        <v>-24.19</v>
+        <v>-28.19</v>
       </c>
       <c r="I88" t="n">
-        <v>5803.5</v>
+        <v>5756.5</v>
       </c>
       <c r="J88" t="n">
         <v>5745.52</v>
       </c>
       <c r="K88" t="n">
-        <v>57.98</v>
+        <v>10.98</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="89">
@@ -11334,31 +11334,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>114.03</v>
+        <v>113.5</v>
       </c>
       <c r="D89" t="n">
         <v>117.73</v>
       </c>
       <c r="E89" t="n">
-        <v>-3.7</v>
+        <v>-4.23</v>
       </c>
       <c r="F89" t="n">
-        <v>114.3</v>
+        <v>115.19</v>
       </c>
       <c r="G89" t="n">
         <v>114.37</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I89" t="n">
-        <v>112.3</v>
+        <v>113.2</v>
       </c>
       <c r="J89" t="n">
         <v>112.87</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.57</v>
+        <v>0.33</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3.14</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="90">
@@ -11386,31 +11386,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5536</v>
+        <v>5474</v>
       </c>
       <c r="D90" t="n">
         <v>5756.99</v>
       </c>
       <c r="E90" t="n">
-        <v>-220.99</v>
+        <v>-282.99</v>
       </c>
       <c r="F90" t="n">
-        <v>5544</v>
+        <v>5543.5</v>
       </c>
       <c r="G90" t="n">
         <v>5665.61</v>
       </c>
       <c r="H90" t="n">
-        <v>-121.61</v>
+        <v>-122.11</v>
       </c>
       <c r="I90" t="n">
-        <v>5430.5</v>
+        <v>5425</v>
       </c>
       <c r="J90" t="n">
         <v>5392.75</v>
       </c>
       <c r="K90" t="n">
-        <v>37.75</v>
+        <v>32.25</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3.84</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="91">
@@ -11438,31 +11438,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="D91" t="n">
         <v>1288.55</v>
       </c>
       <c r="E91" t="n">
-        <v>-13.55</v>
+        <v>-0.55</v>
       </c>
       <c r="F91" t="n">
-        <v>1291.1</v>
+        <v>1298.3</v>
       </c>
       <c r="G91" t="n">
         <v>1292.67</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.57</v>
+        <v>5.63</v>
       </c>
       <c r="I91" t="n">
-        <v>1267</v>
+        <v>1280.7</v>
       </c>
       <c r="J91" t="n">
         <v>1251.31</v>
       </c>
       <c r="K91" t="n">
-        <v>15.69</v>
+        <v>29.39</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="92">
@@ -11490,31 +11490,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1819</v>
+        <v>1810</v>
       </c>
       <c r="D92" t="n">
         <v>1821.49</v>
       </c>
       <c r="E92" t="n">
-        <v>-2.49</v>
+        <v>-11.49</v>
       </c>
       <c r="F92" t="n">
-        <v>1836</v>
+        <v>1822.6</v>
       </c>
       <c r="G92" t="n">
         <v>1862.32</v>
       </c>
       <c r="H92" t="n">
-        <v>-26.32</v>
+        <v>-39.72</v>
       </c>
       <c r="I92" t="n">
-        <v>1809.8</v>
+        <v>1783.1</v>
       </c>
       <c r="J92" t="n">
         <v>1771.37</v>
       </c>
       <c r="K92" t="n">
-        <v>38.43</v>
+        <v>11.73</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.14</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="93">
@@ -11542,31 +11542,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D93" t="n">
         <v>1669.93</v>
       </c>
       <c r="E93" t="n">
-        <v>-26.93</v>
+        <v>-29.93</v>
       </c>
       <c r="F93" t="n">
-        <v>1660.3</v>
+        <v>1665.9</v>
       </c>
       <c r="G93" t="n">
         <v>1666.17</v>
       </c>
       <c r="H93" t="n">
-        <v>-5.87</v>
+        <v>-0.27</v>
       </c>
       <c r="I93" t="n">
-        <v>1640</v>
+        <v>1630.8</v>
       </c>
       <c r="J93" t="n">
         <v>1612.18</v>
       </c>
       <c r="K93" t="n">
-        <v>27.82</v>
+        <v>18.62</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="94">
@@ -11594,31 +11594,31 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>318</v>
+        <v>310.25</v>
       </c>
       <c r="D94" t="n">
         <v>333.72</v>
       </c>
       <c r="E94" t="n">
-        <v>-15.72</v>
+        <v>-23.47</v>
       </c>
       <c r="F94" t="n">
-        <v>318.5</v>
+        <v>316.25</v>
       </c>
       <c r="G94" t="n">
         <v>325.32</v>
       </c>
       <c r="H94" t="n">
-        <v>-6.82</v>
+        <v>-9.07</v>
       </c>
       <c r="I94" t="n">
-        <v>306.2</v>
+        <v>309.5</v>
       </c>
       <c r="J94" t="n">
         <v>309.87</v>
       </c>
       <c r="K94" t="n">
-        <v>-3.67</v>
+        <v>-0.37</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>4.71</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="95">
@@ -11646,31 +11646,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>182.5</v>
+        <v>181.14</v>
       </c>
       <c r="D95" t="n">
         <v>190.82</v>
       </c>
       <c r="E95" t="n">
-        <v>-8.32</v>
+        <v>-9.68</v>
       </c>
       <c r="F95" t="n">
-        <v>184.85</v>
+        <v>185.74</v>
       </c>
       <c r="G95" t="n">
         <v>185.1</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.25</v>
+        <v>0.64</v>
       </c>
       <c r="I95" t="n">
-        <v>179.88</v>
+        <v>179.94</v>
       </c>
       <c r="J95" t="n">
         <v>179.05</v>
       </c>
       <c r="K95" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4.36</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="96">
@@ -11698,31 +11698,31 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8000</v>
+        <v>7975</v>
       </c>
       <c r="D96" t="n">
         <v>8177.27</v>
       </c>
       <c r="E96" t="n">
-        <v>-177.27</v>
+        <v>-202.27</v>
       </c>
       <c r="F96" t="n">
-        <v>8110</v>
+        <v>8024</v>
       </c>
       <c r="G96" t="n">
         <v>8068.89</v>
       </c>
       <c r="H96" t="n">
-        <v>41.11</v>
+        <v>-44.89</v>
       </c>
       <c r="I96" t="n">
-        <v>7955</v>
+        <v>7938</v>
       </c>
       <c r="J96" t="n">
         <v>7883.41</v>
       </c>
       <c r="K96" t="n">
-        <v>71.59</v>
+        <v>54.59</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="97">
@@ -11750,31 +11750,31 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1360</v>
+        <v>1282</v>
       </c>
       <c r="D97" t="n">
         <v>1292.75</v>
       </c>
       <c r="E97" t="n">
-        <v>67.25</v>
+        <v>-10.75</v>
       </c>
       <c r="F97" t="n">
-        <v>1391</v>
+        <v>1298.5</v>
       </c>
       <c r="G97" t="n">
         <v>1384.9</v>
       </c>
       <c r="H97" t="n">
-        <v>6.1</v>
+        <v>-86.40000000000001</v>
       </c>
       <c r="I97" t="n">
-        <v>1291.1</v>
+        <v>1236.7</v>
       </c>
       <c r="J97" t="n">
         <v>1330.1</v>
       </c>
       <c r="K97" t="n">
-        <v>-39</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>5.2</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="98">
@@ -11802,31 +11802,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11780</v>
+        <v>12038</v>
       </c>
       <c r="D98" t="n">
         <v>12160.68</v>
       </c>
       <c r="E98" t="n">
-        <v>-380.68</v>
+        <v>-122.68</v>
       </c>
       <c r="F98" t="n">
-        <v>12061</v>
+        <v>12124</v>
       </c>
       <c r="G98" t="n">
         <v>11841.03</v>
       </c>
       <c r="H98" t="n">
-        <v>219.97</v>
+        <v>282.97</v>
       </c>
       <c r="I98" t="n">
-        <v>11720</v>
+        <v>11921</v>
       </c>
       <c r="J98" t="n">
         <v>11639.18</v>
       </c>
       <c r="K98" t="n">
-        <v>80.81999999999999</v>
+        <v>281.82</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3.13</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="99">
@@ -11854,31 +11854,31 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5284</v>
+        <v>5333.5</v>
       </c>
       <c r="D99" t="n">
         <v>5434.61</v>
       </c>
       <c r="E99" t="n">
-        <v>-150.61</v>
+        <v>-101.11</v>
       </c>
       <c r="F99" t="n">
-        <v>5330</v>
+        <v>5355</v>
       </c>
       <c r="G99" t="n">
         <v>5368.18</v>
       </c>
       <c r="H99" t="n">
-        <v>-38.18</v>
+        <v>-13.18</v>
       </c>
       <c r="I99" t="n">
-        <v>5217.5</v>
+        <v>5297</v>
       </c>
       <c r="J99" t="n">
         <v>5177.46</v>
       </c>
       <c r="K99" t="n">
-        <v>40.04</v>
+        <v>119.54</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -11887,11 +11887,11 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.77</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="100">
@@ -11906,31 +11906,31 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>616</v>
+        <v>621.8</v>
       </c>
       <c r="D100" t="n">
         <v>669.85</v>
       </c>
       <c r="E100" t="n">
-        <v>-53.85</v>
+        <v>-48.05</v>
       </c>
       <c r="F100" t="n">
-        <v>627</v>
+        <v>630.75</v>
       </c>
       <c r="G100" t="n">
         <v>634.36</v>
       </c>
       <c r="H100" t="n">
-        <v>-7.36</v>
+        <v>-3.61</v>
       </c>
       <c r="I100" t="n">
-        <v>613.1</v>
+        <v>610.6</v>
       </c>
       <c r="J100" t="n">
         <v>597.0700000000001</v>
       </c>
       <c r="K100" t="n">
-        <v>16.03</v>
+        <v>13.53</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>8.039999999999999</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="101">
@@ -11958,31 +11958,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2735.5</v>
+        <v>2750</v>
       </c>
       <c r="D101" t="n">
         <v>2738.31</v>
       </c>
       <c r="E101" t="n">
-        <v>-2.81</v>
+        <v>11.69</v>
       </c>
       <c r="F101" t="n">
-        <v>2747.6</v>
+        <v>2761.5</v>
       </c>
       <c r="G101" t="n">
         <v>2769.11</v>
       </c>
       <c r="H101" t="n">
-        <v>-21.51</v>
+        <v>-7.61</v>
       </c>
       <c r="I101" t="n">
-        <v>2720</v>
+        <v>2713.5</v>
       </c>
       <c r="J101" t="n">
         <v>2687.95</v>
       </c>
       <c r="K101" t="n">
-        <v>32.05</v>
+        <v>25.55</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="102">
@@ -12010,31 +12010,31 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4037.4</v>
+        <v>4080</v>
       </c>
       <c r="D102" t="n">
         <v>4104.98</v>
       </c>
       <c r="E102" t="n">
-        <v>-67.58</v>
+        <v>-24.98</v>
       </c>
       <c r="F102" t="n">
-        <v>4075.5</v>
+        <v>4080</v>
       </c>
       <c r="G102" t="n">
         <v>4051.84</v>
       </c>
       <c r="H102" t="n">
-        <v>23.66</v>
+        <v>28.16</v>
       </c>
       <c r="I102" t="n">
-        <v>4028.5</v>
+        <v>4025.8</v>
       </c>
       <c r="J102" t="n">
         <v>3994.08</v>
       </c>
       <c r="K102" t="n">
-        <v>34.42</v>
+        <v>31.72</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1.65</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="103">
@@ -12062,31 +12062,31 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3460.1</v>
+        <v>3517</v>
       </c>
       <c r="D103" t="n">
         <v>3657.22</v>
       </c>
       <c r="E103" t="n">
-        <v>-197.12</v>
+        <v>-140.22</v>
       </c>
       <c r="F103" t="n">
-        <v>3514.6</v>
+        <v>3534.6</v>
       </c>
       <c r="G103" t="n">
         <v>3512.32</v>
       </c>
       <c r="H103" t="n">
-        <v>2.28</v>
+        <v>22.28</v>
       </c>
       <c r="I103" t="n">
-        <v>3455.1</v>
+        <v>3491.1</v>
       </c>
       <c r="J103" t="n">
         <v>3392.55</v>
       </c>
       <c r="K103" t="n">
-        <v>62.55</v>
+        <v>98.55</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>5.39</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="104">
@@ -12114,31 +12114,31 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2032</v>
+        <v>2021.3</v>
       </c>
       <c r="D104" t="n">
         <v>2019.29</v>
       </c>
       <c r="E104" t="n">
-        <v>12.71</v>
+        <v>2.01</v>
       </c>
       <c r="F104" t="n">
-        <v>2043.9</v>
+        <v>2037.1</v>
       </c>
       <c r="G104" t="n">
         <v>2061.07</v>
       </c>
       <c r="H104" t="n">
-        <v>-17.17</v>
+        <v>-23.97</v>
       </c>
       <c r="I104" t="n">
-        <v>2012</v>
+        <v>1992.6</v>
       </c>
       <c r="J104" t="n">
         <v>1993.54</v>
       </c>
       <c r="K104" t="n">
-        <v>18.46</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="105">
@@ -12166,31 +12166,31 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1463</v>
+        <v>1467.7</v>
       </c>
       <c r="D105" t="n">
         <v>1489.04</v>
       </c>
       <c r="E105" t="n">
-        <v>-26.04</v>
+        <v>-21.34</v>
       </c>
       <c r="F105" t="n">
-        <v>1469.8</v>
+        <v>1483.7</v>
       </c>
       <c r="G105" t="n">
         <v>1478.57</v>
       </c>
       <c r="H105" t="n">
-        <v>-8.77</v>
+        <v>5.13</v>
       </c>
       <c r="I105" t="n">
-        <v>1457.2</v>
+        <v>1462</v>
       </c>
       <c r="J105" t="n">
         <v>1439.41</v>
       </c>
       <c r="K105" t="n">
-        <v>17.79</v>
+        <v>22.59</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="106">
@@ -12218,31 +12218,31 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>512</v>
+        <v>501.9</v>
       </c>
       <c r="D106" t="n">
         <v>522.21</v>
       </c>
       <c r="E106" t="n">
-        <v>-10.21</v>
+        <v>-20.31</v>
       </c>
       <c r="F106" t="n">
-        <v>512</v>
+        <v>507.4</v>
       </c>
       <c r="G106" t="n">
         <v>520.1</v>
       </c>
       <c r="H106" t="n">
-        <v>-8.1</v>
+        <v>-12.7</v>
       </c>
       <c r="I106" t="n">
-        <v>498.75</v>
+        <v>498.25</v>
       </c>
       <c r="J106" t="n">
         <v>501.73</v>
       </c>
       <c r="K106" t="n">
-        <v>-2.98</v>
+        <v>-3.48</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -12251,11 +12251,11 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1.96</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="107">
@@ -12270,31 +12270,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>788</v>
+        <v>789.45</v>
       </c>
       <c r="D107" t="n">
         <v>796.34</v>
       </c>
       <c r="E107" t="n">
-        <v>-8.34</v>
+        <v>-6.89</v>
       </c>
       <c r="F107" t="n">
-        <v>796.5</v>
+        <v>798.4</v>
       </c>
       <c r="G107" t="n">
         <v>801.3099999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>-4.81</v>
+        <v>-2.91</v>
       </c>
       <c r="I107" t="n">
-        <v>784.05</v>
+        <v>780.05</v>
       </c>
       <c r="J107" t="n">
         <v>771.53</v>
       </c>
       <c r="K107" t="n">
-        <v>12.52</v>
+        <v>8.52</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1.05</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="108">
@@ -12322,31 +12322,31 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1168</v>
+        <v>1175.6</v>
       </c>
       <c r="D108" t="n">
         <v>1178.26</v>
       </c>
       <c r="E108" t="n">
-        <v>-10.26</v>
+        <v>-2.66</v>
       </c>
       <c r="F108" t="n">
-        <v>1176.7</v>
+        <v>1189.9</v>
       </c>
       <c r="G108" t="n">
         <v>1190.23</v>
       </c>
       <c r="H108" t="n">
-        <v>-13.53</v>
+        <v>-0.33</v>
       </c>
       <c r="I108" t="n">
-        <v>1147.8</v>
+        <v>1161.7</v>
       </c>
       <c r="J108" t="n">
         <v>1141.68</v>
       </c>
       <c r="K108" t="n">
-        <v>6.12</v>
+        <v>20.02</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0.87</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="109">
@@ -12374,31 +12374,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>14023</v>
+        <v>14115</v>
       </c>
       <c r="D109" t="n">
         <v>14383.7</v>
       </c>
       <c r="E109" t="n">
-        <v>-360.7</v>
+        <v>-268.7</v>
       </c>
       <c r="F109" t="n">
-        <v>14198</v>
+        <v>14271</v>
       </c>
       <c r="G109" t="n">
         <v>14273.99</v>
       </c>
       <c r="H109" t="n">
-        <v>-75.98999999999999</v>
+        <v>-2.99</v>
       </c>
       <c r="I109" t="n">
-        <v>14011</v>
+        <v>14001</v>
       </c>
       <c r="J109" t="n">
         <v>13719.2</v>
       </c>
       <c r="K109" t="n">
-        <v>291.8</v>
+        <v>281.8</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -12407,11 +12407,11 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6104,6 +6104,1410 @@
       </c>
       <c r="N109" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>11579</v>
+      </c>
+      <c r="D110" t="n">
+        <v>11558.42</v>
+      </c>
+      <c r="E110" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11587</v>
+      </c>
+      <c r="G110" t="n">
+        <v>11558.42</v>
+      </c>
+      <c r="H110" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="I110" t="n">
+        <v>11410</v>
+      </c>
+      <c r="J110" t="n">
+        <v>11371.84</v>
+      </c>
+      <c r="K110" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>8049</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8061.87</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8049</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8245.42</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-196.42</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7940</v>
+      </c>
+      <c r="J111" t="n">
+        <v>8021.49</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-81.48999999999999</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2740</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2844.75</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-104.75</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2748.4</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2844.75</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-96.34999999999999</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2698.2</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2740</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D113" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F113" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>120.99</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I113" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="J113" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>5895</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6017.33</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-122.33</v>
+      </c>
+      <c r="F114" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G114" t="n">
+        <v>6030.82</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-114.82</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5844</v>
+      </c>
+      <c r="J114" t="n">
+        <v>5866.76</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-22.76</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F115" t="n">
+        <v>177.38</v>
+      </c>
+      <c r="G115" t="n">
+        <v>181.16</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="I115" t="n">
+        <v>174.43</v>
+      </c>
+      <c r="J115" t="n">
+        <v>176.25</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>11891</v>
+      </c>
+      <c r="D116" t="n">
+        <v>12046.18</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-155.18</v>
+      </c>
+      <c r="F116" t="n">
+        <v>11891</v>
+      </c>
+      <c r="G116" t="n">
+        <v>12046.18</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-155.18</v>
+      </c>
+      <c r="I116" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J116" t="n">
+        <v>11728.34</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-78.34</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>11679</v>
+      </c>
+      <c r="D117" t="n">
+        <v>11658.24</v>
+      </c>
+      <c r="E117" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F117" t="n">
+        <v>11899</v>
+      </c>
+      <c r="G117" t="n">
+        <v>11951.71</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-52.71</v>
+      </c>
+      <c r="I117" t="n">
+        <v>11532</v>
+      </c>
+      <c r="J117" t="n">
+        <v>11626.71</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-94.70999999999999</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>5333</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5415.71</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-82.70999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>5333</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5476.36</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-143.36</v>
+      </c>
+      <c r="I118" t="n">
+        <v>5228</v>
+      </c>
+      <c r="J118" t="n">
+        <v>5328.09</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-100.09</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2240</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2236.02</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2245</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2246.63</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2192.7</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2188.23</v>
+      </c>
+      <c r="K119" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1644.81</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-19.81</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1660.49</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1622.1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1615.26</v>
+      </c>
+      <c r="K120" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>187</v>
+      </c>
+      <c r="D121" t="n">
+        <v>183.57</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="F121" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="G121" t="n">
+        <v>192.31</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I121" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="J121" t="n">
+        <v>187</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1232.4</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1272</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1278.7</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1272</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1232.4</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1225.65</v>
+      </c>
+      <c r="K122" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5427.13</v>
+      </c>
+      <c r="E123" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5530</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5544.99</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J123" t="n">
+        <v>5392.25</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1941.54</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1945</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1978.44</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-33.44</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1901.3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1924.24</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-22.94</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>279.85</v>
+      </c>
+      <c r="D125" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>281.9</v>
+      </c>
+      <c r="G125" t="n">
+        <v>281.63</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I125" t="n">
+        <v>277</v>
+      </c>
+      <c r="J125" t="n">
+        <v>274.16</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4020</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4082.15</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-62.15</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4044.1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4087.49</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-43.39</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3990</v>
+      </c>
+      <c r="J126" t="n">
+        <v>3975.44</v>
+      </c>
+      <c r="K126" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>512.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>509.19</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F127" t="n">
+        <v>523.8</v>
+      </c>
+      <c r="G127" t="n">
+        <v>509.19</v>
+      </c>
+      <c r="H127" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="I127" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>499.53</v>
+      </c>
+      <c r="K127" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1484.08</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-21.08</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1468.8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1492.03</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-23.23</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1456.1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1451.28</v>
+      </c>
+      <c r="K128" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>614.65</v>
+      </c>
+      <c r="D129" t="n">
+        <v>598.79</v>
+      </c>
+      <c r="E129" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="F129" t="n">
+        <v>620.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>615.76</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I129" t="n">
+        <v>604.25</v>
+      </c>
+      <c r="J129" t="n">
+        <v>598.5599999999999</v>
+      </c>
+      <c r="K129" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1801.5</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1867.32</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-65.81999999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1819.1</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1867.32</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-48.22</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1780.4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1742.03</v>
+      </c>
+      <c r="K130" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3383.96</v>
+      </c>
+      <c r="E131" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3471.8</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3406.31</v>
+      </c>
+      <c r="H131" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="J131" t="n">
+        <v>3320.14</v>
+      </c>
+      <c r="K131" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2020.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2089.33</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-68.83</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2028.4</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2089.33</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-60.93</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2006.1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1973.8</v>
+      </c>
+      <c r="K132" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1377.37</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-38.37</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1364</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1377.37</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-13.37</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1329.6</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1298.83</v>
+      </c>
+      <c r="K133" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D134" t="n">
+        <v>14041.16</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-241.16</v>
+      </c>
+      <c r="F134" t="n">
+        <v>14090</v>
+      </c>
+      <c r="G134" t="n">
+        <v>14041.16</v>
+      </c>
+      <c r="H134" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="I134" t="n">
+        <v>13670</v>
+      </c>
+      <c r="J134" t="n">
+        <v>13456.8</v>
+      </c>
+      <c r="K134" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-41.46</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1167.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1202.46</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-34.96</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1140</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1145.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="D136" t="n">
+        <v>304.31</v>
+      </c>
+      <c r="E136" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="F136" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="G136" t="n">
+        <v>318.08</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I136" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="J136" t="n">
+        <v>309.31</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -6117,7 +7521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6710,6 +8114,110 @@
       </c>
       <c r="N11" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24473.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24517.51</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-44.21</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24265.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24310.16</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-44.21</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="D13" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="G13" t="n">
+        <v>58096.46</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-210.61</v>
+      </c>
+      <c r="I13" t="n">
+        <v>57254</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57464.61</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-210.61</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6723,7 +8231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12414,6 +13922,1410 @@
         <v>1.87</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>5895</v>
+      </c>
+      <c r="D110" t="n">
+        <v>6177.02</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-282.02</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6088.42</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-172.42</v>
+      </c>
+      <c r="I110" t="n">
+        <v>5844</v>
+      </c>
+      <c r="J110" t="n">
+        <v>5808.58</v>
+      </c>
+      <c r="K110" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2740</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2900.21</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-160.21</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2748.4</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2818.87</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-70.47</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2698.2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2708.16</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D112" t="n">
+        <v>118.47</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F112" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>121.16</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="I112" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="J112" t="n">
+        <v>118.54</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>11579</v>
+      </c>
+      <c r="D113" t="n">
+        <v>11783.36</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-204.36</v>
+      </c>
+      <c r="F113" t="n">
+        <v>11587</v>
+      </c>
+      <c r="G113" t="n">
+        <v>11879.66</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-292.66</v>
+      </c>
+      <c r="I113" t="n">
+        <v>11410</v>
+      </c>
+      <c r="J113" t="n">
+        <v>11469.14</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-59.14</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>8049</v>
+      </c>
+      <c r="D114" t="n">
+        <v>8211.66</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-162.66</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8049</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8251.139999999999</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-202.14</v>
+      </c>
+      <c r="I114" t="n">
+        <v>7940</v>
+      </c>
+      <c r="J114" t="n">
+        <v>7977.81</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-37.81</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>181.04</v>
+      </c>
+      <c r="E115" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="F115" t="n">
+        <v>177.38</v>
+      </c>
+      <c r="G115" t="n">
+        <v>182.47</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I115" t="n">
+        <v>174.43</v>
+      </c>
+      <c r="J115" t="n">
+        <v>174.13</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>11891</v>
+      </c>
+      <c r="D116" t="n">
+        <v>12228.54</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-337.54</v>
+      </c>
+      <c r="F116" t="n">
+        <v>11891</v>
+      </c>
+      <c r="G116" t="n">
+        <v>12150.06</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-259.06</v>
+      </c>
+      <c r="I116" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J116" t="n">
+        <v>11815.73</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-165.73</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1972.57</v>
+      </c>
+      <c r="E117" t="n">
+        <v>-27.57</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1945</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1988.96</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-43.96</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1901.3</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1931.49</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-30.19</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OFSS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>11679</v>
+      </c>
+      <c r="D118" t="n">
+        <v>12120.46</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-441.46</v>
+      </c>
+      <c r="F118" t="n">
+        <v>11899</v>
+      </c>
+      <c r="G118" t="n">
+        <v>12210.25</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-311.25</v>
+      </c>
+      <c r="I118" t="n">
+        <v>11532</v>
+      </c>
+      <c r="J118" t="n">
+        <v>11395.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>136.04</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>187</v>
+      </c>
+      <c r="D119" t="n">
+        <v>187.69</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="G119" t="n">
+        <v>192.58</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="I119" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="J119" t="n">
+        <v>184.67</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>5333</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5549.1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-216.1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>5333</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5498.13</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-165.13</v>
+      </c>
+      <c r="I120" t="n">
+        <v>5228</v>
+      </c>
+      <c r="J120" t="n">
+        <v>5262.28</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-34.28</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1232.4</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1303.87</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-71.47</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1278.7</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1271.07</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1232.4</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1215.67</v>
+      </c>
+      <c r="K121" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2240</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2291.52</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-51.52</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2245</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2309.78</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-64.78</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2192.7</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2209.97</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-17.27</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>5474</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5612.24</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-138.24</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5530</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5693.68</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-163.68</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J123" t="n">
+        <v>5363.5</v>
+      </c>
+      <c r="K123" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1685.24</v>
+      </c>
+      <c r="E124" t="n">
+        <v>-60.24</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1675.23</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-18.23</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1622.1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1603.52</v>
+      </c>
+      <c r="K124" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>512.05</v>
+      </c>
+      <c r="D125" t="n">
+        <v>522.52</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-10.47</v>
+      </c>
+      <c r="F125" t="n">
+        <v>523.8</v>
+      </c>
+      <c r="G125" t="n">
+        <v>528.67</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="I125" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>504.68</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>279.85</v>
+      </c>
+      <c r="D126" t="n">
+        <v>285.48</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="F126" t="n">
+        <v>281.9</v>
+      </c>
+      <c r="G126" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="I126" t="n">
+        <v>277</v>
+      </c>
+      <c r="J126" t="n">
+        <v>276.68</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>614.65</v>
+      </c>
+      <c r="D127" t="n">
+        <v>621.11</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="F127" t="n">
+        <v>620.8</v>
+      </c>
+      <c r="G127" t="n">
+        <v>641.2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="I127" t="n">
+        <v>604.25</v>
+      </c>
+      <c r="J127" t="n">
+        <v>600.8200000000001</v>
+      </c>
+      <c r="K127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>4020</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4138.24</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-118.24</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4044.1</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4102.15</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-58.05</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3990</v>
+      </c>
+      <c r="J128" t="n">
+        <v>3998.67</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1801.5</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1932.65</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-131.15</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1819.1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1875.33</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-56.23</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1780.4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1763.98</v>
+      </c>
+      <c r="K129" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3472.84</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-69.23999999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3471.8</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3514.37</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-42.57</v>
+      </c>
+      <c r="I130" t="n">
+        <v>3403.6</v>
+      </c>
+      <c r="J130" t="n">
+        <v>3354.39</v>
+      </c>
+      <c r="K130" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1463</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1512.83</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-49.83</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1468.8</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1500.86</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-32.06</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1456.1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1449.22</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="D132" t="n">
+        <v>314.46</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F132" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="G132" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="I132" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="J132" t="n">
+        <v>307.88</v>
+      </c>
+      <c r="K132" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2020.5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2141.19</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-120.69</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2028.4</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2083.43</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-55.03</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2006.1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1993.42</v>
+      </c>
+      <c r="K133" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1425.56</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-86.56</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1364</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1393.89</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-29.89</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1329.6</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1311.1</v>
+      </c>
+      <c r="K134" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1237.34</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-76.34</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1167.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1201.87</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-34.37</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1140</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1141.89</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D136" t="n">
+        <v>14415.02</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-615.02</v>
+      </c>
+      <c r="F136" t="n">
+        <v>14090</v>
+      </c>
+      <c r="G136" t="n">
+        <v>14253.96</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-163.96</v>
+      </c>
+      <c r="I136" t="n">
+        <v>13670</v>
+      </c>
+      <c r="J136" t="n">
+        <v>13596.83</v>
+      </c>
+      <c r="K136" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -6118,31 +6118,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11579</v>
+        <v>11550</v>
       </c>
       <c r="D110" t="n">
         <v>11558.42</v>
       </c>
       <c r="E110" t="n">
-        <v>20.58</v>
+        <v>-8.42</v>
       </c>
       <c r="F110" t="n">
-        <v>11587</v>
+        <v>11599</v>
       </c>
       <c r="G110" t="n">
         <v>11558.42</v>
       </c>
       <c r="H110" t="n">
-        <v>28.58</v>
+        <v>40.58</v>
       </c>
       <c r="I110" t="n">
-        <v>11410</v>
+        <v>11412</v>
       </c>
       <c r="J110" t="n">
         <v>11371.84</v>
       </c>
       <c r="K110" t="n">
-        <v>38.16</v>
+        <v>40.16</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6170,31 +6170,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8049</v>
+        <v>8000</v>
       </c>
       <c r="D111" t="n">
         <v>8061.87</v>
       </c>
       <c r="E111" t="n">
-        <v>-12.87</v>
+        <v>-61.87</v>
       </c>
       <c r="F111" t="n">
-        <v>8049</v>
+        <v>8110</v>
       </c>
       <c r="G111" t="n">
         <v>8245.42</v>
       </c>
       <c r="H111" t="n">
-        <v>-196.42</v>
+        <v>-135.42</v>
       </c>
       <c r="I111" t="n">
-        <v>7940</v>
+        <v>7955</v>
       </c>
       <c r="J111" t="n">
         <v>8021.49</v>
       </c>
       <c r="K111" t="n">
-        <v>-81.48999999999999</v>
+        <v>-66.48999999999999</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="112">
@@ -6222,31 +6222,31 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2740</v>
+        <v>2735.5</v>
       </c>
       <c r="D112" t="n">
         <v>2844.75</v>
       </c>
       <c r="E112" t="n">
-        <v>-104.75</v>
+        <v>-109.25</v>
       </c>
       <c r="F112" t="n">
-        <v>2748.4</v>
+        <v>2747.6</v>
       </c>
       <c r="G112" t="n">
         <v>2844.75</v>
       </c>
       <c r="H112" t="n">
-        <v>-96.34999999999999</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>2698.2</v>
+        <v>2720</v>
       </c>
       <c r="J112" t="n">
         <v>2740</v>
       </c>
       <c r="K112" t="n">
-        <v>-41.8</v>
+        <v>-20</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6255,11 +6255,11 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="113">
@@ -6274,31 +6274,31 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>118.98</v>
+        <v>114.03</v>
       </c>
       <c r="D113" t="n">
         <v>117.1</v>
       </c>
       <c r="E113" t="n">
-        <v>1.88</v>
+        <v>-3.07</v>
       </c>
       <c r="F113" t="n">
-        <v>119.5</v>
+        <v>114.3</v>
       </c>
       <c r="G113" t="n">
         <v>120.99</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.49</v>
+        <v>-6.69</v>
       </c>
       <c r="I113" t="n">
-        <v>113.72</v>
+        <v>112.3</v>
       </c>
       <c r="J113" t="n">
         <v>117.76</v>
       </c>
       <c r="K113" t="n">
-        <v>-4.04</v>
+        <v>-5.46</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6307,11 +6307,11 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="114">
@@ -6326,31 +6326,31 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5895</v>
+        <v>5865.5</v>
       </c>
       <c r="D114" t="n">
         <v>6017.33</v>
       </c>
       <c r="E114" t="n">
-        <v>-122.33</v>
+        <v>-151.83</v>
       </c>
       <c r="F114" t="n">
-        <v>5916</v>
+        <v>5937</v>
       </c>
       <c r="G114" t="n">
         <v>6030.82</v>
       </c>
       <c r="H114" t="n">
-        <v>-114.82</v>
+        <v>-93.81999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>5844</v>
+        <v>5803.5</v>
       </c>
       <c r="J114" t="n">
         <v>5866.76</v>
       </c>
       <c r="K114" t="n">
-        <v>-22.76</v>
+        <v>-63.26</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="115">
@@ -6378,31 +6378,31 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>176.7</v>
+        <v>174.83</v>
       </c>
       <c r="D115" t="n">
         <v>176.38</v>
       </c>
       <c r="E115" t="n">
-        <v>0.32</v>
+        <v>-1.55</v>
       </c>
       <c r="F115" t="n">
-        <v>177.38</v>
+        <v>176.33</v>
       </c>
       <c r="G115" t="n">
         <v>181.16</v>
       </c>
       <c r="H115" t="n">
-        <v>-3.78</v>
+        <v>-4.83</v>
       </c>
       <c r="I115" t="n">
-        <v>174.43</v>
+        <v>172</v>
       </c>
       <c r="J115" t="n">
         <v>176.25</v>
       </c>
       <c r="K115" t="n">
-        <v>-1.82</v>
+        <v>-4.25</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="116">
@@ -6430,31 +6430,31 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>11891</v>
+        <v>11780</v>
       </c>
       <c r="D116" t="n">
         <v>12046.18</v>
       </c>
       <c r="E116" t="n">
-        <v>-155.18</v>
+        <v>-266.18</v>
       </c>
       <c r="F116" t="n">
-        <v>11891</v>
+        <v>12061</v>
       </c>
       <c r="G116" t="n">
         <v>12046.18</v>
       </c>
       <c r="H116" t="n">
-        <v>-155.18</v>
+        <v>14.82</v>
       </c>
       <c r="I116" t="n">
-        <v>11650</v>
+        <v>11720</v>
       </c>
       <c r="J116" t="n">
         <v>11728.34</v>
       </c>
       <c r="K116" t="n">
-        <v>-78.34</v>
+        <v>-8.34</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1.29</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="117">
@@ -6482,31 +6482,31 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11679</v>
+        <v>11896</v>
       </c>
       <c r="D117" t="n">
         <v>11658.24</v>
       </c>
       <c r="E117" t="n">
-        <v>20.76</v>
+        <v>237.76</v>
       </c>
       <c r="F117" t="n">
-        <v>11899</v>
+        <v>11968</v>
       </c>
       <c r="G117" t="n">
         <v>11951.71</v>
       </c>
       <c r="H117" t="n">
-        <v>-52.71</v>
+        <v>16.29</v>
       </c>
       <c r="I117" t="n">
-        <v>11532</v>
+        <v>11675</v>
       </c>
       <c r="J117" t="n">
         <v>11626.71</v>
       </c>
       <c r="K117" t="n">
-        <v>-94.70999999999999</v>
+        <v>48.29</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="118">
@@ -6534,31 +6534,31 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5333</v>
+        <v>5284</v>
       </c>
       <c r="D118" t="n">
         <v>5415.71</v>
       </c>
       <c r="E118" t="n">
-        <v>-82.70999999999999</v>
+        <v>-131.71</v>
       </c>
       <c r="F118" t="n">
-        <v>5333</v>
+        <v>5330</v>
       </c>
       <c r="G118" t="n">
         <v>5476.36</v>
       </c>
       <c r="H118" t="n">
-        <v>-143.36</v>
+        <v>-146.36</v>
       </c>
       <c r="I118" t="n">
-        <v>5228</v>
+        <v>5217.5</v>
       </c>
       <c r="J118" t="n">
         <v>5328.09</v>
       </c>
       <c r="K118" t="n">
-        <v>-100.09</v>
+        <v>-110.59</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1.53</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="119">
@@ -6586,31 +6586,31 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2240</v>
+        <v>2200</v>
       </c>
       <c r="D119" t="n">
         <v>2236.02</v>
       </c>
       <c r="E119" t="n">
-        <v>3.98</v>
+        <v>-36.02</v>
       </c>
       <c r="F119" t="n">
-        <v>2245</v>
+        <v>2237</v>
       </c>
       <c r="G119" t="n">
         <v>2246.63</v>
       </c>
       <c r="H119" t="n">
-        <v>-1.63</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>2192.7</v>
+        <v>2200</v>
       </c>
       <c r="J119" t="n">
         <v>2188.23</v>
       </c>
       <c r="K119" t="n">
-        <v>4.47</v>
+        <v>11.77</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0.18</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="120">
@@ -6638,31 +6638,31 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1625</v>
+        <v>1643</v>
       </c>
       <c r="D120" t="n">
         <v>1644.81</v>
       </c>
       <c r="E120" t="n">
-        <v>-19.81</v>
+        <v>-1.81</v>
       </c>
       <c r="F120" t="n">
-        <v>1657</v>
+        <v>1660.3</v>
       </c>
       <c r="G120" t="n">
         <v>1660.49</v>
       </c>
       <c r="H120" t="n">
-        <v>-3.49</v>
+        <v>-0.19</v>
       </c>
       <c r="I120" t="n">
-        <v>1622.1</v>
+        <v>1640</v>
       </c>
       <c r="J120" t="n">
         <v>1615.26</v>
       </c>
       <c r="K120" t="n">
-        <v>6.84</v>
+        <v>24.74</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1.2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="121">
@@ -6690,31 +6690,31 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>187</v>
+        <v>182.5</v>
       </c>
       <c r="D121" t="n">
         <v>183.57</v>
       </c>
       <c r="E121" t="n">
-        <v>3.43</v>
+        <v>-1.07</v>
       </c>
       <c r="F121" t="n">
-        <v>187.6</v>
+        <v>184.85</v>
       </c>
       <c r="G121" t="n">
         <v>192.31</v>
       </c>
       <c r="H121" t="n">
-        <v>-4.71</v>
+        <v>-7.46</v>
       </c>
       <c r="I121" t="n">
-        <v>181.82</v>
+        <v>179.88</v>
       </c>
       <c r="J121" t="n">
         <v>187</v>
       </c>
       <c r="K121" t="n">
-        <v>-5.18</v>
+        <v>-7.12</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1.87</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="122">
@@ -6742,31 +6742,31 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1232.4</v>
+        <v>1275</v>
       </c>
       <c r="D122" t="n">
         <v>1272</v>
       </c>
       <c r="E122" t="n">
-        <v>-39.6</v>
+        <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>1278.7</v>
+        <v>1291.1</v>
       </c>
       <c r="G122" t="n">
         <v>1272</v>
       </c>
       <c r="H122" t="n">
-        <v>6.7</v>
+        <v>19.1</v>
       </c>
       <c r="I122" t="n">
-        <v>1232.4</v>
+        <v>1267</v>
       </c>
       <c r="J122" t="n">
         <v>1225.65</v>
       </c>
       <c r="K122" t="n">
-        <v>6.75</v>
+        <v>41.35</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>3.11</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="123">
@@ -6794,31 +6794,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5474</v>
+        <v>5536</v>
       </c>
       <c r="D123" t="n">
         <v>5427.13</v>
       </c>
       <c r="E123" t="n">
-        <v>46.87</v>
+        <v>108.87</v>
       </c>
       <c r="F123" t="n">
-        <v>5530</v>
+        <v>5544</v>
       </c>
       <c r="G123" t="n">
         <v>5544.99</v>
       </c>
       <c r="H123" t="n">
-        <v>-14.99</v>
+        <v>-0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>5390</v>
+        <v>5430.5</v>
       </c>
       <c r="J123" t="n">
         <v>5392.25</v>
       </c>
       <c r="K123" t="n">
-        <v>-2.25</v>
+        <v>38.25</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.86</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="124">
@@ -6846,31 +6846,31 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1945</v>
+        <v>1915.2</v>
       </c>
       <c r="D124" t="n">
         <v>1941.54</v>
       </c>
       <c r="E124" t="n">
-        <v>3.46</v>
+        <v>-26.34</v>
       </c>
       <c r="F124" t="n">
-        <v>1945</v>
+        <v>1938.3</v>
       </c>
       <c r="G124" t="n">
         <v>1978.44</v>
       </c>
       <c r="H124" t="n">
-        <v>-33.44</v>
+        <v>-40.14</v>
       </c>
       <c r="I124" t="n">
-        <v>1901.3</v>
+        <v>1914.4</v>
       </c>
       <c r="J124" t="n">
         <v>1924.24</v>
       </c>
       <c r="K124" t="n">
-        <v>-22.94</v>
+        <v>-9.84</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="125">
@@ -6898,31 +6898,31 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>279.85</v>
+        <v>277</v>
       </c>
       <c r="D125" t="n">
         <v>279.35</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5</v>
+        <v>-2.35</v>
       </c>
       <c r="F125" t="n">
-        <v>281.9</v>
+        <v>279.15</v>
       </c>
       <c r="G125" t="n">
         <v>281.63</v>
       </c>
       <c r="H125" t="n">
-        <v>0.27</v>
+        <v>-2.48</v>
       </c>
       <c r="I125" t="n">
-        <v>277</v>
+        <v>273.4</v>
       </c>
       <c r="J125" t="n">
         <v>274.16</v>
       </c>
       <c r="K125" t="n">
-        <v>2.84</v>
+        <v>-0.76</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0.18</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="126">
@@ -6950,31 +6950,31 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4020</v>
+        <v>4037.4</v>
       </c>
       <c r="D126" t="n">
         <v>4082.15</v>
       </c>
       <c r="E126" t="n">
-        <v>-62.15</v>
+        <v>-44.75</v>
       </c>
       <c r="F126" t="n">
-        <v>4044.1</v>
+        <v>4075.5</v>
       </c>
       <c r="G126" t="n">
         <v>4087.49</v>
       </c>
       <c r="H126" t="n">
-        <v>-43.39</v>
+        <v>-11.99</v>
       </c>
       <c r="I126" t="n">
-        <v>3990</v>
+        <v>4028.5</v>
       </c>
       <c r="J126" t="n">
         <v>3975.44</v>
       </c>
       <c r="K126" t="n">
-        <v>14.56</v>
+        <v>53.06</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="127">
@@ -7002,31 +7002,31 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>512.05</v>
+        <v>512</v>
       </c>
       <c r="D127" t="n">
         <v>509.19</v>
       </c>
       <c r="E127" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="F127" t="n">
-        <v>523.8</v>
+        <v>512</v>
       </c>
       <c r="G127" t="n">
         <v>509.19</v>
       </c>
       <c r="H127" t="n">
-        <v>14.61</v>
+        <v>2.81</v>
       </c>
       <c r="I127" t="n">
-        <v>510.4</v>
+        <v>498.75</v>
       </c>
       <c r="J127" t="n">
         <v>499.53</v>
       </c>
       <c r="K127" t="n">
-        <v>10.87</v>
+        <v>-0.78</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="128">
@@ -7063,22 +7063,22 @@
         <v>-21.08</v>
       </c>
       <c r="F128" t="n">
-        <v>1468.8</v>
+        <v>1469.8</v>
       </c>
       <c r="G128" t="n">
         <v>1492.03</v>
       </c>
       <c r="H128" t="n">
-        <v>-23.23</v>
+        <v>-22.23</v>
       </c>
       <c r="I128" t="n">
-        <v>1456.1</v>
+        <v>1457.2</v>
       </c>
       <c r="J128" t="n">
         <v>1451.28</v>
       </c>
       <c r="K128" t="n">
-        <v>4.82</v>
+        <v>5.92</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7106,31 +7106,31 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>614.65</v>
+        <v>616</v>
       </c>
       <c r="D129" t="n">
         <v>598.79</v>
       </c>
       <c r="E129" t="n">
-        <v>15.86</v>
+        <v>17.21</v>
       </c>
       <c r="F129" t="n">
-        <v>620.8</v>
+        <v>627</v>
       </c>
       <c r="G129" t="n">
         <v>615.76</v>
       </c>
       <c r="H129" t="n">
-        <v>5.04</v>
+        <v>11.24</v>
       </c>
       <c r="I129" t="n">
-        <v>604.25</v>
+        <v>613.1</v>
       </c>
       <c r="J129" t="n">
         <v>598.5599999999999</v>
       </c>
       <c r="K129" t="n">
-        <v>5.69</v>
+        <v>14.54</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="130">
@@ -7158,31 +7158,31 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1801.5</v>
+        <v>1819</v>
       </c>
       <c r="D130" t="n">
         <v>1867.32</v>
       </c>
       <c r="E130" t="n">
-        <v>-65.81999999999999</v>
+        <v>-48.32</v>
       </c>
       <c r="F130" t="n">
-        <v>1819.1</v>
+        <v>1836</v>
       </c>
       <c r="G130" t="n">
         <v>1867.32</v>
       </c>
       <c r="H130" t="n">
-        <v>-48.22</v>
+        <v>-31.32</v>
       </c>
       <c r="I130" t="n">
-        <v>1780.4</v>
+        <v>1809.8</v>
       </c>
       <c r="J130" t="n">
         <v>1742.03</v>
       </c>
       <c r="K130" t="n">
-        <v>38.37</v>
+        <v>67.77</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>3.52</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="131">
@@ -7210,31 +7210,31 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3403.6</v>
+        <v>3460.1</v>
       </c>
       <c r="D131" t="n">
         <v>3383.96</v>
       </c>
       <c r="E131" t="n">
-        <v>19.64</v>
+        <v>76.14</v>
       </c>
       <c r="F131" t="n">
-        <v>3471.8</v>
+        <v>3514.6</v>
       </c>
       <c r="G131" t="n">
         <v>3406.31</v>
       </c>
       <c r="H131" t="n">
-        <v>65.48999999999999</v>
+        <v>108.29</v>
       </c>
       <c r="I131" t="n">
-        <v>3403.6</v>
+        <v>3455.1</v>
       </c>
       <c r="J131" t="n">
         <v>3320.14</v>
       </c>
       <c r="K131" t="n">
-        <v>83.45999999999999</v>
+        <v>134.96</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0.58</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="132">
@@ -7262,31 +7262,31 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2020.5</v>
+        <v>2032</v>
       </c>
       <c r="D132" t="n">
         <v>2089.33</v>
       </c>
       <c r="E132" t="n">
-        <v>-68.83</v>
+        <v>-57.33</v>
       </c>
       <c r="F132" t="n">
-        <v>2028.4</v>
+        <v>2043.9</v>
       </c>
       <c r="G132" t="n">
         <v>2089.33</v>
       </c>
       <c r="H132" t="n">
-        <v>-60.93</v>
+        <v>-45.43</v>
       </c>
       <c r="I132" t="n">
-        <v>2006.1</v>
+        <v>2012</v>
       </c>
       <c r="J132" t="n">
         <v>1973.8</v>
       </c>
       <c r="K132" t="n">
-        <v>32.3</v>
+        <v>38.2</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="133">
@@ -7314,31 +7314,31 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="D133" t="n">
         <v>1377.37</v>
       </c>
       <c r="E133" t="n">
-        <v>-38.37</v>
+        <v>-17.37</v>
       </c>
       <c r="F133" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="G133" t="n">
         <v>1377.37</v>
       </c>
       <c r="H133" t="n">
-        <v>-13.37</v>
+        <v>13.63</v>
       </c>
       <c r="I133" t="n">
-        <v>1329.6</v>
+        <v>1291.1</v>
       </c>
       <c r="J133" t="n">
         <v>1298.83</v>
       </c>
       <c r="K133" t="n">
-        <v>30.77</v>
+        <v>-7.73</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>2.79</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="134">
@@ -7366,31 +7366,31 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>13800</v>
+        <v>14023</v>
       </c>
       <c r="D134" t="n">
         <v>14041.16</v>
       </c>
       <c r="E134" t="n">
-        <v>-241.16</v>
+        <v>-18.16</v>
       </c>
       <c r="F134" t="n">
-        <v>14090</v>
+        <v>14198</v>
       </c>
       <c r="G134" t="n">
         <v>14041.16</v>
       </c>
       <c r="H134" t="n">
-        <v>48.84</v>
+        <v>156.84</v>
       </c>
       <c r="I134" t="n">
-        <v>13670</v>
+        <v>14011</v>
       </c>
       <c r="J134" t="n">
         <v>13456.8</v>
       </c>
       <c r="K134" t="n">
-        <v>213.2</v>
+        <v>554.2</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1.72</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="135">
@@ -7418,31 +7418,31 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="D135" t="n">
         <v>1202.46</v>
       </c>
       <c r="E135" t="n">
-        <v>-41.46</v>
+        <v>-34.46</v>
       </c>
       <c r="F135" t="n">
-        <v>1167.5</v>
+        <v>1176.7</v>
       </c>
       <c r="G135" t="n">
         <v>1202.46</v>
       </c>
       <c r="H135" t="n">
-        <v>-34.96</v>
+        <v>-25.76</v>
       </c>
       <c r="I135" t="n">
-        <v>1140</v>
+        <v>1147.8</v>
       </c>
       <c r="J135" t="n">
         <v>1145.8</v>
       </c>
       <c r="K135" t="n">
-        <v>-5.8</v>
+        <v>2</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="136">
@@ -7470,31 +7470,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>314.05</v>
+        <v>318</v>
       </c>
       <c r="D136" t="n">
         <v>304.31</v>
       </c>
       <c r="E136" t="n">
-        <v>9.74</v>
+        <v>13.69</v>
       </c>
       <c r="F136" t="n">
-        <v>318.95</v>
+        <v>318.5</v>
       </c>
       <c r="G136" t="n">
         <v>318.08</v>
       </c>
       <c r="H136" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>312.6</v>
+        <v>306.2</v>
       </c>
       <c r="J136" t="n">
         <v>309.31</v>
       </c>
       <c r="K136" t="n">
-        <v>3.29</v>
+        <v>-3.11</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -8128,31 +8128,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24435.95</v>
+        <v>24471.7</v>
       </c>
       <c r="D12" t="n">
         <v>24435.95</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F12" t="n">
-        <v>24473.3</v>
+        <v>24576.85</v>
       </c>
       <c r="G12" t="n">
         <v>24517.51</v>
       </c>
       <c r="H12" t="n">
-        <v>-44.21</v>
+        <v>59.34</v>
       </c>
       <c r="I12" t="n">
-        <v>24265.95</v>
+        <v>24429.25</v>
       </c>
       <c r="J12" t="n">
         <v>24310.16</v>
       </c>
       <c r="K12" t="n">
-        <v>-44.21</v>
+        <v>119.09</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
@@ -8180,31 +8180,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57885.85</v>
+        <v>57446.25</v>
       </c>
       <c r="D13" t="n">
         <v>57885.85</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-439.6</v>
       </c>
       <c r="F13" t="n">
-        <v>57885.85</v>
+        <v>57607.25</v>
       </c>
       <c r="G13" t="n">
         <v>58096.46</v>
       </c>
       <c r="H13" t="n">
-        <v>-210.61</v>
+        <v>-489.21</v>
       </c>
       <c r="I13" t="n">
-        <v>57254</v>
+        <v>57158.1</v>
       </c>
       <c r="J13" t="n">
         <v>57464.61</v>
       </c>
       <c r="K13" t="n">
-        <v>-210.61</v>
+        <v>-306.51</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -13934,31 +13934,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5895</v>
+        <v>5865.5</v>
       </c>
       <c r="D110" t="n">
         <v>6177.02</v>
       </c>
       <c r="E110" t="n">
-        <v>-282.02</v>
+        <v>-311.52</v>
       </c>
       <c r="F110" t="n">
-        <v>5916</v>
+        <v>5937</v>
       </c>
       <c r="G110" t="n">
         <v>6088.42</v>
       </c>
       <c r="H110" t="n">
-        <v>-172.42</v>
+        <v>-151.42</v>
       </c>
       <c r="I110" t="n">
-        <v>5844</v>
+        <v>5803.5</v>
       </c>
       <c r="J110" t="n">
         <v>5808.58</v>
       </c>
       <c r="K110" t="n">
-        <v>35.42</v>
+        <v>-5.08</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>4.57</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="111">
@@ -13986,31 +13986,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2740</v>
+        <v>2735.5</v>
       </c>
       <c r="D111" t="n">
         <v>2900.21</v>
       </c>
       <c r="E111" t="n">
-        <v>-160.21</v>
+        <v>-164.71</v>
       </c>
       <c r="F111" t="n">
-        <v>2748.4</v>
+        <v>2747.6</v>
       </c>
       <c r="G111" t="n">
         <v>2818.87</v>
       </c>
       <c r="H111" t="n">
-        <v>-70.47</v>
+        <v>-71.27</v>
       </c>
       <c r="I111" t="n">
-        <v>2698.2</v>
+        <v>2720</v>
       </c>
       <c r="J111" t="n">
         <v>2708.16</v>
       </c>
       <c r="K111" t="n">
-        <v>-9.960000000000001</v>
+        <v>11.84</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>5.52</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="112">
@@ -14038,31 +14038,31 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>118.98</v>
+        <v>114.03</v>
       </c>
       <c r="D112" t="n">
         <v>118.47</v>
       </c>
       <c r="E112" t="n">
-        <v>0.51</v>
+        <v>-4.44</v>
       </c>
       <c r="F112" t="n">
-        <v>119.5</v>
+        <v>114.3</v>
       </c>
       <c r="G112" t="n">
         <v>121.16</v>
       </c>
       <c r="H112" t="n">
-        <v>-1.66</v>
+        <v>-6.86</v>
       </c>
       <c r="I112" t="n">
-        <v>113.72</v>
+        <v>112.3</v>
       </c>
       <c r="J112" t="n">
         <v>118.54</v>
       </c>
       <c r="K112" t="n">
-        <v>-4.82</v>
+        <v>-6.24</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -14071,11 +14071,11 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0.43</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="113">
@@ -14090,31 +14090,31 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11579</v>
+        <v>11550</v>
       </c>
       <c r="D113" t="n">
         <v>11783.36</v>
       </c>
       <c r="E113" t="n">
-        <v>-204.36</v>
+        <v>-233.36</v>
       </c>
       <c r="F113" t="n">
-        <v>11587</v>
+        <v>11599</v>
       </c>
       <c r="G113" t="n">
         <v>11879.66</v>
       </c>
       <c r="H113" t="n">
-        <v>-292.66</v>
+        <v>-280.66</v>
       </c>
       <c r="I113" t="n">
-        <v>11410</v>
+        <v>11412</v>
       </c>
       <c r="J113" t="n">
         <v>11469.14</v>
       </c>
       <c r="K113" t="n">
-        <v>-59.14</v>
+        <v>-57.14</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="114">
@@ -14142,31 +14142,31 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8049</v>
+        <v>8000</v>
       </c>
       <c r="D114" t="n">
         <v>8211.66</v>
       </c>
       <c r="E114" t="n">
-        <v>-162.66</v>
+        <v>-211.66</v>
       </c>
       <c r="F114" t="n">
-        <v>8049</v>
+        <v>8110</v>
       </c>
       <c r="G114" t="n">
         <v>8251.139999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>-202.14</v>
+        <v>-141.14</v>
       </c>
       <c r="I114" t="n">
-        <v>7940</v>
+        <v>7955</v>
       </c>
       <c r="J114" t="n">
         <v>7977.81</v>
       </c>
       <c r="K114" t="n">
-        <v>-37.81</v>
+        <v>-22.81</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -14175,11 +14175,11 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="115">
@@ -14194,31 +14194,31 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>176.7</v>
+        <v>174.83</v>
       </c>
       <c r="D115" t="n">
         <v>181.04</v>
       </c>
       <c r="E115" t="n">
-        <v>-4.34</v>
+        <v>-6.21</v>
       </c>
       <c r="F115" t="n">
-        <v>177.38</v>
+        <v>176.33</v>
       </c>
       <c r="G115" t="n">
         <v>182.47</v>
       </c>
       <c r="H115" t="n">
-        <v>-5.09</v>
+        <v>-6.14</v>
       </c>
       <c r="I115" t="n">
-        <v>174.43</v>
+        <v>172</v>
       </c>
       <c r="J115" t="n">
         <v>174.13</v>
       </c>
       <c r="K115" t="n">
-        <v>0.3</v>
+        <v>-2.13</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -14227,11 +14227,11 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="116">
@@ -14246,31 +14246,31 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>11891</v>
+        <v>11780</v>
       </c>
       <c r="D116" t="n">
         <v>12228.54</v>
       </c>
       <c r="E116" t="n">
-        <v>-337.54</v>
+        <v>-448.54</v>
       </c>
       <c r="F116" t="n">
-        <v>11891</v>
+        <v>12061</v>
       </c>
       <c r="G116" t="n">
         <v>12150.06</v>
       </c>
       <c r="H116" t="n">
-        <v>-259.06</v>
+        <v>-89.06</v>
       </c>
       <c r="I116" t="n">
-        <v>11650</v>
+        <v>11720</v>
       </c>
       <c r="J116" t="n">
         <v>11815.73</v>
       </c>
       <c r="K116" t="n">
-        <v>-165.73</v>
+        <v>-95.73</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2.76</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="117">
@@ -14298,31 +14298,31 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1945</v>
+        <v>1915.2</v>
       </c>
       <c r="D117" t="n">
         <v>1972.57</v>
       </c>
       <c r="E117" t="n">
-        <v>-27.57</v>
+        <v>-57.37</v>
       </c>
       <c r="F117" t="n">
-        <v>1945</v>
+        <v>1938.3</v>
       </c>
       <c r="G117" t="n">
         <v>1988.96</v>
       </c>
       <c r="H117" t="n">
-        <v>-43.96</v>
+        <v>-50.66</v>
       </c>
       <c r="I117" t="n">
-        <v>1901.3</v>
+        <v>1914.4</v>
       </c>
       <c r="J117" t="n">
         <v>1931.49</v>
       </c>
       <c r="K117" t="n">
-        <v>-30.19</v>
+        <v>-17.09</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -14331,11 +14331,11 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1.4</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="118">
@@ -14350,31 +14350,31 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11679</v>
+        <v>11896</v>
       </c>
       <c r="D118" t="n">
         <v>12120.46</v>
       </c>
       <c r="E118" t="n">
-        <v>-441.46</v>
+        <v>-224.46</v>
       </c>
       <c r="F118" t="n">
-        <v>11899</v>
+        <v>11968</v>
       </c>
       <c r="G118" t="n">
         <v>12210.25</v>
       </c>
       <c r="H118" t="n">
-        <v>-311.25</v>
+        <v>-242.25</v>
       </c>
       <c r="I118" t="n">
-        <v>11532</v>
+        <v>11675</v>
       </c>
       <c r="J118" t="n">
         <v>11395.96</v>
       </c>
       <c r="K118" t="n">
-        <v>136.04</v>
+        <v>279.04</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -14383,11 +14383,11 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3.64</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="119">
@@ -14402,31 +14402,31 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>187</v>
+        <v>182.5</v>
       </c>
       <c r="D119" t="n">
         <v>187.69</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-5.19</v>
       </c>
       <c r="F119" t="n">
-        <v>187.6</v>
+        <v>184.85</v>
       </c>
       <c r="G119" t="n">
         <v>192.58</v>
       </c>
       <c r="H119" t="n">
-        <v>-4.98</v>
+        <v>-7.73</v>
       </c>
       <c r="I119" t="n">
-        <v>181.82</v>
+        <v>179.88</v>
       </c>
       <c r="J119" t="n">
         <v>184.67</v>
       </c>
       <c r="K119" t="n">
-        <v>-2.85</v>
+        <v>-4.79</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -14435,11 +14435,11 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0.37</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="120">
@@ -14454,31 +14454,31 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>5333</v>
+        <v>5284</v>
       </c>
       <c r="D120" t="n">
         <v>5549.1</v>
       </c>
       <c r="E120" t="n">
-        <v>-216.1</v>
+        <v>-265.1</v>
       </c>
       <c r="F120" t="n">
-        <v>5333</v>
+        <v>5330</v>
       </c>
       <c r="G120" t="n">
         <v>5498.13</v>
       </c>
       <c r="H120" t="n">
-        <v>-165.13</v>
+        <v>-168.13</v>
       </c>
       <c r="I120" t="n">
-        <v>5228</v>
+        <v>5217.5</v>
       </c>
       <c r="J120" t="n">
         <v>5262.28</v>
       </c>
       <c r="K120" t="n">
-        <v>-34.28</v>
+        <v>-44.78</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3.89</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="121">
@@ -14506,31 +14506,31 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1232.4</v>
+        <v>1275</v>
       </c>
       <c r="D121" t="n">
         <v>1303.87</v>
       </c>
       <c r="E121" t="n">
-        <v>-71.47</v>
+        <v>-28.87</v>
       </c>
       <c r="F121" t="n">
-        <v>1278.7</v>
+        <v>1291.1</v>
       </c>
       <c r="G121" t="n">
         <v>1271.07</v>
       </c>
       <c r="H121" t="n">
-        <v>7.63</v>
+        <v>20.03</v>
       </c>
       <c r="I121" t="n">
-        <v>1232.4</v>
+        <v>1267</v>
       </c>
       <c r="J121" t="n">
         <v>1215.67</v>
       </c>
       <c r="K121" t="n">
-        <v>16.73</v>
+        <v>51.33</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -14539,11 +14539,11 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>5.48</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="122">
@@ -14558,31 +14558,31 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2240</v>
+        <v>2200</v>
       </c>
       <c r="D122" t="n">
         <v>2291.52</v>
       </c>
       <c r="E122" t="n">
-        <v>-51.52</v>
+        <v>-91.52</v>
       </c>
       <c r="F122" t="n">
-        <v>2245</v>
+        <v>2237</v>
       </c>
       <c r="G122" t="n">
         <v>2309.78</v>
       </c>
       <c r="H122" t="n">
-        <v>-64.78</v>
+        <v>-72.78</v>
       </c>
       <c r="I122" t="n">
-        <v>2192.7</v>
+        <v>2200</v>
       </c>
       <c r="J122" t="n">
         <v>2209.97</v>
       </c>
       <c r="K122" t="n">
-        <v>-17.27</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -14591,11 +14591,11 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>2.25</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="123">
@@ -14610,31 +14610,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5474</v>
+        <v>5536</v>
       </c>
       <c r="D123" t="n">
         <v>5612.24</v>
       </c>
       <c r="E123" t="n">
-        <v>-138.24</v>
+        <v>-76.23999999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>5530</v>
+        <v>5544</v>
       </c>
       <c r="G123" t="n">
         <v>5693.68</v>
       </c>
       <c r="H123" t="n">
-        <v>-163.68</v>
+        <v>-149.68</v>
       </c>
       <c r="I123" t="n">
-        <v>5390</v>
+        <v>5430.5</v>
       </c>
       <c r="J123" t="n">
         <v>5363.5</v>
       </c>
       <c r="K123" t="n">
-        <v>26.5</v>
+        <v>67</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.46</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="124">
@@ -14662,31 +14662,31 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1625</v>
+        <v>1643</v>
       </c>
       <c r="D124" t="n">
         <v>1685.24</v>
       </c>
       <c r="E124" t="n">
-        <v>-60.24</v>
+        <v>-42.24</v>
       </c>
       <c r="F124" t="n">
-        <v>1657</v>
+        <v>1660.3</v>
       </c>
       <c r="G124" t="n">
         <v>1675.23</v>
       </c>
       <c r="H124" t="n">
-        <v>-18.23</v>
+        <v>-14.93</v>
       </c>
       <c r="I124" t="n">
-        <v>1622.1</v>
+        <v>1640</v>
       </c>
       <c r="J124" t="n">
         <v>1603.52</v>
       </c>
       <c r="K124" t="n">
-        <v>18.58</v>
+        <v>36.48</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>3.57</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="125">
@@ -14714,31 +14714,31 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>512.05</v>
+        <v>512</v>
       </c>
       <c r="D125" t="n">
         <v>522.52</v>
       </c>
       <c r="E125" t="n">
-        <v>-10.47</v>
+        <v>-10.52</v>
       </c>
       <c r="F125" t="n">
-        <v>523.8</v>
+        <v>512</v>
       </c>
       <c r="G125" t="n">
         <v>528.67</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.87</v>
+        <v>-16.67</v>
       </c>
       <c r="I125" t="n">
-        <v>510.4</v>
+        <v>498.75</v>
       </c>
       <c r="J125" t="n">
         <v>504.68</v>
       </c>
       <c r="K125" t="n">
-        <v>5.72</v>
+        <v>-5.93</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="126">
@@ -14766,31 +14766,31 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>279.85</v>
+        <v>277</v>
       </c>
       <c r="D126" t="n">
         <v>285.48</v>
       </c>
       <c r="E126" t="n">
-        <v>-5.63</v>
+        <v>-8.48</v>
       </c>
       <c r="F126" t="n">
-        <v>281.9</v>
+        <v>279.15</v>
       </c>
       <c r="G126" t="n">
         <v>287.79</v>
       </c>
       <c r="H126" t="n">
-        <v>-5.89</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>277</v>
+        <v>273.4</v>
       </c>
       <c r="J126" t="n">
         <v>276.68</v>
       </c>
       <c r="K126" t="n">
-        <v>0.32</v>
+        <v>-3.28</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -14799,11 +14799,11 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1.97</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="127">
@@ -14818,31 +14818,31 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>614.65</v>
+        <v>616</v>
       </c>
       <c r="D127" t="n">
         <v>621.11</v>
       </c>
       <c r="E127" t="n">
-        <v>-6.46</v>
+        <v>-5.11</v>
       </c>
       <c r="F127" t="n">
-        <v>620.8</v>
+        <v>627</v>
       </c>
       <c r="G127" t="n">
         <v>641.2</v>
       </c>
       <c r="H127" t="n">
-        <v>-20.4</v>
+        <v>-14.2</v>
       </c>
       <c r="I127" t="n">
-        <v>604.25</v>
+        <v>613.1</v>
       </c>
       <c r="J127" t="n">
         <v>600.8200000000001</v>
       </c>
       <c r="K127" t="n">
-        <v>3.43</v>
+        <v>12.28</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="128">
@@ -14870,31 +14870,31 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4020</v>
+        <v>4037.4</v>
       </c>
       <c r="D128" t="n">
         <v>4138.24</v>
       </c>
       <c r="E128" t="n">
-        <v>-118.24</v>
+        <v>-100.84</v>
       </c>
       <c r="F128" t="n">
-        <v>4044.1</v>
+        <v>4075.5</v>
       </c>
       <c r="G128" t="n">
         <v>4102.15</v>
       </c>
       <c r="H128" t="n">
-        <v>-58.05</v>
+        <v>-26.65</v>
       </c>
       <c r="I128" t="n">
-        <v>3990</v>
+        <v>4028.5</v>
       </c>
       <c r="J128" t="n">
         <v>3998.67</v>
       </c>
       <c r="K128" t="n">
-        <v>-8.67</v>
+        <v>29.83</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -14903,11 +14903,11 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="129">
@@ -14922,31 +14922,31 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1801.5</v>
+        <v>1819</v>
       </c>
       <c r="D129" t="n">
         <v>1932.65</v>
       </c>
       <c r="E129" t="n">
-        <v>-131.15</v>
+        <v>-113.65</v>
       </c>
       <c r="F129" t="n">
-        <v>1819.1</v>
+        <v>1836</v>
       </c>
       <c r="G129" t="n">
         <v>1875.33</v>
       </c>
       <c r="H129" t="n">
-        <v>-56.23</v>
+        <v>-39.33</v>
       </c>
       <c r="I129" t="n">
-        <v>1780.4</v>
+        <v>1809.8</v>
       </c>
       <c r="J129" t="n">
         <v>1763.98</v>
       </c>
       <c r="K129" t="n">
-        <v>16.42</v>
+        <v>45.82</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>6.79</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="130">
@@ -14974,31 +14974,31 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3403.6</v>
+        <v>3460.1</v>
       </c>
       <c r="D130" t="n">
         <v>3472.84</v>
       </c>
       <c r="E130" t="n">
-        <v>-69.23999999999999</v>
+        <v>-12.74</v>
       </c>
       <c r="F130" t="n">
-        <v>3471.8</v>
+        <v>3514.6</v>
       </c>
       <c r="G130" t="n">
         <v>3514.37</v>
       </c>
       <c r="H130" t="n">
-        <v>-42.57</v>
+        <v>0.23</v>
       </c>
       <c r="I130" t="n">
-        <v>3403.6</v>
+        <v>3455.1</v>
       </c>
       <c r="J130" t="n">
         <v>3354.39</v>
       </c>
       <c r="K130" t="n">
-        <v>49.21</v>
+        <v>100.71</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>1.99</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="131">
@@ -15035,22 +15035,22 @@
         <v>-49.83</v>
       </c>
       <c r="F131" t="n">
-        <v>1468.8</v>
+        <v>1469.8</v>
       </c>
       <c r="G131" t="n">
         <v>1500.86</v>
       </c>
       <c r="H131" t="n">
-        <v>-32.06</v>
+        <v>-31.06</v>
       </c>
       <c r="I131" t="n">
-        <v>1456.1</v>
+        <v>1457.2</v>
       </c>
       <c r="J131" t="n">
         <v>1449.22</v>
       </c>
       <c r="K131" t="n">
-        <v>6.88</v>
+        <v>7.98</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -15078,31 +15078,31 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>314.05</v>
+        <v>318</v>
       </c>
       <c r="D132" t="n">
         <v>314.46</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.41</v>
+        <v>3.54</v>
       </c>
       <c r="F132" t="n">
-        <v>318.95</v>
+        <v>318.5</v>
       </c>
       <c r="G132" t="n">
         <v>326.43</v>
       </c>
       <c r="H132" t="n">
-        <v>-7.48</v>
+        <v>-7.93</v>
       </c>
       <c r="I132" t="n">
-        <v>312.6</v>
+        <v>306.2</v>
       </c>
       <c r="J132" t="n">
         <v>307.88</v>
       </c>
       <c r="K132" t="n">
-        <v>4.72</v>
+        <v>-1.68</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0.13</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="133">
@@ -15130,31 +15130,31 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2020.5</v>
+        <v>2032</v>
       </c>
       <c r="D133" t="n">
         <v>2141.19</v>
       </c>
       <c r="E133" t="n">
-        <v>-120.69</v>
+        <v>-109.19</v>
       </c>
       <c r="F133" t="n">
-        <v>2028.4</v>
+        <v>2043.9</v>
       </c>
       <c r="G133" t="n">
         <v>2083.43</v>
       </c>
       <c r="H133" t="n">
-        <v>-55.03</v>
+        <v>-39.53</v>
       </c>
       <c r="I133" t="n">
-        <v>2006.1</v>
+        <v>2012</v>
       </c>
       <c r="J133" t="n">
         <v>1993.42</v>
       </c>
       <c r="K133" t="n">
-        <v>12.68</v>
+        <v>18.58</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>5.64</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="134">
@@ -15182,31 +15182,31 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="D134" t="n">
         <v>1425.56</v>
       </c>
       <c r="E134" t="n">
-        <v>-86.56</v>
+        <v>-65.56</v>
       </c>
       <c r="F134" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="G134" t="n">
         <v>1393.89</v>
       </c>
       <c r="H134" t="n">
-        <v>-29.89</v>
+        <v>-2.89</v>
       </c>
       <c r="I134" t="n">
-        <v>1329.6</v>
+        <v>1291.1</v>
       </c>
       <c r="J134" t="n">
         <v>1311.1</v>
       </c>
       <c r="K134" t="n">
-        <v>18.5</v>
+        <v>-20</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>6.07</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="135">
@@ -15234,31 +15234,31 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="D135" t="n">
         <v>1237.34</v>
       </c>
       <c r="E135" t="n">
-        <v>-76.34</v>
+        <v>-69.34</v>
       </c>
       <c r="F135" t="n">
-        <v>1167.5</v>
+        <v>1176.7</v>
       </c>
       <c r="G135" t="n">
         <v>1201.87</v>
       </c>
       <c r="H135" t="n">
-        <v>-34.37</v>
+        <v>-25.17</v>
       </c>
       <c r="I135" t="n">
-        <v>1140</v>
+        <v>1147.8</v>
       </c>
       <c r="J135" t="n">
         <v>1141.89</v>
       </c>
       <c r="K135" t="n">
-        <v>-1.89</v>
+        <v>5.91</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>6.17</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="136">
@@ -15286,31 +15286,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>13800</v>
+        <v>14023</v>
       </c>
       <c r="D136" t="n">
         <v>14415.02</v>
       </c>
       <c r="E136" t="n">
-        <v>-615.02</v>
+        <v>-392.02</v>
       </c>
       <c r="F136" t="n">
-        <v>14090</v>
+        <v>14198</v>
       </c>
       <c r="G136" t="n">
         <v>14253.96</v>
       </c>
       <c r="H136" t="n">
-        <v>-163.96</v>
+        <v>-55.96</v>
       </c>
       <c r="I136" t="n">
-        <v>13670</v>
+        <v>14011</v>
       </c>
       <c r="J136" t="n">
         <v>13596.83</v>
       </c>
       <c r="K136" t="n">
-        <v>73.17</v>
+        <v>414.17</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>4.27</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7508,6 +7508,1618 @@
       </c>
       <c r="N136" t="n">
         <v>4.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D137" t="n">
+        <v>8102.18</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="F137" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>8102.18</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8011</v>
+      </c>
+      <c r="J137" t="n">
+        <v>7927.17</v>
+      </c>
+      <c r="K137" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1071.36</v>
+      </c>
+      <c r="E138" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1086.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1094.8</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1074.26</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1639</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1651.35</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1652.8</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1661.69</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1626.3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1630.69</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1252.87</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1264.7</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1254.77</v>
+      </c>
+      <c r="H140" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1237</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1231.28</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5523</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5678.86</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-155.86</v>
+      </c>
+      <c r="F141" t="n">
+        <v>5529</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5678.86</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-149.86</v>
+      </c>
+      <c r="I141" t="n">
+        <v>5406</v>
+      </c>
+      <c r="J141" t="n">
+        <v>5482.76</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1795.92</v>
+      </c>
+      <c r="E142" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1829.9</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1795.92</v>
+      </c>
+      <c r="H142" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1788</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1760.38</v>
+      </c>
+      <c r="K142" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>5370</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5281.32</v>
+      </c>
+      <c r="E143" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>5370</v>
+      </c>
+      <c r="G143" t="n">
+        <v>5323.7</v>
+      </c>
+      <c r="H143" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5281.5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>5225.19</v>
+      </c>
+      <c r="K143" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>11500</v>
+      </c>
+      <c r="D144" t="n">
+        <v>11583.54</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-83.54000000000001</v>
+      </c>
+      <c r="F144" t="n">
+        <v>11570</v>
+      </c>
+      <c r="G144" t="n">
+        <v>11583.54</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-13.54</v>
+      </c>
+      <c r="I144" t="n">
+        <v>11410</v>
+      </c>
+      <c r="J144" t="n">
+        <v>11237.11</v>
+      </c>
+      <c r="K144" t="n">
+        <v>172.89</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D145" t="n">
+        <v>5748.02</v>
+      </c>
+      <c r="E145" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="F145" t="n">
+        <v>5934</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5783.85</v>
+      </c>
+      <c r="H145" t="n">
+        <v>150.15</v>
+      </c>
+      <c r="I145" t="n">
+        <v>5802</v>
+      </c>
+      <c r="J145" t="n">
+        <v>5685.73</v>
+      </c>
+      <c r="K145" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2670.88</v>
+      </c>
+      <c r="E146" t="n">
+        <v>84.62</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2779.43</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-23.93</v>
+      </c>
+      <c r="I146" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2727.08</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>615</v>
+      </c>
+      <c r="D147" t="n">
+        <v>637.74</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-22.74</v>
+      </c>
+      <c r="F147" t="n">
+        <v>615.3</v>
+      </c>
+      <c r="G147" t="n">
+        <v>637.74</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-22.44</v>
+      </c>
+      <c r="I147" t="n">
+        <v>603</v>
+      </c>
+      <c r="J147" t="n">
+        <v>599.63</v>
+      </c>
+      <c r="K147" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>4058.3</v>
+      </c>
+      <c r="E148" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="G148" t="n">
+        <v>4090.61</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-19.91</v>
+      </c>
+      <c r="I148" t="n">
+        <v>3990</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4013.03</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-23.03</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>3428.2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3533.38</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-105.18</v>
+      </c>
+      <c r="F149" t="n">
+        <v>3440</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3533.38</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-93.38</v>
+      </c>
+      <c r="I149" t="n">
+        <v>3396.5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3329.44</v>
+      </c>
+      <c r="K149" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>318</v>
+      </c>
+      <c r="D150" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="F150" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="G150" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-15.61</v>
+      </c>
+      <c r="I150" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>313.13</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>533.65</v>
+      </c>
+      <c r="D151" t="n">
+        <v>540.89</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="F151" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>540.89</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="I151" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>517.74</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>14035</v>
+      </c>
+      <c r="D152" t="n">
+        <v>14129.03</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-94.03</v>
+      </c>
+      <c r="F152" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G152" t="n">
+        <v>14129.03</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-64.03</v>
+      </c>
+      <c r="I152" t="n">
+        <v>13645</v>
+      </c>
+      <c r="J152" t="n">
+        <v>13608.7</v>
+      </c>
+      <c r="K152" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="D153" t="n">
+        <v>186.89</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="F153" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="G153" t="n">
+        <v>188.82</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I153" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="J153" t="n">
+        <v>185.29</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>176.23</v>
+      </c>
+      <c r="D154" t="n">
+        <v>176.08</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F154" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="G154" t="n">
+        <v>176.89</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I154" t="n">
+        <v>176.23</v>
+      </c>
+      <c r="J154" t="n">
+        <v>173.52</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1357.3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1350.91</v>
+      </c>
+      <c r="E155" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1369.4</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1350.91</v>
+      </c>
+      <c r="H155" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1305.64</v>
+      </c>
+      <c r="K155" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1985.19</v>
+      </c>
+      <c r="E156" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2038</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1985.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="I156" t="n">
+        <v>2006.7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1968.88</v>
+      </c>
+      <c r="K156" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>7710</v>
+      </c>
+      <c r="D157" t="n">
+        <v>7639.04</v>
+      </c>
+      <c r="E157" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="F157" t="n">
+        <v>7772</v>
+      </c>
+      <c r="G157" t="n">
+        <v>7823.79</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-51.79</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7659</v>
+      </c>
+      <c r="J157" t="n">
+        <v>7678.06</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-19.06</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>11706</v>
+      </c>
+      <c r="D158" t="n">
+        <v>11538.88</v>
+      </c>
+      <c r="E158" t="n">
+        <v>167.12</v>
+      </c>
+      <c r="F158" t="n">
+        <v>11905</v>
+      </c>
+      <c r="G158" t="n">
+        <v>11538.88</v>
+      </c>
+      <c r="H158" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="I158" t="n">
+        <v>11570</v>
+      </c>
+      <c r="J158" t="n">
+        <v>11473.64</v>
+      </c>
+      <c r="K158" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2237.1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2218.67</v>
+      </c>
+      <c r="E159" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2273.9</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2218.67</v>
+      </c>
+      <c r="H159" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2219.5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2173.44</v>
+      </c>
+      <c r="K159" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1939.1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1928.09</v>
+      </c>
+      <c r="E160" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1957.36</v>
+      </c>
+      <c r="H160" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1920.55</v>
+      </c>
+      <c r="K160" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1046.25</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E161" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1073</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1052.94</v>
+      </c>
+      <c r="H161" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1040</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1033.02</v>
+      </c>
+      <c r="K161" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="D162" t="n">
+        <v>115.42</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F162" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="G162" t="n">
+        <v>116.28</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I162" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="J162" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="D163" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F163" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="G163" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="H163" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="I163" t="n">
+        <v>273</v>
+      </c>
+      <c r="J163" t="n">
+        <v>272.79</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1158.28</v>
+      </c>
+      <c r="E164" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1184.9</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1176.27</v>
+      </c>
+      <c r="H164" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1149.2</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1153.53</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="D165" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F165" t="n">
+        <v>413.65</v>
+      </c>
+      <c r="G165" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="H165" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="I165" t="n">
+        <v>400</v>
+      </c>
+      <c r="J165" t="n">
+        <v>387.32</v>
+      </c>
+      <c r="K165" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1458.8</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1451.27</v>
+      </c>
+      <c r="E166" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1476.44</v>
+      </c>
+      <c r="H166" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1456.2</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1452.16</v>
+      </c>
+      <c r="K166" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>897</v>
+      </c>
+      <c r="D167" t="n">
+        <v>887.36</v>
+      </c>
+      <c r="E167" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="F167" t="n">
+        <v>903.8</v>
+      </c>
+      <c r="G167" t="n">
+        <v>906.5599999999999</v>
+      </c>
+      <c r="H167" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="I167" t="n">
+        <v>883.15</v>
+      </c>
+      <c r="J167" t="n">
+        <v>889.5599999999999</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>
@@ -7521,7 +9133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8218,6 +9830,110 @@
       </c>
       <c r="N13" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>24431.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24447.84</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>24311.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24327.64</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>57799.15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>57773.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>57548.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>57522.85</v>
+      </c>
+      <c r="K15" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8231,7 +9947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15326,6 +17042,1618 @@
         <v>2.72</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D137" t="n">
+        <v>8244.049999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-144.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>8180.71</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-80.70999999999999</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8011</v>
+      </c>
+      <c r="J137" t="n">
+        <v>7990.12</v>
+      </c>
+      <c r="K137" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1090.86</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-7.86</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1086.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1094.5</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1067.78</v>
+      </c>
+      <c r="K138" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2730.94</v>
+      </c>
+      <c r="E139" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2755.5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2796.03</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-40.53</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2708.16</v>
+      </c>
+      <c r="K139" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>5523</v>
+      </c>
+      <c r="D140" t="n">
+        <v>5863.17</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-340.17</v>
+      </c>
+      <c r="F140" t="n">
+        <v>5529</v>
+      </c>
+      <c r="G140" t="n">
+        <v>5656.75</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-127.75</v>
+      </c>
+      <c r="I140" t="n">
+        <v>5406</v>
+      </c>
+      <c r="J140" t="n">
+        <v>5388.09</v>
+      </c>
+      <c r="K140" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1639</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1690.74</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-51.74</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1652.8</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1666.26</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-13.46</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1626.3</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1608.43</v>
+      </c>
+      <c r="K141" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1857.35</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-28.35</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1829.9</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1876.35</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-46.45</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1788</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1782</v>
+      </c>
+      <c r="K142" t="n">
+        <v>6</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>5370</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5404.49</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-34.49</v>
+      </c>
+      <c r="F143" t="n">
+        <v>5370</v>
+      </c>
+      <c r="G143" t="n">
+        <v>5453.27</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-83.27</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5281.5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>5274.48</v>
+      </c>
+      <c r="K143" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5888.68</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-38.68</v>
+      </c>
+      <c r="F144" t="n">
+        <v>5934</v>
+      </c>
+      <c r="G144" t="n">
+        <v>5947.12</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-13.12</v>
+      </c>
+      <c r="I144" t="n">
+        <v>5802</v>
+      </c>
+      <c r="J144" t="n">
+        <v>5741.05</v>
+      </c>
+      <c r="K144" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1285.61</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-45.61</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1264.7</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1262.55</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1237</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1215.42</v>
+      </c>
+      <c r="K145" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>318</v>
+      </c>
+      <c r="D146" t="n">
+        <v>345.26</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-27.26</v>
+      </c>
+      <c r="F146" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="G146" t="n">
+        <v>325.18</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="I146" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="J146" t="n">
+        <v>310.63</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>11500</v>
+      </c>
+      <c r="D147" t="n">
+        <v>11804.6</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-304.6</v>
+      </c>
+      <c r="F147" t="n">
+        <v>11570</v>
+      </c>
+      <c r="G147" t="n">
+        <v>11631.83</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-61.83</v>
+      </c>
+      <c r="I147" t="n">
+        <v>11410</v>
+      </c>
+      <c r="J147" t="n">
+        <v>11330.86</v>
+      </c>
+      <c r="K147" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>615</v>
+      </c>
+      <c r="D148" t="n">
+        <v>661.27</v>
+      </c>
+      <c r="E148" t="n">
+        <v>-46.27</v>
+      </c>
+      <c r="F148" t="n">
+        <v>615.3</v>
+      </c>
+      <c r="G148" t="n">
+        <v>632.51</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-17.21</v>
+      </c>
+      <c r="I148" t="n">
+        <v>603</v>
+      </c>
+      <c r="J148" t="n">
+        <v>597.99</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4112.83</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-42.13</v>
+      </c>
+      <c r="F149" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="G149" t="n">
+        <v>4095.46</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-24.76</v>
+      </c>
+      <c r="I149" t="n">
+        <v>3990</v>
+      </c>
+      <c r="J149" t="n">
+        <v>4027.53</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-37.53</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>3428.2</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3622.49</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-194.29</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3440</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3487.56</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-47.56</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3396.5</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3362.49</v>
+      </c>
+      <c r="K150" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>533.65</v>
+      </c>
+      <c r="D151" t="n">
+        <v>555.09</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F151" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>543.42</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="I151" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>523.02</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-9.32</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1357.3</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1397.88</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-40.58</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1369.4</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1393.17</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-23.77</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1321.86</v>
+      </c>
+      <c r="K152" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2033.03</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="F153" t="n">
+        <v>2038</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2057.9</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2006.7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1987.84</v>
+      </c>
+      <c r="K153" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>14035</v>
+      </c>
+      <c r="D154" t="n">
+        <v>14508.23</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-473.23</v>
+      </c>
+      <c r="F154" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G154" t="n">
+        <v>14299.69</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-234.69</v>
+      </c>
+      <c r="I154" t="n">
+        <v>13645</v>
+      </c>
+      <c r="J154" t="n">
+        <v>13749.48</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-104.48</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ABB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>7710</v>
+      </c>
+      <c r="D155" t="n">
+        <v>7833.76</v>
+      </c>
+      <c r="E155" t="n">
+        <v>-123.76</v>
+      </c>
+      <c r="F155" t="n">
+        <v>7772</v>
+      </c>
+      <c r="G155" t="n">
+        <v>7857.27</v>
+      </c>
+      <c r="H155" t="n">
+        <v>-85.27</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7659</v>
+      </c>
+      <c r="J155" t="n">
+        <v>7551.73</v>
+      </c>
+      <c r="K155" t="n">
+        <v>107.27</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="D156" t="n">
+        <v>192.02</v>
+      </c>
+      <c r="E156" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="F156" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="G156" t="n">
+        <v>190.12</v>
+      </c>
+      <c r="H156" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="I156" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="J156" t="n">
+        <v>182.62</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>11706</v>
+      </c>
+      <c r="D157" t="n">
+        <v>11723.22</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-17.22</v>
+      </c>
+      <c r="F157" t="n">
+        <v>11905</v>
+      </c>
+      <c r="G157" t="n">
+        <v>11805.5</v>
+      </c>
+      <c r="H157" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I157" t="n">
+        <v>11570</v>
+      </c>
+      <c r="J157" t="n">
+        <v>11560.25</v>
+      </c>
+      <c r="K157" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>176.23</v>
+      </c>
+      <c r="D158" t="n">
+        <v>180.69</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="F158" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="G158" t="n">
+        <v>179.44</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="I158" t="n">
+        <v>176.23</v>
+      </c>
+      <c r="J158" t="n">
+        <v>172.72</v>
+      </c>
+      <c r="K158" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2237.1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2273.83</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-36.73</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2273.9</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2275.07</v>
+      </c>
+      <c r="H159" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2219.5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2194.8</v>
+      </c>
+      <c r="K159" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1939.1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1960.58</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-21.48</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1957.2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1913.74</v>
+      </c>
+      <c r="K160" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1046.25</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1058.02</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1073</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1061.39</v>
+      </c>
+      <c r="H161" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1040</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1028.47</v>
+      </c>
+      <c r="K161" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="D162" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F162" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="G162" t="n">
+        <v>118.47</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I162" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="J162" t="n">
+        <v>116.22</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1191.1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1184.9</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1206.99</v>
+      </c>
+      <c r="H163" t="n">
+        <v>-22.09</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1149.2</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1157.66</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="D164" t="n">
+        <v>407.87</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="F164" t="n">
+        <v>413.65</v>
+      </c>
+      <c r="G164" t="n">
+        <v>409.06</v>
+      </c>
+      <c r="H164" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I164" t="n">
+        <v>400</v>
+      </c>
+      <c r="J164" t="n">
+        <v>391.59</v>
+      </c>
+      <c r="K164" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="D165" t="n">
+        <v>284.62</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="F165" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="G165" t="n">
+        <v>282.61</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I165" t="n">
+        <v>273</v>
+      </c>
+      <c r="J165" t="n">
+        <v>275.1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1458.8</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1473.34</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-14.54</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1471.76</v>
+      </c>
+      <c r="H166" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1456.2</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1440.21</v>
+      </c>
+      <c r="K166" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>897</v>
+      </c>
+      <c r="D167" t="n">
+        <v>904.84</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="F167" t="n">
+        <v>903.8</v>
+      </c>
+      <c r="G167" t="n">
+        <v>907.8200000000001</v>
+      </c>
+      <c r="H167" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="I167" t="n">
+        <v>883.15</v>
+      </c>
+      <c r="J167" t="n">
+        <v>883.4</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stocks Prediction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indexes Prediction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Futures Predictions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7522,31 +7522,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="D137" t="n">
         <v>8102.18</v>
       </c>
       <c r="E137" t="n">
-        <v>-2.18</v>
+        <v>-53.18</v>
       </c>
       <c r="F137" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="G137" t="n">
         <v>8102.18</v>
       </c>
       <c r="H137" t="n">
-        <v>-2.18</v>
+        <v>-53.18</v>
       </c>
       <c r="I137" t="n">
-        <v>8011</v>
+        <v>7940</v>
       </c>
       <c r="J137" t="n">
         <v>7927.17</v>
       </c>
       <c r="K137" t="n">
-        <v>83.83</v>
+        <v>12.83</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>0.03</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="138">
@@ -7574,31 +7574,31 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D138" t="n">
         <v>1071.36</v>
       </c>
       <c r="E138" t="n">
-        <v>11.64</v>
+        <v>10.64</v>
       </c>
       <c r="F138" t="n">
-        <v>1086.8</v>
+        <v>1085.5</v>
       </c>
       <c r="G138" t="n">
         <v>1094.8</v>
       </c>
       <c r="H138" t="n">
-        <v>-8</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="J138" t="n">
         <v>1074.26</v>
       </c>
       <c r="K138" t="n">
-        <v>-1.26</v>
+        <v>-8.26</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="139">
@@ -7626,31 +7626,31 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="D139" t="n">
         <v>1651.35</v>
       </c>
       <c r="E139" t="n">
-        <v>-12.35</v>
+        <v>-26.35</v>
       </c>
       <c r="F139" t="n">
-        <v>1652.8</v>
+        <v>1657</v>
       </c>
       <c r="G139" t="n">
         <v>1661.69</v>
       </c>
       <c r="H139" t="n">
-        <v>-8.890000000000001</v>
+        <v>-4.69</v>
       </c>
       <c r="I139" t="n">
-        <v>1626.3</v>
+        <v>1622.1</v>
       </c>
       <c r="J139" t="n">
         <v>1630.69</v>
       </c>
       <c r="K139" t="n">
-        <v>-4.39</v>
+        <v>-8.59</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="140">
@@ -7678,31 +7678,31 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1240</v>
+        <v>1232.4</v>
       </c>
       <c r="D140" t="n">
         <v>1252.87</v>
       </c>
       <c r="E140" t="n">
-        <v>-12.87</v>
+        <v>-20.47</v>
       </c>
       <c r="F140" t="n">
-        <v>1264.7</v>
+        <v>1278.7</v>
       </c>
       <c r="G140" t="n">
         <v>1254.77</v>
       </c>
       <c r="H140" t="n">
-        <v>9.93</v>
+        <v>23.93</v>
       </c>
       <c r="I140" t="n">
-        <v>1237</v>
+        <v>1232.4</v>
       </c>
       <c r="J140" t="n">
         <v>1231.28</v>
       </c>
       <c r="K140" t="n">
-        <v>5.72</v>
+        <v>1.12</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="141">
@@ -7730,31 +7730,31 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5523</v>
+        <v>5474</v>
       </c>
       <c r="D141" t="n">
         <v>5678.86</v>
       </c>
       <c r="E141" t="n">
-        <v>-155.86</v>
+        <v>-204.86</v>
       </c>
       <c r="F141" t="n">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="G141" t="n">
         <v>5678.86</v>
       </c>
       <c r="H141" t="n">
-        <v>-149.86</v>
+        <v>-148.86</v>
       </c>
       <c r="I141" t="n">
-        <v>5406</v>
+        <v>5390</v>
       </c>
       <c r="J141" t="n">
         <v>5482.76</v>
       </c>
       <c r="K141" t="n">
-        <v>-76.76000000000001</v>
+        <v>-92.76000000000001</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7763,11 +7763,11 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2.74</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="142">
@@ -7782,31 +7782,31 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1829</v>
+        <v>1801.5</v>
       </c>
       <c r="D142" t="n">
         <v>1795.92</v>
       </c>
       <c r="E142" t="n">
-        <v>33.08</v>
+        <v>5.58</v>
       </c>
       <c r="F142" t="n">
-        <v>1829.9</v>
+        <v>1819.1</v>
       </c>
       <c r="G142" t="n">
         <v>1795.92</v>
       </c>
       <c r="H142" t="n">
-        <v>33.98</v>
+        <v>23.18</v>
       </c>
       <c r="I142" t="n">
-        <v>1788</v>
+        <v>1780.4</v>
       </c>
       <c r="J142" t="n">
         <v>1760.38</v>
       </c>
       <c r="K142" t="n">
-        <v>27.62</v>
+        <v>20.02</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>1.84</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="143">
@@ -7834,31 +7834,31 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5370</v>
+        <v>5333</v>
       </c>
       <c r="D143" t="n">
         <v>5281.32</v>
       </c>
       <c r="E143" t="n">
-        <v>88.68000000000001</v>
+        <v>51.68</v>
       </c>
       <c r="F143" t="n">
-        <v>5370</v>
+        <v>5333</v>
       </c>
       <c r="G143" t="n">
         <v>5323.7</v>
       </c>
       <c r="H143" t="n">
-        <v>46.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I143" t="n">
-        <v>5281.5</v>
+        <v>5228</v>
       </c>
       <c r="J143" t="n">
         <v>5225.19</v>
       </c>
       <c r="K143" t="n">
-        <v>56.31</v>
+        <v>2.81</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>1.68</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="144">
@@ -7886,22 +7886,22 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>11500</v>
+        <v>11579</v>
       </c>
       <c r="D144" t="n">
         <v>11583.54</v>
       </c>
       <c r="E144" t="n">
-        <v>-83.54000000000001</v>
+        <v>-4.54</v>
       </c>
       <c r="F144" t="n">
-        <v>11570</v>
+        <v>11587</v>
       </c>
       <c r="G144" t="n">
         <v>11583.54</v>
       </c>
       <c r="H144" t="n">
-        <v>-13.54</v>
+        <v>3.46</v>
       </c>
       <c r="I144" t="n">
         <v>11410</v>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0.72</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="145">
@@ -7938,31 +7938,31 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5850</v>
+        <v>5895</v>
       </c>
       <c r="D145" t="n">
         <v>5748.02</v>
       </c>
       <c r="E145" t="n">
-        <v>101.98</v>
+        <v>146.98</v>
       </c>
       <c r="F145" t="n">
-        <v>5934</v>
+        <v>5916</v>
       </c>
       <c r="G145" t="n">
         <v>5783.85</v>
       </c>
       <c r="H145" t="n">
-        <v>150.15</v>
+        <v>132.15</v>
       </c>
       <c r="I145" t="n">
-        <v>5802</v>
+        <v>5844</v>
       </c>
       <c r="J145" t="n">
         <v>5685.73</v>
       </c>
       <c r="K145" t="n">
-        <v>116.27</v>
+        <v>158.27</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="146">
@@ -7990,31 +7990,31 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2755.5</v>
+        <v>2740</v>
       </c>
       <c r="D146" t="n">
         <v>2670.88</v>
       </c>
       <c r="E146" t="n">
-        <v>84.62</v>
+        <v>69.12</v>
       </c>
       <c r="F146" t="n">
-        <v>2755.5</v>
+        <v>2748.4</v>
       </c>
       <c r="G146" t="n">
         <v>2779.43</v>
       </c>
       <c r="H146" t="n">
-        <v>-23.93</v>
+        <v>-31.03</v>
       </c>
       <c r="I146" t="n">
-        <v>2720</v>
+        <v>2698.2</v>
       </c>
       <c r="J146" t="n">
         <v>2727.08</v>
       </c>
       <c r="K146" t="n">
-        <v>-7.08</v>
+        <v>-28.88</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>3.17</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="147">
@@ -8042,31 +8042,31 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>615</v>
+        <v>614.65</v>
       </c>
       <c r="D147" t="n">
         <v>637.74</v>
       </c>
       <c r="E147" t="n">
-        <v>-22.74</v>
+        <v>-23.09</v>
       </c>
       <c r="F147" t="n">
-        <v>615.3</v>
+        <v>620.8</v>
       </c>
       <c r="G147" t="n">
         <v>637.74</v>
       </c>
       <c r="H147" t="n">
-        <v>-22.44</v>
+        <v>-16.94</v>
       </c>
       <c r="I147" t="n">
-        <v>603</v>
+        <v>604.25</v>
       </c>
       <c r="J147" t="n">
         <v>599.63</v>
       </c>
       <c r="K147" t="n">
-        <v>3.37</v>
+        <v>4.62</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="148">
@@ -8094,22 +8094,22 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4070.7</v>
+        <v>4020</v>
       </c>
       <c r="D148" t="n">
         <v>4058.3</v>
       </c>
       <c r="E148" t="n">
-        <v>12.4</v>
+        <v>-38.3</v>
       </c>
       <c r="F148" t="n">
-        <v>4070.7</v>
+        <v>4044.1</v>
       </c>
       <c r="G148" t="n">
         <v>4090.61</v>
       </c>
       <c r="H148" t="n">
-        <v>-19.91</v>
+        <v>-46.51</v>
       </c>
       <c r="I148" t="n">
         <v>3990</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>0.31</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8146,31 +8146,31 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3428.2</v>
+        <v>3403.6</v>
       </c>
       <c r="D149" t="n">
         <v>3533.38</v>
       </c>
       <c r="E149" t="n">
-        <v>-105.18</v>
+        <v>-129.78</v>
       </c>
       <c r="F149" t="n">
-        <v>3440</v>
+        <v>3471.8</v>
       </c>
       <c r="G149" t="n">
         <v>3533.38</v>
       </c>
       <c r="H149" t="n">
-        <v>-93.38</v>
+        <v>-61.58</v>
       </c>
       <c r="I149" t="n">
-        <v>3396.5</v>
+        <v>3403.6</v>
       </c>
       <c r="J149" t="n">
         <v>3329.44</v>
       </c>
       <c r="K149" t="n">
-        <v>67.06</v>
+        <v>74.16</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2.98</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="150">
@@ -8198,31 +8198,31 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>318</v>
+        <v>314.05</v>
       </c>
       <c r="D150" t="n">
         <v>334.96</v>
       </c>
       <c r="E150" t="n">
-        <v>-16.96</v>
+        <v>-20.91</v>
       </c>
       <c r="F150" t="n">
-        <v>319.35</v>
+        <v>318.95</v>
       </c>
       <c r="G150" t="n">
         <v>334.96</v>
       </c>
       <c r="H150" t="n">
-        <v>-15.61</v>
+        <v>-16.01</v>
       </c>
       <c r="I150" t="n">
-        <v>313.3</v>
+        <v>312.6</v>
       </c>
       <c r="J150" t="n">
         <v>313.13</v>
       </c>
       <c r="K150" t="n">
-        <v>0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>5.06</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="151">
@@ -8250,31 +8250,31 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>533.65</v>
+        <v>512.05</v>
       </c>
       <c r="D151" t="n">
         <v>540.89</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.24</v>
+        <v>-28.84</v>
       </c>
       <c r="F151" t="n">
-        <v>535.5</v>
+        <v>523.8</v>
       </c>
       <c r="G151" t="n">
         <v>540.89</v>
       </c>
       <c r="H151" t="n">
-        <v>-5.39</v>
+        <v>-17.09</v>
       </c>
       <c r="I151" t="n">
-        <v>513.7</v>
+        <v>510.4</v>
       </c>
       <c r="J151" t="n">
         <v>517.74</v>
       </c>
       <c r="K151" t="n">
-        <v>-4.04</v>
+        <v>-7.34</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1.34</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="152">
@@ -8302,31 +8302,31 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>14035</v>
+        <v>13800</v>
       </c>
       <c r="D152" t="n">
         <v>14129.03</v>
       </c>
       <c r="E152" t="n">
-        <v>-94.03</v>
+        <v>-329.03</v>
       </c>
       <c r="F152" t="n">
-        <v>14065</v>
+        <v>14090</v>
       </c>
       <c r="G152" t="n">
         <v>14129.03</v>
       </c>
       <c r="H152" t="n">
-        <v>-64.03</v>
+        <v>-39.03</v>
       </c>
       <c r="I152" t="n">
-        <v>13645</v>
+        <v>13670</v>
       </c>
       <c r="J152" t="n">
         <v>13608.7</v>
       </c>
       <c r="K152" t="n">
-        <v>36.3</v>
+        <v>61.3</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="153">
@@ -8354,31 +8354,31 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>186.5</v>
+        <v>187</v>
       </c>
       <c r="D153" t="n">
         <v>186.89</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.39</v>
+        <v>0.11</v>
       </c>
       <c r="F153" t="n">
-        <v>188.7</v>
+        <v>187.6</v>
       </c>
       <c r="G153" t="n">
         <v>188.82</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.12</v>
+        <v>-1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>185.32</v>
+        <v>181.82</v>
       </c>
       <c r="J153" t="n">
         <v>185.29</v>
       </c>
       <c r="K153" t="n">
-        <v>0.03</v>
+        <v>-3.47</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="154">
@@ -8406,31 +8406,31 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>176.23</v>
+        <v>176.7</v>
       </c>
       <c r="D154" t="n">
         <v>176.08</v>
       </c>
       <c r="E154" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="F154" t="n">
-        <v>182.7</v>
+        <v>177.38</v>
       </c>
       <c r="G154" t="n">
         <v>176.89</v>
       </c>
       <c r="H154" t="n">
-        <v>5.81</v>
+        <v>0.49</v>
       </c>
       <c r="I154" t="n">
-        <v>176.23</v>
+        <v>174.43</v>
       </c>
       <c r="J154" t="n">
         <v>173.52</v>
       </c>
       <c r="K154" t="n">
-        <v>2.71</v>
+        <v>0.91</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="155">
@@ -8458,31 +8458,31 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1357.3</v>
+        <v>1339</v>
       </c>
       <c r="D155" t="n">
         <v>1350.91</v>
       </c>
       <c r="E155" t="n">
-        <v>6.39</v>
+        <v>-11.91</v>
       </c>
       <c r="F155" t="n">
-        <v>1369.4</v>
+        <v>1364</v>
       </c>
       <c r="G155" t="n">
         <v>1350.91</v>
       </c>
       <c r="H155" t="n">
-        <v>18.49</v>
+        <v>13.09</v>
       </c>
       <c r="I155" t="n">
-        <v>1336.5</v>
+        <v>1329.6</v>
       </c>
       <c r="J155" t="n">
         <v>1305.64</v>
       </c>
       <c r="K155" t="n">
-        <v>30.86</v>
+        <v>23.96</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="156">
@@ -8510,31 +8510,31 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2025</v>
+        <v>2020.5</v>
       </c>
       <c r="D156" t="n">
         <v>1985.19</v>
       </c>
       <c r="E156" t="n">
-        <v>39.81</v>
+        <v>35.31</v>
       </c>
       <c r="F156" t="n">
-        <v>2038</v>
+        <v>2028.4</v>
       </c>
       <c r="G156" t="n">
         <v>1985.19</v>
       </c>
       <c r="H156" t="n">
-        <v>52.81</v>
+        <v>43.21</v>
       </c>
       <c r="I156" t="n">
-        <v>2006.7</v>
+        <v>2006.1</v>
       </c>
       <c r="J156" t="n">
         <v>1968.88</v>
       </c>
       <c r="K156" t="n">
-        <v>37.82</v>
+        <v>37.22</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="157">
@@ -8571,22 +8571,22 @@
         <v>70.95999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>7772</v>
+        <v>7741</v>
       </c>
       <c r="G157" t="n">
         <v>7823.79</v>
       </c>
       <c r="H157" t="n">
-        <v>-51.79</v>
+        <v>-82.79000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>7659</v>
+        <v>7585.5</v>
       </c>
       <c r="J157" t="n">
         <v>7678.06</v>
       </c>
       <c r="K157" t="n">
-        <v>-19.06</v>
+        <v>-92.56</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8614,31 +8614,31 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>11706</v>
+        <v>11891</v>
       </c>
       <c r="D158" t="n">
         <v>11538.88</v>
       </c>
       <c r="E158" t="n">
-        <v>167.12</v>
+        <v>352.12</v>
       </c>
       <c r="F158" t="n">
-        <v>11905</v>
+        <v>11891</v>
       </c>
       <c r="G158" t="n">
         <v>11538.88</v>
       </c>
       <c r="H158" t="n">
-        <v>366.12</v>
+        <v>352.12</v>
       </c>
       <c r="I158" t="n">
-        <v>11570</v>
+        <v>11650</v>
       </c>
       <c r="J158" t="n">
         <v>11473.64</v>
       </c>
       <c r="K158" t="n">
-        <v>96.36</v>
+        <v>176.36</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8647,11 +8647,11 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="159">
@@ -8666,31 +8666,31 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2237.1</v>
+        <v>2240</v>
       </c>
       <c r="D159" t="n">
         <v>2218.67</v>
       </c>
       <c r="E159" t="n">
-        <v>18.43</v>
+        <v>21.33</v>
       </c>
       <c r="F159" t="n">
-        <v>2273.9</v>
+        <v>2245</v>
       </c>
       <c r="G159" t="n">
         <v>2218.67</v>
       </c>
       <c r="H159" t="n">
-        <v>55.23</v>
+        <v>26.33</v>
       </c>
       <c r="I159" t="n">
-        <v>2219.5</v>
+        <v>2192.7</v>
       </c>
       <c r="J159" t="n">
         <v>2173.44</v>
       </c>
       <c r="K159" t="n">
-        <v>46.06</v>
+        <v>19.26</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="160">
@@ -8718,31 +8718,31 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1939.1</v>
+        <v>1945</v>
       </c>
       <c r="D160" t="n">
         <v>1928.09</v>
       </c>
       <c r="E160" t="n">
-        <v>11.01</v>
+        <v>16.91</v>
       </c>
       <c r="F160" t="n">
-        <v>1970</v>
+        <v>1945</v>
       </c>
       <c r="G160" t="n">
         <v>1957.36</v>
       </c>
       <c r="H160" t="n">
-        <v>12.64</v>
+        <v>-12.36</v>
       </c>
       <c r="I160" t="n">
-        <v>1930.5</v>
+        <v>1901.3</v>
       </c>
       <c r="J160" t="n">
         <v>1920.55</v>
       </c>
       <c r="K160" t="n">
-        <v>9.949999999999999</v>
+        <v>-19.25</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="161">
@@ -8770,31 +8770,31 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1046.25</v>
+        <v>1078.5</v>
       </c>
       <c r="D161" t="n">
         <v>1035</v>
       </c>
       <c r="E161" t="n">
-        <v>11.25</v>
+        <v>43.5</v>
       </c>
       <c r="F161" t="n">
-        <v>1073</v>
+        <v>1087.95</v>
       </c>
       <c r="G161" t="n">
         <v>1052.94</v>
       </c>
       <c r="H161" t="n">
-        <v>20.06</v>
+        <v>35.01</v>
       </c>
       <c r="I161" t="n">
-        <v>1040</v>
+        <v>1056.9</v>
       </c>
       <c r="J161" t="n">
         <v>1033.02</v>
       </c>
       <c r="K161" t="n">
-        <v>6.98</v>
+        <v>23.88</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8803,11 +8803,11 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="162">
@@ -8822,31 +8822,31 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>117.59</v>
+        <v>118.98</v>
       </c>
       <c r="D162" t="n">
         <v>115.42</v>
       </c>
       <c r="E162" t="n">
-        <v>2.17</v>
+        <v>3.56</v>
       </c>
       <c r="F162" t="n">
-        <v>119.35</v>
+        <v>119.5</v>
       </c>
       <c r="G162" t="n">
         <v>116.28</v>
       </c>
       <c r="H162" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="I162" t="n">
-        <v>117.31</v>
+        <v>113.72</v>
       </c>
       <c r="J162" t="n">
         <v>115.38</v>
       </c>
       <c r="K162" t="n">
-        <v>1.93</v>
+        <v>-1.66</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8855,11 +8855,11 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>1.88</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="163">
@@ -8874,31 +8874,31 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>279.3</v>
+        <v>279.85</v>
       </c>
       <c r="D163" t="n">
         <v>279.16</v>
       </c>
       <c r="E163" t="n">
-        <v>0.14</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F163" t="n">
-        <v>287.4</v>
+        <v>281.9</v>
       </c>
       <c r="G163" t="n">
         <v>279.16</v>
       </c>
       <c r="H163" t="n">
-        <v>8.24</v>
+        <v>2.74</v>
       </c>
       <c r="I163" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J163" t="n">
         <v>272.79</v>
       </c>
       <c r="K163" t="n">
-        <v>0.21</v>
+        <v>4.21</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="164">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1183</v>
+        <v>1161</v>
       </c>
       <c r="D164" t="n">
         <v>1158.28</v>
       </c>
       <c r="E164" t="n">
-        <v>24.72</v>
+        <v>2.72</v>
       </c>
       <c r="F164" t="n">
-        <v>1184.9</v>
+        <v>1167.5</v>
       </c>
       <c r="G164" t="n">
         <v>1176.27</v>
       </c>
       <c r="H164" t="n">
-        <v>8.630000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="I164" t="n">
-        <v>1149.2</v>
+        <v>1140</v>
       </c>
       <c r="J164" t="n">
         <v>1153.53</v>
       </c>
       <c r="K164" t="n">
-        <v>-4.33</v>
+        <v>-13.53</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>2.13</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="165">
@@ -8978,31 +8978,31 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>400.5</v>
+        <v>420</v>
       </c>
       <c r="D165" t="n">
         <v>396.19</v>
       </c>
       <c r="E165" t="n">
-        <v>4.31</v>
+        <v>23.81</v>
       </c>
       <c r="F165" t="n">
-        <v>413.65</v>
+        <v>422.2</v>
       </c>
       <c r="G165" t="n">
         <v>396.19</v>
       </c>
       <c r="H165" t="n">
-        <v>17.46</v>
+        <v>26.01</v>
       </c>
       <c r="I165" t="n">
-        <v>400</v>
+        <v>398.5</v>
       </c>
       <c r="J165" t="n">
         <v>387.32</v>
       </c>
       <c r="K165" t="n">
-        <v>12.68</v>
+        <v>11.18</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9011,11 +9011,11 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1.09</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="166">
@@ -9030,31 +9030,31 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1458.8</v>
+        <v>1463</v>
       </c>
       <c r="D166" t="n">
         <v>1451.27</v>
       </c>
       <c r="E166" t="n">
-        <v>7.53</v>
+        <v>11.73</v>
       </c>
       <c r="F166" t="n">
-        <v>1464.4</v>
+        <v>1468.8</v>
       </c>
       <c r="G166" t="n">
         <v>1476.44</v>
       </c>
       <c r="H166" t="n">
-        <v>-12.04</v>
+        <v>-7.64</v>
       </c>
       <c r="I166" t="n">
-        <v>1456.2</v>
+        <v>1456.1</v>
       </c>
       <c r="J166" t="n">
         <v>1452.16</v>
       </c>
       <c r="K166" t="n">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9091,22 +9091,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="F167" t="n">
-        <v>903.8</v>
+        <v>897.65</v>
       </c>
       <c r="G167" t="n">
         <v>906.5599999999999</v>
       </c>
       <c r="H167" t="n">
-        <v>-2.76</v>
+        <v>-8.91</v>
       </c>
       <c r="I167" t="n">
-        <v>883.15</v>
+        <v>873.1</v>
       </c>
       <c r="J167" t="n">
         <v>889.5599999999999</v>
       </c>
       <c r="K167" t="n">
-        <v>-6.41</v>
+        <v>-16.46</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9844,31 +9844,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24395.85</v>
+        <v>24435.95</v>
       </c>
       <c r="D14" t="n">
         <v>24395.85</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="F14" t="n">
-        <v>24431.6</v>
+        <v>24473.3</v>
       </c>
       <c r="G14" t="n">
         <v>24447.84</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.24</v>
+        <v>25.46</v>
       </c>
       <c r="I14" t="n">
-        <v>24311.4</v>
+        <v>24265.95</v>
       </c>
       <c r="J14" t="n">
         <v>24327.64</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.24</v>
+        <v>-61.69</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15">
@@ -9896,31 +9896,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57635.25</v>
+        <v>57885.85</v>
       </c>
       <c r="D15" t="n">
         <v>57635.25</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>250.6</v>
       </c>
       <c r="F15" t="n">
-        <v>57799.15</v>
+        <v>57885.85</v>
       </c>
       <c r="G15" t="n">
         <v>57773.4</v>
       </c>
       <c r="H15" t="n">
-        <v>25.75</v>
+        <v>112.45</v>
       </c>
       <c r="I15" t="n">
-        <v>57548.6</v>
+        <v>57254</v>
       </c>
       <c r="J15" t="n">
         <v>57522.85</v>
       </c>
       <c r="K15" t="n">
-        <v>25.75</v>
+        <v>-268.85</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -17054,31 +17054,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="D137" t="n">
         <v>8244.049999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>-144.05</v>
+        <v>-195.05</v>
       </c>
       <c r="F137" t="n">
-        <v>8100</v>
+        <v>8049</v>
       </c>
       <c r="G137" t="n">
         <v>8180.71</v>
       </c>
       <c r="H137" t="n">
-        <v>-80.70999999999999</v>
+        <v>-131.71</v>
       </c>
       <c r="I137" t="n">
-        <v>8011</v>
+        <v>7940</v>
       </c>
       <c r="J137" t="n">
         <v>7990.12</v>
       </c>
       <c r="K137" t="n">
-        <v>20.88</v>
+        <v>-50.12</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="138">
@@ -17106,31 +17106,31 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D138" t="n">
         <v>1090.86</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.86</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>1086.8</v>
+        <v>1085.5</v>
       </c>
       <c r="G138" t="n">
         <v>1094.5</v>
       </c>
       <c r="H138" t="n">
-        <v>-7.7</v>
+        <v>-9</v>
       </c>
       <c r="I138" t="n">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="J138" t="n">
         <v>1067.78</v>
       </c>
       <c r="K138" t="n">
-        <v>5.22</v>
+        <v>-1.78</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -17158,31 +17158,31 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2755.5</v>
+        <v>2740</v>
       </c>
       <c r="D139" t="n">
         <v>2730.94</v>
       </c>
       <c r="E139" t="n">
-        <v>24.56</v>
+        <v>9.06</v>
       </c>
       <c r="F139" t="n">
-        <v>2755.5</v>
+        <v>2748.4</v>
       </c>
       <c r="G139" t="n">
         <v>2796.03</v>
       </c>
       <c r="H139" t="n">
-        <v>-40.53</v>
+        <v>-47.63</v>
       </c>
       <c r="I139" t="n">
-        <v>2720</v>
+        <v>2698.2</v>
       </c>
       <c r="J139" t="n">
         <v>2708.16</v>
       </c>
       <c r="K139" t="n">
-        <v>11.84</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0.9</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="140">
@@ -17210,31 +17210,31 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5523</v>
+        <v>5474</v>
       </c>
       <c r="D140" t="n">
         <v>5863.17</v>
       </c>
       <c r="E140" t="n">
-        <v>-340.17</v>
+        <v>-389.17</v>
       </c>
       <c r="F140" t="n">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="G140" t="n">
         <v>5656.75</v>
       </c>
       <c r="H140" t="n">
-        <v>-127.75</v>
+        <v>-126.75</v>
       </c>
       <c r="I140" t="n">
-        <v>5406</v>
+        <v>5390</v>
       </c>
       <c r="J140" t="n">
         <v>5388.09</v>
       </c>
       <c r="K140" t="n">
-        <v>17.91</v>
+        <v>1.91</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5.8</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="141">
@@ -17262,31 +17262,31 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="D141" t="n">
         <v>1690.74</v>
       </c>
       <c r="E141" t="n">
-        <v>-51.74</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="F141" t="n">
-        <v>1652.8</v>
+        <v>1657</v>
       </c>
       <c r="G141" t="n">
         <v>1666.26</v>
       </c>
       <c r="H141" t="n">
-        <v>-13.46</v>
+        <v>-9.26</v>
       </c>
       <c r="I141" t="n">
-        <v>1626.3</v>
+        <v>1622.1</v>
       </c>
       <c r="J141" t="n">
         <v>1608.43</v>
       </c>
       <c r="K141" t="n">
-        <v>17.87</v>
+        <v>13.67</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>3.06</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="142">
@@ -17314,31 +17314,31 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1829</v>
+        <v>1801.5</v>
       </c>
       <c r="D142" t="n">
         <v>1857.35</v>
       </c>
       <c r="E142" t="n">
-        <v>-28.35</v>
+        <v>-55.85</v>
       </c>
       <c r="F142" t="n">
-        <v>1829.9</v>
+        <v>1819.1</v>
       </c>
       <c r="G142" t="n">
         <v>1876.35</v>
       </c>
       <c r="H142" t="n">
-        <v>-46.45</v>
+        <v>-57.25</v>
       </c>
       <c r="I142" t="n">
-        <v>1788</v>
+        <v>1780.4</v>
       </c>
       <c r="J142" t="n">
         <v>1782</v>
       </c>
       <c r="K142" t="n">
-        <v>6</v>
+        <v>-1.6</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -17347,11 +17347,11 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>1.53</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="143">
@@ -17366,31 +17366,31 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5370</v>
+        <v>5333</v>
       </c>
       <c r="D143" t="n">
         <v>5404.49</v>
       </c>
       <c r="E143" t="n">
-        <v>-34.49</v>
+        <v>-71.48999999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>5370</v>
+        <v>5333</v>
       </c>
       <c r="G143" t="n">
         <v>5453.27</v>
       </c>
       <c r="H143" t="n">
-        <v>-83.27</v>
+        <v>-120.27</v>
       </c>
       <c r="I143" t="n">
-        <v>5281.5</v>
+        <v>5228</v>
       </c>
       <c r="J143" t="n">
         <v>5274.48</v>
       </c>
       <c r="K143" t="n">
-        <v>7.02</v>
+        <v>-46.48</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0.64</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="144">
@@ -17418,31 +17418,31 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5850</v>
+        <v>5895</v>
       </c>
       <c r="D144" t="n">
         <v>5888.68</v>
       </c>
       <c r="E144" t="n">
-        <v>-38.68</v>
+        <v>6.32</v>
       </c>
       <c r="F144" t="n">
-        <v>5934</v>
+        <v>5916</v>
       </c>
       <c r="G144" t="n">
         <v>5947.12</v>
       </c>
       <c r="H144" t="n">
-        <v>-13.12</v>
+        <v>-31.12</v>
       </c>
       <c r="I144" t="n">
-        <v>5802</v>
+        <v>5844</v>
       </c>
       <c r="J144" t="n">
         <v>5741.05</v>
       </c>
       <c r="K144" t="n">
-        <v>60.95</v>
+        <v>102.95</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0.66</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="145">
@@ -17470,31 +17470,31 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1240</v>
+        <v>1232.4</v>
       </c>
       <c r="D145" t="n">
         <v>1285.61</v>
       </c>
       <c r="E145" t="n">
-        <v>-45.61</v>
+        <v>-53.21</v>
       </c>
       <c r="F145" t="n">
-        <v>1264.7</v>
+        <v>1278.7</v>
       </c>
       <c r="G145" t="n">
         <v>1262.55</v>
       </c>
       <c r="H145" t="n">
-        <v>2.15</v>
+        <v>16.15</v>
       </c>
       <c r="I145" t="n">
-        <v>1237</v>
+        <v>1232.4</v>
       </c>
       <c r="J145" t="n">
         <v>1215.42</v>
       </c>
       <c r="K145" t="n">
-        <v>21.58</v>
+        <v>16.98</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -17503,11 +17503,11 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>3.55</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="146">
@@ -17522,31 +17522,31 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>318</v>
+        <v>314.05</v>
       </c>
       <c r="D146" t="n">
         <v>345.26</v>
       </c>
       <c r="E146" t="n">
-        <v>-27.26</v>
+        <v>-31.21</v>
       </c>
       <c r="F146" t="n">
-        <v>319.35</v>
+        <v>318.95</v>
       </c>
       <c r="G146" t="n">
         <v>325.18</v>
       </c>
       <c r="H146" t="n">
-        <v>-5.83</v>
+        <v>-6.23</v>
       </c>
       <c r="I146" t="n">
-        <v>313.3</v>
+        <v>312.6</v>
       </c>
       <c r="J146" t="n">
         <v>310.63</v>
       </c>
       <c r="K146" t="n">
-        <v>2.67</v>
+        <v>1.97</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>7.9</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -17574,22 +17574,22 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>11500</v>
+        <v>11579</v>
       </c>
       <c r="D147" t="n">
         <v>11804.6</v>
       </c>
       <c r="E147" t="n">
-        <v>-304.6</v>
+        <v>-225.6</v>
       </c>
       <c r="F147" t="n">
-        <v>11570</v>
+        <v>11587</v>
       </c>
       <c r="G147" t="n">
         <v>11631.83</v>
       </c>
       <c r="H147" t="n">
-        <v>-61.83</v>
+        <v>-44.83</v>
       </c>
       <c r="I147" t="n">
         <v>11410</v>
@@ -17607,11 +17607,11 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N147" t="n">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="148">
@@ -17626,31 +17626,31 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>615</v>
+        <v>614.65</v>
       </c>
       <c r="D148" t="n">
         <v>661.27</v>
       </c>
       <c r="E148" t="n">
-        <v>-46.27</v>
+        <v>-46.62</v>
       </c>
       <c r="F148" t="n">
-        <v>615.3</v>
+        <v>620.8</v>
       </c>
       <c r="G148" t="n">
         <v>632.51</v>
       </c>
       <c r="H148" t="n">
-        <v>-17.21</v>
+        <v>-11.71</v>
       </c>
       <c r="I148" t="n">
-        <v>603</v>
+        <v>604.25</v>
       </c>
       <c r="J148" t="n">
         <v>597.99</v>
       </c>
       <c r="K148" t="n">
-        <v>5.01</v>
+        <v>6.26</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="149">
@@ -17678,22 +17678,22 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4070.7</v>
+        <v>4020</v>
       </c>
       <c r="D149" t="n">
         <v>4112.83</v>
       </c>
       <c r="E149" t="n">
-        <v>-42.13</v>
+        <v>-92.83</v>
       </c>
       <c r="F149" t="n">
-        <v>4070.7</v>
+        <v>4044.1</v>
       </c>
       <c r="G149" t="n">
         <v>4095.46</v>
       </c>
       <c r="H149" t="n">
-        <v>-24.76</v>
+        <v>-51.36</v>
       </c>
       <c r="I149" t="n">
         <v>3990</v>
@@ -17715,7 +17715,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="150">
@@ -17730,31 +17730,31 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3428.2</v>
+        <v>3403.6</v>
       </c>
       <c r="D150" t="n">
         <v>3622.49</v>
       </c>
       <c r="E150" t="n">
-        <v>-194.29</v>
+        <v>-218.89</v>
       </c>
       <c r="F150" t="n">
-        <v>3440</v>
+        <v>3471.8</v>
       </c>
       <c r="G150" t="n">
         <v>3487.56</v>
       </c>
       <c r="H150" t="n">
-        <v>-47.56</v>
+        <v>-15.76</v>
       </c>
       <c r="I150" t="n">
-        <v>3396.5</v>
+        <v>3403.6</v>
       </c>
       <c r="J150" t="n">
         <v>3362.49</v>
       </c>
       <c r="K150" t="n">
-        <v>34.01</v>
+        <v>41.11</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>5.36</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="151">
@@ -17782,31 +17782,31 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>533.65</v>
+        <v>512.05</v>
       </c>
       <c r="D151" t="n">
         <v>555.09</v>
       </c>
       <c r="E151" t="n">
-        <v>-21.44</v>
+        <v>-43.04</v>
       </c>
       <c r="F151" t="n">
-        <v>535.5</v>
+        <v>523.8</v>
       </c>
       <c r="G151" t="n">
         <v>543.42</v>
       </c>
       <c r="H151" t="n">
-        <v>-7.92</v>
+        <v>-19.62</v>
       </c>
       <c r="I151" t="n">
-        <v>513.7</v>
+        <v>510.4</v>
       </c>
       <c r="J151" t="n">
         <v>523.02</v>
       </c>
       <c r="K151" t="n">
-        <v>-9.32</v>
+        <v>-12.62</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3.86</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="152">
@@ -17834,31 +17834,31 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1357.3</v>
+        <v>1339</v>
       </c>
       <c r="D152" t="n">
         <v>1397.88</v>
       </c>
       <c r="E152" t="n">
-        <v>-40.58</v>
+        <v>-58.88</v>
       </c>
       <c r="F152" t="n">
-        <v>1369.4</v>
+        <v>1364</v>
       </c>
       <c r="G152" t="n">
         <v>1393.17</v>
       </c>
       <c r="H152" t="n">
-        <v>-23.77</v>
+        <v>-29.17</v>
       </c>
       <c r="I152" t="n">
-        <v>1336.5</v>
+        <v>1329.6</v>
       </c>
       <c r="J152" t="n">
         <v>1321.86</v>
       </c>
       <c r="K152" t="n">
-        <v>14.64</v>
+        <v>7.74</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>2.9</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="153">
@@ -17886,31 +17886,31 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2025</v>
+        <v>2020.5</v>
       </c>
       <c r="D153" t="n">
         <v>2033.03</v>
       </c>
       <c r="E153" t="n">
-        <v>-8.029999999999999</v>
+        <v>-12.53</v>
       </c>
       <c r="F153" t="n">
-        <v>2038</v>
+        <v>2028.4</v>
       </c>
       <c r="G153" t="n">
         <v>2057.9</v>
       </c>
       <c r="H153" t="n">
-        <v>-19.9</v>
+        <v>-29.5</v>
       </c>
       <c r="I153" t="n">
-        <v>2006.7</v>
+        <v>2006.1</v>
       </c>
       <c r="J153" t="n">
         <v>1987.84</v>
       </c>
       <c r="K153" t="n">
-        <v>18.86</v>
+        <v>18.26</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="154">
@@ -17938,31 +17938,31 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>14035</v>
+        <v>13800</v>
       </c>
       <c r="D154" t="n">
         <v>14508.23</v>
       </c>
       <c r="E154" t="n">
-        <v>-473.23</v>
+        <v>-708.23</v>
       </c>
       <c r="F154" t="n">
-        <v>14065</v>
+        <v>14090</v>
       </c>
       <c r="G154" t="n">
         <v>14299.69</v>
       </c>
       <c r="H154" t="n">
-        <v>-234.69</v>
+        <v>-209.69</v>
       </c>
       <c r="I154" t="n">
-        <v>13645</v>
+        <v>13670</v>
       </c>
       <c r="J154" t="n">
         <v>13749.48</v>
       </c>
       <c r="K154" t="n">
-        <v>-104.48</v>
+        <v>-79.48</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3.26</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="155">
@@ -17999,22 +17999,22 @@
         <v>-123.76</v>
       </c>
       <c r="F155" t="n">
-        <v>7772</v>
+        <v>7741</v>
       </c>
       <c r="G155" t="n">
         <v>7857.27</v>
       </c>
       <c r="H155" t="n">
-        <v>-85.27</v>
+        <v>-116.27</v>
       </c>
       <c r="I155" t="n">
-        <v>7659</v>
+        <v>7585.5</v>
       </c>
       <c r="J155" t="n">
         <v>7551.73</v>
       </c>
       <c r="K155" t="n">
-        <v>107.27</v>
+        <v>33.77</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -18042,31 +18042,31 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>186.5</v>
+        <v>187</v>
       </c>
       <c r="D156" t="n">
         <v>192.02</v>
       </c>
       <c r="E156" t="n">
-        <v>-5.52</v>
+        <v>-5.02</v>
       </c>
       <c r="F156" t="n">
-        <v>188.7</v>
+        <v>187.6</v>
       </c>
       <c r="G156" t="n">
         <v>190.12</v>
       </c>
       <c r="H156" t="n">
-        <v>-1.42</v>
+        <v>-2.52</v>
       </c>
       <c r="I156" t="n">
-        <v>185.32</v>
+        <v>181.82</v>
       </c>
       <c r="J156" t="n">
         <v>182.62</v>
       </c>
       <c r="K156" t="n">
-        <v>2.7</v>
+        <v>-0.8</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="157">
@@ -18094,31 +18094,31 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>11706</v>
+        <v>11891</v>
       </c>
       <c r="D157" t="n">
         <v>11723.22</v>
       </c>
       <c r="E157" t="n">
-        <v>-17.22</v>
+        <v>167.78</v>
       </c>
       <c r="F157" t="n">
-        <v>11905</v>
+        <v>11891</v>
       </c>
       <c r="G157" t="n">
         <v>11805.5</v>
       </c>
       <c r="H157" t="n">
-        <v>99.5</v>
+        <v>85.5</v>
       </c>
       <c r="I157" t="n">
-        <v>11570</v>
+        <v>11650</v>
       </c>
       <c r="J157" t="n">
         <v>11560.25</v>
       </c>
       <c r="K157" t="n">
-        <v>9.75</v>
+        <v>89.75</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0.15</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="158">
@@ -18146,31 +18146,31 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>176.23</v>
+        <v>176.7</v>
       </c>
       <c r="D158" t="n">
         <v>180.69</v>
       </c>
       <c r="E158" t="n">
-        <v>-4.46</v>
+        <v>-3.99</v>
       </c>
       <c r="F158" t="n">
-        <v>182.7</v>
+        <v>177.38</v>
       </c>
       <c r="G158" t="n">
         <v>179.44</v>
       </c>
       <c r="H158" t="n">
-        <v>3.26</v>
+        <v>-2.06</v>
       </c>
       <c r="I158" t="n">
-        <v>176.23</v>
+        <v>174.43</v>
       </c>
       <c r="J158" t="n">
         <v>172.72</v>
       </c>
       <c r="K158" t="n">
-        <v>3.51</v>
+        <v>1.71</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="159">
@@ -18198,31 +18198,31 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2237.1</v>
+        <v>2240</v>
       </c>
       <c r="D159" t="n">
         <v>2273.83</v>
       </c>
       <c r="E159" t="n">
-        <v>-36.73</v>
+        <v>-33.83</v>
       </c>
       <c r="F159" t="n">
-        <v>2273.9</v>
+        <v>2245</v>
       </c>
       <c r="G159" t="n">
         <v>2275.07</v>
       </c>
       <c r="H159" t="n">
-        <v>-1.17</v>
+        <v>-30.07</v>
       </c>
       <c r="I159" t="n">
-        <v>2219.5</v>
+        <v>2192.7</v>
       </c>
       <c r="J159" t="n">
         <v>2194.8</v>
       </c>
       <c r="K159" t="n">
-        <v>24.7</v>
+        <v>-2.1</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="160">
@@ -18250,31 +18250,31 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1939.1</v>
+        <v>1945</v>
       </c>
       <c r="D160" t="n">
         <v>1960.58</v>
       </c>
       <c r="E160" t="n">
-        <v>-21.48</v>
+        <v>-15.58</v>
       </c>
       <c r="F160" t="n">
-        <v>1970</v>
+        <v>1945</v>
       </c>
       <c r="G160" t="n">
         <v>1957.2</v>
       </c>
       <c r="H160" t="n">
-        <v>12.8</v>
+        <v>-12.2</v>
       </c>
       <c r="I160" t="n">
-        <v>1930.5</v>
+        <v>1901.3</v>
       </c>
       <c r="J160" t="n">
         <v>1913.74</v>
       </c>
       <c r="K160" t="n">
-        <v>16.76</v>
+        <v>-12.44</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="161">
@@ -18302,31 +18302,31 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1046.25</v>
+        <v>1078.5</v>
       </c>
       <c r="D161" t="n">
         <v>1058.02</v>
       </c>
       <c r="E161" t="n">
-        <v>-11.77</v>
+        <v>20.48</v>
       </c>
       <c r="F161" t="n">
-        <v>1073</v>
+        <v>1087.95</v>
       </c>
       <c r="G161" t="n">
         <v>1061.39</v>
       </c>
       <c r="H161" t="n">
-        <v>11.61</v>
+        <v>26.56</v>
       </c>
       <c r="I161" t="n">
-        <v>1040</v>
+        <v>1056.9</v>
       </c>
       <c r="J161" t="n">
         <v>1028.47</v>
       </c>
       <c r="K161" t="n">
-        <v>11.53</v>
+        <v>28.43</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="162">
@@ -18354,31 +18354,31 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>117.59</v>
+        <v>118.98</v>
       </c>
       <c r="D162" t="n">
         <v>117.15</v>
       </c>
       <c r="E162" t="n">
-        <v>0.44</v>
+        <v>1.83</v>
       </c>
       <c r="F162" t="n">
-        <v>119.35</v>
+        <v>119.5</v>
       </c>
       <c r="G162" t="n">
         <v>118.47</v>
       </c>
       <c r="H162" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="I162" t="n">
-        <v>117.31</v>
+        <v>113.72</v>
       </c>
       <c r="J162" t="n">
         <v>116.22</v>
       </c>
       <c r="K162" t="n">
-        <v>1.09</v>
+        <v>-2.5</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0.38</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="163">
@@ -18406,31 +18406,31 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1183</v>
+        <v>1161</v>
       </c>
       <c r="D163" t="n">
         <v>1191.1</v>
       </c>
       <c r="E163" t="n">
-        <v>-8.1</v>
+        <v>-30.1</v>
       </c>
       <c r="F163" t="n">
-        <v>1184.9</v>
+        <v>1167.5</v>
       </c>
       <c r="G163" t="n">
         <v>1206.99</v>
       </c>
       <c r="H163" t="n">
-        <v>-22.09</v>
+        <v>-39.49</v>
       </c>
       <c r="I163" t="n">
-        <v>1149.2</v>
+        <v>1140</v>
       </c>
       <c r="J163" t="n">
         <v>1157.66</v>
       </c>
       <c r="K163" t="n">
-        <v>-8.460000000000001</v>
+        <v>-17.66</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -18439,11 +18439,11 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0.68</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="164">
@@ -18458,31 +18458,31 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>400.5</v>
+        <v>420</v>
       </c>
       <c r="D164" t="n">
         <v>407.87</v>
       </c>
       <c r="E164" t="n">
-        <v>-7.37</v>
+        <v>12.13</v>
       </c>
       <c r="F164" t="n">
-        <v>413.65</v>
+        <v>422.2</v>
       </c>
       <c r="G164" t="n">
         <v>409.06</v>
       </c>
       <c r="H164" t="n">
-        <v>4.59</v>
+        <v>13.14</v>
       </c>
       <c r="I164" t="n">
-        <v>400</v>
+        <v>398.5</v>
       </c>
       <c r="J164" t="n">
         <v>391.59</v>
       </c>
       <c r="K164" t="n">
-        <v>8.41</v>
+        <v>6.91</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>1.81</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="165">
@@ -18510,31 +18510,31 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>279.3</v>
+        <v>279.85</v>
       </c>
       <c r="D165" t="n">
         <v>284.62</v>
       </c>
       <c r="E165" t="n">
-        <v>-5.32</v>
+        <v>-4.77</v>
       </c>
       <c r="F165" t="n">
-        <v>287.4</v>
+        <v>281.9</v>
       </c>
       <c r="G165" t="n">
         <v>282.61</v>
       </c>
       <c r="H165" t="n">
-        <v>4.79</v>
+        <v>-0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J165" t="n">
         <v>275.1</v>
       </c>
       <c r="K165" t="n">
-        <v>-2.1</v>
+        <v>1.9</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="166">
@@ -18562,31 +18562,31 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1458.8</v>
+        <v>1463</v>
       </c>
       <c r="D166" t="n">
         <v>1473.34</v>
       </c>
       <c r="E166" t="n">
-        <v>-14.54</v>
+        <v>-10.34</v>
       </c>
       <c r="F166" t="n">
-        <v>1464.4</v>
+        <v>1468.8</v>
       </c>
       <c r="G166" t="n">
         <v>1471.76</v>
       </c>
       <c r="H166" t="n">
-        <v>-7.36</v>
+        <v>-2.96</v>
       </c>
       <c r="I166" t="n">
-        <v>1456.2</v>
+        <v>1456.1</v>
       </c>
       <c r="J166" t="n">
         <v>1440.21</v>
       </c>
       <c r="K166" t="n">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="167">
@@ -18623,22 +18623,22 @@
         <v>-7.84</v>
       </c>
       <c r="F167" t="n">
-        <v>903.8</v>
+        <v>897.65</v>
       </c>
       <c r="G167" t="n">
         <v>907.8200000000001</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.02</v>
+        <v>-10.17</v>
       </c>
       <c r="I167" t="n">
-        <v>883.15</v>
+        <v>873.1</v>
       </c>
       <c r="J167" t="n">
         <v>883.4</v>
       </c>
       <c r="K167" t="n">
-        <v>-0.25</v>
+        <v>-10.3</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9120,6 +9120,1566 @@
       </c>
       <c r="N167" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>118</v>
+      </c>
+      <c r="D168" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="F168" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G168" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="H168" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="I168" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="J168" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1067.7</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1086.93</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-19.23</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1082</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1089.74</v>
+      </c>
+      <c r="H169" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1065.1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1057.42</v>
+      </c>
+      <c r="K169" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>11828</v>
+      </c>
+      <c r="D170" t="n">
+        <v>11780.86</v>
+      </c>
+      <c r="E170" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="F170" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G170" t="n">
+        <v>12109.86</v>
+      </c>
+      <c r="H170" t="n">
+        <v>-259.86</v>
+      </c>
+      <c r="I170" t="n">
+        <v>11318</v>
+      </c>
+      <c r="J170" t="n">
+        <v>11751.99</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-433.99</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>11475</v>
+      </c>
+      <c r="D171" t="n">
+        <v>11562.29</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-87.29000000000001</v>
+      </c>
+      <c r="F171" t="n">
+        <v>11541</v>
+      </c>
+      <c r="G171" t="n">
+        <v>11562.29</v>
+      </c>
+      <c r="H171" t="n">
+        <v>-21.29</v>
+      </c>
+      <c r="I171" t="n">
+        <v>11387</v>
+      </c>
+      <c r="J171" t="n">
+        <v>11214.54</v>
+      </c>
+      <c r="K171" t="n">
+        <v>172.46</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1229.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1246.9</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1268.15</v>
+      </c>
+      <c r="H172" t="n">
+        <v>-21.25</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1230.1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1230.63</v>
+      </c>
+      <c r="K172" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>187.38</v>
+      </c>
+      <c r="D173" t="n">
+        <v>189.94</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F173" t="n">
+        <v>189.34</v>
+      </c>
+      <c r="G173" t="n">
+        <v>192.97</v>
+      </c>
+      <c r="H173" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="I173" t="n">
+        <v>186.39</v>
+      </c>
+      <c r="J173" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="K173" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1992.1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2038.57</v>
+      </c>
+      <c r="E174" t="n">
+        <v>-46.47</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2005.8</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2039.97</v>
+      </c>
+      <c r="H174" t="n">
+        <v>-34.17</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1932</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1992.1</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-60.1</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>8066.5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>8077.69</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="F175" t="n">
+        <v>8143</v>
+      </c>
+      <c r="G175" t="n">
+        <v>8093.76</v>
+      </c>
+      <c r="H175" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8030</v>
+      </c>
+      <c r="J175" t="n">
+        <v>7900.17</v>
+      </c>
+      <c r="K175" t="n">
+        <v>129.83</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>5580</v>
+      </c>
+      <c r="D176" t="n">
+        <v>5421.76</v>
+      </c>
+      <c r="E176" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5618.5</v>
+      </c>
+      <c r="G176" t="n">
+        <v>5718.11</v>
+      </c>
+      <c r="H176" t="n">
+        <v>-99.61</v>
+      </c>
+      <c r="I176" t="n">
+        <v>5447</v>
+      </c>
+      <c r="J176" t="n">
+        <v>5549.31</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-102.31</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1632.8</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1619.59</v>
+      </c>
+      <c r="E177" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1667.09</v>
+      </c>
+      <c r="H177" t="n">
+        <v>-15.09</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1614.4</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5985.55</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-195.55</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5849</v>
+      </c>
+      <c r="G178" t="n">
+        <v>5985.55</v>
+      </c>
+      <c r="H178" t="n">
+        <v>-136.55</v>
+      </c>
+      <c r="I178" t="n">
+        <v>5765</v>
+      </c>
+      <c r="J178" t="n">
+        <v>5694.13</v>
+      </c>
+      <c r="K178" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>3428.3</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3328.8</v>
+      </c>
+      <c r="E179" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3417.82</v>
+      </c>
+      <c r="H179" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I179" t="n">
+        <v>3378.3</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3334.66</v>
+      </c>
+      <c r="K179" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D180" t="n">
+        <v>301.01</v>
+      </c>
+      <c r="E180" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="F180" t="n">
+        <v>325</v>
+      </c>
+      <c r="G180" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I180" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="K180" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>14130</v>
+      </c>
+      <c r="D181" t="n">
+        <v>13911.32</v>
+      </c>
+      <c r="E181" t="n">
+        <v>218.68</v>
+      </c>
+      <c r="F181" t="n">
+        <v>14209</v>
+      </c>
+      <c r="G181" t="n">
+        <v>13911.32</v>
+      </c>
+      <c r="H181" t="n">
+        <v>297.68</v>
+      </c>
+      <c r="I181" t="n">
+        <v>13999</v>
+      </c>
+      <c r="J181" t="n">
+        <v>13697.56</v>
+      </c>
+      <c r="K181" t="n">
+        <v>301.44</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>601</v>
+      </c>
+      <c r="D182" t="n">
+        <v>583.87</v>
+      </c>
+      <c r="E182" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="F182" t="n">
+        <v>615.9</v>
+      </c>
+      <c r="G182" t="n">
+        <v>606.37</v>
+      </c>
+      <c r="H182" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I182" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="J182" t="n">
+        <v>588.14</v>
+      </c>
+      <c r="K182" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D183" t="n">
+        <v>5404.88</v>
+      </c>
+      <c r="E183" t="n">
+        <v>-94.88</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5370</v>
+      </c>
+      <c r="G183" t="n">
+        <v>5404.88</v>
+      </c>
+      <c r="H183" t="n">
+        <v>-34.88</v>
+      </c>
+      <c r="I183" t="n">
+        <v>5310</v>
+      </c>
+      <c r="J183" t="n">
+        <v>5220.06</v>
+      </c>
+      <c r="K183" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>171.64</v>
+      </c>
+      <c r="D184" t="n">
+        <v>173.62</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="F184" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G184" t="n">
+        <v>174.94</v>
+      </c>
+      <c r="H184" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="I184" t="n">
+        <v>169.75</v>
+      </c>
+      <c r="J184" t="n">
+        <v>169.74</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D185" t="n">
+        <v>7781.82</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-132.82</v>
+      </c>
+      <c r="F185" t="n">
+        <v>7825</v>
+      </c>
+      <c r="G185" t="n">
+        <v>7793.45</v>
+      </c>
+      <c r="H185" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="I185" t="n">
+        <v>7639</v>
+      </c>
+      <c r="J185" t="n">
+        <v>7561.84</v>
+      </c>
+      <c r="K185" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2199</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2237.89</v>
+      </c>
+      <c r="E186" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2255</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2237.89</v>
+      </c>
+      <c r="H186" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="I186" t="n">
+        <v>2191.6</v>
+      </c>
+      <c r="J186" t="n">
+        <v>2135.13</v>
+      </c>
+      <c r="K186" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1832.18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>-20.18</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1836.4</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1832.18</v>
+      </c>
+      <c r="H187" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1804.2</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1760.46</v>
+      </c>
+      <c r="K187" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1341.8</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1367.1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1365.14</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1337</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1324.46</v>
+      </c>
+      <c r="K188" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>4057</v>
+      </c>
+      <c r="D189" t="n">
+        <v>4054.81</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4072.5</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4138.36</v>
+      </c>
+      <c r="H189" t="n">
+        <v>-65.86</v>
+      </c>
+      <c r="I189" t="n">
+        <v>4033.1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>4038.69</v>
+      </c>
+      <c r="K189" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="D190" t="n">
+        <v>285.56</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="F190" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="G190" t="n">
+        <v>285.73</v>
+      </c>
+      <c r="H190" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="I190" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="J190" t="n">
+        <v>277.17</v>
+      </c>
+      <c r="K190" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1473.41</v>
+      </c>
+      <c r="E191" t="n">
+        <v>-23.41</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1474.3</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1481.82</v>
+      </c>
+      <c r="H191" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="I191" t="n">
+        <v>1449.2</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1437.94</v>
+      </c>
+      <c r="K191" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>376</v>
+      </c>
+      <c r="D192" t="n">
+        <v>401.79</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-25.79</v>
+      </c>
+      <c r="F192" t="n">
+        <v>384.95</v>
+      </c>
+      <c r="G192" t="n">
+        <v>401.79</v>
+      </c>
+      <c r="H192" t="n">
+        <v>-16.84</v>
+      </c>
+      <c r="I192" t="n">
+        <v>375</v>
+      </c>
+      <c r="J192" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="K192" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2008.3</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2060.38</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-52.08</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2033.6</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2060.38</v>
+      </c>
+      <c r="H193" t="n">
+        <v>-26.78</v>
+      </c>
+      <c r="I193" t="n">
+        <v>2006.6</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1952.58</v>
+      </c>
+      <c r="K193" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1029.5</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1081.36</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-51.86</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1036.8</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1081.36</v>
+      </c>
+      <c r="H194" t="n">
+        <v>-44.56</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1021.35</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1000.9</v>
+      </c>
+      <c r="K194" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1192.24</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-12.24</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1191.5</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1192.24</v>
+      </c>
+      <c r="H195" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1167</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1142.98</v>
+      </c>
+      <c r="K195" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>527</v>
+      </c>
+      <c r="D196" t="n">
+        <v>502.9</v>
+      </c>
+      <c r="E196" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>543.7</v>
+      </c>
+      <c r="G196" t="n">
+        <v>521.27</v>
+      </c>
+      <c r="H196" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="I196" t="n">
+        <v>527</v>
+      </c>
+      <c r="J196" t="n">
+        <v>510.37</v>
+      </c>
+      <c r="K196" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>894.95</v>
+      </c>
+      <c r="D197" t="n">
+        <v>911.91</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="F197" t="n">
+        <v>902.8</v>
+      </c>
+      <c r="G197" t="n">
+        <v>911.91</v>
+      </c>
+      <c r="H197" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="I197" t="n">
+        <v>885.3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>884.1799999999999</v>
+      </c>
+      <c r="K197" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>
@@ -9133,7 +10693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9934,6 +11494,110 @@
       </c>
       <c r="N15" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24366</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24366</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24405.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>24415.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>24296.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24306.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>57681.45</v>
+      </c>
+      <c r="G17" t="n">
+        <v>57654.89</v>
+      </c>
+      <c r="H17" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="I17" t="n">
+        <v>57380.45</v>
+      </c>
+      <c r="J17" t="n">
+        <v>57353.89</v>
+      </c>
+      <c r="K17" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9947,7 +11611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18654,6 +20318,1566 @@
         <v>0.87</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>118</v>
+      </c>
+      <c r="D168" t="n">
+        <v>124.42</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-6.42</v>
+      </c>
+      <c r="F168" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G168" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="H168" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="I168" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="J168" t="n">
+        <v>116.63</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OFSS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>11828</v>
+      </c>
+      <c r="D169" t="n">
+        <v>12141.43</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-313.43</v>
+      </c>
+      <c r="F169" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G169" t="n">
+        <v>12231.3</v>
+      </c>
+      <c r="H169" t="n">
+        <v>-381.3</v>
+      </c>
+      <c r="I169" t="n">
+        <v>11318</v>
+      </c>
+      <c r="J169" t="n">
+        <v>11554.45</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-236.45</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>5580</v>
+      </c>
+      <c r="D170" t="n">
+        <v>5594.79</v>
+      </c>
+      <c r="E170" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="F170" t="n">
+        <v>5618.5</v>
+      </c>
+      <c r="G170" t="n">
+        <v>5777.31</v>
+      </c>
+      <c r="H170" t="n">
+        <v>-158.81</v>
+      </c>
+      <c r="I170" t="n">
+        <v>5447</v>
+      </c>
+      <c r="J170" t="n">
+        <v>5445.64</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1067.7</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1106.62</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-38.92</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1082</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1091.24</v>
+      </c>
+      <c r="H171" t="n">
+        <v>-9.24</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1065.1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1052.7</v>
+      </c>
+      <c r="K171" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1261.44</v>
+      </c>
+      <c r="E172" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1246.9</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1276.74</v>
+      </c>
+      <c r="H172" t="n">
+        <v>-29.84</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1230.1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1215.49</v>
+      </c>
+      <c r="K172" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3428.3</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3407.86</v>
+      </c>
+      <c r="E173" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="F173" t="n">
+        <v>3430</v>
+      </c>
+      <c r="G173" t="n">
+        <v>3522.51</v>
+      </c>
+      <c r="H173" t="n">
+        <v>-92.51000000000001</v>
+      </c>
+      <c r="I173" t="n">
+        <v>3378.3</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3366.1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D174" t="n">
+        <v>309.81</v>
+      </c>
+      <c r="E174" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="F174" t="n">
+        <v>325</v>
+      </c>
+      <c r="G174" t="n">
+        <v>328.95</v>
+      </c>
+      <c r="H174" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="I174" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>311.44</v>
+      </c>
+      <c r="K174" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>11475</v>
+      </c>
+      <c r="D175" t="n">
+        <v>11781.82</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-306.82</v>
+      </c>
+      <c r="F175" t="n">
+        <v>11541</v>
+      </c>
+      <c r="G175" t="n">
+        <v>11737.66</v>
+      </c>
+      <c r="H175" t="n">
+        <v>-196.66</v>
+      </c>
+      <c r="I175" t="n">
+        <v>11387</v>
+      </c>
+      <c r="J175" t="n">
+        <v>11306.52</v>
+      </c>
+      <c r="K175" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1632.8</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1657.38</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-24.58</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1677.01</v>
+      </c>
+      <c r="H176" t="n">
+        <v>-25.01</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1614.4</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1603.67</v>
+      </c>
+      <c r="K176" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>187.38</v>
+      </c>
+      <c r="D177" t="n">
+        <v>193.32</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="F177" t="n">
+        <v>189.34</v>
+      </c>
+      <c r="G177" t="n">
+        <v>192.38</v>
+      </c>
+      <c r="H177" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="I177" t="n">
+        <v>186.39</v>
+      </c>
+      <c r="J177" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="K177" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1992.1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2059.2</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-67.09999999999999</v>
+      </c>
+      <c r="F178" t="n">
+        <v>2005.8</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2033.05</v>
+      </c>
+      <c r="H178" t="n">
+        <v>-27.25</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1932</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1966.36</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-34.36</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D179" t="n">
+        <v>6134.12</v>
+      </c>
+      <c r="E179" t="n">
+        <v>-344.12</v>
+      </c>
+      <c r="F179" t="n">
+        <v>5849</v>
+      </c>
+      <c r="G179" t="n">
+        <v>5955.1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>-106.1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>5765</v>
+      </c>
+      <c r="J179" t="n">
+        <v>5680.44</v>
+      </c>
+      <c r="K179" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>601</v>
+      </c>
+      <c r="D180" t="n">
+        <v>605.66</v>
+      </c>
+      <c r="E180" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="F180" t="n">
+        <v>615.9</v>
+      </c>
+      <c r="G180" t="n">
+        <v>625.39</v>
+      </c>
+      <c r="H180" t="n">
+        <v>-9.49</v>
+      </c>
+      <c r="I180" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="J180" t="n">
+        <v>584.17</v>
+      </c>
+      <c r="K180" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>8066.5</v>
+      </c>
+      <c r="D181" t="n">
+        <v>8213.74</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-147.24</v>
+      </c>
+      <c r="F181" t="n">
+        <v>8143</v>
+      </c>
+      <c r="G181" t="n">
+        <v>8234.459999999999</v>
+      </c>
+      <c r="H181" t="n">
+        <v>-91.45999999999999</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8030</v>
+      </c>
+      <c r="J181" t="n">
+        <v>7960.64</v>
+      </c>
+      <c r="K181" t="n">
+        <v>69.36</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>14130</v>
+      </c>
+      <c r="D182" t="n">
+        <v>14288.94</v>
+      </c>
+      <c r="E182" t="n">
+        <v>-158.94</v>
+      </c>
+      <c r="F182" t="n">
+        <v>14209</v>
+      </c>
+      <c r="G182" t="n">
+        <v>14564.62</v>
+      </c>
+      <c r="H182" t="n">
+        <v>-355.62</v>
+      </c>
+      <c r="I182" t="n">
+        <v>13999</v>
+      </c>
+      <c r="J182" t="n">
+        <v>13838.77</v>
+      </c>
+      <c r="K182" t="n">
+        <v>160.23</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D183" t="n">
+        <v>5527.49</v>
+      </c>
+      <c r="E183" t="n">
+        <v>-217.49</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5370</v>
+      </c>
+      <c r="G183" t="n">
+        <v>5450.48</v>
+      </c>
+      <c r="H183" t="n">
+        <v>-80.48</v>
+      </c>
+      <c r="I183" t="n">
+        <v>5310</v>
+      </c>
+      <c r="J183" t="n">
+        <v>5217.77</v>
+      </c>
+      <c r="K183" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>171.64</v>
+      </c>
+      <c r="D184" t="n">
+        <v>178.54</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="F184" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G184" t="n">
+        <v>177.11</v>
+      </c>
+      <c r="H184" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I184" t="n">
+        <v>169.75</v>
+      </c>
+      <c r="J184" t="n">
+        <v>167.96</v>
+      </c>
+      <c r="K184" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>376</v>
+      </c>
+      <c r="D185" t="n">
+        <v>415.79</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-39.79</v>
+      </c>
+      <c r="F185" t="n">
+        <v>384.95</v>
+      </c>
+      <c r="G185" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="H185" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="I185" t="n">
+        <v>375</v>
+      </c>
+      <c r="J185" t="n">
+        <v>366.15</v>
+      </c>
+      <c r="K185" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>9.57</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ABB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D186" t="n">
+        <v>7989.01</v>
+      </c>
+      <c r="E186" t="n">
+        <v>-340.01</v>
+      </c>
+      <c r="F186" t="n">
+        <v>7825</v>
+      </c>
+      <c r="G186" t="n">
+        <v>7880.44</v>
+      </c>
+      <c r="H186" t="n">
+        <v>-55.44</v>
+      </c>
+      <c r="I186" t="n">
+        <v>7639</v>
+      </c>
+      <c r="J186" t="n">
+        <v>7494.24</v>
+      </c>
+      <c r="K186" t="n">
+        <v>144.76</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2199</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2295.05</v>
+      </c>
+      <c r="E187" t="n">
+        <v>-96.05</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2255</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2263.23</v>
+      </c>
+      <c r="H187" t="n">
+        <v>-8.23</v>
+      </c>
+      <c r="I187" t="n">
+        <v>2191.6</v>
+      </c>
+      <c r="J187" t="n">
+        <v>2156.24</v>
+      </c>
+      <c r="K187" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1893.76</v>
+      </c>
+      <c r="E188" t="n">
+        <v>-81.76000000000001</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1836.4</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1879.03</v>
+      </c>
+      <c r="H188" t="n">
+        <v>-42.63</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1804.2</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1766.13</v>
+      </c>
+      <c r="K188" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1029.5</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1107.55</v>
+      </c>
+      <c r="E189" t="n">
+        <v>-78.05</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1036.8</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1058.28</v>
+      </c>
+      <c r="H189" t="n">
+        <v>-21.48</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1021.35</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1010.46</v>
+      </c>
+      <c r="K189" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1387.17</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-44.17</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1367.1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1392.93</v>
+      </c>
+      <c r="H190" t="n">
+        <v>-25.83</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1337</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1308.81</v>
+      </c>
+      <c r="K190" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>4057</v>
+      </c>
+      <c r="D191" t="n">
+        <v>4104.58</v>
+      </c>
+      <c r="E191" t="n">
+        <v>-47.58</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4072.5</v>
+      </c>
+      <c r="G191" t="n">
+        <v>4127.47</v>
+      </c>
+      <c r="H191" t="n">
+        <v>-54.97</v>
+      </c>
+      <c r="I191" t="n">
+        <v>4033.1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>4014.32</v>
+      </c>
+      <c r="K191" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="D192" t="n">
+        <v>291.64</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="F192" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="G192" t="n">
+        <v>289.69</v>
+      </c>
+      <c r="H192" t="n">
+        <v>-6.19</v>
+      </c>
+      <c r="I192" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="J192" t="n">
+        <v>277.97</v>
+      </c>
+      <c r="K192" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>527</v>
+      </c>
+      <c r="D193" t="n">
+        <v>517.03</v>
+      </c>
+      <c r="E193" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="F193" t="n">
+        <v>543.7</v>
+      </c>
+      <c r="G193" t="n">
+        <v>543.71</v>
+      </c>
+      <c r="H193" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I193" t="n">
+        <v>527</v>
+      </c>
+      <c r="J193" t="n">
+        <v>515.76</v>
+      </c>
+      <c r="K193" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2008.3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2110.23</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-101.93</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2033.6</v>
+      </c>
+      <c r="G194" t="n">
+        <v>2064.37</v>
+      </c>
+      <c r="H194" t="n">
+        <v>-30.77</v>
+      </c>
+      <c r="I194" t="n">
+        <v>2006.6</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1971.21</v>
+      </c>
+      <c r="K194" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CIPLA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1497.51</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-47.51</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1474.3</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1479.52</v>
+      </c>
+      <c r="H195" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1449.2</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1431.47</v>
+      </c>
+      <c r="K195" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1225.54</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-45.54</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1191.5</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1217.2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1167</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1154.99</v>
+      </c>
+      <c r="K196" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>894.95</v>
+      </c>
+      <c r="D197" t="n">
+        <v>929.49</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-34.54</v>
+      </c>
+      <c r="F197" t="n">
+        <v>902.8</v>
+      </c>
+      <c r="G197" t="n">
+        <v>915.6900000000001</v>
+      </c>
+      <c r="H197" t="n">
+        <v>-12.89</v>
+      </c>
+      <c r="I197" t="n">
+        <v>885.3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>881.61</v>
+      </c>
+      <c r="K197" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -9134,31 +9134,31 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>118</v>
+        <v>117.59</v>
       </c>
       <c r="D168" t="n">
         <v>122.61</v>
       </c>
       <c r="E168" t="n">
-        <v>-4.61</v>
+        <v>-5.02</v>
       </c>
       <c r="F168" t="n">
-        <v>118.9</v>
+        <v>119.35</v>
       </c>
       <c r="G168" t="n">
         <v>122.61</v>
       </c>
       <c r="H168" t="n">
-        <v>-3.71</v>
+        <v>-3.26</v>
       </c>
       <c r="I168" t="n">
-        <v>117.4</v>
+        <v>117.31</v>
       </c>
       <c r="J168" t="n">
         <v>115.8</v>
       </c>
       <c r="K168" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="169">
@@ -9186,31 +9186,31 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1067.7</v>
+        <v>1083</v>
       </c>
       <c r="D169" t="n">
         <v>1086.93</v>
       </c>
       <c r="E169" t="n">
-        <v>-19.23</v>
+        <v>-3.93</v>
       </c>
       <c r="F169" t="n">
-        <v>1082</v>
+        <v>1086.8</v>
       </c>
       <c r="G169" t="n">
         <v>1089.74</v>
       </c>
       <c r="H169" t="n">
-        <v>-7.74</v>
+        <v>-2.94</v>
       </c>
       <c r="I169" t="n">
-        <v>1065.1</v>
+        <v>1073</v>
       </c>
       <c r="J169" t="n">
         <v>1057.42</v>
       </c>
       <c r="K169" t="n">
-        <v>7.68</v>
+        <v>15.58</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>1.77</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="170">
@@ -9238,31 +9238,31 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>11828</v>
+        <v>11420</v>
       </c>
       <c r="D170" t="n">
         <v>11780.86</v>
       </c>
       <c r="E170" t="n">
-        <v>47.14</v>
+        <v>-360.86</v>
       </c>
       <c r="F170" t="n">
-        <v>11850</v>
+        <v>11686</v>
       </c>
       <c r="G170" t="n">
         <v>12109.86</v>
       </c>
       <c r="H170" t="n">
-        <v>-259.86</v>
+        <v>-423.86</v>
       </c>
       <c r="I170" t="n">
-        <v>11318</v>
+        <v>11350</v>
       </c>
       <c r="J170" t="n">
         <v>11751.99</v>
       </c>
       <c r="K170" t="n">
-        <v>-433.99</v>
+        <v>-401.99</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9271,11 +9271,11 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0.4</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="171">
@@ -9290,31 +9290,31 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11475</v>
+        <v>11500</v>
       </c>
       <c r="D171" t="n">
         <v>11562.29</v>
       </c>
       <c r="E171" t="n">
-        <v>-87.29000000000001</v>
+        <v>-62.29</v>
       </c>
       <c r="F171" t="n">
-        <v>11541</v>
+        <v>11570</v>
       </c>
       <c r="G171" t="n">
         <v>11562.29</v>
       </c>
       <c r="H171" t="n">
-        <v>-21.29</v>
+        <v>7.71</v>
       </c>
       <c r="I171" t="n">
-        <v>11387</v>
+        <v>11410</v>
       </c>
       <c r="J171" t="n">
         <v>11214.54</v>
       </c>
       <c r="K171" t="n">
-        <v>172.46</v>
+        <v>195.46</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0.75</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="172">
@@ -9351,22 +9351,22 @@
         <v>10.5</v>
       </c>
       <c r="F172" t="n">
-        <v>1246.9</v>
+        <v>1264.7</v>
       </c>
       <c r="G172" t="n">
         <v>1268.15</v>
       </c>
       <c r="H172" t="n">
-        <v>-21.25</v>
+        <v>-3.45</v>
       </c>
       <c r="I172" t="n">
-        <v>1230.1</v>
+        <v>1237</v>
       </c>
       <c r="J172" t="n">
         <v>1230.63</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.53</v>
+        <v>6.37</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -9394,31 +9394,31 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>187.38</v>
+        <v>186.5</v>
       </c>
       <c r="D173" t="n">
         <v>189.94</v>
       </c>
       <c r="E173" t="n">
-        <v>-2.56</v>
+        <v>-3.44</v>
       </c>
       <c r="F173" t="n">
-        <v>189.34</v>
+        <v>188.7</v>
       </c>
       <c r="G173" t="n">
         <v>192.97</v>
       </c>
       <c r="H173" t="n">
-        <v>-3.63</v>
+        <v>-4.27</v>
       </c>
       <c r="I173" t="n">
-        <v>186.39</v>
+        <v>185.32</v>
       </c>
       <c r="J173" t="n">
         <v>187.3</v>
       </c>
       <c r="K173" t="n">
-        <v>-0.91</v>
+        <v>-1.98</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="174">
@@ -9446,31 +9446,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1992.1</v>
+        <v>1939.1</v>
       </c>
       <c r="D174" t="n">
         <v>2038.57</v>
       </c>
       <c r="E174" t="n">
-        <v>-46.47</v>
+        <v>-99.47</v>
       </c>
       <c r="F174" t="n">
-        <v>2005.8</v>
+        <v>1970</v>
       </c>
       <c r="G174" t="n">
         <v>2039.97</v>
       </c>
       <c r="H174" t="n">
-        <v>-34.17</v>
+        <v>-69.97</v>
       </c>
       <c r="I174" t="n">
-        <v>1932</v>
+        <v>1930.5</v>
       </c>
       <c r="J174" t="n">
         <v>1992.1</v>
       </c>
       <c r="K174" t="n">
-        <v>-60.1</v>
+        <v>-61.6</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9479,11 +9479,11 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2.28</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="175">
@@ -9498,31 +9498,31 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8066.5</v>
+        <v>8100</v>
       </c>
       <c r="D175" t="n">
         <v>8077.69</v>
       </c>
       <c r="E175" t="n">
-        <v>-11.19</v>
+        <v>22.31</v>
       </c>
       <c r="F175" t="n">
-        <v>8143</v>
+        <v>8100</v>
       </c>
       <c r="G175" t="n">
         <v>8093.76</v>
       </c>
       <c r="H175" t="n">
-        <v>49.24</v>
+        <v>6.24</v>
       </c>
       <c r="I175" t="n">
-        <v>8030</v>
+        <v>8011</v>
       </c>
       <c r="J175" t="n">
         <v>7900.17</v>
       </c>
       <c r="K175" t="n">
-        <v>129.83</v>
+        <v>110.83</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="176">
@@ -9550,31 +9550,31 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5580</v>
+        <v>5523</v>
       </c>
       <c r="D176" t="n">
         <v>5421.76</v>
       </c>
       <c r="E176" t="n">
-        <v>158.24</v>
+        <v>101.24</v>
       </c>
       <c r="F176" t="n">
-        <v>5618.5</v>
+        <v>5529</v>
       </c>
       <c r="G176" t="n">
         <v>5718.11</v>
       </c>
       <c r="H176" t="n">
-        <v>-99.61</v>
+        <v>-189.11</v>
       </c>
       <c r="I176" t="n">
-        <v>5447</v>
+        <v>5406</v>
       </c>
       <c r="J176" t="n">
         <v>5549.31</v>
       </c>
       <c r="K176" t="n">
-        <v>-102.31</v>
+        <v>-143.31</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -9583,11 +9583,11 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="177">
@@ -9602,31 +9602,31 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1632.8</v>
+        <v>1639</v>
       </c>
       <c r="D177" t="n">
         <v>1619.59</v>
       </c>
       <c r="E177" t="n">
-        <v>13.21</v>
+        <v>19.41</v>
       </c>
       <c r="F177" t="n">
-        <v>1652</v>
+        <v>1652.8</v>
       </c>
       <c r="G177" t="n">
         <v>1667.09</v>
       </c>
       <c r="H177" t="n">
-        <v>-15.09</v>
+        <v>-14.29</v>
       </c>
       <c r="I177" t="n">
-        <v>1614.4</v>
+        <v>1626.3</v>
       </c>
       <c r="J177" t="n">
         <v>1617.66</v>
       </c>
       <c r="K177" t="n">
-        <v>-3.26</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="178">
@@ -9654,31 +9654,31 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5790</v>
+        <v>5850</v>
       </c>
       <c r="D178" t="n">
         <v>5985.55</v>
       </c>
       <c r="E178" t="n">
-        <v>-195.55</v>
+        <v>-135.55</v>
       </c>
       <c r="F178" t="n">
-        <v>5849</v>
+        <v>5934</v>
       </c>
       <c r="G178" t="n">
         <v>5985.55</v>
       </c>
       <c r="H178" t="n">
-        <v>-136.55</v>
+        <v>-51.55</v>
       </c>
       <c r="I178" t="n">
-        <v>5765</v>
+        <v>5802</v>
       </c>
       <c r="J178" t="n">
         <v>5694.13</v>
       </c>
       <c r="K178" t="n">
-        <v>70.87</v>
+        <v>107.87</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>3.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="179">
@@ -9706,31 +9706,31 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3428.3</v>
+        <v>3428.2</v>
       </c>
       <c r="D179" t="n">
         <v>3328.8</v>
       </c>
       <c r="E179" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F179" t="n">
-        <v>3430</v>
+        <v>3440</v>
       </c>
       <c r="G179" t="n">
         <v>3417.82</v>
       </c>
       <c r="H179" t="n">
-        <v>12.18</v>
+        <v>22.18</v>
       </c>
       <c r="I179" t="n">
-        <v>3378.3</v>
+        <v>3396.5</v>
       </c>
       <c r="J179" t="n">
         <v>3334.66</v>
       </c>
       <c r="K179" t="n">
-        <v>43.64</v>
+        <v>61.84</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9758,31 +9758,31 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>318.5</v>
+        <v>318</v>
       </c>
       <c r="D180" t="n">
         <v>301.01</v>
       </c>
       <c r="E180" t="n">
-        <v>17.49</v>
+        <v>16.99</v>
       </c>
       <c r="F180" t="n">
-        <v>325</v>
+        <v>319.35</v>
       </c>
       <c r="G180" t="n">
         <v>324.15</v>
       </c>
       <c r="H180" t="n">
-        <v>0.85</v>
+        <v>-4.8</v>
       </c>
       <c r="I180" t="n">
-        <v>316.8</v>
+        <v>313.3</v>
       </c>
       <c r="J180" t="n">
         <v>314.5</v>
       </c>
       <c r="K180" t="n">
-        <v>2.3</v>
+        <v>-1.2</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="181">
@@ -9810,31 +9810,31 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>14130</v>
+        <v>14035</v>
       </c>
       <c r="D181" t="n">
         <v>13911.32</v>
       </c>
       <c r="E181" t="n">
-        <v>218.68</v>
+        <v>123.68</v>
       </c>
       <c r="F181" t="n">
-        <v>14209</v>
+        <v>14065</v>
       </c>
       <c r="G181" t="n">
         <v>13911.32</v>
       </c>
       <c r="H181" t="n">
-        <v>297.68</v>
+        <v>153.68</v>
       </c>
       <c r="I181" t="n">
-        <v>13999</v>
+        <v>13645</v>
       </c>
       <c r="J181" t="n">
         <v>13697.56</v>
       </c>
       <c r="K181" t="n">
-        <v>301.44</v>
+        <v>-52.56</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1.57</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="182">
@@ -9862,31 +9862,31 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="D182" t="n">
         <v>583.87</v>
       </c>
       <c r="E182" t="n">
-        <v>17.13</v>
+        <v>31.13</v>
       </c>
       <c r="F182" t="n">
-        <v>615.9</v>
+        <v>615.3</v>
       </c>
       <c r="G182" t="n">
         <v>606.37</v>
       </c>
       <c r="H182" t="n">
-        <v>9.529999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="I182" t="n">
-        <v>599.5</v>
+        <v>603</v>
       </c>
       <c r="J182" t="n">
         <v>588.14</v>
       </c>
       <c r="K182" t="n">
-        <v>11.36</v>
+        <v>14.86</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>2.93</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="183">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5310</v>
+        <v>5370</v>
       </c>
       <c r="D183" t="n">
         <v>5404.88</v>
       </c>
       <c r="E183" t="n">
-        <v>-94.88</v>
+        <v>-34.88</v>
       </c>
       <c r="F183" t="n">
         <v>5370</v>
@@ -9932,13 +9932,13 @@
         <v>-34.88</v>
       </c>
       <c r="I183" t="n">
-        <v>5310</v>
+        <v>5281.5</v>
       </c>
       <c r="J183" t="n">
         <v>5220.06</v>
       </c>
       <c r="K183" t="n">
-        <v>89.94</v>
+        <v>61.44</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1.76</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="184">
@@ -9966,31 +9966,31 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>171.64</v>
+        <v>176.23</v>
       </c>
       <c r="D184" t="n">
         <v>173.62</v>
       </c>
       <c r="E184" t="n">
-        <v>-1.98</v>
+        <v>2.61</v>
       </c>
       <c r="F184" t="n">
-        <v>179.5</v>
+        <v>182.7</v>
       </c>
       <c r="G184" t="n">
         <v>174.94</v>
       </c>
       <c r="H184" t="n">
-        <v>4.56</v>
+        <v>7.76</v>
       </c>
       <c r="I184" t="n">
-        <v>169.75</v>
+        <v>176.23</v>
       </c>
       <c r="J184" t="n">
         <v>169.74</v>
       </c>
       <c r="K184" t="n">
-        <v>0.01</v>
+        <v>6.49</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="185">
@@ -10018,31 +10018,31 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7649</v>
+        <v>7710</v>
       </c>
       <c r="D185" t="n">
         <v>7781.82</v>
       </c>
       <c r="E185" t="n">
-        <v>-132.82</v>
+        <v>-71.81999999999999</v>
       </c>
       <c r="F185" t="n">
-        <v>7825</v>
+        <v>7772</v>
       </c>
       <c r="G185" t="n">
         <v>7793.45</v>
       </c>
       <c r="H185" t="n">
-        <v>31.55</v>
+        <v>-21.45</v>
       </c>
       <c r="I185" t="n">
-        <v>7639</v>
+        <v>7659</v>
       </c>
       <c r="J185" t="n">
         <v>7561.84</v>
       </c>
       <c r="K185" t="n">
-        <v>77.16</v>
+        <v>97.16</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="186">
@@ -10070,31 +10070,31 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2199</v>
+        <v>2237.1</v>
       </c>
       <c r="D186" t="n">
         <v>2237.89</v>
       </c>
       <c r="E186" t="n">
-        <v>-38.89</v>
+        <v>-0.79</v>
       </c>
       <c r="F186" t="n">
-        <v>2255</v>
+        <v>2273.9</v>
       </c>
       <c r="G186" t="n">
         <v>2237.89</v>
       </c>
       <c r="H186" t="n">
-        <v>17.11</v>
+        <v>36.01</v>
       </c>
       <c r="I186" t="n">
-        <v>2191.6</v>
+        <v>2219.5</v>
       </c>
       <c r="J186" t="n">
         <v>2135.13</v>
       </c>
       <c r="K186" t="n">
-        <v>56.47</v>
+        <v>84.37</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>1.74</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="187">
@@ -10122,31 +10122,31 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D187" t="n">
         <v>1832.18</v>
       </c>
       <c r="E187" t="n">
-        <v>-20.18</v>
+        <v>-3.18</v>
       </c>
       <c r="F187" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G187" t="n">
         <v>1832.18</v>
       </c>
       <c r="H187" t="n">
-        <v>4.22</v>
+        <v>-2.28</v>
       </c>
       <c r="I187" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J187" t="n">
         <v>1760.46</v>
       </c>
       <c r="K187" t="n">
-        <v>43.74</v>
+        <v>27.54</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1.1</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="188">
@@ -10174,31 +10174,31 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1343</v>
+        <v>1357.3</v>
       </c>
       <c r="D188" t="n">
         <v>1341.8</v>
       </c>
       <c r="E188" t="n">
-        <v>1.2</v>
+        <v>15.5</v>
       </c>
       <c r="F188" t="n">
-        <v>1367.1</v>
+        <v>1369.4</v>
       </c>
       <c r="G188" t="n">
         <v>1365.14</v>
       </c>
       <c r="H188" t="n">
-        <v>1.96</v>
+        <v>4.26</v>
       </c>
       <c r="I188" t="n">
-        <v>1337</v>
+        <v>1336.5</v>
       </c>
       <c r="J188" t="n">
         <v>1324.46</v>
       </c>
       <c r="K188" t="n">
-        <v>12.54</v>
+        <v>12.04</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>0.09</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="189">
@@ -10226,31 +10226,31 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4057</v>
+        <v>4070.7</v>
       </c>
       <c r="D189" t="n">
         <v>4054.81</v>
       </c>
       <c r="E189" t="n">
-        <v>2.19</v>
+        <v>15.89</v>
       </c>
       <c r="F189" t="n">
-        <v>4072.5</v>
+        <v>4070.7</v>
       </c>
       <c r="G189" t="n">
         <v>4138.36</v>
       </c>
       <c r="H189" t="n">
-        <v>-65.86</v>
+        <v>-67.66</v>
       </c>
       <c r="I189" t="n">
-        <v>4033.1</v>
+        <v>3990</v>
       </c>
       <c r="J189" t="n">
         <v>4038.69</v>
       </c>
       <c r="K189" t="n">
-        <v>-5.59</v>
+        <v>-48.69</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0.05</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="190">
@@ -10278,31 +10278,31 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>282.6</v>
+        <v>279.3</v>
       </c>
       <c r="D190" t="n">
         <v>285.56</v>
       </c>
       <c r="E190" t="n">
-        <v>-2.96</v>
+        <v>-6.26</v>
       </c>
       <c r="F190" t="n">
-        <v>283.5</v>
+        <v>287.4</v>
       </c>
       <c r="G190" t="n">
         <v>285.73</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.23</v>
+        <v>1.67</v>
       </c>
       <c r="I190" t="n">
-        <v>277.15</v>
+        <v>273</v>
       </c>
       <c r="J190" t="n">
         <v>277.17</v>
       </c>
       <c r="K190" t="n">
-        <v>-0.02</v>
+        <v>-4.17</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1.04</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="191">
@@ -10330,31 +10330,31 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1450</v>
+        <v>1458.8</v>
       </c>
       <c r="D191" t="n">
         <v>1473.41</v>
       </c>
       <c r="E191" t="n">
-        <v>-23.41</v>
+        <v>-14.61</v>
       </c>
       <c r="F191" t="n">
-        <v>1474.3</v>
+        <v>1464.4</v>
       </c>
       <c r="G191" t="n">
         <v>1481.82</v>
       </c>
       <c r="H191" t="n">
-        <v>-7.52</v>
+        <v>-17.42</v>
       </c>
       <c r="I191" t="n">
-        <v>1449.2</v>
+        <v>1456.2</v>
       </c>
       <c r="J191" t="n">
         <v>1437.94</v>
       </c>
       <c r="K191" t="n">
-        <v>11.26</v>
+        <v>18.26</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1.59</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="192">
@@ -10382,31 +10382,31 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>376</v>
+        <v>400.5</v>
       </c>
       <c r="D192" t="n">
         <v>401.79</v>
       </c>
       <c r="E192" t="n">
-        <v>-25.79</v>
+        <v>-1.29</v>
       </c>
       <c r="F192" t="n">
-        <v>384.95</v>
+        <v>413.65</v>
       </c>
       <c r="G192" t="n">
         <v>401.79</v>
       </c>
       <c r="H192" t="n">
-        <v>-16.84</v>
+        <v>11.86</v>
       </c>
       <c r="I192" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="J192" t="n">
         <v>361.7</v>
       </c>
       <c r="K192" t="n">
-        <v>13.3</v>
+        <v>38.3</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>6.42</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="193">
@@ -10434,31 +10434,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2008.3</v>
+        <v>2025</v>
       </c>
       <c r="D193" t="n">
         <v>2060.38</v>
       </c>
       <c r="E193" t="n">
-        <v>-52.08</v>
+        <v>-35.38</v>
       </c>
       <c r="F193" t="n">
-        <v>2033.6</v>
+        <v>2038</v>
       </c>
       <c r="G193" t="n">
         <v>2060.38</v>
       </c>
       <c r="H193" t="n">
-        <v>-26.78</v>
+        <v>-22.38</v>
       </c>
       <c r="I193" t="n">
-        <v>2006.6</v>
+        <v>2006.7</v>
       </c>
       <c r="J193" t="n">
         <v>1952.58</v>
       </c>
       <c r="K193" t="n">
-        <v>54.02</v>
+        <v>54.12</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="194">
@@ -10486,31 +10486,31 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1029.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D194" t="n">
         <v>1081.36</v>
       </c>
       <c r="E194" t="n">
-        <v>-51.86</v>
+        <v>-35.11</v>
       </c>
       <c r="F194" t="n">
-        <v>1036.8</v>
+        <v>1073</v>
       </c>
       <c r="G194" t="n">
         <v>1081.36</v>
       </c>
       <c r="H194" t="n">
-        <v>-44.56</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>1021.35</v>
+        <v>1040</v>
       </c>
       <c r="J194" t="n">
         <v>1000.9</v>
       </c>
       <c r="K194" t="n">
-        <v>20.45</v>
+        <v>39.1</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="195">
@@ -10538,31 +10538,31 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D195" t="n">
         <v>1192.24</v>
       </c>
       <c r="E195" t="n">
-        <v>-12.24</v>
+        <v>-9.24</v>
       </c>
       <c r="F195" t="n">
-        <v>1191.5</v>
+        <v>1184.9</v>
       </c>
       <c r="G195" t="n">
         <v>1192.24</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.74</v>
+        <v>-7.34</v>
       </c>
       <c r="I195" t="n">
-        <v>1167</v>
+        <v>1149.2</v>
       </c>
       <c r="J195" t="n">
         <v>1142.98</v>
       </c>
       <c r="K195" t="n">
-        <v>24.02</v>
+        <v>6.22</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="196">
@@ -10590,31 +10590,31 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>527</v>
+        <v>533.65</v>
       </c>
       <c r="D196" t="n">
         <v>502.9</v>
       </c>
       <c r="E196" t="n">
-        <v>24.1</v>
+        <v>30.75</v>
       </c>
       <c r="F196" t="n">
-        <v>543.7</v>
+        <v>535.5</v>
       </c>
       <c r="G196" t="n">
         <v>521.27</v>
       </c>
       <c r="H196" t="n">
-        <v>22.43</v>
+        <v>14.23</v>
       </c>
       <c r="I196" t="n">
-        <v>527</v>
+        <v>513.7</v>
       </c>
       <c r="J196" t="n">
         <v>510.37</v>
       </c>
       <c r="K196" t="n">
-        <v>16.63</v>
+        <v>3.33</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>4.79</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="197">
@@ -10642,31 +10642,31 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>894.95</v>
+        <v>897</v>
       </c>
       <c r="D197" t="n">
         <v>911.91</v>
       </c>
       <c r="E197" t="n">
-        <v>-16.96</v>
+        <v>-14.91</v>
       </c>
       <c r="F197" t="n">
-        <v>902.8</v>
+        <v>903.8</v>
       </c>
       <c r="G197" t="n">
         <v>911.91</v>
       </c>
       <c r="H197" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>885.3</v>
+        <v>883.15</v>
       </c>
       <c r="J197" t="n">
         <v>884.1799999999999</v>
       </c>
       <c r="K197" t="n">
-        <v>1.12</v>
+        <v>-1.03</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -11508,31 +11508,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24366</v>
+        <v>24395.85</v>
       </c>
       <c r="D16" t="n">
         <v>24366</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>29.85</v>
       </c>
       <c r="F16" t="n">
-        <v>24405.2</v>
+        <v>24431.6</v>
       </c>
       <c r="G16" t="n">
         <v>24415.2</v>
       </c>
       <c r="H16" t="n">
-        <v>-10</v>
+        <v>16.4</v>
       </c>
       <c r="I16" t="n">
-        <v>24296.8</v>
+        <v>24311.4</v>
       </c>
       <c r="J16" t="n">
         <v>24306.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-10</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
@@ -11560,31 +11560,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57491.1</v>
+        <v>57635.25</v>
       </c>
       <c r="D17" t="n">
         <v>57491.1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>144.15</v>
       </c>
       <c r="F17" t="n">
-        <v>57681.45</v>
+        <v>57799.15</v>
       </c>
       <c r="G17" t="n">
         <v>57654.89</v>
       </c>
       <c r="H17" t="n">
-        <v>26.56</v>
+        <v>144.26</v>
       </c>
       <c r="I17" t="n">
-        <v>57380.45</v>
+        <v>57548.6</v>
       </c>
       <c r="J17" t="n">
         <v>57353.89</v>
       </c>
       <c r="K17" t="n">
-        <v>26.56</v>
+        <v>194.71</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -20330,31 +20330,31 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>118</v>
+        <v>117.59</v>
       </c>
       <c r="D168" t="n">
         <v>124.42</v>
       </c>
       <c r="E168" t="n">
-        <v>-6.42</v>
+        <v>-6.83</v>
       </c>
       <c r="F168" t="n">
-        <v>118.9</v>
+        <v>119.35</v>
       </c>
       <c r="G168" t="n">
         <v>120.23</v>
       </c>
       <c r="H168" t="n">
-        <v>-1.33</v>
+        <v>-0.88</v>
       </c>
       <c r="I168" t="n">
-        <v>117.4</v>
+        <v>117.31</v>
       </c>
       <c r="J168" t="n">
         <v>116.63</v>
       </c>
       <c r="K168" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>5.16</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="169">
@@ -20382,31 +20382,31 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>11828</v>
+        <v>11420</v>
       </c>
       <c r="D169" t="n">
         <v>12141.43</v>
       </c>
       <c r="E169" t="n">
-        <v>-313.43</v>
+        <v>-721.4299999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>11850</v>
+        <v>11686</v>
       </c>
       <c r="G169" t="n">
         <v>12231.3</v>
       </c>
       <c r="H169" t="n">
-        <v>-381.3</v>
+        <v>-545.3</v>
       </c>
       <c r="I169" t="n">
-        <v>11318</v>
+        <v>11350</v>
       </c>
       <c r="J169" t="n">
         <v>11554.45</v>
       </c>
       <c r="K169" t="n">
-        <v>-236.45</v>
+        <v>-204.45</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>2.58</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="170">
@@ -20434,31 +20434,31 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5580</v>
+        <v>5523</v>
       </c>
       <c r="D170" t="n">
         <v>5594.79</v>
       </c>
       <c r="E170" t="n">
-        <v>-14.79</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="F170" t="n">
-        <v>5618.5</v>
+        <v>5529</v>
       </c>
       <c r="G170" t="n">
         <v>5777.31</v>
       </c>
       <c r="H170" t="n">
-        <v>-158.81</v>
+        <v>-248.31</v>
       </c>
       <c r="I170" t="n">
-        <v>5447</v>
+        <v>5406</v>
       </c>
       <c r="J170" t="n">
         <v>5445.64</v>
       </c>
       <c r="K170" t="n">
-        <v>1.36</v>
+        <v>-39.64</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="171">
@@ -20486,31 +20486,31 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1067.7</v>
+        <v>1083</v>
       </c>
       <c r="D171" t="n">
         <v>1106.62</v>
       </c>
       <c r="E171" t="n">
-        <v>-38.92</v>
+        <v>-23.62</v>
       </c>
       <c r="F171" t="n">
-        <v>1082</v>
+        <v>1086.8</v>
       </c>
       <c r="G171" t="n">
         <v>1091.24</v>
       </c>
       <c r="H171" t="n">
-        <v>-9.24</v>
+        <v>-4.44</v>
       </c>
       <c r="I171" t="n">
-        <v>1065.1</v>
+        <v>1073</v>
       </c>
       <c r="J171" t="n">
         <v>1052.7</v>
       </c>
       <c r="K171" t="n">
-        <v>12.4</v>
+        <v>20.3</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -20519,11 +20519,11 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N171" t="n">
-        <v>3.52</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="172">
@@ -20547,22 +20547,22 @@
         <v>-21.44</v>
       </c>
       <c r="F172" t="n">
-        <v>1246.9</v>
+        <v>1264.7</v>
       </c>
       <c r="G172" t="n">
         <v>1276.74</v>
       </c>
       <c r="H172" t="n">
-        <v>-29.84</v>
+        <v>-12.04</v>
       </c>
       <c r="I172" t="n">
-        <v>1230.1</v>
+        <v>1237</v>
       </c>
       <c r="J172" t="n">
         <v>1215.49</v>
       </c>
       <c r="K172" t="n">
-        <v>14.61</v>
+        <v>21.51</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -20590,31 +20590,31 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3428.3</v>
+        <v>3428.2</v>
       </c>
       <c r="D173" t="n">
         <v>3407.86</v>
       </c>
       <c r="E173" t="n">
-        <v>20.44</v>
+        <v>20.34</v>
       </c>
       <c r="F173" t="n">
-        <v>3430</v>
+        <v>3440</v>
       </c>
       <c r="G173" t="n">
         <v>3522.51</v>
       </c>
       <c r="H173" t="n">
-        <v>-92.51000000000001</v>
+        <v>-82.51000000000001</v>
       </c>
       <c r="I173" t="n">
-        <v>3378.3</v>
+        <v>3396.5</v>
       </c>
       <c r="J173" t="n">
         <v>3366.1</v>
       </c>
       <c r="K173" t="n">
-        <v>12.2</v>
+        <v>30.4</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -20642,31 +20642,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>318.5</v>
+        <v>318</v>
       </c>
       <c r="D174" t="n">
         <v>309.81</v>
       </c>
       <c r="E174" t="n">
-        <v>8.69</v>
+        <v>8.19</v>
       </c>
       <c r="F174" t="n">
-        <v>325</v>
+        <v>319.35</v>
       </c>
       <c r="G174" t="n">
         <v>328.95</v>
       </c>
       <c r="H174" t="n">
-        <v>-3.95</v>
+        <v>-9.6</v>
       </c>
       <c r="I174" t="n">
-        <v>316.8</v>
+        <v>313.3</v>
       </c>
       <c r="J174" t="n">
         <v>311.44</v>
       </c>
       <c r="K174" t="n">
-        <v>5.36</v>
+        <v>1.86</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="175">
@@ -20694,31 +20694,31 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>11475</v>
+        <v>11500</v>
       </c>
       <c r="D175" t="n">
         <v>11781.82</v>
       </c>
       <c r="E175" t="n">
-        <v>-306.82</v>
+        <v>-281.82</v>
       </c>
       <c r="F175" t="n">
-        <v>11541</v>
+        <v>11570</v>
       </c>
       <c r="G175" t="n">
         <v>11737.66</v>
       </c>
       <c r="H175" t="n">
-        <v>-196.66</v>
+        <v>-167.66</v>
       </c>
       <c r="I175" t="n">
-        <v>11387</v>
+        <v>11410</v>
       </c>
       <c r="J175" t="n">
         <v>11306.52</v>
       </c>
       <c r="K175" t="n">
-        <v>80.48</v>
+        <v>103.48</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -20727,11 +20727,11 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="176">
@@ -20746,31 +20746,31 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1632.8</v>
+        <v>1639</v>
       </c>
       <c r="D176" t="n">
         <v>1657.38</v>
       </c>
       <c r="E176" t="n">
-        <v>-24.58</v>
+        <v>-18.38</v>
       </c>
       <c r="F176" t="n">
-        <v>1652</v>
+        <v>1652.8</v>
       </c>
       <c r="G176" t="n">
         <v>1677.01</v>
       </c>
       <c r="H176" t="n">
-        <v>-25.01</v>
+        <v>-24.21</v>
       </c>
       <c r="I176" t="n">
-        <v>1614.4</v>
+        <v>1626.3</v>
       </c>
       <c r="J176" t="n">
         <v>1603.67</v>
       </c>
       <c r="K176" t="n">
-        <v>10.73</v>
+        <v>22.63</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="177">
@@ -20798,31 +20798,31 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>187.38</v>
+        <v>186.5</v>
       </c>
       <c r="D177" t="n">
         <v>193.32</v>
       </c>
       <c r="E177" t="n">
-        <v>-5.94</v>
+        <v>-6.82</v>
       </c>
       <c r="F177" t="n">
-        <v>189.34</v>
+        <v>188.7</v>
       </c>
       <c r="G177" t="n">
         <v>192.38</v>
       </c>
       <c r="H177" t="n">
-        <v>-3.04</v>
+        <v>-3.68</v>
       </c>
       <c r="I177" t="n">
-        <v>186.39</v>
+        <v>185.32</v>
       </c>
       <c r="J177" t="n">
         <v>184.1</v>
       </c>
       <c r="K177" t="n">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>3.07</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="178">
@@ -20850,31 +20850,31 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1992.1</v>
+        <v>1939.1</v>
       </c>
       <c r="D178" t="n">
         <v>2059.2</v>
       </c>
       <c r="E178" t="n">
-        <v>-67.09999999999999</v>
+        <v>-120.1</v>
       </c>
       <c r="F178" t="n">
-        <v>2005.8</v>
+        <v>1970</v>
       </c>
       <c r="G178" t="n">
         <v>2033.05</v>
       </c>
       <c r="H178" t="n">
-        <v>-27.25</v>
+        <v>-63.05</v>
       </c>
       <c r="I178" t="n">
-        <v>1932</v>
+        <v>1930.5</v>
       </c>
       <c r="J178" t="n">
         <v>1966.36</v>
       </c>
       <c r="K178" t="n">
-        <v>-34.36</v>
+        <v>-35.86</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>3.26</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="179">
@@ -20902,31 +20902,31 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5790</v>
+        <v>5850</v>
       </c>
       <c r="D179" t="n">
         <v>6134.12</v>
       </c>
       <c r="E179" t="n">
-        <v>-344.12</v>
+        <v>-284.12</v>
       </c>
       <c r="F179" t="n">
-        <v>5849</v>
+        <v>5934</v>
       </c>
       <c r="G179" t="n">
         <v>5955.1</v>
       </c>
       <c r="H179" t="n">
-        <v>-106.1</v>
+        <v>-21.1</v>
       </c>
       <c r="I179" t="n">
-        <v>5765</v>
+        <v>5802</v>
       </c>
       <c r="J179" t="n">
         <v>5680.44</v>
       </c>
       <c r="K179" t="n">
-        <v>84.56</v>
+        <v>121.56</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>5.61</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="180">
@@ -20954,31 +20954,31 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="D180" t="n">
         <v>605.66</v>
       </c>
       <c r="E180" t="n">
-        <v>-4.66</v>
+        <v>9.34</v>
       </c>
       <c r="F180" t="n">
-        <v>615.9</v>
+        <v>615.3</v>
       </c>
       <c r="G180" t="n">
         <v>625.39</v>
       </c>
       <c r="H180" t="n">
-        <v>-9.49</v>
+        <v>-10.09</v>
       </c>
       <c r="I180" t="n">
-        <v>599.5</v>
+        <v>603</v>
       </c>
       <c r="J180" t="n">
         <v>584.17</v>
       </c>
       <c r="K180" t="n">
-        <v>15.33</v>
+        <v>18.83</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0.77</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="181">
@@ -21006,31 +21006,31 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>8066.5</v>
+        <v>8100</v>
       </c>
       <c r="D181" t="n">
         <v>8213.74</v>
       </c>
       <c r="E181" t="n">
-        <v>-147.24</v>
+        <v>-113.74</v>
       </c>
       <c r="F181" t="n">
-        <v>8143</v>
+        <v>8100</v>
       </c>
       <c r="G181" t="n">
         <v>8234.459999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>-91.45999999999999</v>
+        <v>-134.46</v>
       </c>
       <c r="I181" t="n">
-        <v>8030</v>
+        <v>8011</v>
       </c>
       <c r="J181" t="n">
         <v>7960.64</v>
       </c>
       <c r="K181" t="n">
-        <v>69.36</v>
+        <v>50.36</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="182">
@@ -21058,31 +21058,31 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>14130</v>
+        <v>14035</v>
       </c>
       <c r="D182" t="n">
         <v>14288.94</v>
       </c>
       <c r="E182" t="n">
-        <v>-158.94</v>
+        <v>-253.94</v>
       </c>
       <c r="F182" t="n">
-        <v>14209</v>
+        <v>14065</v>
       </c>
       <c r="G182" t="n">
         <v>14564.62</v>
       </c>
       <c r="H182" t="n">
-        <v>-355.62</v>
+        <v>-499.62</v>
       </c>
       <c r="I182" t="n">
-        <v>13999</v>
+        <v>13645</v>
       </c>
       <c r="J182" t="n">
         <v>13838.77</v>
       </c>
       <c r="K182" t="n">
-        <v>160.23</v>
+        <v>-193.77</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="183">
@@ -21110,13 +21110,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5310</v>
+        <v>5370</v>
       </c>
       <c r="D183" t="n">
         <v>5527.49</v>
       </c>
       <c r="E183" t="n">
-        <v>-217.49</v>
+        <v>-157.49</v>
       </c>
       <c r="F183" t="n">
         <v>5370</v>
@@ -21128,13 +21128,13 @@
         <v>-80.48</v>
       </c>
       <c r="I183" t="n">
-        <v>5310</v>
+        <v>5281.5</v>
       </c>
       <c r="J183" t="n">
         <v>5217.77</v>
       </c>
       <c r="K183" t="n">
-        <v>92.23</v>
+        <v>63.73</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>3.93</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="184">
@@ -21162,31 +21162,31 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>171.64</v>
+        <v>176.23</v>
       </c>
       <c r="D184" t="n">
         <v>178.54</v>
       </c>
       <c r="E184" t="n">
-        <v>-6.9</v>
+        <v>-2.31</v>
       </c>
       <c r="F184" t="n">
-        <v>179.5</v>
+        <v>182.7</v>
       </c>
       <c r="G184" t="n">
         <v>177.11</v>
       </c>
       <c r="H184" t="n">
-        <v>2.39</v>
+        <v>5.59</v>
       </c>
       <c r="I184" t="n">
-        <v>169.75</v>
+        <v>176.23</v>
       </c>
       <c r="J184" t="n">
         <v>167.96</v>
       </c>
       <c r="K184" t="n">
-        <v>1.79</v>
+        <v>8.27</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.86</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="185">
@@ -21214,31 +21214,31 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>376</v>
+        <v>400.5</v>
       </c>
       <c r="D185" t="n">
         <v>415.79</v>
       </c>
       <c r="E185" t="n">
-        <v>-39.79</v>
+        <v>-15.29</v>
       </c>
       <c r="F185" t="n">
-        <v>384.95</v>
+        <v>413.65</v>
       </c>
       <c r="G185" t="n">
         <v>390.36</v>
       </c>
       <c r="H185" t="n">
-        <v>-5.41</v>
+        <v>23.29</v>
       </c>
       <c r="I185" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="J185" t="n">
         <v>366.15</v>
       </c>
       <c r="K185" t="n">
-        <v>8.85</v>
+        <v>33.85</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -21247,11 +21247,11 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>9.57</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="186">
@@ -21266,31 +21266,31 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>7649</v>
+        <v>7710</v>
       </c>
       <c r="D186" t="n">
         <v>7989.01</v>
       </c>
       <c r="E186" t="n">
-        <v>-340.01</v>
+        <v>-279.01</v>
       </c>
       <c r="F186" t="n">
-        <v>7825</v>
+        <v>7772</v>
       </c>
       <c r="G186" t="n">
         <v>7880.44</v>
       </c>
       <c r="H186" t="n">
-        <v>-55.44</v>
+        <v>-108.44</v>
       </c>
       <c r="I186" t="n">
-        <v>7639</v>
+        <v>7659</v>
       </c>
       <c r="J186" t="n">
         <v>7494.24</v>
       </c>
       <c r="K186" t="n">
-        <v>144.76</v>
+        <v>164.76</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>4.26</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="187">
@@ -21318,31 +21318,31 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2199</v>
+        <v>2237.1</v>
       </c>
       <c r="D187" t="n">
         <v>2295.05</v>
       </c>
       <c r="E187" t="n">
-        <v>-96.05</v>
+        <v>-57.95</v>
       </c>
       <c r="F187" t="n">
-        <v>2255</v>
+        <v>2273.9</v>
       </c>
       <c r="G187" t="n">
         <v>2263.23</v>
       </c>
       <c r="H187" t="n">
-        <v>-8.23</v>
+        <v>10.67</v>
       </c>
       <c r="I187" t="n">
-        <v>2191.6</v>
+        <v>2219.5</v>
       </c>
       <c r="J187" t="n">
         <v>2156.24</v>
       </c>
       <c r="K187" t="n">
-        <v>35.36</v>
+        <v>63.26</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -21351,11 +21351,11 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N187" t="n">
-        <v>4.19</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="188">
@@ -21370,31 +21370,31 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D188" t="n">
         <v>1893.76</v>
       </c>
       <c r="E188" t="n">
-        <v>-81.76000000000001</v>
+        <v>-64.76000000000001</v>
       </c>
       <c r="F188" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G188" t="n">
         <v>1879.03</v>
       </c>
       <c r="H188" t="n">
-        <v>-42.63</v>
+        <v>-49.13</v>
       </c>
       <c r="I188" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J188" t="n">
         <v>1766.13</v>
       </c>
       <c r="K188" t="n">
-        <v>38.07</v>
+        <v>21.87</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>4.32</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="189">
@@ -21422,31 +21422,31 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1029.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D189" t="n">
         <v>1107.55</v>
       </c>
       <c r="E189" t="n">
-        <v>-78.05</v>
+        <v>-61.3</v>
       </c>
       <c r="F189" t="n">
-        <v>1036.8</v>
+        <v>1073</v>
       </c>
       <c r="G189" t="n">
         <v>1058.28</v>
       </c>
       <c r="H189" t="n">
-        <v>-21.48</v>
+        <v>14.72</v>
       </c>
       <c r="I189" t="n">
-        <v>1021.35</v>
+        <v>1040</v>
       </c>
       <c r="J189" t="n">
         <v>1010.46</v>
       </c>
       <c r="K189" t="n">
-        <v>10.89</v>
+        <v>29.54</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>7.05</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="190">
@@ -21474,31 +21474,31 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1343</v>
+        <v>1357.3</v>
       </c>
       <c r="D190" t="n">
         <v>1387.17</v>
       </c>
       <c r="E190" t="n">
-        <v>-44.17</v>
+        <v>-29.87</v>
       </c>
       <c r="F190" t="n">
-        <v>1367.1</v>
+        <v>1369.4</v>
       </c>
       <c r="G190" t="n">
         <v>1392.93</v>
       </c>
       <c r="H190" t="n">
-        <v>-25.83</v>
+        <v>-23.53</v>
       </c>
       <c r="I190" t="n">
-        <v>1337</v>
+        <v>1336.5</v>
       </c>
       <c r="J190" t="n">
         <v>1308.81</v>
       </c>
       <c r="K190" t="n">
-        <v>28.19</v>
+        <v>27.69</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -21507,11 +21507,11 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N190" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="191">
@@ -21526,31 +21526,31 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>4057</v>
+        <v>4070.7</v>
       </c>
       <c r="D191" t="n">
         <v>4104.58</v>
       </c>
       <c r="E191" t="n">
-        <v>-47.58</v>
+        <v>-33.88</v>
       </c>
       <c r="F191" t="n">
-        <v>4072.5</v>
+        <v>4070.7</v>
       </c>
       <c r="G191" t="n">
         <v>4127.47</v>
       </c>
       <c r="H191" t="n">
-        <v>-54.97</v>
+        <v>-56.77</v>
       </c>
       <c r="I191" t="n">
-        <v>4033.1</v>
+        <v>3990</v>
       </c>
       <c r="J191" t="n">
         <v>4014.32</v>
       </c>
       <c r="K191" t="n">
-        <v>18.78</v>
+        <v>-24.32</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1.16</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="192">
@@ -21578,31 +21578,31 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>282.6</v>
+        <v>279.3</v>
       </c>
       <c r="D192" t="n">
         <v>291.64</v>
       </c>
       <c r="E192" t="n">
-        <v>-9.039999999999999</v>
+        <v>-12.34</v>
       </c>
       <c r="F192" t="n">
-        <v>283.5</v>
+        <v>287.4</v>
       </c>
       <c r="G192" t="n">
         <v>289.69</v>
       </c>
       <c r="H192" t="n">
-        <v>-6.19</v>
+        <v>-2.29</v>
       </c>
       <c r="I192" t="n">
-        <v>277.15</v>
+        <v>273</v>
       </c>
       <c r="J192" t="n">
         <v>277.97</v>
       </c>
       <c r="K192" t="n">
-        <v>-0.82</v>
+        <v>-4.97</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>3.1</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="193">
@@ -21630,31 +21630,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>527</v>
+        <v>533.65</v>
       </c>
       <c r="D193" t="n">
         <v>517.03</v>
       </c>
       <c r="E193" t="n">
-        <v>9.970000000000001</v>
+        <v>16.62</v>
       </c>
       <c r="F193" t="n">
-        <v>543.7</v>
+        <v>535.5</v>
       </c>
       <c r="G193" t="n">
         <v>543.71</v>
       </c>
       <c r="H193" t="n">
-        <v>-0.01</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="I193" t="n">
-        <v>527</v>
+        <v>513.7</v>
       </c>
       <c r="J193" t="n">
         <v>515.76</v>
       </c>
       <c r="K193" t="n">
-        <v>11.24</v>
+        <v>-2.06</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1.93</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="194">
@@ -21682,31 +21682,31 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2008.3</v>
+        <v>2025</v>
       </c>
       <c r="D194" t="n">
         <v>2110.23</v>
       </c>
       <c r="E194" t="n">
-        <v>-101.93</v>
+        <v>-85.23</v>
       </c>
       <c r="F194" t="n">
-        <v>2033.6</v>
+        <v>2038</v>
       </c>
       <c r="G194" t="n">
         <v>2064.37</v>
       </c>
       <c r="H194" t="n">
-        <v>-30.77</v>
+        <v>-26.37</v>
       </c>
       <c r="I194" t="n">
-        <v>2006.6</v>
+        <v>2006.7</v>
       </c>
       <c r="J194" t="n">
         <v>1971.21</v>
       </c>
       <c r="K194" t="n">
-        <v>35.39</v>
+        <v>35.49</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>4.83</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="195">
@@ -21734,31 +21734,31 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1450</v>
+        <v>1458.8</v>
       </c>
       <c r="D195" t="n">
         <v>1497.51</v>
       </c>
       <c r="E195" t="n">
-        <v>-47.51</v>
+        <v>-38.71</v>
       </c>
       <c r="F195" t="n">
-        <v>1474.3</v>
+        <v>1464.4</v>
       </c>
       <c r="G195" t="n">
         <v>1479.52</v>
       </c>
       <c r="H195" t="n">
-        <v>-5.22</v>
+        <v>-15.12</v>
       </c>
       <c r="I195" t="n">
-        <v>1449.2</v>
+        <v>1456.2</v>
       </c>
       <c r="J195" t="n">
         <v>1431.47</v>
       </c>
       <c r="K195" t="n">
-        <v>17.73</v>
+        <v>24.73</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>3.17</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="196">
@@ -21786,31 +21786,31 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D196" t="n">
         <v>1225.54</v>
       </c>
       <c r="E196" t="n">
-        <v>-45.54</v>
+        <v>-42.54</v>
       </c>
       <c r="F196" t="n">
-        <v>1191.5</v>
+        <v>1184.9</v>
       </c>
       <c r="G196" t="n">
         <v>1217.2</v>
       </c>
       <c r="H196" t="n">
-        <v>-25.7</v>
+        <v>-32.3</v>
       </c>
       <c r="I196" t="n">
-        <v>1167</v>
+        <v>1149.2</v>
       </c>
       <c r="J196" t="n">
         <v>1154.99</v>
       </c>
       <c r="K196" t="n">
-        <v>12.01</v>
+        <v>-5.79</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="197">
@@ -21838,31 +21838,31 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>894.95</v>
+        <v>897</v>
       </c>
       <c r="D197" t="n">
         <v>929.49</v>
       </c>
       <c r="E197" t="n">
-        <v>-34.54</v>
+        <v>-32.49</v>
       </c>
       <c r="F197" t="n">
-        <v>902.8</v>
+        <v>903.8</v>
       </c>
       <c r="G197" t="n">
         <v>915.6900000000001</v>
       </c>
       <c r="H197" t="n">
-        <v>-12.89</v>
+        <v>-11.89</v>
       </c>
       <c r="I197" t="n">
-        <v>885.3</v>
+        <v>883.15</v>
       </c>
       <c r="J197" t="n">
         <v>881.61</v>
       </c>
       <c r="K197" t="n">
-        <v>3.69</v>
+        <v>1.54</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -9134,31 +9134,31 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>117.59</v>
+        <v>118</v>
       </c>
       <c r="D168" t="n">
-        <v>122.61</v>
+        <v>114.07</v>
       </c>
       <c r="E168" t="n">
-        <v>-5.02</v>
+        <v>3.93</v>
       </c>
       <c r="F168" t="n">
-        <v>119.35</v>
+        <v>118.9</v>
       </c>
       <c r="G168" t="n">
-        <v>122.61</v>
+        <v>118.72</v>
       </c>
       <c r="H168" t="n">
-        <v>-3.26</v>
+        <v>0.18</v>
       </c>
       <c r="I168" t="n">
-        <v>117.31</v>
+        <v>117.4</v>
       </c>
       <c r="J168" t="n">
-        <v>115.8</v>
+        <v>116.76</v>
       </c>
       <c r="K168" t="n">
-        <v>1.51</v>
+        <v>0.64</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>4.09</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="169">
@@ -9186,31 +9186,31 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1083</v>
+        <v>1067.7</v>
       </c>
       <c r="D169" t="n">
-        <v>1086.93</v>
+        <v>1072.34</v>
       </c>
       <c r="E169" t="n">
-        <v>-3.93</v>
+        <v>-4.64</v>
       </c>
       <c r="F169" t="n">
-        <v>1086.8</v>
+        <v>1082</v>
       </c>
       <c r="G169" t="n">
-        <v>1089.74</v>
+        <v>1081.22</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.94</v>
+        <v>0.78</v>
       </c>
       <c r="I169" t="n">
-        <v>1073</v>
+        <v>1065.1</v>
       </c>
       <c r="J169" t="n">
-        <v>1057.42</v>
+        <v>1062.44</v>
       </c>
       <c r="K169" t="n">
-        <v>15.58</v>
+        <v>2.66</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="170">
@@ -9234,35 +9234,35 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>11420</v>
+        <v>5580</v>
       </c>
       <c r="D170" t="n">
-        <v>11780.86</v>
+        <v>5729.65</v>
       </c>
       <c r="E170" t="n">
-        <v>-360.86</v>
+        <v>-149.65</v>
       </c>
       <c r="F170" t="n">
-        <v>11686</v>
+        <v>5618.5</v>
       </c>
       <c r="G170" t="n">
-        <v>12109.86</v>
+        <v>5729.65</v>
       </c>
       <c r="H170" t="n">
-        <v>-423.86</v>
+        <v>-111.15</v>
       </c>
       <c r="I170" t="n">
-        <v>11350</v>
+        <v>5447</v>
       </c>
       <c r="J170" t="n">
-        <v>11751.99</v>
+        <v>5507.17</v>
       </c>
       <c r="K170" t="n">
-        <v>-401.99</v>
+        <v>-60.17</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9271,11 +9271,11 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>3.06</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="171">
@@ -9286,35 +9286,35 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11500</v>
+        <v>11828</v>
       </c>
       <c r="D171" t="n">
-        <v>11562.29</v>
+        <v>11594.94</v>
       </c>
       <c r="E171" t="n">
-        <v>-62.29</v>
+        <v>233.06</v>
       </c>
       <c r="F171" t="n">
-        <v>11570</v>
+        <v>11850</v>
       </c>
       <c r="G171" t="n">
-        <v>11562.29</v>
+        <v>12105.29</v>
       </c>
       <c r="H171" t="n">
-        <v>7.71</v>
+        <v>-255.29</v>
       </c>
       <c r="I171" t="n">
-        <v>11410</v>
+        <v>11318</v>
       </c>
       <c r="J171" t="n">
-        <v>11214.54</v>
+        <v>11828</v>
       </c>
       <c r="K171" t="n">
-        <v>195.46</v>
+        <v>-510</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0.54</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="172">
@@ -9338,35 +9338,35 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1240</v>
+        <v>3428.3</v>
       </c>
       <c r="D172" t="n">
-        <v>1229.5</v>
+        <v>3558.92</v>
       </c>
       <c r="E172" t="n">
-        <v>10.5</v>
+        <v>-130.62</v>
       </c>
       <c r="F172" t="n">
-        <v>1264.7</v>
+        <v>3430</v>
       </c>
       <c r="G172" t="n">
-        <v>1268.15</v>
+        <v>3558.92</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.45</v>
+        <v>-128.92</v>
       </c>
       <c r="I172" t="n">
-        <v>1237</v>
+        <v>3378.3</v>
       </c>
       <c r="J172" t="n">
-        <v>1230.63</v>
+        <v>3362.29</v>
       </c>
       <c r="K172" t="n">
-        <v>6.37</v>
+        <v>16.01</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0.85</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="173">
@@ -9390,35 +9390,35 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>186.5</v>
+        <v>8066.5</v>
       </c>
       <c r="D173" t="n">
-        <v>189.94</v>
+        <v>8153.47</v>
       </c>
       <c r="E173" t="n">
-        <v>-3.44</v>
+        <v>-86.97</v>
       </c>
       <c r="F173" t="n">
-        <v>188.7</v>
+        <v>8143</v>
       </c>
       <c r="G173" t="n">
-        <v>192.97</v>
+        <v>8153.47</v>
       </c>
       <c r="H173" t="n">
-        <v>-4.27</v>
+        <v>-10.47</v>
       </c>
       <c r="I173" t="n">
-        <v>185.32</v>
+        <v>8030</v>
       </c>
       <c r="J173" t="n">
-        <v>187.3</v>
+        <v>7965.64</v>
       </c>
       <c r="K173" t="n">
-        <v>-1.98</v>
+        <v>64.36</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1.81</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="174">
@@ -9442,35 +9442,35 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1939.1</v>
+        <v>187.38</v>
       </c>
       <c r="D174" t="n">
-        <v>2038.57</v>
+        <v>186.39</v>
       </c>
       <c r="E174" t="n">
-        <v>-99.47</v>
+        <v>0.99</v>
       </c>
       <c r="F174" t="n">
-        <v>1970</v>
+        <v>189.34</v>
       </c>
       <c r="G174" t="n">
-        <v>2039.97</v>
+        <v>192.11</v>
       </c>
       <c r="H174" t="n">
-        <v>-69.97</v>
+        <v>-2.77</v>
       </c>
       <c r="I174" t="n">
-        <v>1930.5</v>
+        <v>186.39</v>
       </c>
       <c r="J174" t="n">
-        <v>1992.1</v>
+        <v>187.38</v>
       </c>
       <c r="K174" t="n">
-        <v>-61.6</v>
+        <v>-0.99</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9479,11 +9479,11 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>4.88</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="175">
@@ -9494,35 +9494,35 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8100</v>
+        <v>5790</v>
       </c>
       <c r="D175" t="n">
-        <v>8077.69</v>
+        <v>5704.13</v>
       </c>
       <c r="E175" t="n">
-        <v>22.31</v>
+        <v>85.87</v>
       </c>
       <c r="F175" t="n">
-        <v>8100</v>
+        <v>5849</v>
       </c>
       <c r="G175" t="n">
-        <v>8093.76</v>
+        <v>5841.09</v>
       </c>
       <c r="H175" t="n">
-        <v>6.24</v>
+        <v>7.91</v>
       </c>
       <c r="I175" t="n">
-        <v>8011</v>
+        <v>5765</v>
       </c>
       <c r="J175" t="n">
-        <v>7900.17</v>
+        <v>5738.86</v>
       </c>
       <c r="K175" t="n">
-        <v>110.83</v>
+        <v>26.14</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0.28</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="176">
@@ -9546,35 +9546,35 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5523</v>
+        <v>1632.8</v>
       </c>
       <c r="D176" t="n">
-        <v>5421.76</v>
+        <v>1665.58</v>
       </c>
       <c r="E176" t="n">
-        <v>101.24</v>
+        <v>-32.78</v>
       </c>
       <c r="F176" t="n">
-        <v>5529</v>
+        <v>1652</v>
       </c>
       <c r="G176" t="n">
-        <v>5718.11</v>
+        <v>1665.58</v>
       </c>
       <c r="H176" t="n">
-        <v>-189.11</v>
+        <v>-13.58</v>
       </c>
       <c r="I176" t="n">
-        <v>5406</v>
+        <v>1614.4</v>
       </c>
       <c r="J176" t="n">
-        <v>5549.31</v>
+        <v>1631.3</v>
       </c>
       <c r="K176" t="n">
-        <v>-143.31</v>
+        <v>-16.9</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="177">
@@ -9598,35 +9598,35 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1639</v>
+        <v>318.5</v>
       </c>
       <c r="D177" t="n">
-        <v>1619.59</v>
+        <v>339.17</v>
       </c>
       <c r="E177" t="n">
-        <v>19.41</v>
+        <v>-20.67</v>
       </c>
       <c r="F177" t="n">
-        <v>1652.8</v>
+        <v>325</v>
       </c>
       <c r="G177" t="n">
-        <v>1667.09</v>
+        <v>339.17</v>
       </c>
       <c r="H177" t="n">
-        <v>-14.29</v>
+        <v>-14.17</v>
       </c>
       <c r="I177" t="n">
-        <v>1626.3</v>
+        <v>316.8</v>
       </c>
       <c r="J177" t="n">
-        <v>1617.66</v>
+        <v>317.11</v>
       </c>
       <c r="K177" t="n">
-        <v>8.640000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1.2</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="178">
@@ -9650,35 +9650,35 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5850</v>
+        <v>1992.1</v>
       </c>
       <c r="D178" t="n">
-        <v>5985.55</v>
+        <v>1920.95</v>
       </c>
       <c r="E178" t="n">
-        <v>-135.55</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F178" t="n">
-        <v>5934</v>
+        <v>2005.8</v>
       </c>
       <c r="G178" t="n">
-        <v>5985.55</v>
+        <v>2030.91</v>
       </c>
       <c r="H178" t="n">
-        <v>-51.55</v>
+        <v>-25.11</v>
       </c>
       <c r="I178" t="n">
-        <v>5802</v>
+        <v>1932</v>
       </c>
       <c r="J178" t="n">
-        <v>5694.13</v>
+        <v>1992.1</v>
       </c>
       <c r="K178" t="n">
-        <v>107.87</v>
+        <v>-60.1</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9687,11 +9687,11 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="179">
@@ -9702,39 +9702,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3428.2</v>
+        <v>5310</v>
       </c>
       <c r="D179" t="n">
-        <v>3328.8</v>
+        <v>5317.96</v>
       </c>
       <c r="E179" t="n">
-        <v>99.40000000000001</v>
+        <v>-7.96</v>
       </c>
       <c r="F179" t="n">
-        <v>3440</v>
+        <v>5370</v>
       </c>
       <c r="G179" t="n">
-        <v>3417.82</v>
+        <v>5357.07</v>
       </c>
       <c r="H179" t="n">
-        <v>22.18</v>
+        <v>12.93</v>
       </c>
       <c r="I179" t="n">
-        <v>3396.5</v>
+        <v>5310</v>
       </c>
       <c r="J179" t="n">
-        <v>3334.66</v>
+        <v>5263.32</v>
       </c>
       <c r="K179" t="n">
-        <v>61.84</v>
+        <v>46.68</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>2.99</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="180">
@@ -9754,39 +9754,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>318</v>
+        <v>14130</v>
       </c>
       <c r="D180" t="n">
-        <v>301.01</v>
+        <v>14369.66</v>
       </c>
       <c r="E180" t="n">
-        <v>16.99</v>
+        <v>-239.66</v>
       </c>
       <c r="F180" t="n">
-        <v>319.35</v>
+        <v>14209</v>
       </c>
       <c r="G180" t="n">
-        <v>324.15</v>
+        <v>14369.66</v>
       </c>
       <c r="H180" t="n">
-        <v>-4.8</v>
+        <v>-160.66</v>
       </c>
       <c r="I180" t="n">
-        <v>313.3</v>
+        <v>13999</v>
       </c>
       <c r="J180" t="n">
-        <v>314.5</v>
+        <v>13811.08</v>
       </c>
       <c r="K180" t="n">
-        <v>-1.2</v>
+        <v>187.92</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>5.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="181">
@@ -9806,39 +9806,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>14035</v>
+        <v>1240</v>
       </c>
       <c r="D181" t="n">
-        <v>13911.32</v>
+        <v>1260.59</v>
       </c>
       <c r="E181" t="n">
-        <v>123.68</v>
+        <v>-20.59</v>
       </c>
       <c r="F181" t="n">
-        <v>14065</v>
+        <v>1246.9</v>
       </c>
       <c r="G181" t="n">
-        <v>13911.32</v>
+        <v>1261.6</v>
       </c>
       <c r="H181" t="n">
-        <v>153.68</v>
+        <v>-14.7</v>
       </c>
       <c r="I181" t="n">
-        <v>13645</v>
+        <v>1230.1</v>
       </c>
       <c r="J181" t="n">
-        <v>13697.56</v>
+        <v>1239.9</v>
       </c>
       <c r="K181" t="n">
-        <v>-52.56</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0.89</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="182">
@@ -9858,39 +9858,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>615</v>
+        <v>376</v>
       </c>
       <c r="D182" t="n">
-        <v>583.87</v>
+        <v>377.79</v>
       </c>
       <c r="E182" t="n">
-        <v>31.13</v>
+        <v>-1.79</v>
       </c>
       <c r="F182" t="n">
-        <v>615.3</v>
+        <v>384.95</v>
       </c>
       <c r="G182" t="n">
-        <v>606.37</v>
+        <v>377.79</v>
       </c>
       <c r="H182" t="n">
-        <v>8.93</v>
+        <v>7.16</v>
       </c>
       <c r="I182" t="n">
-        <v>603</v>
+        <v>375</v>
       </c>
       <c r="J182" t="n">
-        <v>588.14</v>
+        <v>364.69</v>
       </c>
       <c r="K182" t="n">
-        <v>14.86</v>
+        <v>10.31</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>5.33</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="183">
@@ -9910,35 +9910,35 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5370</v>
+        <v>7649</v>
       </c>
       <c r="D183" t="n">
-        <v>5404.88</v>
+        <v>7639.02</v>
       </c>
       <c r="E183" t="n">
-        <v>-34.88</v>
+        <v>9.98</v>
       </c>
       <c r="F183" t="n">
-        <v>5370</v>
+        <v>7825</v>
       </c>
       <c r="G183" t="n">
-        <v>5404.88</v>
+        <v>7758.82</v>
       </c>
       <c r="H183" t="n">
-        <v>-34.88</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="I183" t="n">
-        <v>5281.5</v>
+        <v>7639</v>
       </c>
       <c r="J183" t="n">
-        <v>5220.06</v>
+        <v>7624.51</v>
       </c>
       <c r="K183" t="n">
-        <v>61.44</v>
+        <v>14.49</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="184">
@@ -9962,35 +9962,35 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>176.23</v>
+        <v>11475</v>
       </c>
       <c r="D184" t="n">
-        <v>173.62</v>
+        <v>11504.45</v>
       </c>
       <c r="E184" t="n">
-        <v>2.61</v>
+        <v>-29.45</v>
       </c>
       <c r="F184" t="n">
-        <v>182.7</v>
+        <v>11541</v>
       </c>
       <c r="G184" t="n">
-        <v>174.94</v>
+        <v>11504.45</v>
       </c>
       <c r="H184" t="n">
-        <v>7.76</v>
+        <v>36.55</v>
       </c>
       <c r="I184" t="n">
-        <v>176.23</v>
+        <v>11387</v>
       </c>
       <c r="J184" t="n">
-        <v>169.74</v>
+        <v>11317.78</v>
       </c>
       <c r="K184" t="n">
-        <v>6.49</v>
+        <v>69.22</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="185">
@@ -10014,35 +10014,35 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7710</v>
+        <v>1812</v>
       </c>
       <c r="D185" t="n">
-        <v>7781.82</v>
+        <v>1823.32</v>
       </c>
       <c r="E185" t="n">
-        <v>-71.81999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="F185" t="n">
-        <v>7772</v>
+        <v>1836.4</v>
       </c>
       <c r="G185" t="n">
-        <v>7793.45</v>
+        <v>1823.32</v>
       </c>
       <c r="H185" t="n">
-        <v>-21.45</v>
+        <v>13.08</v>
       </c>
       <c r="I185" t="n">
-        <v>7659</v>
+        <v>1804.2</v>
       </c>
       <c r="J185" t="n">
-        <v>7561.84</v>
+        <v>1772.18</v>
       </c>
       <c r="K185" t="n">
-        <v>97.16</v>
+        <v>32.02</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="186">
@@ -10070,31 +10070,31 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2237.1</v>
+        <v>2199</v>
       </c>
       <c r="D186" t="n">
-        <v>2237.89</v>
+        <v>2215.81</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.79</v>
+        <v>-16.81</v>
       </c>
       <c r="F186" t="n">
-        <v>2273.9</v>
+        <v>2255</v>
       </c>
       <c r="G186" t="n">
-        <v>2237.89</v>
+        <v>2215.81</v>
       </c>
       <c r="H186" t="n">
-        <v>36.01</v>
+        <v>39.19</v>
       </c>
       <c r="I186" t="n">
-        <v>2219.5</v>
+        <v>2191.6</v>
       </c>
       <c r="J186" t="n">
-        <v>2135.13</v>
+        <v>2152.82</v>
       </c>
       <c r="K186" t="n">
-        <v>84.37</v>
+        <v>38.78</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="187">
@@ -10118,35 +10118,35 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1829</v>
+        <v>4057</v>
       </c>
       <c r="D187" t="n">
-        <v>1832.18</v>
+        <v>4109.5</v>
       </c>
       <c r="E187" t="n">
-        <v>-3.18</v>
+        <v>-52.5</v>
       </c>
       <c r="F187" t="n">
-        <v>1829.9</v>
+        <v>4072.5</v>
       </c>
       <c r="G187" t="n">
-        <v>1832.18</v>
+        <v>4119.97</v>
       </c>
       <c r="H187" t="n">
-        <v>-2.28</v>
+        <v>-47.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1788</v>
+        <v>4033.1</v>
       </c>
       <c r="J187" t="n">
-        <v>1760.46</v>
+        <v>4057</v>
       </c>
       <c r="K187" t="n">
-        <v>27.54</v>
+        <v>-23.9</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>0.17</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="188">
@@ -10170,35 +10170,35 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1357.3</v>
+        <v>171.64</v>
       </c>
       <c r="D188" t="n">
-        <v>1341.8</v>
+        <v>175.61</v>
       </c>
       <c r="E188" t="n">
-        <v>15.5</v>
+        <v>-3.97</v>
       </c>
       <c r="F188" t="n">
-        <v>1369.4</v>
+        <v>179.5</v>
       </c>
       <c r="G188" t="n">
-        <v>1365.14</v>
+        <v>175.61</v>
       </c>
       <c r="H188" t="n">
-        <v>4.26</v>
+        <v>3.89</v>
       </c>
       <c r="I188" t="n">
-        <v>1336.5</v>
+        <v>169.75</v>
       </c>
       <c r="J188" t="n">
-        <v>1324.46</v>
+        <v>171.41</v>
       </c>
       <c r="K188" t="n">
-        <v>12.04</v>
+        <v>-1.66</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1.16</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="189">
@@ -10222,35 +10222,35 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4070.7</v>
+        <v>1029.5</v>
       </c>
       <c r="D189" t="n">
-        <v>4054.81</v>
+        <v>1004.04</v>
       </c>
       <c r="E189" t="n">
-        <v>15.89</v>
+        <v>25.46</v>
       </c>
       <c r="F189" t="n">
-        <v>4070.7</v>
+        <v>1036.8</v>
       </c>
       <c r="G189" t="n">
-        <v>4138.36</v>
+        <v>1022.66</v>
       </c>
       <c r="H189" t="n">
-        <v>-67.66</v>
+        <v>14.14</v>
       </c>
       <c r="I189" t="n">
-        <v>3990</v>
+        <v>1021.35</v>
       </c>
       <c r="J189" t="n">
-        <v>4038.69</v>
+        <v>1009.19</v>
       </c>
       <c r="K189" t="n">
-        <v>-48.69</v>
+        <v>12.16</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0.39</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="190">
@@ -10278,31 +10278,31 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>279.3</v>
+        <v>282.6</v>
       </c>
       <c r="D190" t="n">
-        <v>285.56</v>
+        <v>278.62</v>
       </c>
       <c r="E190" t="n">
-        <v>-6.26</v>
+        <v>3.98</v>
       </c>
       <c r="F190" t="n">
-        <v>287.4</v>
+        <v>283.5</v>
       </c>
       <c r="G190" t="n">
-        <v>285.73</v>
+        <v>283.43</v>
       </c>
       <c r="H190" t="n">
-        <v>1.67</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>273</v>
+        <v>277.15</v>
       </c>
       <c r="J190" t="n">
-        <v>277.17</v>
+        <v>278.41</v>
       </c>
       <c r="K190" t="n">
-        <v>-4.17</v>
+        <v>-1.26</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>2.19</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="191">
@@ -10330,31 +10330,31 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1458.8</v>
+        <v>1450</v>
       </c>
       <c r="D191" t="n">
-        <v>1473.41</v>
+        <v>1447.1</v>
       </c>
       <c r="E191" t="n">
-        <v>-14.61</v>
+        <v>2.9</v>
       </c>
       <c r="F191" t="n">
-        <v>1464.4</v>
+        <v>1474.3</v>
       </c>
       <c r="G191" t="n">
-        <v>1481.82</v>
+        <v>1460.9</v>
       </c>
       <c r="H191" t="n">
-        <v>-17.42</v>
+        <v>13.4</v>
       </c>
       <c r="I191" t="n">
-        <v>1456.2</v>
+        <v>1449.2</v>
       </c>
       <c r="J191" t="n">
-        <v>1437.94</v>
+        <v>1436.58</v>
       </c>
       <c r="K191" t="n">
-        <v>18.26</v>
+        <v>12.62</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="192">
@@ -10378,35 +10378,35 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>400.5</v>
+        <v>601</v>
       </c>
       <c r="D192" t="n">
-        <v>401.79</v>
+        <v>638.11</v>
       </c>
       <c r="E192" t="n">
-        <v>-1.29</v>
+        <v>-37.11</v>
       </c>
       <c r="F192" t="n">
-        <v>413.65</v>
+        <v>615.9</v>
       </c>
       <c r="G192" t="n">
-        <v>401.79</v>
+        <v>638.11</v>
       </c>
       <c r="H192" t="n">
-        <v>11.86</v>
+        <v>-22.21</v>
       </c>
       <c r="I192" t="n">
-        <v>400</v>
+        <v>599.5</v>
       </c>
       <c r="J192" t="n">
-        <v>361.7</v>
+        <v>589.05</v>
       </c>
       <c r="K192" t="n">
-        <v>38.3</v>
+        <v>10.45</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0.32</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="193">
@@ -10434,31 +10434,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2025</v>
+        <v>2008.3</v>
       </c>
       <c r="D193" t="n">
-        <v>2060.38</v>
+        <v>1989.61</v>
       </c>
       <c r="E193" t="n">
-        <v>-35.38</v>
+        <v>18.69</v>
       </c>
       <c r="F193" t="n">
-        <v>2038</v>
+        <v>2033.6</v>
       </c>
       <c r="G193" t="n">
-        <v>2060.38</v>
+        <v>1989.61</v>
       </c>
       <c r="H193" t="n">
-        <v>-22.38</v>
+        <v>43.99</v>
       </c>
       <c r="I193" t="n">
-        <v>2006.7</v>
+        <v>2006.6</v>
       </c>
       <c r="J193" t="n">
-        <v>1952.58</v>
+        <v>1968.34</v>
       </c>
       <c r="K193" t="n">
-        <v>54.12</v>
+        <v>38.26</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1.72</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10482,35 +10482,35 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1046.25</v>
+        <v>1180</v>
       </c>
       <c r="D194" t="n">
-        <v>1081.36</v>
+        <v>1180.22</v>
       </c>
       <c r="E194" t="n">
-        <v>-35.11</v>
+        <v>-0.22</v>
       </c>
       <c r="F194" t="n">
-        <v>1073</v>
+        <v>1191.5</v>
       </c>
       <c r="G194" t="n">
-        <v>1081.36</v>
+        <v>1180.22</v>
       </c>
       <c r="H194" t="n">
-        <v>-8.359999999999999</v>
+        <v>11.28</v>
       </c>
       <c r="I194" t="n">
-        <v>1040</v>
+        <v>1167</v>
       </c>
       <c r="J194" t="n">
-        <v>1000.9</v>
+        <v>1152.46</v>
       </c>
       <c r="K194" t="n">
-        <v>39.1</v>
+        <v>14.54</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>3.25</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="195">
@@ -10534,35 +10534,35 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1183</v>
+        <v>1343</v>
       </c>
       <c r="D195" t="n">
-        <v>1192.24</v>
+        <v>1369.38</v>
       </c>
       <c r="E195" t="n">
-        <v>-9.24</v>
+        <v>-26.38</v>
       </c>
       <c r="F195" t="n">
-        <v>1184.9</v>
+        <v>1367.1</v>
       </c>
       <c r="G195" t="n">
-        <v>1192.24</v>
+        <v>1369.38</v>
       </c>
       <c r="H195" t="n">
-        <v>-7.34</v>
+        <v>-2.28</v>
       </c>
       <c r="I195" t="n">
-        <v>1149.2</v>
+        <v>1337</v>
       </c>
       <c r="J195" t="n">
-        <v>1142.98</v>
+        <v>1319.59</v>
       </c>
       <c r="K195" t="n">
-        <v>6.22</v>
+        <v>17.41</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0.78</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="196">
@@ -10590,31 +10590,31 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>533.65</v>
+        <v>527</v>
       </c>
       <c r="D196" t="n">
-        <v>502.9</v>
+        <v>563.7</v>
       </c>
       <c r="E196" t="n">
-        <v>30.75</v>
+        <v>-36.7</v>
       </c>
       <c r="F196" t="n">
-        <v>535.5</v>
+        <v>543.7</v>
       </c>
       <c r="G196" t="n">
-        <v>521.27</v>
+        <v>563.7</v>
       </c>
       <c r="H196" t="n">
-        <v>14.23</v>
+        <v>-20</v>
       </c>
       <c r="I196" t="n">
-        <v>513.7</v>
+        <v>527</v>
       </c>
       <c r="J196" t="n">
-        <v>510.37</v>
+        <v>514.75</v>
       </c>
       <c r="K196" t="n">
-        <v>3.33</v>
+        <v>12.25</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -10623,11 +10623,11 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>6.11</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="197">
@@ -10642,31 +10642,31 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>897</v>
+        <v>894.95</v>
       </c>
       <c r="D197" t="n">
-        <v>911.91</v>
+        <v>887.36</v>
       </c>
       <c r="E197" t="n">
-        <v>-14.91</v>
+        <v>7.59</v>
       </c>
       <c r="F197" t="n">
-        <v>903.8</v>
+        <v>902.8</v>
       </c>
       <c r="G197" t="n">
-        <v>911.91</v>
+        <v>907.2</v>
       </c>
       <c r="H197" t="n">
-        <v>-8.109999999999999</v>
+        <v>-4.4</v>
       </c>
       <c r="I197" t="n">
-        <v>883.15</v>
+        <v>885.3</v>
       </c>
       <c r="J197" t="n">
-        <v>884.1799999999999</v>
+        <v>891.47</v>
       </c>
       <c r="K197" t="n">
-        <v>-1.03</v>
+        <v>-6.17</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1.64</v>
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -11508,31 +11508,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24395.85</v>
+        <v>24366</v>
       </c>
       <c r="D16" t="n">
         <v>24366</v>
       </c>
       <c r="E16" t="n">
-        <v>29.85</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>24431.6</v>
+        <v>24405.2</v>
       </c>
       <c r="G16" t="n">
         <v>24415.2</v>
       </c>
       <c r="H16" t="n">
-        <v>16.4</v>
+        <v>-10</v>
       </c>
       <c r="I16" t="n">
-        <v>24311.4</v>
+        <v>24296.8</v>
       </c>
       <c r="J16" t="n">
         <v>24306.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>-10</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -11560,31 +11560,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57635.25</v>
+        <v>57491.1</v>
       </c>
       <c r="D17" t="n">
         <v>57491.1</v>
       </c>
       <c r="E17" t="n">
-        <v>144.15</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>57799.15</v>
+        <v>57681.45</v>
       </c>
       <c r="G17" t="n">
         <v>57654.89</v>
       </c>
       <c r="H17" t="n">
-        <v>144.26</v>
+        <v>26.56</v>
       </c>
       <c r="I17" t="n">
-        <v>57548.6</v>
+        <v>57380.45</v>
       </c>
       <c r="J17" t="n">
         <v>57353.89</v>
       </c>
       <c r="K17" t="n">
-        <v>194.71</v>
+        <v>26.56</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20330,31 +20330,31 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>117.59</v>
+        <v>118</v>
       </c>
       <c r="D168" t="n">
-        <v>124.42</v>
+        <v>115.74</v>
       </c>
       <c r="E168" t="n">
-        <v>-6.83</v>
+        <v>2.26</v>
       </c>
       <c r="F168" t="n">
-        <v>119.35</v>
+        <v>118.9</v>
       </c>
       <c r="G168" t="n">
-        <v>120.23</v>
+        <v>119.67</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.88</v>
+        <v>-0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>117.31</v>
+        <v>117.4</v>
       </c>
       <c r="J168" t="n">
-        <v>116.63</v>
+        <v>117.57</v>
       </c>
       <c r="K168" t="n">
-        <v>0.68</v>
+        <v>-0.17</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -20363,11 +20363,11 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>5.49</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="169">
@@ -20378,35 +20378,35 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OFSS (AUG-2026 FUT)</t>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>11420</v>
+        <v>5580</v>
       </c>
       <c r="D169" t="n">
-        <v>12141.43</v>
+        <v>5907.99</v>
       </c>
       <c r="E169" t="n">
-        <v>-721.4299999999999</v>
+        <v>-327.99</v>
       </c>
       <c r="F169" t="n">
-        <v>11686</v>
+        <v>5618.5</v>
       </c>
       <c r="G169" t="n">
-        <v>12231.3</v>
+        <v>5747.37</v>
       </c>
       <c r="H169" t="n">
-        <v>-545.3</v>
+        <v>-128.87</v>
       </c>
       <c r="I169" t="n">
-        <v>11350</v>
+        <v>5447</v>
       </c>
       <c r="J169" t="n">
-        <v>11554.45</v>
+        <v>5492.54</v>
       </c>
       <c r="K169" t="n">
-        <v>-204.45</v>
+        <v>-45.54</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>5.94</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="170">
@@ -20430,35 +20430,35 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PERSISTENT (AUG-2026 FUT)</t>
+          <t>OFSS (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5523</v>
+        <v>11828</v>
       </c>
       <c r="D170" t="n">
-        <v>5594.79</v>
+        <v>11905.55</v>
       </c>
       <c r="E170" t="n">
-        <v>-71.79000000000001</v>
+        <v>-77.55</v>
       </c>
       <c r="F170" t="n">
-        <v>5529</v>
+        <v>11850</v>
       </c>
       <c r="G170" t="n">
-        <v>5777.31</v>
+        <v>12171.35</v>
       </c>
       <c r="H170" t="n">
-        <v>-248.31</v>
+        <v>-321.35</v>
       </c>
       <c r="I170" t="n">
-        <v>5406</v>
+        <v>11318</v>
       </c>
       <c r="J170" t="n">
-        <v>5445.64</v>
+        <v>11651.33</v>
       </c>
       <c r="K170" t="n">
-        <v>-39.64</v>
+        <v>-333.33</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>1.28</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="171">
@@ -20486,31 +20486,31 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1083</v>
+        <v>1067.7</v>
       </c>
       <c r="D171" t="n">
-        <v>1106.62</v>
+        <v>1091.61</v>
       </c>
       <c r="E171" t="n">
-        <v>-23.62</v>
+        <v>-23.91</v>
       </c>
       <c r="F171" t="n">
-        <v>1086.8</v>
+        <v>1082</v>
       </c>
       <c r="G171" t="n">
-        <v>1091.24</v>
+        <v>1086.23</v>
       </c>
       <c r="H171" t="n">
-        <v>-4.44</v>
+        <v>-4.23</v>
       </c>
       <c r="I171" t="n">
-        <v>1073</v>
+        <v>1065.1</v>
       </c>
       <c r="J171" t="n">
-        <v>1052.7</v>
+        <v>1061.26</v>
       </c>
       <c r="K171" t="n">
-        <v>20.3</v>
+        <v>3.84</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="172">
@@ -20534,35 +20534,35 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>UNOMINDA (AUG-2026 FUT)</t>
+          <t>M&amp;M (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1240</v>
+        <v>3428.3</v>
       </c>
       <c r="D172" t="n">
-        <v>1261.44</v>
+        <v>3642.9</v>
       </c>
       <c r="E172" t="n">
-        <v>-21.44</v>
+        <v>-214.6</v>
       </c>
       <c r="F172" t="n">
-        <v>1264.7</v>
+        <v>3430</v>
       </c>
       <c r="G172" t="n">
-        <v>1276.74</v>
+        <v>3506.34</v>
       </c>
       <c r="H172" t="n">
-        <v>-12.04</v>
+        <v>-76.34</v>
       </c>
       <c r="I172" t="n">
-        <v>1237</v>
+        <v>3378.3</v>
       </c>
       <c r="J172" t="n">
-        <v>1215.49</v>
+        <v>3393.47</v>
       </c>
       <c r="K172" t="n">
-        <v>21.51</v>
+        <v>-15.17</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -20571,11 +20571,11 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1.7</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="173">
@@ -20586,35 +20586,35 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>M&amp;M (AUG-2026 FUT)</t>
+          <t>ETERNAL (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3428.2</v>
+        <v>318.5</v>
       </c>
       <c r="D173" t="n">
-        <v>3407.86</v>
+        <v>349.05</v>
       </c>
       <c r="E173" t="n">
-        <v>20.34</v>
+        <v>-30.55</v>
       </c>
       <c r="F173" t="n">
-        <v>3440</v>
+        <v>325</v>
       </c>
       <c r="G173" t="n">
-        <v>3522.51</v>
+        <v>327.45</v>
       </c>
       <c r="H173" t="n">
-        <v>-82.51000000000001</v>
+        <v>-2.45</v>
       </c>
       <c r="I173" t="n">
-        <v>3396.5</v>
+        <v>316.8</v>
       </c>
       <c r="J173" t="n">
-        <v>3366.1</v>
+        <v>313.98</v>
       </c>
       <c r="K173" t="n">
-        <v>30.4</v>
+        <v>2.82</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -20623,11 +20623,11 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>0.6</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="174">
@@ -20638,35 +20638,35 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ETERNAL (AUG-2026 FUT)</t>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>318</v>
+        <v>187.38</v>
       </c>
       <c r="D174" t="n">
-        <v>309.81</v>
+        <v>189.68</v>
       </c>
       <c r="E174" t="n">
-        <v>8.19</v>
+        <v>-2.3</v>
       </c>
       <c r="F174" t="n">
-        <v>319.35</v>
+        <v>189.34</v>
       </c>
       <c r="G174" t="n">
-        <v>328.95</v>
+        <v>191.5</v>
       </c>
       <c r="H174" t="n">
-        <v>-9.6</v>
+        <v>-2.16</v>
       </c>
       <c r="I174" t="n">
-        <v>313.3</v>
+        <v>186.39</v>
       </c>
       <c r="J174" t="n">
-        <v>311.44</v>
+        <v>185.59</v>
       </c>
       <c r="K174" t="n">
-        <v>1.86</v>
+        <v>0.8</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2.64</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="175">
@@ -20690,35 +20690,35 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>11500</v>
+        <v>1992.1</v>
       </c>
       <c r="D175" t="n">
-        <v>11781.82</v>
+        <v>1941.42</v>
       </c>
       <c r="E175" t="n">
-        <v>-281.82</v>
+        <v>50.68</v>
       </c>
       <c r="F175" t="n">
-        <v>11570</v>
+        <v>2005.8</v>
       </c>
       <c r="G175" t="n">
-        <v>11737.66</v>
+        <v>2023.71</v>
       </c>
       <c r="H175" t="n">
-        <v>-167.66</v>
+        <v>-17.91</v>
       </c>
       <c r="I175" t="n">
-        <v>11410</v>
+        <v>1932</v>
       </c>
       <c r="J175" t="n">
-        <v>11306.52</v>
+        <v>1982.36</v>
       </c>
       <c r="K175" t="n">
-        <v>103.48</v>
+        <v>-50.36</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="176">
@@ -20742,35 +20742,35 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TECHM (AUG-2026 FUT)</t>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1639</v>
+        <v>5790</v>
       </c>
       <c r="D176" t="n">
-        <v>1657.38</v>
+        <v>5844.85</v>
       </c>
       <c r="E176" t="n">
-        <v>-18.38</v>
+        <v>-54.85</v>
       </c>
       <c r="F176" t="n">
-        <v>1652.8</v>
+        <v>5849</v>
       </c>
       <c r="G176" t="n">
-        <v>1677.01</v>
+        <v>5927.77</v>
       </c>
       <c r="H176" t="n">
-        <v>-24.21</v>
+        <v>-78.77</v>
       </c>
       <c r="I176" t="n">
-        <v>1626.3</v>
+        <v>5765</v>
       </c>
       <c r="J176" t="n">
-        <v>1603.67</v>
+        <v>5726.64</v>
       </c>
       <c r="K176" t="n">
-        <v>22.63</v>
+        <v>38.36</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -20794,39 +20794,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>UNIONBANK (AUG-2026 FUT)</t>
+          <t>TECHM (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>186.5</v>
+        <v>1632.8</v>
       </c>
       <c r="D177" t="n">
-        <v>193.32</v>
+        <v>1704.19</v>
       </c>
       <c r="E177" t="n">
-        <v>-6.82</v>
+        <v>-71.39</v>
       </c>
       <c r="F177" t="n">
-        <v>188.7</v>
+        <v>1652</v>
       </c>
       <c r="G177" t="n">
-        <v>192.38</v>
+        <v>1669.32</v>
       </c>
       <c r="H177" t="n">
-        <v>-3.68</v>
+        <v>-17.32</v>
       </c>
       <c r="I177" t="n">
-        <v>185.32</v>
+        <v>1614.4</v>
       </c>
       <c r="J177" t="n">
-        <v>184.1</v>
+        <v>1616.72</v>
       </c>
       <c r="K177" t="n">
-        <v>1.22</v>
+        <v>-2.32</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -20835,7 +20835,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>3.53</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="178">
@@ -20846,39 +20846,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BHARTIARTL (AUG-2026 FUT)</t>
+          <t>EICHERMOT (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1939.1</v>
+        <v>8066.5</v>
       </c>
       <c r="D178" t="n">
-        <v>2059.2</v>
+        <v>8289.58</v>
       </c>
       <c r="E178" t="n">
-        <v>-120.1</v>
+        <v>-223.08</v>
       </c>
       <c r="F178" t="n">
-        <v>1970</v>
+        <v>8143</v>
       </c>
       <c r="G178" t="n">
-        <v>2033.05</v>
+        <v>8196.65</v>
       </c>
       <c r="H178" t="n">
-        <v>-63.05</v>
+        <v>-53.65</v>
       </c>
       <c r="I178" t="n">
-        <v>1930.5</v>
+        <v>8030</v>
       </c>
       <c r="J178" t="n">
-        <v>1966.36</v>
+        <v>8025.38</v>
       </c>
       <c r="K178" t="n">
-        <v>-35.86</v>
+        <v>4.62</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>5.83</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="179">
@@ -20898,48 +20898,48 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+          <t>INDIGO (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5850</v>
+        <v>5310</v>
       </c>
       <c r="D179" t="n">
-        <v>6134.12</v>
+        <v>5437.8</v>
       </c>
       <c r="E179" t="n">
-        <v>-284.12</v>
+        <v>-127.8</v>
       </c>
       <c r="F179" t="n">
-        <v>5934</v>
+        <v>5370</v>
       </c>
       <c r="G179" t="n">
-        <v>5955.1</v>
+        <v>5425.47</v>
       </c>
       <c r="H179" t="n">
-        <v>-21.1</v>
+        <v>-55.47</v>
       </c>
       <c r="I179" t="n">
-        <v>5802</v>
+        <v>5310</v>
       </c>
       <c r="J179" t="n">
-        <v>5680.44</v>
+        <v>5260.2</v>
       </c>
       <c r="K179" t="n">
-        <v>121.56</v>
+        <v>49.8</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>4.63</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="180">
@@ -20950,35 +20950,35 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PGEL (AUG-2026 FUT)</t>
+          <t>DIXON (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>615</v>
+        <v>14130</v>
       </c>
       <c r="D180" t="n">
-        <v>605.66</v>
+        <v>14757.57</v>
       </c>
       <c r="E180" t="n">
-        <v>9.34</v>
+        <v>-627.5700000000001</v>
       </c>
       <c r="F180" t="n">
-        <v>615.3</v>
+        <v>14209</v>
       </c>
       <c r="G180" t="n">
-        <v>625.39</v>
+        <v>14497.77</v>
       </c>
       <c r="H180" t="n">
-        <v>-10.09</v>
+        <v>-288.77</v>
       </c>
       <c r="I180" t="n">
-        <v>603</v>
+        <v>13999</v>
       </c>
       <c r="J180" t="n">
-        <v>584.17</v>
+        <v>13951.29</v>
       </c>
       <c r="K180" t="n">
-        <v>18.83</v>
+        <v>47.71</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -20987,11 +20987,11 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>1.54</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="181">
@@ -21002,35 +21002,35 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EICHERMOT (AUG-2026 FUT)</t>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>8100</v>
+        <v>1240</v>
       </c>
       <c r="D181" t="n">
-        <v>8213.74</v>
+        <v>1293.25</v>
       </c>
       <c r="E181" t="n">
-        <v>-113.74</v>
+        <v>-53.25</v>
       </c>
       <c r="F181" t="n">
-        <v>8100</v>
+        <v>1246.9</v>
       </c>
       <c r="G181" t="n">
-        <v>8234.459999999999</v>
+        <v>1270.98</v>
       </c>
       <c r="H181" t="n">
-        <v>-134.46</v>
+        <v>-24.08</v>
       </c>
       <c r="I181" t="n">
-        <v>8011</v>
+        <v>1230.1</v>
       </c>
       <c r="J181" t="n">
-        <v>7960.64</v>
+        <v>1225.29</v>
       </c>
       <c r="K181" t="n">
-        <v>50.36</v>
+        <v>4.81</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -21039,11 +21039,11 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1.38</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="182">
@@ -21054,35 +21054,35 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DIXON (AUG-2026 FUT)</t>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>14035</v>
+        <v>171.64</v>
       </c>
       <c r="D182" t="n">
-        <v>14288.94</v>
+        <v>180.55</v>
       </c>
       <c r="E182" t="n">
-        <v>-253.94</v>
+        <v>-8.91</v>
       </c>
       <c r="F182" t="n">
-        <v>14065</v>
+        <v>179.5</v>
       </c>
       <c r="G182" t="n">
-        <v>14564.62</v>
+        <v>176.29</v>
       </c>
       <c r="H182" t="n">
-        <v>-499.62</v>
+        <v>3.21</v>
       </c>
       <c r="I182" t="n">
-        <v>13645</v>
+        <v>169.75</v>
       </c>
       <c r="J182" t="n">
-        <v>13838.77</v>
+        <v>169.32</v>
       </c>
       <c r="K182" t="n">
-        <v>-193.77</v>
+        <v>0.43</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1.78</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="183">
@@ -21106,35 +21106,35 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>INDIGO (AUG-2026 FUT)</t>
+          <t>PGEL (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5370</v>
+        <v>601</v>
       </c>
       <c r="D183" t="n">
-        <v>5527.49</v>
+        <v>661.83</v>
       </c>
       <c r="E183" t="n">
-        <v>-157.49</v>
+        <v>-60.83</v>
       </c>
       <c r="F183" t="n">
-        <v>5370</v>
+        <v>615.9</v>
       </c>
       <c r="G183" t="n">
-        <v>5450.48</v>
+        <v>622.52</v>
       </c>
       <c r="H183" t="n">
-        <v>-80.48</v>
+        <v>-6.62</v>
       </c>
       <c r="I183" t="n">
-        <v>5281.5</v>
+        <v>599.5</v>
       </c>
       <c r="J183" t="n">
-        <v>5217.77</v>
+        <v>588.92</v>
       </c>
       <c r="K183" t="n">
-        <v>63.73</v>
+        <v>10.58</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>2.85</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="184">
@@ -21158,35 +21158,35 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ASHOKLEY (AUG-2026 FUT)</t>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>176.23</v>
+        <v>376</v>
       </c>
       <c r="D184" t="n">
-        <v>178.54</v>
+        <v>390.9</v>
       </c>
       <c r="E184" t="n">
-        <v>-2.31</v>
+        <v>-14.9</v>
       </c>
       <c r="F184" t="n">
-        <v>182.7</v>
+        <v>384.95</v>
       </c>
       <c r="G184" t="n">
-        <v>177.11</v>
+        <v>388.57</v>
       </c>
       <c r="H184" t="n">
-        <v>5.59</v>
+        <v>-3.62</v>
       </c>
       <c r="I184" t="n">
-        <v>176.23</v>
+        <v>375</v>
       </c>
       <c r="J184" t="n">
-        <v>167.96</v>
+        <v>369.13</v>
       </c>
       <c r="K184" t="n">
-        <v>8.27</v>
+        <v>5.87</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -21195,11 +21195,11 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.29</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="185">
@@ -21210,35 +21210,35 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NATIONALUM (AUG-2026 FUT)</t>
+          <t>ABB (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>400.5</v>
+        <v>7649</v>
       </c>
       <c r="D185" t="n">
-        <v>415.79</v>
+        <v>7841.27</v>
       </c>
       <c r="E185" t="n">
-        <v>-15.29</v>
+        <v>-192.27</v>
       </c>
       <c r="F185" t="n">
-        <v>413.65</v>
+        <v>7825</v>
       </c>
       <c r="G185" t="n">
-        <v>390.36</v>
+        <v>7844.27</v>
       </c>
       <c r="H185" t="n">
-        <v>23.29</v>
+        <v>-19.27</v>
       </c>
       <c r="I185" t="n">
-        <v>400</v>
+        <v>7639</v>
       </c>
       <c r="J185" t="n">
-        <v>366.15</v>
+        <v>7555.18</v>
       </c>
       <c r="K185" t="n">
-        <v>33.85</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="186">
@@ -21262,35 +21262,35 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ABB (AUG-2026 FUT)</t>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>7710</v>
+        <v>11475</v>
       </c>
       <c r="D186" t="n">
-        <v>7989.01</v>
+        <v>11710.61</v>
       </c>
       <c r="E186" t="n">
-        <v>-279.01</v>
+        <v>-235.61</v>
       </c>
       <c r="F186" t="n">
-        <v>7772</v>
+        <v>11541</v>
       </c>
       <c r="G186" t="n">
-        <v>7880.44</v>
+        <v>11673.66</v>
       </c>
       <c r="H186" t="n">
-        <v>-108.44</v>
+        <v>-132.66</v>
       </c>
       <c r="I186" t="n">
-        <v>7659</v>
+        <v>11387</v>
       </c>
       <c r="J186" t="n">
-        <v>7494.24</v>
+        <v>11406.2</v>
       </c>
       <c r="K186" t="n">
-        <v>164.76</v>
+        <v>-19.2</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -21299,11 +21299,11 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>3.49</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="187">
@@ -21314,35 +21314,35 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HYUNDAI (AUG-2026 FUT)</t>
+          <t>COFORGE (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2237.1</v>
+        <v>1812</v>
       </c>
       <c r="D187" t="n">
-        <v>2295.05</v>
+        <v>1884.34</v>
       </c>
       <c r="E187" t="n">
-        <v>-57.95</v>
+        <v>-72.34</v>
       </c>
       <c r="F187" t="n">
-        <v>2273.9</v>
+        <v>1836.4</v>
       </c>
       <c r="G187" t="n">
-        <v>2263.23</v>
+        <v>1870.41</v>
       </c>
       <c r="H187" t="n">
-        <v>10.67</v>
+        <v>-34.01</v>
       </c>
       <c r="I187" t="n">
-        <v>2219.5</v>
+        <v>1804.2</v>
       </c>
       <c r="J187" t="n">
-        <v>2156.24</v>
+        <v>1780.5</v>
       </c>
       <c r="K187" t="n">
-        <v>63.26</v>
+        <v>23.7</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -21351,11 +21351,11 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N187" t="n">
-        <v>2.52</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="188">
@@ -21366,35 +21366,35 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>COFORGE (AUG-2026 FUT)</t>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1829</v>
+        <v>2199</v>
       </c>
       <c r="D188" t="n">
-        <v>1893.76</v>
+        <v>2272.07</v>
       </c>
       <c r="E188" t="n">
-        <v>-64.76000000000001</v>
+        <v>-73.06999999999999</v>
       </c>
       <c r="F188" t="n">
-        <v>1829.9</v>
+        <v>2255</v>
       </c>
       <c r="G188" t="n">
-        <v>1879.03</v>
+        <v>2252.84</v>
       </c>
       <c r="H188" t="n">
-        <v>-49.13</v>
+        <v>2.16</v>
       </c>
       <c r="I188" t="n">
-        <v>1788</v>
+        <v>2191.6</v>
       </c>
       <c r="J188" t="n">
-        <v>1766.13</v>
+        <v>2173.78</v>
       </c>
       <c r="K188" t="n">
-        <v>21.87</v>
+        <v>17.82</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -21403,11 +21403,11 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N188" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="189">
@@ -21422,31 +21422,31 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1046.25</v>
+        <v>1029.5</v>
       </c>
       <c r="D189" t="n">
-        <v>1107.55</v>
+        <v>1028.21</v>
       </c>
       <c r="E189" t="n">
-        <v>-61.3</v>
+        <v>1.29</v>
       </c>
       <c r="F189" t="n">
-        <v>1073</v>
+        <v>1036.8</v>
       </c>
       <c r="G189" t="n">
-        <v>1058.28</v>
+        <v>1053.41</v>
       </c>
       <c r="H189" t="n">
-        <v>14.72</v>
+        <v>-16.61</v>
       </c>
       <c r="I189" t="n">
-        <v>1040</v>
+        <v>1021.35</v>
       </c>
       <c r="J189" t="n">
-        <v>1010.46</v>
+        <v>1018.68</v>
       </c>
       <c r="K189" t="n">
-        <v>29.54</v>
+        <v>2.67</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -21455,11 +21455,11 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N189" t="n">
-        <v>5.53</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="190">
@@ -21470,35 +21470,35 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAUKRI (AUG-2026 FUT)</t>
+          <t>LT (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1357.3</v>
+        <v>4057</v>
       </c>
       <c r="D190" t="n">
-        <v>1387.17</v>
+        <v>4159.32</v>
       </c>
       <c r="E190" t="n">
-        <v>-29.87</v>
+        <v>-102.32</v>
       </c>
       <c r="F190" t="n">
-        <v>1369.4</v>
+        <v>4072.5</v>
       </c>
       <c r="G190" t="n">
-        <v>1392.93</v>
+        <v>4108.51</v>
       </c>
       <c r="H190" t="n">
-        <v>-23.53</v>
+        <v>-36.01</v>
       </c>
       <c r="I190" t="n">
-        <v>1336.5</v>
+        <v>4033.1</v>
       </c>
       <c r="J190" t="n">
-        <v>1308.81</v>
+        <v>4046.97</v>
       </c>
       <c r="K190" t="n">
-        <v>27.69</v>
+        <v>-13.87</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="191">
@@ -21522,35 +21522,35 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LT (AUG-2026 FUT)</t>
+          <t>PETRONET (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>4070.7</v>
+        <v>282.6</v>
       </c>
       <c r="D191" t="n">
-        <v>4104.58</v>
+        <v>284.5</v>
       </c>
       <c r="E191" t="n">
-        <v>-33.88</v>
+        <v>-1.9</v>
       </c>
       <c r="F191" t="n">
-        <v>4070.7</v>
+        <v>283.5</v>
       </c>
       <c r="G191" t="n">
-        <v>4127.47</v>
+        <v>288.36</v>
       </c>
       <c r="H191" t="n">
-        <v>-56.77</v>
+        <v>-4.86</v>
       </c>
       <c r="I191" t="n">
-        <v>3990</v>
+        <v>277.15</v>
       </c>
       <c r="J191" t="n">
-        <v>4014.32</v>
+        <v>280.23</v>
       </c>
       <c r="K191" t="n">
-        <v>-24.32</v>
+        <v>-3.08</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="192">
@@ -21574,35 +21574,35 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PETRONET (AUG-2026 FUT)</t>
+          <t>CONCOR (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>279.3</v>
+        <v>527</v>
       </c>
       <c r="D192" t="n">
-        <v>291.64</v>
+        <v>579.3099999999999</v>
       </c>
       <c r="E192" t="n">
-        <v>-12.34</v>
+        <v>-52.31</v>
       </c>
       <c r="F192" t="n">
-        <v>287.4</v>
+        <v>543.7</v>
       </c>
       <c r="G192" t="n">
-        <v>289.69</v>
+        <v>541.0700000000001</v>
       </c>
       <c r="H192" t="n">
-        <v>-2.29</v>
+        <v>2.63</v>
       </c>
       <c r="I192" t="n">
-        <v>273</v>
+        <v>527</v>
       </c>
       <c r="J192" t="n">
-        <v>277.97</v>
+        <v>520.0599999999999</v>
       </c>
       <c r="K192" t="n">
-        <v>-4.97</v>
+        <v>6.94</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>4.23</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="193">
@@ -21626,35 +21626,35 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CONCOR (AUG-2026 FUT)</t>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>533.65</v>
+        <v>2008.3</v>
       </c>
       <c r="D193" t="n">
-        <v>517.03</v>
+        <v>2037.88</v>
       </c>
       <c r="E193" t="n">
-        <v>16.62</v>
+        <v>-29.58</v>
       </c>
       <c r="F193" t="n">
-        <v>535.5</v>
+        <v>2033.6</v>
       </c>
       <c r="G193" t="n">
-        <v>543.71</v>
+        <v>2055.3</v>
       </c>
       <c r="H193" t="n">
-        <v>-8.210000000000001</v>
+        <v>-21.7</v>
       </c>
       <c r="I193" t="n">
-        <v>513.7</v>
+        <v>2006.6</v>
       </c>
       <c r="J193" t="n">
-        <v>515.76</v>
+        <v>1986.91</v>
       </c>
       <c r="K193" t="n">
-        <v>-2.06</v>
+        <v>19.69</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>3.21</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="194">
@@ -21678,35 +21678,35 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+          <t>NAUKRI (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2025</v>
+        <v>1343</v>
       </c>
       <c r="D194" t="n">
-        <v>2110.23</v>
+        <v>1416.19</v>
       </c>
       <c r="E194" t="n">
-        <v>-85.23</v>
+        <v>-73.19</v>
       </c>
       <c r="F194" t="n">
-        <v>2038</v>
+        <v>1367.1</v>
       </c>
       <c r="G194" t="n">
-        <v>2064.37</v>
+        <v>1387.22</v>
       </c>
       <c r="H194" t="n">
-        <v>-26.37</v>
+        <v>-20.12</v>
       </c>
       <c r="I194" t="n">
-        <v>2006.7</v>
+        <v>1337</v>
       </c>
       <c r="J194" t="n">
-        <v>1971.21</v>
+        <v>1318.94</v>
       </c>
       <c r="K194" t="n">
-        <v>35.49</v>
+        <v>18.06</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>4.04</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="195">
@@ -21734,31 +21734,31 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1458.8</v>
+        <v>1450</v>
       </c>
       <c r="D195" t="n">
-        <v>1497.51</v>
+        <v>1466.44</v>
       </c>
       <c r="E195" t="n">
-        <v>-38.71</v>
+        <v>-16.44</v>
       </c>
       <c r="F195" t="n">
-        <v>1464.4</v>
+        <v>1474.3</v>
       </c>
       <c r="G195" t="n">
-        <v>1479.52</v>
+        <v>1468.76</v>
       </c>
       <c r="H195" t="n">
-        <v>-15.12</v>
+        <v>5.54</v>
       </c>
       <c r="I195" t="n">
-        <v>1456.2</v>
+        <v>1449.2</v>
       </c>
       <c r="J195" t="n">
-        <v>1431.47</v>
+        <v>1446.14</v>
       </c>
       <c r="K195" t="n">
-        <v>24.73</v>
+        <v>3.06</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -21767,11 +21767,11 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N195" t="n">
-        <v>2.58</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="196">
@@ -21786,31 +21786,31 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="D196" t="n">
-        <v>1225.54</v>
+        <v>1213.03</v>
       </c>
       <c r="E196" t="n">
-        <v>-42.54</v>
+        <v>-33.03</v>
       </c>
       <c r="F196" t="n">
-        <v>1184.9</v>
+        <v>1191.5</v>
       </c>
       <c r="G196" t="n">
-        <v>1217.2</v>
+        <v>1211.62</v>
       </c>
       <c r="H196" t="n">
-        <v>-32.3</v>
+        <v>-20.12</v>
       </c>
       <c r="I196" t="n">
-        <v>1149.2</v>
+        <v>1167</v>
       </c>
       <c r="J196" t="n">
-        <v>1154.99</v>
+        <v>1164.39</v>
       </c>
       <c r="K196" t="n">
-        <v>-5.79</v>
+        <v>2.61</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>3.47</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="197">
@@ -21838,31 +21838,31 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>897</v>
+        <v>894.95</v>
       </c>
       <c r="D197" t="n">
-        <v>929.49</v>
+        <v>904.34</v>
       </c>
       <c r="E197" t="n">
-        <v>-32.49</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="F197" t="n">
-        <v>903.8</v>
+        <v>902.8</v>
       </c>
       <c r="G197" t="n">
-        <v>915.6900000000001</v>
+        <v>911.49</v>
       </c>
       <c r="H197" t="n">
-        <v>-11.89</v>
+        <v>-8.69</v>
       </c>
       <c r="I197" t="n">
-        <v>883.15</v>
+        <v>885.3</v>
       </c>
       <c r="J197" t="n">
-        <v>881.61</v>
+        <v>888.78</v>
       </c>
       <c r="K197" t="n">
-        <v>1.54</v>
+        <v>-3.48</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -21871,11 +21871,11 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N197" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -9446,31 +9446,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>187.38</v>
+        <v>186.5</v>
       </c>
       <c r="D174" t="n">
         <v>186.39</v>
       </c>
       <c r="E174" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="F174" t="n">
-        <v>189.34</v>
+        <v>188.7</v>
       </c>
       <c r="G174" t="n">
         <v>192.11</v>
       </c>
       <c r="H174" t="n">
-        <v>-2.77</v>
+        <v>-3.41</v>
       </c>
       <c r="I174" t="n">
-        <v>186.39</v>
+        <v>185.32</v>
       </c>
       <c r="J174" t="n">
         <v>187.38</v>
       </c>
       <c r="K174" t="n">
-        <v>-0.99</v>
+        <v>-2.06</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="175">
@@ -9498,31 +9498,31 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5790</v>
+        <v>5850</v>
       </c>
       <c r="D175" t="n">
         <v>5704.13</v>
       </c>
       <c r="E175" t="n">
-        <v>85.87</v>
+        <v>145.87</v>
       </c>
       <c r="F175" t="n">
-        <v>5849</v>
+        <v>5934</v>
       </c>
       <c r="G175" t="n">
         <v>5841.09</v>
       </c>
       <c r="H175" t="n">
-        <v>7.91</v>
+        <v>92.91</v>
       </c>
       <c r="I175" t="n">
-        <v>5765</v>
+        <v>5802</v>
       </c>
       <c r="J175" t="n">
         <v>5738.86</v>
       </c>
       <c r="K175" t="n">
-        <v>26.14</v>
+        <v>63.14</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="176">
@@ -9862,31 +9862,31 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>376</v>
+        <v>400.5</v>
       </c>
       <c r="D182" t="n">
         <v>377.79</v>
       </c>
       <c r="E182" t="n">
-        <v>-1.79</v>
+        <v>22.71</v>
       </c>
       <c r="F182" t="n">
-        <v>384.95</v>
+        <v>413.65</v>
       </c>
       <c r="G182" t="n">
         <v>377.79</v>
       </c>
       <c r="H182" t="n">
-        <v>7.16</v>
+        <v>35.86</v>
       </c>
       <c r="I182" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="J182" t="n">
         <v>364.69</v>
       </c>
       <c r="K182" t="n">
-        <v>10.31</v>
+        <v>35.31</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9895,11 +9895,11 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="183">
@@ -9914,31 +9914,31 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>7649</v>
+        <v>7710</v>
       </c>
       <c r="D183" t="n">
         <v>7639.02</v>
       </c>
       <c r="E183" t="n">
-        <v>9.98</v>
+        <v>70.98</v>
       </c>
       <c r="F183" t="n">
-        <v>7825</v>
+        <v>7772</v>
       </c>
       <c r="G183" t="n">
         <v>7758.82</v>
       </c>
       <c r="H183" t="n">
-        <v>66.18000000000001</v>
+        <v>13.18</v>
       </c>
       <c r="I183" t="n">
-        <v>7639</v>
+        <v>7659</v>
       </c>
       <c r="J183" t="n">
         <v>7624.51</v>
       </c>
       <c r="K183" t="n">
-        <v>14.49</v>
+        <v>34.49</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0.13</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="184">
@@ -10018,31 +10018,31 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D185" t="n">
         <v>1823.32</v>
       </c>
       <c r="E185" t="n">
-        <v>-11.32</v>
+        <v>5.68</v>
       </c>
       <c r="F185" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G185" t="n">
         <v>1823.32</v>
       </c>
       <c r="H185" t="n">
-        <v>13.08</v>
+        <v>6.58</v>
       </c>
       <c r="I185" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J185" t="n">
         <v>1772.18</v>
       </c>
       <c r="K185" t="n">
-        <v>32.02</v>
+        <v>15.82</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="186">
@@ -20642,31 +20642,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>187.38</v>
+        <v>186.5</v>
       </c>
       <c r="D174" t="n">
         <v>189.68</v>
       </c>
       <c r="E174" t="n">
-        <v>-2.3</v>
+        <v>-3.18</v>
       </c>
       <c r="F174" t="n">
-        <v>189.34</v>
+        <v>188.7</v>
       </c>
       <c r="G174" t="n">
         <v>191.5</v>
       </c>
       <c r="H174" t="n">
-        <v>-2.16</v>
+        <v>-2.8</v>
       </c>
       <c r="I174" t="n">
-        <v>186.39</v>
+        <v>185.32</v>
       </c>
       <c r="J174" t="n">
         <v>185.59</v>
       </c>
       <c r="K174" t="n">
-        <v>0.8</v>
+        <v>-0.27</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>1.21</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="175">
@@ -20746,31 +20746,31 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5790</v>
+        <v>5850</v>
       </c>
       <c r="D176" t="n">
         <v>5844.85</v>
       </c>
       <c r="E176" t="n">
-        <v>-54.85</v>
+        <v>5.15</v>
       </c>
       <c r="F176" t="n">
-        <v>5849</v>
+        <v>5934</v>
       </c>
       <c r="G176" t="n">
         <v>5927.77</v>
       </c>
       <c r="H176" t="n">
-        <v>-78.77</v>
+        <v>6.23</v>
       </c>
       <c r="I176" t="n">
-        <v>5765</v>
+        <v>5802</v>
       </c>
       <c r="J176" t="n">
         <v>5726.64</v>
       </c>
       <c r="K176" t="n">
-        <v>38.36</v>
+        <v>75.36</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="177">
@@ -21162,31 +21162,31 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>376</v>
+        <v>400.5</v>
       </c>
       <c r="D184" t="n">
         <v>390.9</v>
       </c>
       <c r="E184" t="n">
-        <v>-14.9</v>
+        <v>9.6</v>
       </c>
       <c r="F184" t="n">
-        <v>384.95</v>
+        <v>413.65</v>
       </c>
       <c r="G184" t="n">
         <v>388.57</v>
       </c>
       <c r="H184" t="n">
-        <v>-3.62</v>
+        <v>25.08</v>
       </c>
       <c r="I184" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="J184" t="n">
         <v>369.13</v>
       </c>
       <c r="K184" t="n">
-        <v>5.87</v>
+        <v>30.87</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -21195,11 +21195,11 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.81</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="185">
@@ -21214,31 +21214,31 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7649</v>
+        <v>7710</v>
       </c>
       <c r="D185" t="n">
         <v>7841.27</v>
       </c>
       <c r="E185" t="n">
-        <v>-192.27</v>
+        <v>-131.27</v>
       </c>
       <c r="F185" t="n">
-        <v>7825</v>
+        <v>7772</v>
       </c>
       <c r="G185" t="n">
         <v>7844.27</v>
       </c>
       <c r="H185" t="n">
-        <v>-19.27</v>
+        <v>-72.27</v>
       </c>
       <c r="I185" t="n">
-        <v>7639</v>
+        <v>7659</v>
       </c>
       <c r="J185" t="n">
         <v>7555.18</v>
       </c>
       <c r="K185" t="n">
-        <v>83.81999999999999</v>
+        <v>103.82</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="186">
@@ -21318,31 +21318,31 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1812</v>
+        <v>1829</v>
       </c>
       <c r="D187" t="n">
         <v>1884.34</v>
       </c>
       <c r="E187" t="n">
-        <v>-72.34</v>
+        <v>-55.34</v>
       </c>
       <c r="F187" t="n">
-        <v>1836.4</v>
+        <v>1829.9</v>
       </c>
       <c r="G187" t="n">
         <v>1870.41</v>
       </c>
       <c r="H187" t="n">
-        <v>-34.01</v>
+        <v>-40.51</v>
       </c>
       <c r="I187" t="n">
-        <v>1804.2</v>
+        <v>1788</v>
       </c>
       <c r="J187" t="n">
         <v>1780.5</v>
       </c>
       <c r="K187" t="n">
-        <v>23.7</v>
+        <v>7.5</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>3.84</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="188">

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N197"/>
+  <dimension ref="A1:N227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10680,6 +10680,1566 @@
       </c>
       <c r="N197" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="D198" t="n">
+        <v>190.94</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F198" t="n">
+        <v>190.15</v>
+      </c>
+      <c r="G198" t="n">
+        <v>193.61</v>
+      </c>
+      <c r="H198" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="I198" t="n">
+        <v>184.27</v>
+      </c>
+      <c r="J198" t="n">
+        <v>188.62</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>174.54</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F199" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>181.19</v>
+      </c>
+      <c r="H199" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I199" t="n">
+        <v>171.98</v>
+      </c>
+      <c r="J199" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="K199" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D200" t="n">
+        <v>7793.01</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-133.01</v>
+      </c>
+      <c r="F200" t="n">
+        <v>7760</v>
+      </c>
+      <c r="G200" t="n">
+        <v>7793.01</v>
+      </c>
+      <c r="H200" t="n">
+        <v>-33.01</v>
+      </c>
+      <c r="I200" t="n">
+        <v>7627</v>
+      </c>
+      <c r="J200" t="n">
+        <v>7557.5</v>
+      </c>
+      <c r="K200" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>5745</v>
+      </c>
+      <c r="D201" t="n">
+        <v>5939.03</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-194.03</v>
+      </c>
+      <c r="F201" t="n">
+        <v>5811.5</v>
+      </c>
+      <c r="G201" t="n">
+        <v>5939.03</v>
+      </c>
+      <c r="H201" t="n">
+        <v>-127.53</v>
+      </c>
+      <c r="I201" t="n">
+        <v>5740</v>
+      </c>
+      <c r="J201" t="n">
+        <v>5644.95</v>
+      </c>
+      <c r="K201" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1061.2</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1065.06</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1068.8</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1079.14</v>
+      </c>
+      <c r="H202" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1052.4</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1051.01</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1049.9</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1085.14</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-35.24</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1085.14</v>
+      </c>
+      <c r="H203" t="n">
+        <v>-25.14</v>
+      </c>
+      <c r="I203" t="n">
+        <v>1032.7</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1045.02</v>
+      </c>
+      <c r="K203" t="n">
+        <v>-12.32</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>5570</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5474.57</v>
+      </c>
+      <c r="E204" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="F204" t="n">
+        <v>5613</v>
+      </c>
+      <c r="G204" t="n">
+        <v>5703.39</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-90.39</v>
+      </c>
+      <c r="I204" t="n">
+        <v>5520</v>
+      </c>
+      <c r="J204" t="n">
+        <v>5556.07</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-36.07</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1269.9</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1259.16</v>
+      </c>
+      <c r="E205" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1263.84</v>
+      </c>
+      <c r="H205" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1237.57</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>117.32</v>
+      </c>
+      <c r="D206" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="F206" t="n">
+        <v>118.06</v>
+      </c>
+      <c r="G206" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I206" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="J206" t="n">
+        <v>115.36</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="D207" t="n">
+        <v>414.13</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-26.58</v>
+      </c>
+      <c r="F207" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="G207" t="n">
+        <v>414.13</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-22.63</v>
+      </c>
+      <c r="I207" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J207" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="K207" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1355.8</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1340.33</v>
+      </c>
+      <c r="E208" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1374</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1351.8</v>
+      </c>
+      <c r="H208" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1340.7</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1315.63</v>
+      </c>
+      <c r="K208" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>11789</v>
+      </c>
+      <c r="D209" t="n">
+        <v>12122.16</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-333.16</v>
+      </c>
+      <c r="F209" t="n">
+        <v>11920</v>
+      </c>
+      <c r="G209" t="n">
+        <v>12122.16</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-202.16</v>
+      </c>
+      <c r="I209" t="n">
+        <v>11742</v>
+      </c>
+      <c r="J209" t="n">
+        <v>11614.72</v>
+      </c>
+      <c r="K209" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>4086.7</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4066.74</v>
+      </c>
+      <c r="E210" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="F210" t="n">
+        <v>4086.7</v>
+      </c>
+      <c r="G210" t="n">
+        <v>4131.85</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-45.15</v>
+      </c>
+      <c r="I210" t="n">
+        <v>4026</v>
+      </c>
+      <c r="J210" t="n">
+        <v>4025.37</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>614</v>
+      </c>
+      <c r="D211" t="n">
+        <v>582.91</v>
+      </c>
+      <c r="E211" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="F211" t="n">
+        <v>614</v>
+      </c>
+      <c r="G211" t="n">
+        <v>619.24</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I211" t="n">
+        <v>594.25</v>
+      </c>
+      <c r="J211" t="n">
+        <v>602.92</v>
+      </c>
+      <c r="K211" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>318</v>
+      </c>
+      <c r="D212" t="n">
+        <v>301.01</v>
+      </c>
+      <c r="E212" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F212" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="G212" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="H212" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I212" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="J212" t="n">
+        <v>316.79</v>
+      </c>
+      <c r="K212" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>5275.5</v>
+      </c>
+      <c r="D213" t="n">
+        <v>5309.72</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-34.22</v>
+      </c>
+      <c r="F213" t="n">
+        <v>5332.5</v>
+      </c>
+      <c r="G213" t="n">
+        <v>5386.06</v>
+      </c>
+      <c r="H213" t="n">
+        <v>-53.56</v>
+      </c>
+      <c r="I213" t="n">
+        <v>5262.5</v>
+      </c>
+      <c r="J213" t="n">
+        <v>5246.39</v>
+      </c>
+      <c r="K213" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1806</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1826.13</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-20.13</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1821</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1826.13</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1799.6</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1760.55</v>
+      </c>
+      <c r="K214" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>11379</v>
+      </c>
+      <c r="D215" t="n">
+        <v>11440.67</v>
+      </c>
+      <c r="E215" t="n">
+        <v>-61.67</v>
+      </c>
+      <c r="F215" t="n">
+        <v>11574</v>
+      </c>
+      <c r="G215" t="n">
+        <v>11488.9</v>
+      </c>
+      <c r="H215" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="I215" t="n">
+        <v>11306</v>
+      </c>
+      <c r="J215" t="n">
+        <v>11186.56</v>
+      </c>
+      <c r="K215" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1590.94</v>
+      </c>
+      <c r="E216" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1638.9</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1638.15</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1604.2</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1595.48</v>
+      </c>
+      <c r="K216" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2081.3</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2065.98</v>
+      </c>
+      <c r="E217" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2110.9</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2081.91</v>
+      </c>
+      <c r="H217" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="I217" t="n">
+        <v>2072.4</v>
+      </c>
+      <c r="J217" t="n">
+        <v>2026.46</v>
+      </c>
+      <c r="K217" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2190.76</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2209.6</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2190.76</v>
+      </c>
+      <c r="H218" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="I218" t="n">
+        <v>2172.4</v>
+      </c>
+      <c r="J218" t="n">
+        <v>2128.63</v>
+      </c>
+      <c r="K218" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>955</v>
+      </c>
+      <c r="D219" t="n">
+        <v>947.97</v>
+      </c>
+      <c r="E219" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="F219" t="n">
+        <v>964</v>
+      </c>
+      <c r="G219" t="n">
+        <v>947.97</v>
+      </c>
+      <c r="H219" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="I219" t="n">
+        <v>897.1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>933.12</v>
+      </c>
+      <c r="K219" t="n">
+        <v>-36.02</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2040.02</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-35.02</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2028.2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2040.02</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1997.2</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1953.72</v>
+      </c>
+      <c r="K220" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>3390.4</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3292.1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F221" t="n">
+        <v>3451.9</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3292.1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="I221" t="n">
+        <v>3388.3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3305.46</v>
+      </c>
+      <c r="K221" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1182.16</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1174.7</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I222" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1153.24</v>
+      </c>
+      <c r="K222" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1969.3</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2058.58</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-89.28</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1993.2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>2058.58</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-65.38</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1969.3</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1956.69</v>
+      </c>
+      <c r="K223" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>14025</v>
+      </c>
+      <c r="D224" t="n">
+        <v>13901.39</v>
+      </c>
+      <c r="E224" t="n">
+        <v>123.61</v>
+      </c>
+      <c r="F224" t="n">
+        <v>14287</v>
+      </c>
+      <c r="G224" t="n">
+        <v>13901.39</v>
+      </c>
+      <c r="H224" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="I224" t="n">
+        <v>14025</v>
+      </c>
+      <c r="J224" t="n">
+        <v>13622.58</v>
+      </c>
+      <c r="K224" t="n">
+        <v>402.42</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="D225" t="n">
+        <v>288.11</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="F225" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="G225" t="n">
+        <v>288.11</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="I225" t="n">
+        <v>281.65</v>
+      </c>
+      <c r="J225" t="n">
+        <v>275.07</v>
+      </c>
+      <c r="K225" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="D226" t="n">
+        <v>494.28</v>
+      </c>
+      <c r="E226" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="F226" t="n">
+        <v>530</v>
+      </c>
+      <c r="G226" t="n">
+        <v>512.17</v>
+      </c>
+      <c r="H226" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="I226" t="n">
+        <v>518.3</v>
+      </c>
+      <c r="J226" t="n">
+        <v>508.18</v>
+      </c>
+      <c r="K226" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>881.2</v>
+      </c>
+      <c r="D227" t="n">
+        <v>895.84</v>
+      </c>
+      <c r="E227" t="n">
+        <v>-14.64</v>
+      </c>
+      <c r="F227" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="G227" t="n">
+        <v>895.84</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="I227" t="n">
+        <v>870.3</v>
+      </c>
+      <c r="J227" t="n">
+        <v>870.1799999999999</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -10693,7 +12253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11597,6 +13157,110 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>24287.65</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24287.65</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24360.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24356.19</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="I18" t="n">
+        <v>24226.95</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24223.04</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>57497.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57497.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>57757.25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>57796.84</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-39.59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>57119.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>57159.19</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-39.59</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11611,7 +13275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N197"/>
+  <dimension ref="A1:N227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21878,6 +23542,1566 @@
         <v>1.04</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>179.62</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="F198" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>182.59</v>
+      </c>
+      <c r="H198" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="I198" t="n">
+        <v>171.98</v>
+      </c>
+      <c r="J198" t="n">
+        <v>173.32</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="D199" t="n">
+        <v>429.55</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-42</v>
+      </c>
+      <c r="F199" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="G199" t="n">
+        <v>402.43</v>
+      </c>
+      <c r="H199" t="n">
+        <v>-10.93</v>
+      </c>
+      <c r="I199" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J199" t="n">
+        <v>377.08</v>
+      </c>
+      <c r="K199" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>5745</v>
+      </c>
+      <c r="D200" t="n">
+        <v>6085.2</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-340.2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>5811.5</v>
+      </c>
+      <c r="G200" t="n">
+        <v>5895.89</v>
+      </c>
+      <c r="H200" t="n">
+        <v>-84.39</v>
+      </c>
+      <c r="I200" t="n">
+        <v>5740</v>
+      </c>
+      <c r="J200" t="n">
+        <v>5642.69</v>
+      </c>
+      <c r="K200" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="D201" t="n">
+        <v>194.67</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="F201" t="n">
+        <v>190.15</v>
+      </c>
+      <c r="G201" t="n">
+        <v>193.34</v>
+      </c>
+      <c r="H201" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="I201" t="n">
+        <v>184.27</v>
+      </c>
+      <c r="J201" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="K201" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1049.9</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1111.81</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-61.91</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1077.43</v>
+      </c>
+      <c r="H202" t="n">
+        <v>-17.43</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1032.7</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1031.23</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>5570</v>
+      </c>
+      <c r="D203" t="n">
+        <v>5638.08</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-68.08</v>
+      </c>
+      <c r="F203" t="n">
+        <v>5613</v>
+      </c>
+      <c r="G203" t="n">
+        <v>5751.2</v>
+      </c>
+      <c r="H203" t="n">
+        <v>-138.2</v>
+      </c>
+      <c r="I203" t="n">
+        <v>5520</v>
+      </c>
+      <c r="J203" t="n">
+        <v>5444.4</v>
+      </c>
+      <c r="K203" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1269.9</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1288.32</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-18.42</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1301.48</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-29.48</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1248.61</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-12.71</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PGEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>614</v>
+      </c>
+      <c r="D205" t="n">
+        <v>604.05</v>
+      </c>
+      <c r="E205" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F205" t="n">
+        <v>614</v>
+      </c>
+      <c r="G205" t="n">
+        <v>637.02</v>
+      </c>
+      <c r="H205" t="n">
+        <v>-23.02</v>
+      </c>
+      <c r="I205" t="n">
+        <v>594.25</v>
+      </c>
+      <c r="J205" t="n">
+        <v>597.86</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>117.32</v>
+      </c>
+      <c r="D206" t="n">
+        <v>124.07</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="F206" t="n">
+        <v>118.06</v>
+      </c>
+      <c r="G206" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="I206" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="J206" t="n">
+        <v>116.13</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>318</v>
+      </c>
+      <c r="D207" t="n">
+        <v>308.97</v>
+      </c>
+      <c r="E207" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="F207" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="G207" t="n">
+        <v>326.91</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="I207" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="J207" t="n">
+        <v>311.91</v>
+      </c>
+      <c r="K207" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1355.8</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1384.57</v>
+      </c>
+      <c r="E208" t="n">
+        <v>-28.77</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1374</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1402.38</v>
+      </c>
+      <c r="H208" t="n">
+        <v>-28.38</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1340.7</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1323.35</v>
+      </c>
+      <c r="K208" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OFSS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>11789</v>
+      </c>
+      <c r="D209" t="n">
+        <v>12484.66</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-695.66</v>
+      </c>
+      <c r="F209" t="n">
+        <v>11920</v>
+      </c>
+      <c r="G209" t="n">
+        <v>12158.68</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-238.68</v>
+      </c>
+      <c r="I209" t="n">
+        <v>11742</v>
+      </c>
+      <c r="J209" t="n">
+        <v>11533.65</v>
+      </c>
+      <c r="K209" t="n">
+        <v>208.35</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ABB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D210" t="n">
+        <v>7994.78</v>
+      </c>
+      <c r="E210" t="n">
+        <v>-334.78</v>
+      </c>
+      <c r="F210" t="n">
+        <v>7760</v>
+      </c>
+      <c r="G210" t="n">
+        <v>7870.62</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-110.62</v>
+      </c>
+      <c r="I210" t="n">
+        <v>7627</v>
+      </c>
+      <c r="J210" t="n">
+        <v>7516.46</v>
+      </c>
+      <c r="K210" t="n">
+        <v>110.54</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1061.2</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1084.84</v>
+      </c>
+      <c r="E211" t="n">
+        <v>-23.64</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1068.8</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1082.91</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-14.11</v>
+      </c>
+      <c r="I211" t="n">
+        <v>1052.4</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1046.96</v>
+      </c>
+      <c r="K211" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>4086.7</v>
+      </c>
+      <c r="D212" t="n">
+        <v>4117.2</v>
+      </c>
+      <c r="E212" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="F212" t="n">
+        <v>4086.7</v>
+      </c>
+      <c r="G212" t="n">
+        <v>4146.01</v>
+      </c>
+      <c r="H212" t="n">
+        <v>-59.31</v>
+      </c>
+      <c r="I212" t="n">
+        <v>4026</v>
+      </c>
+      <c r="J212" t="n">
+        <v>4050.24</v>
+      </c>
+      <c r="K212" t="n">
+        <v>-24.24</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1627.8</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1638.9</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1650.05</v>
+      </c>
+      <c r="H213" t="n">
+        <v>-11.15</v>
+      </c>
+      <c r="I213" t="n">
+        <v>1604.2</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1583.02</v>
+      </c>
+      <c r="K213" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2081.3</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2125.25</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-43.95</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2110.9</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2144.13</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-33.23</v>
+      </c>
+      <c r="I214" t="n">
+        <v>2072.4</v>
+      </c>
+      <c r="J214" t="n">
+        <v>2038.06</v>
+      </c>
+      <c r="K214" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>3390.4</v>
+      </c>
+      <c r="D215" t="n">
+        <v>3366.99</v>
+      </c>
+      <c r="E215" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F215" t="n">
+        <v>3451.9</v>
+      </c>
+      <c r="G215" t="n">
+        <v>3473.37</v>
+      </c>
+      <c r="H215" t="n">
+        <v>-21.47</v>
+      </c>
+      <c r="I215" t="n">
+        <v>3388.3</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3334.61</v>
+      </c>
+      <c r="K215" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>5275.5</v>
+      </c>
+      <c r="D216" t="n">
+        <v>5411.18</v>
+      </c>
+      <c r="E216" t="n">
+        <v>-135.68</v>
+      </c>
+      <c r="F216" t="n">
+        <v>5332.5</v>
+      </c>
+      <c r="G216" t="n">
+        <v>5386.11</v>
+      </c>
+      <c r="H216" t="n">
+        <v>-53.61</v>
+      </c>
+      <c r="I216" t="n">
+        <v>5262.5</v>
+      </c>
+      <c r="J216" t="n">
+        <v>5202.71</v>
+      </c>
+      <c r="K216" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>955</v>
+      </c>
+      <c r="D217" t="n">
+        <v>967.45</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-12.45</v>
+      </c>
+      <c r="F217" t="n">
+        <v>964</v>
+      </c>
+      <c r="G217" t="n">
+        <v>976.35</v>
+      </c>
+      <c r="H217" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="I217" t="n">
+        <v>897.1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>940.83</v>
+      </c>
+      <c r="K217" t="n">
+        <v>-43.73</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1806</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1886.93</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-80.93000000000001</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1821</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1868.53</v>
+      </c>
+      <c r="H218" t="n">
+        <v>-47.53</v>
+      </c>
+      <c r="I218" t="n">
+        <v>1799.6</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1762.42</v>
+      </c>
+      <c r="K218" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1969.3</v>
+      </c>
+      <c r="D219" t="n">
+        <v>2096.61</v>
+      </c>
+      <c r="E219" t="n">
+        <v>-127.31</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1993.2</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2009.39</v>
+      </c>
+      <c r="H219" t="n">
+        <v>-16.19</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1969.3</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1943.03</v>
+      </c>
+      <c r="K219" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>11379</v>
+      </c>
+      <c r="D220" t="n">
+        <v>11640.65</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-261.65</v>
+      </c>
+      <c r="F220" t="n">
+        <v>11574</v>
+      </c>
+      <c r="G220" t="n">
+        <v>11599.75</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-25.75</v>
+      </c>
+      <c r="I220" t="n">
+        <v>11306</v>
+      </c>
+      <c r="J220" t="n">
+        <v>11235.45</v>
+      </c>
+      <c r="K220" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D221" t="n">
+        <v>2248.02</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-58.02</v>
+      </c>
+      <c r="F221" t="n">
+        <v>2209.6</v>
+      </c>
+      <c r="G221" t="n">
+        <v>2250.73</v>
+      </c>
+      <c r="H221" t="n">
+        <v>-41.13</v>
+      </c>
+      <c r="I221" t="n">
+        <v>2172.4</v>
+      </c>
+      <c r="J221" t="n">
+        <v>2148.57</v>
+      </c>
+      <c r="K221" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2087.53</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-82.53</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2028.2</v>
+      </c>
+      <c r="G222" t="n">
+        <v>2055.1</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="I222" t="n">
+        <v>1997.2</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1971.22</v>
+      </c>
+      <c r="K222" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="D223" t="n">
+        <v>508.61</v>
+      </c>
+      <c r="E223" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="F223" t="n">
+        <v>530</v>
+      </c>
+      <c r="G223" t="n">
+        <v>540.49</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-10.49</v>
+      </c>
+      <c r="I223" t="n">
+        <v>518.3</v>
+      </c>
+      <c r="J223" t="n">
+        <v>513.48</v>
+      </c>
+      <c r="K223" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1213.99</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-40.99</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1174.7</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1206.42</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-31.72</v>
+      </c>
+      <c r="I224" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1150.14</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>14025</v>
+      </c>
+      <c r="D225" t="n">
+        <v>14269.8</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-244.8</v>
+      </c>
+      <c r="F225" t="n">
+        <v>14287</v>
+      </c>
+      <c r="G225" t="n">
+        <v>14418.88</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-131.88</v>
+      </c>
+      <c r="I225" t="n">
+        <v>14025</v>
+      </c>
+      <c r="J225" t="n">
+        <v>13755.95</v>
+      </c>
+      <c r="K225" t="n">
+        <v>269.05</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="D226" t="n">
+        <v>294.31</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-12.51</v>
+      </c>
+      <c r="F226" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="G226" t="n">
+        <v>288.36</v>
+      </c>
+      <c r="H226" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="I226" t="n">
+        <v>281.65</v>
+      </c>
+      <c r="J226" t="n">
+        <v>277.41</v>
+      </c>
+      <c r="K226" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>881.2</v>
+      </c>
+      <c r="D227" t="n">
+        <v>913.52</v>
+      </c>
+      <c r="E227" t="n">
+        <v>-32.32</v>
+      </c>
+      <c r="F227" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="G227" t="n">
+        <v>900.21</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I227" t="n">
+        <v>870.3</v>
+      </c>
+      <c r="J227" t="n">
+        <v>868.64</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -10694,31 +10694,31 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>188.9</v>
+        <v>187.38</v>
       </c>
       <c r="D198" t="n">
         <v>190.94</v>
       </c>
       <c r="E198" t="n">
-        <v>-2.04</v>
+        <v>-3.56</v>
       </c>
       <c r="F198" t="n">
-        <v>190.15</v>
+        <v>189.34</v>
       </c>
       <c r="G198" t="n">
         <v>193.61</v>
       </c>
       <c r="H198" t="n">
-        <v>-3.46</v>
+        <v>-4.27</v>
       </c>
       <c r="I198" t="n">
-        <v>184.27</v>
+        <v>186.39</v>
       </c>
       <c r="J198" t="n">
         <v>188.62</v>
       </c>
       <c r="K198" t="n">
-        <v>-4.35</v>
+        <v>-2.23</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="199">
@@ -10746,31 +10746,31 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>177.1</v>
+        <v>171.64</v>
       </c>
       <c r="D199" t="n">
         <v>174.54</v>
       </c>
       <c r="E199" t="n">
-        <v>2.56</v>
+        <v>-2.9</v>
       </c>
       <c r="F199" t="n">
-        <v>179.1</v>
+        <v>179.5</v>
       </c>
       <c r="G199" t="n">
         <v>181.19</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.09</v>
+        <v>-1.69</v>
       </c>
       <c r="I199" t="n">
-        <v>171.98</v>
+        <v>169.75</v>
       </c>
       <c r="J199" t="n">
         <v>176.5</v>
       </c>
       <c r="K199" t="n">
-        <v>-4.52</v>
+        <v>-6.75</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="200">
@@ -10798,31 +10798,31 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>7660</v>
+        <v>7649</v>
       </c>
       <c r="D200" t="n">
         <v>7793.01</v>
       </c>
       <c r="E200" t="n">
-        <v>-133.01</v>
+        <v>-144.01</v>
       </c>
       <c r="F200" t="n">
-        <v>7760</v>
+        <v>7825</v>
       </c>
       <c r="G200" t="n">
         <v>7793.01</v>
       </c>
       <c r="H200" t="n">
-        <v>-33.01</v>
+        <v>31.99</v>
       </c>
       <c r="I200" t="n">
-        <v>7627</v>
+        <v>7639</v>
       </c>
       <c r="J200" t="n">
         <v>7557.5</v>
       </c>
       <c r="K200" t="n">
-        <v>69.5</v>
+        <v>81.5</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="201">
@@ -10850,31 +10850,31 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>5745</v>
+        <v>5790</v>
       </c>
       <c r="D201" t="n">
         <v>5939.03</v>
       </c>
       <c r="E201" t="n">
-        <v>-194.03</v>
+        <v>-149.03</v>
       </c>
       <c r="F201" t="n">
-        <v>5811.5</v>
+        <v>5849</v>
       </c>
       <c r="G201" t="n">
         <v>5939.03</v>
       </c>
       <c r="H201" t="n">
-        <v>-127.53</v>
+        <v>-90.03</v>
       </c>
       <c r="I201" t="n">
-        <v>5740</v>
+        <v>5765</v>
       </c>
       <c r="J201" t="n">
         <v>5644.95</v>
       </c>
       <c r="K201" t="n">
-        <v>95.05</v>
+        <v>120.05</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>3.27</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="202">
@@ -10902,31 +10902,31 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1061.2</v>
+        <v>1067.7</v>
       </c>
       <c r="D202" t="n">
         <v>1065.06</v>
       </c>
       <c r="E202" t="n">
-        <v>-3.86</v>
+        <v>2.64</v>
       </c>
       <c r="F202" t="n">
-        <v>1068.8</v>
+        <v>1082</v>
       </c>
       <c r="G202" t="n">
         <v>1079.14</v>
       </c>
       <c r="H202" t="n">
-        <v>-10.34</v>
+        <v>2.86</v>
       </c>
       <c r="I202" t="n">
-        <v>1052.4</v>
+        <v>1065.1</v>
       </c>
       <c r="J202" t="n">
         <v>1051.01</v>
       </c>
       <c r="K202" t="n">
-        <v>1.39</v>
+        <v>14.09</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="203">
@@ -10954,31 +10954,31 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1049.9</v>
+        <v>1029.5</v>
       </c>
       <c r="D203" t="n">
         <v>1085.14</v>
       </c>
       <c r="E203" t="n">
-        <v>-35.24</v>
+        <v>-55.64</v>
       </c>
       <c r="F203" t="n">
-        <v>1060</v>
+        <v>1036.8</v>
       </c>
       <c r="G203" t="n">
         <v>1085.14</v>
       </c>
       <c r="H203" t="n">
-        <v>-25.14</v>
+        <v>-48.34</v>
       </c>
       <c r="I203" t="n">
-        <v>1032.7</v>
+        <v>1021.35</v>
       </c>
       <c r="J203" t="n">
         <v>1045.02</v>
       </c>
       <c r="K203" t="n">
-        <v>-12.32</v>
+        <v>-23.67</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -10987,11 +10987,11 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>3.25</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="204">
@@ -11006,31 +11006,31 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>5570</v>
+        <v>5580</v>
       </c>
       <c r="D204" t="n">
         <v>5474.57</v>
       </c>
       <c r="E204" t="n">
-        <v>95.43000000000001</v>
+        <v>105.43</v>
       </c>
       <c r="F204" t="n">
-        <v>5613</v>
+        <v>5618.5</v>
       </c>
       <c r="G204" t="n">
         <v>5703.39</v>
       </c>
       <c r="H204" t="n">
-        <v>-90.39</v>
+        <v>-84.89</v>
       </c>
       <c r="I204" t="n">
-        <v>5520</v>
+        <v>5447</v>
       </c>
       <c r="J204" t="n">
         <v>5556.07</v>
       </c>
       <c r="K204" t="n">
-        <v>-36.07</v>
+        <v>-109.07</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="205">
@@ -11058,31 +11058,31 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1269.9</v>
+        <v>1240</v>
       </c>
       <c r="D205" t="n">
         <v>1259.16</v>
       </c>
       <c r="E205" t="n">
-        <v>10.74</v>
+        <v>-19.16</v>
       </c>
       <c r="F205" t="n">
-        <v>1272</v>
+        <v>1246.9</v>
       </c>
       <c r="G205" t="n">
         <v>1263.84</v>
       </c>
       <c r="H205" t="n">
-        <v>8.16</v>
+        <v>-16.94</v>
       </c>
       <c r="I205" t="n">
-        <v>1235.9</v>
+        <v>1230.1</v>
       </c>
       <c r="J205" t="n">
         <v>1237.57</v>
       </c>
       <c r="K205" t="n">
-        <v>-1.67</v>
+        <v>-7.47</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0.85</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="206">
@@ -11110,31 +11110,31 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>117.32</v>
+        <v>118</v>
       </c>
       <c r="D206" t="n">
         <v>122.33</v>
       </c>
       <c r="E206" t="n">
-        <v>-5.01</v>
+        <v>-4.33</v>
       </c>
       <c r="F206" t="n">
-        <v>118.06</v>
+        <v>118.9</v>
       </c>
       <c r="G206" t="n">
         <v>122.33</v>
       </c>
       <c r="H206" t="n">
-        <v>-4.27</v>
+        <v>-3.43</v>
       </c>
       <c r="I206" t="n">
-        <v>115.32</v>
+        <v>117.4</v>
       </c>
       <c r="J206" t="n">
         <v>115.36</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.04</v>
+        <v>2.04</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="207">
@@ -11162,31 +11162,31 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>387.55</v>
+        <v>376</v>
       </c>
       <c r="D207" t="n">
         <v>414.13</v>
       </c>
       <c r="E207" t="n">
-        <v>-26.58</v>
+        <v>-38.13</v>
       </c>
       <c r="F207" t="n">
-        <v>391.5</v>
+        <v>384.95</v>
       </c>
       <c r="G207" t="n">
         <v>414.13</v>
       </c>
       <c r="H207" t="n">
-        <v>-22.63</v>
+        <v>-29.18</v>
       </c>
       <c r="I207" t="n">
-        <v>376.5</v>
+        <v>375</v>
       </c>
       <c r="J207" t="n">
         <v>373.35</v>
       </c>
       <c r="K207" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>6.42</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -11214,31 +11214,31 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1355.8</v>
+        <v>1343</v>
       </c>
       <c r="D208" t="n">
         <v>1340.33</v>
       </c>
       <c r="E208" t="n">
-        <v>15.47</v>
+        <v>2.67</v>
       </c>
       <c r="F208" t="n">
-        <v>1374</v>
+        <v>1367.1</v>
       </c>
       <c r="G208" t="n">
         <v>1351.8</v>
       </c>
       <c r="H208" t="n">
-        <v>22.2</v>
+        <v>15.3</v>
       </c>
       <c r="I208" t="n">
-        <v>1340.7</v>
+        <v>1337</v>
       </c>
       <c r="J208" t="n">
         <v>1315.63</v>
       </c>
       <c r="K208" t="n">
-        <v>25.07</v>
+        <v>21.37</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="209">
@@ -11266,31 +11266,31 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>11789</v>
+        <v>11828</v>
       </c>
       <c r="D209" t="n">
         <v>12122.16</v>
       </c>
       <c r="E209" t="n">
-        <v>-333.16</v>
+        <v>-294.16</v>
       </c>
       <c r="F209" t="n">
-        <v>11920</v>
+        <v>11850</v>
       </c>
       <c r="G209" t="n">
         <v>12122.16</v>
       </c>
       <c r="H209" t="n">
-        <v>-202.16</v>
+        <v>-272.16</v>
       </c>
       <c r="I209" t="n">
-        <v>11742</v>
+        <v>11318</v>
       </c>
       <c r="J209" t="n">
         <v>11614.72</v>
       </c>
       <c r="K209" t="n">
-        <v>127.28</v>
+        <v>-296.72</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="210">
@@ -11318,31 +11318,31 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4086.7</v>
+        <v>4057</v>
       </c>
       <c r="D210" t="n">
         <v>4066.74</v>
       </c>
       <c r="E210" t="n">
-        <v>19.96</v>
+        <v>-9.74</v>
       </c>
       <c r="F210" t="n">
-        <v>4086.7</v>
+        <v>4072.5</v>
       </c>
       <c r="G210" t="n">
         <v>4131.85</v>
       </c>
       <c r="H210" t="n">
-        <v>-45.15</v>
+        <v>-59.35</v>
       </c>
       <c r="I210" t="n">
-        <v>4026</v>
+        <v>4033.1</v>
       </c>
       <c r="J210" t="n">
         <v>4025.37</v>
       </c>
       <c r="K210" t="n">
-        <v>0.63</v>
+        <v>7.73</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="211">
@@ -11370,31 +11370,31 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D211" t="n">
         <v>582.91</v>
       </c>
       <c r="E211" t="n">
-        <v>31.09</v>
+        <v>18.09</v>
       </c>
       <c r="F211" t="n">
-        <v>614</v>
+        <v>615.9</v>
       </c>
       <c r="G211" t="n">
         <v>619.24</v>
       </c>
       <c r="H211" t="n">
-        <v>-5.24</v>
+        <v>-3.34</v>
       </c>
       <c r="I211" t="n">
-        <v>594.25</v>
+        <v>599.5</v>
       </c>
       <c r="J211" t="n">
         <v>602.92</v>
       </c>
       <c r="K211" t="n">
-        <v>-8.67</v>
+        <v>-3.42</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>5.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="212">
@@ -11422,31 +11422,31 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>318</v>
+        <v>318.5</v>
       </c>
       <c r="D212" t="n">
         <v>301.01</v>
       </c>
       <c r="E212" t="n">
-        <v>16.99</v>
+        <v>17.49</v>
       </c>
       <c r="F212" t="n">
-        <v>321.9</v>
+        <v>325</v>
       </c>
       <c r="G212" t="n">
         <v>325.2</v>
       </c>
       <c r="H212" t="n">
-        <v>-3.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I212" t="n">
-        <v>316.2</v>
+        <v>316.8</v>
       </c>
       <c r="J212" t="n">
         <v>316.79</v>
       </c>
       <c r="K212" t="n">
-        <v>-0.59</v>
+        <v>0.01</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>5.64</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="213">
@@ -11474,31 +11474,31 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>5275.5</v>
+        <v>5310</v>
       </c>
       <c r="D213" t="n">
         <v>5309.72</v>
       </c>
       <c r="E213" t="n">
-        <v>-34.22</v>
+        <v>0.28</v>
       </c>
       <c r="F213" t="n">
-        <v>5332.5</v>
+        <v>5370</v>
       </c>
       <c r="G213" t="n">
         <v>5386.06</v>
       </c>
       <c r="H213" t="n">
-        <v>-53.56</v>
+        <v>-16.06</v>
       </c>
       <c r="I213" t="n">
-        <v>5262.5</v>
+        <v>5310</v>
       </c>
       <c r="J213" t="n">
         <v>5246.39</v>
       </c>
       <c r="K213" t="n">
-        <v>16.11</v>
+        <v>63.61</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="214">
@@ -11526,31 +11526,31 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="D214" t="n">
         <v>1826.13</v>
       </c>
       <c r="E214" t="n">
-        <v>-20.13</v>
+        <v>-14.13</v>
       </c>
       <c r="F214" t="n">
-        <v>1821</v>
+        <v>1836.4</v>
       </c>
       <c r="G214" t="n">
         <v>1826.13</v>
       </c>
       <c r="H214" t="n">
-        <v>-5.13</v>
+        <v>10.27</v>
       </c>
       <c r="I214" t="n">
-        <v>1799.6</v>
+        <v>1804.2</v>
       </c>
       <c r="J214" t="n">
         <v>1760.55</v>
       </c>
       <c r="K214" t="n">
-        <v>39.05</v>
+        <v>43.65</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="215">
@@ -11578,31 +11578,31 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>11379</v>
+        <v>11475</v>
       </c>
       <c r="D215" t="n">
         <v>11440.67</v>
       </c>
       <c r="E215" t="n">
-        <v>-61.67</v>
+        <v>34.33</v>
       </c>
       <c r="F215" t="n">
-        <v>11574</v>
+        <v>11541</v>
       </c>
       <c r="G215" t="n">
         <v>11488.9</v>
       </c>
       <c r="H215" t="n">
-        <v>85.09999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="I215" t="n">
-        <v>11306</v>
+        <v>11387</v>
       </c>
       <c r="J215" t="n">
         <v>11186.56</v>
       </c>
       <c r="K215" t="n">
-        <v>119.44</v>
+        <v>200.44</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="216">
@@ -11630,31 +11630,31 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1610</v>
+        <v>1632.8</v>
       </c>
       <c r="D216" t="n">
         <v>1590.94</v>
       </c>
       <c r="E216" t="n">
-        <v>19.06</v>
+        <v>41.86</v>
       </c>
       <c r="F216" t="n">
-        <v>1638.9</v>
+        <v>1652</v>
       </c>
       <c r="G216" t="n">
         <v>1638.15</v>
       </c>
       <c r="H216" t="n">
-        <v>0.75</v>
+        <v>13.85</v>
       </c>
       <c r="I216" t="n">
-        <v>1604.2</v>
+        <v>1614.4</v>
       </c>
       <c r="J216" t="n">
         <v>1595.48</v>
       </c>
       <c r="K216" t="n">
-        <v>8.720000000000001</v>
+        <v>18.92</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1.2</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="217">
@@ -11682,31 +11682,31 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2081.3</v>
+        <v>2083.3</v>
       </c>
       <c r="D217" t="n">
         <v>2065.98</v>
       </c>
       <c r="E217" t="n">
-        <v>15.32</v>
+        <v>17.32</v>
       </c>
       <c r="F217" t="n">
-        <v>2110.9</v>
+        <v>2099</v>
       </c>
       <c r="G217" t="n">
         <v>2081.91</v>
       </c>
       <c r="H217" t="n">
-        <v>28.99</v>
+        <v>17.09</v>
       </c>
       <c r="I217" t="n">
-        <v>2072.4</v>
+        <v>2037</v>
       </c>
       <c r="J217" t="n">
         <v>2026.46</v>
       </c>
       <c r="K217" t="n">
-        <v>45.94</v>
+        <v>10.54</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="218">
@@ -11734,31 +11734,31 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2190</v>
+        <v>2199</v>
       </c>
       <c r="D218" t="n">
         <v>2190.76</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.76</v>
+        <v>8.24</v>
       </c>
       <c r="F218" t="n">
-        <v>2209.6</v>
+        <v>2255</v>
       </c>
       <c r="G218" t="n">
         <v>2190.76</v>
       </c>
       <c r="H218" t="n">
-        <v>18.84</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>2172.4</v>
+        <v>2191.6</v>
       </c>
       <c r="J218" t="n">
         <v>2128.63</v>
       </c>
       <c r="K218" t="n">
-        <v>43.77</v>
+        <v>62.97</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0.03</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="219">
@@ -11786,31 +11786,31 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>955</v>
+        <v>903.7</v>
       </c>
       <c r="D219" t="n">
         <v>947.97</v>
       </c>
       <c r="E219" t="n">
-        <v>7.03</v>
+        <v>-44.27</v>
       </c>
       <c r="F219" t="n">
-        <v>964</v>
+        <v>905.95</v>
       </c>
       <c r="G219" t="n">
         <v>947.97</v>
       </c>
       <c r="H219" t="n">
-        <v>16.03</v>
+        <v>-42.02</v>
       </c>
       <c r="I219" t="n">
-        <v>897.1</v>
+        <v>890</v>
       </c>
       <c r="J219" t="n">
         <v>933.12</v>
       </c>
       <c r="K219" t="n">
-        <v>-36.02</v>
+        <v>-43.12</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -11819,11 +11819,11 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0.74</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="220">
@@ -11838,31 +11838,31 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2005</v>
+        <v>2008.3</v>
       </c>
       <c r="D220" t="n">
         <v>2040.02</v>
       </c>
       <c r="E220" t="n">
-        <v>-35.02</v>
+        <v>-31.72</v>
       </c>
       <c r="F220" t="n">
-        <v>2028.2</v>
+        <v>2033.6</v>
       </c>
       <c r="G220" t="n">
         <v>2040.02</v>
       </c>
       <c r="H220" t="n">
-        <v>-11.82</v>
+        <v>-6.42</v>
       </c>
       <c r="I220" t="n">
-        <v>1997.2</v>
+        <v>2006.6</v>
       </c>
       <c r="J220" t="n">
         <v>1953.72</v>
       </c>
       <c r="K220" t="n">
-        <v>43.48</v>
+        <v>52.88</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="221">
@@ -11890,31 +11890,31 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3390.4</v>
+        <v>3428.3</v>
       </c>
       <c r="D221" t="n">
         <v>3292.1</v>
       </c>
       <c r="E221" t="n">
-        <v>98.3</v>
+        <v>136.2</v>
       </c>
       <c r="F221" t="n">
-        <v>3451.9</v>
+        <v>3430</v>
       </c>
       <c r="G221" t="n">
         <v>3292.1</v>
       </c>
       <c r="H221" t="n">
-        <v>159.8</v>
+        <v>137.9</v>
       </c>
       <c r="I221" t="n">
-        <v>3388.3</v>
+        <v>3378.3</v>
       </c>
       <c r="J221" t="n">
         <v>3305.46</v>
       </c>
       <c r="K221" t="n">
-        <v>82.84</v>
+        <v>72.84</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="222">
@@ -11942,31 +11942,31 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="D222" t="n">
         <v>1182.16</v>
       </c>
       <c r="E222" t="n">
-        <v>-9.16</v>
+        <v>-2.16</v>
       </c>
       <c r="F222" t="n">
-        <v>1174.7</v>
+        <v>1191.5</v>
       </c>
       <c r="G222" t="n">
         <v>1184.4</v>
       </c>
       <c r="H222" t="n">
-        <v>-9.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I222" t="n">
-        <v>1150.5</v>
+        <v>1167</v>
       </c>
       <c r="J222" t="n">
         <v>1153.24</v>
       </c>
       <c r="K222" t="n">
-        <v>-2.74</v>
+        <v>13.76</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0.77</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="223">
@@ -11994,31 +11994,31 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1969.3</v>
+        <v>1992.1</v>
       </c>
       <c r="D223" t="n">
         <v>2058.58</v>
       </c>
       <c r="E223" t="n">
-        <v>-89.28</v>
+        <v>-66.48</v>
       </c>
       <c r="F223" t="n">
-        <v>1993.2</v>
+        <v>2005.8</v>
       </c>
       <c r="G223" t="n">
         <v>2058.58</v>
       </c>
       <c r="H223" t="n">
-        <v>-65.38</v>
+        <v>-52.78</v>
       </c>
       <c r="I223" t="n">
-        <v>1969.3</v>
+        <v>1932</v>
       </c>
       <c r="J223" t="n">
         <v>1956.69</v>
       </c>
       <c r="K223" t="n">
-        <v>12.61</v>
+        <v>-24.69</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>4.34</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="224">
@@ -12046,31 +12046,31 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>14025</v>
+        <v>14130</v>
       </c>
       <c r="D224" t="n">
         <v>13901.39</v>
       </c>
       <c r="E224" t="n">
-        <v>123.61</v>
+        <v>228.61</v>
       </c>
       <c r="F224" t="n">
-        <v>14287</v>
+        <v>14209</v>
       </c>
       <c r="G224" t="n">
         <v>13901.39</v>
       </c>
       <c r="H224" t="n">
-        <v>385.61</v>
+        <v>307.61</v>
       </c>
       <c r="I224" t="n">
-        <v>14025</v>
+        <v>13999</v>
       </c>
       <c r="J224" t="n">
         <v>13622.58</v>
       </c>
       <c r="K224" t="n">
-        <v>402.42</v>
+        <v>376.42</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>0.89</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="225">
@@ -12098,31 +12098,31 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>281.8</v>
+        <v>282.6</v>
       </c>
       <c r="D225" t="n">
         <v>288.11</v>
       </c>
       <c r="E225" t="n">
-        <v>-6.31</v>
+        <v>-5.51</v>
       </c>
       <c r="F225" t="n">
-        <v>286.4</v>
+        <v>283.5</v>
       </c>
       <c r="G225" t="n">
         <v>288.11</v>
       </c>
       <c r="H225" t="n">
-        <v>-1.71</v>
+        <v>-4.61</v>
       </c>
       <c r="I225" t="n">
-        <v>281.65</v>
+        <v>277.15</v>
       </c>
       <c r="J225" t="n">
         <v>275.07</v>
       </c>
       <c r="K225" t="n">
-        <v>6.58</v>
+        <v>2.08</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="226">
@@ -12150,31 +12150,31 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>524.5</v>
+        <v>527</v>
       </c>
       <c r="D226" t="n">
         <v>494.28</v>
       </c>
       <c r="E226" t="n">
-        <v>30.22</v>
+        <v>32.72</v>
       </c>
       <c r="F226" t="n">
-        <v>530</v>
+        <v>543.7</v>
       </c>
       <c r="G226" t="n">
         <v>512.17</v>
       </c>
       <c r="H226" t="n">
-        <v>17.83</v>
+        <v>31.53</v>
       </c>
       <c r="I226" t="n">
-        <v>518.3</v>
+        <v>527</v>
       </c>
       <c r="J226" t="n">
         <v>508.18</v>
       </c>
       <c r="K226" t="n">
-        <v>10.12</v>
+        <v>18.82</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>6.11</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="227">
@@ -12202,31 +12202,31 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>881.2</v>
+        <v>894.95</v>
       </c>
       <c r="D227" t="n">
         <v>895.84</v>
       </c>
       <c r="E227" t="n">
-        <v>-14.64</v>
+        <v>-0.89</v>
       </c>
       <c r="F227" t="n">
-        <v>891.8</v>
+        <v>902.8</v>
       </c>
       <c r="G227" t="n">
         <v>895.84</v>
       </c>
       <c r="H227" t="n">
-        <v>-4.04</v>
+        <v>6.96</v>
       </c>
       <c r="I227" t="n">
-        <v>870.3</v>
+        <v>885.3</v>
       </c>
       <c r="J227" t="n">
         <v>870.1799999999999</v>
       </c>
       <c r="K227" t="n">
-        <v>0.12</v>
+        <v>15.12</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1.63</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -13172,31 +13172,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24287.65</v>
+        <v>24366</v>
       </c>
       <c r="D18" t="n">
         <v>24287.65</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>24360.1</v>
+        <v>24405.2</v>
       </c>
       <c r="G18" t="n">
         <v>24356.19</v>
       </c>
       <c r="H18" t="n">
-        <v>3.91</v>
+        <v>49.01</v>
       </c>
       <c r="I18" t="n">
-        <v>24226.95</v>
+        <v>24296.8</v>
       </c>
       <c r="J18" t="n">
         <v>24223.04</v>
       </c>
       <c r="K18" t="n">
-        <v>3.91</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="19">
@@ -13224,31 +13224,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57497.8</v>
+        <v>57491.1</v>
       </c>
       <c r="D19" t="n">
         <v>57497.8</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-6.7</v>
       </c>
       <c r="F19" t="n">
-        <v>57757.25</v>
+        <v>57681.45</v>
       </c>
       <c r="G19" t="n">
         <v>57796.84</v>
       </c>
       <c r="H19" t="n">
-        <v>-39.59</v>
+        <v>-115.39</v>
       </c>
       <c r="I19" t="n">
-        <v>57119.6</v>
+        <v>57380.45</v>
       </c>
       <c r="J19" t="n">
         <v>57159.19</v>
       </c>
       <c r="K19" t="n">
-        <v>-39.59</v>
+        <v>221.26</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -23554,31 +23554,31 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>177.1</v>
+        <v>171.64</v>
       </c>
       <c r="D198" t="n">
         <v>179.62</v>
       </c>
       <c r="E198" t="n">
-        <v>-2.52</v>
+        <v>-7.98</v>
       </c>
       <c r="F198" t="n">
-        <v>179.1</v>
+        <v>179.5</v>
       </c>
       <c r="G198" t="n">
         <v>182.59</v>
       </c>
       <c r="H198" t="n">
-        <v>-3.49</v>
+        <v>-3.09</v>
       </c>
       <c r="I198" t="n">
-        <v>171.98</v>
+        <v>169.75</v>
       </c>
       <c r="J198" t="n">
         <v>173.32</v>
       </c>
       <c r="K198" t="n">
-        <v>-1.34</v>
+        <v>-3.57</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>1.4</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="199">
@@ -23606,31 +23606,31 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>387.55</v>
+        <v>376</v>
       </c>
       <c r="D199" t="n">
         <v>429.55</v>
       </c>
       <c r="E199" t="n">
-        <v>-42</v>
+        <v>-53.55</v>
       </c>
       <c r="F199" t="n">
-        <v>391.5</v>
+        <v>384.95</v>
       </c>
       <c r="G199" t="n">
         <v>402.43</v>
       </c>
       <c r="H199" t="n">
-        <v>-10.93</v>
+        <v>-17.48</v>
       </c>
       <c r="I199" t="n">
-        <v>376.5</v>
+        <v>375</v>
       </c>
       <c r="J199" t="n">
         <v>377.08</v>
       </c>
       <c r="K199" t="n">
-        <v>-0.58</v>
+        <v>-2.08</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>9.779999999999999</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="200">
@@ -23658,31 +23658,31 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>5745</v>
+        <v>5790</v>
       </c>
       <c r="D200" t="n">
         <v>6085.2</v>
       </c>
       <c r="E200" t="n">
-        <v>-340.2</v>
+        <v>-295.2</v>
       </c>
       <c r="F200" t="n">
-        <v>5811.5</v>
+        <v>5849</v>
       </c>
       <c r="G200" t="n">
         <v>5895.89</v>
       </c>
       <c r="H200" t="n">
-        <v>-84.39</v>
+        <v>-46.89</v>
       </c>
       <c r="I200" t="n">
-        <v>5740</v>
+        <v>5765</v>
       </c>
       <c r="J200" t="n">
         <v>5642.69</v>
       </c>
       <c r="K200" t="n">
-        <v>97.31</v>
+        <v>122.31</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>5.59</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="201">
@@ -23710,31 +23710,31 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>188.9</v>
+        <v>187.38</v>
       </c>
       <c r="D201" t="n">
         <v>194.67</v>
       </c>
       <c r="E201" t="n">
-        <v>-5.77</v>
+        <v>-7.29</v>
       </c>
       <c r="F201" t="n">
-        <v>190.15</v>
+        <v>189.34</v>
       </c>
       <c r="G201" t="n">
         <v>193.34</v>
       </c>
       <c r="H201" t="n">
-        <v>-3.19</v>
+        <v>-4</v>
       </c>
       <c r="I201" t="n">
-        <v>184.27</v>
+        <v>186.39</v>
       </c>
       <c r="J201" t="n">
         <v>185.92</v>
       </c>
       <c r="K201" t="n">
-        <v>-1.65</v>
+        <v>0.47</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>2.96</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="202">
@@ -23762,31 +23762,31 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1049.9</v>
+        <v>1029.5</v>
       </c>
       <c r="D202" t="n">
         <v>1111.81</v>
       </c>
       <c r="E202" t="n">
-        <v>-61.91</v>
+        <v>-82.31</v>
       </c>
       <c r="F202" t="n">
-        <v>1060</v>
+        <v>1036.8</v>
       </c>
       <c r="G202" t="n">
         <v>1077.43</v>
       </c>
       <c r="H202" t="n">
-        <v>-17.43</v>
+        <v>-40.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1032.7</v>
+        <v>1021.35</v>
       </c>
       <c r="J202" t="n">
         <v>1031.23</v>
       </c>
       <c r="K202" t="n">
-        <v>1.47</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>5.57</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="203">
@@ -23814,31 +23814,31 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>5570</v>
+        <v>5580</v>
       </c>
       <c r="D203" t="n">
         <v>5638.08</v>
       </c>
       <c r="E203" t="n">
-        <v>-68.08</v>
+        <v>-58.08</v>
       </c>
       <c r="F203" t="n">
-        <v>5613</v>
+        <v>5618.5</v>
       </c>
       <c r="G203" t="n">
         <v>5751.2</v>
       </c>
       <c r="H203" t="n">
-        <v>-138.2</v>
+        <v>-132.7</v>
       </c>
       <c r="I203" t="n">
-        <v>5520</v>
+        <v>5447</v>
       </c>
       <c r="J203" t="n">
         <v>5444.4</v>
       </c>
       <c r="K203" t="n">
-        <v>75.59999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="204">
@@ -23866,31 +23866,31 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1269.9</v>
+        <v>1240</v>
       </c>
       <c r="D204" t="n">
         <v>1288.32</v>
       </c>
       <c r="E204" t="n">
-        <v>-18.42</v>
+        <v>-48.32</v>
       </c>
       <c r="F204" t="n">
-        <v>1272</v>
+        <v>1246.9</v>
       </c>
       <c r="G204" t="n">
         <v>1301.48</v>
       </c>
       <c r="H204" t="n">
-        <v>-29.48</v>
+        <v>-54.58</v>
       </c>
       <c r="I204" t="n">
-        <v>1235.9</v>
+        <v>1230.1</v>
       </c>
       <c r="J204" t="n">
         <v>1248.61</v>
       </c>
       <c r="K204" t="n">
-        <v>-12.71</v>
+        <v>-18.51</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -23899,11 +23899,11 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1.43</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="205">
@@ -23918,31 +23918,31 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D205" t="n">
         <v>604.05</v>
       </c>
       <c r="E205" t="n">
-        <v>9.949999999999999</v>
+        <v>-3.05</v>
       </c>
       <c r="F205" t="n">
-        <v>614</v>
+        <v>615.9</v>
       </c>
       <c r="G205" t="n">
         <v>637.02</v>
       </c>
       <c r="H205" t="n">
-        <v>-23.02</v>
+        <v>-21.12</v>
       </c>
       <c r="I205" t="n">
-        <v>594.25</v>
+        <v>599.5</v>
       </c>
       <c r="J205" t="n">
         <v>597.86</v>
       </c>
       <c r="K205" t="n">
-        <v>-3.61</v>
+        <v>1.64</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="206">
@@ -23970,31 +23970,31 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>117.32</v>
+        <v>118</v>
       </c>
       <c r="D206" t="n">
         <v>124.07</v>
       </c>
       <c r="E206" t="n">
-        <v>-6.75</v>
+        <v>-6.07</v>
       </c>
       <c r="F206" t="n">
-        <v>118.06</v>
+        <v>118.9</v>
       </c>
       <c r="G206" t="n">
         <v>119.23</v>
       </c>
       <c r="H206" t="n">
-        <v>-1.17</v>
+        <v>-0.33</v>
       </c>
       <c r="I206" t="n">
-        <v>115.32</v>
+        <v>117.4</v>
       </c>
       <c r="J206" t="n">
         <v>116.13</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>5.44</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="207">
@@ -24022,31 +24022,31 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>318</v>
+        <v>318.5</v>
       </c>
       <c r="D207" t="n">
         <v>308.97</v>
       </c>
       <c r="E207" t="n">
-        <v>9.029999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F207" t="n">
-        <v>321.9</v>
+        <v>325</v>
       </c>
       <c r="G207" t="n">
         <v>326.91</v>
       </c>
       <c r="H207" t="n">
-        <v>-5.01</v>
+        <v>-1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>316.2</v>
+        <v>316.8</v>
       </c>
       <c r="J207" t="n">
         <v>311.91</v>
       </c>
       <c r="K207" t="n">
-        <v>4.29</v>
+        <v>4.89</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="208">
@@ -24074,31 +24074,31 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1355.8</v>
+        <v>1343</v>
       </c>
       <c r="D208" t="n">
         <v>1384.57</v>
       </c>
       <c r="E208" t="n">
-        <v>-28.77</v>
+        <v>-41.57</v>
       </c>
       <c r="F208" t="n">
-        <v>1374</v>
+        <v>1367.1</v>
       </c>
       <c r="G208" t="n">
         <v>1402.38</v>
       </c>
       <c r="H208" t="n">
-        <v>-28.38</v>
+        <v>-35.28</v>
       </c>
       <c r="I208" t="n">
-        <v>1340.7</v>
+        <v>1337</v>
       </c>
       <c r="J208" t="n">
         <v>1323.35</v>
       </c>
       <c r="K208" t="n">
-        <v>17.35</v>
+        <v>13.65</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -24107,11 +24107,11 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N208" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -24126,31 +24126,31 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>11789</v>
+        <v>11828</v>
       </c>
       <c r="D209" t="n">
         <v>12484.66</v>
       </c>
       <c r="E209" t="n">
-        <v>-695.66</v>
+        <v>-656.66</v>
       </c>
       <c r="F209" t="n">
-        <v>11920</v>
+        <v>11850</v>
       </c>
       <c r="G209" t="n">
         <v>12158.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-238.68</v>
+        <v>-308.68</v>
       </c>
       <c r="I209" t="n">
-        <v>11742</v>
+        <v>11318</v>
       </c>
       <c r="J209" t="n">
         <v>11533.65</v>
       </c>
       <c r="K209" t="n">
-        <v>208.35</v>
+        <v>-215.65</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>5.57</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="210">
@@ -24178,31 +24178,31 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>7660</v>
+        <v>7649</v>
       </c>
       <c r="D210" t="n">
         <v>7994.78</v>
       </c>
       <c r="E210" t="n">
-        <v>-334.78</v>
+        <v>-345.78</v>
       </c>
       <c r="F210" t="n">
-        <v>7760</v>
+        <v>7825</v>
       </c>
       <c r="G210" t="n">
         <v>7870.62</v>
       </c>
       <c r="H210" t="n">
-        <v>-110.62</v>
+        <v>-45.62</v>
       </c>
       <c r="I210" t="n">
-        <v>7627</v>
+        <v>7639</v>
       </c>
       <c r="J210" t="n">
         <v>7516.46</v>
       </c>
       <c r="K210" t="n">
-        <v>110.54</v>
+        <v>122.54</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>4.19</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="211">
@@ -24230,31 +24230,31 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1061.2</v>
+        <v>1067.7</v>
       </c>
       <c r="D211" t="n">
         <v>1084.84</v>
       </c>
       <c r="E211" t="n">
-        <v>-23.64</v>
+        <v>-17.14</v>
       </c>
       <c r="F211" t="n">
-        <v>1068.8</v>
+        <v>1082</v>
       </c>
       <c r="G211" t="n">
         <v>1082.91</v>
       </c>
       <c r="H211" t="n">
-        <v>-14.11</v>
+        <v>-0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>1052.4</v>
+        <v>1065.1</v>
       </c>
       <c r="J211" t="n">
         <v>1046.96</v>
       </c>
       <c r="K211" t="n">
-        <v>5.44</v>
+        <v>18.14</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="212">
@@ -24282,31 +24282,31 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>4086.7</v>
+        <v>4057</v>
       </c>
       <c r="D212" t="n">
         <v>4117.2</v>
       </c>
       <c r="E212" t="n">
-        <v>-30.5</v>
+        <v>-60.2</v>
       </c>
       <c r="F212" t="n">
-        <v>4086.7</v>
+        <v>4072.5</v>
       </c>
       <c r="G212" t="n">
         <v>4146.01</v>
       </c>
       <c r="H212" t="n">
-        <v>-59.31</v>
+        <v>-73.51000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>4026</v>
+        <v>4033.1</v>
       </c>
       <c r="J212" t="n">
         <v>4050.24</v>
       </c>
       <c r="K212" t="n">
-        <v>-24.24</v>
+        <v>-17.14</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>0.74</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="213">
@@ -24334,31 +24334,31 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1610</v>
+        <v>1632.8</v>
       </c>
       <c r="D213" t="n">
         <v>1627.8</v>
       </c>
       <c r="E213" t="n">
-        <v>-17.8</v>
+        <v>5</v>
       </c>
       <c r="F213" t="n">
-        <v>1638.9</v>
+        <v>1652</v>
       </c>
       <c r="G213" t="n">
         <v>1650.05</v>
       </c>
       <c r="H213" t="n">
-        <v>-11.15</v>
+        <v>1.95</v>
       </c>
       <c r="I213" t="n">
-        <v>1604.2</v>
+        <v>1614.4</v>
       </c>
       <c r="J213" t="n">
         <v>1583.02</v>
       </c>
       <c r="K213" t="n">
-        <v>21.18</v>
+        <v>31.38</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1.09</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="214">
@@ -24386,31 +24386,31 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2081.3</v>
+        <v>2083.3</v>
       </c>
       <c r="D214" t="n">
         <v>2125.25</v>
       </c>
       <c r="E214" t="n">
-        <v>-43.95</v>
+        <v>-41.95</v>
       </c>
       <c r="F214" t="n">
-        <v>2110.9</v>
+        <v>2099</v>
       </c>
       <c r="G214" t="n">
         <v>2144.13</v>
       </c>
       <c r="H214" t="n">
-        <v>-33.23</v>
+        <v>-45.13</v>
       </c>
       <c r="I214" t="n">
-        <v>2072.4</v>
+        <v>2037</v>
       </c>
       <c r="J214" t="n">
         <v>2038.06</v>
       </c>
       <c r="K214" t="n">
-        <v>34.34</v>
+        <v>-1.06</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="215">
@@ -24438,31 +24438,31 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3390.4</v>
+        <v>3428.3</v>
       </c>
       <c r="D215" t="n">
         <v>3366.99</v>
       </c>
       <c r="E215" t="n">
-        <v>23.41</v>
+        <v>61.31</v>
       </c>
       <c r="F215" t="n">
-        <v>3451.9</v>
+        <v>3430</v>
       </c>
       <c r="G215" t="n">
         <v>3473.37</v>
       </c>
       <c r="H215" t="n">
-        <v>-21.47</v>
+        <v>-43.37</v>
       </c>
       <c r="I215" t="n">
-        <v>3388.3</v>
+        <v>3378.3</v>
       </c>
       <c r="J215" t="n">
         <v>3334.61</v>
       </c>
       <c r="K215" t="n">
-        <v>53.69</v>
+        <v>43.69</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>0.7</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="216">
@@ -24490,31 +24490,31 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>5275.5</v>
+        <v>5310</v>
       </c>
       <c r="D216" t="n">
         <v>5411.18</v>
       </c>
       <c r="E216" t="n">
-        <v>-135.68</v>
+        <v>-101.18</v>
       </c>
       <c r="F216" t="n">
-        <v>5332.5</v>
+        <v>5370</v>
       </c>
       <c r="G216" t="n">
         <v>5386.11</v>
       </c>
       <c r="H216" t="n">
-        <v>-53.61</v>
+        <v>-16.11</v>
       </c>
       <c r="I216" t="n">
-        <v>5262.5</v>
+        <v>5310</v>
       </c>
       <c r="J216" t="n">
         <v>5202.71</v>
       </c>
       <c r="K216" t="n">
-        <v>59.79</v>
+        <v>107.29</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -24523,11 +24523,11 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="217">
@@ -24542,31 +24542,31 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>955</v>
+        <v>903.7</v>
       </c>
       <c r="D217" t="n">
         <v>967.45</v>
       </c>
       <c r="E217" t="n">
-        <v>-12.45</v>
+        <v>-63.75</v>
       </c>
       <c r="F217" t="n">
-        <v>964</v>
+        <v>905.95</v>
       </c>
       <c r="G217" t="n">
         <v>976.35</v>
       </c>
       <c r="H217" t="n">
-        <v>-12.35</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="I217" t="n">
-        <v>897.1</v>
+        <v>890</v>
       </c>
       <c r="J217" t="n">
         <v>940.83</v>
       </c>
       <c r="K217" t="n">
-        <v>-43.73</v>
+        <v>-50.83</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -24575,11 +24575,11 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1.29</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="218">
@@ -24594,31 +24594,31 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="D218" t="n">
         <v>1886.93</v>
       </c>
       <c r="E218" t="n">
-        <v>-80.93000000000001</v>
+        <v>-74.93000000000001</v>
       </c>
       <c r="F218" t="n">
-        <v>1821</v>
+        <v>1836.4</v>
       </c>
       <c r="G218" t="n">
         <v>1868.53</v>
       </c>
       <c r="H218" t="n">
-        <v>-47.53</v>
+        <v>-32.13</v>
       </c>
       <c r="I218" t="n">
-        <v>1799.6</v>
+        <v>1804.2</v>
       </c>
       <c r="J218" t="n">
         <v>1762.42</v>
       </c>
       <c r="K218" t="n">
-        <v>37.18</v>
+        <v>41.78</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>4.29</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="219">
@@ -24646,31 +24646,31 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1969.3</v>
+        <v>1992.1</v>
       </c>
       <c r="D219" t="n">
         <v>2096.61</v>
       </c>
       <c r="E219" t="n">
-        <v>-127.31</v>
+        <v>-104.51</v>
       </c>
       <c r="F219" t="n">
-        <v>1993.2</v>
+        <v>2005.8</v>
       </c>
       <c r="G219" t="n">
         <v>2009.39</v>
       </c>
       <c r="H219" t="n">
-        <v>-16.19</v>
+        <v>-3.59</v>
       </c>
       <c r="I219" t="n">
-        <v>1969.3</v>
+        <v>1932</v>
       </c>
       <c r="J219" t="n">
         <v>1943.03</v>
       </c>
       <c r="K219" t="n">
-        <v>26.27</v>
+        <v>-11.03</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>6.07</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="220">
@@ -24698,31 +24698,31 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>11379</v>
+        <v>11475</v>
       </c>
       <c r="D220" t="n">
         <v>11640.65</v>
       </c>
       <c r="E220" t="n">
-        <v>-261.65</v>
+        <v>-165.65</v>
       </c>
       <c r="F220" t="n">
-        <v>11574</v>
+        <v>11541</v>
       </c>
       <c r="G220" t="n">
         <v>11599.75</v>
       </c>
       <c r="H220" t="n">
-        <v>-25.75</v>
+        <v>-58.75</v>
       </c>
       <c r="I220" t="n">
-        <v>11306</v>
+        <v>11387</v>
       </c>
       <c r="J220" t="n">
         <v>11235.45</v>
       </c>
       <c r="K220" t="n">
-        <v>70.55</v>
+        <v>151.55</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="221">
@@ -24750,31 +24750,31 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2190</v>
+        <v>2199</v>
       </c>
       <c r="D221" t="n">
         <v>2248.02</v>
       </c>
       <c r="E221" t="n">
-        <v>-58.02</v>
+        <v>-49.02</v>
       </c>
       <c r="F221" t="n">
-        <v>2209.6</v>
+        <v>2255</v>
       </c>
       <c r="G221" t="n">
         <v>2250.73</v>
       </c>
       <c r="H221" t="n">
-        <v>-41.13</v>
+        <v>4.27</v>
       </c>
       <c r="I221" t="n">
-        <v>2172.4</v>
+        <v>2191.6</v>
       </c>
       <c r="J221" t="n">
         <v>2148.57</v>
       </c>
       <c r="K221" t="n">
-        <v>23.83</v>
+        <v>43.03</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -24783,11 +24783,11 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2.58</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="222">
@@ -24802,31 +24802,31 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2005</v>
+        <v>2008.3</v>
       </c>
       <c r="D222" t="n">
         <v>2087.53</v>
       </c>
       <c r="E222" t="n">
-        <v>-82.53</v>
+        <v>-79.23</v>
       </c>
       <c r="F222" t="n">
-        <v>2028.2</v>
+        <v>2033.6</v>
       </c>
       <c r="G222" t="n">
         <v>2055.1</v>
       </c>
       <c r="H222" t="n">
-        <v>-26.9</v>
+        <v>-21.5</v>
       </c>
       <c r="I222" t="n">
-        <v>1997.2</v>
+        <v>2006.6</v>
       </c>
       <c r="J222" t="n">
         <v>1971.22</v>
       </c>
       <c r="K222" t="n">
-        <v>25.98</v>
+        <v>35.38</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="223">
@@ -24854,31 +24854,31 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>524.5</v>
+        <v>527</v>
       </c>
       <c r="D223" t="n">
         <v>508.61</v>
       </c>
       <c r="E223" t="n">
-        <v>15.89</v>
+        <v>18.39</v>
       </c>
       <c r="F223" t="n">
-        <v>530</v>
+        <v>543.7</v>
       </c>
       <c r="G223" t="n">
         <v>540.49</v>
       </c>
       <c r="H223" t="n">
-        <v>-10.49</v>
+        <v>3.21</v>
       </c>
       <c r="I223" t="n">
-        <v>518.3</v>
+        <v>527</v>
       </c>
       <c r="J223" t="n">
         <v>513.48</v>
       </c>
       <c r="K223" t="n">
-        <v>4.82</v>
+        <v>13.52</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="224">
@@ -24906,31 +24906,31 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="D224" t="n">
         <v>1213.99</v>
       </c>
       <c r="E224" t="n">
-        <v>-40.99</v>
+        <v>-33.99</v>
       </c>
       <c r="F224" t="n">
-        <v>1174.7</v>
+        <v>1191.5</v>
       </c>
       <c r="G224" t="n">
         <v>1206.42</v>
       </c>
       <c r="H224" t="n">
-        <v>-31.72</v>
+        <v>-14.92</v>
       </c>
       <c r="I224" t="n">
-        <v>1150.5</v>
+        <v>1167</v>
       </c>
       <c r="J224" t="n">
         <v>1150.14</v>
       </c>
       <c r="K224" t="n">
-        <v>0.36</v>
+        <v>16.86</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="225">
@@ -24958,31 +24958,31 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>14025</v>
+        <v>14130</v>
       </c>
       <c r="D225" t="n">
         <v>14269.8</v>
       </c>
       <c r="E225" t="n">
-        <v>-244.8</v>
+        <v>-139.8</v>
       </c>
       <c r="F225" t="n">
-        <v>14287</v>
+        <v>14209</v>
       </c>
       <c r="G225" t="n">
         <v>14418.88</v>
       </c>
       <c r="H225" t="n">
-        <v>-131.88</v>
+        <v>-209.88</v>
       </c>
       <c r="I225" t="n">
-        <v>14025</v>
+        <v>13999</v>
       </c>
       <c r="J225" t="n">
         <v>13755.95</v>
       </c>
       <c r="K225" t="n">
-        <v>269.05</v>
+        <v>243.05</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1.72</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="226">
@@ -25010,31 +25010,31 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>281.8</v>
+        <v>282.6</v>
       </c>
       <c r="D226" t="n">
         <v>294.31</v>
       </c>
       <c r="E226" t="n">
-        <v>-12.51</v>
+        <v>-11.71</v>
       </c>
       <c r="F226" t="n">
-        <v>286.4</v>
+        <v>283.5</v>
       </c>
       <c r="G226" t="n">
         <v>288.36</v>
       </c>
       <c r="H226" t="n">
-        <v>-1.96</v>
+        <v>-4.86</v>
       </c>
       <c r="I226" t="n">
-        <v>281.65</v>
+        <v>277.15</v>
       </c>
       <c r="J226" t="n">
         <v>277.41</v>
       </c>
       <c r="K226" t="n">
-        <v>4.24</v>
+        <v>-0.26</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="227">
@@ -25062,31 +25062,31 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>881.2</v>
+        <v>894.95</v>
       </c>
       <c r="D227" t="n">
         <v>913.52</v>
       </c>
       <c r="E227" t="n">
-        <v>-32.32</v>
+        <v>-18.57</v>
       </c>
       <c r="F227" t="n">
-        <v>891.8</v>
+        <v>902.8</v>
       </c>
       <c r="G227" t="n">
         <v>900.21</v>
       </c>
       <c r="H227" t="n">
-        <v>-8.41</v>
+        <v>2.59</v>
       </c>
       <c r="I227" t="n">
-        <v>870.3</v>
+        <v>885.3</v>
       </c>
       <c r="J227" t="n">
         <v>868.64</v>
       </c>
       <c r="K227" t="n">
-        <v>1.66</v>
+        <v>16.66</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -25095,11 +25095,11 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>3.54</v>
+        <v>2.03</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12240,6 +12240,1358 @@
       </c>
       <c r="N227" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>5745.5</v>
+      </c>
+      <c r="D228" t="n">
+        <v>5646.15</v>
+      </c>
+      <c r="E228" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="F228" t="n">
+        <v>5778</v>
+      </c>
+      <c r="G228" t="n">
+        <v>5719.7</v>
+      </c>
+      <c r="H228" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="I228" t="n">
+        <v>5694.5</v>
+      </c>
+      <c r="J228" t="n">
+        <v>5601.44</v>
+      </c>
+      <c r="K228" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2115</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2149.79</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-34.79</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2122</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2149.79</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-27.79</v>
+      </c>
+      <c r="I229" t="n">
+        <v>2075.1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>2098.65</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-23.55</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1064.05</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1067.7</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1064.71</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1042.38</v>
+      </c>
+      <c r="K230" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1273</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1263.65</v>
+      </c>
+      <c r="E231" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1281.2</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1281.43</v>
+      </c>
+      <c r="H231" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1263</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1254.36</v>
+      </c>
+      <c r="K231" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1934.2</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1886.72</v>
+      </c>
+      <c r="E232" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1959.7</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1967.12</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1923.2</v>
+      </c>
+      <c r="J232" t="n">
+        <v>1926.27</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>3421.5</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3591.55</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-170.05</v>
+      </c>
+      <c r="F233" t="n">
+        <v>3435</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3591.55</v>
+      </c>
+      <c r="H233" t="n">
+        <v>-156.55</v>
+      </c>
+      <c r="I233" t="n">
+        <v>3390.2</v>
+      </c>
+      <c r="J233" t="n">
+        <v>3340.95</v>
+      </c>
+      <c r="K233" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>388</v>
+      </c>
+      <c r="D234" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="E234" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="F234" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="G234" t="n">
+        <v>383.58</v>
+      </c>
+      <c r="H234" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I234" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="J234" t="n">
+        <v>375.23</v>
+      </c>
+      <c r="K234" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-21.54</v>
+      </c>
+      <c r="F235" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="G235" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="I235" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="J235" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="D236" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="E236" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F236" t="n">
+        <v>117.99</v>
+      </c>
+      <c r="G236" t="n">
+        <v>118.51</v>
+      </c>
+      <c r="H236" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I236" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J236" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1773.35</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1795</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1773.35</v>
+      </c>
+      <c r="H237" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I237" t="n">
+        <v>1762.2</v>
+      </c>
+      <c r="J237" t="n">
+        <v>1727.77</v>
+      </c>
+      <c r="K237" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>14150</v>
+      </c>
+      <c r="D238" t="n">
+        <v>14497.83</v>
+      </c>
+      <c r="E238" t="n">
+        <v>-347.83</v>
+      </c>
+      <c r="F238" t="n">
+        <v>14420</v>
+      </c>
+      <c r="G238" t="n">
+        <v>14497.83</v>
+      </c>
+      <c r="H238" t="n">
+        <v>-77.83</v>
+      </c>
+      <c r="I238" t="n">
+        <v>14066</v>
+      </c>
+      <c r="J238" t="n">
+        <v>13762.25</v>
+      </c>
+      <c r="K238" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1368.46</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-13.56</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1368.8</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1368.46</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1331.1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1320.97</v>
+      </c>
+      <c r="K239" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1592</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-55.33</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1608</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="H240" t="n">
+        <v>-39.33</v>
+      </c>
+      <c r="I240" t="n">
+        <v>1579.9</v>
+      </c>
+      <c r="J240" t="n">
+        <v>1588.49</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="D241" t="n">
+        <v>174.81</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F241" t="n">
+        <v>177.59</v>
+      </c>
+      <c r="G241" t="n">
+        <v>178.96</v>
+      </c>
+      <c r="H241" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="I241" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="J241" t="n">
+        <v>175.22</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2186</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2211.78</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-25.78</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2221.9</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2211.78</v>
+      </c>
+      <c r="H242" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="I242" t="n">
+        <v>2179</v>
+      </c>
+      <c r="J242" t="n">
+        <v>2126.27</v>
+      </c>
+      <c r="K242" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2011.2</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1995.77</v>
+      </c>
+      <c r="E243" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="F243" t="n">
+        <v>2018.8</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1995.77</v>
+      </c>
+      <c r="H243" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I243" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1962.36</v>
+      </c>
+      <c r="K243" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>11254</v>
+      </c>
+      <c r="D244" t="n">
+        <v>11378.06</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-124.06</v>
+      </c>
+      <c r="F244" t="n">
+        <v>11435</v>
+      </c>
+      <c r="G244" t="n">
+        <v>11442.61</v>
+      </c>
+      <c r="H244" t="n">
+        <v>-7.61</v>
+      </c>
+      <c r="I244" t="n">
+        <v>11211</v>
+      </c>
+      <c r="J244" t="n">
+        <v>11204.88</v>
+      </c>
+      <c r="K244" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>4064.3</v>
+      </c>
+      <c r="D245" t="n">
+        <v>4086.98</v>
+      </c>
+      <c r="E245" t="n">
+        <v>-22.68</v>
+      </c>
+      <c r="F245" t="n">
+        <v>4085</v>
+      </c>
+      <c r="G245" t="n">
+        <v>4086.98</v>
+      </c>
+      <c r="H245" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="I245" t="n">
+        <v>4050</v>
+      </c>
+      <c r="J245" t="n">
+        <v>4006.69</v>
+      </c>
+      <c r="K245" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="D246" t="n">
+        <v>283.02</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F246" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="G246" t="n">
+        <v>286.47</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I246" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="J246" t="n">
+        <v>280.36</v>
+      </c>
+      <c r="K246" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>7546</v>
+      </c>
+      <c r="D247" t="n">
+        <v>7465.8</v>
+      </c>
+      <c r="E247" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F247" t="n">
+        <v>7734</v>
+      </c>
+      <c r="G247" t="n">
+        <v>7656.55</v>
+      </c>
+      <c r="H247" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="I247" t="n">
+        <v>7528.5</v>
+      </c>
+      <c r="J247" t="n">
+        <v>7496.93</v>
+      </c>
+      <c r="K247" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>183.49</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F248" t="n">
+        <v>190.58</v>
+      </c>
+      <c r="G248" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="I248" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="J248" t="n">
+        <v>183.15</v>
+      </c>
+      <c r="K248" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1041.6</v>
+      </c>
+      <c r="D249" t="n">
+        <v>996.48</v>
+      </c>
+      <c r="E249" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1050.6</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1061.43</v>
+      </c>
+      <c r="H249" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="I249" t="n">
+        <v>1038</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1039.46</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1163.6</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="E250" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="H250" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1154</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1141.13</v>
+      </c>
+      <c r="K250" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>875</v>
+      </c>
+      <c r="D251" t="n">
+        <v>881.13</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="F251" t="n">
+        <v>887</v>
+      </c>
+      <c r="G251" t="n">
+        <v>881.67</v>
+      </c>
+      <c r="H251" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I251" t="n">
+        <v>874</v>
+      </c>
+      <c r="J251" t="n">
+        <v>863.08</v>
+      </c>
+      <c r="K251" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>518.25</v>
+      </c>
+      <c r="D252" t="n">
+        <v>556.98</v>
+      </c>
+      <c r="E252" t="n">
+        <v>-38.73</v>
+      </c>
+      <c r="F252" t="n">
+        <v>524.85</v>
+      </c>
+      <c r="G252" t="n">
+        <v>556.98</v>
+      </c>
+      <c r="H252" t="n">
+        <v>-32.13</v>
+      </c>
+      <c r="I252" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="J252" t="n">
+        <v>506.25</v>
+      </c>
+      <c r="K252" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>938</v>
+      </c>
+      <c r="D253" t="n">
+        <v>901.35</v>
+      </c>
+      <c r="E253" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="F253" t="n">
+        <v>961.35</v>
+      </c>
+      <c r="G253" t="n">
+        <v>901.35</v>
+      </c>
+      <c r="H253" t="n">
+        <v>60</v>
+      </c>
+      <c r="I253" t="n">
+        <v>933.1</v>
+      </c>
+      <c r="J253" t="n">
+        <v>913.21</v>
+      </c>
+      <c r="K253" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>4.07</v>
       </c>
     </row>
   </sheetData>
@@ -12253,7 +13605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13262,6 +14614,110 @@
       </c>
       <c r="N19" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24269.65</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24231.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24116.65</v>
+      </c>
+      <c r="K20" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>57262.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57262.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>57584.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>57492.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>57217.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>57125.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13275,7 +14731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25102,6 +26558,1358 @@
         <v>2.03</v>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>5745.5</v>
+      </c>
+      <c r="D228" t="n">
+        <v>5781.28</v>
+      </c>
+      <c r="E228" t="n">
+        <v>-35.78</v>
+      </c>
+      <c r="F228" t="n">
+        <v>5778</v>
+      </c>
+      <c r="G228" t="n">
+        <v>5869.22</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-91.22</v>
+      </c>
+      <c r="I228" t="n">
+        <v>5694.5</v>
+      </c>
+      <c r="J228" t="n">
+        <v>5651.9</v>
+      </c>
+      <c r="K228" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>3421.5</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3671.86</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-250.36</v>
+      </c>
+      <c r="F229" t="n">
+        <v>3435</v>
+      </c>
+      <c r="G229" t="n">
+        <v>3490.02</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-55.02</v>
+      </c>
+      <c r="I229" t="n">
+        <v>3390.2</v>
+      </c>
+      <c r="J229" t="n">
+        <v>3369.68</v>
+      </c>
+      <c r="K229" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>388</v>
+      </c>
+      <c r="D230" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="E230" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="F230" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="G230" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>-10.25</v>
+      </c>
+      <c r="I230" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="J230" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="K230" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="D231" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-29.01</v>
+      </c>
+      <c r="F231" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="G231" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="H231" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="I231" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="J231" t="n">
+        <v>310.81</v>
+      </c>
+      <c r="K231" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1273</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1293.65</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-20.65</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1281.2</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1300.18</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-18.98</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1263</v>
+      </c>
+      <c r="J232" t="n">
+        <v>1252.44</v>
+      </c>
+      <c r="K232" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="D233" t="n">
+        <v>115.01</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F233" t="n">
+        <v>117.99</v>
+      </c>
+      <c r="G233" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="H233" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I233" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J233" t="n">
+        <v>115.34</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1934.2</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1922.83</v>
+      </c>
+      <c r="E234" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1959.7</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1966.97</v>
+      </c>
+      <c r="H234" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1923.2</v>
+      </c>
+      <c r="J234" t="n">
+        <v>1909.43</v>
+      </c>
+      <c r="K234" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2115</v>
+      </c>
+      <c r="D235" t="n">
+        <v>2209.62</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-94.62</v>
+      </c>
+      <c r="F235" t="n">
+        <v>2122</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2168.45</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-46.45</v>
+      </c>
+      <c r="I235" t="n">
+        <v>2075.1</v>
+      </c>
+      <c r="J235" t="n">
+        <v>2074.53</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1084.12</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-31.12</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1067.7</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1070.55</v>
+      </c>
+      <c r="H236" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="I236" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J236" t="n">
+        <v>1039.74</v>
+      </c>
+      <c r="K236" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>14150</v>
+      </c>
+      <c r="D237" t="n">
+        <v>14879.56</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-729.5599999999999</v>
+      </c>
+      <c r="F237" t="n">
+        <v>14420</v>
+      </c>
+      <c r="G237" t="n">
+        <v>14487.22</v>
+      </c>
+      <c r="H237" t="n">
+        <v>-67.22</v>
+      </c>
+      <c r="I237" t="n">
+        <v>14066</v>
+      </c>
+      <c r="J237" t="n">
+        <v>13894.74</v>
+      </c>
+      <c r="K237" t="n">
+        <v>171.26</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1041.6</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1022.18</v>
+      </c>
+      <c r="E238" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1050.6</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1066.28</v>
+      </c>
+      <c r="H238" t="n">
+        <v>-15.68</v>
+      </c>
+      <c r="I238" t="n">
+        <v>1038</v>
+      </c>
+      <c r="J238" t="n">
+        <v>1022.91</v>
+      </c>
+      <c r="K238" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1592</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1682.28</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-90.28</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1608</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1622.48</v>
+      </c>
+      <c r="H239" t="n">
+        <v>-14.48</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1579.9</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1568.95</v>
+      </c>
+      <c r="K239" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="D240" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="F240" t="n">
+        <v>177.59</v>
+      </c>
+      <c r="G240" t="n">
+        <v>181.33</v>
+      </c>
+      <c r="H240" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="I240" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="J240" t="n">
+        <v>172.58</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2011.2</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2041.92</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-30.72</v>
+      </c>
+      <c r="F241" t="n">
+        <v>2018.8</v>
+      </c>
+      <c r="G241" t="n">
+        <v>2052.95</v>
+      </c>
+      <c r="H241" t="n">
+        <v>-34.15</v>
+      </c>
+      <c r="I241" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J241" t="n">
+        <v>1979.62</v>
+      </c>
+      <c r="K241" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1831.33</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-58.33</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1795</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1826.08</v>
+      </c>
+      <c r="H242" t="n">
+        <v>-31.08</v>
+      </c>
+      <c r="I242" t="n">
+        <v>1762.2</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1732.79</v>
+      </c>
+      <c r="K242" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="D243" t="n">
+        <v>288.61</v>
+      </c>
+      <c r="E243" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="F243" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="G243" t="n">
+        <v>291.27</v>
+      </c>
+      <c r="H243" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="I243" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="J243" t="n">
+        <v>282.46</v>
+      </c>
+      <c r="K243" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1412.39</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-57.49</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1368.8</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1394.68</v>
+      </c>
+      <c r="H244" t="n">
+        <v>-25.88</v>
+      </c>
+      <c r="I244" t="n">
+        <v>1331.1</v>
+      </c>
+      <c r="J244" t="n">
+        <v>1324.77</v>
+      </c>
+      <c r="K244" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ABB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>7546</v>
+      </c>
+      <c r="D245" t="n">
+        <v>7650.54</v>
+      </c>
+      <c r="E245" t="n">
+        <v>-104.54</v>
+      </c>
+      <c r="F245" t="n">
+        <v>7734</v>
+      </c>
+      <c r="G245" t="n">
+        <v>7714.35</v>
+      </c>
+      <c r="H245" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="I245" t="n">
+        <v>7528.5</v>
+      </c>
+      <c r="J245" t="n">
+        <v>7418.61</v>
+      </c>
+      <c r="K245" t="n">
+        <v>109.89</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="D246" t="n">
+        <v>187.98</v>
+      </c>
+      <c r="E246" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F246" t="n">
+        <v>190.58</v>
+      </c>
+      <c r="G246" t="n">
+        <v>189.58</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="J246" t="n">
+        <v>182.41</v>
+      </c>
+      <c r="K246" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2186</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2269.83</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-83.83</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2221.9</v>
+      </c>
+      <c r="G247" t="n">
+        <v>2237.93</v>
+      </c>
+      <c r="H247" t="n">
+        <v>-16.03</v>
+      </c>
+      <c r="I247" t="n">
+        <v>2179</v>
+      </c>
+      <c r="J247" t="n">
+        <v>2146.7</v>
+      </c>
+      <c r="K247" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>11254</v>
+      </c>
+      <c r="D248" t="n">
+        <v>11581.77</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-327.77</v>
+      </c>
+      <c r="F248" t="n">
+        <v>11435</v>
+      </c>
+      <c r="G248" t="n">
+        <v>11431.27</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I248" t="n">
+        <v>11211</v>
+      </c>
+      <c r="J248" t="n">
+        <v>11120.13</v>
+      </c>
+      <c r="K248" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>4064.3</v>
+      </c>
+      <c r="D249" t="n">
+        <v>4138.98</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-74.68000000000001</v>
+      </c>
+      <c r="F249" t="n">
+        <v>4085</v>
+      </c>
+      <c r="G249" t="n">
+        <v>4108.14</v>
+      </c>
+      <c r="H249" t="n">
+        <v>-23.14</v>
+      </c>
+      <c r="I249" t="n">
+        <v>4050</v>
+      </c>
+      <c r="J249" t="n">
+        <v>4031.31</v>
+      </c>
+      <c r="K249" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>518.25</v>
+      </c>
+      <c r="D250" t="n">
+        <v>569.2</v>
+      </c>
+      <c r="E250" t="n">
+        <v>-50.95</v>
+      </c>
+      <c r="F250" t="n">
+        <v>524.85</v>
+      </c>
+      <c r="G250" t="n">
+        <v>528.4299999999999</v>
+      </c>
+      <c r="H250" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I250" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="J250" t="n">
+        <v>510.55</v>
+      </c>
+      <c r="K250" t="n">
+        <v>7</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1163.6</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1201.92</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-38.32</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1191.64</v>
+      </c>
+      <c r="H251" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="I251" t="n">
+        <v>1154</v>
+      </c>
+      <c r="J251" t="n">
+        <v>1142.37</v>
+      </c>
+      <c r="K251" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>938</v>
+      </c>
+      <c r="D252" t="n">
+        <v>924.17</v>
+      </c>
+      <c r="E252" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="F252" t="n">
+        <v>961.35</v>
+      </c>
+      <c r="G252" t="n">
+        <v>959.45</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I252" t="n">
+        <v>933.1</v>
+      </c>
+      <c r="J252" t="n">
+        <v>921.76</v>
+      </c>
+      <c r="K252" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>875</v>
+      </c>
+      <c r="D253" t="n">
+        <v>900.36</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-25.36</v>
+      </c>
+      <c r="F253" t="n">
+        <v>887</v>
+      </c>
+      <c r="G253" t="n">
+        <v>892.08</v>
+      </c>
+      <c r="H253" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="I253" t="n">
+        <v>874</v>
+      </c>
+      <c r="J253" t="n">
+        <v>862.1</v>
+      </c>
+      <c r="K253" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -12254,31 +12254,31 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>5745.5</v>
+        <v>5745</v>
       </c>
       <c r="D228" t="n">
         <v>5646.15</v>
       </c>
       <c r="E228" t="n">
-        <v>99.34999999999999</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="F228" t="n">
-        <v>5778</v>
+        <v>5811.5</v>
       </c>
       <c r="G228" t="n">
         <v>5719.7</v>
       </c>
       <c r="H228" t="n">
-        <v>58.3</v>
+        <v>91.8</v>
       </c>
       <c r="I228" t="n">
-        <v>5694.5</v>
+        <v>5740</v>
       </c>
       <c r="J228" t="n">
         <v>5601.44</v>
       </c>
       <c r="K228" t="n">
-        <v>93.06</v>
+        <v>138.56</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="229">
@@ -12306,31 +12306,31 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2115</v>
+        <v>2081.3</v>
       </c>
       <c r="D229" t="n">
         <v>2149.79</v>
       </c>
       <c r="E229" t="n">
-        <v>-34.79</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="F229" t="n">
-        <v>2122</v>
+        <v>2110.9</v>
       </c>
       <c r="G229" t="n">
         <v>2149.79</v>
       </c>
       <c r="H229" t="n">
-        <v>-27.79</v>
+        <v>-38.89</v>
       </c>
       <c r="I229" t="n">
-        <v>2075.1</v>
+        <v>2072.4</v>
       </c>
       <c r="J229" t="n">
         <v>2098.65</v>
       </c>
       <c r="K229" t="n">
-        <v>-23.55</v>
+        <v>-26.25</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1.62</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="230">
@@ -12358,31 +12358,31 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1053</v>
+        <v>1061.2</v>
       </c>
       <c r="D230" t="n">
         <v>1064.05</v>
       </c>
       <c r="E230" t="n">
-        <v>-11.05</v>
+        <v>-2.85</v>
       </c>
       <c r="F230" t="n">
-        <v>1067.7</v>
+        <v>1068.8</v>
       </c>
       <c r="G230" t="n">
         <v>1064.71</v>
       </c>
       <c r="H230" t="n">
-        <v>2.99</v>
+        <v>4.09</v>
       </c>
       <c r="I230" t="n">
-        <v>1053</v>
+        <v>1052.4</v>
       </c>
       <c r="J230" t="n">
         <v>1042.38</v>
       </c>
       <c r="K230" t="n">
-        <v>10.62</v>
+        <v>10.02</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="231">
@@ -12410,31 +12410,31 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1273</v>
+        <v>1269.9</v>
       </c>
       <c r="D231" t="n">
         <v>1263.65</v>
       </c>
       <c r="E231" t="n">
-        <v>9.35</v>
+        <v>6.25</v>
       </c>
       <c r="F231" t="n">
-        <v>1281.2</v>
+        <v>1272</v>
       </c>
       <c r="G231" t="n">
         <v>1281.43</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.23</v>
+        <v>-9.43</v>
       </c>
       <c r="I231" t="n">
-        <v>1263</v>
+        <v>1235.9</v>
       </c>
       <c r="J231" t="n">
         <v>1254.36</v>
       </c>
       <c r="K231" t="n">
-        <v>8.640000000000001</v>
+        <v>-18.46</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="232">
@@ -12462,31 +12462,31 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1934.2</v>
+        <v>1969.3</v>
       </c>
       <c r="D232" t="n">
         <v>1886.72</v>
       </c>
       <c r="E232" t="n">
-        <v>47.48</v>
+        <v>82.58</v>
       </c>
       <c r="F232" t="n">
-        <v>1959.7</v>
+        <v>1993.2</v>
       </c>
       <c r="G232" t="n">
         <v>1967.12</v>
       </c>
       <c r="H232" t="n">
-        <v>-7.42</v>
+        <v>26.08</v>
       </c>
       <c r="I232" t="n">
-        <v>1923.2</v>
+        <v>1969.3</v>
       </c>
       <c r="J232" t="n">
         <v>1926.27</v>
       </c>
       <c r="K232" t="n">
-        <v>-3.07</v>
+        <v>43.03</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>2.52</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="233">
@@ -12514,31 +12514,31 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3421.5</v>
+        <v>3390.4</v>
       </c>
       <c r="D233" t="n">
         <v>3591.55</v>
       </c>
       <c r="E233" t="n">
-        <v>-170.05</v>
+        <v>-201.15</v>
       </c>
       <c r="F233" t="n">
-        <v>3435</v>
+        <v>3451.9</v>
       </c>
       <c r="G233" t="n">
         <v>3591.55</v>
       </c>
       <c r="H233" t="n">
-        <v>-156.55</v>
+        <v>-139.65</v>
       </c>
       <c r="I233" t="n">
-        <v>3390.2</v>
+        <v>3388.3</v>
       </c>
       <c r="J233" t="n">
         <v>3340.95</v>
       </c>
       <c r="K233" t="n">
-        <v>49.25</v>
+        <v>47.35</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>4.73</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="234">
@@ -12566,31 +12566,31 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>388</v>
+        <v>387.55</v>
       </c>
       <c r="D234" t="n">
         <v>355.09</v>
       </c>
       <c r="E234" t="n">
-        <v>32.91</v>
+        <v>32.46</v>
       </c>
       <c r="F234" t="n">
-        <v>390.85</v>
+        <v>391.5</v>
       </c>
       <c r="G234" t="n">
         <v>383.58</v>
       </c>
       <c r="H234" t="n">
-        <v>7.27</v>
+        <v>7.92</v>
       </c>
       <c r="I234" t="n">
-        <v>385.8</v>
+        <v>376.5</v>
       </c>
       <c r="J234" t="n">
         <v>375.23</v>
       </c>
       <c r="K234" t="n">
-        <v>10.57</v>
+        <v>1.27</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>9.27</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -12618,31 +12618,31 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>315.9</v>
+        <v>318</v>
       </c>
       <c r="D235" t="n">
         <v>337.44</v>
       </c>
       <c r="E235" t="n">
-        <v>-21.54</v>
+        <v>-19.44</v>
       </c>
       <c r="F235" t="n">
-        <v>321.2</v>
+        <v>321.9</v>
       </c>
       <c r="G235" t="n">
         <v>337.44</v>
       </c>
       <c r="H235" t="n">
-        <v>-16.24</v>
+        <v>-15.54</v>
       </c>
       <c r="I235" t="n">
-        <v>315.55</v>
+        <v>316.2</v>
       </c>
       <c r="J235" t="n">
         <v>315.62</v>
       </c>
       <c r="K235" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>6.38</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="236">
@@ -12670,31 +12670,31 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>116.5</v>
+        <v>117.32</v>
       </c>
       <c r="D236" t="n">
         <v>113.3</v>
       </c>
       <c r="E236" t="n">
-        <v>3.2</v>
+        <v>4.02</v>
       </c>
       <c r="F236" t="n">
-        <v>117.99</v>
+        <v>118.06</v>
       </c>
       <c r="G236" t="n">
         <v>118.51</v>
       </c>
       <c r="H236" t="n">
-        <v>-0.52</v>
+        <v>-0.45</v>
       </c>
       <c r="I236" t="n">
-        <v>116.5</v>
+        <v>115.32</v>
       </c>
       <c r="J236" t="n">
         <v>116.24</v>
       </c>
       <c r="K236" t="n">
-        <v>0.26</v>
+        <v>-0.92</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="237">
@@ -12722,31 +12722,31 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1773</v>
+        <v>1806</v>
       </c>
       <c r="D237" t="n">
         <v>1773.35</v>
       </c>
       <c r="E237" t="n">
-        <v>-0.35</v>
+        <v>32.65</v>
       </c>
       <c r="F237" t="n">
-        <v>1795</v>
+        <v>1821</v>
       </c>
       <c r="G237" t="n">
         <v>1773.35</v>
       </c>
       <c r="H237" t="n">
-        <v>21.65</v>
+        <v>47.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1762.2</v>
+        <v>1799.6</v>
       </c>
       <c r="J237" t="n">
         <v>1727.77</v>
       </c>
       <c r="K237" t="n">
-        <v>34.43</v>
+        <v>71.83</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>0.02</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="238">
@@ -12774,31 +12774,31 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>14150</v>
+        <v>14025</v>
       </c>
       <c r="D238" t="n">
         <v>14497.83</v>
       </c>
       <c r="E238" t="n">
-        <v>-347.83</v>
+        <v>-472.83</v>
       </c>
       <c r="F238" t="n">
-        <v>14420</v>
+        <v>14287</v>
       </c>
       <c r="G238" t="n">
         <v>14497.83</v>
       </c>
       <c r="H238" t="n">
-        <v>-77.83</v>
+        <v>-210.83</v>
       </c>
       <c r="I238" t="n">
-        <v>14066</v>
+        <v>14025</v>
       </c>
       <c r="J238" t="n">
         <v>13762.25</v>
       </c>
       <c r="K238" t="n">
-        <v>303.75</v>
+        <v>262.75</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>2.4</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="239">
@@ -12826,31 +12826,31 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1354.9</v>
+        <v>1355.8</v>
       </c>
       <c r="D239" t="n">
         <v>1368.46</v>
       </c>
       <c r="E239" t="n">
-        <v>-13.56</v>
+        <v>-12.66</v>
       </c>
       <c r="F239" t="n">
-        <v>1368.8</v>
+        <v>1374</v>
       </c>
       <c r="G239" t="n">
         <v>1368.46</v>
       </c>
       <c r="H239" t="n">
-        <v>0.34</v>
+        <v>5.54</v>
       </c>
       <c r="I239" t="n">
-        <v>1331.1</v>
+        <v>1340.7</v>
       </c>
       <c r="J239" t="n">
         <v>1320.97</v>
       </c>
       <c r="K239" t="n">
-        <v>10.13</v>
+        <v>19.73</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="240">
@@ -12878,31 +12878,31 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1592</v>
+        <v>1610</v>
       </c>
       <c r="D240" t="n">
         <v>1647.33</v>
       </c>
       <c r="E240" t="n">
-        <v>-55.33</v>
+        <v>-37.33</v>
       </c>
       <c r="F240" t="n">
-        <v>1608</v>
+        <v>1638.9</v>
       </c>
       <c r="G240" t="n">
         <v>1647.33</v>
       </c>
       <c r="H240" t="n">
-        <v>-39.33</v>
+        <v>-8.43</v>
       </c>
       <c r="I240" t="n">
-        <v>1579.9</v>
+        <v>1604.2</v>
       </c>
       <c r="J240" t="n">
         <v>1588.49</v>
       </c>
       <c r="K240" t="n">
-        <v>-8.59</v>
+        <v>15.71</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>3.36</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="241">
@@ -12930,31 +12930,31 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>176.35</v>
+        <v>177.1</v>
       </c>
       <c r="D241" t="n">
         <v>174.81</v>
       </c>
       <c r="E241" t="n">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="F241" t="n">
-        <v>177.59</v>
+        <v>179.1</v>
       </c>
       <c r="G241" t="n">
         <v>178.96</v>
       </c>
       <c r="H241" t="n">
-        <v>-1.37</v>
+        <v>0.14</v>
       </c>
       <c r="I241" t="n">
-        <v>174.5</v>
+        <v>171.98</v>
       </c>
       <c r="J241" t="n">
         <v>175.22</v>
       </c>
       <c r="K241" t="n">
-        <v>-0.72</v>
+        <v>-3.24</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0.88</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="242">
@@ -12982,31 +12982,31 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="D242" t="n">
         <v>2211.78</v>
       </c>
       <c r="E242" t="n">
-        <v>-25.78</v>
+        <v>-21.78</v>
       </c>
       <c r="F242" t="n">
-        <v>2221.9</v>
+        <v>2209.6</v>
       </c>
       <c r="G242" t="n">
         <v>2211.78</v>
       </c>
       <c r="H242" t="n">
-        <v>10.12</v>
+        <v>-2.18</v>
       </c>
       <c r="I242" t="n">
-        <v>2179</v>
+        <v>2172.4</v>
       </c>
       <c r="J242" t="n">
         <v>2126.27</v>
       </c>
       <c r="K242" t="n">
-        <v>52.73</v>
+        <v>46.13</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>1.17</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="243">
@@ -13034,31 +13034,31 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2011.2</v>
+        <v>2005</v>
       </c>
       <c r="D243" t="n">
         <v>1995.77</v>
       </c>
       <c r="E243" t="n">
-        <v>15.43</v>
+        <v>9.23</v>
       </c>
       <c r="F243" t="n">
-        <v>2018.8</v>
+        <v>2028.2</v>
       </c>
       <c r="G243" t="n">
         <v>1995.77</v>
       </c>
       <c r="H243" t="n">
-        <v>23.03</v>
+        <v>32.43</v>
       </c>
       <c r="I243" t="n">
-        <v>1998</v>
+        <v>1997.2</v>
       </c>
       <c r="J243" t="n">
         <v>1962.36</v>
       </c>
       <c r="K243" t="n">
-        <v>35.64</v>
+        <v>34.84</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="244">
@@ -13086,31 +13086,31 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>11254</v>
+        <v>11379</v>
       </c>
       <c r="D244" t="n">
         <v>11378.06</v>
       </c>
       <c r="E244" t="n">
-        <v>-124.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F244" t="n">
-        <v>11435</v>
+        <v>11574</v>
       </c>
       <c r="G244" t="n">
         <v>11442.61</v>
       </c>
       <c r="H244" t="n">
-        <v>-7.61</v>
+        <v>131.39</v>
       </c>
       <c r="I244" t="n">
-        <v>11211</v>
+        <v>11306</v>
       </c>
       <c r="J244" t="n">
         <v>11204.88</v>
       </c>
       <c r="K244" t="n">
-        <v>6.12</v>
+        <v>101.12</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1.09</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="245">
@@ -13138,31 +13138,31 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>4064.3</v>
+        <v>4086.7</v>
       </c>
       <c r="D245" t="n">
         <v>4086.98</v>
       </c>
       <c r="E245" t="n">
-        <v>-22.68</v>
+        <v>-0.28</v>
       </c>
       <c r="F245" t="n">
-        <v>4085</v>
+        <v>4086.7</v>
       </c>
       <c r="G245" t="n">
         <v>4086.98</v>
       </c>
       <c r="H245" t="n">
-        <v>-1.98</v>
+        <v>-0.28</v>
       </c>
       <c r="I245" t="n">
-        <v>4050</v>
+        <v>4026</v>
       </c>
       <c r="J245" t="n">
         <v>4006.69</v>
       </c>
       <c r="K245" t="n">
-        <v>43.31</v>
+        <v>19.31</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.55</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="246">
@@ -13190,31 +13190,31 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>286.25</v>
+        <v>281.8</v>
       </c>
       <c r="D246" t="n">
         <v>283.02</v>
       </c>
       <c r="E246" t="n">
-        <v>3.23</v>
+        <v>-1.22</v>
       </c>
       <c r="F246" t="n">
-        <v>286.95</v>
+        <v>286.4</v>
       </c>
       <c r="G246" t="n">
         <v>286.47</v>
       </c>
       <c r="H246" t="n">
-        <v>0.48</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I246" t="n">
-        <v>281.8</v>
+        <v>281.65</v>
       </c>
       <c r="J246" t="n">
         <v>280.36</v>
       </c>
       <c r="K246" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="247">
@@ -13242,31 +13242,31 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>7546</v>
+        <v>7660</v>
       </c>
       <c r="D247" t="n">
         <v>7465.8</v>
       </c>
       <c r="E247" t="n">
-        <v>80.2</v>
+        <v>194.2</v>
       </c>
       <c r="F247" t="n">
-        <v>7734</v>
+        <v>7760</v>
       </c>
       <c r="G247" t="n">
         <v>7656.55</v>
       </c>
       <c r="H247" t="n">
-        <v>77.45</v>
+        <v>103.45</v>
       </c>
       <c r="I247" t="n">
-        <v>7528.5</v>
+        <v>7627</v>
       </c>
       <c r="J247" t="n">
         <v>7496.93</v>
       </c>
       <c r="K247" t="n">
-        <v>31.57</v>
+        <v>130.07</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>1.07</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="248">
@@ -13294,31 +13294,31 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>185.5</v>
+        <v>188.9</v>
       </c>
       <c r="D248" t="n">
         <v>183.49</v>
       </c>
       <c r="E248" t="n">
-        <v>2.01</v>
+        <v>5.41</v>
       </c>
       <c r="F248" t="n">
-        <v>190.58</v>
+        <v>190.15</v>
       </c>
       <c r="G248" t="n">
         <v>187.1</v>
       </c>
       <c r="H248" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="I248" t="n">
-        <v>185.5</v>
+        <v>184.27</v>
       </c>
       <c r="J248" t="n">
         <v>183.15</v>
       </c>
       <c r="K248" t="n">
-        <v>2.35</v>
+        <v>1.12</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1.1</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="249">
@@ -13346,31 +13346,31 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1041.6</v>
+        <v>1049.9</v>
       </c>
       <c r="D249" t="n">
         <v>996.48</v>
       </c>
       <c r="E249" t="n">
-        <v>45.12</v>
+        <v>53.42</v>
       </c>
       <c r="F249" t="n">
-        <v>1050.6</v>
+        <v>1060</v>
       </c>
       <c r="G249" t="n">
         <v>1061.43</v>
       </c>
       <c r="H249" t="n">
-        <v>-10.83</v>
+        <v>-1.43</v>
       </c>
       <c r="I249" t="n">
-        <v>1038</v>
+        <v>1032.7</v>
       </c>
       <c r="J249" t="n">
         <v>1039.46</v>
       </c>
       <c r="K249" t="n">
-        <v>-1.46</v>
+        <v>-6.76</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>4.53</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="250">
@@ -13398,31 +13398,31 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1163.6</v>
+        <v>1173</v>
       </c>
       <c r="D250" t="n">
         <v>1170.76</v>
       </c>
       <c r="E250" t="n">
-        <v>-7.16</v>
+        <v>2.24</v>
       </c>
       <c r="F250" t="n">
-        <v>1185</v>
+        <v>1174.7</v>
       </c>
       <c r="G250" t="n">
         <v>1170.76</v>
       </c>
       <c r="H250" t="n">
-        <v>14.24</v>
+        <v>3.94</v>
       </c>
       <c r="I250" t="n">
-        <v>1154</v>
+        <v>1150.5</v>
       </c>
       <c r="J250" t="n">
         <v>1141.13</v>
       </c>
       <c r="K250" t="n">
-        <v>12.87</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="251">
@@ -13450,31 +13450,31 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>875</v>
+        <v>881.2</v>
       </c>
       <c r="D251" t="n">
         <v>881.13</v>
       </c>
       <c r="E251" t="n">
-        <v>-6.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F251" t="n">
-        <v>887</v>
+        <v>891.8</v>
       </c>
       <c r="G251" t="n">
         <v>881.67</v>
       </c>
       <c r="H251" t="n">
-        <v>5.33</v>
+        <v>10.13</v>
       </c>
       <c r="I251" t="n">
-        <v>874</v>
+        <v>870.3</v>
       </c>
       <c r="J251" t="n">
         <v>863.08</v>
       </c>
       <c r="K251" t="n">
-        <v>10.92</v>
+        <v>7.22</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="252">
@@ -13502,31 +13502,31 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>518.25</v>
+        <v>524.5</v>
       </c>
       <c r="D252" t="n">
         <v>556.98</v>
       </c>
       <c r="E252" t="n">
-        <v>-38.73</v>
+        <v>-32.48</v>
       </c>
       <c r="F252" t="n">
-        <v>524.85</v>
+        <v>530</v>
       </c>
       <c r="G252" t="n">
         <v>556.98</v>
       </c>
       <c r="H252" t="n">
-        <v>-32.13</v>
+        <v>-26.98</v>
       </c>
       <c r="I252" t="n">
-        <v>517.55</v>
+        <v>518.3</v>
       </c>
       <c r="J252" t="n">
         <v>506.25</v>
       </c>
       <c r="K252" t="n">
-        <v>11.3</v>
+        <v>12.05</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>6.95</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="253">
@@ -13554,31 +13554,31 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="D253" t="n">
         <v>901.35</v>
       </c>
       <c r="E253" t="n">
-        <v>36.65</v>
+        <v>53.65</v>
       </c>
       <c r="F253" t="n">
-        <v>961.35</v>
+        <v>964</v>
       </c>
       <c r="G253" t="n">
         <v>901.35</v>
       </c>
       <c r="H253" t="n">
-        <v>60</v>
+        <v>62.65</v>
       </c>
       <c r="I253" t="n">
-        <v>933.1</v>
+        <v>897.1</v>
       </c>
       <c r="J253" t="n">
         <v>913.21</v>
       </c>
       <c r="K253" t="n">
-        <v>19.89</v>
+        <v>-16.11</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>4.07</v>
+        <v>5.95</v>
       </c>
     </row>
   </sheetData>
@@ -14628,31 +14628,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24154.9</v>
+        <v>24287.65</v>
       </c>
       <c r="D20" t="n">
         <v>24154.9</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>132.75</v>
       </c>
       <c r="F20" t="n">
-        <v>24269.65</v>
+        <v>24360.1</v>
       </c>
       <c r="G20" t="n">
         <v>24231.4</v>
       </c>
       <c r="H20" t="n">
-        <v>38.25</v>
+        <v>128.7</v>
       </c>
       <c r="I20" t="n">
-        <v>24154.9</v>
+        <v>24226.95</v>
       </c>
       <c r="J20" t="n">
         <v>24116.65</v>
       </c>
       <c r="K20" t="n">
-        <v>38.25</v>
+        <v>110.3</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="21">
@@ -14680,31 +14680,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57262.4</v>
+        <v>57497.8</v>
       </c>
       <c r="D21" t="n">
         <v>57262.4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>235.4</v>
       </c>
       <c r="F21" t="n">
-        <v>57584.7</v>
+        <v>57757.25</v>
       </c>
       <c r="G21" t="n">
         <v>57492.2</v>
       </c>
       <c r="H21" t="n">
-        <v>92.5</v>
+        <v>265.05</v>
       </c>
       <c r="I21" t="n">
-        <v>57217.6</v>
+        <v>57119.6</v>
       </c>
       <c r="J21" t="n">
         <v>57125.1</v>
       </c>
       <c r="K21" t="n">
-        <v>92.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -26570,31 +26570,31 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>5745.5</v>
+        <v>5745</v>
       </c>
       <c r="D228" t="n">
         <v>5781.28</v>
       </c>
       <c r="E228" t="n">
-        <v>-35.78</v>
+        <v>-36.28</v>
       </c>
       <c r="F228" t="n">
-        <v>5778</v>
+        <v>5811.5</v>
       </c>
       <c r="G228" t="n">
         <v>5869.22</v>
       </c>
       <c r="H228" t="n">
-        <v>-91.22</v>
+        <v>-57.72</v>
       </c>
       <c r="I228" t="n">
-        <v>5694.5</v>
+        <v>5740</v>
       </c>
       <c r="J228" t="n">
         <v>5651.9</v>
       </c>
       <c r="K228" t="n">
-        <v>42.6</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="229">
@@ -26622,31 +26622,31 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>3421.5</v>
+        <v>3390.4</v>
       </c>
       <c r="D229" t="n">
         <v>3671.86</v>
       </c>
       <c r="E229" t="n">
-        <v>-250.36</v>
+        <v>-281.46</v>
       </c>
       <c r="F229" t="n">
-        <v>3435</v>
+        <v>3451.9</v>
       </c>
       <c r="G229" t="n">
         <v>3490.02</v>
       </c>
       <c r="H229" t="n">
-        <v>-55.02</v>
+        <v>-38.12</v>
       </c>
       <c r="I229" t="n">
-        <v>3390.2</v>
+        <v>3388.3</v>
       </c>
       <c r="J229" t="n">
         <v>3369.68</v>
       </c>
       <c r="K229" t="n">
-        <v>20.52</v>
+        <v>18.62</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>6.82</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="230">
@@ -26674,31 +26674,31 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>388</v>
+        <v>387.55</v>
       </c>
       <c r="D230" t="n">
         <v>368.12</v>
       </c>
       <c r="E230" t="n">
-        <v>19.88</v>
+        <v>19.43</v>
       </c>
       <c r="F230" t="n">
-        <v>390.85</v>
+        <v>391.5</v>
       </c>
       <c r="G230" t="n">
         <v>401.1</v>
       </c>
       <c r="H230" t="n">
-        <v>-10.25</v>
+        <v>-9.6</v>
       </c>
       <c r="I230" t="n">
-        <v>385.8</v>
+        <v>376.5</v>
       </c>
       <c r="J230" t="n">
         <v>378.07</v>
       </c>
       <c r="K230" t="n">
-        <v>7.73</v>
+        <v>-1.57</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>5.4</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="231">
@@ -26726,31 +26726,31 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>315.9</v>
+        <v>318</v>
       </c>
       <c r="D231" t="n">
         <v>344.91</v>
       </c>
       <c r="E231" t="n">
-        <v>-29.01</v>
+        <v>-26.91</v>
       </c>
       <c r="F231" t="n">
-        <v>321.2</v>
+        <v>321.9</v>
       </c>
       <c r="G231" t="n">
         <v>322.62</v>
       </c>
       <c r="H231" t="n">
-        <v>-1.42</v>
+        <v>-0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>315.55</v>
+        <v>316.2</v>
       </c>
       <c r="J231" t="n">
         <v>310.81</v>
       </c>
       <c r="K231" t="n">
-        <v>4.74</v>
+        <v>5.39</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>8.41</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="232">
@@ -26778,31 +26778,31 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1273</v>
+        <v>1269.9</v>
       </c>
       <c r="D232" t="n">
         <v>1293.65</v>
       </c>
       <c r="E232" t="n">
-        <v>-20.65</v>
+        <v>-23.75</v>
       </c>
       <c r="F232" t="n">
-        <v>1281.2</v>
+        <v>1272</v>
       </c>
       <c r="G232" t="n">
         <v>1300.18</v>
       </c>
       <c r="H232" t="n">
-        <v>-18.98</v>
+        <v>-28.18</v>
       </c>
       <c r="I232" t="n">
-        <v>1263</v>
+        <v>1235.9</v>
       </c>
       <c r="J232" t="n">
         <v>1252.44</v>
       </c>
       <c r="K232" t="n">
-        <v>10.56</v>
+        <v>-16.54</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="233">
@@ -26830,31 +26830,31 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>116.5</v>
+        <v>117.32</v>
       </c>
       <c r="D233" t="n">
         <v>115.01</v>
       </c>
       <c r="E233" t="n">
-        <v>1.49</v>
+        <v>2.31</v>
       </c>
       <c r="F233" t="n">
-        <v>117.99</v>
+        <v>118.06</v>
       </c>
       <c r="G233" t="n">
         <v>118.05</v>
       </c>
       <c r="H233" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I233" t="n">
-        <v>116.5</v>
+        <v>115.32</v>
       </c>
       <c r="J233" t="n">
         <v>115.34</v>
       </c>
       <c r="K233" t="n">
-        <v>1.16</v>
+        <v>-0.02</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1.3</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="234">
@@ -26882,31 +26882,31 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1934.2</v>
+        <v>1969.3</v>
       </c>
       <c r="D234" t="n">
         <v>1922.83</v>
       </c>
       <c r="E234" t="n">
-        <v>11.37</v>
+        <v>46.47</v>
       </c>
       <c r="F234" t="n">
-        <v>1959.7</v>
+        <v>1993.2</v>
       </c>
       <c r="G234" t="n">
         <v>1966.97</v>
       </c>
       <c r="H234" t="n">
-        <v>-7.27</v>
+        <v>26.23</v>
       </c>
       <c r="I234" t="n">
-        <v>1923.2</v>
+        <v>1969.3</v>
       </c>
       <c r="J234" t="n">
         <v>1909.43</v>
       </c>
       <c r="K234" t="n">
-        <v>13.77</v>
+        <v>59.87</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>0.59</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="235">
@@ -26934,31 +26934,31 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>2115</v>
+        <v>2081.3</v>
       </c>
       <c r="D235" t="n">
         <v>2209.62</v>
       </c>
       <c r="E235" t="n">
-        <v>-94.62</v>
+        <v>-128.32</v>
       </c>
       <c r="F235" t="n">
-        <v>2122</v>
+        <v>2110.9</v>
       </c>
       <c r="G235" t="n">
         <v>2168.45</v>
       </c>
       <c r="H235" t="n">
-        <v>-46.45</v>
+        <v>-57.55</v>
       </c>
       <c r="I235" t="n">
-        <v>2075.1</v>
+        <v>2072.4</v>
       </c>
       <c r="J235" t="n">
         <v>2074.53</v>
       </c>
       <c r="K235" t="n">
-        <v>0.57</v>
+        <v>-2.13</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>4.28</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="236">
@@ -26986,31 +26986,31 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1053</v>
+        <v>1061.2</v>
       </c>
       <c r="D236" t="n">
         <v>1084.12</v>
       </c>
       <c r="E236" t="n">
-        <v>-31.12</v>
+        <v>-22.92</v>
       </c>
       <c r="F236" t="n">
-        <v>1067.7</v>
+        <v>1068.8</v>
       </c>
       <c r="G236" t="n">
         <v>1070.55</v>
       </c>
       <c r="H236" t="n">
-        <v>-2.85</v>
+        <v>-1.75</v>
       </c>
       <c r="I236" t="n">
-        <v>1053</v>
+        <v>1052.4</v>
       </c>
       <c r="J236" t="n">
         <v>1039.74</v>
       </c>
       <c r="K236" t="n">
-        <v>13.26</v>
+        <v>12.66</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -27019,11 +27019,11 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>2.87</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="237">
@@ -27038,31 +27038,31 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>14150</v>
+        <v>14025</v>
       </c>
       <c r="D237" t="n">
         <v>14879.56</v>
       </c>
       <c r="E237" t="n">
-        <v>-729.5599999999999</v>
+        <v>-854.5599999999999</v>
       </c>
       <c r="F237" t="n">
-        <v>14420</v>
+        <v>14287</v>
       </c>
       <c r="G237" t="n">
         <v>14487.22</v>
       </c>
       <c r="H237" t="n">
-        <v>-67.22</v>
+        <v>-200.22</v>
       </c>
       <c r="I237" t="n">
-        <v>14066</v>
+        <v>14025</v>
       </c>
       <c r="J237" t="n">
         <v>13894.74</v>
       </c>
       <c r="K237" t="n">
-        <v>171.26</v>
+        <v>130.26</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>4.9</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="238">
@@ -27090,31 +27090,31 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1041.6</v>
+        <v>1049.9</v>
       </c>
       <c r="D238" t="n">
         <v>1022.18</v>
       </c>
       <c r="E238" t="n">
-        <v>19.42</v>
+        <v>27.72</v>
       </c>
       <c r="F238" t="n">
-        <v>1050.6</v>
+        <v>1060</v>
       </c>
       <c r="G238" t="n">
         <v>1066.28</v>
       </c>
       <c r="H238" t="n">
-        <v>-15.68</v>
+        <v>-6.28</v>
       </c>
       <c r="I238" t="n">
-        <v>1038</v>
+        <v>1032.7</v>
       </c>
       <c r="J238" t="n">
         <v>1022.91</v>
       </c>
       <c r="K238" t="n">
-        <v>15.09</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>1.9</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="239">
@@ -27142,31 +27142,31 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1592</v>
+        <v>1610</v>
       </c>
       <c r="D239" t="n">
         <v>1682.28</v>
       </c>
       <c r="E239" t="n">
-        <v>-90.28</v>
+        <v>-72.28</v>
       </c>
       <c r="F239" t="n">
-        <v>1608</v>
+        <v>1638.9</v>
       </c>
       <c r="G239" t="n">
         <v>1622.48</v>
       </c>
       <c r="H239" t="n">
-        <v>-14.48</v>
+        <v>16.42</v>
       </c>
       <c r="I239" t="n">
-        <v>1579.9</v>
+        <v>1604.2</v>
       </c>
       <c r="J239" t="n">
         <v>1568.95</v>
       </c>
       <c r="K239" t="n">
-        <v>10.95</v>
+        <v>35.25</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>5.37</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="240">
@@ -27194,31 +27194,31 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>176.35</v>
+        <v>177.1</v>
       </c>
       <c r="D240" t="n">
         <v>180.2</v>
       </c>
       <c r="E240" t="n">
-        <v>-3.85</v>
+        <v>-3.1</v>
       </c>
       <c r="F240" t="n">
-        <v>177.59</v>
+        <v>179.1</v>
       </c>
       <c r="G240" t="n">
         <v>181.33</v>
       </c>
       <c r="H240" t="n">
-        <v>-3.74</v>
+        <v>-2.23</v>
       </c>
       <c r="I240" t="n">
-        <v>174.5</v>
+        <v>171.98</v>
       </c>
       <c r="J240" t="n">
         <v>172.58</v>
       </c>
       <c r="K240" t="n">
-        <v>1.92</v>
+        <v>-0.6</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="241">
@@ -27246,31 +27246,31 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>2011.2</v>
+        <v>2005</v>
       </c>
       <c r="D241" t="n">
         <v>2041.92</v>
       </c>
       <c r="E241" t="n">
-        <v>-30.72</v>
+        <v>-36.92</v>
       </c>
       <c r="F241" t="n">
-        <v>2018.8</v>
+        <v>2028.2</v>
       </c>
       <c r="G241" t="n">
         <v>2052.95</v>
       </c>
       <c r="H241" t="n">
-        <v>-34.15</v>
+        <v>-24.75</v>
       </c>
       <c r="I241" t="n">
-        <v>1998</v>
+        <v>1997.2</v>
       </c>
       <c r="J241" t="n">
         <v>1979.62</v>
       </c>
       <c r="K241" t="n">
-        <v>18.38</v>
+        <v>17.58</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="242">
@@ -27298,31 +27298,31 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1773</v>
+        <v>1806</v>
       </c>
       <c r="D242" t="n">
         <v>1831.33</v>
       </c>
       <c r="E242" t="n">
-        <v>-58.33</v>
+        <v>-25.33</v>
       </c>
       <c r="F242" t="n">
-        <v>1795</v>
+        <v>1821</v>
       </c>
       <c r="G242" t="n">
         <v>1826.08</v>
       </c>
       <c r="H242" t="n">
-        <v>-31.08</v>
+        <v>-5.08</v>
       </c>
       <c r="I242" t="n">
-        <v>1762.2</v>
+        <v>1799.6</v>
       </c>
       <c r="J242" t="n">
         <v>1732.79</v>
       </c>
       <c r="K242" t="n">
-        <v>29.41</v>
+        <v>66.81</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -27331,11 +27331,11 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>3.19</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="243">
@@ -27350,31 +27350,31 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>286.25</v>
+        <v>281.8</v>
       </c>
       <c r="D243" t="n">
         <v>288.61</v>
       </c>
       <c r="E243" t="n">
-        <v>-2.36</v>
+        <v>-6.81</v>
       </c>
       <c r="F243" t="n">
-        <v>286.95</v>
+        <v>286.4</v>
       </c>
       <c r="G243" t="n">
         <v>291.27</v>
       </c>
       <c r="H243" t="n">
-        <v>-4.32</v>
+        <v>-4.87</v>
       </c>
       <c r="I243" t="n">
-        <v>281.8</v>
+        <v>281.65</v>
       </c>
       <c r="J243" t="n">
         <v>282.46</v>
       </c>
       <c r="K243" t="n">
-        <v>-0.66</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0.82</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="244">
@@ -27402,31 +27402,31 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1354.9</v>
+        <v>1355.8</v>
       </c>
       <c r="D244" t="n">
         <v>1412.39</v>
       </c>
       <c r="E244" t="n">
-        <v>-57.49</v>
+        <v>-56.59</v>
       </c>
       <c r="F244" t="n">
-        <v>1368.8</v>
+        <v>1374</v>
       </c>
       <c r="G244" t="n">
         <v>1394.68</v>
       </c>
       <c r="H244" t="n">
-        <v>-25.88</v>
+        <v>-20.68</v>
       </c>
       <c r="I244" t="n">
-        <v>1331.1</v>
+        <v>1340.7</v>
       </c>
       <c r="J244" t="n">
         <v>1324.77</v>
       </c>
       <c r="K244" t="n">
-        <v>6.33</v>
+        <v>15.93</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="245">
@@ -27454,31 +27454,31 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>7546</v>
+        <v>7660</v>
       </c>
       <c r="D245" t="n">
         <v>7650.54</v>
       </c>
       <c r="E245" t="n">
-        <v>-104.54</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F245" t="n">
-        <v>7734</v>
+        <v>7760</v>
       </c>
       <c r="G245" t="n">
         <v>7714.35</v>
       </c>
       <c r="H245" t="n">
-        <v>19.65</v>
+        <v>45.65</v>
       </c>
       <c r="I245" t="n">
-        <v>7528.5</v>
+        <v>7627</v>
       </c>
       <c r="J245" t="n">
         <v>7418.61</v>
       </c>
       <c r="K245" t="n">
-        <v>109.89</v>
+        <v>208.39</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1.37</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="246">
@@ -27506,31 +27506,31 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>185.5</v>
+        <v>188.9</v>
       </c>
       <c r="D246" t="n">
         <v>187.98</v>
       </c>
       <c r="E246" t="n">
-        <v>-2.48</v>
+        <v>0.92</v>
       </c>
       <c r="F246" t="n">
-        <v>190.58</v>
+        <v>190.15</v>
       </c>
       <c r="G246" t="n">
         <v>189.58</v>
       </c>
       <c r="H246" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="I246" t="n">
-        <v>185.5</v>
+        <v>184.27</v>
       </c>
       <c r="J246" t="n">
         <v>182.41</v>
       </c>
       <c r="K246" t="n">
-        <v>3.09</v>
+        <v>1.86</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1.32</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="247">
@@ -27558,31 +27558,31 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="D247" t="n">
         <v>2269.83</v>
       </c>
       <c r="E247" t="n">
-        <v>-83.83</v>
+        <v>-79.83</v>
       </c>
       <c r="F247" t="n">
-        <v>2221.9</v>
+        <v>2209.6</v>
       </c>
       <c r="G247" t="n">
         <v>2237.93</v>
       </c>
       <c r="H247" t="n">
-        <v>-16.03</v>
+        <v>-28.33</v>
       </c>
       <c r="I247" t="n">
-        <v>2179</v>
+        <v>2172.4</v>
       </c>
       <c r="J247" t="n">
         <v>2146.7</v>
       </c>
       <c r="K247" t="n">
-        <v>32.3</v>
+        <v>25.7</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>3.69</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="248">
@@ -27610,31 +27610,31 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>11254</v>
+        <v>11379</v>
       </c>
       <c r="D248" t="n">
         <v>11581.77</v>
       </c>
       <c r="E248" t="n">
-        <v>-327.77</v>
+        <v>-202.77</v>
       </c>
       <c r="F248" t="n">
-        <v>11435</v>
+        <v>11574</v>
       </c>
       <c r="G248" t="n">
         <v>11431.27</v>
       </c>
       <c r="H248" t="n">
-        <v>3.73</v>
+        <v>142.73</v>
       </c>
       <c r="I248" t="n">
-        <v>11211</v>
+        <v>11306</v>
       </c>
       <c r="J248" t="n">
         <v>11120.13</v>
       </c>
       <c r="K248" t="n">
-        <v>90.87</v>
+        <v>185.87</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -27643,11 +27643,11 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2.83</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="249">
@@ -27662,31 +27662,31 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4064.3</v>
+        <v>4086.7</v>
       </c>
       <c r="D249" t="n">
         <v>4138.98</v>
       </c>
       <c r="E249" t="n">
-        <v>-74.68000000000001</v>
+        <v>-52.28</v>
       </c>
       <c r="F249" t="n">
-        <v>4085</v>
+        <v>4086.7</v>
       </c>
       <c r="G249" t="n">
         <v>4108.14</v>
       </c>
       <c r="H249" t="n">
-        <v>-23.14</v>
+        <v>-21.44</v>
       </c>
       <c r="I249" t="n">
-        <v>4050</v>
+        <v>4026</v>
       </c>
       <c r="J249" t="n">
         <v>4031.31</v>
       </c>
       <c r="K249" t="n">
-        <v>18.69</v>
+        <v>-5.31</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="250">
@@ -27714,31 +27714,31 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>518.25</v>
+        <v>524.5</v>
       </c>
       <c r="D250" t="n">
         <v>569.2</v>
       </c>
       <c r="E250" t="n">
-        <v>-50.95</v>
+        <v>-44.7</v>
       </c>
       <c r="F250" t="n">
-        <v>524.85</v>
+        <v>530</v>
       </c>
       <c r="G250" t="n">
         <v>528.4299999999999</v>
       </c>
       <c r="H250" t="n">
-        <v>-3.58</v>
+        <v>1.57</v>
       </c>
       <c r="I250" t="n">
-        <v>517.55</v>
+        <v>518.3</v>
       </c>
       <c r="J250" t="n">
         <v>510.55</v>
       </c>
       <c r="K250" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>8.949999999999999</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="251">
@@ -27766,31 +27766,31 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1163.6</v>
+        <v>1173</v>
       </c>
       <c r="D251" t="n">
         <v>1201.92</v>
       </c>
       <c r="E251" t="n">
-        <v>-38.32</v>
+        <v>-28.92</v>
       </c>
       <c r="F251" t="n">
-        <v>1185</v>
+        <v>1174.7</v>
       </c>
       <c r="G251" t="n">
         <v>1191.64</v>
       </c>
       <c r="H251" t="n">
-        <v>-6.64</v>
+        <v>-16.94</v>
       </c>
       <c r="I251" t="n">
-        <v>1154</v>
+        <v>1150.5</v>
       </c>
       <c r="J251" t="n">
         <v>1142.37</v>
       </c>
       <c r="K251" t="n">
-        <v>11.63</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -27799,11 +27799,11 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>3.19</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="252">
@@ -27818,31 +27818,31 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="D252" t="n">
         <v>924.17</v>
       </c>
       <c r="E252" t="n">
-        <v>13.83</v>
+        <v>30.83</v>
       </c>
       <c r="F252" t="n">
-        <v>961.35</v>
+        <v>964</v>
       </c>
       <c r="G252" t="n">
         <v>959.45</v>
       </c>
       <c r="H252" t="n">
-        <v>1.9</v>
+        <v>4.55</v>
       </c>
       <c r="I252" t="n">
-        <v>933.1</v>
+        <v>897.1</v>
       </c>
       <c r="J252" t="n">
         <v>921.76</v>
       </c>
       <c r="K252" t="n">
-        <v>11.34</v>
+        <v>-24.66</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1.5</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="253">
@@ -27870,31 +27870,31 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>875</v>
+        <v>881.2</v>
       </c>
       <c r="D253" t="n">
         <v>900.36</v>
       </c>
       <c r="E253" t="n">
-        <v>-25.36</v>
+        <v>-19.16</v>
       </c>
       <c r="F253" t="n">
-        <v>887</v>
+        <v>891.8</v>
       </c>
       <c r="G253" t="n">
         <v>892.08</v>
       </c>
       <c r="H253" t="n">
-        <v>-5.08</v>
+        <v>-0.28</v>
       </c>
       <c r="I253" t="n">
-        <v>874</v>
+        <v>870.3</v>
       </c>
       <c r="J253" t="n">
         <v>862.1</v>
       </c>
       <c r="K253" t="n">
-        <v>11.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -27903,11 +27903,11 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N253" t="n">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N253"/>
+  <dimension ref="A1:N279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13592,6 +13592,1358 @@
       </c>
       <c r="N253" t="n">
         <v>5.95</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="D254" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="E254" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="F254" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="G254" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="H254" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="I254" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="J254" t="n">
+        <v>117.34</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>11774</v>
+      </c>
+      <c r="D255" t="n">
+        <v>11809.19</v>
+      </c>
+      <c r="E255" t="n">
+        <v>-35.19</v>
+      </c>
+      <c r="F255" t="n">
+        <v>11854</v>
+      </c>
+      <c r="G255" t="n">
+        <v>12117.36</v>
+      </c>
+      <c r="H255" t="n">
+        <v>-263.36</v>
+      </c>
+      <c r="I255" t="n">
+        <v>11640</v>
+      </c>
+      <c r="J255" t="n">
+        <v>11774</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-134</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="D256" t="n">
+        <v>194.91</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="F256" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="G256" t="n">
+        <v>194.91</v>
+      </c>
+      <c r="H256" t="n">
+        <v>-7.31</v>
+      </c>
+      <c r="I256" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="J256" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1376.58</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1376.58</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I257" t="n">
+        <v>1351.5</v>
+      </c>
+      <c r="J257" t="n">
+        <v>1338.45</v>
+      </c>
+      <c r="K257" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>1272</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1288.53</v>
+      </c>
+      <c r="E258" t="n">
+        <v>-16.53</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1288</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1288.53</v>
+      </c>
+      <c r="H258" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="I258" t="n">
+        <v>1259</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1243.88</v>
+      </c>
+      <c r="K258" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2121.8</v>
+      </c>
+      <c r="D259" t="n">
+        <v>2070.63</v>
+      </c>
+      <c r="E259" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="F259" t="n">
+        <v>2121.8</v>
+      </c>
+      <c r="G259" t="n">
+        <v>2130.79</v>
+      </c>
+      <c r="H259" t="n">
+        <v>-8.99</v>
+      </c>
+      <c r="I259" t="n">
+        <v>2097.2</v>
+      </c>
+      <c r="J259" t="n">
+        <v>2072.54</v>
+      </c>
+      <c r="K259" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D260" t="n">
+        <v>2037.47</v>
+      </c>
+      <c r="E260" t="n">
+        <v>-25.47</v>
+      </c>
+      <c r="F260" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G260" t="n">
+        <v>2037.47</v>
+      </c>
+      <c r="H260" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1968.74</v>
+      </c>
+      <c r="K260" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1813.1</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1861.25</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-48.15</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1861.25</v>
+      </c>
+      <c r="H261" t="n">
+        <v>-43.25</v>
+      </c>
+      <c r="I261" t="n">
+        <v>1785.4</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1767.88</v>
+      </c>
+      <c r="K261" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>320</v>
+      </c>
+      <c r="D262" t="n">
+        <v>303.98</v>
+      </c>
+      <c r="E262" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="F262" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="G262" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="H262" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="I262" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="J262" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>14462</v>
+      </c>
+      <c r="D263" t="n">
+        <v>14102.32</v>
+      </c>
+      <c r="E263" t="n">
+        <v>359.68</v>
+      </c>
+      <c r="F263" t="n">
+        <v>14550</v>
+      </c>
+      <c r="G263" t="n">
+        <v>14407.41</v>
+      </c>
+      <c r="H263" t="n">
+        <v>142.59</v>
+      </c>
+      <c r="I263" t="n">
+        <v>14026</v>
+      </c>
+      <c r="J263" t="n">
+        <v>14110.8</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-84.8</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>5709.5</v>
+      </c>
+      <c r="D264" t="n">
+        <v>5855.95</v>
+      </c>
+      <c r="E264" t="n">
+        <v>-146.45</v>
+      </c>
+      <c r="F264" t="n">
+        <v>5767.5</v>
+      </c>
+      <c r="G264" t="n">
+        <v>5855.95</v>
+      </c>
+      <c r="H264" t="n">
+        <v>-88.45</v>
+      </c>
+      <c r="I264" t="n">
+        <v>5664.5</v>
+      </c>
+      <c r="J264" t="n">
+        <v>5574.16</v>
+      </c>
+      <c r="K264" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="D265" t="n">
+        <v>425.26</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-38.71</v>
+      </c>
+      <c r="F265" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="G265" t="n">
+        <v>425.26</v>
+      </c>
+      <c r="H265" t="n">
+        <v>-38.71</v>
+      </c>
+      <c r="I265" t="n">
+        <v>379</v>
+      </c>
+      <c r="J265" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>3415</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3249.52</v>
+      </c>
+      <c r="E266" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3425.6</v>
+      </c>
+      <c r="G266" t="n">
+        <v>3358.81</v>
+      </c>
+      <c r="H266" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="I266" t="n">
+        <v>3371.1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>3347.22</v>
+      </c>
+      <c r="K266" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>5510</v>
+      </c>
+      <c r="D267" t="n">
+        <v>5514.7</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="F267" t="n">
+        <v>5577</v>
+      </c>
+      <c r="G267" t="n">
+        <v>5625.41</v>
+      </c>
+      <c r="H267" t="n">
+        <v>-48.41</v>
+      </c>
+      <c r="I267" t="n">
+        <v>5475.5</v>
+      </c>
+      <c r="J267" t="n">
+        <v>5474.84</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>11380</v>
+      </c>
+      <c r="D268" t="n">
+        <v>11471.96</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-91.95999999999999</v>
+      </c>
+      <c r="F268" t="n">
+        <v>11383</v>
+      </c>
+      <c r="G268" t="n">
+        <v>11482.91</v>
+      </c>
+      <c r="H268" t="n">
+        <v>-99.91</v>
+      </c>
+      <c r="I268" t="n">
+        <v>11234</v>
+      </c>
+      <c r="J268" t="n">
+        <v>11181.79</v>
+      </c>
+      <c r="K268" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1048.6</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1054.16</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1054.8</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1064.76</v>
+      </c>
+      <c r="H269" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1041.4</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1036.06</v>
+      </c>
+      <c r="K269" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="D270" t="n">
+        <v>289.21</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F270" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="G270" t="n">
+        <v>289.21</v>
+      </c>
+      <c r="H270" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I270" t="n">
+        <v>285.65</v>
+      </c>
+      <c r="J270" t="n">
+        <v>282.61</v>
+      </c>
+      <c r="K270" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1192.21</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1185.5</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1192.21</v>
+      </c>
+      <c r="H271" t="n">
+        <v>-6.71</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1157.5</v>
+      </c>
+      <c r="J271" t="n">
+        <v>1155.29</v>
+      </c>
+      <c r="K271" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>4041.3</v>
+      </c>
+      <c r="D272" t="n">
+        <v>4073.34</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-32.04</v>
+      </c>
+      <c r="F272" t="n">
+        <v>4069</v>
+      </c>
+      <c r="G272" t="n">
+        <v>4108.7</v>
+      </c>
+      <c r="H272" t="n">
+        <v>-39.7</v>
+      </c>
+      <c r="I272" t="n">
+        <v>4024.8</v>
+      </c>
+      <c r="J272" t="n">
+        <v>4001.68</v>
+      </c>
+      <c r="K272" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2174.5</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2170.31</v>
+      </c>
+      <c r="E273" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F273" t="n">
+        <v>2218.8</v>
+      </c>
+      <c r="G273" t="n">
+        <v>2170.31</v>
+      </c>
+      <c r="H273" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="I273" t="n">
+        <v>2160.1</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2119.1</v>
+      </c>
+      <c r="K273" t="n">
+        <v>41</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="D274" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="F274" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="G274" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="H274" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I274" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="J274" t="n">
+        <v>170.49</v>
+      </c>
+      <c r="K274" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1038.95</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1103.4</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-64.45</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1039.2</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1103.4</v>
+      </c>
+      <c r="H275" t="n">
+        <v>-64.2</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1025.55</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-7.65</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>942.1</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1006.16</v>
+      </c>
+      <c r="E276" t="n">
+        <v>-64.06</v>
+      </c>
+      <c r="F276" t="n">
+        <v>948.45</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1006.16</v>
+      </c>
+      <c r="H276" t="n">
+        <v>-57.71</v>
+      </c>
+      <c r="I276" t="n">
+        <v>930.05</v>
+      </c>
+      <c r="J276" t="n">
+        <v>930.6799999999999</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>1589.8</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1566.21</v>
+      </c>
+      <c r="E277" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1610.7</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1632.03</v>
+      </c>
+      <c r="H277" t="n">
+        <v>-21.33</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1575.8</v>
+      </c>
+      <c r="J277" t="n">
+        <v>1588.66</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-12.86</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>873.15</v>
+      </c>
+      <c r="D278" t="n">
+        <v>880.21</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="F278" t="n">
+        <v>881</v>
+      </c>
+      <c r="G278" t="n">
+        <v>892.14</v>
+      </c>
+      <c r="H278" t="n">
+        <v>-11.14</v>
+      </c>
+      <c r="I278" t="n">
+        <v>865</v>
+      </c>
+      <c r="J278" t="n">
+        <v>868.29</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="D279" t="n">
+        <v>488.23</v>
+      </c>
+      <c r="E279" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="F279" t="n">
+        <v>519.65</v>
+      </c>
+      <c r="G279" t="n">
+        <v>495.68</v>
+      </c>
+      <c r="H279" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="I279" t="n">
+        <v>511.55</v>
+      </c>
+      <c r="J279" t="n">
+        <v>503.49</v>
+      </c>
+      <c r="K279" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>5.35</v>
       </c>
     </row>
   </sheetData>
@@ -13605,7 +14957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14718,6 +16070,110 @@
       </c>
       <c r="N21" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24172.85</v>
+      </c>
+      <c r="G22" t="n">
+        <v>24158.89</v>
+      </c>
+      <c r="H22" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="I22" t="n">
+        <v>24025.65</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24011.69</v>
+      </c>
+      <c r="K22" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>57356.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>57397.15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>57001.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>57042.05</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14731,7 +16187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N253"/>
+  <dimension ref="A1:N279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27910,6 +29366,1358 @@
         <v>2.13</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="D254" t="n">
+        <v>124.48</v>
+      </c>
+      <c r="E254" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F254" t="n">
+        <v>117.59</v>
+      </c>
+      <c r="G254" t="n">
+        <v>119.98</v>
+      </c>
+      <c r="H254" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="I254" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="J254" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>5510</v>
+      </c>
+      <c r="D255" t="n">
+        <v>5656.68</v>
+      </c>
+      <c r="E255" t="n">
+        <v>-146.68</v>
+      </c>
+      <c r="F255" t="n">
+        <v>5577</v>
+      </c>
+      <c r="G255" t="n">
+        <v>5684.4</v>
+      </c>
+      <c r="H255" t="n">
+        <v>-107.4</v>
+      </c>
+      <c r="I255" t="n">
+        <v>5475.5</v>
+      </c>
+      <c r="J255" t="n">
+        <v>5423.26</v>
+      </c>
+      <c r="K255" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>320</v>
+      </c>
+      <c r="D256" t="n">
+        <v>310.81</v>
+      </c>
+      <c r="E256" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="F256" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="G256" t="n">
+        <v>329.12</v>
+      </c>
+      <c r="H256" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="I256" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="J256" t="n">
+        <v>315.73</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="D257" t="n">
+        <v>198.72</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="F257" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="G257" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="H257" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I257" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="J257" t="n">
+        <v>184.12</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2121.8</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2129.58</v>
+      </c>
+      <c r="E258" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="F258" t="n">
+        <v>2121.8</v>
+      </c>
+      <c r="G258" t="n">
+        <v>2194.54</v>
+      </c>
+      <c r="H258" t="n">
+        <v>-72.73999999999999</v>
+      </c>
+      <c r="I258" t="n">
+        <v>2097.2</v>
+      </c>
+      <c r="J258" t="n">
+        <v>2084.18</v>
+      </c>
+      <c r="K258" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>OFSS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>11774</v>
+      </c>
+      <c r="D259" t="n">
+        <v>12103.03</v>
+      </c>
+      <c r="E259" t="n">
+        <v>-329.03</v>
+      </c>
+      <c r="F259" t="n">
+        <v>11854</v>
+      </c>
+      <c r="G259" t="n">
+        <v>12161.71</v>
+      </c>
+      <c r="H259" t="n">
+        <v>-307.71</v>
+      </c>
+      <c r="I259" t="n">
+        <v>11640</v>
+      </c>
+      <c r="J259" t="n">
+        <v>11577.27</v>
+      </c>
+      <c r="K259" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>1813.1</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1909.32</v>
+      </c>
+      <c r="E260" t="n">
+        <v>-96.22</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G260" t="n">
+        <v>1870.62</v>
+      </c>
+      <c r="H260" t="n">
+        <v>-52.62</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1785.4</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1784.46</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1417.82</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-39.42</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1427.65</v>
+      </c>
+      <c r="H261" t="n">
+        <v>-49.25</v>
+      </c>
+      <c r="I261" t="n">
+        <v>1351.5</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1352.45</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1272</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1318.03</v>
+      </c>
+      <c r="E262" t="n">
+        <v>-46.03</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1288</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1308.76</v>
+      </c>
+      <c r="H262" t="n">
+        <v>-20.76</v>
+      </c>
+      <c r="I262" t="n">
+        <v>1259</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1254.61</v>
+      </c>
+      <c r="K262" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D263" t="n">
+        <v>2082.89</v>
+      </c>
+      <c r="E263" t="n">
+        <v>-70.89</v>
+      </c>
+      <c r="F263" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G263" t="n">
+        <v>2068.96</v>
+      </c>
+      <c r="H263" t="n">
+        <v>-55.96</v>
+      </c>
+      <c r="I263" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J263" t="n">
+        <v>1985.41</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="D264" t="n">
+        <v>440.95</v>
+      </c>
+      <c r="E264" t="n">
+        <v>-54.4</v>
+      </c>
+      <c r="F264" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="G264" t="n">
+        <v>402.95</v>
+      </c>
+      <c r="H264" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="I264" t="n">
+        <v>379</v>
+      </c>
+      <c r="J264" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="K264" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>14462</v>
+      </c>
+      <c r="D265" t="n">
+        <v>14456.94</v>
+      </c>
+      <c r="E265" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="F265" t="n">
+        <v>14550</v>
+      </c>
+      <c r="G265" t="n">
+        <v>14911.34</v>
+      </c>
+      <c r="H265" t="n">
+        <v>-361.34</v>
+      </c>
+      <c r="I265" t="n">
+        <v>14026</v>
+      </c>
+      <c r="J265" t="n">
+        <v>14240.67</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-214.67</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>3415</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3316.42</v>
+      </c>
+      <c r="E266" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3425.6</v>
+      </c>
+      <c r="G266" t="n">
+        <v>3506.06</v>
+      </c>
+      <c r="H266" t="n">
+        <v>-80.45999999999999</v>
+      </c>
+      <c r="I266" t="n">
+        <v>3371.1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>3374.11</v>
+      </c>
+      <c r="K266" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>5709.5</v>
+      </c>
+      <c r="D267" t="n">
+        <v>5999.72</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-290.22</v>
+      </c>
+      <c r="F267" t="n">
+        <v>5767.5</v>
+      </c>
+      <c r="G267" t="n">
+        <v>5883.61</v>
+      </c>
+      <c r="H267" t="n">
+        <v>-116.11</v>
+      </c>
+      <c r="I267" t="n">
+        <v>5664.5</v>
+      </c>
+      <c r="J267" t="n">
+        <v>5624.62</v>
+      </c>
+      <c r="K267" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>11380</v>
+      </c>
+      <c r="D268" t="n">
+        <v>11679.57</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-299.57</v>
+      </c>
+      <c r="F268" t="n">
+        <v>11383</v>
+      </c>
+      <c r="G268" t="n">
+        <v>11656.05</v>
+      </c>
+      <c r="H268" t="n">
+        <v>-273.05</v>
+      </c>
+      <c r="I268" t="n">
+        <v>11234</v>
+      </c>
+      <c r="J268" t="n">
+        <v>11264.45</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-30.45</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1038.95</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1132.14</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-93.19</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1039.2</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1072.12</v>
+      </c>
+      <c r="H269" t="n">
+        <v>-32.92</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1025.55</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1022.38</v>
+      </c>
+      <c r="K269" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>942.1</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1032.29</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-90.19</v>
+      </c>
+      <c r="F270" t="n">
+        <v>948.45</v>
+      </c>
+      <c r="G270" t="n">
+        <v>972.13</v>
+      </c>
+      <c r="H270" t="n">
+        <v>-23.68</v>
+      </c>
+      <c r="I270" t="n">
+        <v>930.05</v>
+      </c>
+      <c r="J270" t="n">
+        <v>927.12</v>
+      </c>
+      <c r="K270" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1048.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1074.56</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-25.96</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1054.8</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1075.31</v>
+      </c>
+      <c r="H271" t="n">
+        <v>-20.51</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1041.4</v>
+      </c>
+      <c r="J271" t="n">
+        <v>1036.98</v>
+      </c>
+      <c r="K271" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="D272" t="n">
+        <v>294.97</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="F272" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="G272" t="n">
+        <v>295.66</v>
+      </c>
+      <c r="H272" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="I272" t="n">
+        <v>285.65</v>
+      </c>
+      <c r="J272" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="D273" t="n">
+        <v>182.36</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="F273" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="G273" t="n">
+        <v>179.56</v>
+      </c>
+      <c r="H273" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="I273" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="J273" t="n">
+        <v>169.64</v>
+      </c>
+      <c r="K273" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1224.43</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-43.93</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1185.5</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1219.32</v>
+      </c>
+      <c r="H274" t="n">
+        <v>-33.82</v>
+      </c>
+      <c r="I274" t="n">
+        <v>1157.5</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1160.81</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>TECHM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1589.8</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1598.95</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-9.15</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1610.7</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1632.68</v>
+      </c>
+      <c r="H275" t="n">
+        <v>-21.98</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1575.8</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1570.4</v>
+      </c>
+      <c r="K275" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>4041.3</v>
+      </c>
+      <c r="D276" t="n">
+        <v>4115.23</v>
+      </c>
+      <c r="E276" t="n">
+        <v>-73.93000000000001</v>
+      </c>
+      <c r="F276" t="n">
+        <v>4069</v>
+      </c>
+      <c r="G276" t="n">
+        <v>4108.8</v>
+      </c>
+      <c r="H276" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="I276" t="n">
+        <v>4024.8</v>
+      </c>
+      <c r="J276" t="n">
+        <v>4023.33</v>
+      </c>
+      <c r="K276" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2174.5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>2227.53</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-53.03</v>
+      </c>
+      <c r="F277" t="n">
+        <v>2218.8</v>
+      </c>
+      <c r="G277" t="n">
+        <v>2244.63</v>
+      </c>
+      <c r="H277" t="n">
+        <v>-25.83</v>
+      </c>
+      <c r="I277" t="n">
+        <v>2160.1</v>
+      </c>
+      <c r="J277" t="n">
+        <v>2139.28</v>
+      </c>
+      <c r="K277" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="D278" t="n">
+        <v>498.93</v>
+      </c>
+      <c r="E278" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="F278" t="n">
+        <v>519.65</v>
+      </c>
+      <c r="G278" t="n">
+        <v>528.72</v>
+      </c>
+      <c r="H278" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="I278" t="n">
+        <v>511.55</v>
+      </c>
+      <c r="J278" t="n">
+        <v>507.7</v>
+      </c>
+      <c r="K278" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>873.15</v>
+      </c>
+      <c r="D279" t="n">
+        <v>898.98</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-25.83</v>
+      </c>
+      <c r="F279" t="n">
+        <v>881</v>
+      </c>
+      <c r="G279" t="n">
+        <v>897.0599999999999</v>
+      </c>
+      <c r="H279" t="n">
+        <v>-16.06</v>
+      </c>
+      <c r="I279" t="n">
+        <v>865</v>
+      </c>
+      <c r="J279" t="n">
+        <v>862.22</v>
+      </c>
+      <c r="K279" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -13606,31 +13606,31 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>117.48</v>
+        <v>116.5</v>
       </c>
       <c r="D254" t="n">
         <v>122.62</v>
       </c>
       <c r="E254" t="n">
-        <v>-5.14</v>
+        <v>-6.12</v>
       </c>
       <c r="F254" t="n">
-        <v>117.59</v>
+        <v>117.99</v>
       </c>
       <c r="G254" t="n">
         <v>122.62</v>
       </c>
       <c r="H254" t="n">
-        <v>-5.03</v>
+        <v>-4.63</v>
       </c>
       <c r="I254" t="n">
-        <v>116.03</v>
+        <v>116.5</v>
       </c>
       <c r="J254" t="n">
         <v>117.34</v>
       </c>
       <c r="K254" t="n">
-        <v>-1.31</v>
+        <v>-0.84</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>4.19</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="255">
@@ -13658,31 +13658,31 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>11774</v>
+        <v>11623</v>
       </c>
       <c r="D255" t="n">
         <v>11809.19</v>
       </c>
       <c r="E255" t="n">
-        <v>-35.19</v>
+        <v>-186.19</v>
       </c>
       <c r="F255" t="n">
-        <v>11854</v>
+        <v>11840</v>
       </c>
       <c r="G255" t="n">
         <v>12117.36</v>
       </c>
       <c r="H255" t="n">
-        <v>-263.36</v>
+        <v>-277.36</v>
       </c>
       <c r="I255" t="n">
-        <v>11640</v>
+        <v>11614</v>
       </c>
       <c r="J255" t="n">
         <v>11774</v>
       </c>
       <c r="K255" t="n">
-        <v>-134</v>
+        <v>-160</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0.3</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="256">
@@ -13710,31 +13710,31 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>186.9</v>
+        <v>185.5</v>
       </c>
       <c r="D256" t="n">
         <v>194.91</v>
       </c>
       <c r="E256" t="n">
-        <v>-8.01</v>
+        <v>-9.41</v>
       </c>
       <c r="F256" t="n">
-        <v>187.6</v>
+        <v>190.58</v>
       </c>
       <c r="G256" t="n">
         <v>194.91</v>
       </c>
       <c r="H256" t="n">
-        <v>-7.31</v>
+        <v>-4.33</v>
       </c>
       <c r="I256" t="n">
-        <v>184.9</v>
+        <v>185.5</v>
       </c>
       <c r="J256" t="n">
         <v>186.9</v>
       </c>
       <c r="K256" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>4.11</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="257">
@@ -13762,31 +13762,31 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1378.4</v>
+        <v>1354.9</v>
       </c>
       <c r="D257" t="n">
         <v>1376.58</v>
       </c>
       <c r="E257" t="n">
-        <v>1.82</v>
+        <v>-21.68</v>
       </c>
       <c r="F257" t="n">
-        <v>1378.4</v>
+        <v>1368.8</v>
       </c>
       <c r="G257" t="n">
         <v>1376.58</v>
       </c>
       <c r="H257" t="n">
-        <v>1.82</v>
+        <v>-7.78</v>
       </c>
       <c r="I257" t="n">
-        <v>1351.5</v>
+        <v>1331.1</v>
       </c>
       <c r="J257" t="n">
         <v>1338.45</v>
       </c>
       <c r="K257" t="n">
-        <v>13.05</v>
+        <v>-7.35</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0.13</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="258">
@@ -13814,31 +13814,31 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D258" t="n">
         <v>1288.53</v>
       </c>
       <c r="E258" t="n">
-        <v>-16.53</v>
+        <v>-15.53</v>
       </c>
       <c r="F258" t="n">
-        <v>1288</v>
+        <v>1281.2</v>
       </c>
       <c r="G258" t="n">
         <v>1288.53</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.53</v>
+        <v>-7.33</v>
       </c>
       <c r="I258" t="n">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="J258" t="n">
         <v>1243.88</v>
       </c>
       <c r="K258" t="n">
-        <v>15.12</v>
+        <v>19.12</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="259">
@@ -13866,31 +13866,31 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2121.8</v>
+        <v>2115</v>
       </c>
       <c r="D259" t="n">
         <v>2070.63</v>
       </c>
       <c r="E259" t="n">
-        <v>51.17</v>
+        <v>44.37</v>
       </c>
       <c r="F259" t="n">
-        <v>2121.8</v>
+        <v>2122</v>
       </c>
       <c r="G259" t="n">
         <v>2130.79</v>
       </c>
       <c r="H259" t="n">
-        <v>-8.99</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>2097.2</v>
+        <v>2075.1</v>
       </c>
       <c r="J259" t="n">
         <v>2072.54</v>
       </c>
       <c r="K259" t="n">
-        <v>24.66</v>
+        <v>2.56</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="260">
@@ -13918,31 +13918,31 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2012</v>
+        <v>2011.2</v>
       </c>
       <c r="D260" t="n">
         <v>2037.47</v>
       </c>
       <c r="E260" t="n">
-        <v>-25.47</v>
+        <v>-26.27</v>
       </c>
       <c r="F260" t="n">
-        <v>2013</v>
+        <v>2018.8</v>
       </c>
       <c r="G260" t="n">
         <v>2037.47</v>
       </c>
       <c r="H260" t="n">
-        <v>-24.47</v>
+        <v>-18.67</v>
       </c>
       <c r="I260" t="n">
-        <v>1985</v>
+        <v>1998</v>
       </c>
       <c r="J260" t="n">
         <v>1968.74</v>
       </c>
       <c r="K260" t="n">
-        <v>16.26</v>
+        <v>29.26</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="261">
@@ -13970,31 +13970,31 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1813.1</v>
+        <v>1773</v>
       </c>
       <c r="D261" t="n">
         <v>1861.25</v>
       </c>
       <c r="E261" t="n">
-        <v>-48.15</v>
+        <v>-88.25</v>
       </c>
       <c r="F261" t="n">
-        <v>1818</v>
+        <v>1795</v>
       </c>
       <c r="G261" t="n">
         <v>1861.25</v>
       </c>
       <c r="H261" t="n">
-        <v>-43.25</v>
+        <v>-66.25</v>
       </c>
       <c r="I261" t="n">
-        <v>1785.4</v>
+        <v>1762.2</v>
       </c>
       <c r="J261" t="n">
         <v>1767.88</v>
       </c>
       <c r="K261" t="n">
-        <v>17.52</v>
+        <v>-5.68</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2.59</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="262">
@@ -14022,31 +14022,31 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>320</v>
+        <v>315.9</v>
       </c>
       <c r="D262" t="n">
         <v>303.98</v>
       </c>
       <c r="E262" t="n">
-        <v>16.02</v>
+        <v>11.92</v>
       </c>
       <c r="F262" t="n">
-        <v>322.85</v>
+        <v>321.2</v>
       </c>
       <c r="G262" t="n">
         <v>327.01</v>
       </c>
       <c r="H262" t="n">
-        <v>-4.16</v>
+        <v>-5.81</v>
       </c>
       <c r="I262" t="n">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="J262" t="n">
         <v>318.26</v>
       </c>
       <c r="K262" t="n">
-        <v>-2.41</v>
+        <v>-2.71</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>5.27</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="263">
@@ -14074,31 +14074,31 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>14462</v>
+        <v>14150</v>
       </c>
       <c r="D263" t="n">
         <v>14102.32</v>
       </c>
       <c r="E263" t="n">
-        <v>359.68</v>
+        <v>47.68</v>
       </c>
       <c r="F263" t="n">
-        <v>14550</v>
+        <v>14420</v>
       </c>
       <c r="G263" t="n">
         <v>14407.41</v>
       </c>
       <c r="H263" t="n">
-        <v>142.59</v>
+        <v>12.59</v>
       </c>
       <c r="I263" t="n">
-        <v>14026</v>
+        <v>14066</v>
       </c>
       <c r="J263" t="n">
         <v>14110.8</v>
       </c>
       <c r="K263" t="n">
-        <v>-84.8</v>
+        <v>-44.8</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2.55</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="264">
@@ -14126,31 +14126,31 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>5709.5</v>
+        <v>5745.5</v>
       </c>
       <c r="D264" t="n">
         <v>5855.95</v>
       </c>
       <c r="E264" t="n">
-        <v>-146.45</v>
+        <v>-110.45</v>
       </c>
       <c r="F264" t="n">
-        <v>5767.5</v>
+        <v>5778</v>
       </c>
       <c r="G264" t="n">
         <v>5855.95</v>
       </c>
       <c r="H264" t="n">
-        <v>-88.45</v>
+        <v>-77.95</v>
       </c>
       <c r="I264" t="n">
-        <v>5664.5</v>
+        <v>5694.5</v>
       </c>
       <c r="J264" t="n">
         <v>5574.16</v>
       </c>
       <c r="K264" t="n">
-        <v>90.34</v>
+        <v>120.34</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="265">
@@ -14178,31 +14178,31 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>386.55</v>
+        <v>388</v>
       </c>
       <c r="D265" t="n">
         <v>425.26</v>
       </c>
       <c r="E265" t="n">
-        <v>-38.71</v>
+        <v>-37.26</v>
       </c>
       <c r="F265" t="n">
-        <v>386.55</v>
+        <v>390.85</v>
       </c>
       <c r="G265" t="n">
         <v>425.26</v>
       </c>
       <c r="H265" t="n">
-        <v>-38.71</v>
+        <v>-34.41</v>
       </c>
       <c r="I265" t="n">
-        <v>379</v>
+        <v>385.8</v>
       </c>
       <c r="J265" t="n">
         <v>381.42</v>
       </c>
       <c r="K265" t="n">
-        <v>-2.42</v>
+        <v>4.38</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>9.1</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="266">
@@ -14230,31 +14230,31 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3415</v>
+        <v>3421.5</v>
       </c>
       <c r="D266" t="n">
         <v>3249.52</v>
       </c>
       <c r="E266" t="n">
-        <v>165.48</v>
+        <v>171.98</v>
       </c>
       <c r="F266" t="n">
-        <v>3425.6</v>
+        <v>3435</v>
       </c>
       <c r="G266" t="n">
         <v>3358.81</v>
       </c>
       <c r="H266" t="n">
-        <v>66.79000000000001</v>
+        <v>76.19</v>
       </c>
       <c r="I266" t="n">
-        <v>3371.1</v>
+        <v>3390.2</v>
       </c>
       <c r="J266" t="n">
         <v>3347.22</v>
       </c>
       <c r="K266" t="n">
-        <v>23.88</v>
+        <v>42.98</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>5.09</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="267">
@@ -14282,31 +14282,31 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>5510</v>
+        <v>5442.5</v>
       </c>
       <c r="D267" t="n">
         <v>5514.7</v>
       </c>
       <c r="E267" t="n">
-        <v>-4.7</v>
+        <v>-72.2</v>
       </c>
       <c r="F267" t="n">
-        <v>5577</v>
+        <v>5571.5</v>
       </c>
       <c r="G267" t="n">
         <v>5625.41</v>
       </c>
       <c r="H267" t="n">
-        <v>-48.41</v>
+        <v>-53.91</v>
       </c>
       <c r="I267" t="n">
-        <v>5475.5</v>
+        <v>5442.5</v>
       </c>
       <c r="J267" t="n">
         <v>5474.84</v>
       </c>
       <c r="K267" t="n">
-        <v>0.66</v>
+        <v>-32.34</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0.09</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="268">
@@ -14334,31 +14334,31 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>11380</v>
+        <v>11254</v>
       </c>
       <c r="D268" t="n">
         <v>11471.96</v>
       </c>
       <c r="E268" t="n">
-        <v>-91.95999999999999</v>
+        <v>-217.96</v>
       </c>
       <c r="F268" t="n">
-        <v>11383</v>
+        <v>11435</v>
       </c>
       <c r="G268" t="n">
         <v>11482.91</v>
       </c>
       <c r="H268" t="n">
-        <v>-99.91</v>
+        <v>-47.91</v>
       </c>
       <c r="I268" t="n">
-        <v>11234</v>
+        <v>11211</v>
       </c>
       <c r="J268" t="n">
         <v>11181.79</v>
       </c>
       <c r="K268" t="n">
-        <v>52.21</v>
+        <v>29.21</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="269">
@@ -14386,31 +14386,31 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1048.6</v>
+        <v>1053</v>
       </c>
       <c r="D269" t="n">
         <v>1054.16</v>
       </c>
       <c r="E269" t="n">
-        <v>-5.56</v>
+        <v>-1.16</v>
       </c>
       <c r="F269" t="n">
-        <v>1054.8</v>
+        <v>1067.7</v>
       </c>
       <c r="G269" t="n">
         <v>1064.76</v>
       </c>
       <c r="H269" t="n">
-        <v>-9.960000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="I269" t="n">
-        <v>1041.4</v>
+        <v>1053</v>
       </c>
       <c r="J269" t="n">
         <v>1036.06</v>
       </c>
       <c r="K269" t="n">
-        <v>5.34</v>
+        <v>16.94</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0.53</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="270">
@@ -14438,31 +14438,31 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>288.15</v>
+        <v>286.25</v>
       </c>
       <c r="D270" t="n">
         <v>289.21</v>
       </c>
       <c r="E270" t="n">
-        <v>-1.06</v>
+        <v>-2.96</v>
       </c>
       <c r="F270" t="n">
-        <v>291.5</v>
+        <v>286.95</v>
       </c>
       <c r="G270" t="n">
         <v>289.21</v>
       </c>
       <c r="H270" t="n">
-        <v>2.29</v>
+        <v>-2.26</v>
       </c>
       <c r="I270" t="n">
-        <v>285.65</v>
+        <v>281.8</v>
       </c>
       <c r="J270" t="n">
         <v>282.61</v>
       </c>
       <c r="K270" t="n">
-        <v>3.04</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0.37</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="271">
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1180.5</v>
+        <v>1163.6</v>
       </c>
       <c r="D271" t="n">
         <v>1192.21</v>
       </c>
       <c r="E271" t="n">
-        <v>-11.71</v>
+        <v>-28.61</v>
       </c>
       <c r="F271" t="n">
-        <v>1185.5</v>
+        <v>1185</v>
       </c>
       <c r="G271" t="n">
         <v>1192.21</v>
       </c>
       <c r="H271" t="n">
-        <v>-6.71</v>
+        <v>-7.21</v>
       </c>
       <c r="I271" t="n">
-        <v>1157.5</v>
+        <v>1154</v>
       </c>
       <c r="J271" t="n">
         <v>1155.29</v>
       </c>
       <c r="K271" t="n">
-        <v>2.21</v>
+        <v>-1.29</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0.98</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="272">
@@ -14542,31 +14542,31 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>4041.3</v>
+        <v>4064.3</v>
       </c>
       <c r="D272" t="n">
         <v>4073.34</v>
       </c>
       <c r="E272" t="n">
-        <v>-32.04</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>4069</v>
+        <v>4085</v>
       </c>
       <c r="G272" t="n">
         <v>4108.7</v>
       </c>
       <c r="H272" t="n">
-        <v>-39.7</v>
+        <v>-23.7</v>
       </c>
       <c r="I272" t="n">
-        <v>4024.8</v>
+        <v>4050</v>
       </c>
       <c r="J272" t="n">
         <v>4001.68</v>
       </c>
       <c r="K272" t="n">
-        <v>23.12</v>
+        <v>48.32</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0.79</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="273">
@@ -14594,31 +14594,31 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2174.5</v>
+        <v>2186</v>
       </c>
       <c r="D273" t="n">
         <v>2170.31</v>
       </c>
       <c r="E273" t="n">
-        <v>4.19</v>
+        <v>15.69</v>
       </c>
       <c r="F273" t="n">
-        <v>2218.8</v>
+        <v>2221.9</v>
       </c>
       <c r="G273" t="n">
         <v>2170.31</v>
       </c>
       <c r="H273" t="n">
-        <v>48.49</v>
+        <v>51.59</v>
       </c>
       <c r="I273" t="n">
-        <v>2160.1</v>
+        <v>2179</v>
       </c>
       <c r="J273" t="n">
         <v>2119.1</v>
       </c>
       <c r="K273" t="n">
-        <v>41</v>
+        <v>59.9</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0.19</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="274">
@@ -14646,31 +14646,31 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>173.1</v>
+        <v>176.35</v>
       </c>
       <c r="D274" t="n">
         <v>176.77</v>
       </c>
       <c r="E274" t="n">
-        <v>-3.67</v>
+        <v>-0.42</v>
       </c>
       <c r="F274" t="n">
-        <v>176.1</v>
+        <v>177.59</v>
       </c>
       <c r="G274" t="n">
         <v>176.77</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.67</v>
+        <v>0.82</v>
       </c>
       <c r="I274" t="n">
-        <v>173.1</v>
+        <v>174.5</v>
       </c>
       <c r="J274" t="n">
         <v>170.49</v>
       </c>
       <c r="K274" t="n">
-        <v>2.61</v>
+        <v>4.01</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2.08</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="275">
@@ -14698,31 +14698,31 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1038.95</v>
+        <v>1041.6</v>
       </c>
       <c r="D275" t="n">
         <v>1103.4</v>
       </c>
       <c r="E275" t="n">
-        <v>-64.45</v>
+        <v>-61.8</v>
       </c>
       <c r="F275" t="n">
-        <v>1039.2</v>
+        <v>1050.6</v>
       </c>
       <c r="G275" t="n">
         <v>1103.4</v>
       </c>
       <c r="H275" t="n">
-        <v>-64.2</v>
+        <v>-52.8</v>
       </c>
       <c r="I275" t="n">
-        <v>1025.55</v>
+        <v>1038</v>
       </c>
       <c r="J275" t="n">
         <v>1033.2</v>
       </c>
       <c r="K275" t="n">
-        <v>-7.65</v>
+        <v>4.8</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>5.84</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="276">
@@ -14750,31 +14750,31 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>942.1</v>
+        <v>938</v>
       </c>
       <c r="D276" t="n">
         <v>1006.16</v>
       </c>
       <c r="E276" t="n">
-        <v>-64.06</v>
+        <v>-68.16</v>
       </c>
       <c r="F276" t="n">
-        <v>948.45</v>
+        <v>961.35</v>
       </c>
       <c r="G276" t="n">
         <v>1006.16</v>
       </c>
       <c r="H276" t="n">
-        <v>-57.71</v>
+        <v>-44.81</v>
       </c>
       <c r="I276" t="n">
-        <v>930.05</v>
+        <v>933.1</v>
       </c>
       <c r="J276" t="n">
         <v>930.6799999999999</v>
       </c>
       <c r="K276" t="n">
-        <v>-0.63</v>
+        <v>2.42</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>6.37</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="277">
@@ -14802,31 +14802,31 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1589.8</v>
+        <v>1592</v>
       </c>
       <c r="D277" t="n">
         <v>1566.21</v>
       </c>
       <c r="E277" t="n">
-        <v>23.59</v>
+        <v>25.79</v>
       </c>
       <c r="F277" t="n">
-        <v>1610.7</v>
+        <v>1608</v>
       </c>
       <c r="G277" t="n">
         <v>1632.03</v>
       </c>
       <c r="H277" t="n">
-        <v>-21.33</v>
+        <v>-24.03</v>
       </c>
       <c r="I277" t="n">
-        <v>1575.8</v>
+        <v>1579.9</v>
       </c>
       <c r="J277" t="n">
         <v>1588.66</v>
       </c>
       <c r="K277" t="n">
-        <v>-12.86</v>
+        <v>-8.76</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="278">
@@ -14854,31 +14854,31 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>873.15</v>
+        <v>875</v>
       </c>
       <c r="D278" t="n">
         <v>880.21</v>
       </c>
       <c r="E278" t="n">
-        <v>-7.06</v>
+        <v>-5.21</v>
       </c>
       <c r="F278" t="n">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="G278" t="n">
         <v>892.14</v>
       </c>
       <c r="H278" t="n">
-        <v>-11.14</v>
+        <v>-5.14</v>
       </c>
       <c r="I278" t="n">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="J278" t="n">
         <v>868.29</v>
       </c>
       <c r="K278" t="n">
-        <v>-3.29</v>
+        <v>5.71</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="279">
@@ -14906,31 +14906,31 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>514.35</v>
+        <v>518.25</v>
       </c>
       <c r="D279" t="n">
         <v>488.23</v>
       </c>
       <c r="E279" t="n">
-        <v>26.12</v>
+        <v>30.02</v>
       </c>
       <c r="F279" t="n">
-        <v>519.65</v>
+        <v>524.85</v>
       </c>
       <c r="G279" t="n">
         <v>495.68</v>
       </c>
       <c r="H279" t="n">
-        <v>23.97</v>
+        <v>29.17</v>
       </c>
       <c r="I279" t="n">
-        <v>511.55</v>
+        <v>517.55</v>
       </c>
       <c r="J279" t="n">
         <v>503.49</v>
       </c>
       <c r="K279" t="n">
-        <v>8.06</v>
+        <v>14.06</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>5.35</v>
+        <v>6.15</v>
       </c>
     </row>
   </sheetData>
@@ -16084,31 +16084,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24078.3</v>
+        <v>24154.9</v>
       </c>
       <c r="D22" t="n">
         <v>24078.3</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>24172.85</v>
+        <v>24269.65</v>
       </c>
       <c r="G22" t="n">
         <v>24158.89</v>
       </c>
       <c r="H22" t="n">
-        <v>13.96</v>
+        <v>110.76</v>
       </c>
       <c r="I22" t="n">
-        <v>24025.65</v>
+        <v>24154.9</v>
       </c>
       <c r="J22" t="n">
         <v>24011.69</v>
       </c>
       <c r="K22" t="n">
-        <v>13.96</v>
+        <v>143.21</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="23">
@@ -16136,31 +16136,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57239.75</v>
+        <v>57262.4</v>
       </c>
       <c r="D23" t="n">
         <v>57239.75</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="F23" t="n">
-        <v>57356.85</v>
+        <v>57584.7</v>
       </c>
       <c r="G23" t="n">
         <v>57397.15</v>
       </c>
       <c r="H23" t="n">
-        <v>-40.3</v>
+        <v>187.55</v>
       </c>
       <c r="I23" t="n">
-        <v>57001.75</v>
+        <v>57217.6</v>
       </c>
       <c r="J23" t="n">
         <v>57042.05</v>
       </c>
       <c r="K23" t="n">
-        <v>-40.3</v>
+        <v>175.55</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -29378,31 +29378,31 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>117.48</v>
+        <v>116.5</v>
       </c>
       <c r="D254" t="n">
         <v>124.48</v>
       </c>
       <c r="E254" t="n">
-        <v>-7</v>
+        <v>-7.98</v>
       </c>
       <c r="F254" t="n">
-        <v>117.59</v>
+        <v>117.99</v>
       </c>
       <c r="G254" t="n">
         <v>119.98</v>
       </c>
       <c r="H254" t="n">
-        <v>-2.39</v>
+        <v>-1.99</v>
       </c>
       <c r="I254" t="n">
-        <v>116.03</v>
+        <v>116.5</v>
       </c>
       <c r="J254" t="n">
         <v>116.54</v>
       </c>
       <c r="K254" t="n">
-        <v>-0.51</v>
+        <v>-0.04</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>5.62</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="255">
@@ -29430,31 +29430,31 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>5510</v>
+        <v>5442.5</v>
       </c>
       <c r="D255" t="n">
         <v>5656.68</v>
       </c>
       <c r="E255" t="n">
-        <v>-146.68</v>
+        <v>-214.18</v>
       </c>
       <c r="F255" t="n">
-        <v>5577</v>
+        <v>5571.5</v>
       </c>
       <c r="G255" t="n">
         <v>5684.4</v>
       </c>
       <c r="H255" t="n">
-        <v>-107.4</v>
+        <v>-112.9</v>
       </c>
       <c r="I255" t="n">
-        <v>5475.5</v>
+        <v>5442.5</v>
       </c>
       <c r="J255" t="n">
         <v>5423.26</v>
       </c>
       <c r="K255" t="n">
-        <v>52.24</v>
+        <v>19.24</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2.59</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="256">
@@ -29482,31 +29482,31 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>320</v>
+        <v>315.9</v>
       </c>
       <c r="D256" t="n">
         <v>310.81</v>
       </c>
       <c r="E256" t="n">
-        <v>9.19</v>
+        <v>5.09</v>
       </c>
       <c r="F256" t="n">
-        <v>322.85</v>
+        <v>321.2</v>
       </c>
       <c r="G256" t="n">
         <v>329.12</v>
       </c>
       <c r="H256" t="n">
-        <v>-6.27</v>
+        <v>-7.92</v>
       </c>
       <c r="I256" t="n">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="J256" t="n">
         <v>315.73</v>
       </c>
       <c r="K256" t="n">
-        <v>0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>2.96</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="257">
@@ -29534,31 +29534,31 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>186.9</v>
+        <v>185.5</v>
       </c>
       <c r="D257" t="n">
         <v>198.72</v>
       </c>
       <c r="E257" t="n">
-        <v>-11.82</v>
+        <v>-13.22</v>
       </c>
       <c r="F257" t="n">
-        <v>187.6</v>
+        <v>190.58</v>
       </c>
       <c r="G257" t="n">
         <v>192.6</v>
       </c>
       <c r="H257" t="n">
-        <v>-5</v>
+        <v>-2.02</v>
       </c>
       <c r="I257" t="n">
-        <v>184.9</v>
+        <v>185.5</v>
       </c>
       <c r="J257" t="n">
         <v>184.12</v>
       </c>
       <c r="K257" t="n">
-        <v>0.78</v>
+        <v>1.38</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>5.95</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="258">
@@ -29586,31 +29586,31 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2121.8</v>
+        <v>2115</v>
       </c>
       <c r="D258" t="n">
         <v>2129.58</v>
       </c>
       <c r="E258" t="n">
-        <v>-7.78</v>
+        <v>-14.58</v>
       </c>
       <c r="F258" t="n">
-        <v>2121.8</v>
+        <v>2122</v>
       </c>
       <c r="G258" t="n">
         <v>2194.54</v>
       </c>
       <c r="H258" t="n">
-        <v>-72.73999999999999</v>
+        <v>-72.54000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>2097.2</v>
+        <v>2075.1</v>
       </c>
       <c r="J258" t="n">
         <v>2084.18</v>
       </c>
       <c r="K258" t="n">
-        <v>13.02</v>
+        <v>-9.08</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0.37</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="259">
@@ -29638,31 +29638,31 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>11774</v>
+        <v>11623</v>
       </c>
       <c r="D259" t="n">
         <v>12103.03</v>
       </c>
       <c r="E259" t="n">
-        <v>-329.03</v>
+        <v>-480.03</v>
       </c>
       <c r="F259" t="n">
-        <v>11854</v>
+        <v>11840</v>
       </c>
       <c r="G259" t="n">
         <v>12161.71</v>
       </c>
       <c r="H259" t="n">
-        <v>-307.71</v>
+        <v>-321.71</v>
       </c>
       <c r="I259" t="n">
-        <v>11640</v>
+        <v>11614</v>
       </c>
       <c r="J259" t="n">
         <v>11577.27</v>
       </c>
       <c r="K259" t="n">
-        <v>62.73</v>
+        <v>36.73</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2.72</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="260">
@@ -29690,31 +29690,31 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1813.1</v>
+        <v>1773</v>
       </c>
       <c r="D260" t="n">
         <v>1909.32</v>
       </c>
       <c r="E260" t="n">
-        <v>-96.22</v>
+        <v>-136.32</v>
       </c>
       <c r="F260" t="n">
-        <v>1818</v>
+        <v>1795</v>
       </c>
       <c r="G260" t="n">
         <v>1870.62</v>
       </c>
       <c r="H260" t="n">
-        <v>-52.62</v>
+        <v>-75.62</v>
       </c>
       <c r="I260" t="n">
-        <v>1785.4</v>
+        <v>1762.2</v>
       </c>
       <c r="J260" t="n">
         <v>1784.46</v>
       </c>
       <c r="K260" t="n">
-        <v>0.9399999999999999</v>
+        <v>-22.26</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>5.04</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="261">
@@ -29742,31 +29742,31 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1378.4</v>
+        <v>1354.9</v>
       </c>
       <c r="D261" t="n">
         <v>1417.82</v>
       </c>
       <c r="E261" t="n">
-        <v>-39.42</v>
+        <v>-62.92</v>
       </c>
       <c r="F261" t="n">
-        <v>1378.4</v>
+        <v>1368.8</v>
       </c>
       <c r="G261" t="n">
         <v>1427.65</v>
       </c>
       <c r="H261" t="n">
-        <v>-49.25</v>
+        <v>-58.85</v>
       </c>
       <c r="I261" t="n">
-        <v>1351.5</v>
+        <v>1331.1</v>
       </c>
       <c r="J261" t="n">
         <v>1352.45</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.95</v>
+        <v>-21.35</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2.78</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="262">
@@ -29794,31 +29794,31 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D262" t="n">
         <v>1318.03</v>
       </c>
       <c r="E262" t="n">
-        <v>-46.03</v>
+        <v>-45.03</v>
       </c>
       <c r="F262" t="n">
-        <v>1288</v>
+        <v>1281.2</v>
       </c>
       <c r="G262" t="n">
         <v>1308.76</v>
       </c>
       <c r="H262" t="n">
-        <v>-20.76</v>
+        <v>-27.56</v>
       </c>
       <c r="I262" t="n">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="J262" t="n">
         <v>1254.61</v>
       </c>
       <c r="K262" t="n">
-        <v>4.39</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="263">
@@ -29846,31 +29846,31 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>2012</v>
+        <v>2011.2</v>
       </c>
       <c r="D263" t="n">
         <v>2082.89</v>
       </c>
       <c r="E263" t="n">
-        <v>-70.89</v>
+        <v>-71.69</v>
       </c>
       <c r="F263" t="n">
-        <v>2013</v>
+        <v>2018.8</v>
       </c>
       <c r="G263" t="n">
         <v>2068.96</v>
       </c>
       <c r="H263" t="n">
-        <v>-55.96</v>
+        <v>-50.16</v>
       </c>
       <c r="I263" t="n">
-        <v>1985</v>
+        <v>1998</v>
       </c>
       <c r="J263" t="n">
         <v>1985.41</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.41</v>
+        <v>12.59</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="264">
@@ -29898,31 +29898,31 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>386.55</v>
+        <v>388</v>
       </c>
       <c r="D264" t="n">
         <v>440.95</v>
       </c>
       <c r="E264" t="n">
-        <v>-54.4</v>
+        <v>-52.95</v>
       </c>
       <c r="F264" t="n">
-        <v>386.55</v>
+        <v>390.85</v>
       </c>
       <c r="G264" t="n">
         <v>402.95</v>
       </c>
       <c r="H264" t="n">
-        <v>-16.4</v>
+        <v>-12.1</v>
       </c>
       <c r="I264" t="n">
-        <v>379</v>
+        <v>385.8</v>
       </c>
       <c r="J264" t="n">
         <v>377.32</v>
       </c>
       <c r="K264" t="n">
-        <v>1.68</v>
+        <v>8.48</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>12.34</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="265">
@@ -29950,31 +29950,31 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>14462</v>
+        <v>14150</v>
       </c>
       <c r="D265" t="n">
         <v>14456.94</v>
       </c>
       <c r="E265" t="n">
-        <v>5.06</v>
+        <v>-306.94</v>
       </c>
       <c r="F265" t="n">
-        <v>14550</v>
+        <v>14420</v>
       </c>
       <c r="G265" t="n">
         <v>14911.34</v>
       </c>
       <c r="H265" t="n">
-        <v>-361.34</v>
+        <v>-491.34</v>
       </c>
       <c r="I265" t="n">
-        <v>14026</v>
+        <v>14066</v>
       </c>
       <c r="J265" t="n">
         <v>14240.67</v>
       </c>
       <c r="K265" t="n">
-        <v>-214.67</v>
+        <v>-174.67</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>0.04</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="266">
@@ -30002,31 +30002,31 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3415</v>
+        <v>3421.5</v>
       </c>
       <c r="D266" t="n">
         <v>3316.42</v>
       </c>
       <c r="E266" t="n">
-        <v>98.58</v>
+        <v>105.08</v>
       </c>
       <c r="F266" t="n">
-        <v>3425.6</v>
+        <v>3435</v>
       </c>
       <c r="G266" t="n">
         <v>3506.06</v>
       </c>
       <c r="H266" t="n">
-        <v>-80.45999999999999</v>
+        <v>-71.06</v>
       </c>
       <c r="I266" t="n">
-        <v>3371.1</v>
+        <v>3390.2</v>
       </c>
       <c r="J266" t="n">
         <v>3374.11</v>
       </c>
       <c r="K266" t="n">
-        <v>-3.01</v>
+        <v>16.09</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="267">
@@ -30054,31 +30054,31 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>5709.5</v>
+        <v>5745.5</v>
       </c>
       <c r="D267" t="n">
         <v>5999.72</v>
       </c>
       <c r="E267" t="n">
-        <v>-290.22</v>
+        <v>-254.22</v>
       </c>
       <c r="F267" t="n">
-        <v>5767.5</v>
+        <v>5778</v>
       </c>
       <c r="G267" t="n">
         <v>5883.61</v>
       </c>
       <c r="H267" t="n">
-        <v>-116.11</v>
+        <v>-105.61</v>
       </c>
       <c r="I267" t="n">
-        <v>5664.5</v>
+        <v>5694.5</v>
       </c>
       <c r="J267" t="n">
         <v>5624.62</v>
       </c>
       <c r="K267" t="n">
-        <v>39.88</v>
+        <v>69.88</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>4.84</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="268">
@@ -30106,31 +30106,31 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>11380</v>
+        <v>11254</v>
       </c>
       <c r="D268" t="n">
         <v>11679.57</v>
       </c>
       <c r="E268" t="n">
-        <v>-299.57</v>
+        <v>-425.57</v>
       </c>
       <c r="F268" t="n">
-        <v>11383</v>
+        <v>11435</v>
       </c>
       <c r="G268" t="n">
         <v>11656.05</v>
       </c>
       <c r="H268" t="n">
-        <v>-273.05</v>
+        <v>-221.05</v>
       </c>
       <c r="I268" t="n">
-        <v>11234</v>
+        <v>11211</v>
       </c>
       <c r="J268" t="n">
         <v>11264.45</v>
       </c>
       <c r="K268" t="n">
-        <v>-30.45</v>
+        <v>-53.45</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>2.56</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="269">
@@ -30158,31 +30158,31 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1038.95</v>
+        <v>1041.6</v>
       </c>
       <c r="D269" t="n">
         <v>1132.14</v>
       </c>
       <c r="E269" t="n">
-        <v>-93.19</v>
+        <v>-90.54000000000001</v>
       </c>
       <c r="F269" t="n">
-        <v>1039.2</v>
+        <v>1050.6</v>
       </c>
       <c r="G269" t="n">
         <v>1072.12</v>
       </c>
       <c r="H269" t="n">
-        <v>-32.92</v>
+        <v>-21.52</v>
       </c>
       <c r="I269" t="n">
-        <v>1025.55</v>
+        <v>1038</v>
       </c>
       <c r="J269" t="n">
         <v>1022.38</v>
       </c>
       <c r="K269" t="n">
-        <v>3.17</v>
+        <v>15.62</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>8.23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270">
@@ -30210,31 +30210,31 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>942.1</v>
+        <v>938</v>
       </c>
       <c r="D270" t="n">
         <v>1032.29</v>
       </c>
       <c r="E270" t="n">
-        <v>-90.19</v>
+        <v>-94.29000000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>948.45</v>
+        <v>961.35</v>
       </c>
       <c r="G270" t="n">
         <v>972.13</v>
       </c>
       <c r="H270" t="n">
-        <v>-23.68</v>
+        <v>-10.78</v>
       </c>
       <c r="I270" t="n">
-        <v>930.05</v>
+        <v>933.1</v>
       </c>
       <c r="J270" t="n">
         <v>927.12</v>
       </c>
       <c r="K270" t="n">
-        <v>2.93</v>
+        <v>5.98</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>8.74</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -30262,31 +30262,31 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1048.6</v>
+        <v>1053</v>
       </c>
       <c r="D271" t="n">
         <v>1074.56</v>
       </c>
       <c r="E271" t="n">
-        <v>-25.96</v>
+        <v>-21.56</v>
       </c>
       <c r="F271" t="n">
-        <v>1054.8</v>
+        <v>1067.7</v>
       </c>
       <c r="G271" t="n">
         <v>1075.31</v>
       </c>
       <c r="H271" t="n">
-        <v>-20.51</v>
+        <v>-7.61</v>
       </c>
       <c r="I271" t="n">
-        <v>1041.4</v>
+        <v>1053</v>
       </c>
       <c r="J271" t="n">
         <v>1036.98</v>
       </c>
       <c r="K271" t="n">
-        <v>4.42</v>
+        <v>16.02</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="272">
@@ -30314,31 +30314,31 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>288.15</v>
+        <v>286.25</v>
       </c>
       <c r="D272" t="n">
         <v>294.97</v>
       </c>
       <c r="E272" t="n">
-        <v>-6.82</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="F272" t="n">
-        <v>291.5</v>
+        <v>286.95</v>
       </c>
       <c r="G272" t="n">
         <v>295.66</v>
       </c>
       <c r="H272" t="n">
-        <v>-4.16</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="I272" t="n">
-        <v>285.65</v>
+        <v>281.8</v>
       </c>
       <c r="J272" t="n">
         <v>284.84</v>
       </c>
       <c r="K272" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.04</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -30347,11 +30347,11 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N272" t="n">
-        <v>2.31</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="273">
@@ -30366,31 +30366,31 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>173.1</v>
+        <v>176.35</v>
       </c>
       <c r="D273" t="n">
         <v>182.36</v>
       </c>
       <c r="E273" t="n">
-        <v>-9.26</v>
+        <v>-6.01</v>
       </c>
       <c r="F273" t="n">
-        <v>176.1</v>
+        <v>177.59</v>
       </c>
       <c r="G273" t="n">
         <v>179.56</v>
       </c>
       <c r="H273" t="n">
-        <v>-3.46</v>
+        <v>-1.97</v>
       </c>
       <c r="I273" t="n">
-        <v>173.1</v>
+        <v>174.5</v>
       </c>
       <c r="J273" t="n">
         <v>169.64</v>
       </c>
       <c r="K273" t="n">
-        <v>3.46</v>
+        <v>4.86</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>5.08</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="274">
@@ -30418,31 +30418,31 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1180.5</v>
+        <v>1163.6</v>
       </c>
       <c r="D274" t="n">
         <v>1224.43</v>
       </c>
       <c r="E274" t="n">
-        <v>-43.93</v>
+        <v>-60.83</v>
       </c>
       <c r="F274" t="n">
-        <v>1185.5</v>
+        <v>1185</v>
       </c>
       <c r="G274" t="n">
         <v>1219.32</v>
       </c>
       <c r="H274" t="n">
-        <v>-33.82</v>
+        <v>-34.32</v>
       </c>
       <c r="I274" t="n">
-        <v>1157.5</v>
+        <v>1154</v>
       </c>
       <c r="J274" t="n">
         <v>1160.81</v>
       </c>
       <c r="K274" t="n">
-        <v>-3.31</v>
+        <v>-6.81</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>3.59</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="275">
@@ -30470,31 +30470,31 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1589.8</v>
+        <v>1592</v>
       </c>
       <c r="D275" t="n">
         <v>1598.95</v>
       </c>
       <c r="E275" t="n">
-        <v>-9.15</v>
+        <v>-6.95</v>
       </c>
       <c r="F275" t="n">
-        <v>1610.7</v>
+        <v>1608</v>
       </c>
       <c r="G275" t="n">
         <v>1632.68</v>
       </c>
       <c r="H275" t="n">
-        <v>-21.98</v>
+        <v>-24.68</v>
       </c>
       <c r="I275" t="n">
-        <v>1575.8</v>
+        <v>1579.9</v>
       </c>
       <c r="J275" t="n">
         <v>1570.4</v>
       </c>
       <c r="K275" t="n">
-        <v>5.4</v>
+        <v>9.5</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="276">
@@ -30522,31 +30522,31 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>4041.3</v>
+        <v>4064.3</v>
       </c>
       <c r="D276" t="n">
         <v>4115.23</v>
       </c>
       <c r="E276" t="n">
-        <v>-73.93000000000001</v>
+        <v>-50.93</v>
       </c>
       <c r="F276" t="n">
-        <v>4069</v>
+        <v>4085</v>
       </c>
       <c r="G276" t="n">
         <v>4108.8</v>
       </c>
       <c r="H276" t="n">
-        <v>-39.8</v>
+        <v>-23.8</v>
       </c>
       <c r="I276" t="n">
-        <v>4024.8</v>
+        <v>4050</v>
       </c>
       <c r="J276" t="n">
         <v>4023.33</v>
       </c>
       <c r="K276" t="n">
-        <v>1.47</v>
+        <v>26.67</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="277">
@@ -30574,31 +30574,31 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2174.5</v>
+        <v>2186</v>
       </c>
       <c r="D277" t="n">
         <v>2227.53</v>
       </c>
       <c r="E277" t="n">
-        <v>-53.03</v>
+        <v>-41.53</v>
       </c>
       <c r="F277" t="n">
-        <v>2218.8</v>
+        <v>2221.9</v>
       </c>
       <c r="G277" t="n">
         <v>2244.63</v>
       </c>
       <c r="H277" t="n">
-        <v>-25.83</v>
+        <v>-22.73</v>
       </c>
       <c r="I277" t="n">
-        <v>2160.1</v>
+        <v>2179</v>
       </c>
       <c r="J277" t="n">
         <v>2139.28</v>
       </c>
       <c r="K277" t="n">
-        <v>20.82</v>
+        <v>39.72</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="278">
@@ -30626,31 +30626,31 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>514.35</v>
+        <v>518.25</v>
       </c>
       <c r="D278" t="n">
         <v>498.93</v>
       </c>
       <c r="E278" t="n">
-        <v>15.42</v>
+        <v>19.32</v>
       </c>
       <c r="F278" t="n">
-        <v>519.65</v>
+        <v>524.85</v>
       </c>
       <c r="G278" t="n">
         <v>528.72</v>
       </c>
       <c r="H278" t="n">
-        <v>-9.07</v>
+        <v>-3.87</v>
       </c>
       <c r="I278" t="n">
-        <v>511.55</v>
+        <v>517.55</v>
       </c>
       <c r="J278" t="n">
         <v>507.7</v>
       </c>
       <c r="K278" t="n">
-        <v>3.85</v>
+        <v>9.85</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>3.09</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="279">
@@ -30678,31 +30678,31 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>873.15</v>
+        <v>875</v>
       </c>
       <c r="D279" t="n">
         <v>898.98</v>
       </c>
       <c r="E279" t="n">
-        <v>-25.83</v>
+        <v>-23.98</v>
       </c>
       <c r="F279" t="n">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="G279" t="n">
         <v>897.0599999999999</v>
       </c>
       <c r="H279" t="n">
-        <v>-16.06</v>
+        <v>-10.06</v>
       </c>
       <c r="I279" t="n">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="J279" t="n">
         <v>862.22</v>
       </c>
       <c r="K279" t="n">
-        <v>2.78</v>
+        <v>11.78</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N279"/>
+  <dimension ref="A1:N308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14944,6 +14944,1514 @@
       </c>
       <c r="N279" t="n">
         <v>6.15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>118</v>
+      </c>
+      <c r="D280" t="n">
+        <v>113</v>
+      </c>
+      <c r="E280" t="n">
+        <v>5</v>
+      </c>
+      <c r="F280" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G280" t="n">
+        <v>118.24</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I280" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="J280" t="n">
+        <v>115.96</v>
+      </c>
+      <c r="K280" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="D281" t="n">
+        <v>174.77</v>
+      </c>
+      <c r="E281" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F281" t="n">
+        <v>175.57</v>
+      </c>
+      <c r="G281" t="n">
+        <v>174.77</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I281" t="n">
+        <v>172.61</v>
+      </c>
+      <c r="J281" t="n">
+        <v>171.11</v>
+      </c>
+      <c r="K281" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D282" t="n">
+        <v>2203.35</v>
+      </c>
+      <c r="E282" t="n">
+        <v>-63.35</v>
+      </c>
+      <c r="F282" t="n">
+        <v>2153.7</v>
+      </c>
+      <c r="G282" t="n">
+        <v>2203.35</v>
+      </c>
+      <c r="H282" t="n">
+        <v>-49.65</v>
+      </c>
+      <c r="I282" t="n">
+        <v>2125</v>
+      </c>
+      <c r="J282" t="n">
+        <v>2101.37</v>
+      </c>
+      <c r="K282" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>5674</v>
+      </c>
+      <c r="D283" t="n">
+        <v>5679.22</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="F283" t="n">
+        <v>5706</v>
+      </c>
+      <c r="G283" t="n">
+        <v>5799.2</v>
+      </c>
+      <c r="H283" t="n">
+        <v>-93.2</v>
+      </c>
+      <c r="I283" t="n">
+        <v>5534</v>
+      </c>
+      <c r="J283" t="n">
+        <v>5674</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-140</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D284" t="n">
+        <v>5677.29</v>
+      </c>
+      <c r="E284" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="F284" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="G284" t="n">
+        <v>5677.29</v>
+      </c>
+      <c r="H284" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="I284" t="n">
+        <v>5670</v>
+      </c>
+      <c r="J284" t="n">
+        <v>5588.81</v>
+      </c>
+      <c r="K284" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D285" t="n">
+        <v>15019.39</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-169.39</v>
+      </c>
+      <c r="F285" t="n">
+        <v>14953</v>
+      </c>
+      <c r="G285" t="n">
+        <v>15019.39</v>
+      </c>
+      <c r="H285" t="n">
+        <v>-66.39</v>
+      </c>
+      <c r="I285" t="n">
+        <v>14470</v>
+      </c>
+      <c r="J285" t="n">
+        <v>14441.25</v>
+      </c>
+      <c r="K285" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="D286" t="n">
+        <v>475.42</v>
+      </c>
+      <c r="E286" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F286" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="G286" t="n">
+        <v>486.32</v>
+      </c>
+      <c r="H286" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="I286" t="n">
+        <v>465</v>
+      </c>
+      <c r="J286" t="n">
+        <v>477.09</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-12.09</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>4081</v>
+      </c>
+      <c r="D287" t="n">
+        <v>4104.52</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-23.52</v>
+      </c>
+      <c r="F287" t="n">
+        <v>4084.9</v>
+      </c>
+      <c r="G287" t="n">
+        <v>4104.52</v>
+      </c>
+      <c r="H287" t="n">
+        <v>-19.62</v>
+      </c>
+      <c r="I287" t="n">
+        <v>4048.3</v>
+      </c>
+      <c r="J287" t="n">
+        <v>4031.94</v>
+      </c>
+      <c r="K287" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>676.15</v>
+      </c>
+      <c r="D288" t="n">
+        <v>668.4400000000001</v>
+      </c>
+      <c r="E288" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="F288" t="n">
+        <v>682.45</v>
+      </c>
+      <c r="G288" t="n">
+        <v>668.4400000000001</v>
+      </c>
+      <c r="H288" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="I288" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="J288" t="n">
+        <v>658.89</v>
+      </c>
+      <c r="K288" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>3424.8</v>
+      </c>
+      <c r="D289" t="n">
+        <v>3634.89</v>
+      </c>
+      <c r="E289" t="n">
+        <v>-210.09</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3456.4</v>
+      </c>
+      <c r="G289" t="n">
+        <v>3634.89</v>
+      </c>
+      <c r="H289" t="n">
+        <v>-178.49</v>
+      </c>
+      <c r="I289" t="n">
+        <v>3401</v>
+      </c>
+      <c r="J289" t="n">
+        <v>3353.77</v>
+      </c>
+      <c r="K289" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="D290" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-17.18</v>
+      </c>
+      <c r="F290" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="G290" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="H290" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="I290" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J290" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2005.94</v>
+      </c>
+      <c r="E291" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2030.1</v>
+      </c>
+      <c r="G291" t="n">
+        <v>2005.94</v>
+      </c>
+      <c r="H291" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="I291" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1968.15</v>
+      </c>
+      <c r="K291" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>1941.7</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1919.55</v>
+      </c>
+      <c r="E292" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1952.2</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1944.35</v>
+      </c>
+      <c r="H292" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I292" t="n">
+        <v>1933</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1906.78</v>
+      </c>
+      <c r="K292" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2227</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2261.05</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-34.05</v>
+      </c>
+      <c r="F293" t="n">
+        <v>2233.7</v>
+      </c>
+      <c r="G293" t="n">
+        <v>2261.05</v>
+      </c>
+      <c r="H293" t="n">
+        <v>-27.35</v>
+      </c>
+      <c r="I293" t="n">
+        <v>2180.4</v>
+      </c>
+      <c r="J293" t="n">
+        <v>2183.32</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1055.22</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1052.9</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1055.22</v>
+      </c>
+      <c r="H294" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1045.7</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1026.08</v>
+      </c>
+      <c r="K294" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>735.85</v>
+      </c>
+      <c r="D295" t="n">
+        <v>727.46</v>
+      </c>
+      <c r="E295" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="F295" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="G295" t="n">
+        <v>745.61</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-8.51</v>
+      </c>
+      <c r="I295" t="n">
+        <v>725.75</v>
+      </c>
+      <c r="J295" t="n">
+        <v>731.51</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>1260.5</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1255.27</v>
+      </c>
+      <c r="E296" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1282.6</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1267.47</v>
+      </c>
+      <c r="H296" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1260.5</v>
+      </c>
+      <c r="J296" t="n">
+        <v>1243.16</v>
+      </c>
+      <c r="K296" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1183.52</v>
+      </c>
+      <c r="E297" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1210.68</v>
+      </c>
+      <c r="H297" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1186</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1187.5</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>11368</v>
+      </c>
+      <c r="D298" t="n">
+        <v>11241.22</v>
+      </c>
+      <c r="E298" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="F298" t="n">
+        <v>11423</v>
+      </c>
+      <c r="G298" t="n">
+        <v>11359.28</v>
+      </c>
+      <c r="H298" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="I298" t="n">
+        <v>11303</v>
+      </c>
+      <c r="J298" t="n">
+        <v>11138.95</v>
+      </c>
+      <c r="K298" t="n">
+        <v>164.05</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>973.4</v>
+      </c>
+      <c r="D299" t="n">
+        <v>914.72</v>
+      </c>
+      <c r="E299" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="F299" t="n">
+        <v>989.55</v>
+      </c>
+      <c r="G299" t="n">
+        <v>978.86</v>
+      </c>
+      <c r="H299" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="I299" t="n">
+        <v>942.15</v>
+      </c>
+      <c r="J299" t="n">
+        <v>960.09</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-17.94</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="D300" t="n">
+        <v>290.73</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F300" t="n">
+        <v>293.75</v>
+      </c>
+      <c r="G300" t="n">
+        <v>291.04</v>
+      </c>
+      <c r="H300" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I300" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="J300" t="n">
+        <v>285.39</v>
+      </c>
+      <c r="K300" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2570</v>
+      </c>
+      <c r="D301" t="n">
+        <v>2540.69</v>
+      </c>
+      <c r="E301" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="F301" t="n">
+        <v>2583.2</v>
+      </c>
+      <c r="G301" t="n">
+        <v>2540.69</v>
+      </c>
+      <c r="H301" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="I301" t="n">
+        <v>2552</v>
+      </c>
+      <c r="J301" t="n">
+        <v>2495.69</v>
+      </c>
+      <c r="K301" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1807.12</v>
+      </c>
+      <c r="E302" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1888.5</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1868.99</v>
+      </c>
+      <c r="H302" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="I302" t="n">
+        <v>1826.5</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1838.06</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D303" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="E303" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="F303" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="G303" t="n">
+        <v>389.84</v>
+      </c>
+      <c r="H303" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I303" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="J303" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="K303" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>1360.9</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1350.18</v>
+      </c>
+      <c r="E304" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1390.1</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1350.18</v>
+      </c>
+      <c r="H304" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="I304" t="n">
+        <v>1355.3</v>
+      </c>
+      <c r="J304" t="n">
+        <v>1317.49</v>
+      </c>
+      <c r="K304" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>519</v>
+      </c>
+      <c r="D305" t="n">
+        <v>555.3200000000001</v>
+      </c>
+      <c r="E305" t="n">
+        <v>-36.32</v>
+      </c>
+      <c r="F305" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="G305" t="n">
+        <v>555.3200000000001</v>
+      </c>
+      <c r="H305" t="n">
+        <v>-30.92</v>
+      </c>
+      <c r="I305" t="n">
+        <v>513.8</v>
+      </c>
+      <c r="J305" t="n">
+        <v>506.69</v>
+      </c>
+      <c r="K305" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="D306" t="n">
+        <v>177.17</v>
+      </c>
+      <c r="E306" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="F306" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="G306" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I306" t="n">
+        <v>184.39</v>
+      </c>
+      <c r="J306" t="n">
+        <v>182.74</v>
+      </c>
+      <c r="K306" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N306" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1029.85</v>
+      </c>
+      <c r="D307" t="n">
+        <v>979.95</v>
+      </c>
+      <c r="E307" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G307" t="n">
+        <v>1021.07</v>
+      </c>
+      <c r="H307" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="I307" t="n">
+        <v>1013</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1001.8</v>
+      </c>
+      <c r="K307" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>871</v>
+      </c>
+      <c r="D308" t="n">
+        <v>872.77</v>
+      </c>
+      <c r="E308" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="F308" t="n">
+        <v>883.8</v>
+      </c>
+      <c r="G308" t="n">
+        <v>876.28</v>
+      </c>
+      <c r="H308" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="I308" t="n">
+        <v>871</v>
+      </c>
+      <c r="J308" t="n">
+        <v>859.49</v>
+      </c>
+      <c r="K308" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -14957,7 +16465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16174,6 +17682,110 @@
       </c>
       <c r="N23" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24265.15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>24269.81</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I24" t="n">
+        <v>24184.55</v>
+      </c>
+      <c r="J24" t="n">
+        <v>24189.21</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>57702.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>57655.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I25" t="n">
+        <v>57431.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>57384.15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -16187,7 +17799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N279"/>
+  <dimension ref="A1:N308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30718,6 +32330,1514 @@
         <v>2.67</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>118</v>
+      </c>
+      <c r="D280" t="n">
+        <v>114.69</v>
+      </c>
+      <c r="E280" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F280" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G280" t="n">
+        <v>119.19</v>
+      </c>
+      <c r="H280" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I280" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="J280" t="n">
+        <v>116.71</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D281" t="n">
+        <v>2263.58</v>
+      </c>
+      <c r="E281" t="n">
+        <v>-123.58</v>
+      </c>
+      <c r="F281" t="n">
+        <v>2153.7</v>
+      </c>
+      <c r="G281" t="n">
+        <v>2187.17</v>
+      </c>
+      <c r="H281" t="n">
+        <v>-33.47</v>
+      </c>
+      <c r="I281" t="n">
+        <v>2125</v>
+      </c>
+      <c r="J281" t="n">
+        <v>2097.15</v>
+      </c>
+      <c r="K281" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>5674</v>
+      </c>
+      <c r="D282" t="n">
+        <v>5781.4</v>
+      </c>
+      <c r="E282" t="n">
+        <v>-107.4</v>
+      </c>
+      <c r="F282" t="n">
+        <v>5706</v>
+      </c>
+      <c r="G282" t="n">
+        <v>5782.32</v>
+      </c>
+      <c r="H282" t="n">
+        <v>-76.31999999999999</v>
+      </c>
+      <c r="I282" t="n">
+        <v>5534</v>
+      </c>
+      <c r="J282" t="n">
+        <v>5573.14</v>
+      </c>
+      <c r="K282" t="n">
+        <v>-39.14</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D283" t="n">
+        <v>5815.11</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-74.61</v>
+      </c>
+      <c r="F283" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="G283" t="n">
+        <v>5850.23</v>
+      </c>
+      <c r="H283" t="n">
+        <v>-109.73</v>
+      </c>
+      <c r="I283" t="n">
+        <v>5670</v>
+      </c>
+      <c r="J283" t="n">
+        <v>5638.35</v>
+      </c>
+      <c r="K283" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>OIL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="D284" t="n">
+        <v>487.94</v>
+      </c>
+      <c r="E284" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="F284" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="G284" t="n">
+        <v>491.05</v>
+      </c>
+      <c r="H284" t="n">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="I284" t="n">
+        <v>465</v>
+      </c>
+      <c r="J284" t="n">
+        <v>471.62</v>
+      </c>
+      <c r="K284" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>3424.8</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3701.86</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-277.06</v>
+      </c>
+      <c r="F285" t="n">
+        <v>3456.4</v>
+      </c>
+      <c r="G285" t="n">
+        <v>3471.1</v>
+      </c>
+      <c r="H285" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="I285" t="n">
+        <v>3401</v>
+      </c>
+      <c r="J285" t="n">
+        <v>3378.45</v>
+      </c>
+      <c r="K285" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="D286" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="E286" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F286" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="G286" t="n">
+        <v>333.38</v>
+      </c>
+      <c r="H286" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="I286" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J286" t="n">
+        <v>322.76</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="D287" t="n">
+        <v>180.17</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="F287" t="n">
+        <v>175.57</v>
+      </c>
+      <c r="G287" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="H287" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="I287" t="n">
+        <v>172.61</v>
+      </c>
+      <c r="J287" t="n">
+        <v>169.86</v>
+      </c>
+      <c r="K287" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>DLF (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>676.15</v>
+      </c>
+      <c r="D288" t="n">
+        <v>684.04</v>
+      </c>
+      <c r="E288" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="F288" t="n">
+        <v>682.45</v>
+      </c>
+      <c r="G288" t="n">
+        <v>688.48</v>
+      </c>
+      <c r="H288" t="n">
+        <v>-6.03</v>
+      </c>
+      <c r="I288" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="J288" t="n">
+        <v>664.5700000000001</v>
+      </c>
+      <c r="K288" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>1941.7</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1954.78</v>
+      </c>
+      <c r="E289" t="n">
+        <v>-13.08</v>
+      </c>
+      <c r="F289" t="n">
+        <v>1952.2</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1967.81</v>
+      </c>
+      <c r="H289" t="n">
+        <v>-15.61</v>
+      </c>
+      <c r="I289" t="n">
+        <v>1933</v>
+      </c>
+      <c r="J289" t="n">
+        <v>1915.53</v>
+      </c>
+      <c r="K289" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D290" t="n">
+        <v>15401.04</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-551.04</v>
+      </c>
+      <c r="F290" t="n">
+        <v>14953</v>
+      </c>
+      <c r="G290" t="n">
+        <v>15150</v>
+      </c>
+      <c r="H290" t="n">
+        <v>-197</v>
+      </c>
+      <c r="I290" t="n">
+        <v>14470</v>
+      </c>
+      <c r="J290" t="n">
+        <v>14573.45</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-103.45</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2049.07</v>
+      </c>
+      <c r="E291" t="n">
+        <v>-33.07</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2030.1</v>
+      </c>
+      <c r="G291" t="n">
+        <v>2049.2</v>
+      </c>
+      <c r="H291" t="n">
+        <v>-19.1</v>
+      </c>
+      <c r="I291" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1984.2</v>
+      </c>
+      <c r="K291" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>4081</v>
+      </c>
+      <c r="D292" t="n">
+        <v>4143.29</v>
+      </c>
+      <c r="E292" t="n">
+        <v>-62.29</v>
+      </c>
+      <c r="F292" t="n">
+        <v>4084.9</v>
+      </c>
+      <c r="G292" t="n">
+        <v>4101.14</v>
+      </c>
+      <c r="H292" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="I292" t="n">
+        <v>4048.3</v>
+      </c>
+      <c r="J292" t="n">
+        <v>4052.47</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2227</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2317.81</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-90.81</v>
+      </c>
+      <c r="F293" t="n">
+        <v>2233.7</v>
+      </c>
+      <c r="G293" t="n">
+        <v>2271.34</v>
+      </c>
+      <c r="H293" t="n">
+        <v>-37.64</v>
+      </c>
+      <c r="I293" t="n">
+        <v>2180.4</v>
+      </c>
+      <c r="J293" t="n">
+        <v>2186.02</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>INDHOTEL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>735.85</v>
+      </c>
+      <c r="D294" t="n">
+        <v>737.99</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="F294" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="G294" t="n">
+        <v>743.03</v>
+      </c>
+      <c r="H294" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="I294" t="n">
+        <v>725.75</v>
+      </c>
+      <c r="J294" t="n">
+        <v>728.01</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>973.4</v>
+      </c>
+      <c r="D295" t="n">
+        <v>936.92</v>
+      </c>
+      <c r="E295" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="F295" t="n">
+        <v>989.55</v>
+      </c>
+      <c r="G295" t="n">
+        <v>992.01</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="I295" t="n">
+        <v>942.15</v>
+      </c>
+      <c r="J295" t="n">
+        <v>956.09</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-13.94</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1845.26</v>
+      </c>
+      <c r="E296" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1888.5</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1912.28</v>
+      </c>
+      <c r="H296" t="n">
+        <v>-23.78</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1826.5</v>
+      </c>
+      <c r="J296" t="n">
+        <v>1852.86</v>
+      </c>
+      <c r="K296" t="n">
+        <v>-26.36</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>1260.5</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1284.73</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-24.23</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1282.6</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1283.62</v>
+      </c>
+      <c r="H297" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1260.5</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1238.81</v>
+      </c>
+      <c r="K297" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D298" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="E298" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="F298" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="G298" t="n">
+        <v>396.94</v>
+      </c>
+      <c r="H298" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I298" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="J298" t="n">
+        <v>375.72</v>
+      </c>
+      <c r="K298" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>519</v>
+      </c>
+      <c r="D299" t="n">
+        <v>567.26</v>
+      </c>
+      <c r="E299" t="n">
+        <v>-48.26</v>
+      </c>
+      <c r="F299" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="G299" t="n">
+        <v>527.55</v>
+      </c>
+      <c r="H299" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="I299" t="n">
+        <v>513.8</v>
+      </c>
+      <c r="J299" t="n">
+        <v>510.82</v>
+      </c>
+      <c r="K299" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>8.51</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1074.87</v>
+      </c>
+      <c r="E300" t="n">
+        <v>-26.87</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1052.9</v>
+      </c>
+      <c r="G300" t="n">
+        <v>1062.36</v>
+      </c>
+      <c r="H300" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="I300" t="n">
+        <v>1045.7</v>
+      </c>
+      <c r="J300" t="n">
+        <v>1033.67</v>
+      </c>
+      <c r="K300" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1212.1</v>
+      </c>
+      <c r="E301" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1222.9</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1225.85</v>
+      </c>
+      <c r="H301" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="I301" t="n">
+        <v>1186</v>
+      </c>
+      <c r="J301" t="n">
+        <v>1181.7</v>
+      </c>
+      <c r="K301" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>11368</v>
+      </c>
+      <c r="D302" t="n">
+        <v>11442.49</v>
+      </c>
+      <c r="E302" t="n">
+        <v>-74.48999999999999</v>
+      </c>
+      <c r="F302" t="n">
+        <v>11423</v>
+      </c>
+      <c r="G302" t="n">
+        <v>11516.06</v>
+      </c>
+      <c r="H302" t="n">
+        <v>-93.06</v>
+      </c>
+      <c r="I302" t="n">
+        <v>11303</v>
+      </c>
+      <c r="J302" t="n">
+        <v>11218.47</v>
+      </c>
+      <c r="K302" t="n">
+        <v>84.53</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="D303" t="n">
+        <v>181.47</v>
+      </c>
+      <c r="E303" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="F303" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="G303" t="n">
+        <v>188.22</v>
+      </c>
+      <c r="H303" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I303" t="n">
+        <v>184.39</v>
+      </c>
+      <c r="J303" t="n">
+        <v>181.39</v>
+      </c>
+      <c r="K303" t="n">
+        <v>3</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="D304" t="n">
+        <v>296.38</v>
+      </c>
+      <c r="E304" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="F304" t="n">
+        <v>293.75</v>
+      </c>
+      <c r="G304" t="n">
+        <v>295.62</v>
+      </c>
+      <c r="H304" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="I304" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="J304" t="n">
+        <v>287.25</v>
+      </c>
+      <c r="K304" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>1029.85</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1004.56</v>
+      </c>
+      <c r="E305" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="F305" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G305" t="n">
+        <v>1050.37</v>
+      </c>
+      <c r="H305" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="I305" t="n">
+        <v>1013</v>
+      </c>
+      <c r="J305" t="n">
+        <v>1010.9</v>
+      </c>
+      <c r="K305" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>MAZDOCK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2570</v>
+      </c>
+      <c r="D306" t="n">
+        <v>2608.88</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-38.88</v>
+      </c>
+      <c r="F306" t="n">
+        <v>2583.2</v>
+      </c>
+      <c r="G306" t="n">
+        <v>2625.43</v>
+      </c>
+      <c r="H306" t="n">
+        <v>-42.23</v>
+      </c>
+      <c r="I306" t="n">
+        <v>2552</v>
+      </c>
+      <c r="J306" t="n">
+        <v>2519.46</v>
+      </c>
+      <c r="K306" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N306" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1360.9</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1390.56</v>
+      </c>
+      <c r="E307" t="n">
+        <v>-29.66</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1390.1</v>
+      </c>
+      <c r="G307" t="n">
+        <v>1394.25</v>
+      </c>
+      <c r="H307" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="I307" t="n">
+        <v>1355.3</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1331.11</v>
+      </c>
+      <c r="K307" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>871</v>
+      </c>
+      <c r="D308" t="n">
+        <v>891.58</v>
+      </c>
+      <c r="E308" t="n">
+        <v>-20.58</v>
+      </c>
+      <c r="F308" t="n">
+        <v>883.8</v>
+      </c>
+      <c r="G308" t="n">
+        <v>885.39</v>
+      </c>
+      <c r="H308" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="I308" t="n">
+        <v>871</v>
+      </c>
+      <c r="J308" t="n">
+        <v>857.23</v>
+      </c>
+      <c r="K308" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -14958,31 +14958,31 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>118</v>
+        <v>117.48</v>
       </c>
       <c r="D280" t="n">
         <v>113</v>
       </c>
       <c r="E280" t="n">
-        <v>5</v>
+        <v>4.48</v>
       </c>
       <c r="F280" t="n">
-        <v>119.1</v>
+        <v>117.59</v>
       </c>
       <c r="G280" t="n">
         <v>118.24</v>
       </c>
       <c r="H280" t="n">
-        <v>0.86</v>
+        <v>-0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>117.44</v>
+        <v>116.03</v>
       </c>
       <c r="J280" t="n">
         <v>115.96</v>
       </c>
       <c r="K280" t="n">
-        <v>1.48</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>4.42</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="281">
@@ -15010,31 +15010,31 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>173.8</v>
+        <v>173.1</v>
       </c>
       <c r="D281" t="n">
         <v>174.77</v>
       </c>
       <c r="E281" t="n">
-        <v>-0.97</v>
+        <v>-1.67</v>
       </c>
       <c r="F281" t="n">
-        <v>175.57</v>
+        <v>176.1</v>
       </c>
       <c r="G281" t="n">
         <v>174.77</v>
       </c>
       <c r="H281" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="I281" t="n">
-        <v>172.61</v>
+        <v>173.1</v>
       </c>
       <c r="J281" t="n">
         <v>171.11</v>
       </c>
       <c r="K281" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="282">
@@ -15062,31 +15062,31 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2140</v>
+        <v>2121.8</v>
       </c>
       <c r="D282" t="n">
         <v>2203.35</v>
       </c>
       <c r="E282" t="n">
-        <v>-63.35</v>
+        <v>-81.55</v>
       </c>
       <c r="F282" t="n">
-        <v>2153.7</v>
+        <v>2121.8</v>
       </c>
       <c r="G282" t="n">
         <v>2203.35</v>
       </c>
       <c r="H282" t="n">
-        <v>-49.65</v>
+        <v>-81.55</v>
       </c>
       <c r="I282" t="n">
-        <v>2125</v>
+        <v>2097.2</v>
       </c>
       <c r="J282" t="n">
         <v>2101.37</v>
       </c>
       <c r="K282" t="n">
-        <v>23.63</v>
+        <v>-4.17</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="283">
@@ -15114,31 +15114,31 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>5674</v>
+        <v>5510</v>
       </c>
       <c r="D283" t="n">
         <v>5679.22</v>
       </c>
       <c r="E283" t="n">
-        <v>-5.22</v>
+        <v>-169.22</v>
       </c>
       <c r="F283" t="n">
-        <v>5706</v>
+        <v>5577</v>
       </c>
       <c r="G283" t="n">
         <v>5799.2</v>
       </c>
       <c r="H283" t="n">
-        <v>-93.2</v>
+        <v>-222.2</v>
       </c>
       <c r="I283" t="n">
-        <v>5534</v>
+        <v>5475.5</v>
       </c>
       <c r="J283" t="n">
         <v>5674</v>
       </c>
       <c r="K283" t="n">
-        <v>-140</v>
+        <v>-198.5</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -15147,11 +15147,11 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N283" t="n">
-        <v>0.09</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="284">
@@ -15166,31 +15166,31 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>5740.5</v>
+        <v>5709.5</v>
       </c>
       <c r="D284" t="n">
         <v>5677.29</v>
       </c>
       <c r="E284" t="n">
-        <v>63.21</v>
+        <v>32.21</v>
       </c>
       <c r="F284" t="n">
-        <v>5740.5</v>
+        <v>5767.5</v>
       </c>
       <c r="G284" t="n">
         <v>5677.29</v>
       </c>
       <c r="H284" t="n">
-        <v>63.21</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>5670</v>
+        <v>5664.5</v>
       </c>
       <c r="J284" t="n">
         <v>5588.81</v>
       </c>
       <c r="K284" t="n">
-        <v>81.19</v>
+        <v>75.69</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>1.11</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="285">
@@ -15218,31 +15218,31 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>14850</v>
+        <v>14462</v>
       </c>
       <c r="D285" t="n">
         <v>15019.39</v>
       </c>
       <c r="E285" t="n">
-        <v>-169.39</v>
+        <v>-557.39</v>
       </c>
       <c r="F285" t="n">
-        <v>14953</v>
+        <v>14550</v>
       </c>
       <c r="G285" t="n">
         <v>15019.39</v>
       </c>
       <c r="H285" t="n">
-        <v>-66.39</v>
+        <v>-469.39</v>
       </c>
       <c r="I285" t="n">
-        <v>14470</v>
+        <v>14026</v>
       </c>
       <c r="J285" t="n">
         <v>14441.25</v>
       </c>
       <c r="K285" t="n">
-        <v>28.75</v>
+        <v>-415.25</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -15251,11 +15251,11 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N285" t="n">
-        <v>1.13</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="286">
@@ -15270,31 +15270,31 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>480.9</v>
+        <v>474.85</v>
       </c>
       <c r="D286" t="n">
         <v>475.42</v>
       </c>
       <c r="E286" t="n">
-        <v>5.48</v>
+        <v>-0.57</v>
       </c>
       <c r="F286" t="n">
-        <v>481.5</v>
+        <v>485.8</v>
       </c>
       <c r="G286" t="n">
         <v>486.32</v>
       </c>
       <c r="H286" t="n">
-        <v>-4.82</v>
+        <v>-0.52</v>
       </c>
       <c r="I286" t="n">
-        <v>465</v>
+        <v>472.9</v>
       </c>
       <c r="J286" t="n">
         <v>477.09</v>
       </c>
       <c r="K286" t="n">
-        <v>-12.09</v>
+        <v>-4.19</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>1.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="287">
@@ -15322,31 +15322,31 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>4081</v>
+        <v>4041.3</v>
       </c>
       <c r="D287" t="n">
         <v>4104.52</v>
       </c>
       <c r="E287" t="n">
-        <v>-23.52</v>
+        <v>-63.22</v>
       </c>
       <c r="F287" t="n">
-        <v>4084.9</v>
+        <v>4069</v>
       </c>
       <c r="G287" t="n">
         <v>4104.52</v>
       </c>
       <c r="H287" t="n">
-        <v>-19.62</v>
+        <v>-35.52</v>
       </c>
       <c r="I287" t="n">
-        <v>4048.3</v>
+        <v>4024.8</v>
       </c>
       <c r="J287" t="n">
         <v>4031.94</v>
       </c>
       <c r="K287" t="n">
-        <v>16.36</v>
+        <v>-7.14</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>0.57</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="288">
@@ -15374,31 +15374,31 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>676.15</v>
+        <v>669.9</v>
       </c>
       <c r="D288" t="n">
         <v>668.4400000000001</v>
       </c>
       <c r="E288" t="n">
-        <v>7.71</v>
+        <v>1.46</v>
       </c>
       <c r="F288" t="n">
-        <v>682.45</v>
+        <v>674.65</v>
       </c>
       <c r="G288" t="n">
         <v>668.4400000000001</v>
       </c>
       <c r="H288" t="n">
-        <v>14.01</v>
+        <v>6.21</v>
       </c>
       <c r="I288" t="n">
-        <v>671.95</v>
+        <v>658.3</v>
       </c>
       <c r="J288" t="n">
         <v>658.89</v>
       </c>
       <c r="K288" t="n">
-        <v>13.06</v>
+        <v>-0.59</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>1.15</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="289">
@@ -15426,31 +15426,31 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3424.8</v>
+        <v>3415</v>
       </c>
       <c r="D289" t="n">
         <v>3634.89</v>
       </c>
       <c r="E289" t="n">
-        <v>-210.09</v>
+        <v>-219.89</v>
       </c>
       <c r="F289" t="n">
-        <v>3456.4</v>
+        <v>3425.6</v>
       </c>
       <c r="G289" t="n">
         <v>3634.89</v>
       </c>
       <c r="H289" t="n">
-        <v>-178.49</v>
+        <v>-209.29</v>
       </c>
       <c r="I289" t="n">
-        <v>3401</v>
+        <v>3371.1</v>
       </c>
       <c r="J289" t="n">
         <v>3353.77</v>
       </c>
       <c r="K289" t="n">
-        <v>47.23</v>
+        <v>17.33</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>5.78</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="290">
@@ -15478,31 +15478,31 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>327.95</v>
+        <v>320</v>
       </c>
       <c r="D290" t="n">
         <v>345.13</v>
       </c>
       <c r="E290" t="n">
-        <v>-17.18</v>
+        <v>-25.13</v>
       </c>
       <c r="F290" t="n">
-        <v>328.5</v>
+        <v>322.85</v>
       </c>
       <c r="G290" t="n">
         <v>345.13</v>
       </c>
       <c r="H290" t="n">
-        <v>-16.63</v>
+        <v>-22.28</v>
       </c>
       <c r="I290" t="n">
-        <v>321.35</v>
+        <v>315.85</v>
       </c>
       <c r="J290" t="n">
         <v>327.95</v>
       </c>
       <c r="K290" t="n">
-        <v>-6.6</v>
+        <v>-12.1</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>4.98</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="291">
@@ -15530,31 +15530,31 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D291" t="n">
         <v>2005.94</v>
       </c>
       <c r="E291" t="n">
-        <v>10.06</v>
+        <v>6.06</v>
       </c>
       <c r="F291" t="n">
-        <v>2030.1</v>
+        <v>2013</v>
       </c>
       <c r="G291" t="n">
         <v>2005.94</v>
       </c>
       <c r="H291" t="n">
-        <v>24.16</v>
+        <v>7.06</v>
       </c>
       <c r="I291" t="n">
-        <v>2013</v>
+        <v>1985</v>
       </c>
       <c r="J291" t="n">
         <v>1968.15</v>
       </c>
       <c r="K291" t="n">
-        <v>44.85</v>
+        <v>16.85</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="292">
@@ -15582,31 +15582,31 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1941.7</v>
+        <v>1922</v>
       </c>
       <c r="D292" t="n">
         <v>1919.55</v>
       </c>
       <c r="E292" t="n">
-        <v>22.15</v>
+        <v>2.45</v>
       </c>
       <c r="F292" t="n">
-        <v>1952.2</v>
+        <v>1941.8</v>
       </c>
       <c r="G292" t="n">
         <v>1944.35</v>
       </c>
       <c r="H292" t="n">
-        <v>7.85</v>
+        <v>-2.55</v>
       </c>
       <c r="I292" t="n">
-        <v>1933</v>
+        <v>1922</v>
       </c>
       <c r="J292" t="n">
         <v>1906.78</v>
       </c>
       <c r="K292" t="n">
-        <v>26.22</v>
+        <v>15.22</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>1.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="293">
@@ -15634,31 +15634,31 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2227</v>
+        <v>2174.5</v>
       </c>
       <c r="D293" t="n">
         <v>2261.05</v>
       </c>
       <c r="E293" t="n">
-        <v>-34.05</v>
+        <v>-86.55</v>
       </c>
       <c r="F293" t="n">
-        <v>2233.7</v>
+        <v>2218.8</v>
       </c>
       <c r="G293" t="n">
         <v>2261.05</v>
       </c>
       <c r="H293" t="n">
-        <v>-27.35</v>
+        <v>-42.25</v>
       </c>
       <c r="I293" t="n">
-        <v>2180.4</v>
+        <v>2160.1</v>
       </c>
       <c r="J293" t="n">
         <v>2183.32</v>
       </c>
       <c r="K293" t="n">
-        <v>-2.92</v>
+        <v>-23.22</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>1.51</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="294">
@@ -15686,31 +15686,31 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1048</v>
+        <v>1048.6</v>
       </c>
       <c r="D294" t="n">
         <v>1055.22</v>
       </c>
       <c r="E294" t="n">
-        <v>-7.22</v>
+        <v>-6.62</v>
       </c>
       <c r="F294" t="n">
-        <v>1052.9</v>
+        <v>1054.8</v>
       </c>
       <c r="G294" t="n">
         <v>1055.22</v>
       </c>
       <c r="H294" t="n">
-        <v>-2.32</v>
+        <v>-0.42</v>
       </c>
       <c r="I294" t="n">
-        <v>1045.7</v>
+        <v>1041.4</v>
       </c>
       <c r="J294" t="n">
         <v>1026.08</v>
       </c>
       <c r="K294" t="n">
-        <v>19.62</v>
+        <v>15.32</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="295">
@@ -15738,31 +15738,31 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>735.85</v>
+        <v>723.35</v>
       </c>
       <c r="D295" t="n">
         <v>727.46</v>
       </c>
       <c r="E295" t="n">
-        <v>8.390000000000001</v>
+        <v>-4.11</v>
       </c>
       <c r="F295" t="n">
-        <v>737.1</v>
+        <v>724.95</v>
       </c>
       <c r="G295" t="n">
         <v>745.61</v>
       </c>
       <c r="H295" t="n">
-        <v>-8.51</v>
+        <v>-20.66</v>
       </c>
       <c r="I295" t="n">
-        <v>725.75</v>
+        <v>714.15</v>
       </c>
       <c r="J295" t="n">
         <v>731.51</v>
       </c>
       <c r="K295" t="n">
-        <v>-5.76</v>
+        <v>-17.36</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>1.15</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="296">
@@ -15790,31 +15790,31 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1260.5</v>
+        <v>1272</v>
       </c>
       <c r="D296" t="n">
         <v>1255.27</v>
       </c>
       <c r="E296" t="n">
-        <v>5.23</v>
+        <v>16.73</v>
       </c>
       <c r="F296" t="n">
-        <v>1282.6</v>
+        <v>1288</v>
       </c>
       <c r="G296" t="n">
         <v>1267.47</v>
       </c>
       <c r="H296" t="n">
-        <v>15.13</v>
+        <v>20.53</v>
       </c>
       <c r="I296" t="n">
-        <v>1260.5</v>
+        <v>1259</v>
       </c>
       <c r="J296" t="n">
         <v>1243.16</v>
       </c>
       <c r="K296" t="n">
-        <v>17.34</v>
+        <v>15.84</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>0.42</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="297">
@@ -15842,31 +15842,31 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1203</v>
+        <v>1180.5</v>
       </c>
       <c r="D297" t="n">
         <v>1183.52</v>
       </c>
       <c r="E297" t="n">
-        <v>19.48</v>
+        <v>-3.02</v>
       </c>
       <c r="F297" t="n">
-        <v>1222.9</v>
+        <v>1185.5</v>
       </c>
       <c r="G297" t="n">
         <v>1210.68</v>
       </c>
       <c r="H297" t="n">
-        <v>12.22</v>
+        <v>-25.18</v>
       </c>
       <c r="I297" t="n">
-        <v>1186</v>
+        <v>1157.5</v>
       </c>
       <c r="J297" t="n">
         <v>1187.5</v>
       </c>
       <c r="K297" t="n">
-        <v>-1.5</v>
+        <v>-30</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>1.65</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="298">
@@ -15894,31 +15894,31 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>11368</v>
+        <v>11380</v>
       </c>
       <c r="D298" t="n">
         <v>11241.22</v>
       </c>
       <c r="E298" t="n">
-        <v>126.78</v>
+        <v>138.78</v>
       </c>
       <c r="F298" t="n">
-        <v>11423</v>
+        <v>11383</v>
       </c>
       <c r="G298" t="n">
         <v>11359.28</v>
       </c>
       <c r="H298" t="n">
-        <v>63.72</v>
+        <v>23.72</v>
       </c>
       <c r="I298" t="n">
-        <v>11303</v>
+        <v>11234</v>
       </c>
       <c r="J298" t="n">
         <v>11138.95</v>
       </c>
       <c r="K298" t="n">
-        <v>164.05</v>
+        <v>95.05</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="299">
@@ -15946,31 +15946,31 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>973.4</v>
+        <v>942.1</v>
       </c>
       <c r="D299" t="n">
         <v>914.72</v>
       </c>
       <c r="E299" t="n">
-        <v>58.68</v>
+        <v>27.38</v>
       </c>
       <c r="F299" t="n">
-        <v>989.55</v>
+        <v>948.45</v>
       </c>
       <c r="G299" t="n">
         <v>978.86</v>
       </c>
       <c r="H299" t="n">
-        <v>10.69</v>
+        <v>-30.41</v>
       </c>
       <c r="I299" t="n">
-        <v>942.15</v>
+        <v>930.05</v>
       </c>
       <c r="J299" t="n">
         <v>960.09</v>
       </c>
       <c r="K299" t="n">
-        <v>-17.94</v>
+        <v>-30.04</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>6.42</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="300">
@@ -15998,31 +15998,31 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>291.4</v>
+        <v>288.15</v>
       </c>
       <c r="D300" t="n">
         <v>290.73</v>
       </c>
       <c r="E300" t="n">
-        <v>0.67</v>
+        <v>-2.58</v>
       </c>
       <c r="F300" t="n">
-        <v>293.75</v>
+        <v>291.5</v>
       </c>
       <c r="G300" t="n">
         <v>291.04</v>
       </c>
       <c r="H300" t="n">
-        <v>2.71</v>
+        <v>0.46</v>
       </c>
       <c r="I300" t="n">
-        <v>286.6</v>
+        <v>285.65</v>
       </c>
       <c r="J300" t="n">
         <v>285.39</v>
       </c>
       <c r="K300" t="n">
-        <v>1.21</v>
+        <v>0.26</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0.23</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="301">
@@ -16050,31 +16050,31 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2570</v>
+        <v>2559.18</v>
       </c>
       <c r="D301" t="n">
         <v>2540.69</v>
       </c>
       <c r="E301" t="n">
-        <v>29.31</v>
+        <v>18.49</v>
       </c>
       <c r="F301" t="n">
-        <v>2583.2</v>
+        <v>2599.81</v>
       </c>
       <c r="G301" t="n">
         <v>2540.69</v>
       </c>
       <c r="H301" t="n">
-        <v>42.51</v>
+        <v>59.12</v>
       </c>
       <c r="I301" t="n">
-        <v>2552</v>
+        <v>2533.43</v>
       </c>
       <c r="J301" t="n">
         <v>2495.69</v>
       </c>
       <c r="K301" t="n">
-        <v>56.31</v>
+        <v>37.74</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>1.15</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="302">
@@ -16102,31 +16102,31 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1882</v>
+        <v>1813.1</v>
       </c>
       <c r="D302" t="n">
         <v>1807.12</v>
       </c>
       <c r="E302" t="n">
-        <v>74.88</v>
+        <v>5.98</v>
       </c>
       <c r="F302" t="n">
-        <v>1888.5</v>
+        <v>1818</v>
       </c>
       <c r="G302" t="n">
         <v>1868.99</v>
       </c>
       <c r="H302" t="n">
-        <v>19.51</v>
+        <v>-50.99</v>
       </c>
       <c r="I302" t="n">
-        <v>1826.5</v>
+        <v>1785.4</v>
       </c>
       <c r="J302" t="n">
         <v>1838.06</v>
       </c>
       <c r="K302" t="n">
-        <v>-11.56</v>
+        <v>-52.66</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>4.14</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="303">
@@ -16154,31 +16154,31 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>385.6</v>
+        <v>386.55</v>
       </c>
       <c r="D303" t="n">
         <v>354.62</v>
       </c>
       <c r="E303" t="n">
-        <v>30.98</v>
+        <v>31.93</v>
       </c>
       <c r="F303" t="n">
-        <v>395.75</v>
+        <v>386.55</v>
       </c>
       <c r="G303" t="n">
         <v>389.84</v>
       </c>
       <c r="H303" t="n">
-        <v>5.91</v>
+        <v>-3.29</v>
       </c>
       <c r="I303" t="n">
-        <v>385.1</v>
+        <v>379</v>
       </c>
       <c r="J303" t="n">
         <v>382.45</v>
       </c>
       <c r="K303" t="n">
-        <v>2.65</v>
+        <v>-3.45</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>8.74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304">
@@ -16206,31 +16206,31 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1360.9</v>
+        <v>1378.4</v>
       </c>
       <c r="D304" t="n">
         <v>1350.18</v>
       </c>
       <c r="E304" t="n">
-        <v>10.72</v>
+        <v>28.22</v>
       </c>
       <c r="F304" t="n">
-        <v>1390.1</v>
+        <v>1378.4</v>
       </c>
       <c r="G304" t="n">
         <v>1350.18</v>
       </c>
       <c r="H304" t="n">
-        <v>39.92</v>
+        <v>28.22</v>
       </c>
       <c r="I304" t="n">
-        <v>1355.3</v>
+        <v>1351.5</v>
       </c>
       <c r="J304" t="n">
         <v>1317.49</v>
       </c>
       <c r="K304" t="n">
-        <v>37.81</v>
+        <v>34.01</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>0.79</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="305">
@@ -16258,31 +16258,31 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>519</v>
+        <v>514.35</v>
       </c>
       <c r="D305" t="n">
         <v>555.3200000000001</v>
       </c>
       <c r="E305" t="n">
-        <v>-36.32</v>
+        <v>-40.97</v>
       </c>
       <c r="F305" t="n">
-        <v>524.4</v>
+        <v>519.65</v>
       </c>
       <c r="G305" t="n">
         <v>555.3200000000001</v>
       </c>
       <c r="H305" t="n">
-        <v>-30.92</v>
+        <v>-35.67</v>
       </c>
       <c r="I305" t="n">
-        <v>513.8</v>
+        <v>511.55</v>
       </c>
       <c r="J305" t="n">
         <v>506.69</v>
       </c>
       <c r="K305" t="n">
-        <v>7.11</v>
+        <v>4.86</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>6.54</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="306">
@@ -16310,31 +16310,31 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>184.68</v>
+        <v>186.9</v>
       </c>
       <c r="D306" t="n">
         <v>177.17</v>
       </c>
       <c r="E306" t="n">
-        <v>7.51</v>
+        <v>9.73</v>
       </c>
       <c r="F306" t="n">
-        <v>189.46</v>
+        <v>187.6</v>
       </c>
       <c r="G306" t="n">
         <v>186.29</v>
       </c>
       <c r="H306" t="n">
-        <v>3.17</v>
+        <v>1.31</v>
       </c>
       <c r="I306" t="n">
-        <v>184.39</v>
+        <v>184.9</v>
       </c>
       <c r="J306" t="n">
         <v>182.74</v>
       </c>
       <c r="K306" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.24</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="307">
@@ -16362,31 +16362,31 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1029.85</v>
+        <v>1038.95</v>
       </c>
       <c r="D307" t="n">
         <v>979.95</v>
       </c>
       <c r="E307" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="F307" t="n">
-        <v>1048</v>
+        <v>1039.2</v>
       </c>
       <c r="G307" t="n">
         <v>1021.07</v>
       </c>
       <c r="H307" t="n">
-        <v>26.93</v>
+        <v>18.13</v>
       </c>
       <c r="I307" t="n">
-        <v>1013</v>
+        <v>1025.55</v>
       </c>
       <c r="J307" t="n">
         <v>1001.8</v>
       </c>
       <c r="K307" t="n">
-        <v>11.2</v>
+        <v>23.75</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -16395,11 +16395,11 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N307" t="n">
-        <v>5.09</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="308">
@@ -16414,31 +16414,31 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>871</v>
+        <v>873.15</v>
       </c>
       <c r="D308" t="n">
         <v>872.77</v>
       </c>
       <c r="E308" t="n">
-        <v>-1.77</v>
+        <v>0.38</v>
       </c>
       <c r="F308" t="n">
-        <v>883.8</v>
+        <v>881</v>
       </c>
       <c r="G308" t="n">
         <v>876.28</v>
       </c>
       <c r="H308" t="n">
-        <v>7.52</v>
+        <v>4.72</v>
       </c>
       <c r="I308" t="n">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="J308" t="n">
         <v>859.49</v>
       </c>
       <c r="K308" t="n">
-        <v>11.51</v>
+        <v>5.51</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -17696,31 +17696,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24231.85</v>
+        <v>24078.3</v>
       </c>
       <c r="D24" t="n">
         <v>24231.85</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-153.55</v>
       </c>
       <c r="F24" t="n">
-        <v>24265.15</v>
+        <v>24172.85</v>
       </c>
       <c r="G24" t="n">
         <v>24269.81</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.66</v>
+        <v>-96.95999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>24184.55</v>
+        <v>24025.65</v>
       </c>
       <c r="J24" t="n">
         <v>24189.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.66</v>
+        <v>-163.56</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="25">
@@ -17748,31 +17748,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57495.9</v>
+        <v>57239.75</v>
       </c>
       <c r="D25" t="n">
         <v>57495.9</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-256.15</v>
       </c>
       <c r="F25" t="n">
-        <v>57702.95</v>
+        <v>57356.85</v>
       </c>
       <c r="G25" t="n">
         <v>57655.3</v>
       </c>
       <c r="H25" t="n">
-        <v>47.65</v>
+        <v>-298.45</v>
       </c>
       <c r="I25" t="n">
-        <v>57431.8</v>
+        <v>57001.75</v>
       </c>
       <c r="J25" t="n">
         <v>57384.15</v>
       </c>
       <c r="K25" t="n">
-        <v>47.65</v>
+        <v>-382.4</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -32342,31 +32342,31 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>118</v>
+        <v>117.48</v>
       </c>
       <c r="D280" t="n">
         <v>114.69</v>
       </c>
       <c r="E280" t="n">
-        <v>3.31</v>
+        <v>2.79</v>
       </c>
       <c r="F280" t="n">
-        <v>119.1</v>
+        <v>117.59</v>
       </c>
       <c r="G280" t="n">
         <v>119.19</v>
       </c>
       <c r="H280" t="n">
-        <v>-0.09</v>
+        <v>-1.6</v>
       </c>
       <c r="I280" t="n">
-        <v>117.44</v>
+        <v>116.03</v>
       </c>
       <c r="J280" t="n">
         <v>116.71</v>
       </c>
       <c r="K280" t="n">
-        <v>0.73</v>
+        <v>-0.68</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="281">
@@ -32394,31 +32394,31 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2140</v>
+        <v>2121.8</v>
       </c>
       <c r="D281" t="n">
         <v>2263.58</v>
       </c>
       <c r="E281" t="n">
-        <v>-123.58</v>
+        <v>-141.78</v>
       </c>
       <c r="F281" t="n">
-        <v>2153.7</v>
+        <v>2121.8</v>
       </c>
       <c r="G281" t="n">
         <v>2187.17</v>
       </c>
       <c r="H281" t="n">
-        <v>-33.47</v>
+        <v>-65.37</v>
       </c>
       <c r="I281" t="n">
-        <v>2125</v>
+        <v>2097.2</v>
       </c>
       <c r="J281" t="n">
         <v>2097.15</v>
       </c>
       <c r="K281" t="n">
-        <v>27.85</v>
+        <v>0.05</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>5.46</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="282">
@@ -32446,31 +32446,31 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>5674</v>
+        <v>5510</v>
       </c>
       <c r="D282" t="n">
         <v>5781.4</v>
       </c>
       <c r="E282" t="n">
-        <v>-107.4</v>
+        <v>-271.4</v>
       </c>
       <c r="F282" t="n">
-        <v>5706</v>
+        <v>5577</v>
       </c>
       <c r="G282" t="n">
         <v>5782.32</v>
       </c>
       <c r="H282" t="n">
-        <v>-76.31999999999999</v>
+        <v>-205.32</v>
       </c>
       <c r="I282" t="n">
-        <v>5534</v>
+        <v>5475.5</v>
       </c>
       <c r="J282" t="n">
         <v>5573.14</v>
       </c>
       <c r="K282" t="n">
-        <v>-39.14</v>
+        <v>-97.64</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -32479,11 +32479,11 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N282" t="n">
-        <v>1.86</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="283">
@@ -32498,31 +32498,31 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>5740.5</v>
+        <v>5709.5</v>
       </c>
       <c r="D283" t="n">
         <v>5815.11</v>
       </c>
       <c r="E283" t="n">
-        <v>-74.61</v>
+        <v>-105.61</v>
       </c>
       <c r="F283" t="n">
-        <v>5740.5</v>
+        <v>5767.5</v>
       </c>
       <c r="G283" t="n">
         <v>5850.23</v>
       </c>
       <c r="H283" t="n">
-        <v>-109.73</v>
+        <v>-82.73</v>
       </c>
       <c r="I283" t="n">
-        <v>5670</v>
+        <v>5664.5</v>
       </c>
       <c r="J283" t="n">
         <v>5638.35</v>
       </c>
       <c r="K283" t="n">
-        <v>31.65</v>
+        <v>26.15</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>1.28</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="284">
@@ -32550,31 +32550,31 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>480.9</v>
+        <v>474.85</v>
       </c>
       <c r="D284" t="n">
         <v>487.94</v>
       </c>
       <c r="E284" t="n">
-        <v>-7.04</v>
+        <v>-13.09</v>
       </c>
       <c r="F284" t="n">
-        <v>481.5</v>
+        <v>485.8</v>
       </c>
       <c r="G284" t="n">
         <v>491.05</v>
       </c>
       <c r="H284" t="n">
-        <v>-9.550000000000001</v>
+        <v>-5.25</v>
       </c>
       <c r="I284" t="n">
-        <v>465</v>
+        <v>472.9</v>
       </c>
       <c r="J284" t="n">
         <v>471.62</v>
       </c>
       <c r="K284" t="n">
-        <v>-6.62</v>
+        <v>1.28</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>1.44</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="285">
@@ -32602,31 +32602,31 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3424.8</v>
+        <v>3415</v>
       </c>
       <c r="D285" t="n">
         <v>3701.86</v>
       </c>
       <c r="E285" t="n">
-        <v>-277.06</v>
+        <v>-286.86</v>
       </c>
       <c r="F285" t="n">
-        <v>3456.4</v>
+        <v>3425.6</v>
       </c>
       <c r="G285" t="n">
         <v>3471.1</v>
       </c>
       <c r="H285" t="n">
-        <v>-14.7</v>
+        <v>-45.5</v>
       </c>
       <c r="I285" t="n">
-        <v>3401</v>
+        <v>3371.1</v>
       </c>
       <c r="J285" t="n">
         <v>3378.45</v>
       </c>
       <c r="K285" t="n">
-        <v>22.55</v>
+        <v>-7.35</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>7.48</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="286">
@@ -32654,31 +32654,31 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>327.95</v>
+        <v>320</v>
       </c>
       <c r="D286" t="n">
         <v>350.95</v>
       </c>
       <c r="E286" t="n">
-        <v>-23</v>
+        <v>-30.95</v>
       </c>
       <c r="F286" t="n">
-        <v>328.5</v>
+        <v>322.85</v>
       </c>
       <c r="G286" t="n">
         <v>333.38</v>
       </c>
       <c r="H286" t="n">
-        <v>-4.88</v>
+        <v>-10.53</v>
       </c>
       <c r="I286" t="n">
-        <v>321.35</v>
+        <v>315.85</v>
       </c>
       <c r="J286" t="n">
         <v>322.76</v>
       </c>
       <c r="K286" t="n">
-        <v>-1.41</v>
+        <v>-6.91</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>6.55</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="287">
@@ -32706,31 +32706,31 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>173.8</v>
+        <v>173.1</v>
       </c>
       <c r="D287" t="n">
         <v>180.17</v>
       </c>
       <c r="E287" t="n">
-        <v>-6.37</v>
+        <v>-7.07</v>
       </c>
       <c r="F287" t="n">
-        <v>175.57</v>
+        <v>176.1</v>
       </c>
       <c r="G287" t="n">
         <v>178.22</v>
       </c>
       <c r="H287" t="n">
-        <v>-2.65</v>
+        <v>-2.12</v>
       </c>
       <c r="I287" t="n">
-        <v>172.61</v>
+        <v>173.1</v>
       </c>
       <c r="J287" t="n">
         <v>169.86</v>
       </c>
       <c r="K287" t="n">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>3.54</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="288">
@@ -32758,31 +32758,31 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>676.15</v>
+        <v>669.9</v>
       </c>
       <c r="D288" t="n">
         <v>684.04</v>
       </c>
       <c r="E288" t="n">
-        <v>-7.89</v>
+        <v>-14.14</v>
       </c>
       <c r="F288" t="n">
-        <v>682.45</v>
+        <v>674.65</v>
       </c>
       <c r="G288" t="n">
         <v>688.48</v>
       </c>
       <c r="H288" t="n">
-        <v>-6.03</v>
+        <v>-13.83</v>
       </c>
       <c r="I288" t="n">
-        <v>671.95</v>
+        <v>658.3</v>
       </c>
       <c r="J288" t="n">
         <v>664.5700000000001</v>
       </c>
       <c r="K288" t="n">
-        <v>7.38</v>
+        <v>-6.27</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>1.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="289">
@@ -32810,31 +32810,31 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>1941.7</v>
+        <v>1922</v>
       </c>
       <c r="D289" t="n">
         <v>1954.78</v>
       </c>
       <c r="E289" t="n">
-        <v>-13.08</v>
+        <v>-32.78</v>
       </c>
       <c r="F289" t="n">
-        <v>1952.2</v>
+        <v>1941.8</v>
       </c>
       <c r="G289" t="n">
         <v>1967.81</v>
       </c>
       <c r="H289" t="n">
-        <v>-15.61</v>
+        <v>-26.01</v>
       </c>
       <c r="I289" t="n">
-        <v>1933</v>
+        <v>1922</v>
       </c>
       <c r="J289" t="n">
         <v>1915.53</v>
       </c>
       <c r="K289" t="n">
-        <v>17.47</v>
+        <v>6.47</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>0.67</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="290">
@@ -32862,31 +32862,31 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>14850</v>
+        <v>14462</v>
       </c>
       <c r="D290" t="n">
         <v>15401.04</v>
       </c>
       <c r="E290" t="n">
-        <v>-551.04</v>
+        <v>-939.04</v>
       </c>
       <c r="F290" t="n">
-        <v>14953</v>
+        <v>14550</v>
       </c>
       <c r="G290" t="n">
         <v>15150</v>
       </c>
       <c r="H290" t="n">
-        <v>-197</v>
+        <v>-600</v>
       </c>
       <c r="I290" t="n">
-        <v>14470</v>
+        <v>14026</v>
       </c>
       <c r="J290" t="n">
         <v>14573.45</v>
       </c>
       <c r="K290" t="n">
-        <v>-103.45</v>
+        <v>-547.45</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>3.58</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="291">
@@ -32914,31 +32914,31 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D291" t="n">
         <v>2049.07</v>
       </c>
       <c r="E291" t="n">
-        <v>-33.07</v>
+        <v>-37.07</v>
       </c>
       <c r="F291" t="n">
-        <v>2030.1</v>
+        <v>2013</v>
       </c>
       <c r="G291" t="n">
         <v>2049.2</v>
       </c>
       <c r="H291" t="n">
-        <v>-19.1</v>
+        <v>-36.2</v>
       </c>
       <c r="I291" t="n">
-        <v>2013</v>
+        <v>1985</v>
       </c>
       <c r="J291" t="n">
         <v>1984.2</v>
       </c>
       <c r="K291" t="n">
-        <v>28.8</v>
+        <v>0.8</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="292">
@@ -32966,31 +32966,31 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>4081</v>
+        <v>4041.3</v>
       </c>
       <c r="D292" t="n">
         <v>4143.29</v>
       </c>
       <c r="E292" t="n">
-        <v>-62.29</v>
+        <v>-101.99</v>
       </c>
       <c r="F292" t="n">
-        <v>4084.9</v>
+        <v>4069</v>
       </c>
       <c r="G292" t="n">
         <v>4101.14</v>
       </c>
       <c r="H292" t="n">
-        <v>-16.24</v>
+        <v>-32.14</v>
       </c>
       <c r="I292" t="n">
-        <v>4048.3</v>
+        <v>4024.8</v>
       </c>
       <c r="J292" t="n">
         <v>4052.47</v>
       </c>
       <c r="K292" t="n">
-        <v>-4.17</v>
+        <v>-27.67</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="293">
@@ -33018,31 +33018,31 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2227</v>
+        <v>2174.5</v>
       </c>
       <c r="D293" t="n">
         <v>2317.81</v>
       </c>
       <c r="E293" t="n">
-        <v>-90.81</v>
+        <v>-143.31</v>
       </c>
       <c r="F293" t="n">
-        <v>2233.7</v>
+        <v>2218.8</v>
       </c>
       <c r="G293" t="n">
         <v>2271.34</v>
       </c>
       <c r="H293" t="n">
-        <v>-37.64</v>
+        <v>-52.54</v>
       </c>
       <c r="I293" t="n">
-        <v>2180.4</v>
+        <v>2160.1</v>
       </c>
       <c r="J293" t="n">
         <v>2186.02</v>
       </c>
       <c r="K293" t="n">
-        <v>-5.62</v>
+        <v>-25.92</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>3.92</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="294">
@@ -33070,31 +33070,31 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>735.85</v>
+        <v>723.35</v>
       </c>
       <c r="D294" t="n">
         <v>737.99</v>
       </c>
       <c r="E294" t="n">
-        <v>-2.14</v>
+        <v>-14.64</v>
       </c>
       <c r="F294" t="n">
-        <v>737.1</v>
+        <v>724.95</v>
       </c>
       <c r="G294" t="n">
         <v>743.03</v>
       </c>
       <c r="H294" t="n">
-        <v>-5.93</v>
+        <v>-18.08</v>
       </c>
       <c r="I294" t="n">
-        <v>725.75</v>
+        <v>714.15</v>
       </c>
       <c r="J294" t="n">
         <v>728.01</v>
       </c>
       <c r="K294" t="n">
-        <v>-2.26</v>
+        <v>-13.86</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>0.29</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="295">
@@ -33122,31 +33122,31 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>973.4</v>
+        <v>942.1</v>
       </c>
       <c r="D295" t="n">
         <v>936.92</v>
       </c>
       <c r="E295" t="n">
-        <v>36.48</v>
+        <v>5.18</v>
       </c>
       <c r="F295" t="n">
-        <v>989.55</v>
+        <v>948.45</v>
       </c>
       <c r="G295" t="n">
         <v>992.01</v>
       </c>
       <c r="H295" t="n">
-        <v>-2.46</v>
+        <v>-43.56</v>
       </c>
       <c r="I295" t="n">
-        <v>942.15</v>
+        <v>930.05</v>
       </c>
       <c r="J295" t="n">
         <v>956.09</v>
       </c>
       <c r="K295" t="n">
-        <v>-13.94</v>
+        <v>-26.04</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>3.89</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="296">
@@ -33174,31 +33174,31 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1882</v>
+        <v>1813.1</v>
       </c>
       <c r="D296" t="n">
         <v>1845.26</v>
       </c>
       <c r="E296" t="n">
-        <v>36.74</v>
+        <v>-32.16</v>
       </c>
       <c r="F296" t="n">
-        <v>1888.5</v>
+        <v>1818</v>
       </c>
       <c r="G296" t="n">
         <v>1912.28</v>
       </c>
       <c r="H296" t="n">
-        <v>-23.78</v>
+        <v>-94.28</v>
       </c>
       <c r="I296" t="n">
-        <v>1826.5</v>
+        <v>1785.4</v>
       </c>
       <c r="J296" t="n">
         <v>1852.86</v>
       </c>
       <c r="K296" t="n">
-        <v>-26.36</v>
+        <v>-67.45999999999999</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="297">
@@ -33226,31 +33226,31 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1260.5</v>
+        <v>1272</v>
       </c>
       <c r="D297" t="n">
         <v>1284.73</v>
       </c>
       <c r="E297" t="n">
-        <v>-24.23</v>
+        <v>-12.73</v>
       </c>
       <c r="F297" t="n">
-        <v>1282.6</v>
+        <v>1288</v>
       </c>
       <c r="G297" t="n">
         <v>1283.62</v>
       </c>
       <c r="H297" t="n">
-        <v>-1.02</v>
+        <v>4.38</v>
       </c>
       <c r="I297" t="n">
-        <v>1260.5</v>
+        <v>1259</v>
       </c>
       <c r="J297" t="n">
         <v>1238.81</v>
       </c>
       <c r="K297" t="n">
-        <v>21.69</v>
+        <v>20.19</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>1.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="298">
@@ -33278,31 +33278,31 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>385.6</v>
+        <v>386.55</v>
       </c>
       <c r="D298" t="n">
         <v>367.05</v>
       </c>
       <c r="E298" t="n">
-        <v>18.55</v>
+        <v>19.5</v>
       </c>
       <c r="F298" t="n">
-        <v>395.75</v>
+        <v>386.55</v>
       </c>
       <c r="G298" t="n">
         <v>396.94</v>
       </c>
       <c r="H298" t="n">
-        <v>-1.19</v>
+        <v>-10.39</v>
       </c>
       <c r="I298" t="n">
-        <v>385.1</v>
+        <v>379</v>
       </c>
       <c r="J298" t="n">
         <v>375.72</v>
       </c>
       <c r="K298" t="n">
-        <v>9.380000000000001</v>
+        <v>3.28</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>5.05</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="299">
@@ -33330,31 +33330,31 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>519</v>
+        <v>514.35</v>
       </c>
       <c r="D299" t="n">
         <v>567.26</v>
       </c>
       <c r="E299" t="n">
-        <v>-48.26</v>
+        <v>-52.91</v>
       </c>
       <c r="F299" t="n">
-        <v>524.4</v>
+        <v>519.65</v>
       </c>
       <c r="G299" t="n">
         <v>527.55</v>
       </c>
       <c r="H299" t="n">
-        <v>-3.15</v>
+        <v>-7.9</v>
       </c>
       <c r="I299" t="n">
-        <v>513.8</v>
+        <v>511.55</v>
       </c>
       <c r="J299" t="n">
         <v>510.82</v>
       </c>
       <c r="K299" t="n">
-        <v>2.98</v>
+        <v>0.73</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>8.51</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="300">
@@ -33382,31 +33382,31 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1048</v>
+        <v>1048.6</v>
       </c>
       <c r="D300" t="n">
         <v>1074.87</v>
       </c>
       <c r="E300" t="n">
-        <v>-26.87</v>
+        <v>-26.27</v>
       </c>
       <c r="F300" t="n">
-        <v>1052.9</v>
+        <v>1054.8</v>
       </c>
       <c r="G300" t="n">
         <v>1062.36</v>
       </c>
       <c r="H300" t="n">
-        <v>-9.460000000000001</v>
+        <v>-7.56</v>
       </c>
       <c r="I300" t="n">
-        <v>1045.7</v>
+        <v>1041.4</v>
       </c>
       <c r="J300" t="n">
         <v>1033.67</v>
       </c>
       <c r="K300" t="n">
-        <v>12.03</v>
+        <v>7.73</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="301">
@@ -33434,31 +33434,31 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>1203</v>
+        <v>1180.5</v>
       </c>
       <c r="D301" t="n">
         <v>1212.1</v>
       </c>
       <c r="E301" t="n">
-        <v>-9.1</v>
+        <v>-31.6</v>
       </c>
       <c r="F301" t="n">
-        <v>1222.9</v>
+        <v>1185.5</v>
       </c>
       <c r="G301" t="n">
         <v>1225.85</v>
       </c>
       <c r="H301" t="n">
-        <v>-2.95</v>
+        <v>-40.35</v>
       </c>
       <c r="I301" t="n">
-        <v>1186</v>
+        <v>1157.5</v>
       </c>
       <c r="J301" t="n">
         <v>1181.7</v>
       </c>
       <c r="K301" t="n">
-        <v>4.3</v>
+        <v>-24.2</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -33467,11 +33467,11 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N301" t="n">
-        <v>0.75</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="302">
@@ -33486,31 +33486,31 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>11368</v>
+        <v>11380</v>
       </c>
       <c r="D302" t="n">
         <v>11442.49</v>
       </c>
       <c r="E302" t="n">
-        <v>-74.48999999999999</v>
+        <v>-62.49</v>
       </c>
       <c r="F302" t="n">
-        <v>11423</v>
+        <v>11383</v>
       </c>
       <c r="G302" t="n">
         <v>11516.06</v>
       </c>
       <c r="H302" t="n">
-        <v>-93.06</v>
+        <v>-133.06</v>
       </c>
       <c r="I302" t="n">
-        <v>11303</v>
+        <v>11234</v>
       </c>
       <c r="J302" t="n">
         <v>11218.47</v>
       </c>
       <c r="K302" t="n">
-        <v>84.53</v>
+        <v>15.53</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="303">
@@ -33538,31 +33538,31 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>184.68</v>
+        <v>186.9</v>
       </c>
       <c r="D303" t="n">
         <v>181.47</v>
       </c>
       <c r="E303" t="n">
-        <v>3.21</v>
+        <v>5.43</v>
       </c>
       <c r="F303" t="n">
-        <v>189.46</v>
+        <v>187.6</v>
       </c>
       <c r="G303" t="n">
         <v>188.22</v>
       </c>
       <c r="H303" t="n">
-        <v>1.24</v>
+        <v>-0.62</v>
       </c>
       <c r="I303" t="n">
-        <v>184.39</v>
+        <v>184.9</v>
       </c>
       <c r="J303" t="n">
         <v>181.39</v>
       </c>
       <c r="K303" t="n">
-        <v>3</v>
+        <v>3.51</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="304">
@@ -33590,31 +33590,31 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>291.4</v>
+        <v>288.15</v>
       </c>
       <c r="D304" t="n">
         <v>296.38</v>
       </c>
       <c r="E304" t="n">
-        <v>-4.98</v>
+        <v>-8.23</v>
       </c>
       <c r="F304" t="n">
-        <v>293.75</v>
+        <v>291.5</v>
       </c>
       <c r="G304" t="n">
         <v>295.62</v>
       </c>
       <c r="H304" t="n">
-        <v>-1.87</v>
+        <v>-4.12</v>
       </c>
       <c r="I304" t="n">
-        <v>286.6</v>
+        <v>285.65</v>
       </c>
       <c r="J304" t="n">
         <v>287.25</v>
       </c>
       <c r="K304" t="n">
-        <v>-0.65</v>
+        <v>-1.6</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -33623,11 +33623,11 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N304" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="305">
@@ -33642,31 +33642,31 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>1029.85</v>
+        <v>1038.95</v>
       </c>
       <c r="D305" t="n">
         <v>1004.56</v>
       </c>
       <c r="E305" t="n">
-        <v>25.29</v>
+        <v>34.39</v>
       </c>
       <c r="F305" t="n">
-        <v>1048</v>
+        <v>1039.2</v>
       </c>
       <c r="G305" t="n">
         <v>1050.37</v>
       </c>
       <c r="H305" t="n">
-        <v>-2.37</v>
+        <v>-11.17</v>
       </c>
       <c r="I305" t="n">
-        <v>1013</v>
+        <v>1025.55</v>
       </c>
       <c r="J305" t="n">
         <v>1010.9</v>
       </c>
       <c r="K305" t="n">
-        <v>2.1</v>
+        <v>14.65</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>2.52</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="306">
@@ -33694,31 +33694,31 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2570</v>
+        <v>2559.18</v>
       </c>
       <c r="D306" t="n">
         <v>2608.88</v>
       </c>
       <c r="E306" t="n">
-        <v>-38.88</v>
+        <v>-49.7</v>
       </c>
       <c r="F306" t="n">
-        <v>2583.2</v>
+        <v>2599.81</v>
       </c>
       <c r="G306" t="n">
         <v>2625.43</v>
       </c>
       <c r="H306" t="n">
-        <v>-42.23</v>
+        <v>-25.62</v>
       </c>
       <c r="I306" t="n">
-        <v>2552</v>
+        <v>2533.43</v>
       </c>
       <c r="J306" t="n">
         <v>2519.46</v>
       </c>
       <c r="K306" t="n">
-        <v>32.54</v>
+        <v>13.97</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="307">
@@ -33746,31 +33746,31 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1360.9</v>
+        <v>1378.4</v>
       </c>
       <c r="D307" t="n">
         <v>1390.56</v>
       </c>
       <c r="E307" t="n">
-        <v>-29.66</v>
+        <v>-12.16</v>
       </c>
       <c r="F307" t="n">
-        <v>1390.1</v>
+        <v>1378.4</v>
       </c>
       <c r="G307" t="n">
         <v>1394.25</v>
       </c>
       <c r="H307" t="n">
-        <v>-4.15</v>
+        <v>-15.85</v>
       </c>
       <c r="I307" t="n">
-        <v>1355.3</v>
+        <v>1351.5</v>
       </c>
       <c r="J307" t="n">
         <v>1331.11</v>
       </c>
       <c r="K307" t="n">
-        <v>24.19</v>
+        <v>20.39</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>2.13</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="308">
@@ -33798,31 +33798,31 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>871</v>
+        <v>873.15</v>
       </c>
       <c r="D308" t="n">
         <v>891.58</v>
       </c>
       <c r="E308" t="n">
-        <v>-20.58</v>
+        <v>-18.43</v>
       </c>
       <c r="F308" t="n">
-        <v>883.8</v>
+        <v>881</v>
       </c>
       <c r="G308" t="n">
         <v>885.39</v>
       </c>
       <c r="H308" t="n">
-        <v>-1.59</v>
+        <v>-4.39</v>
       </c>
       <c r="I308" t="n">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="J308" t="n">
         <v>857.23</v>
       </c>
       <c r="K308" t="n">
-        <v>13.77</v>
+        <v>7.77</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N308"/>
+  <dimension ref="A1:N340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16452,6 +16452,1670 @@
       </c>
       <c r="N308" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2032.5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2054.95</v>
+      </c>
+      <c r="E309" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="F309" t="n">
+        <v>2032.5</v>
+      </c>
+      <c r="G309" t="n">
+        <v>2054.95</v>
+      </c>
+      <c r="H309" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="I309" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J309" t="n">
+        <v>1991.09</v>
+      </c>
+      <c r="K309" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="D310" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="F310" t="n">
+        <v>684.45</v>
+      </c>
+      <c r="G310" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="H310" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="I310" t="n">
+        <v>675.25</v>
+      </c>
+      <c r="J310" t="n">
+        <v>655.47</v>
+      </c>
+      <c r="K310" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1048.7</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1050.46</v>
+      </c>
+      <c r="E311" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1054.7</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1050.46</v>
+      </c>
+      <c r="H311" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I311" t="n">
+        <v>1040.1</v>
+      </c>
+      <c r="J311" t="n">
+        <v>1019.46</v>
+      </c>
+      <c r="K311" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N311" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>293</v>
+      </c>
+      <c r="D312" t="n">
+        <v>292.72</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F312" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="G312" t="n">
+        <v>292.72</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I312" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="J312" t="n">
+        <v>284.32</v>
+      </c>
+      <c r="K312" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1946</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1964.08</v>
+      </c>
+      <c r="E313" t="n">
+        <v>-18.08</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1954.9</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1972.01</v>
+      </c>
+      <c r="H313" t="n">
+        <v>-17.11</v>
+      </c>
+      <c r="I313" t="n">
+        <v>1940.5</v>
+      </c>
+      <c r="J313" t="n">
+        <v>1921.32</v>
+      </c>
+      <c r="K313" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>475</v>
+      </c>
+      <c r="D314" t="n">
+        <v>478.23</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="F314" t="n">
+        <v>482</v>
+      </c>
+      <c r="G314" t="n">
+        <v>478.23</v>
+      </c>
+      <c r="H314" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I314" t="n">
+        <v>475</v>
+      </c>
+      <c r="J314" t="n">
+        <v>462.93</v>
+      </c>
+      <c r="K314" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1913.14</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1913.14</v>
+      </c>
+      <c r="H315" t="n">
+        <v>-21.44</v>
+      </c>
+      <c r="I315" t="n">
+        <v>1851</v>
+      </c>
+      <c r="J315" t="n">
+        <v>1832.84</v>
+      </c>
+      <c r="K315" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>5735</v>
+      </c>
+      <c r="D316" t="n">
+        <v>5813.66</v>
+      </c>
+      <c r="E316" t="n">
+        <v>-78.66</v>
+      </c>
+      <c r="F316" t="n">
+        <v>5735</v>
+      </c>
+      <c r="G316" t="n">
+        <v>5813.66</v>
+      </c>
+      <c r="H316" t="n">
+        <v>-78.66</v>
+      </c>
+      <c r="I316" t="n">
+        <v>5642</v>
+      </c>
+      <c r="J316" t="n">
+        <v>5557.57</v>
+      </c>
+      <c r="K316" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>3185</v>
+      </c>
+      <c r="D317" t="n">
+        <v>3190.49</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="F317" t="n">
+        <v>3211.4</v>
+      </c>
+      <c r="G317" t="n">
+        <v>3249.54</v>
+      </c>
+      <c r="H317" t="n">
+        <v>-38.14</v>
+      </c>
+      <c r="I317" t="n">
+        <v>3132</v>
+      </c>
+      <c r="J317" t="n">
+        <v>3166.76</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-34.76</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>1795.2</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1789.64</v>
+      </c>
+      <c r="E318" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F318" t="n">
+        <v>1799</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1789.64</v>
+      </c>
+      <c r="H318" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I318" t="n">
+        <v>1757</v>
+      </c>
+      <c r="J318" t="n">
+        <v>1725.02</v>
+      </c>
+      <c r="K318" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>5667.5</v>
+      </c>
+      <c r="D319" t="n">
+        <v>5542.6</v>
+      </c>
+      <c r="E319" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="F319" t="n">
+        <v>5722</v>
+      </c>
+      <c r="G319" t="n">
+        <v>5725.33</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="I319" t="n">
+        <v>5602</v>
+      </c>
+      <c r="J319" t="n">
+        <v>5577.53</v>
+      </c>
+      <c r="K319" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>990</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1027.79</v>
+      </c>
+      <c r="E320" t="n">
+        <v>-37.79</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1004</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1027.79</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-23.79</v>
+      </c>
+      <c r="I320" t="n">
+        <v>968.55</v>
+      </c>
+      <c r="J320" t="n">
+        <v>956.1900000000001</v>
+      </c>
+      <c r="K320" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>11724</v>
+      </c>
+      <c r="D321" t="n">
+        <v>11687.68</v>
+      </c>
+      <c r="E321" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="F321" t="n">
+        <v>11870</v>
+      </c>
+      <c r="G321" t="n">
+        <v>11830.43</v>
+      </c>
+      <c r="H321" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="I321" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J321" t="n">
+        <v>11524.58</v>
+      </c>
+      <c r="K321" t="n">
+        <v>125.42</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>328</v>
+      </c>
+      <c r="D322" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="E322" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="F322" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="G322" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="H322" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I322" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="J322" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1292.12</v>
+      </c>
+      <c r="E323" t="n">
+        <v>-27.12</v>
+      </c>
+      <c r="F323" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1292.12</v>
+      </c>
+      <c r="H323" t="n">
+        <v>-25.12</v>
+      </c>
+      <c r="I323" t="n">
+        <v>1252</v>
+      </c>
+      <c r="J323" t="n">
+        <v>1223.39</v>
+      </c>
+      <c r="K323" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D324" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="E324" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="F324" t="n">
+        <v>117.52</v>
+      </c>
+      <c r="G324" t="n">
+        <v>122.14</v>
+      </c>
+      <c r="H324" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="I324" t="n">
+        <v>115.41</v>
+      </c>
+      <c r="J324" t="n">
+        <v>113.63</v>
+      </c>
+      <c r="K324" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1105.03</v>
+      </c>
+      <c r="E325" t="n">
+        <v>-71.03</v>
+      </c>
+      <c r="F325" t="n">
+        <v>1040.45</v>
+      </c>
+      <c r="G325" t="n">
+        <v>1105.03</v>
+      </c>
+      <c r="H325" t="n">
+        <v>-64.58</v>
+      </c>
+      <c r="I325" t="n">
+        <v>1024.6</v>
+      </c>
+      <c r="J325" t="n">
+        <v>1022.2</v>
+      </c>
+      <c r="K325" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="D326" t="n">
+        <v>433.84</v>
+      </c>
+      <c r="E326" t="n">
+        <v>-39.39</v>
+      </c>
+      <c r="F326" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="G326" t="n">
+        <v>433.84</v>
+      </c>
+      <c r="H326" t="n">
+        <v>-36.34</v>
+      </c>
+      <c r="I326" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="J326" t="n">
+        <v>390.67</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>2139</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2076.31</v>
+      </c>
+      <c r="E327" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="F327" t="n">
+        <v>2162.2</v>
+      </c>
+      <c r="G327" t="n">
+        <v>2118.48</v>
+      </c>
+      <c r="H327" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I327" t="n">
+        <v>2126.3</v>
+      </c>
+      <c r="J327" t="n">
+        <v>2066.74</v>
+      </c>
+      <c r="K327" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="D328" t="n">
+        <v>3231.44</v>
+      </c>
+      <c r="E328" t="n">
+        <v>180.76</v>
+      </c>
+      <c r="F328" t="n">
+        <v>3453.9</v>
+      </c>
+      <c r="G328" t="n">
+        <v>3365.55</v>
+      </c>
+      <c r="H328" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="I328" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="J328" t="n">
+        <v>3329.82</v>
+      </c>
+      <c r="K328" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>173</v>
+      </c>
+      <c r="D329" t="n">
+        <v>172.71</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F329" t="n">
+        <v>173.69</v>
+      </c>
+      <c r="G329" t="n">
+        <v>172.71</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I329" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="J329" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="K329" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>4093</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="E330" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F330" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G330" t="n">
+        <v>4101.72</v>
+      </c>
+      <c r="H330" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="I330" t="n">
+        <v>4061.4</v>
+      </c>
+      <c r="J330" t="n">
+        <v>4014.48</v>
+      </c>
+      <c r="K330" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D331" t="n">
+        <v>1625.95</v>
+      </c>
+      <c r="E331" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1651.3</v>
+      </c>
+      <c r="G331" t="n">
+        <v>1625.95</v>
+      </c>
+      <c r="H331" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I331" t="n">
+        <v>1590</v>
+      </c>
+      <c r="J331" t="n">
+        <v>1568.44</v>
+      </c>
+      <c r="K331" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>11320</v>
+      </c>
+      <c r="D332" t="n">
+        <v>11551.48</v>
+      </c>
+      <c r="E332" t="n">
+        <v>-231.48</v>
+      </c>
+      <c r="F332" t="n">
+        <v>11410</v>
+      </c>
+      <c r="G332" t="n">
+        <v>11551.48</v>
+      </c>
+      <c r="H332" t="n">
+        <v>-141.48</v>
+      </c>
+      <c r="I332" t="n">
+        <v>11280</v>
+      </c>
+      <c r="J332" t="n">
+        <v>11031.46</v>
+      </c>
+      <c r="K332" t="n">
+        <v>248.54</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2552</v>
+      </c>
+      <c r="D333" t="n">
+        <v>2591.15</v>
+      </c>
+      <c r="E333" t="n">
+        <v>-39.15</v>
+      </c>
+      <c r="F333" t="n">
+        <v>2596</v>
+      </c>
+      <c r="G333" t="n">
+        <v>2591.15</v>
+      </c>
+      <c r="H333" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I333" t="n">
+        <v>2542</v>
+      </c>
+      <c r="J333" t="n">
+        <v>2463.59</v>
+      </c>
+      <c r="K333" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1205.51</v>
+      </c>
+      <c r="E334" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G334" t="n">
+        <v>1205.51</v>
+      </c>
+      <c r="H334" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="I334" t="n">
+        <v>1190.1</v>
+      </c>
+      <c r="J334" t="n">
+        <v>1171.8</v>
+      </c>
+      <c r="K334" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>876.9</v>
+      </c>
+      <c r="D335" t="n">
+        <v>884.3099999999999</v>
+      </c>
+      <c r="E335" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="F335" t="n">
+        <v>880.9</v>
+      </c>
+      <c r="G335" t="n">
+        <v>884.3099999999999</v>
+      </c>
+      <c r="H335" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="I335" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="J335" t="n">
+        <v>850.8099999999999</v>
+      </c>
+      <c r="K335" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1350.1</v>
+      </c>
+      <c r="D336" t="n">
+        <v>1389.34</v>
+      </c>
+      <c r="E336" t="n">
+        <v>-39.24</v>
+      </c>
+      <c r="F336" t="n">
+        <v>1367.8</v>
+      </c>
+      <c r="G336" t="n">
+        <v>1389.34</v>
+      </c>
+      <c r="H336" t="n">
+        <v>-21.54</v>
+      </c>
+      <c r="I336" t="n">
+        <v>1345.2</v>
+      </c>
+      <c r="J336" t="n">
+        <v>1296.01</v>
+      </c>
+      <c r="K336" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="D337" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="E337" t="n">
+        <v>-11.63</v>
+      </c>
+      <c r="F337" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="G337" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="H337" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="I337" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J337" t="n">
+        <v>178.56</v>
+      </c>
+      <c r="K337" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2218.8</v>
+      </c>
+      <c r="D338" t="n">
+        <v>2150.93</v>
+      </c>
+      <c r="E338" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="F338" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="G338" t="n">
+        <v>2217.3</v>
+      </c>
+      <c r="H338" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="I338" t="n">
+        <v>2211.1</v>
+      </c>
+      <c r="J338" t="n">
+        <v>2159.24</v>
+      </c>
+      <c r="K338" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>515.05</v>
+      </c>
+      <c r="D339" t="n">
+        <v>480.87</v>
+      </c>
+      <c r="E339" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="F339" t="n">
+        <v>523</v>
+      </c>
+      <c r="G339" t="n">
+        <v>505.57</v>
+      </c>
+      <c r="H339" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I339" t="n">
+        <v>512.15</v>
+      </c>
+      <c r="J339" t="n">
+        <v>498.74</v>
+      </c>
+      <c r="K339" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D340" t="n">
+        <v>14413.31</v>
+      </c>
+      <c r="E340" t="n">
+        <v>436.69</v>
+      </c>
+      <c r="F340" t="n">
+        <v>14924</v>
+      </c>
+      <c r="G340" t="n">
+        <v>14511.32</v>
+      </c>
+      <c r="H340" t="n">
+        <v>412.68</v>
+      </c>
+      <c r="I340" t="n">
+        <v>14620</v>
+      </c>
+      <c r="J340" t="n">
+        <v>14376.37</v>
+      </c>
+      <c r="K340" t="n">
+        <v>243.63</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>
@@ -16465,7 +18129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17786,6 +19450,110 @@
       </c>
       <c r="N25" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>24252</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24252</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24284.05</v>
+      </c>
+      <c r="G26" t="n">
+        <v>24288.44</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="I26" t="n">
+        <v>24206.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>24211.19</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="D27" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>57772.45</v>
+      </c>
+      <c r="G27" t="n">
+        <v>57862.41</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-89.95999999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>57481.55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>57571.51</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-89.95999999999999</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -17799,7 +19567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N308"/>
+  <dimension ref="A1:N340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33838,6 +35606,1670 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2032.5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2088.59</v>
+      </c>
+      <c r="E309" t="n">
+        <v>-56.09</v>
+      </c>
+      <c r="F309" t="n">
+        <v>2032.5</v>
+      </c>
+      <c r="G309" t="n">
+        <v>2054.98</v>
+      </c>
+      <c r="H309" t="n">
+        <v>-22.48</v>
+      </c>
+      <c r="I309" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J309" t="n">
+        <v>1992.59</v>
+      </c>
+      <c r="K309" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>DLF (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="D310" t="n">
+        <v>701.34</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-23.24</v>
+      </c>
+      <c r="F310" t="n">
+        <v>684.45</v>
+      </c>
+      <c r="G310" t="n">
+        <v>690.4400000000001</v>
+      </c>
+      <c r="H310" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="I310" t="n">
+        <v>675.25</v>
+      </c>
+      <c r="J310" t="n">
+        <v>661.12</v>
+      </c>
+      <c r="K310" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>328</v>
+      </c>
+      <c r="D311" t="n">
+        <v>312.65</v>
+      </c>
+      <c r="E311" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="F311" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="G311" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="H311" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="I311" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="J311" t="n">
+        <v>320.73</v>
+      </c>
+      <c r="K311" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N311" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>MCX (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>3185</v>
+      </c>
+      <c r="D312" t="n">
+        <v>3284.74</v>
+      </c>
+      <c r="E312" t="n">
+        <v>-99.73999999999999</v>
+      </c>
+      <c r="F312" t="n">
+        <v>3211.4</v>
+      </c>
+      <c r="G312" t="n">
+        <v>3275.48</v>
+      </c>
+      <c r="H312" t="n">
+        <v>-64.08</v>
+      </c>
+      <c r="I312" t="n">
+        <v>3132</v>
+      </c>
+      <c r="J312" t="n">
+        <v>3080.65</v>
+      </c>
+      <c r="K312" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>POLICYBZR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1795.2</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1842.9</v>
+      </c>
+      <c r="E313" t="n">
+        <v>-47.7</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1799</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1838.04</v>
+      </c>
+      <c r="H313" t="n">
+        <v>-39.04</v>
+      </c>
+      <c r="I313" t="n">
+        <v>1757</v>
+      </c>
+      <c r="J313" t="n">
+        <v>1742.56</v>
+      </c>
+      <c r="K313" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>1048.7</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1069.51</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-20.81</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1054.7</v>
+      </c>
+      <c r="G314" t="n">
+        <v>1062.07</v>
+      </c>
+      <c r="H314" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="I314" t="n">
+        <v>1040.1</v>
+      </c>
+      <c r="J314" t="n">
+        <v>1026.77</v>
+      </c>
+      <c r="K314" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>5667.5</v>
+      </c>
+      <c r="D315" t="n">
+        <v>5673.46</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="F315" t="n">
+        <v>5722</v>
+      </c>
+      <c r="G315" t="n">
+        <v>5769.39</v>
+      </c>
+      <c r="H315" t="n">
+        <v>-47.39</v>
+      </c>
+      <c r="I315" t="n">
+        <v>5602</v>
+      </c>
+      <c r="J315" t="n">
+        <v>5526.55</v>
+      </c>
+      <c r="K315" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>293</v>
+      </c>
+      <c r="D316" t="n">
+        <v>298.58</v>
+      </c>
+      <c r="E316" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="F316" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="G316" t="n">
+        <v>297.26</v>
+      </c>
+      <c r="H316" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="I316" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="J316" t="n">
+        <v>286.49</v>
+      </c>
+      <c r="K316" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>1946</v>
+      </c>
+      <c r="D317" t="n">
+        <v>1999.83</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-53.83</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1954.9</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1970.93</v>
+      </c>
+      <c r="H317" t="n">
+        <v>-16.03</v>
+      </c>
+      <c r="I317" t="n">
+        <v>1940.5</v>
+      </c>
+      <c r="J317" t="n">
+        <v>1905.21</v>
+      </c>
+      <c r="K317" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D318" t="n">
+        <v>124</v>
+      </c>
+      <c r="E318" t="n">
+        <v>-7.45</v>
+      </c>
+      <c r="F318" t="n">
+        <v>117.52</v>
+      </c>
+      <c r="G318" t="n">
+        <v>117.71</v>
+      </c>
+      <c r="H318" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I318" t="n">
+        <v>115.41</v>
+      </c>
+      <c r="J318" t="n">
+        <v>114.37</v>
+      </c>
+      <c r="K318" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1134.23</v>
+      </c>
+      <c r="E319" t="n">
+        <v>-100.23</v>
+      </c>
+      <c r="F319" t="n">
+        <v>1040.45</v>
+      </c>
+      <c r="G319" t="n">
+        <v>1055.37</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-14.92</v>
+      </c>
+      <c r="I319" t="n">
+        <v>1024.6</v>
+      </c>
+      <c r="J319" t="n">
+        <v>1006.18</v>
+      </c>
+      <c r="K319" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>OIL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>475</v>
+      </c>
+      <c r="D320" t="n">
+        <v>491.69</v>
+      </c>
+      <c r="E320" t="n">
+        <v>-16.69</v>
+      </c>
+      <c r="F320" t="n">
+        <v>482</v>
+      </c>
+      <c r="G320" t="n">
+        <v>485.61</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="I320" t="n">
+        <v>475</v>
+      </c>
+      <c r="J320" t="n">
+        <v>461.63</v>
+      </c>
+      <c r="K320" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="D321" t="n">
+        <v>449.33</v>
+      </c>
+      <c r="E321" t="n">
+        <v>-54.88</v>
+      </c>
+      <c r="F321" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="G321" t="n">
+        <v>406.49</v>
+      </c>
+      <c r="H321" t="n">
+        <v>-8.99</v>
+      </c>
+      <c r="I321" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="J321" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="K321" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>12.21</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>990</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1054.29</v>
+      </c>
+      <c r="E322" t="n">
+        <v>-64.29000000000001</v>
+      </c>
+      <c r="F322" t="n">
+        <v>1004</v>
+      </c>
+      <c r="G322" t="n">
+        <v>1009.86</v>
+      </c>
+      <c r="H322" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="I322" t="n">
+        <v>968.55</v>
+      </c>
+      <c r="J322" t="n">
+        <v>963.83</v>
+      </c>
+      <c r="K322" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>OFSS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>11724</v>
+      </c>
+      <c r="D323" t="n">
+        <v>11972.65</v>
+      </c>
+      <c r="E323" t="n">
+        <v>-248.65</v>
+      </c>
+      <c r="F323" t="n">
+        <v>11870</v>
+      </c>
+      <c r="G323" t="n">
+        <v>11943.45</v>
+      </c>
+      <c r="H323" t="n">
+        <v>-73.45</v>
+      </c>
+      <c r="I323" t="n">
+        <v>11650</v>
+      </c>
+      <c r="J323" t="n">
+        <v>11425.84</v>
+      </c>
+      <c r="K323" t="n">
+        <v>224.16</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1954.25</v>
+      </c>
+      <c r="E324" t="n">
+        <v>-62.55</v>
+      </c>
+      <c r="F324" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="G324" t="n">
+        <v>1921.86</v>
+      </c>
+      <c r="H324" t="n">
+        <v>-30.16</v>
+      </c>
+      <c r="I324" t="n">
+        <v>1851</v>
+      </c>
+      <c r="J324" t="n">
+        <v>1847.56</v>
+      </c>
+      <c r="K324" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>5735</v>
+      </c>
+      <c r="D325" t="n">
+        <v>5937.51</v>
+      </c>
+      <c r="E325" t="n">
+        <v>-202.51</v>
+      </c>
+      <c r="F325" t="n">
+        <v>5735</v>
+      </c>
+      <c r="G325" t="n">
+        <v>5825.46</v>
+      </c>
+      <c r="H325" t="n">
+        <v>-90.45999999999999</v>
+      </c>
+      <c r="I325" t="n">
+        <v>5642</v>
+      </c>
+      <c r="J325" t="n">
+        <v>5601.93</v>
+      </c>
+      <c r="K325" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>2139</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2126.67</v>
+      </c>
+      <c r="E326" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="F326" t="n">
+        <v>2162.2</v>
+      </c>
+      <c r="G326" t="n">
+        <v>2178.78</v>
+      </c>
+      <c r="H326" t="n">
+        <v>-16.58</v>
+      </c>
+      <c r="I326" t="n">
+        <v>2126.3</v>
+      </c>
+      <c r="J326" t="n">
+        <v>2084.8</v>
+      </c>
+      <c r="K326" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="D327" t="n">
+        <v>3277.52</v>
+      </c>
+      <c r="E327" t="n">
+        <v>134.68</v>
+      </c>
+      <c r="F327" t="n">
+        <v>3453.9</v>
+      </c>
+      <c r="G327" t="n">
+        <v>3443.05</v>
+      </c>
+      <c r="H327" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I327" t="n">
+        <v>3412.2</v>
+      </c>
+      <c r="J327" t="n">
+        <v>3350.41</v>
+      </c>
+      <c r="K327" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1322.27</v>
+      </c>
+      <c r="E328" t="n">
+        <v>-57.27</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G328" t="n">
+        <v>1287.42</v>
+      </c>
+      <c r="H328" t="n">
+        <v>-20.42</v>
+      </c>
+      <c r="I328" t="n">
+        <v>1252</v>
+      </c>
+      <c r="J328" t="n">
+        <v>1233.78</v>
+      </c>
+      <c r="K328" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>4093</v>
+      </c>
+      <c r="D329" t="n">
+        <v>4099.22</v>
+      </c>
+      <c r="E329" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="F329" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G329" t="n">
+        <v>4109.87</v>
+      </c>
+      <c r="H329" t="n">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="I329" t="n">
+        <v>4061.4</v>
+      </c>
+      <c r="J329" t="n">
+        <v>4034.1</v>
+      </c>
+      <c r="K329" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>PRESTIGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1673.1</v>
+      </c>
+      <c r="E330" t="n">
+        <v>-42.1</v>
+      </c>
+      <c r="F330" t="n">
+        <v>1651.3</v>
+      </c>
+      <c r="G330" t="n">
+        <v>1668.73</v>
+      </c>
+      <c r="H330" t="n">
+        <v>-17.43</v>
+      </c>
+      <c r="I330" t="n">
+        <v>1590</v>
+      </c>
+      <c r="J330" t="n">
+        <v>1584.08</v>
+      </c>
+      <c r="K330" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>11320</v>
+      </c>
+      <c r="D331" t="n">
+        <v>11732.29</v>
+      </c>
+      <c r="E331" t="n">
+        <v>-412.29</v>
+      </c>
+      <c r="F331" t="n">
+        <v>11410</v>
+      </c>
+      <c r="G331" t="n">
+        <v>11437.43</v>
+      </c>
+      <c r="H331" t="n">
+        <v>-27.43</v>
+      </c>
+      <c r="I331" t="n">
+        <v>11280</v>
+      </c>
+      <c r="J331" t="n">
+        <v>11103.58</v>
+      </c>
+      <c r="K331" t="n">
+        <v>176.42</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>173</v>
+      </c>
+      <c r="D332" t="n">
+        <v>177.56</v>
+      </c>
+      <c r="E332" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="F332" t="n">
+        <v>173.69</v>
+      </c>
+      <c r="G332" t="n">
+        <v>176.84</v>
+      </c>
+      <c r="H332" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="I332" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="J332" t="n">
+        <v>168.15</v>
+      </c>
+      <c r="K332" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="D333" t="n">
+        <v>199.84</v>
+      </c>
+      <c r="E333" t="n">
+        <v>-16.39</v>
+      </c>
+      <c r="F333" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="G333" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="H333" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I333" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J333" t="n">
+        <v>178.78</v>
+      </c>
+      <c r="K333" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2218.8</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2193.81</v>
+      </c>
+      <c r="E334" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F334" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="G334" t="n">
+        <v>2250.9</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I334" t="n">
+        <v>2211.1</v>
+      </c>
+      <c r="J334" t="n">
+        <v>2169.52</v>
+      </c>
+      <c r="K334" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>515.05</v>
+      </c>
+      <c r="D335" t="n">
+        <v>491.48</v>
+      </c>
+      <c r="E335" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F335" t="n">
+        <v>523</v>
+      </c>
+      <c r="G335" t="n">
+        <v>523.5599999999999</v>
+      </c>
+      <c r="H335" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="I335" t="n">
+        <v>512.15</v>
+      </c>
+      <c r="J335" t="n">
+        <v>502.82</v>
+      </c>
+      <c r="K335" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>MAZDOCK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>2552</v>
+      </c>
+      <c r="D336" t="n">
+        <v>2656.3</v>
+      </c>
+      <c r="E336" t="n">
+        <v>-104.3</v>
+      </c>
+      <c r="F336" t="n">
+        <v>2596</v>
+      </c>
+      <c r="G336" t="n">
+        <v>2601.63</v>
+      </c>
+      <c r="H336" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="I336" t="n">
+        <v>2542</v>
+      </c>
+      <c r="J336" t="n">
+        <v>2485.69</v>
+      </c>
+      <c r="K336" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D337" t="n">
+        <v>14734.66</v>
+      </c>
+      <c r="E337" t="n">
+        <v>115.34</v>
+      </c>
+      <c r="F337" t="n">
+        <v>14924</v>
+      </c>
+      <c r="G337" t="n">
+        <v>15098.35</v>
+      </c>
+      <c r="H337" t="n">
+        <v>-174.35</v>
+      </c>
+      <c r="I337" t="n">
+        <v>14620</v>
+      </c>
+      <c r="J337" t="n">
+        <v>14494.75</v>
+      </c>
+      <c r="K337" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>1350.1</v>
+      </c>
+      <c r="D338" t="n">
+        <v>1432.09</v>
+      </c>
+      <c r="E338" t="n">
+        <v>-81.98999999999999</v>
+      </c>
+      <c r="F338" t="n">
+        <v>1367.8</v>
+      </c>
+      <c r="G338" t="n">
+        <v>1383.61</v>
+      </c>
+      <c r="H338" t="n">
+        <v>-15.81</v>
+      </c>
+      <c r="I338" t="n">
+        <v>1345.2</v>
+      </c>
+      <c r="J338" t="n">
+        <v>1309.54</v>
+      </c>
+      <c r="K338" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1235.01</v>
+      </c>
+      <c r="E339" t="n">
+        <v>-36.01</v>
+      </c>
+      <c r="F339" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G339" t="n">
+        <v>1221.54</v>
+      </c>
+      <c r="H339" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="I339" t="n">
+        <v>1190.1</v>
+      </c>
+      <c r="J339" t="n">
+        <v>1168.43</v>
+      </c>
+      <c r="K339" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>876.9</v>
+      </c>
+      <c r="D340" t="n">
+        <v>902.0700000000001</v>
+      </c>
+      <c r="E340" t="n">
+        <v>-25.17</v>
+      </c>
+      <c r="F340" t="n">
+        <v>880.9</v>
+      </c>
+      <c r="G340" t="n">
+        <v>889.71</v>
+      </c>
+      <c r="H340" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="I340" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="J340" t="n">
+        <v>857.3200000000001</v>
+      </c>
+      <c r="K340" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -16466,31 +16466,31 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2032.5</v>
+        <v>2016</v>
       </c>
       <c r="D309" t="n">
         <v>2054.95</v>
       </c>
       <c r="E309" t="n">
-        <v>-22.45</v>
+        <v>-38.95</v>
       </c>
       <c r="F309" t="n">
-        <v>2032.5</v>
+        <v>2030.1</v>
       </c>
       <c r="G309" t="n">
         <v>2054.95</v>
       </c>
       <c r="H309" t="n">
-        <v>-22.45</v>
+        <v>-24.85</v>
       </c>
       <c r="I309" t="n">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="J309" t="n">
         <v>1991.09</v>
       </c>
       <c r="K309" t="n">
-        <v>13.91</v>
+        <v>21.91</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="310">
@@ -16518,31 +16518,31 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>678.1</v>
+        <v>676.15</v>
       </c>
       <c r="D310" t="n">
         <v>685.01</v>
       </c>
       <c r="E310" t="n">
-        <v>-6.91</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="F310" t="n">
-        <v>684.45</v>
+        <v>682.45</v>
       </c>
       <c r="G310" t="n">
         <v>685.01</v>
       </c>
       <c r="H310" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.56</v>
       </c>
       <c r="I310" t="n">
-        <v>675.25</v>
+        <v>671.95</v>
       </c>
       <c r="J310" t="n">
         <v>655.47</v>
       </c>
       <c r="K310" t="n">
-        <v>19.78</v>
+        <v>16.48</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="311">
@@ -16570,31 +16570,31 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1048.7</v>
+        <v>1048</v>
       </c>
       <c r="D311" t="n">
         <v>1050.46</v>
       </c>
       <c r="E311" t="n">
-        <v>-1.76</v>
+        <v>-2.46</v>
       </c>
       <c r="F311" t="n">
-        <v>1054.7</v>
+        <v>1052.9</v>
       </c>
       <c r="G311" t="n">
         <v>1050.46</v>
       </c>
       <c r="H311" t="n">
-        <v>4.24</v>
+        <v>2.44</v>
       </c>
       <c r="I311" t="n">
-        <v>1040.1</v>
+        <v>1045.7</v>
       </c>
       <c r="J311" t="n">
         <v>1019.46</v>
       </c>
       <c r="K311" t="n">
-        <v>20.64</v>
+        <v>26.24</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="312">
@@ -16622,31 +16622,31 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>293</v>
+        <v>291.4</v>
       </c>
       <c r="D312" t="n">
         <v>292.72</v>
       </c>
       <c r="E312" t="n">
-        <v>0.28</v>
+        <v>-1.32</v>
       </c>
       <c r="F312" t="n">
-        <v>293.5</v>
+        <v>293.75</v>
       </c>
       <c r="G312" t="n">
         <v>292.72</v>
       </c>
       <c r="H312" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="I312" t="n">
-        <v>289.75</v>
+        <v>286.6</v>
       </c>
       <c r="J312" t="n">
         <v>284.32</v>
       </c>
       <c r="K312" t="n">
-        <v>5.43</v>
+        <v>2.28</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="313">
@@ -16674,31 +16674,31 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1946</v>
+        <v>1941.7</v>
       </c>
       <c r="D313" t="n">
         <v>1964.08</v>
       </c>
       <c r="E313" t="n">
-        <v>-18.08</v>
+        <v>-22.38</v>
       </c>
       <c r="F313" t="n">
-        <v>1954.9</v>
+        <v>1952.2</v>
       </c>
       <c r="G313" t="n">
         <v>1972.01</v>
       </c>
       <c r="H313" t="n">
-        <v>-17.11</v>
+        <v>-19.81</v>
       </c>
       <c r="I313" t="n">
-        <v>1940.5</v>
+        <v>1933</v>
       </c>
       <c r="J313" t="n">
         <v>1921.32</v>
       </c>
       <c r="K313" t="n">
-        <v>19.18</v>
+        <v>11.68</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="314">
@@ -16726,31 +16726,31 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>475</v>
+        <v>480.9</v>
       </c>
       <c r="D314" t="n">
         <v>478.23</v>
       </c>
       <c r="E314" t="n">
-        <v>-3.23</v>
+        <v>2.67</v>
       </c>
       <c r="F314" t="n">
-        <v>482</v>
+        <v>481.5</v>
       </c>
       <c r="G314" t="n">
         <v>478.23</v>
       </c>
       <c r="H314" t="n">
-        <v>3.77</v>
+        <v>3.27</v>
       </c>
       <c r="I314" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J314" t="n">
         <v>462.93</v>
       </c>
       <c r="K314" t="n">
-        <v>12.07</v>
+        <v>2.07</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="315">
@@ -16778,31 +16778,31 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1891.7</v>
+        <v>1882</v>
       </c>
       <c r="D315" t="n">
         <v>1913.14</v>
       </c>
       <c r="E315" t="n">
-        <v>-21.44</v>
+        <v>-31.14</v>
       </c>
       <c r="F315" t="n">
-        <v>1891.7</v>
+        <v>1888.5</v>
       </c>
       <c r="G315" t="n">
         <v>1913.14</v>
       </c>
       <c r="H315" t="n">
-        <v>-21.44</v>
+        <v>-24.64</v>
       </c>
       <c r="I315" t="n">
-        <v>1851</v>
+        <v>1826.5</v>
       </c>
       <c r="J315" t="n">
         <v>1832.84</v>
       </c>
       <c r="K315" t="n">
-        <v>18.16</v>
+        <v>-6.34</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="316">
@@ -16830,31 +16830,31 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>5735</v>
+        <v>5740.5</v>
       </c>
       <c r="D316" t="n">
         <v>5813.66</v>
       </c>
       <c r="E316" t="n">
-        <v>-78.66</v>
+        <v>-73.16</v>
       </c>
       <c r="F316" t="n">
-        <v>5735</v>
+        <v>5740.5</v>
       </c>
       <c r="G316" t="n">
         <v>5813.66</v>
       </c>
       <c r="H316" t="n">
-        <v>-78.66</v>
+        <v>-73.16</v>
       </c>
       <c r="I316" t="n">
-        <v>5642</v>
+        <v>5670</v>
       </c>
       <c r="J316" t="n">
         <v>5557.57</v>
       </c>
       <c r="K316" t="n">
-        <v>84.43000000000001</v>
+        <v>112.43</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="317">
@@ -16882,31 +16882,31 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3185</v>
+        <v>3126</v>
       </c>
       <c r="D317" t="n">
         <v>3190.49</v>
       </c>
       <c r="E317" t="n">
-        <v>-5.49</v>
+        <v>-64.48999999999999</v>
       </c>
       <c r="F317" t="n">
-        <v>3211.4</v>
+        <v>3133.2</v>
       </c>
       <c r="G317" t="n">
         <v>3249.54</v>
       </c>
       <c r="H317" t="n">
-        <v>-38.14</v>
+        <v>-116.34</v>
       </c>
       <c r="I317" t="n">
-        <v>3132</v>
+        <v>3006</v>
       </c>
       <c r="J317" t="n">
         <v>3166.76</v>
       </c>
       <c r="K317" t="n">
-        <v>-34.76</v>
+        <v>-160.76</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>0.17</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="318">
@@ -16934,31 +16934,31 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1795.2</v>
+        <v>1779.6</v>
       </c>
       <c r="D318" t="n">
         <v>1789.64</v>
       </c>
       <c r="E318" t="n">
-        <v>5.56</v>
+        <v>-10.04</v>
       </c>
       <c r="F318" t="n">
-        <v>1799</v>
+        <v>1803.4</v>
       </c>
       <c r="G318" t="n">
         <v>1789.64</v>
       </c>
       <c r="H318" t="n">
-        <v>9.359999999999999</v>
+        <v>13.76</v>
       </c>
       <c r="I318" t="n">
-        <v>1757</v>
+        <v>1764</v>
       </c>
       <c r="J318" t="n">
         <v>1725.02</v>
       </c>
       <c r="K318" t="n">
-        <v>31.98</v>
+        <v>38.98</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="319">
@@ -16986,31 +16986,31 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>5667.5</v>
+        <v>5674</v>
       </c>
       <c r="D319" t="n">
         <v>5542.6</v>
       </c>
       <c r="E319" t="n">
-        <v>124.9</v>
+        <v>131.4</v>
       </c>
       <c r="F319" t="n">
-        <v>5722</v>
+        <v>5706</v>
       </c>
       <c r="G319" t="n">
         <v>5725.33</v>
       </c>
       <c r="H319" t="n">
-        <v>-3.33</v>
+        <v>-19.33</v>
       </c>
       <c r="I319" t="n">
-        <v>5602</v>
+        <v>5534</v>
       </c>
       <c r="J319" t="n">
         <v>5577.53</v>
       </c>
       <c r="K319" t="n">
-        <v>24.47</v>
+        <v>-43.53</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="320">
@@ -17038,31 +17038,31 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>990</v>
+        <v>973.4</v>
       </c>
       <c r="D320" t="n">
         <v>1027.79</v>
       </c>
       <c r="E320" t="n">
-        <v>-37.79</v>
+        <v>-54.39</v>
       </c>
       <c r="F320" t="n">
-        <v>1004</v>
+        <v>989.55</v>
       </c>
       <c r="G320" t="n">
         <v>1027.79</v>
       </c>
       <c r="H320" t="n">
-        <v>-23.79</v>
+        <v>-38.24</v>
       </c>
       <c r="I320" t="n">
-        <v>968.55</v>
+        <v>942.15</v>
       </c>
       <c r="J320" t="n">
         <v>956.1900000000001</v>
       </c>
       <c r="K320" t="n">
-        <v>12.36</v>
+        <v>-14.04</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>3.68</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="321">
@@ -17090,31 +17090,31 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>11724</v>
+        <v>11826</v>
       </c>
       <c r="D321" t="n">
         <v>11687.68</v>
       </c>
       <c r="E321" t="n">
-        <v>36.32</v>
+        <v>138.32</v>
       </c>
       <c r="F321" t="n">
-        <v>11870</v>
+        <v>11917</v>
       </c>
       <c r="G321" t="n">
         <v>11830.43</v>
       </c>
       <c r="H321" t="n">
-        <v>39.57</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>11650</v>
+        <v>11680</v>
       </c>
       <c r="J321" t="n">
         <v>11524.58</v>
       </c>
       <c r="K321" t="n">
-        <v>125.42</v>
+        <v>155.42</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>0.31</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="322">
@@ -17142,31 +17142,31 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>328</v>
+        <v>327.95</v>
       </c>
       <c r="D322" t="n">
         <v>306.55</v>
       </c>
       <c r="E322" t="n">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="F322" t="n">
-        <v>331.7</v>
+        <v>328.5</v>
       </c>
       <c r="G322" t="n">
         <v>331.99</v>
       </c>
       <c r="H322" t="n">
-        <v>-0.29</v>
+        <v>-3.49</v>
       </c>
       <c r="I322" t="n">
-        <v>324.1</v>
+        <v>321.35</v>
       </c>
       <c r="J322" t="n">
         <v>323.44</v>
       </c>
       <c r="K322" t="n">
-        <v>0.66</v>
+        <v>-2.09</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>7</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="323">
@@ -17194,31 +17194,31 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1265</v>
+        <v>1260.5</v>
       </c>
       <c r="D323" t="n">
         <v>1292.12</v>
       </c>
       <c r="E323" t="n">
-        <v>-27.12</v>
+        <v>-31.62</v>
       </c>
       <c r="F323" t="n">
-        <v>1267</v>
+        <v>1282.6</v>
       </c>
       <c r="G323" t="n">
         <v>1292.12</v>
       </c>
       <c r="H323" t="n">
-        <v>-25.12</v>
+        <v>-9.52</v>
       </c>
       <c r="I323" t="n">
-        <v>1252</v>
+        <v>1260.5</v>
       </c>
       <c r="J323" t="n">
         <v>1223.39</v>
       </c>
       <c r="K323" t="n">
-        <v>28.61</v>
+        <v>37.11</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="324">
@@ -17246,31 +17246,31 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>116.55</v>
+        <v>118</v>
       </c>
       <c r="D324" t="n">
         <v>122.14</v>
       </c>
       <c r="E324" t="n">
-        <v>-5.59</v>
+        <v>-4.14</v>
       </c>
       <c r="F324" t="n">
-        <v>117.52</v>
+        <v>119.1</v>
       </c>
       <c r="G324" t="n">
         <v>122.14</v>
       </c>
       <c r="H324" t="n">
-        <v>-4.62</v>
+        <v>-3.04</v>
       </c>
       <c r="I324" t="n">
-        <v>115.41</v>
+        <v>117.44</v>
       </c>
       <c r="J324" t="n">
         <v>113.63</v>
       </c>
       <c r="K324" t="n">
-        <v>1.78</v>
+        <v>3.81</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>4.58</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="325">
@@ -17298,31 +17298,31 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1034</v>
+        <v>1029.85</v>
       </c>
       <c r="D325" t="n">
         <v>1105.03</v>
       </c>
       <c r="E325" t="n">
-        <v>-71.03</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="F325" t="n">
-        <v>1040.45</v>
+        <v>1048</v>
       </c>
       <c r="G325" t="n">
         <v>1105.03</v>
       </c>
       <c r="H325" t="n">
-        <v>-64.58</v>
+        <v>-57.03</v>
       </c>
       <c r="I325" t="n">
-        <v>1024.6</v>
+        <v>1013</v>
       </c>
       <c r="J325" t="n">
         <v>1022.2</v>
       </c>
       <c r="K325" t="n">
-        <v>2.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>6.43</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="326">
@@ -17350,31 +17350,31 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>394.45</v>
+        <v>385.6</v>
       </c>
       <c r="D326" t="n">
         <v>433.84</v>
       </c>
       <c r="E326" t="n">
-        <v>-39.39</v>
+        <v>-48.24</v>
       </c>
       <c r="F326" t="n">
-        <v>397.5</v>
+        <v>395.75</v>
       </c>
       <c r="G326" t="n">
         <v>433.84</v>
       </c>
       <c r="H326" t="n">
-        <v>-36.34</v>
+        <v>-38.09</v>
       </c>
       <c r="I326" t="n">
-        <v>384.6</v>
+        <v>385.1</v>
       </c>
       <c r="J326" t="n">
         <v>390.67</v>
       </c>
       <c r="K326" t="n">
-        <v>-6.07</v>
+        <v>-5.57</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -17383,11 +17383,11 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N326" t="n">
-        <v>9.08</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="327">
@@ -17402,31 +17402,31 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="D327" t="n">
         <v>2076.31</v>
       </c>
       <c r="E327" t="n">
-        <v>62.69</v>
+        <v>63.69</v>
       </c>
       <c r="F327" t="n">
-        <v>2162.2</v>
+        <v>2153.7</v>
       </c>
       <c r="G327" t="n">
         <v>2118.48</v>
       </c>
       <c r="H327" t="n">
-        <v>43.72</v>
+        <v>35.22</v>
       </c>
       <c r="I327" t="n">
-        <v>2126.3</v>
+        <v>2125</v>
       </c>
       <c r="J327" t="n">
         <v>2066.74</v>
       </c>
       <c r="K327" t="n">
-        <v>59.56</v>
+        <v>58.26</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="328">
@@ -17454,31 +17454,31 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3412.2</v>
+        <v>3424.8</v>
       </c>
       <c r="D328" t="n">
         <v>3231.44</v>
       </c>
       <c r="E328" t="n">
-        <v>180.76</v>
+        <v>193.36</v>
       </c>
       <c r="F328" t="n">
-        <v>3453.9</v>
+        <v>3456.4</v>
       </c>
       <c r="G328" t="n">
         <v>3365.55</v>
       </c>
       <c r="H328" t="n">
-        <v>88.34999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="I328" t="n">
-        <v>3412.2</v>
+        <v>3401</v>
       </c>
       <c r="J328" t="n">
         <v>3329.82</v>
       </c>
       <c r="K328" t="n">
-        <v>82.38</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="329">
@@ -17506,31 +17506,31 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>173</v>
+        <v>173.8</v>
       </c>
       <c r="D329" t="n">
         <v>172.71</v>
       </c>
       <c r="E329" t="n">
-        <v>0.29</v>
+        <v>1.09</v>
       </c>
       <c r="F329" t="n">
-        <v>173.69</v>
+        <v>175.57</v>
       </c>
       <c r="G329" t="n">
         <v>172.71</v>
       </c>
       <c r="H329" t="n">
-        <v>0.98</v>
+        <v>2.86</v>
       </c>
       <c r="I329" t="n">
-        <v>172.3</v>
+        <v>172.61</v>
       </c>
       <c r="J329" t="n">
         <v>167.6</v>
       </c>
       <c r="K329" t="n">
-        <v>4.7</v>
+        <v>5.01</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0.17</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="330">
@@ -17558,31 +17558,31 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4093</v>
+        <v>4081</v>
       </c>
       <c r="D330" t="n">
         <v>4062.2</v>
       </c>
       <c r="E330" t="n">
-        <v>30.8</v>
+        <v>18.8</v>
       </c>
       <c r="F330" t="n">
-        <v>4100</v>
+        <v>4084.9</v>
       </c>
       <c r="G330" t="n">
         <v>4101.72</v>
       </c>
       <c r="H330" t="n">
-        <v>-1.72</v>
+        <v>-16.82</v>
       </c>
       <c r="I330" t="n">
-        <v>4061.4</v>
+        <v>4048.3</v>
       </c>
       <c r="J330" t="n">
         <v>4014.48</v>
       </c>
       <c r="K330" t="n">
-        <v>46.92</v>
+        <v>33.82</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="331">
@@ -17610,31 +17610,31 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1631</v>
+        <v>1585.5</v>
       </c>
       <c r="D331" t="n">
         <v>1625.95</v>
       </c>
       <c r="E331" t="n">
-        <v>5.05</v>
+        <v>-40.45</v>
       </c>
       <c r="F331" t="n">
-        <v>1651.3</v>
+        <v>1610</v>
       </c>
       <c r="G331" t="n">
         <v>1625.95</v>
       </c>
       <c r="H331" t="n">
-        <v>25.35</v>
+        <v>-15.95</v>
       </c>
       <c r="I331" t="n">
-        <v>1590</v>
+        <v>1581</v>
       </c>
       <c r="J331" t="n">
         <v>1568.44</v>
       </c>
       <c r="K331" t="n">
-        <v>21.56</v>
+        <v>12.56</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>0.31</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="332">
@@ -17662,31 +17662,31 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>11320</v>
+        <v>11368</v>
       </c>
       <c r="D332" t="n">
         <v>11551.48</v>
       </c>
       <c r="E332" t="n">
-        <v>-231.48</v>
+        <v>-183.48</v>
       </c>
       <c r="F332" t="n">
-        <v>11410</v>
+        <v>11423</v>
       </c>
       <c r="G332" t="n">
         <v>11551.48</v>
       </c>
       <c r="H332" t="n">
-        <v>-141.48</v>
+        <v>-128.48</v>
       </c>
       <c r="I332" t="n">
-        <v>11280</v>
+        <v>11303</v>
       </c>
       <c r="J332" t="n">
         <v>11031.46</v>
       </c>
       <c r="K332" t="n">
-        <v>248.54</v>
+        <v>271.54</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="333">
@@ -17714,31 +17714,31 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2552</v>
+        <v>2570</v>
       </c>
       <c r="D333" t="n">
         <v>2591.15</v>
       </c>
       <c r="E333" t="n">
-        <v>-39.15</v>
+        <v>-21.15</v>
       </c>
       <c r="F333" t="n">
-        <v>2596</v>
+        <v>2583.2</v>
       </c>
       <c r="G333" t="n">
         <v>2591.15</v>
       </c>
       <c r="H333" t="n">
-        <v>4.85</v>
+        <v>-7.95</v>
       </c>
       <c r="I333" t="n">
-        <v>2542</v>
+        <v>2552</v>
       </c>
       <c r="J333" t="n">
         <v>2463.59</v>
       </c>
       <c r="K333" t="n">
-        <v>78.41</v>
+        <v>88.41</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>1.51</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="334">
@@ -17766,31 +17766,31 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D334" t="n">
         <v>1205.51</v>
       </c>
       <c r="E334" t="n">
-        <v>-6.51</v>
+        <v>-2.51</v>
       </c>
       <c r="F334" t="n">
-        <v>1214</v>
+        <v>1222.9</v>
       </c>
       <c r="G334" t="n">
         <v>1205.51</v>
       </c>
       <c r="H334" t="n">
-        <v>8.49</v>
+        <v>17.39</v>
       </c>
       <c r="I334" t="n">
-        <v>1190.1</v>
+        <v>1186</v>
       </c>
       <c r="J334" t="n">
         <v>1171.8</v>
       </c>
       <c r="K334" t="n">
-        <v>18.3</v>
+        <v>14.2</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="335">
@@ -17818,31 +17818,31 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>876.9</v>
+        <v>871</v>
       </c>
       <c r="D335" t="n">
         <v>884.3099999999999</v>
       </c>
       <c r="E335" t="n">
-        <v>-7.41</v>
+        <v>-13.31</v>
       </c>
       <c r="F335" t="n">
-        <v>880.9</v>
+        <v>883.8</v>
       </c>
       <c r="G335" t="n">
         <v>884.3099999999999</v>
       </c>
       <c r="H335" t="n">
-        <v>-3.41</v>
+        <v>-0.51</v>
       </c>
       <c r="I335" t="n">
-        <v>870.5</v>
+        <v>871</v>
       </c>
       <c r="J335" t="n">
         <v>850.8099999999999</v>
       </c>
       <c r="K335" t="n">
-        <v>19.69</v>
+        <v>20.19</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>0.84</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="336">
@@ -17870,31 +17870,31 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>1350.1</v>
+        <v>1360.9</v>
       </c>
       <c r="D336" t="n">
         <v>1389.34</v>
       </c>
       <c r="E336" t="n">
-        <v>-39.24</v>
+        <v>-28.44</v>
       </c>
       <c r="F336" t="n">
-        <v>1367.8</v>
+        <v>1390.1</v>
       </c>
       <c r="G336" t="n">
         <v>1389.34</v>
       </c>
       <c r="H336" t="n">
-        <v>-21.54</v>
+        <v>0.76</v>
       </c>
       <c r="I336" t="n">
-        <v>1345.2</v>
+        <v>1355.3</v>
       </c>
       <c r="J336" t="n">
         <v>1296.01</v>
       </c>
       <c r="K336" t="n">
-        <v>49.19</v>
+        <v>59.29</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>2.82</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="337">
@@ -17922,31 +17922,31 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>183.45</v>
+        <v>184.68</v>
       </c>
       <c r="D337" t="n">
         <v>195.08</v>
       </c>
       <c r="E337" t="n">
-        <v>-11.63</v>
+        <v>-10.4</v>
       </c>
       <c r="F337" t="n">
-        <v>185.3</v>
+        <v>189.46</v>
       </c>
       <c r="G337" t="n">
         <v>195.08</v>
       </c>
       <c r="H337" t="n">
-        <v>-9.779999999999999</v>
+        <v>-5.62</v>
       </c>
       <c r="I337" t="n">
-        <v>182.5</v>
+        <v>184.39</v>
       </c>
       <c r="J337" t="n">
         <v>178.56</v>
       </c>
       <c r="K337" t="n">
-        <v>3.94</v>
+        <v>5.83</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>5.96</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="338">
@@ -17974,31 +17974,31 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2218.8</v>
+        <v>2227</v>
       </c>
       <c r="D338" t="n">
         <v>2150.93</v>
       </c>
       <c r="E338" t="n">
-        <v>67.87</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F338" t="n">
-        <v>2251.7</v>
+        <v>2233.7</v>
       </c>
       <c r="G338" t="n">
         <v>2217.3</v>
       </c>
       <c r="H338" t="n">
-        <v>34.4</v>
+        <v>16.4</v>
       </c>
       <c r="I338" t="n">
-        <v>2211.1</v>
+        <v>2180.4</v>
       </c>
       <c r="J338" t="n">
         <v>2159.24</v>
       </c>
       <c r="K338" t="n">
-        <v>51.86</v>
+        <v>21.16</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>3.16</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="339">
@@ -18026,31 +18026,31 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>515.05</v>
+        <v>519</v>
       </c>
       <c r="D339" t="n">
         <v>480.87</v>
       </c>
       <c r="E339" t="n">
-        <v>34.18</v>
+        <v>38.13</v>
       </c>
       <c r="F339" t="n">
-        <v>523</v>
+        <v>524.4</v>
       </c>
       <c r="G339" t="n">
         <v>505.57</v>
       </c>
       <c r="H339" t="n">
-        <v>17.43</v>
+        <v>18.83</v>
       </c>
       <c r="I339" t="n">
-        <v>512.15</v>
+        <v>513.8</v>
       </c>
       <c r="J339" t="n">
         <v>498.74</v>
       </c>
       <c r="K339" t="n">
-        <v>13.41</v>
+        <v>15.06</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>7.11</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="340">
@@ -18087,22 +18087,22 @@
         <v>436.69</v>
       </c>
       <c r="F340" t="n">
-        <v>14924</v>
+        <v>14953</v>
       </c>
       <c r="G340" t="n">
         <v>14511.32</v>
       </c>
       <c r="H340" t="n">
-        <v>412.68</v>
+        <v>441.68</v>
       </c>
       <c r="I340" t="n">
-        <v>14620</v>
+        <v>14470</v>
       </c>
       <c r="J340" t="n">
         <v>14376.37</v>
       </c>
       <c r="K340" t="n">
-        <v>243.63</v>
+        <v>93.63</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -19464,31 +19464,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24252</v>
+        <v>24231.85</v>
       </c>
       <c r="D26" t="n">
         <v>24252</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-20.15</v>
       </c>
       <c r="F26" t="n">
-        <v>24284.05</v>
+        <v>24265.15</v>
       </c>
       <c r="G26" t="n">
         <v>24288.44</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.39</v>
+        <v>-23.29</v>
       </c>
       <c r="I26" t="n">
-        <v>24206.8</v>
+        <v>24184.55</v>
       </c>
       <c r="J26" t="n">
         <v>24211.19</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.39</v>
+        <v>-26.64</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="27">
@@ -19516,31 +19516,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57761.95</v>
+        <v>57495.9</v>
       </c>
       <c r="D27" t="n">
         <v>57761.95</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-266.05</v>
       </c>
       <c r="F27" t="n">
-        <v>57772.45</v>
+        <v>57702.95</v>
       </c>
       <c r="G27" t="n">
         <v>57862.41</v>
       </c>
       <c r="H27" t="n">
-        <v>-89.95999999999999</v>
+        <v>-159.46</v>
       </c>
       <c r="I27" t="n">
-        <v>57481.55</v>
+        <v>57431.8</v>
       </c>
       <c r="J27" t="n">
         <v>57571.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-89.95999999999999</v>
+        <v>-139.71</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -35618,31 +35618,31 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2032.5</v>
+        <v>2016</v>
       </c>
       <c r="D309" t="n">
         <v>2088.59</v>
       </c>
       <c r="E309" t="n">
-        <v>-56.09</v>
+        <v>-72.59</v>
       </c>
       <c r="F309" t="n">
-        <v>2032.5</v>
+        <v>2030.1</v>
       </c>
       <c r="G309" t="n">
         <v>2054.98</v>
       </c>
       <c r="H309" t="n">
-        <v>-22.48</v>
+        <v>-24.88</v>
       </c>
       <c r="I309" t="n">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="J309" t="n">
         <v>1992.59</v>
       </c>
       <c r="K309" t="n">
-        <v>12.41</v>
+        <v>20.41</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>2.69</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="310">
@@ -35670,31 +35670,31 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>678.1</v>
+        <v>676.15</v>
       </c>
       <c r="D310" t="n">
         <v>701.34</v>
       </c>
       <c r="E310" t="n">
-        <v>-23.24</v>
+        <v>-25.19</v>
       </c>
       <c r="F310" t="n">
-        <v>684.45</v>
+        <v>682.45</v>
       </c>
       <c r="G310" t="n">
         <v>690.4400000000001</v>
       </c>
       <c r="H310" t="n">
-        <v>-5.99</v>
+        <v>-7.99</v>
       </c>
       <c r="I310" t="n">
-        <v>675.25</v>
+        <v>671.95</v>
       </c>
       <c r="J310" t="n">
         <v>661.12</v>
       </c>
       <c r="K310" t="n">
-        <v>14.13</v>
+        <v>10.83</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>3.31</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="311">
@@ -35722,31 +35722,31 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>328</v>
+        <v>327.95</v>
       </c>
       <c r="D311" t="n">
         <v>312.65</v>
       </c>
       <c r="E311" t="n">
-        <v>15.35</v>
+        <v>15.3</v>
       </c>
       <c r="F311" t="n">
-        <v>331.7</v>
+        <v>328.5</v>
       </c>
       <c r="G311" t="n">
         <v>332.73</v>
       </c>
       <c r="H311" t="n">
-        <v>-1.03</v>
+        <v>-4.23</v>
       </c>
       <c r="I311" t="n">
-        <v>324.1</v>
+        <v>321.35</v>
       </c>
       <c r="J311" t="n">
         <v>320.73</v>
       </c>
       <c r="K311" t="n">
-        <v>3.37</v>
+        <v>0.62</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="312">
@@ -35774,31 +35774,31 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3185</v>
+        <v>3126</v>
       </c>
       <c r="D312" t="n">
         <v>3284.74</v>
       </c>
       <c r="E312" t="n">
-        <v>-99.73999999999999</v>
+        <v>-158.74</v>
       </c>
       <c r="F312" t="n">
-        <v>3211.4</v>
+        <v>3133.2</v>
       </c>
       <c r="G312" t="n">
         <v>3275.48</v>
       </c>
       <c r="H312" t="n">
-        <v>-64.08</v>
+        <v>-142.28</v>
       </c>
       <c r="I312" t="n">
-        <v>3132</v>
+        <v>3006</v>
       </c>
       <c r="J312" t="n">
         <v>3080.65</v>
       </c>
       <c r="K312" t="n">
-        <v>51.35</v>
+        <v>-74.65000000000001</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>3.04</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="313">
@@ -35826,31 +35826,31 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1795.2</v>
+        <v>1779.6</v>
       </c>
       <c r="D313" t="n">
         <v>1842.9</v>
       </c>
       <c r="E313" t="n">
-        <v>-47.7</v>
+        <v>-63.3</v>
       </c>
       <c r="F313" t="n">
-        <v>1799</v>
+        <v>1803.4</v>
       </c>
       <c r="G313" t="n">
         <v>1838.04</v>
       </c>
       <c r="H313" t="n">
-        <v>-39.04</v>
+        <v>-34.64</v>
       </c>
       <c r="I313" t="n">
-        <v>1757</v>
+        <v>1764</v>
       </c>
       <c r="J313" t="n">
         <v>1742.56</v>
       </c>
       <c r="K313" t="n">
-        <v>14.44</v>
+        <v>21.44</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>2.59</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="314">
@@ -35878,31 +35878,31 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>1048.7</v>
+        <v>1048</v>
       </c>
       <c r="D314" t="n">
         <v>1069.51</v>
       </c>
       <c r="E314" t="n">
-        <v>-20.81</v>
+        <v>-21.51</v>
       </c>
       <c r="F314" t="n">
-        <v>1054.7</v>
+        <v>1052.9</v>
       </c>
       <c r="G314" t="n">
         <v>1062.07</v>
       </c>
       <c r="H314" t="n">
-        <v>-7.37</v>
+        <v>-9.17</v>
       </c>
       <c r="I314" t="n">
-        <v>1040.1</v>
+        <v>1045.7</v>
       </c>
       <c r="J314" t="n">
         <v>1026.77</v>
       </c>
       <c r="K314" t="n">
-        <v>13.33</v>
+        <v>18.93</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="315">
@@ -35930,31 +35930,31 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>5667.5</v>
+        <v>5674</v>
       </c>
       <c r="D315" t="n">
         <v>5673.46</v>
       </c>
       <c r="E315" t="n">
-        <v>-5.96</v>
+        <v>0.54</v>
       </c>
       <c r="F315" t="n">
-        <v>5722</v>
+        <v>5706</v>
       </c>
       <c r="G315" t="n">
         <v>5769.39</v>
       </c>
       <c r="H315" t="n">
-        <v>-47.39</v>
+        <v>-63.39</v>
       </c>
       <c r="I315" t="n">
-        <v>5602</v>
+        <v>5534</v>
       </c>
       <c r="J315" t="n">
         <v>5526.55</v>
       </c>
       <c r="K315" t="n">
-        <v>75.45</v>
+        <v>7.45</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="316">
@@ -35982,31 +35982,31 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>293</v>
+        <v>291.4</v>
       </c>
       <c r="D316" t="n">
         <v>298.58</v>
       </c>
       <c r="E316" t="n">
-        <v>-5.58</v>
+        <v>-7.18</v>
       </c>
       <c r="F316" t="n">
-        <v>293.5</v>
+        <v>293.75</v>
       </c>
       <c r="G316" t="n">
         <v>297.26</v>
       </c>
       <c r="H316" t="n">
-        <v>-3.76</v>
+        <v>-3.51</v>
       </c>
       <c r="I316" t="n">
-        <v>289.75</v>
+        <v>286.6</v>
       </c>
       <c r="J316" t="n">
         <v>286.49</v>
       </c>
       <c r="K316" t="n">
-        <v>3.26</v>
+        <v>0.11</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="317">
@@ -36034,31 +36034,31 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1946</v>
+        <v>1941.7</v>
       </c>
       <c r="D317" t="n">
         <v>1999.83</v>
       </c>
       <c r="E317" t="n">
-        <v>-53.83</v>
+        <v>-58.13</v>
       </c>
       <c r="F317" t="n">
-        <v>1954.9</v>
+        <v>1952.2</v>
       </c>
       <c r="G317" t="n">
         <v>1970.93</v>
       </c>
       <c r="H317" t="n">
-        <v>-16.03</v>
+        <v>-18.73</v>
       </c>
       <c r="I317" t="n">
-        <v>1940.5</v>
+        <v>1933</v>
       </c>
       <c r="J317" t="n">
         <v>1905.21</v>
       </c>
       <c r="K317" t="n">
-        <v>35.29</v>
+        <v>27.79</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="318">
@@ -36086,31 +36086,31 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>116.55</v>
+        <v>118</v>
       </c>
       <c r="D318" t="n">
         <v>124</v>
       </c>
       <c r="E318" t="n">
-        <v>-7.45</v>
+        <v>-6</v>
       </c>
       <c r="F318" t="n">
-        <v>117.52</v>
+        <v>119.1</v>
       </c>
       <c r="G318" t="n">
         <v>117.71</v>
       </c>
       <c r="H318" t="n">
-        <v>-0.19</v>
+        <v>1.39</v>
       </c>
       <c r="I318" t="n">
-        <v>115.41</v>
+        <v>117.44</v>
       </c>
       <c r="J318" t="n">
         <v>114.37</v>
       </c>
       <c r="K318" t="n">
-        <v>1.04</v>
+        <v>3.07</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>6.01</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="319">
@@ -36138,31 +36138,31 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>1034</v>
+        <v>1029.85</v>
       </c>
       <c r="D319" t="n">
         <v>1134.23</v>
       </c>
       <c r="E319" t="n">
-        <v>-100.23</v>
+        <v>-104.38</v>
       </c>
       <c r="F319" t="n">
-        <v>1040.45</v>
+        <v>1048</v>
       </c>
       <c r="G319" t="n">
         <v>1055.37</v>
       </c>
       <c r="H319" t="n">
-        <v>-14.92</v>
+        <v>-7.37</v>
       </c>
       <c r="I319" t="n">
-        <v>1024.6</v>
+        <v>1013</v>
       </c>
       <c r="J319" t="n">
         <v>1006.18</v>
       </c>
       <c r="K319" t="n">
-        <v>18.42</v>
+        <v>6.82</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>8.84</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="320">
@@ -36190,31 +36190,31 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>475</v>
+        <v>480.9</v>
       </c>
       <c r="D320" t="n">
         <v>491.69</v>
       </c>
       <c r="E320" t="n">
-        <v>-16.69</v>
+        <v>-10.79</v>
       </c>
       <c r="F320" t="n">
-        <v>482</v>
+        <v>481.5</v>
       </c>
       <c r="G320" t="n">
         <v>485.61</v>
       </c>
       <c r="H320" t="n">
-        <v>-3.61</v>
+        <v>-4.11</v>
       </c>
       <c r="I320" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J320" t="n">
         <v>461.63</v>
       </c>
       <c r="K320" t="n">
-        <v>13.37</v>
+        <v>3.37</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -36223,11 +36223,11 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N320" t="n">
-        <v>3.39</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="321">
@@ -36242,31 +36242,31 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>394.45</v>
+        <v>385.6</v>
       </c>
       <c r="D321" t="n">
         <v>449.33</v>
       </c>
       <c r="E321" t="n">
-        <v>-54.88</v>
+        <v>-63.73</v>
       </c>
       <c r="F321" t="n">
-        <v>397.5</v>
+        <v>395.75</v>
       </c>
       <c r="G321" t="n">
         <v>406.49</v>
       </c>
       <c r="H321" t="n">
-        <v>-8.99</v>
+        <v>-10.74</v>
       </c>
       <c r="I321" t="n">
-        <v>384.6</v>
+        <v>385.1</v>
       </c>
       <c r="J321" t="n">
         <v>380.9</v>
       </c>
       <c r="K321" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>12.21</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="322">
@@ -36294,31 +36294,31 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>990</v>
+        <v>973.4</v>
       </c>
       <c r="D322" t="n">
         <v>1054.29</v>
       </c>
       <c r="E322" t="n">
-        <v>-64.29000000000001</v>
+        <v>-80.89</v>
       </c>
       <c r="F322" t="n">
-        <v>1004</v>
+        <v>989.55</v>
       </c>
       <c r="G322" t="n">
         <v>1009.86</v>
       </c>
       <c r="H322" t="n">
-        <v>-5.86</v>
+        <v>-20.31</v>
       </c>
       <c r="I322" t="n">
-        <v>968.55</v>
+        <v>942.15</v>
       </c>
       <c r="J322" t="n">
         <v>963.83</v>
       </c>
       <c r="K322" t="n">
-        <v>4.72</v>
+        <v>-21.68</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>6.1</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="323">
@@ -36346,31 +36346,31 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>11724</v>
+        <v>11826</v>
       </c>
       <c r="D323" t="n">
         <v>11972.65</v>
       </c>
       <c r="E323" t="n">
-        <v>-248.65</v>
+        <v>-146.65</v>
       </c>
       <c r="F323" t="n">
-        <v>11870</v>
+        <v>11917</v>
       </c>
       <c r="G323" t="n">
         <v>11943.45</v>
       </c>
       <c r="H323" t="n">
-        <v>-73.45</v>
+        <v>-26.45</v>
       </c>
       <c r="I323" t="n">
-        <v>11650</v>
+        <v>11680</v>
       </c>
       <c r="J323" t="n">
         <v>11425.84</v>
       </c>
       <c r="K323" t="n">
-        <v>224.16</v>
+        <v>254.16</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>2.08</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="324">
@@ -36398,31 +36398,31 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>1891.7</v>
+        <v>1882</v>
       </c>
       <c r="D324" t="n">
         <v>1954.25</v>
       </c>
       <c r="E324" t="n">
-        <v>-62.55</v>
+        <v>-72.25</v>
       </c>
       <c r="F324" t="n">
-        <v>1891.7</v>
+        <v>1888.5</v>
       </c>
       <c r="G324" t="n">
         <v>1921.86</v>
       </c>
       <c r="H324" t="n">
-        <v>-30.16</v>
+        <v>-33.36</v>
       </c>
       <c r="I324" t="n">
-        <v>1851</v>
+        <v>1826.5</v>
       </c>
       <c r="J324" t="n">
         <v>1847.56</v>
       </c>
       <c r="K324" t="n">
-        <v>3.44</v>
+        <v>-21.06</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="325">
@@ -36450,31 +36450,31 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>5735</v>
+        <v>5740.5</v>
       </c>
       <c r="D325" t="n">
         <v>5937.51</v>
       </c>
       <c r="E325" t="n">
-        <v>-202.51</v>
+        <v>-197.01</v>
       </c>
       <c r="F325" t="n">
-        <v>5735</v>
+        <v>5740.5</v>
       </c>
       <c r="G325" t="n">
         <v>5825.46</v>
       </c>
       <c r="H325" t="n">
-        <v>-90.45999999999999</v>
+        <v>-84.95999999999999</v>
       </c>
       <c r="I325" t="n">
-        <v>5642</v>
+        <v>5670</v>
       </c>
       <c r="J325" t="n">
         <v>5601.93</v>
       </c>
       <c r="K325" t="n">
-        <v>40.07</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="326">
@@ -36502,31 +36502,31 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="D326" t="n">
         <v>2126.67</v>
       </c>
       <c r="E326" t="n">
-        <v>12.33</v>
+        <v>13.33</v>
       </c>
       <c r="F326" t="n">
-        <v>2162.2</v>
+        <v>2153.7</v>
       </c>
       <c r="G326" t="n">
         <v>2178.78</v>
       </c>
       <c r="H326" t="n">
-        <v>-16.58</v>
+        <v>-25.08</v>
       </c>
       <c r="I326" t="n">
-        <v>2126.3</v>
+        <v>2125</v>
       </c>
       <c r="J326" t="n">
         <v>2084.8</v>
       </c>
       <c r="K326" t="n">
-        <v>41.5</v>
+        <v>40.2</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="327">
@@ -36554,31 +36554,31 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3412.2</v>
+        <v>3424.8</v>
       </c>
       <c r="D327" t="n">
         <v>3277.52</v>
       </c>
       <c r="E327" t="n">
-        <v>134.68</v>
+        <v>147.28</v>
       </c>
       <c r="F327" t="n">
-        <v>3453.9</v>
+        <v>3456.4</v>
       </c>
       <c r="G327" t="n">
         <v>3443.05</v>
       </c>
       <c r="H327" t="n">
-        <v>10.85</v>
+        <v>13.35</v>
       </c>
       <c r="I327" t="n">
-        <v>3412.2</v>
+        <v>3401</v>
       </c>
       <c r="J327" t="n">
         <v>3350.41</v>
       </c>
       <c r="K327" t="n">
-        <v>61.79</v>
+        <v>50.59</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>4.11</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="328">
@@ -36606,31 +36606,31 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1265</v>
+        <v>1260.5</v>
       </c>
       <c r="D328" t="n">
         <v>1322.27</v>
       </c>
       <c r="E328" t="n">
-        <v>-57.27</v>
+        <v>-61.77</v>
       </c>
       <c r="F328" t="n">
-        <v>1267</v>
+        <v>1282.6</v>
       </c>
       <c r="G328" t="n">
         <v>1287.42</v>
       </c>
       <c r="H328" t="n">
-        <v>-20.42</v>
+        <v>-4.82</v>
       </c>
       <c r="I328" t="n">
-        <v>1252</v>
+        <v>1260.5</v>
       </c>
       <c r="J328" t="n">
         <v>1233.78</v>
       </c>
       <c r="K328" t="n">
-        <v>18.22</v>
+        <v>26.72</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>4.33</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="329">
@@ -36658,31 +36658,31 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>4093</v>
+        <v>4081</v>
       </c>
       <c r="D329" t="n">
         <v>4099.22</v>
       </c>
       <c r="E329" t="n">
-        <v>-6.22</v>
+        <v>-18.22</v>
       </c>
       <c r="F329" t="n">
-        <v>4100</v>
+        <v>4084.9</v>
       </c>
       <c r="G329" t="n">
         <v>4109.87</v>
       </c>
       <c r="H329" t="n">
-        <v>-9.869999999999999</v>
+        <v>-24.97</v>
       </c>
       <c r="I329" t="n">
-        <v>4061.4</v>
+        <v>4048.3</v>
       </c>
       <c r="J329" t="n">
         <v>4034.1</v>
       </c>
       <c r="K329" t="n">
-        <v>27.3</v>
+        <v>14.2</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="330">
@@ -36710,31 +36710,31 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>1631</v>
+        <v>1585.5</v>
       </c>
       <c r="D330" t="n">
         <v>1673.1</v>
       </c>
       <c r="E330" t="n">
-        <v>-42.1</v>
+        <v>-87.59999999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>1651.3</v>
+        <v>1610</v>
       </c>
       <c r="G330" t="n">
         <v>1668.73</v>
       </c>
       <c r="H330" t="n">
-        <v>-17.43</v>
+        <v>-58.73</v>
       </c>
       <c r="I330" t="n">
-        <v>1590</v>
+        <v>1581</v>
       </c>
       <c r="J330" t="n">
         <v>1584.08</v>
       </c>
       <c r="K330" t="n">
-        <v>5.92</v>
+        <v>-3.08</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>2.52</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="331">
@@ -36762,31 +36762,31 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>11320</v>
+        <v>11368</v>
       </c>
       <c r="D331" t="n">
         <v>11732.29</v>
       </c>
       <c r="E331" t="n">
-        <v>-412.29</v>
+        <v>-364.29</v>
       </c>
       <c r="F331" t="n">
-        <v>11410</v>
+        <v>11423</v>
       </c>
       <c r="G331" t="n">
         <v>11437.43</v>
       </c>
       <c r="H331" t="n">
-        <v>-27.43</v>
+        <v>-14.43</v>
       </c>
       <c r="I331" t="n">
-        <v>11280</v>
+        <v>11303</v>
       </c>
       <c r="J331" t="n">
         <v>11103.58</v>
       </c>
       <c r="K331" t="n">
-        <v>176.42</v>
+        <v>199.42</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>3.51</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="332">
@@ -36814,31 +36814,31 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>173</v>
+        <v>173.8</v>
       </c>
       <c r="D332" t="n">
         <v>177.56</v>
       </c>
       <c r="E332" t="n">
-        <v>-4.56</v>
+        <v>-3.76</v>
       </c>
       <c r="F332" t="n">
-        <v>173.69</v>
+        <v>175.57</v>
       </c>
       <c r="G332" t="n">
         <v>176.84</v>
       </c>
       <c r="H332" t="n">
-        <v>-3.15</v>
+        <v>-1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>172.3</v>
+        <v>172.61</v>
       </c>
       <c r="J332" t="n">
         <v>168.15</v>
       </c>
       <c r="K332" t="n">
-        <v>4.15</v>
+        <v>4.46</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -36847,11 +36847,11 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N332" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="333">
@@ -36866,31 +36866,31 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>183.45</v>
+        <v>184.68</v>
       </c>
       <c r="D333" t="n">
         <v>199.84</v>
       </c>
       <c r="E333" t="n">
-        <v>-16.39</v>
+        <v>-15.16</v>
       </c>
       <c r="F333" t="n">
-        <v>185.3</v>
+        <v>189.46</v>
       </c>
       <c r="G333" t="n">
         <v>186.9</v>
       </c>
       <c r="H333" t="n">
-        <v>-1.6</v>
+        <v>2.56</v>
       </c>
       <c r="I333" t="n">
-        <v>182.5</v>
+        <v>184.39</v>
       </c>
       <c r="J333" t="n">
         <v>178.78</v>
       </c>
       <c r="K333" t="n">
-        <v>3.72</v>
+        <v>5.61</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>8.199999999999999</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="334">
@@ -36918,31 +36918,31 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>2218.8</v>
+        <v>2227</v>
       </c>
       <c r="D334" t="n">
         <v>2193.81</v>
       </c>
       <c r="E334" t="n">
-        <v>24.99</v>
+        <v>33.19</v>
       </c>
       <c r="F334" t="n">
-        <v>2251.7</v>
+        <v>2233.7</v>
       </c>
       <c r="G334" t="n">
         <v>2250.9</v>
       </c>
       <c r="H334" t="n">
-        <v>0.8</v>
+        <v>-17.2</v>
       </c>
       <c r="I334" t="n">
-        <v>2211.1</v>
+        <v>2180.4</v>
       </c>
       <c r="J334" t="n">
         <v>2169.52</v>
       </c>
       <c r="K334" t="n">
-        <v>41.58</v>
+        <v>10.88</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="335">
@@ -36970,31 +36970,31 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>515.05</v>
+        <v>519</v>
       </c>
       <c r="D335" t="n">
         <v>491.48</v>
       </c>
       <c r="E335" t="n">
-        <v>23.57</v>
+        <v>27.52</v>
       </c>
       <c r="F335" t="n">
-        <v>523</v>
+        <v>524.4</v>
       </c>
       <c r="G335" t="n">
         <v>523.5599999999999</v>
       </c>
       <c r="H335" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="I335" t="n">
-        <v>512.15</v>
+        <v>513.8</v>
       </c>
       <c r="J335" t="n">
         <v>502.82</v>
       </c>
       <c r="K335" t="n">
-        <v>9.33</v>
+        <v>10.98</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="336">
@@ -37022,31 +37022,31 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>2552</v>
+        <v>2570</v>
       </c>
       <c r="D336" t="n">
         <v>2656.3</v>
       </c>
       <c r="E336" t="n">
-        <v>-104.3</v>
+        <v>-86.3</v>
       </c>
       <c r="F336" t="n">
-        <v>2596</v>
+        <v>2583.2</v>
       </c>
       <c r="G336" t="n">
         <v>2601.63</v>
       </c>
       <c r="H336" t="n">
-        <v>-5.63</v>
+        <v>-18.43</v>
       </c>
       <c r="I336" t="n">
-        <v>2542</v>
+        <v>2552</v>
       </c>
       <c r="J336" t="n">
         <v>2485.69</v>
       </c>
       <c r="K336" t="n">
-        <v>56.31</v>
+        <v>66.31</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>3.93</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="337">
@@ -37083,22 +37083,22 @@
         <v>115.34</v>
       </c>
       <c r="F337" t="n">
-        <v>14924</v>
+        <v>14953</v>
       </c>
       <c r="G337" t="n">
         <v>15098.35</v>
       </c>
       <c r="H337" t="n">
-        <v>-174.35</v>
+        <v>-145.35</v>
       </c>
       <c r="I337" t="n">
-        <v>14620</v>
+        <v>14470</v>
       </c>
       <c r="J337" t="n">
         <v>14494.75</v>
       </c>
       <c r="K337" t="n">
-        <v>125.25</v>
+        <v>-24.75</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -37126,31 +37126,31 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1350.1</v>
+        <v>1360.9</v>
       </c>
       <c r="D338" t="n">
         <v>1432.09</v>
       </c>
       <c r="E338" t="n">
-        <v>-81.98999999999999</v>
+        <v>-71.19</v>
       </c>
       <c r="F338" t="n">
-        <v>1367.8</v>
+        <v>1390.1</v>
       </c>
       <c r="G338" t="n">
         <v>1383.61</v>
       </c>
       <c r="H338" t="n">
-        <v>-15.81</v>
+        <v>6.49</v>
       </c>
       <c r="I338" t="n">
-        <v>1345.2</v>
+        <v>1355.3</v>
       </c>
       <c r="J338" t="n">
         <v>1309.54</v>
       </c>
       <c r="K338" t="n">
-        <v>35.66</v>
+        <v>45.76</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>5.73</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="339">
@@ -37178,31 +37178,31 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D339" t="n">
         <v>1235.01</v>
       </c>
       <c r="E339" t="n">
-        <v>-36.01</v>
+        <v>-32.01</v>
       </c>
       <c r="F339" t="n">
-        <v>1214</v>
+        <v>1222.9</v>
       </c>
       <c r="G339" t="n">
         <v>1221.54</v>
       </c>
       <c r="H339" t="n">
-        <v>-7.54</v>
+        <v>1.36</v>
       </c>
       <c r="I339" t="n">
-        <v>1190.1</v>
+        <v>1186</v>
       </c>
       <c r="J339" t="n">
         <v>1168.43</v>
       </c>
       <c r="K339" t="n">
-        <v>21.67</v>
+        <v>17.57</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -37211,11 +37211,11 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="340">
@@ -37230,31 +37230,31 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>876.9</v>
+        <v>871</v>
       </c>
       <c r="D340" t="n">
         <v>902.0700000000001</v>
       </c>
       <c r="E340" t="n">
-        <v>-25.17</v>
+        <v>-31.07</v>
       </c>
       <c r="F340" t="n">
-        <v>880.9</v>
+        <v>883.8</v>
       </c>
       <c r="G340" t="n">
         <v>889.71</v>
       </c>
       <c r="H340" t="n">
-        <v>-8.81</v>
+        <v>-5.91</v>
       </c>
       <c r="I340" t="n">
-        <v>870.5</v>
+        <v>871</v>
       </c>
       <c r="J340" t="n">
         <v>857.3200000000001</v>
       </c>
       <c r="K340" t="n">
-        <v>13.18</v>
+        <v>13.68</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         </is>
       </c>
       <c r="N340" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -16462,39 +16462,39 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2016</v>
+        <v>291.4</v>
       </c>
       <c r="D309" t="n">
-        <v>2054.95</v>
+        <v>292.72</v>
       </c>
       <c r="E309" t="n">
-        <v>-38.95</v>
+        <v>-1.32</v>
       </c>
       <c r="F309" t="n">
-        <v>2030.1</v>
+        <v>293.75</v>
       </c>
       <c r="G309" t="n">
-        <v>2054.95</v>
+        <v>292.72</v>
       </c>
       <c r="H309" t="n">
-        <v>-24.85</v>
+        <v>1.03</v>
       </c>
       <c r="I309" t="n">
-        <v>2013</v>
+        <v>286.6</v>
       </c>
       <c r="J309" t="n">
-        <v>1991.09</v>
+        <v>284.32</v>
       </c>
       <c r="K309" t="n">
-        <v>21.91</v>
+        <v>2.28</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>1.9</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="310">
@@ -16514,35 +16514,35 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>676.15</v>
+        <v>5740.5</v>
       </c>
       <c r="D310" t="n">
-        <v>685.01</v>
+        <v>5813.66</v>
       </c>
       <c r="E310" t="n">
-        <v>-8.859999999999999</v>
+        <v>-73.16</v>
       </c>
       <c r="F310" t="n">
-        <v>682.45</v>
+        <v>5740.5</v>
       </c>
       <c r="G310" t="n">
-        <v>685.01</v>
+        <v>5813.66</v>
       </c>
       <c r="H310" t="n">
-        <v>-2.56</v>
+        <v>-73.16</v>
       </c>
       <c r="I310" t="n">
-        <v>671.95</v>
+        <v>5670</v>
       </c>
       <c r="J310" t="n">
-        <v>655.47</v>
+        <v>5557.57</v>
       </c>
       <c r="K310" t="n">
-        <v>16.48</v>
+        <v>112.43</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="311">
@@ -16566,35 +16566,35 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1048</v>
+        <v>1779.6</v>
       </c>
       <c r="D311" t="n">
-        <v>1050.46</v>
+        <v>1789.64</v>
       </c>
       <c r="E311" t="n">
-        <v>-2.46</v>
+        <v>-10.04</v>
       </c>
       <c r="F311" t="n">
-        <v>1052.9</v>
+        <v>1803.4</v>
       </c>
       <c r="G311" t="n">
-        <v>1050.46</v>
+        <v>1789.64</v>
       </c>
       <c r="H311" t="n">
-        <v>2.44</v>
+        <v>13.76</v>
       </c>
       <c r="I311" t="n">
-        <v>1045.7</v>
+        <v>1764</v>
       </c>
       <c r="J311" t="n">
-        <v>1019.46</v>
+        <v>1725.02</v>
       </c>
       <c r="K311" t="n">
-        <v>26.24</v>
+        <v>38.98</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="312">
@@ -16618,35 +16618,35 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>291.4</v>
+        <v>973.4</v>
       </c>
       <c r="D312" t="n">
-        <v>292.72</v>
+        <v>1027.79</v>
       </c>
       <c r="E312" t="n">
-        <v>-1.32</v>
+        <v>-54.39</v>
       </c>
       <c r="F312" t="n">
-        <v>293.75</v>
+        <v>989.55</v>
       </c>
       <c r="G312" t="n">
-        <v>292.72</v>
+        <v>1027.79</v>
       </c>
       <c r="H312" t="n">
-        <v>1.03</v>
+        <v>-38.24</v>
       </c>
       <c r="I312" t="n">
-        <v>286.6</v>
+        <v>942.15</v>
       </c>
       <c r="J312" t="n">
-        <v>284.32</v>
+        <v>956.1900000000001</v>
       </c>
       <c r="K312" t="n">
-        <v>2.28</v>
+        <v>-14.04</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>0.45</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="313">
@@ -16670,35 +16670,35 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1941.7</v>
+        <v>1260.5</v>
       </c>
       <c r="D313" t="n">
-        <v>1964.08</v>
+        <v>1292.12</v>
       </c>
       <c r="E313" t="n">
-        <v>-22.38</v>
+        <v>-31.62</v>
       </c>
       <c r="F313" t="n">
-        <v>1952.2</v>
+        <v>1282.6</v>
       </c>
       <c r="G313" t="n">
-        <v>1972.01</v>
+        <v>1292.12</v>
       </c>
       <c r="H313" t="n">
-        <v>-19.81</v>
+        <v>-9.52</v>
       </c>
       <c r="I313" t="n">
-        <v>1933</v>
+        <v>1260.5</v>
       </c>
       <c r="J313" t="n">
-        <v>1921.32</v>
+        <v>1223.39</v>
       </c>
       <c r="K313" t="n">
-        <v>11.68</v>
+        <v>37.11</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="314">
@@ -16722,35 +16722,35 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>480.9</v>
+        <v>1029.85</v>
       </c>
       <c r="D314" t="n">
-        <v>478.23</v>
+        <v>1105.03</v>
       </c>
       <c r="E314" t="n">
-        <v>2.67</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="F314" t="n">
-        <v>481.5</v>
+        <v>1048</v>
       </c>
       <c r="G314" t="n">
-        <v>478.23</v>
+        <v>1105.03</v>
       </c>
       <c r="H314" t="n">
-        <v>3.27</v>
+        <v>-57.03</v>
       </c>
       <c r="I314" t="n">
-        <v>465</v>
+        <v>1013</v>
       </c>
       <c r="J314" t="n">
-        <v>462.93</v>
+        <v>1022.2</v>
       </c>
       <c r="K314" t="n">
-        <v>2.07</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="315">
@@ -16774,39 +16774,39 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1882</v>
+        <v>11368</v>
       </c>
       <c r="D315" t="n">
-        <v>1913.14</v>
+        <v>11551.48</v>
       </c>
       <c r="E315" t="n">
-        <v>-31.14</v>
+        <v>-183.48</v>
       </c>
       <c r="F315" t="n">
-        <v>1888.5</v>
+        <v>11423</v>
       </c>
       <c r="G315" t="n">
-        <v>1913.14</v>
+        <v>11551.48</v>
       </c>
       <c r="H315" t="n">
-        <v>-24.64</v>
+        <v>-128.48</v>
       </c>
       <c r="I315" t="n">
-        <v>1826.5</v>
+        <v>11303</v>
       </c>
       <c r="J315" t="n">
-        <v>1832.84</v>
+        <v>11031.46</v>
       </c>
       <c r="K315" t="n">
-        <v>-6.34</v>
+        <v>271.54</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="316">
@@ -16826,39 +16826,39 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>5740.5</v>
+        <v>1203</v>
       </c>
       <c r="D316" t="n">
-        <v>5813.66</v>
+        <v>1205.51</v>
       </c>
       <c r="E316" t="n">
-        <v>-73.16</v>
+        <v>-2.51</v>
       </c>
       <c r="F316" t="n">
-        <v>5740.5</v>
+        <v>1222.9</v>
       </c>
       <c r="G316" t="n">
-        <v>5813.66</v>
+        <v>1205.51</v>
       </c>
       <c r="H316" t="n">
-        <v>-73.16</v>
+        <v>17.39</v>
       </c>
       <c r="I316" t="n">
-        <v>5670</v>
+        <v>1186</v>
       </c>
       <c r="J316" t="n">
-        <v>5557.57</v>
+        <v>1171.8</v>
       </c>
       <c r="K316" t="n">
-        <v>112.43</v>
+        <v>14.2</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>1.26</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="317">
@@ -16878,39 +16878,39 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3126</v>
+        <v>871</v>
       </c>
       <c r="D317" t="n">
-        <v>3190.49</v>
+        <v>884.3099999999999</v>
       </c>
       <c r="E317" t="n">
-        <v>-64.48999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="F317" t="n">
-        <v>3133.2</v>
+        <v>883.8</v>
       </c>
       <c r="G317" t="n">
-        <v>3249.54</v>
+        <v>884.3099999999999</v>
       </c>
       <c r="H317" t="n">
-        <v>-116.34</v>
+        <v>-0.51</v>
       </c>
       <c r="I317" t="n">
-        <v>3006</v>
+        <v>871</v>
       </c>
       <c r="J317" t="n">
-        <v>3166.76</v>
+        <v>850.8099999999999</v>
       </c>
       <c r="K317" t="n">
-        <v>-160.76</v>
+        <v>20.19</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="318">
@@ -16930,39 +16930,39 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1779.6</v>
+        <v>1360.9</v>
       </c>
       <c r="D318" t="n">
-        <v>1789.64</v>
+        <v>1389.34</v>
       </c>
       <c r="E318" t="n">
-        <v>-10.04</v>
+        <v>-28.44</v>
       </c>
       <c r="F318" t="n">
-        <v>1803.4</v>
+        <v>1390.1</v>
       </c>
       <c r="G318" t="n">
-        <v>1789.64</v>
+        <v>1389.34</v>
       </c>
       <c r="H318" t="n">
-        <v>13.76</v>
+        <v>0.76</v>
       </c>
       <c r="I318" t="n">
-        <v>1764</v>
+        <v>1355.3</v>
       </c>
       <c r="J318" t="n">
-        <v>1725.02</v>
+        <v>1296.01</v>
       </c>
       <c r="K318" t="n">
-        <v>38.98</v>
+        <v>59.29</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="319">
@@ -16982,39 +16982,39 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>5674</v>
+        <v>2227</v>
       </c>
       <c r="D319" t="n">
-        <v>5542.6</v>
+        <v>2150.93</v>
       </c>
       <c r="E319" t="n">
-        <v>131.4</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F319" t="n">
-        <v>5706</v>
+        <v>2233.7</v>
       </c>
       <c r="G319" t="n">
-        <v>5725.33</v>
+        <v>2217.3</v>
       </c>
       <c r="H319" t="n">
-        <v>-19.33</v>
+        <v>16.4</v>
       </c>
       <c r="I319" t="n">
-        <v>5534</v>
+        <v>2180.4</v>
       </c>
       <c r="J319" t="n">
-        <v>5577.53</v>
+        <v>2159.24</v>
       </c>
       <c r="K319" t="n">
-        <v>-43.53</v>
+        <v>21.16</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -17023,7 +17023,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>2.37</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="320">
@@ -17034,39 +17034,39 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>973.4</v>
+        <v>2032.5</v>
       </c>
       <c r="D320" t="n">
-        <v>1027.79</v>
+        <v>2009.94</v>
       </c>
       <c r="E320" t="n">
-        <v>-54.39</v>
+        <v>22.56</v>
       </c>
       <c r="F320" t="n">
-        <v>989.55</v>
+        <v>2032.5</v>
       </c>
       <c r="G320" t="n">
-        <v>1027.79</v>
+        <v>2054.87</v>
       </c>
       <c r="H320" t="n">
-        <v>-38.24</v>
+        <v>-22.37</v>
       </c>
       <c r="I320" t="n">
-        <v>942.15</v>
+        <v>2005</v>
       </c>
       <c r="J320" t="n">
-        <v>956.1900000000001</v>
+        <v>2019</v>
       </c>
       <c r="K320" t="n">
-        <v>-14.04</v>
+        <v>-14</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -17075,7 +17075,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>5.29</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="321">
@@ -17086,35 +17086,35 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>11826</v>
+        <v>1048.7</v>
       </c>
       <c r="D321" t="n">
-        <v>11687.68</v>
+        <v>1054.62</v>
       </c>
       <c r="E321" t="n">
-        <v>138.32</v>
+        <v>-5.92</v>
       </c>
       <c r="F321" t="n">
-        <v>11917</v>
+        <v>1054.7</v>
       </c>
       <c r="G321" t="n">
-        <v>11830.43</v>
+        <v>1054.62</v>
       </c>
       <c r="H321" t="n">
-        <v>86.56999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="I321" t="n">
-        <v>11680</v>
+        <v>1040.1</v>
       </c>
       <c r="J321" t="n">
-        <v>11524.58</v>
+        <v>1033.75</v>
       </c>
       <c r="K321" t="n">
-        <v>155.42</v>
+        <v>6.35</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>1.18</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="322">
@@ -17138,35 +17138,35 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>327.95</v>
+        <v>475</v>
       </c>
       <c r="D322" t="n">
-        <v>306.55</v>
+        <v>481.47</v>
       </c>
       <c r="E322" t="n">
-        <v>21.4</v>
+        <v>-6.47</v>
       </c>
       <c r="F322" t="n">
-        <v>328.5</v>
+        <v>482</v>
       </c>
       <c r="G322" t="n">
-        <v>331.99</v>
+        <v>481.47</v>
       </c>
       <c r="H322" t="n">
-        <v>-3.49</v>
+        <v>0.53</v>
       </c>
       <c r="I322" t="n">
-        <v>321.35</v>
+        <v>475</v>
       </c>
       <c r="J322" t="n">
-        <v>323.44</v>
+        <v>469.41</v>
       </c>
       <c r="K322" t="n">
-        <v>-2.09</v>
+        <v>5.59</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>6.98</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="323">
@@ -17190,35 +17190,35 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1260.5</v>
+        <v>678.1</v>
       </c>
       <c r="D323" t="n">
-        <v>1292.12</v>
+        <v>674.6799999999999</v>
       </c>
       <c r="E323" t="n">
-        <v>-31.62</v>
+        <v>3.42</v>
       </c>
       <c r="F323" t="n">
-        <v>1282.6</v>
+        <v>684.45</v>
       </c>
       <c r="G323" t="n">
-        <v>1292.12</v>
+        <v>674.6799999999999</v>
       </c>
       <c r="H323" t="n">
-        <v>-9.52</v>
+        <v>9.77</v>
       </c>
       <c r="I323" t="n">
-        <v>1260.5</v>
+        <v>675.25</v>
       </c>
       <c r="J323" t="n">
-        <v>1223.39</v>
+        <v>664.66</v>
       </c>
       <c r="K323" t="n">
-        <v>37.11</v>
+        <v>10.59</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>2.45</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="324">
@@ -17242,35 +17242,35 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>118</v>
+        <v>3185</v>
       </c>
       <c r="D324" t="n">
-        <v>122.14</v>
+        <v>3160.81</v>
       </c>
       <c r="E324" t="n">
-        <v>-4.14</v>
+        <v>24.19</v>
       </c>
       <c r="F324" t="n">
-        <v>119.1</v>
+        <v>3211.4</v>
       </c>
       <c r="G324" t="n">
-        <v>122.14</v>
+        <v>3266.55</v>
       </c>
       <c r="H324" t="n">
-        <v>-3.04</v>
+        <v>-55.15</v>
       </c>
       <c r="I324" t="n">
-        <v>117.44</v>
+        <v>3132</v>
       </c>
       <c r="J324" t="n">
-        <v>113.63</v>
+        <v>3185</v>
       </c>
       <c r="K324" t="n">
-        <v>3.81</v>
+        <v>-53</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>3.39</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="325">
@@ -17294,35 +17294,35 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1029.85</v>
+        <v>5667.5</v>
       </c>
       <c r="D325" t="n">
-        <v>1105.03</v>
+        <v>5848.29</v>
       </c>
       <c r="E325" t="n">
-        <v>-75.18000000000001</v>
+        <v>-180.79</v>
       </c>
       <c r="F325" t="n">
-        <v>1048</v>
+        <v>5722</v>
       </c>
       <c r="G325" t="n">
-        <v>1105.03</v>
+        <v>5848.29</v>
       </c>
       <c r="H325" t="n">
-        <v>-57.03</v>
+        <v>-126.29</v>
       </c>
       <c r="I325" t="n">
-        <v>1013</v>
+        <v>5602</v>
       </c>
       <c r="J325" t="n">
-        <v>1022.2</v>
+        <v>5655.6</v>
       </c>
       <c r="K325" t="n">
-        <v>-9.199999999999999</v>
+        <v>-53.6</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>6.8</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="326">
@@ -17346,35 +17346,35 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>385.6</v>
+        <v>116.55</v>
       </c>
       <c r="D326" t="n">
-        <v>433.84</v>
+        <v>113.5</v>
       </c>
       <c r="E326" t="n">
-        <v>-48.24</v>
+        <v>3.05</v>
       </c>
       <c r="F326" t="n">
-        <v>395.75</v>
+        <v>117.52</v>
       </c>
       <c r="G326" t="n">
-        <v>433.84</v>
+        <v>116.85</v>
       </c>
       <c r="H326" t="n">
-        <v>-38.09</v>
+        <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>385.1</v>
+        <v>115.41</v>
       </c>
       <c r="J326" t="n">
-        <v>390.67</v>
+        <v>115.22</v>
       </c>
       <c r="K326" t="n">
-        <v>-5.57</v>
+        <v>0.19</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>11.12</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="327">
@@ -17398,35 +17398,35 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>2140</v>
+        <v>1946</v>
       </c>
       <c r="D327" t="n">
-        <v>2076.31</v>
+        <v>1939.23</v>
       </c>
       <c r="E327" t="n">
-        <v>63.69</v>
+        <v>6.77</v>
       </c>
       <c r="F327" t="n">
-        <v>2153.7</v>
+        <v>1954.9</v>
       </c>
       <c r="G327" t="n">
-        <v>2118.48</v>
+        <v>1982.38</v>
       </c>
       <c r="H327" t="n">
-        <v>35.22</v>
+        <v>-27.48</v>
       </c>
       <c r="I327" t="n">
-        <v>2125</v>
+        <v>1940.5</v>
       </c>
       <c r="J327" t="n">
-        <v>2066.74</v>
+        <v>1946</v>
       </c>
       <c r="K327" t="n">
-        <v>58.26</v>
+        <v>-5.5</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>3.07</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="328">
@@ -17450,35 +17450,35 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3424.8</v>
+        <v>328</v>
       </c>
       <c r="D328" t="n">
-        <v>3231.44</v>
+        <v>353.7</v>
       </c>
       <c r="E328" t="n">
-        <v>193.36</v>
+        <v>-25.7</v>
       </c>
       <c r="F328" t="n">
-        <v>3456.4</v>
+        <v>331.7</v>
       </c>
       <c r="G328" t="n">
-        <v>3365.55</v>
+        <v>353.7</v>
       </c>
       <c r="H328" t="n">
-        <v>90.84999999999999</v>
+        <v>-22</v>
       </c>
       <c r="I328" t="n">
-        <v>3401</v>
+        <v>324.1</v>
       </c>
       <c r="J328" t="n">
-        <v>3329.82</v>
+        <v>327.97</v>
       </c>
       <c r="K328" t="n">
-        <v>71.18000000000001</v>
+        <v>-3.87</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -17487,11 +17487,11 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N328" t="n">
-        <v>5.98</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="329">
@@ -17502,39 +17502,39 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>173.8</v>
+        <v>11724</v>
       </c>
       <c r="D329" t="n">
-        <v>172.71</v>
+        <v>11957.59</v>
       </c>
       <c r="E329" t="n">
-        <v>1.09</v>
+        <v>-233.59</v>
       </c>
       <c r="F329" t="n">
-        <v>175.57</v>
+        <v>11870</v>
       </c>
       <c r="G329" t="n">
-        <v>172.71</v>
+        <v>11957.59</v>
       </c>
       <c r="H329" t="n">
-        <v>2.86</v>
+        <v>-87.59</v>
       </c>
       <c r="I329" t="n">
-        <v>172.61</v>
+        <v>11650</v>
       </c>
       <c r="J329" t="n">
-        <v>167.6</v>
+        <v>11685.84</v>
       </c>
       <c r="K329" t="n">
-        <v>5.01</v>
+        <v>-35.84</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="330">
@@ -17554,39 +17554,39 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>4081</v>
+        <v>1891.7</v>
       </c>
       <c r="D330" t="n">
-        <v>4062.2</v>
+        <v>1875.79</v>
       </c>
       <c r="E330" t="n">
-        <v>18.8</v>
+        <v>15.91</v>
       </c>
       <c r="F330" t="n">
-        <v>4084.9</v>
+        <v>1891.7</v>
       </c>
       <c r="G330" t="n">
-        <v>4101.72</v>
+        <v>1875.79</v>
       </c>
       <c r="H330" t="n">
-        <v>-16.82</v>
+        <v>15.91</v>
       </c>
       <c r="I330" t="n">
-        <v>4048.3</v>
+        <v>1851</v>
       </c>
       <c r="J330" t="n">
-        <v>4014.48</v>
+        <v>1858.54</v>
       </c>
       <c r="K330" t="n">
-        <v>33.82</v>
+        <v>-7.54</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -17595,7 +17595,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="331">
@@ -17606,39 +17606,39 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1585.5</v>
+        <v>2139</v>
       </c>
       <c r="D331" t="n">
-        <v>1625.95</v>
+        <v>2222.24</v>
       </c>
       <c r="E331" t="n">
-        <v>-40.45</v>
+        <v>-83.23999999999999</v>
       </c>
       <c r="F331" t="n">
-        <v>1610</v>
+        <v>2162.2</v>
       </c>
       <c r="G331" t="n">
-        <v>1625.95</v>
+        <v>2222.24</v>
       </c>
       <c r="H331" t="n">
-        <v>-15.95</v>
+        <v>-60.04</v>
       </c>
       <c r="I331" t="n">
-        <v>1581</v>
+        <v>2126.3</v>
       </c>
       <c r="J331" t="n">
-        <v>1568.44</v>
+        <v>2095.72</v>
       </c>
       <c r="K331" t="n">
-        <v>12.56</v>
+        <v>30.58</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>2.49</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="332">
@@ -17658,48 +17658,48 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>11368</v>
+        <v>394.45</v>
       </c>
       <c r="D332" t="n">
-        <v>11551.48</v>
+        <v>353.75</v>
       </c>
       <c r="E332" t="n">
-        <v>-183.48</v>
+        <v>40.7</v>
       </c>
       <c r="F332" t="n">
-        <v>11423</v>
+        <v>397.5</v>
       </c>
       <c r="G332" t="n">
-        <v>11551.48</v>
+        <v>403.03</v>
       </c>
       <c r="H332" t="n">
-        <v>-128.48</v>
+        <v>-5.53</v>
       </c>
       <c r="I332" t="n">
-        <v>11303</v>
+        <v>384.6</v>
       </c>
       <c r="J332" t="n">
-        <v>11031.46</v>
+        <v>394.45</v>
       </c>
       <c r="K332" t="n">
-        <v>271.54</v>
+        <v>-9.85</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N332" t="n">
-        <v>1.59</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="333">
@@ -17710,35 +17710,35 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2570</v>
+        <v>4093</v>
       </c>
       <c r="D333" t="n">
-        <v>2591.15</v>
+        <v>4144.84</v>
       </c>
       <c r="E333" t="n">
-        <v>-21.15</v>
+        <v>-51.84</v>
       </c>
       <c r="F333" t="n">
-        <v>2583.2</v>
+        <v>4100</v>
       </c>
       <c r="G333" t="n">
-        <v>2591.15</v>
+        <v>4144.84</v>
       </c>
       <c r="H333" t="n">
-        <v>-7.95</v>
+        <v>-44.84</v>
       </c>
       <c r="I333" t="n">
-        <v>2552</v>
+        <v>4061.4</v>
       </c>
       <c r="J333" t="n">
-        <v>2463.59</v>
+        <v>4070.76</v>
       </c>
       <c r="K333" t="n">
-        <v>88.41</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>0.82</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="334">
@@ -17762,35 +17762,35 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1203</v>
+        <v>173</v>
       </c>
       <c r="D334" t="n">
-        <v>1205.51</v>
+        <v>175.48</v>
       </c>
       <c r="E334" t="n">
-        <v>-2.51</v>
+        <v>-2.48</v>
       </c>
       <c r="F334" t="n">
-        <v>1222.9</v>
+        <v>173.69</v>
       </c>
       <c r="G334" t="n">
-        <v>1205.51</v>
+        <v>175.48</v>
       </c>
       <c r="H334" t="n">
-        <v>17.39</v>
+        <v>-1.79</v>
       </c>
       <c r="I334" t="n">
-        <v>1186</v>
+        <v>172.3</v>
       </c>
       <c r="J334" t="n">
-        <v>1171.8</v>
+        <v>169.95</v>
       </c>
       <c r="K334" t="n">
-        <v>14.2</v>
+        <v>2.35</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>0.21</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="335">
@@ -17814,35 +17814,35 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>871</v>
+        <v>1631</v>
       </c>
       <c r="D335" t="n">
-        <v>884.3099999999999</v>
+        <v>1603.15</v>
       </c>
       <c r="E335" t="n">
-        <v>-13.31</v>
+        <v>27.85</v>
       </c>
       <c r="F335" t="n">
-        <v>883.8</v>
+        <v>1651.3</v>
       </c>
       <c r="G335" t="n">
-        <v>884.3099999999999</v>
+        <v>1608.2</v>
       </c>
       <c r="H335" t="n">
-        <v>-0.51</v>
+        <v>43.1</v>
       </c>
       <c r="I335" t="n">
-        <v>871</v>
+        <v>1590</v>
       </c>
       <c r="J335" t="n">
-        <v>850.8099999999999</v>
+        <v>1590.43</v>
       </c>
       <c r="K335" t="n">
-        <v>20.19</v>
+        <v>-0.43</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="336">
@@ -17866,35 +17866,35 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>1360.9</v>
+        <v>3412.2</v>
       </c>
       <c r="D336" t="n">
-        <v>1389.34</v>
+        <v>3645.32</v>
       </c>
       <c r="E336" t="n">
-        <v>-28.44</v>
+        <v>-233.12</v>
       </c>
       <c r="F336" t="n">
-        <v>1390.1</v>
+        <v>3453.9</v>
       </c>
       <c r="G336" t="n">
-        <v>1389.34</v>
+        <v>3645.32</v>
       </c>
       <c r="H336" t="n">
-        <v>0.76</v>
+        <v>-191.42</v>
       </c>
       <c r="I336" t="n">
-        <v>1355.3</v>
+        <v>3412.2</v>
       </c>
       <c r="J336" t="n">
-        <v>1296.01</v>
+        <v>3376.5</v>
       </c>
       <c r="K336" t="n">
-        <v>59.29</v>
+        <v>35.7</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>2.05</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="337">
@@ -17918,35 +17918,35 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>184.68</v>
+        <v>2552</v>
       </c>
       <c r="D337" t="n">
-        <v>195.08</v>
+        <v>2551.43</v>
       </c>
       <c r="E337" t="n">
-        <v>-10.4</v>
+        <v>0.57</v>
       </c>
       <c r="F337" t="n">
-        <v>189.46</v>
+        <v>2596</v>
       </c>
       <c r="G337" t="n">
-        <v>195.08</v>
+        <v>2551.43</v>
       </c>
       <c r="H337" t="n">
-        <v>-5.62</v>
+        <v>44.57</v>
       </c>
       <c r="I337" t="n">
-        <v>184.39</v>
+        <v>2542</v>
       </c>
       <c r="J337" t="n">
-        <v>178.56</v>
+        <v>2498.14</v>
       </c>
       <c r="K337" t="n">
-        <v>5.83</v>
+        <v>43.86</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>5.33</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="338">
@@ -17970,35 +17970,35 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2227</v>
+        <v>14850</v>
       </c>
       <c r="D338" t="n">
-        <v>2150.93</v>
+        <v>15422.35</v>
       </c>
       <c r="E338" t="n">
-        <v>76.06999999999999</v>
+        <v>-572.35</v>
       </c>
       <c r="F338" t="n">
-        <v>2233.7</v>
+        <v>14924</v>
       </c>
       <c r="G338" t="n">
-        <v>2217.3</v>
+        <v>15422.35</v>
       </c>
       <c r="H338" t="n">
-        <v>16.4</v>
+        <v>-498.35</v>
       </c>
       <c r="I338" t="n">
-        <v>2180.4</v>
+        <v>14620</v>
       </c>
       <c r="J338" t="n">
-        <v>2159.24</v>
+        <v>14577.94</v>
       </c>
       <c r="K338" t="n">
-        <v>21.16</v>
+        <v>42.06</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="339">
@@ -18022,35 +18022,35 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>519</v>
+        <v>183.45</v>
       </c>
       <c r="D339" t="n">
-        <v>480.87</v>
+        <v>175.06</v>
       </c>
       <c r="E339" t="n">
-        <v>38.13</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F339" t="n">
-        <v>524.4</v>
+        <v>185.3</v>
       </c>
       <c r="G339" t="n">
-        <v>505.57</v>
+        <v>184.32</v>
       </c>
       <c r="H339" t="n">
-        <v>18.83</v>
+        <v>0.98</v>
       </c>
       <c r="I339" t="n">
-        <v>513.8</v>
+        <v>182.5</v>
       </c>
       <c r="J339" t="n">
-        <v>498.74</v>
+        <v>181.07</v>
       </c>
       <c r="K339" t="n">
-        <v>15.06</v>
+        <v>1.43</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -18059,11 +18059,11 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>7.93</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="340">
@@ -18074,35 +18074,35 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>14850</v>
+        <v>515.05</v>
       </c>
       <c r="D340" t="n">
-        <v>14413.31</v>
+        <v>560.33</v>
       </c>
       <c r="E340" t="n">
-        <v>436.69</v>
+        <v>-45.28</v>
       </c>
       <c r="F340" t="n">
-        <v>14953</v>
+        <v>523</v>
       </c>
       <c r="G340" t="n">
-        <v>14511.32</v>
+        <v>560.33</v>
       </c>
       <c r="H340" t="n">
-        <v>441.68</v>
+        <v>-37.33</v>
       </c>
       <c r="I340" t="n">
-        <v>14470</v>
+        <v>512.15</v>
       </c>
       <c r="J340" t="n">
-        <v>14376.37</v>
+        <v>505.74</v>
       </c>
       <c r="K340" t="n">
-        <v>93.63</v>
+        <v>6.41</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -18111,11 +18111,11 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N340" t="n">
-        <v>3.03</v>
+        <v>8.08</v>
       </c>
     </row>
   </sheetData>
@@ -19464,31 +19464,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24231.85</v>
+        <v>24252</v>
       </c>
       <c r="D26" t="n">
         <v>24252</v>
       </c>
       <c r="E26" t="n">
-        <v>-20.15</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>24265.15</v>
+        <v>24284.05</v>
       </c>
       <c r="G26" t="n">
         <v>24288.44</v>
       </c>
       <c r="H26" t="n">
-        <v>-23.29</v>
+        <v>-4.39</v>
       </c>
       <c r="I26" t="n">
-        <v>24184.55</v>
+        <v>24206.8</v>
       </c>
       <c r="J26" t="n">
         <v>24211.19</v>
       </c>
       <c r="K26" t="n">
-        <v>-26.64</v>
+        <v>-4.39</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -19516,31 +19516,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57495.9</v>
+        <v>57761.95</v>
       </c>
       <c r="D27" t="n">
         <v>57761.95</v>
       </c>
       <c r="E27" t="n">
-        <v>-266.05</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>57702.95</v>
+        <v>57772.45</v>
       </c>
       <c r="G27" t="n">
         <v>57862.41</v>
       </c>
       <c r="H27" t="n">
-        <v>-159.46</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>57431.8</v>
+        <v>57481.55</v>
       </c>
       <c r="J27" t="n">
         <v>57571.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-139.71</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -35614,35 +35614,35 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+          <t>POLICYBZR (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2016</v>
+        <v>1779.6</v>
       </c>
       <c r="D309" t="n">
-        <v>2088.59</v>
+        <v>1842.9</v>
       </c>
       <c r="E309" t="n">
-        <v>-72.59</v>
+        <v>-63.3</v>
       </c>
       <c r="F309" t="n">
-        <v>2030.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G309" t="n">
-        <v>2054.98</v>
+        <v>1838.04</v>
       </c>
       <c r="H309" t="n">
-        <v>-24.88</v>
+        <v>-34.64</v>
       </c>
       <c r="I309" t="n">
-        <v>2013</v>
+        <v>1764</v>
       </c>
       <c r="J309" t="n">
-        <v>1992.59</v>
+        <v>1742.56</v>
       </c>
       <c r="K309" t="n">
-        <v>20.41</v>
+        <v>21.44</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="310">
@@ -35666,35 +35666,35 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DLF (AUG-2026 FUT)</t>
+          <t>PETRONET (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>676.15</v>
+        <v>291.4</v>
       </c>
       <c r="D310" t="n">
-        <v>701.34</v>
+        <v>298.58</v>
       </c>
       <c r="E310" t="n">
-        <v>-25.19</v>
+        <v>-7.18</v>
       </c>
       <c r="F310" t="n">
-        <v>682.45</v>
+        <v>293.75</v>
       </c>
       <c r="G310" t="n">
-        <v>690.4400000000001</v>
+        <v>297.26</v>
       </c>
       <c r="H310" t="n">
-        <v>-7.99</v>
+        <v>-3.51</v>
       </c>
       <c r="I310" t="n">
-        <v>671.95</v>
+        <v>286.6</v>
       </c>
       <c r="J310" t="n">
-        <v>661.12</v>
+        <v>286.49</v>
       </c>
       <c r="K310" t="n">
-        <v>10.83</v>
+        <v>0.11</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -35703,11 +35703,11 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N310" t="n">
-        <v>3.59</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="311">
@@ -35718,35 +35718,35 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ETERNAL (AUG-2026 FUT)</t>
+          <t>HINDALCO (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>327.95</v>
+        <v>1029.85</v>
       </c>
       <c r="D311" t="n">
-        <v>312.65</v>
+        <v>1134.23</v>
       </c>
       <c r="E311" t="n">
-        <v>15.3</v>
+        <v>-104.38</v>
       </c>
       <c r="F311" t="n">
-        <v>328.5</v>
+        <v>1048</v>
       </c>
       <c r="G311" t="n">
-        <v>332.73</v>
+        <v>1055.37</v>
       </c>
       <c r="H311" t="n">
-        <v>-4.23</v>
+        <v>-7.37</v>
       </c>
       <c r="I311" t="n">
-        <v>321.35</v>
+        <v>1013</v>
       </c>
       <c r="J311" t="n">
-        <v>320.73</v>
+        <v>1006.18</v>
       </c>
       <c r="K311" t="n">
-        <v>0.62</v>
+        <v>6.82</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -35755,11 +35755,11 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N311" t="n">
-        <v>4.89</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="312">
@@ -35770,35 +35770,35 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MCX (AUG-2026 FUT)</t>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3126</v>
+        <v>973.4</v>
       </c>
       <c r="D312" t="n">
-        <v>3284.74</v>
+        <v>1054.29</v>
       </c>
       <c r="E312" t="n">
-        <v>-158.74</v>
+        <v>-80.89</v>
       </c>
       <c r="F312" t="n">
-        <v>3133.2</v>
+        <v>989.55</v>
       </c>
       <c r="G312" t="n">
-        <v>3275.48</v>
+        <v>1009.86</v>
       </c>
       <c r="H312" t="n">
-        <v>-142.28</v>
+        <v>-20.31</v>
       </c>
       <c r="I312" t="n">
-        <v>3006</v>
+        <v>942.15</v>
       </c>
       <c r="J312" t="n">
-        <v>3080.65</v>
+        <v>963.83</v>
       </c>
       <c r="K312" t="n">
-        <v>-74.65000000000001</v>
+        <v>-21.68</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>4.83</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="313">
@@ -35822,39 +35822,39 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>POLICYBZR (AUG-2026 FUT)</t>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1779.6</v>
+        <v>5740.5</v>
       </c>
       <c r="D313" t="n">
-        <v>1842.9</v>
+        <v>5937.51</v>
       </c>
       <c r="E313" t="n">
-        <v>-63.3</v>
+        <v>-197.01</v>
       </c>
       <c r="F313" t="n">
-        <v>1803.4</v>
+        <v>5740.5</v>
       </c>
       <c r="G313" t="n">
-        <v>1838.04</v>
+        <v>5825.46</v>
       </c>
       <c r="H313" t="n">
-        <v>-34.64</v>
+        <v>-84.95999999999999</v>
       </c>
       <c r="I313" t="n">
-        <v>1764</v>
+        <v>5670</v>
       </c>
       <c r="J313" t="n">
-        <v>1742.56</v>
+        <v>5601.93</v>
       </c>
       <c r="K313" t="n">
-        <v>21.44</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -35863,7 +35863,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>3.43</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="314">
@@ -35874,48 +35874,48 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SBIN (AUG-2026 FUT)</t>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>1048</v>
+        <v>1260.5</v>
       </c>
       <c r="D314" t="n">
-        <v>1069.51</v>
+        <v>1322.27</v>
       </c>
       <c r="E314" t="n">
-        <v>-21.51</v>
+        <v>-61.77</v>
       </c>
       <c r="F314" t="n">
-        <v>1052.9</v>
+        <v>1282.6</v>
       </c>
       <c r="G314" t="n">
-        <v>1062.07</v>
+        <v>1287.42</v>
       </c>
       <c r="H314" t="n">
-        <v>-9.17</v>
+        <v>-4.82</v>
       </c>
       <c r="I314" t="n">
-        <v>1045.7</v>
+        <v>1260.5</v>
       </c>
       <c r="J314" t="n">
-        <v>1026.77</v>
+        <v>1233.78</v>
       </c>
       <c r="K314" t="n">
-        <v>18.93</v>
+        <v>26.72</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N314" t="n">
-        <v>2.01</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="315">
@@ -35926,48 +35926,48 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PERSISTENT (AUG-2026 FUT)</t>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>5674</v>
+        <v>11368</v>
       </c>
       <c r="D315" t="n">
-        <v>5673.46</v>
+        <v>11732.29</v>
       </c>
       <c r="E315" t="n">
-        <v>0.54</v>
+        <v>-364.29</v>
       </c>
       <c r="F315" t="n">
-        <v>5706</v>
+        <v>11423</v>
       </c>
       <c r="G315" t="n">
-        <v>5769.39</v>
+        <v>11437.43</v>
       </c>
       <c r="H315" t="n">
-        <v>-63.39</v>
+        <v>-14.43</v>
       </c>
       <c r="I315" t="n">
-        <v>5534</v>
+        <v>11303</v>
       </c>
       <c r="J315" t="n">
-        <v>5526.55</v>
+        <v>11103.58</v>
       </c>
       <c r="K315" t="n">
-        <v>7.45</v>
+        <v>199.42</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N315" t="n">
-        <v>0.01</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="316">
@@ -35978,39 +35978,39 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PETRONET (AUG-2026 FUT)</t>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>291.4</v>
+        <v>2227</v>
       </c>
       <c r="D316" t="n">
-        <v>298.58</v>
+        <v>2193.81</v>
       </c>
       <c r="E316" t="n">
-        <v>-7.18</v>
+        <v>33.19</v>
       </c>
       <c r="F316" t="n">
-        <v>293.75</v>
+        <v>2233.7</v>
       </c>
       <c r="G316" t="n">
-        <v>297.26</v>
+        <v>2250.9</v>
       </c>
       <c r="H316" t="n">
-        <v>-3.51</v>
+        <v>-17.2</v>
       </c>
       <c r="I316" t="n">
-        <v>286.6</v>
+        <v>2180.4</v>
       </c>
       <c r="J316" t="n">
-        <v>286.49</v>
+        <v>2169.52</v>
       </c>
       <c r="K316" t="n">
-        <v>0.11</v>
+        <v>10.88</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -36019,7 +36019,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="317">
@@ -36030,39 +36030,39 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>BHARTIARTL (AUG-2026 FUT)</t>
+          <t>NAUKRI (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1941.7</v>
+        <v>1360.9</v>
       </c>
       <c r="D317" t="n">
-        <v>1999.83</v>
+        <v>1432.09</v>
       </c>
       <c r="E317" t="n">
-        <v>-58.13</v>
+        <v>-71.19</v>
       </c>
       <c r="F317" t="n">
-        <v>1952.2</v>
+        <v>1390.1</v>
       </c>
       <c r="G317" t="n">
-        <v>1970.93</v>
+        <v>1383.61</v>
       </c>
       <c r="H317" t="n">
-        <v>-18.73</v>
+        <v>6.49</v>
       </c>
       <c r="I317" t="n">
-        <v>1933</v>
+        <v>1355.3</v>
       </c>
       <c r="J317" t="n">
-        <v>1905.21</v>
+        <v>1309.54</v>
       </c>
       <c r="K317" t="n">
-        <v>27.79</v>
+        <v>45.76</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>2.91</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="318">
@@ -36082,48 +36082,48 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PNB (AUG-2026 FUT)</t>
+          <t>360ONE (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>118</v>
+        <v>1203</v>
       </c>
       <c r="D318" t="n">
-        <v>124</v>
+        <v>1235.01</v>
       </c>
       <c r="E318" t="n">
-        <v>-6</v>
+        <v>-32.01</v>
       </c>
       <c r="F318" t="n">
-        <v>119.1</v>
+        <v>1222.9</v>
       </c>
       <c r="G318" t="n">
-        <v>117.71</v>
+        <v>1221.54</v>
       </c>
       <c r="H318" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="I318" t="n">
-        <v>117.44</v>
+        <v>1186</v>
       </c>
       <c r="J318" t="n">
-        <v>114.37</v>
+        <v>1168.43</v>
       </c>
       <c r="K318" t="n">
-        <v>3.07</v>
+        <v>17.57</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N318" t="n">
-        <v>4.84</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="319">
@@ -36134,39 +36134,39 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>HINDALCO (AUG-2026 FUT)</t>
+          <t>INDIANB (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>1029.85</v>
+        <v>871</v>
       </c>
       <c r="D319" t="n">
-        <v>1134.23</v>
+        <v>902.0700000000001</v>
       </c>
       <c r="E319" t="n">
-        <v>-104.38</v>
+        <v>-31.07</v>
       </c>
       <c r="F319" t="n">
-        <v>1048</v>
+        <v>883.8</v>
       </c>
       <c r="G319" t="n">
-        <v>1055.37</v>
+        <v>889.71</v>
       </c>
       <c r="H319" t="n">
-        <v>-7.37</v>
+        <v>-5.91</v>
       </c>
       <c r="I319" t="n">
-        <v>1013</v>
+        <v>871</v>
       </c>
       <c r="J319" t="n">
-        <v>1006.18</v>
+        <v>857.3200000000001</v>
       </c>
       <c r="K319" t="n">
-        <v>6.82</v>
+        <v>13.68</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>🟢 INTRADAY LONG BREAKOUT</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -36175,7 +36175,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>9.199999999999999</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="320">
@@ -36186,35 +36186,35 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>OIL (AUG-2026 FUT)</t>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>480.9</v>
+        <v>2032.5</v>
       </c>
       <c r="D320" t="n">
-        <v>491.69</v>
+        <v>2042.54</v>
       </c>
       <c r="E320" t="n">
-        <v>-10.79</v>
+        <v>-10.04</v>
       </c>
       <c r="F320" t="n">
-        <v>481.5</v>
+        <v>2032.5</v>
       </c>
       <c r="G320" t="n">
-        <v>485.61</v>
+        <v>2065.43</v>
       </c>
       <c r="H320" t="n">
-        <v>-4.11</v>
+        <v>-32.93</v>
       </c>
       <c r="I320" t="n">
-        <v>465</v>
+        <v>2005</v>
       </c>
       <c r="J320" t="n">
-        <v>461.63</v>
+        <v>2020.21</v>
       </c>
       <c r="K320" t="n">
-        <v>3.37</v>
+        <v>-15.21</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>2.19</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="321">
@@ -36238,35 +36238,35 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>NATIONALUM (AUG-2026 FUT)</t>
+          <t>ETERNAL (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>385.6</v>
+        <v>328</v>
       </c>
       <c r="D321" t="n">
-        <v>449.33</v>
+        <v>360.69</v>
       </c>
       <c r="E321" t="n">
-        <v>-63.73</v>
+        <v>-32.69</v>
       </c>
       <c r="F321" t="n">
-        <v>395.75</v>
+        <v>331.7</v>
       </c>
       <c r="G321" t="n">
-        <v>406.49</v>
+        <v>334.42</v>
       </c>
       <c r="H321" t="n">
-        <v>-10.74</v>
+        <v>-2.72</v>
       </c>
       <c r="I321" t="n">
-        <v>385.1</v>
+        <v>324.1</v>
       </c>
       <c r="J321" t="n">
-        <v>380.9</v>
+        <v>325.17</v>
       </c>
       <c r="K321" t="n">
-        <v>4.2</v>
+        <v>-1.07</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>14.18</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="322">
@@ -36290,35 +36290,35 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>MOTILALOFS (AUG-2026 FUT)</t>
+          <t>DLF (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>973.4</v>
+        <v>678.1</v>
       </c>
       <c r="D322" t="n">
-        <v>1054.29</v>
+        <v>690.66</v>
       </c>
       <c r="E322" t="n">
-        <v>-80.89</v>
+        <v>-12.56</v>
       </c>
       <c r="F322" t="n">
-        <v>989.55</v>
+        <v>684.45</v>
       </c>
       <c r="G322" t="n">
-        <v>1009.86</v>
+        <v>693.95</v>
       </c>
       <c r="H322" t="n">
-        <v>-20.31</v>
+        <v>-9.5</v>
       </c>
       <c r="I322" t="n">
-        <v>942.15</v>
+        <v>675.25</v>
       </c>
       <c r="J322" t="n">
-        <v>963.83</v>
+        <v>670.29</v>
       </c>
       <c r="K322" t="n">
-        <v>-21.68</v>
+        <v>4.96</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -36327,11 +36327,11 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N322" t="n">
-        <v>7.67</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="323">
@@ -36342,39 +36342,39 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>OFSS (AUG-2026 FUT)</t>
+          <t>MCX (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>11826</v>
+        <v>3185</v>
       </c>
       <c r="D323" t="n">
-        <v>11972.65</v>
+        <v>3253.72</v>
       </c>
       <c r="E323" t="n">
-        <v>-146.65</v>
+        <v>-68.72</v>
       </c>
       <c r="F323" t="n">
-        <v>11917</v>
+        <v>3211.4</v>
       </c>
       <c r="G323" t="n">
-        <v>11943.45</v>
+        <v>3292.15</v>
       </c>
       <c r="H323" t="n">
-        <v>-26.45</v>
+        <v>-80.75</v>
       </c>
       <c r="I323" t="n">
-        <v>11680</v>
+        <v>3132</v>
       </c>
       <c r="J323" t="n">
-        <v>11425.84</v>
+        <v>3123.36</v>
       </c>
       <c r="K323" t="n">
-        <v>254.16</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -36383,7 +36383,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="324">
@@ -36394,39 +36394,39 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>COFORGE (AUG-2026 FUT)</t>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>1882</v>
+        <v>5667.5</v>
       </c>
       <c r="D324" t="n">
-        <v>1954.25</v>
+        <v>5985.49</v>
       </c>
       <c r="E324" t="n">
-        <v>-72.25</v>
+        <v>-317.99</v>
       </c>
       <c r="F324" t="n">
-        <v>1888.5</v>
+        <v>5722</v>
       </c>
       <c r="G324" t="n">
-        <v>1921.86</v>
+        <v>5798.74</v>
       </c>
       <c r="H324" t="n">
-        <v>-33.36</v>
+        <v>-76.73999999999999</v>
       </c>
       <c r="I324" t="n">
-        <v>1826.5</v>
+        <v>5602</v>
       </c>
       <c r="J324" t="n">
-        <v>1847.56</v>
+        <v>5603.16</v>
       </c>
       <c r="K324" t="n">
-        <v>-21.06</v>
+        <v>-1.16</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -36435,7 +36435,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>3.7</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="325">
@@ -36446,48 +36446,48 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+          <t>SBIN (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>5740.5</v>
+        <v>1048.7</v>
       </c>
       <c r="D325" t="n">
-        <v>5937.51</v>
+        <v>1073.58</v>
       </c>
       <c r="E325" t="n">
-        <v>-197.01</v>
+        <v>-24.88</v>
       </c>
       <c r="F325" t="n">
-        <v>5740.5</v>
+        <v>1054.7</v>
       </c>
       <c r="G325" t="n">
-        <v>5825.46</v>
+        <v>1067.47</v>
       </c>
       <c r="H325" t="n">
-        <v>-84.95999999999999</v>
+        <v>-12.77</v>
       </c>
       <c r="I325" t="n">
-        <v>5670</v>
+        <v>1040.1</v>
       </c>
       <c r="J325" t="n">
-        <v>5601.93</v>
+        <v>1041</v>
       </c>
       <c r="K325" t="n">
-        <v>68.06999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N325" t="n">
-        <v>3.32</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="326">
@@ -36498,39 +36498,39 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>APLAPOLLO (AUG-2026 FUT)</t>
+          <t>PNB (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>2140</v>
+        <v>116.55</v>
       </c>
       <c r="D326" t="n">
-        <v>2126.67</v>
+        <v>115.21</v>
       </c>
       <c r="E326" t="n">
-        <v>13.33</v>
+        <v>1.34</v>
       </c>
       <c r="F326" t="n">
-        <v>2153.7</v>
+        <v>117.52</v>
       </c>
       <c r="G326" t="n">
-        <v>2178.78</v>
+        <v>118.31</v>
       </c>
       <c r="H326" t="n">
-        <v>-25.08</v>
+        <v>-0.79</v>
       </c>
       <c r="I326" t="n">
-        <v>2125</v>
+        <v>115.41</v>
       </c>
       <c r="J326" t="n">
-        <v>2084.8</v>
+        <v>115.95</v>
       </c>
       <c r="K326" t="n">
-        <v>40.2</v>
+        <v>-0.54</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -36539,7 +36539,7 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>0.63</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="327">
@@ -36550,39 +36550,39 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>M&amp;M (AUG-2026 FUT)</t>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3424.8</v>
+        <v>1946</v>
       </c>
       <c r="D327" t="n">
-        <v>3277.52</v>
+        <v>1974.23</v>
       </c>
       <c r="E327" t="n">
-        <v>147.28</v>
+        <v>-28.23</v>
       </c>
       <c r="F327" t="n">
-        <v>3456.4</v>
+        <v>1954.9</v>
       </c>
       <c r="G327" t="n">
-        <v>3443.05</v>
+        <v>1980.96</v>
       </c>
       <c r="H327" t="n">
-        <v>13.35</v>
+        <v>-26.06</v>
       </c>
       <c r="I327" t="n">
-        <v>3401</v>
+        <v>1940.5</v>
       </c>
       <c r="J327" t="n">
-        <v>3350.41</v>
+        <v>1931.63</v>
       </c>
       <c r="K327" t="n">
-        <v>50.59</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -36591,7 +36591,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>4.49</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="328">
@@ -36602,39 +36602,39 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>UNOMINDA (AUG-2026 FUT)</t>
+          <t>OIL (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1260.5</v>
+        <v>475</v>
       </c>
       <c r="D328" t="n">
-        <v>1322.27</v>
+        <v>494.96</v>
       </c>
       <c r="E328" t="n">
-        <v>-61.77</v>
+        <v>-19.96</v>
       </c>
       <c r="F328" t="n">
-        <v>1282.6</v>
+        <v>482</v>
       </c>
       <c r="G328" t="n">
-        <v>1287.42</v>
+        <v>488.08</v>
       </c>
       <c r="H328" t="n">
-        <v>-4.82</v>
+        <v>-6.08</v>
       </c>
       <c r="I328" t="n">
-        <v>1260.5</v>
+        <v>475</v>
       </c>
       <c r="J328" t="n">
-        <v>1233.78</v>
+        <v>468.03</v>
       </c>
       <c r="K328" t="n">
-        <v>26.72</v>
+        <v>6.97</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -36643,7 +36643,7 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>4.67</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="329">
@@ -36654,35 +36654,35 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>LT (AUG-2026 FUT)</t>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>4081</v>
+        <v>394.45</v>
       </c>
       <c r="D329" t="n">
-        <v>4099.22</v>
+        <v>366.32</v>
       </c>
       <c r="E329" t="n">
-        <v>-18.22</v>
+        <v>28.13</v>
       </c>
       <c r="F329" t="n">
-        <v>4084.9</v>
+        <v>397.5</v>
       </c>
       <c r="G329" t="n">
-        <v>4109.87</v>
+        <v>408.55</v>
       </c>
       <c r="H329" t="n">
-        <v>-24.97</v>
+        <v>-11.05</v>
       </c>
       <c r="I329" t="n">
-        <v>4048.3</v>
+        <v>384.6</v>
       </c>
       <c r="J329" t="n">
-        <v>4034.1</v>
+        <v>386.18</v>
       </c>
       <c r="K329" t="n">
-        <v>14.2</v>
+        <v>-1.58</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>0.44</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="330">
@@ -36706,35 +36706,35 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PRESTIGE (AUG-2026 FUT)</t>
+          <t>OFSS (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>1585.5</v>
+        <v>11724</v>
       </c>
       <c r="D330" t="n">
-        <v>1673.1</v>
+        <v>12247.37</v>
       </c>
       <c r="E330" t="n">
-        <v>-87.59999999999999</v>
+        <v>-523.37</v>
       </c>
       <c r="F330" t="n">
-        <v>1610</v>
+        <v>11870</v>
       </c>
       <c r="G330" t="n">
-        <v>1668.73</v>
+        <v>12004.21</v>
       </c>
       <c r="H330" t="n">
-        <v>-58.73</v>
+        <v>-134.21</v>
       </c>
       <c r="I330" t="n">
-        <v>1581</v>
+        <v>11650</v>
       </c>
       <c r="J330" t="n">
-        <v>1584.08</v>
+        <v>11584.26</v>
       </c>
       <c r="K330" t="n">
-        <v>-3.08</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>5.24</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="331">
@@ -36758,35 +36758,35 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+          <t>COFORGE (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>11368</v>
+        <v>1891.7</v>
       </c>
       <c r="D331" t="n">
-        <v>11732.29</v>
+        <v>1915.81</v>
       </c>
       <c r="E331" t="n">
-        <v>-364.29</v>
+        <v>-24.11</v>
       </c>
       <c r="F331" t="n">
-        <v>11423</v>
+        <v>1891.7</v>
       </c>
       <c r="G331" t="n">
-        <v>11437.43</v>
+        <v>1931.64</v>
       </c>
       <c r="H331" t="n">
-        <v>-14.43</v>
+        <v>-39.94</v>
       </c>
       <c r="I331" t="n">
-        <v>11303</v>
+        <v>1851</v>
       </c>
       <c r="J331" t="n">
-        <v>11103.58</v>
+        <v>1873.18</v>
       </c>
       <c r="K331" t="n">
-        <v>199.42</v>
+        <v>-22.18</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -36795,11 +36795,11 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N331" t="n">
-        <v>3.11</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="332">
@@ -36810,48 +36810,48 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>ASHOKLEY (AUG-2026 FUT)</t>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>173.8</v>
+        <v>2139</v>
       </c>
       <c r="D332" t="n">
-        <v>177.56</v>
+        <v>2275.81</v>
       </c>
       <c r="E332" t="n">
-        <v>-3.76</v>
+        <v>-136.81</v>
       </c>
       <c r="F332" t="n">
-        <v>175.57</v>
+        <v>2162.2</v>
       </c>
       <c r="G332" t="n">
-        <v>176.84</v>
+        <v>2189.86</v>
       </c>
       <c r="H332" t="n">
-        <v>-1.27</v>
+        <v>-27.66</v>
       </c>
       <c r="I332" t="n">
-        <v>172.61</v>
+        <v>2126.3</v>
       </c>
       <c r="J332" t="n">
-        <v>168.15</v>
+        <v>2113.7</v>
       </c>
       <c r="K332" t="n">
-        <v>4.46</v>
+        <v>12.6</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N332" t="n">
-        <v>2.12</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="333">
@@ -36862,39 +36862,39 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>UNIONBANK (AUG-2026 FUT)</t>
+          <t>M&amp;M (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>184.68</v>
+        <v>3412.2</v>
       </c>
       <c r="D333" t="n">
-        <v>199.84</v>
+        <v>3696.74</v>
       </c>
       <c r="E333" t="n">
-        <v>-15.16</v>
+        <v>-284.54</v>
       </c>
       <c r="F333" t="n">
-        <v>189.46</v>
+        <v>3453.9</v>
       </c>
       <c r="G333" t="n">
-        <v>186.9</v>
+        <v>3460.55</v>
       </c>
       <c r="H333" t="n">
-        <v>2.56</v>
+        <v>-6.65</v>
       </c>
       <c r="I333" t="n">
-        <v>184.39</v>
+        <v>3412.2</v>
       </c>
       <c r="J333" t="n">
-        <v>178.78</v>
+        <v>3396.86</v>
       </c>
       <c r="K333" t="n">
-        <v>5.61</v>
+        <v>15.34</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -36903,7 +36903,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>7.59</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="334">
@@ -36914,39 +36914,39 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>HYUNDAI (AUG-2026 FUT)</t>
+          <t>LT (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>2227</v>
+        <v>4093</v>
       </c>
       <c r="D334" t="n">
-        <v>2193.81</v>
+        <v>4181.99</v>
       </c>
       <c r="E334" t="n">
-        <v>33.19</v>
+        <v>-88.98999999999999</v>
       </c>
       <c r="F334" t="n">
-        <v>2233.7</v>
+        <v>4100</v>
       </c>
       <c r="G334" t="n">
-        <v>2250.9</v>
+        <v>4130.76</v>
       </c>
       <c r="H334" t="n">
-        <v>-17.2</v>
+        <v>-30.76</v>
       </c>
       <c r="I334" t="n">
-        <v>2180.4</v>
+        <v>4061.4</v>
       </c>
       <c r="J334" t="n">
-        <v>2169.52</v>
+        <v>4090.04</v>
       </c>
       <c r="K334" t="n">
-        <v>10.88</v>
+        <v>-28.64</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -36955,7 +36955,7 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="335">
@@ -36966,39 +36966,39 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>CONCOR (AUG-2026 FUT)</t>
+          <t>PRESTIGE (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>519</v>
+        <v>1631</v>
       </c>
       <c r="D335" t="n">
-        <v>491.48</v>
+        <v>1649.4</v>
       </c>
       <c r="E335" t="n">
-        <v>27.52</v>
+        <v>-18.4</v>
       </c>
       <c r="F335" t="n">
-        <v>524.4</v>
+        <v>1651.3</v>
       </c>
       <c r="G335" t="n">
-        <v>523.5599999999999</v>
+        <v>1677.22</v>
       </c>
       <c r="H335" t="n">
-        <v>0.84</v>
+        <v>-25.92</v>
       </c>
       <c r="I335" t="n">
-        <v>513.8</v>
+        <v>1590</v>
       </c>
       <c r="J335" t="n">
-        <v>502.82</v>
+        <v>1606.04</v>
       </c>
       <c r="K335" t="n">
-        <v>10.98</v>
+        <v>-16.04</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -37007,7 +37007,7 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>5.6</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="336">
@@ -37018,35 +37018,35 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MAZDOCK (AUG-2026 FUT)</t>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>2570</v>
+        <v>173</v>
       </c>
       <c r="D336" t="n">
-        <v>2656.3</v>
+        <v>180.37</v>
       </c>
       <c r="E336" t="n">
-        <v>-86.3</v>
+        <v>-7.37</v>
       </c>
       <c r="F336" t="n">
-        <v>2583.2</v>
+        <v>173.69</v>
       </c>
       <c r="G336" t="n">
-        <v>2601.63</v>
+        <v>177.74</v>
       </c>
       <c r="H336" t="n">
-        <v>-18.43</v>
+        <v>-4.05</v>
       </c>
       <c r="I336" t="n">
-        <v>2552</v>
+        <v>172.3</v>
       </c>
       <c r="J336" t="n">
-        <v>2485.69</v>
+        <v>170.48</v>
       </c>
       <c r="K336" t="n">
-        <v>66.31</v>
+        <v>1.82</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="337">
@@ -37070,35 +37070,35 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DIXON (AUG-2026 FUT)</t>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>14850</v>
+        <v>183.45</v>
       </c>
       <c r="D337" t="n">
-        <v>14734.66</v>
+        <v>179.31</v>
       </c>
       <c r="E337" t="n">
-        <v>115.34</v>
+        <v>4.14</v>
       </c>
       <c r="F337" t="n">
-        <v>14953</v>
+        <v>185.3</v>
       </c>
       <c r="G337" t="n">
-        <v>15098.35</v>
+        <v>187.85</v>
       </c>
       <c r="H337" t="n">
-        <v>-145.35</v>
+        <v>-2.55</v>
       </c>
       <c r="I337" t="n">
-        <v>14470</v>
+        <v>182.5</v>
       </c>
       <c r="J337" t="n">
-        <v>14494.75</v>
+        <v>181.26</v>
       </c>
       <c r="K337" t="n">
-        <v>-24.75</v>
+        <v>1.24</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>0.78</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="338">
@@ -37122,35 +37122,35 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>NAUKRI (AUG-2026 FUT)</t>
+          <t>CONCOR (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1360.9</v>
+        <v>515.05</v>
       </c>
       <c r="D338" t="n">
-        <v>1432.09</v>
+        <v>572.62</v>
       </c>
       <c r="E338" t="n">
-        <v>-71.19</v>
+        <v>-57.57</v>
       </c>
       <c r="F338" t="n">
-        <v>1390.1</v>
+        <v>523</v>
       </c>
       <c r="G338" t="n">
-        <v>1383.61</v>
+        <v>526.22</v>
       </c>
       <c r="H338" t="n">
-        <v>6.49</v>
+        <v>-3.22</v>
       </c>
       <c r="I338" t="n">
-        <v>1355.3</v>
+        <v>512.15</v>
       </c>
       <c r="J338" t="n">
-        <v>1309.54</v>
+        <v>509.79</v>
       </c>
       <c r="K338" t="n">
-        <v>45.76</v>
+        <v>2.36</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>4.97</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="339">
@@ -37174,35 +37174,35 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>360ONE (AUG-2026 FUT)</t>
+          <t>DIXON (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>1203</v>
+        <v>14850</v>
       </c>
       <c r="D339" t="n">
-        <v>1235.01</v>
+        <v>15763.9</v>
       </c>
       <c r="E339" t="n">
-        <v>-32.01</v>
+        <v>-913.9</v>
       </c>
       <c r="F339" t="n">
-        <v>1222.9</v>
+        <v>14924</v>
       </c>
       <c r="G339" t="n">
-        <v>1221.54</v>
+        <v>15175.15</v>
       </c>
       <c r="H339" t="n">
-        <v>1.36</v>
+        <v>-251.15</v>
       </c>
       <c r="I339" t="n">
-        <v>1186</v>
+        <v>14620</v>
       </c>
       <c r="J339" t="n">
-        <v>1168.43</v>
+        <v>14695.72</v>
       </c>
       <c r="K339" t="n">
-        <v>17.57</v>
+        <v>-75.72</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -37211,11 +37211,11 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>2.59</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="340">
@@ -37226,35 +37226,35 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>INDIANB (AUG-2026 FUT)</t>
+          <t>MAZDOCK (AUG-2026 FUT)</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>871</v>
+        <v>2552</v>
       </c>
       <c r="D340" t="n">
-        <v>902.0700000000001</v>
+        <v>2615.19</v>
       </c>
       <c r="E340" t="n">
-        <v>-31.07</v>
+        <v>-63.19</v>
       </c>
       <c r="F340" t="n">
-        <v>883.8</v>
+        <v>2596</v>
       </c>
       <c r="G340" t="n">
-        <v>889.71</v>
+        <v>2614.86</v>
       </c>
       <c r="H340" t="n">
-        <v>-5.91</v>
+        <v>-18.86</v>
       </c>
       <c r="I340" t="n">
-        <v>871</v>
+        <v>2542</v>
       </c>
       <c r="J340" t="n">
-        <v>857.3200000000001</v>
+        <v>2520.15</v>
       </c>
       <c r="K340" t="n">
-        <v>13.68</v>
+        <v>21.85</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -37263,11 +37263,11 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N340" t="n">
-        <v>3.44</v>
+        <v>2.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N340"/>
+  <dimension ref="A1:N368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18116,6 +18116,1462 @@
       </c>
       <c r="N340" t="n">
         <v>8.08</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>689</v>
+      </c>
+      <c r="D341" t="n">
+        <v>698.03</v>
+      </c>
+      <c r="E341" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="F341" t="n">
+        <v>689</v>
+      </c>
+      <c r="G341" t="n">
+        <v>698.03</v>
+      </c>
+      <c r="H341" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="I341" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="J341" t="n">
+        <v>668.46</v>
+      </c>
+      <c r="K341" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="D342" t="n">
+        <v>293.6</v>
+      </c>
+      <c r="E342" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F342" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="G342" t="n">
+        <v>298.16</v>
+      </c>
+      <c r="H342" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="I342" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="J342" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2081.17</v>
+      </c>
+      <c r="E343" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="F343" t="n">
+        <v>2172.8</v>
+      </c>
+      <c r="G343" t="n">
+        <v>2123.58</v>
+      </c>
+      <c r="H343" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="I343" t="n">
+        <v>2131.8</v>
+      </c>
+      <c r="J343" t="n">
+        <v>2087.5</v>
+      </c>
+      <c r="K343" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>3414.1</v>
+      </c>
+      <c r="D344" t="n">
+        <v>3221.33</v>
+      </c>
+      <c r="E344" t="n">
+        <v>192.77</v>
+      </c>
+      <c r="F344" t="n">
+        <v>3444.7</v>
+      </c>
+      <c r="G344" t="n">
+        <v>3418.31</v>
+      </c>
+      <c r="H344" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="I344" t="n">
+        <v>3400</v>
+      </c>
+      <c r="J344" t="n">
+        <v>3344.52</v>
+      </c>
+      <c r="K344" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="D345" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="E345" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F345" t="n">
+        <v>117.03</v>
+      </c>
+      <c r="G345" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="H345" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I345" t="n">
+        <v>115</v>
+      </c>
+      <c r="J345" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="K345" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>5694</v>
+      </c>
+      <c r="D346" t="n">
+        <v>5562.14</v>
+      </c>
+      <c r="E346" t="n">
+        <v>131.86</v>
+      </c>
+      <c r="F346" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G346" t="n">
+        <v>5562.14</v>
+      </c>
+      <c r="H346" t="n">
+        <v>162.86</v>
+      </c>
+      <c r="I346" t="n">
+        <v>5646</v>
+      </c>
+      <c r="J346" t="n">
+        <v>5533.49</v>
+      </c>
+      <c r="K346" t="n">
+        <v>112.51</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>2001.7</v>
+      </c>
+      <c r="D347" t="n">
+        <v>2040.35</v>
+      </c>
+      <c r="E347" t="n">
+        <v>-38.65</v>
+      </c>
+      <c r="F347" t="n">
+        <v>2028.6</v>
+      </c>
+      <c r="G347" t="n">
+        <v>2040.35</v>
+      </c>
+      <c r="H347" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="I347" t="n">
+        <v>1995.3</v>
+      </c>
+      <c r="J347" t="n">
+        <v>1960.26</v>
+      </c>
+      <c r="K347" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>11120</v>
+      </c>
+      <c r="D348" t="n">
+        <v>11031.75</v>
+      </c>
+      <c r="E348" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="F348" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G348" t="n">
+        <v>11152.7</v>
+      </c>
+      <c r="H348" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="I348" t="n">
+        <v>11050</v>
+      </c>
+      <c r="J348" t="n">
+        <v>10895.68</v>
+      </c>
+      <c r="K348" t="n">
+        <v>154.32</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="D349" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="E349" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="F349" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="G349" t="n">
+        <v>330.12</v>
+      </c>
+      <c r="H349" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I349" t="n">
+        <v>323</v>
+      </c>
+      <c r="J349" t="n">
+        <v>322.58</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>3268</v>
+      </c>
+      <c r="D350" t="n">
+        <v>3334.11</v>
+      </c>
+      <c r="E350" t="n">
+        <v>-66.11</v>
+      </c>
+      <c r="F350" t="n">
+        <v>3289.7</v>
+      </c>
+      <c r="G350" t="n">
+        <v>3334.11</v>
+      </c>
+      <c r="H350" t="n">
+        <v>-44.41</v>
+      </c>
+      <c r="I350" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J350" t="n">
+        <v>3257.4</v>
+      </c>
+      <c r="K350" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>477</v>
+      </c>
+      <c r="D351" t="n">
+        <v>474.36</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F351" t="n">
+        <v>479.25</v>
+      </c>
+      <c r="G351" t="n">
+        <v>483.15</v>
+      </c>
+      <c r="H351" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="I351" t="n">
+        <v>472</v>
+      </c>
+      <c r="J351" t="n">
+        <v>472.18</v>
+      </c>
+      <c r="K351" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>173.29</v>
+      </c>
+      <c r="D352" t="n">
+        <v>172.21</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F352" t="n">
+        <v>173.66</v>
+      </c>
+      <c r="G352" t="n">
+        <v>174.16</v>
+      </c>
+      <c r="H352" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I352" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="J352" t="n">
+        <v>170.16</v>
+      </c>
+      <c r="K352" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1050.1</v>
+      </c>
+      <c r="E353" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="G353" t="n">
+        <v>1067.24</v>
+      </c>
+      <c r="H353" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="I353" t="n">
+        <v>1043.3</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1042.84</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="D354" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="E354" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F354" t="n">
+        <v>405</v>
+      </c>
+      <c r="G354" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="H354" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="I354" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="J354" t="n">
+        <v>396.64</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N354" t="n">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>1251.3</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1241.37</v>
+      </c>
+      <c r="E355" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F355" t="n">
+        <v>1261.6</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1249.06</v>
+      </c>
+      <c r="H355" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="I355" t="n">
+        <v>1245.1</v>
+      </c>
+      <c r="J355" t="n">
+        <v>1220.08</v>
+      </c>
+      <c r="K355" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N355" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>5685</v>
+      </c>
+      <c r="D356" t="n">
+        <v>5639.88</v>
+      </c>
+      <c r="E356" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F356" t="n">
+        <v>5728</v>
+      </c>
+      <c r="G356" t="n">
+        <v>5639.88</v>
+      </c>
+      <c r="H356" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="I356" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J356" t="n">
+        <v>5521.63</v>
+      </c>
+      <c r="K356" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D357" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="E357" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="F357" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="G357" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="H357" t="n">
+        <v>-9.24</v>
+      </c>
+      <c r="I357" t="n">
+        <v>182.02</v>
+      </c>
+      <c r="J357" t="n">
+        <v>179.91</v>
+      </c>
+      <c r="K357" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1635.8</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1677.53</v>
+      </c>
+      <c r="E358" t="n">
+        <v>-41.73</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1641.6</v>
+      </c>
+      <c r="G358" t="n">
+        <v>1677.53</v>
+      </c>
+      <c r="H358" t="n">
+        <v>-35.93</v>
+      </c>
+      <c r="I358" t="n">
+        <v>1618.1</v>
+      </c>
+      <c r="J358" t="n">
+        <v>1577.23</v>
+      </c>
+      <c r="K358" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1785</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1770.83</v>
+      </c>
+      <c r="E359" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F359" t="n">
+        <v>1811.8</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1770.83</v>
+      </c>
+      <c r="H359" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="I359" t="n">
+        <v>1773.5</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1728.56</v>
+      </c>
+      <c r="K359" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1903.99</v>
+      </c>
+      <c r="E360" t="n">
+        <v>-30.99</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="G360" t="n">
+        <v>1903.99</v>
+      </c>
+      <c r="H360" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="I360" t="n">
+        <v>1869.6</v>
+      </c>
+      <c r="J360" t="n">
+        <v>1820.59</v>
+      </c>
+      <c r="K360" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>4090</v>
+      </c>
+      <c r="D361" t="n">
+        <v>4071.14</v>
+      </c>
+      <c r="E361" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="F361" t="n">
+        <v>4107.1</v>
+      </c>
+      <c r="G361" t="n">
+        <v>4113.19</v>
+      </c>
+      <c r="H361" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="I361" t="n">
+        <v>4077.7</v>
+      </c>
+      <c r="J361" t="n">
+        <v>4035.27</v>
+      </c>
+      <c r="K361" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>990</v>
+      </c>
+      <c r="D362" t="n">
+        <v>982.14</v>
+      </c>
+      <c r="E362" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="F362" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G362" t="n">
+        <v>1002.82</v>
+      </c>
+      <c r="H362" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I362" t="n">
+        <v>988.3</v>
+      </c>
+      <c r="J362" t="n">
+        <v>980.05</v>
+      </c>
+      <c r="K362" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>2207</v>
+      </c>
+      <c r="D363" t="n">
+        <v>2189.74</v>
+      </c>
+      <c r="E363" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2235.4</v>
+      </c>
+      <c r="G363" t="n">
+        <v>2240.9</v>
+      </c>
+      <c r="H363" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="I363" t="n">
+        <v>2206.1</v>
+      </c>
+      <c r="J363" t="n">
+        <v>2190.22</v>
+      </c>
+      <c r="K363" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>516.4</v>
+      </c>
+      <c r="D364" t="n">
+        <v>478.47</v>
+      </c>
+      <c r="E364" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="F364" t="n">
+        <v>524.2</v>
+      </c>
+      <c r="G364" t="n">
+        <v>486.67</v>
+      </c>
+      <c r="H364" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="I364" t="n">
+        <v>513.05</v>
+      </c>
+      <c r="J364" t="n">
+        <v>501.38</v>
+      </c>
+      <c r="K364" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>7.93</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>2540</v>
+      </c>
+      <c r="D365" t="n">
+        <v>2560.88</v>
+      </c>
+      <c r="E365" t="n">
+        <v>-20.88</v>
+      </c>
+      <c r="F365" t="n">
+        <v>2572.6</v>
+      </c>
+      <c r="G365" t="n">
+        <v>2560.88</v>
+      </c>
+      <c r="H365" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="I365" t="n">
+        <v>2523.4</v>
+      </c>
+      <c r="J365" t="n">
+        <v>2457.21</v>
+      </c>
+      <c r="K365" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1349</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1338.29</v>
+      </c>
+      <c r="E366" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="F366" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G366" t="n">
+        <v>1338.29</v>
+      </c>
+      <c r="H366" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="I366" t="n">
+        <v>1336.7</v>
+      </c>
+      <c r="J366" t="n">
+        <v>1301.3</v>
+      </c>
+      <c r="K366" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N366" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>14570</v>
+      </c>
+      <c r="D367" t="n">
+        <v>14173.87</v>
+      </c>
+      <c r="E367" t="n">
+        <v>396.13</v>
+      </c>
+      <c r="F367" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G367" t="n">
+        <v>14825.24</v>
+      </c>
+      <c r="H367" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="I367" t="n">
+        <v>14484</v>
+      </c>
+      <c r="J367" t="n">
+        <v>14490.99</v>
+      </c>
+      <c r="K367" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N367" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>870.45</v>
+      </c>
+      <c r="D368" t="n">
+        <v>863.54</v>
+      </c>
+      <c r="E368" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="F368" t="n">
+        <v>883.85</v>
+      </c>
+      <c r="G368" t="n">
+        <v>863.9</v>
+      </c>
+      <c r="H368" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="I368" t="n">
+        <v>862</v>
+      </c>
+      <c r="J368" t="n">
+        <v>847.41</v>
+      </c>
+      <c r="K368" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N368" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -18129,7 +19585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19553,6 +21009,110 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24313</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24306.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>24144.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>24137.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="D29" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>57873.75</v>
+      </c>
+      <c r="G29" t="n">
+        <v>57851.15</v>
+      </c>
+      <c r="H29" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>57245.95</v>
+      </c>
+      <c r="J29" t="n">
+        <v>57223.35</v>
+      </c>
+      <c r="K29" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19567,7 +21127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N340"/>
+  <dimension ref="A1:N368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37270,6 +38830,1462 @@
         <v>2.42</v>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D341" t="n">
+        <v>2121.71</v>
+      </c>
+      <c r="E341" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F341" t="n">
+        <v>2172.8</v>
+      </c>
+      <c r="G341" t="n">
+        <v>2174.62</v>
+      </c>
+      <c r="H341" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="I341" t="n">
+        <v>2131.8</v>
+      </c>
+      <c r="J341" t="n">
+        <v>2102.44</v>
+      </c>
+      <c r="K341" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>3414.1</v>
+      </c>
+      <c r="D342" t="n">
+        <v>3262.68</v>
+      </c>
+      <c r="E342" t="n">
+        <v>151.42</v>
+      </c>
+      <c r="F342" t="n">
+        <v>3444.7</v>
+      </c>
+      <c r="G342" t="n">
+        <v>3439.56</v>
+      </c>
+      <c r="H342" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I342" t="n">
+        <v>3400</v>
+      </c>
+      <c r="J342" t="n">
+        <v>3362.82</v>
+      </c>
+      <c r="K342" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>DLF (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>689</v>
+      </c>
+      <c r="D343" t="n">
+        <v>713.8</v>
+      </c>
+      <c r="E343" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="F343" t="n">
+        <v>689</v>
+      </c>
+      <c r="G343" t="n">
+        <v>700.5599999999999</v>
+      </c>
+      <c r="H343" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="I343" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="J343" t="n">
+        <v>673.78</v>
+      </c>
+      <c r="K343" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>OIL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>477</v>
+      </c>
+      <c r="D344" t="n">
+        <v>487.29</v>
+      </c>
+      <c r="E344" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="F344" t="n">
+        <v>479.25</v>
+      </c>
+      <c r="G344" t="n">
+        <v>487.14</v>
+      </c>
+      <c r="H344" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="I344" t="n">
+        <v>472</v>
+      </c>
+      <c r="J344" t="n">
+        <v>464.85</v>
+      </c>
+      <c r="K344" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="D345" t="n">
+        <v>299.07</v>
+      </c>
+      <c r="E345" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="F345" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="G345" t="n">
+        <v>299.79</v>
+      </c>
+      <c r="H345" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="I345" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="J345" t="n">
+        <v>290.26</v>
+      </c>
+      <c r="K345" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="D346" t="n">
+        <v>121.77</v>
+      </c>
+      <c r="E346" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="F346" t="n">
+        <v>117.03</v>
+      </c>
+      <c r="G346" t="n">
+        <v>117.01</v>
+      </c>
+      <c r="H346" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I346" t="n">
+        <v>115</v>
+      </c>
+      <c r="J346" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="K346" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>5694</v>
+      </c>
+      <c r="D347" t="n">
+        <v>5678.44</v>
+      </c>
+      <c r="E347" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="F347" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G347" t="n">
+        <v>5780.4</v>
+      </c>
+      <c r="H347" t="n">
+        <v>-55.4</v>
+      </c>
+      <c r="I347" t="n">
+        <v>5646</v>
+      </c>
+      <c r="J347" t="n">
+        <v>5575.15</v>
+      </c>
+      <c r="K347" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="D348" t="n">
+        <v>468.64</v>
+      </c>
+      <c r="E348" t="n">
+        <v>-65.34</v>
+      </c>
+      <c r="F348" t="n">
+        <v>405</v>
+      </c>
+      <c r="G348" t="n">
+        <v>414.41</v>
+      </c>
+      <c r="H348" t="n">
+        <v>-9.41</v>
+      </c>
+      <c r="I348" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="J348" t="n">
+        <v>391.09</v>
+      </c>
+      <c r="K348" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>MCX (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>3268</v>
+      </c>
+      <c r="D349" t="n">
+        <v>3429.43</v>
+      </c>
+      <c r="E349" t="n">
+        <v>-161.43</v>
+      </c>
+      <c r="F349" t="n">
+        <v>3289.7</v>
+      </c>
+      <c r="G349" t="n">
+        <v>3355.87</v>
+      </c>
+      <c r="H349" t="n">
+        <v>-66.17</v>
+      </c>
+      <c r="I349" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J349" t="n">
+        <v>3170.74</v>
+      </c>
+      <c r="K349" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D350" t="n">
+        <v>198.44</v>
+      </c>
+      <c r="E350" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="F350" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="G350" t="n">
+        <v>186.78</v>
+      </c>
+      <c r="H350" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="I350" t="n">
+        <v>182.02</v>
+      </c>
+      <c r="J350" t="n">
+        <v>179.46</v>
+      </c>
+      <c r="K350" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>173.29</v>
+      </c>
+      <c r="D351" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="E351" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="F351" t="n">
+        <v>173.66</v>
+      </c>
+      <c r="G351" t="n">
+        <v>176.39</v>
+      </c>
+      <c r="H351" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="I351" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="J351" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="K351" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="D352" t="n">
+        <v>1076.15</v>
+      </c>
+      <c r="E352" t="n">
+        <v>-17.65</v>
+      </c>
+      <c r="F352" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="G352" t="n">
+        <v>1078.51</v>
+      </c>
+      <c r="H352" t="n">
+        <v>-20.01</v>
+      </c>
+      <c r="I352" t="n">
+        <v>1043.3</v>
+      </c>
+      <c r="J352" t="n">
+        <v>1033.42</v>
+      </c>
+      <c r="K352" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1251.3</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1268.07</v>
+      </c>
+      <c r="E353" t="n">
+        <v>-16.77</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1261.6</v>
+      </c>
+      <c r="G353" t="n">
+        <v>1271.01</v>
+      </c>
+      <c r="H353" t="n">
+        <v>-9.41</v>
+      </c>
+      <c r="I353" t="n">
+        <v>1245.1</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1224.65</v>
+      </c>
+      <c r="K353" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="D354" t="n">
+        <v>311.5</v>
+      </c>
+      <c r="E354" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="F354" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="G354" t="n">
+        <v>331.41</v>
+      </c>
+      <c r="H354" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I354" t="n">
+        <v>323</v>
+      </c>
+      <c r="J354" t="n">
+        <v>320.87</v>
+      </c>
+      <c r="K354" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N354" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>5685</v>
+      </c>
+      <c r="D355" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="E355" t="n">
+        <v>-76.02</v>
+      </c>
+      <c r="F355" t="n">
+        <v>5728</v>
+      </c>
+      <c r="G355" t="n">
+        <v>5774.36</v>
+      </c>
+      <c r="H355" t="n">
+        <v>-46.36</v>
+      </c>
+      <c r="I355" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J355" t="n">
+        <v>5564</v>
+      </c>
+      <c r="K355" t="n">
+        <v>86</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N355" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>2001.7</v>
+      </c>
+      <c r="D356" t="n">
+        <v>2070.03</v>
+      </c>
+      <c r="E356" t="n">
+        <v>-68.33</v>
+      </c>
+      <c r="F356" t="n">
+        <v>2028.6</v>
+      </c>
+      <c r="G356" t="n">
+        <v>2019.9</v>
+      </c>
+      <c r="H356" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I356" t="n">
+        <v>1995.3</v>
+      </c>
+      <c r="J356" t="n">
+        <v>1969.17</v>
+      </c>
+      <c r="K356" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>PRESTIGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>1635.8</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1725.82</v>
+      </c>
+      <c r="E357" t="n">
+        <v>-90.02</v>
+      </c>
+      <c r="F357" t="n">
+        <v>1641.6</v>
+      </c>
+      <c r="G357" t="n">
+        <v>1672.94</v>
+      </c>
+      <c r="H357" t="n">
+        <v>-31.34</v>
+      </c>
+      <c r="I357" t="n">
+        <v>1618.1</v>
+      </c>
+      <c r="J357" t="n">
+        <v>1592.31</v>
+      </c>
+      <c r="K357" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>11120</v>
+      </c>
+      <c r="D358" t="n">
+        <v>11182.72</v>
+      </c>
+      <c r="E358" t="n">
+        <v>-62.72</v>
+      </c>
+      <c r="F358" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G358" t="n">
+        <v>11211.97</v>
+      </c>
+      <c r="H358" t="n">
+        <v>148.03</v>
+      </c>
+      <c r="I358" t="n">
+        <v>11050</v>
+      </c>
+      <c r="J358" t="n">
+        <v>10946.16</v>
+      </c>
+      <c r="K358" t="n">
+        <v>103.84</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>POLICYBZR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1785</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1822.47</v>
+      </c>
+      <c r="E359" t="n">
+        <v>-37.47</v>
+      </c>
+      <c r="F359" t="n">
+        <v>1811.8</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1826.16</v>
+      </c>
+      <c r="H359" t="n">
+        <v>-14.36</v>
+      </c>
+      <c r="I359" t="n">
+        <v>1773.5</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1737.07</v>
+      </c>
+      <c r="K359" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>516.4</v>
+      </c>
+      <c r="D360" t="n">
+        <v>488.91</v>
+      </c>
+      <c r="E360" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="F360" t="n">
+        <v>524.2</v>
+      </c>
+      <c r="G360" t="n">
+        <v>524.6900000000001</v>
+      </c>
+      <c r="H360" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="I360" t="n">
+        <v>513.05</v>
+      </c>
+      <c r="J360" t="n">
+        <v>505.27</v>
+      </c>
+      <c r="K360" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>4090</v>
+      </c>
+      <c r="D361" t="n">
+        <v>4102.28</v>
+      </c>
+      <c r="E361" t="n">
+        <v>-12.28</v>
+      </c>
+      <c r="F361" t="n">
+        <v>4107.1</v>
+      </c>
+      <c r="G361" t="n">
+        <v>4100.23</v>
+      </c>
+      <c r="H361" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="I361" t="n">
+        <v>4077.7</v>
+      </c>
+      <c r="J361" t="n">
+        <v>4043.97</v>
+      </c>
+      <c r="K361" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>990</v>
+      </c>
+      <c r="D362" t="n">
+        <v>1008.22</v>
+      </c>
+      <c r="E362" t="n">
+        <v>-18.22</v>
+      </c>
+      <c r="F362" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G362" t="n">
+        <v>1010.37</v>
+      </c>
+      <c r="H362" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="I362" t="n">
+        <v>988.3</v>
+      </c>
+      <c r="J362" t="n">
+        <v>965.28</v>
+      </c>
+      <c r="K362" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>2207</v>
+      </c>
+      <c r="D363" t="n">
+        <v>2230.21</v>
+      </c>
+      <c r="E363" t="n">
+        <v>-23.21</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2235.4</v>
+      </c>
+      <c r="G363" t="n">
+        <v>2235.63</v>
+      </c>
+      <c r="H363" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I363" t="n">
+        <v>2206.1</v>
+      </c>
+      <c r="J363" t="n">
+        <v>2164.63</v>
+      </c>
+      <c r="K363" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D364" t="n">
+        <v>1943.39</v>
+      </c>
+      <c r="E364" t="n">
+        <v>-70.39</v>
+      </c>
+      <c r="F364" t="n">
+        <v>1900.8</v>
+      </c>
+      <c r="G364" t="n">
+        <v>1901.03</v>
+      </c>
+      <c r="H364" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I364" t="n">
+        <v>1869.6</v>
+      </c>
+      <c r="J364" t="n">
+        <v>1834.21</v>
+      </c>
+      <c r="K364" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>MAZDOCK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>2540</v>
+      </c>
+      <c r="D365" t="n">
+        <v>2626.09</v>
+      </c>
+      <c r="E365" t="n">
+        <v>-86.09</v>
+      </c>
+      <c r="F365" t="n">
+        <v>2572.6</v>
+      </c>
+      <c r="G365" t="n">
+        <v>2589.6</v>
+      </c>
+      <c r="H365" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I365" t="n">
+        <v>2523.4</v>
+      </c>
+      <c r="J365" t="n">
+        <v>2478.6</v>
+      </c>
+      <c r="K365" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1349</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1377.16</v>
+      </c>
+      <c r="E366" t="n">
+        <v>-28.16</v>
+      </c>
+      <c r="F366" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G366" t="n">
+        <v>1379.96</v>
+      </c>
+      <c r="H366" t="n">
+        <v>-19.96</v>
+      </c>
+      <c r="I366" t="n">
+        <v>1336.7</v>
+      </c>
+      <c r="J366" t="n">
+        <v>1312.88</v>
+      </c>
+      <c r="K366" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N366" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>14570</v>
+      </c>
+      <c r="D367" t="n">
+        <v>14441.11</v>
+      </c>
+      <c r="E367" t="n">
+        <v>128.89</v>
+      </c>
+      <c r="F367" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G367" t="n">
+        <v>14794.91</v>
+      </c>
+      <c r="H367" t="n">
+        <v>205.09</v>
+      </c>
+      <c r="I367" t="n">
+        <v>14484</v>
+      </c>
+      <c r="J367" t="n">
+        <v>14263</v>
+      </c>
+      <c r="K367" t="n">
+        <v>221</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N367" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>870.45</v>
+      </c>
+      <c r="D368" t="n">
+        <v>880.0599999999999</v>
+      </c>
+      <c r="E368" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="F368" t="n">
+        <v>883.85</v>
+      </c>
+      <c r="G368" t="n">
+        <v>882.1799999999999</v>
+      </c>
+      <c r="H368" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I368" t="n">
+        <v>862</v>
+      </c>
+      <c r="J368" t="n">
+        <v>853.4</v>
+      </c>
+      <c r="K368" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N368" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -18130,31 +18130,31 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>689</v>
+        <v>678.1</v>
       </c>
       <c r="D341" t="n">
         <v>698.03</v>
       </c>
       <c r="E341" t="n">
-        <v>-9.029999999999999</v>
+        <v>-19.93</v>
       </c>
       <c r="F341" t="n">
-        <v>689</v>
+        <v>684.45</v>
       </c>
       <c r="G341" t="n">
         <v>698.03</v>
       </c>
       <c r="H341" t="n">
-        <v>-9.029999999999999</v>
+        <v>-13.58</v>
       </c>
       <c r="I341" t="n">
-        <v>678.1</v>
+        <v>675.25</v>
       </c>
       <c r="J341" t="n">
         <v>668.46</v>
       </c>
       <c r="K341" t="n">
-        <v>9.640000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="342">
@@ -18182,31 +18182,31 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>295.95</v>
+        <v>293</v>
       </c>
       <c r="D342" t="n">
         <v>293.6</v>
       </c>
       <c r="E342" t="n">
-        <v>2.35</v>
+        <v>-0.6</v>
       </c>
       <c r="F342" t="n">
-        <v>296.8</v>
+        <v>293.5</v>
       </c>
       <c r="G342" t="n">
         <v>298.16</v>
       </c>
       <c r="H342" t="n">
-        <v>-1.36</v>
+        <v>-4.66</v>
       </c>
       <c r="I342" t="n">
-        <v>291.4</v>
+        <v>289.75</v>
       </c>
       <c r="J342" t="n">
         <v>291.34</v>
       </c>
       <c r="K342" t="n">
-        <v>0.06</v>
+        <v>-1.59</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="343">
@@ -18234,31 +18234,31 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>2145</v>
+        <v>2139</v>
       </c>
       <c r="D343" t="n">
         <v>2081.17</v>
       </c>
       <c r="E343" t="n">
-        <v>63.83</v>
+        <v>57.83</v>
       </c>
       <c r="F343" t="n">
-        <v>2172.8</v>
+        <v>2162.2</v>
       </c>
       <c r="G343" t="n">
         <v>2123.58</v>
       </c>
       <c r="H343" t="n">
-        <v>49.22</v>
+        <v>38.62</v>
       </c>
       <c r="I343" t="n">
-        <v>2131.8</v>
+        <v>2126.3</v>
       </c>
       <c r="J343" t="n">
         <v>2087.5</v>
       </c>
       <c r="K343" t="n">
-        <v>44.3</v>
+        <v>38.8</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="344">
@@ -18286,31 +18286,31 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3414.1</v>
+        <v>3412.2</v>
       </c>
       <c r="D344" t="n">
         <v>3221.33</v>
       </c>
       <c r="E344" t="n">
-        <v>192.77</v>
+        <v>190.87</v>
       </c>
       <c r="F344" t="n">
-        <v>3444.7</v>
+        <v>3453.9</v>
       </c>
       <c r="G344" t="n">
         <v>3418.31</v>
       </c>
       <c r="H344" t="n">
-        <v>26.39</v>
+        <v>35.59</v>
       </c>
       <c r="I344" t="n">
-        <v>3400</v>
+        <v>3412.2</v>
       </c>
       <c r="J344" t="n">
         <v>3344.52</v>
       </c>
       <c r="K344" t="n">
-        <v>55.48</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="345">
@@ -18338,31 +18338,31 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>115.86</v>
+        <v>116.55</v>
       </c>
       <c r="D345" t="n">
         <v>119.93</v>
       </c>
       <c r="E345" t="n">
-        <v>-4.07</v>
+        <v>-3.38</v>
       </c>
       <c r="F345" t="n">
-        <v>117.03</v>
+        <v>117.52</v>
       </c>
       <c r="G345" t="n">
         <v>119.93</v>
       </c>
       <c r="H345" t="n">
-        <v>-2.9</v>
+        <v>-2.41</v>
       </c>
       <c r="I345" t="n">
-        <v>115</v>
+        <v>115.41</v>
       </c>
       <c r="J345" t="n">
         <v>113.72</v>
       </c>
       <c r="K345" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>3.39</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="346">
@@ -18390,31 +18390,31 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>5694</v>
+        <v>5667.5</v>
       </c>
       <c r="D346" t="n">
         <v>5562.14</v>
       </c>
       <c r="E346" t="n">
-        <v>131.86</v>
+        <v>105.36</v>
       </c>
       <c r="F346" t="n">
-        <v>5725</v>
+        <v>5722</v>
       </c>
       <c r="G346" t="n">
         <v>5562.14</v>
       </c>
       <c r="H346" t="n">
-        <v>162.86</v>
+        <v>159.86</v>
       </c>
       <c r="I346" t="n">
-        <v>5646</v>
+        <v>5602</v>
       </c>
       <c r="J346" t="n">
         <v>5533.49</v>
       </c>
       <c r="K346" t="n">
-        <v>112.51</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="347">
@@ -18442,31 +18442,31 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2001.7</v>
+        <v>2032.5</v>
       </c>
       <c r="D347" t="n">
         <v>2040.35</v>
       </c>
       <c r="E347" t="n">
-        <v>-38.65</v>
+        <v>-7.85</v>
       </c>
       <c r="F347" t="n">
-        <v>2028.6</v>
+        <v>2032.5</v>
       </c>
       <c r="G347" t="n">
         <v>2040.35</v>
       </c>
       <c r="H347" t="n">
-        <v>-11.75</v>
+        <v>-7.85</v>
       </c>
       <c r="I347" t="n">
-        <v>1995.3</v>
+        <v>2005</v>
       </c>
       <c r="J347" t="n">
         <v>1960.26</v>
       </c>
       <c r="K347" t="n">
-        <v>35.04</v>
+        <v>44.74</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>1.89</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="348">
@@ -18494,31 +18494,31 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>11120</v>
+        <v>11320</v>
       </c>
       <c r="D348" t="n">
         <v>11031.75</v>
       </c>
       <c r="E348" t="n">
-        <v>88.25</v>
+        <v>288.25</v>
       </c>
       <c r="F348" t="n">
-        <v>11360</v>
+        <v>11410</v>
       </c>
       <c r="G348" t="n">
         <v>11152.7</v>
       </c>
       <c r="H348" t="n">
-        <v>207.3</v>
+        <v>257.3</v>
       </c>
       <c r="I348" t="n">
-        <v>11050</v>
+        <v>11280</v>
       </c>
       <c r="J348" t="n">
         <v>10895.68</v>
       </c>
       <c r="K348" t="n">
-        <v>154.32</v>
+        <v>384.32</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>0.8</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="349">
@@ -18546,31 +18546,31 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>327.15</v>
+        <v>328</v>
       </c>
       <c r="D349" t="n">
         <v>305.81</v>
       </c>
       <c r="E349" t="n">
-        <v>21.34</v>
+        <v>22.19</v>
       </c>
       <c r="F349" t="n">
-        <v>329.5</v>
+        <v>331.7</v>
       </c>
       <c r="G349" t="n">
         <v>330.12</v>
       </c>
       <c r="H349" t="n">
-        <v>-0.62</v>
+        <v>1.58</v>
       </c>
       <c r="I349" t="n">
-        <v>323</v>
+        <v>324.1</v>
       </c>
       <c r="J349" t="n">
         <v>322.58</v>
       </c>
       <c r="K349" t="n">
-        <v>0.42</v>
+        <v>1.52</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>6.98</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="350">
@@ -18598,31 +18598,31 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3268</v>
+        <v>3185</v>
       </c>
       <c r="D350" t="n">
         <v>3334.11</v>
       </c>
       <c r="E350" t="n">
-        <v>-66.11</v>
+        <v>-149.11</v>
       </c>
       <c r="F350" t="n">
-        <v>3289.7</v>
+        <v>3211.4</v>
       </c>
       <c r="G350" t="n">
         <v>3334.11</v>
       </c>
       <c r="H350" t="n">
-        <v>-44.41</v>
+        <v>-122.71</v>
       </c>
       <c r="I350" t="n">
-        <v>3180.1</v>
+        <v>3132</v>
       </c>
       <c r="J350" t="n">
         <v>3257.4</v>
       </c>
       <c r="K350" t="n">
-        <v>-77.3</v>
+        <v>-125.4</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -18631,11 +18631,11 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N350" t="n">
-        <v>1.98</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="351">
@@ -18650,31 +18650,31 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D351" t="n">
         <v>474.36</v>
       </c>
       <c r="E351" t="n">
-        <v>2.64</v>
+        <v>0.64</v>
       </c>
       <c r="F351" t="n">
-        <v>479.25</v>
+        <v>482</v>
       </c>
       <c r="G351" t="n">
         <v>483.15</v>
       </c>
       <c r="H351" t="n">
-        <v>-3.9</v>
+        <v>-1.15</v>
       </c>
       <c r="I351" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="J351" t="n">
         <v>472.18</v>
       </c>
       <c r="K351" t="n">
-        <v>-0.18</v>
+        <v>2.82</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="352">
@@ -18702,31 +18702,31 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>173.29</v>
+        <v>173</v>
       </c>
       <c r="D352" t="n">
         <v>172.21</v>
       </c>
       <c r="E352" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="F352" t="n">
-        <v>173.66</v>
+        <v>173.69</v>
       </c>
       <c r="G352" t="n">
         <v>174.16</v>
       </c>
       <c r="H352" t="n">
-        <v>-0.5</v>
+        <v>-0.47</v>
       </c>
       <c r="I352" t="n">
-        <v>171.65</v>
+        <v>172.3</v>
       </c>
       <c r="J352" t="n">
         <v>170.16</v>
       </c>
       <c r="K352" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="353">
@@ -18754,31 +18754,31 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1058.5</v>
+        <v>1034</v>
       </c>
       <c r="D353" t="n">
         <v>1050.1</v>
       </c>
       <c r="E353" t="n">
-        <v>8.4</v>
+        <v>-16.1</v>
       </c>
       <c r="F353" t="n">
-        <v>1058.5</v>
+        <v>1040.45</v>
       </c>
       <c r="G353" t="n">
         <v>1067.24</v>
       </c>
       <c r="H353" t="n">
-        <v>-8.74</v>
+        <v>-26.79</v>
       </c>
       <c r="I353" t="n">
-        <v>1043.3</v>
+        <v>1024.6</v>
       </c>
       <c r="J353" t="n">
         <v>1042.84</v>
       </c>
       <c r="K353" t="n">
-        <v>0.46</v>
+        <v>-18.24</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>0.8</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="354">
@@ -18806,31 +18806,31 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>403.3</v>
+        <v>393.45</v>
       </c>
       <c r="D354" t="n">
         <v>453.3</v>
       </c>
       <c r="E354" t="n">
-        <v>-50</v>
+        <v>-59.85</v>
       </c>
       <c r="F354" t="n">
-        <v>405</v>
+        <v>396.49</v>
       </c>
       <c r="G354" t="n">
         <v>453.3</v>
       </c>
       <c r="H354" t="n">
-        <v>-48.3</v>
+        <v>-56.81</v>
       </c>
       <c r="I354" t="n">
-        <v>397.5</v>
+        <v>383.62</v>
       </c>
       <c r="J354" t="n">
         <v>396.64</v>
       </c>
       <c r="K354" t="n">
-        <v>0.86</v>
+        <v>-13.02</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -18839,11 +18839,11 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N354" t="n">
-        <v>11.03</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="355">
@@ -18858,31 +18858,31 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1251.3</v>
+        <v>1265</v>
       </c>
       <c r="D355" t="n">
         <v>1241.37</v>
       </c>
       <c r="E355" t="n">
-        <v>9.93</v>
+        <v>23.63</v>
       </c>
       <c r="F355" t="n">
-        <v>1261.6</v>
+        <v>1267</v>
       </c>
       <c r="G355" t="n">
         <v>1249.06</v>
       </c>
       <c r="H355" t="n">
-        <v>12.54</v>
+        <v>17.94</v>
       </c>
       <c r="I355" t="n">
-        <v>1245.1</v>
+        <v>1252</v>
       </c>
       <c r="J355" t="n">
         <v>1220.08</v>
       </c>
       <c r="K355" t="n">
-        <v>25.02</v>
+        <v>31.92</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="356">
@@ -18910,31 +18910,31 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>5685</v>
+        <v>5735</v>
       </c>
       <c r="D356" t="n">
         <v>5639.88</v>
       </c>
       <c r="E356" t="n">
-        <v>45.12</v>
+        <v>95.12</v>
       </c>
       <c r="F356" t="n">
-        <v>5728</v>
+        <v>5735</v>
       </c>
       <c r="G356" t="n">
         <v>5639.88</v>
       </c>
       <c r="H356" t="n">
-        <v>88.12</v>
+        <v>95.12</v>
       </c>
       <c r="I356" t="n">
-        <v>5650</v>
+        <v>5642</v>
       </c>
       <c r="J356" t="n">
         <v>5521.63</v>
       </c>
       <c r="K356" t="n">
-        <v>128.37</v>
+        <v>120.37</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         </is>
       </c>
       <c r="N356" t="n">
-        <v>0.8</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="357">
@@ -18962,31 +18962,31 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>183.6</v>
+        <v>183.45</v>
       </c>
       <c r="D357" t="n">
         <v>193.94</v>
       </c>
       <c r="E357" t="n">
-        <v>-10.34</v>
+        <v>-10.49</v>
       </c>
       <c r="F357" t="n">
-        <v>184.7</v>
+        <v>185.3</v>
       </c>
       <c r="G357" t="n">
         <v>193.94</v>
       </c>
       <c r="H357" t="n">
-        <v>-9.24</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I357" t="n">
-        <v>182.02</v>
+        <v>182.5</v>
       </c>
       <c r="J357" t="n">
         <v>179.91</v>
       </c>
       <c r="K357" t="n">
-        <v>2.11</v>
+        <v>2.59</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>5.33</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="358">
@@ -19014,31 +19014,31 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1635.8</v>
+        <v>1631</v>
       </c>
       <c r="D358" t="n">
         <v>1677.53</v>
       </c>
       <c r="E358" t="n">
-        <v>-41.73</v>
+        <v>-46.53</v>
       </c>
       <c r="F358" t="n">
-        <v>1641.6</v>
+        <v>1651.3</v>
       </c>
       <c r="G358" t="n">
         <v>1677.53</v>
       </c>
       <c r="H358" t="n">
-        <v>-35.93</v>
+        <v>-26.23</v>
       </c>
       <c r="I358" t="n">
-        <v>1618.1</v>
+        <v>1590</v>
       </c>
       <c r="J358" t="n">
         <v>1577.23</v>
       </c>
       <c r="K358" t="n">
-        <v>40.87</v>
+        <v>12.77</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="359">
@@ -19066,31 +19066,31 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1785</v>
+        <v>1795.2</v>
       </c>
       <c r="D359" t="n">
         <v>1770.83</v>
       </c>
       <c r="E359" t="n">
-        <v>14.17</v>
+        <v>24.37</v>
       </c>
       <c r="F359" t="n">
-        <v>1811.8</v>
+        <v>1799</v>
       </c>
       <c r="G359" t="n">
         <v>1770.83</v>
       </c>
       <c r="H359" t="n">
-        <v>40.97</v>
+        <v>28.17</v>
       </c>
       <c r="I359" t="n">
-        <v>1773.5</v>
+        <v>1757</v>
       </c>
       <c r="J359" t="n">
         <v>1728.56</v>
       </c>
       <c r="K359" t="n">
-        <v>44.94</v>
+        <v>28.44</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>0.8</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="360">
@@ -19118,31 +19118,31 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>1873</v>
+        <v>1891.7</v>
       </c>
       <c r="D360" t="n">
         <v>1903.99</v>
       </c>
       <c r="E360" t="n">
-        <v>-30.99</v>
+        <v>-12.29</v>
       </c>
       <c r="F360" t="n">
-        <v>1900.8</v>
+        <v>1891.7</v>
       </c>
       <c r="G360" t="n">
         <v>1903.99</v>
       </c>
       <c r="H360" t="n">
-        <v>-3.19</v>
+        <v>-12.29</v>
       </c>
       <c r="I360" t="n">
-        <v>1869.6</v>
+        <v>1851</v>
       </c>
       <c r="J360" t="n">
         <v>1820.59</v>
       </c>
       <c r="K360" t="n">
-        <v>49.01</v>
+        <v>30.41</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>1.63</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="361">
@@ -19170,31 +19170,31 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>4090</v>
+        <v>4093</v>
       </c>
       <c r="D361" t="n">
         <v>4071.14</v>
       </c>
       <c r="E361" t="n">
-        <v>18.86</v>
+        <v>21.86</v>
       </c>
       <c r="F361" t="n">
-        <v>4107.1</v>
+        <v>4100</v>
       </c>
       <c r="G361" t="n">
         <v>4113.19</v>
       </c>
       <c r="H361" t="n">
-        <v>-6.09</v>
+        <v>-13.19</v>
       </c>
       <c r="I361" t="n">
-        <v>4077.7</v>
+        <v>4061.4</v>
       </c>
       <c r="J361" t="n">
         <v>4035.27</v>
       </c>
       <c r="K361" t="n">
-        <v>42.43</v>
+        <v>26.13</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="362">
@@ -19231,22 +19231,22 @@
         <v>7.86</v>
       </c>
       <c r="F362" t="n">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="G362" t="n">
         <v>1002.82</v>
       </c>
       <c r="H362" t="n">
-        <v>12.18</v>
+        <v>1.18</v>
       </c>
       <c r="I362" t="n">
-        <v>988.3</v>
+        <v>968.55</v>
       </c>
       <c r="J362" t="n">
         <v>980.05</v>
       </c>
       <c r="K362" t="n">
-        <v>8.25</v>
+        <v>-11.5</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -19274,31 +19274,31 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>2207</v>
+        <v>2218.8</v>
       </c>
       <c r="D363" t="n">
         <v>2189.74</v>
       </c>
       <c r="E363" t="n">
-        <v>17.26</v>
+        <v>29.06</v>
       </c>
       <c r="F363" t="n">
-        <v>2235.4</v>
+        <v>2251.7</v>
       </c>
       <c r="G363" t="n">
         <v>2240.9</v>
       </c>
       <c r="H363" t="n">
-        <v>-5.5</v>
+        <v>10.8</v>
       </c>
       <c r="I363" t="n">
-        <v>2206.1</v>
+        <v>2211.1</v>
       </c>
       <c r="J363" t="n">
         <v>2190.22</v>
       </c>
       <c r="K363" t="n">
-        <v>15.88</v>
+        <v>20.88</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>0.79</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="364">
@@ -19326,31 +19326,31 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>516.4</v>
+        <v>515.05</v>
       </c>
       <c r="D364" t="n">
         <v>478.47</v>
       </c>
       <c r="E364" t="n">
-        <v>37.93</v>
+        <v>36.58</v>
       </c>
       <c r="F364" t="n">
-        <v>524.2</v>
+        <v>523</v>
       </c>
       <c r="G364" t="n">
         <v>486.67</v>
       </c>
       <c r="H364" t="n">
-        <v>37.53</v>
+        <v>36.33</v>
       </c>
       <c r="I364" t="n">
-        <v>513.05</v>
+        <v>512.15</v>
       </c>
       <c r="J364" t="n">
         <v>501.38</v>
       </c>
       <c r="K364" t="n">
-        <v>11.67</v>
+        <v>10.77</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="N364" t="n">
-        <v>7.93</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="365">
@@ -19378,31 +19378,31 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2540</v>
+        <v>2552</v>
       </c>
       <c r="D365" t="n">
         <v>2560.88</v>
       </c>
       <c r="E365" t="n">
-        <v>-20.88</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="F365" t="n">
-        <v>2572.6</v>
+        <v>2596</v>
       </c>
       <c r="G365" t="n">
         <v>2560.88</v>
       </c>
       <c r="H365" t="n">
-        <v>11.72</v>
+        <v>35.12</v>
       </c>
       <c r="I365" t="n">
-        <v>2523.4</v>
+        <v>2542</v>
       </c>
       <c r="J365" t="n">
         <v>2457.21</v>
       </c>
       <c r="K365" t="n">
-        <v>66.19</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>0.82</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="366">
@@ -19430,31 +19430,31 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1349</v>
+        <v>1350.1</v>
       </c>
       <c r="D366" t="n">
         <v>1338.29</v>
       </c>
       <c r="E366" t="n">
-        <v>10.71</v>
+        <v>11.81</v>
       </c>
       <c r="F366" t="n">
-        <v>1360</v>
+        <v>1367.8</v>
       </c>
       <c r="G366" t="n">
         <v>1338.29</v>
       </c>
       <c r="H366" t="n">
-        <v>21.71</v>
+        <v>29.51</v>
       </c>
       <c r="I366" t="n">
-        <v>1336.7</v>
+        <v>1345.2</v>
       </c>
       <c r="J366" t="n">
         <v>1301.3</v>
       </c>
       <c r="K366" t="n">
-        <v>35.4</v>
+        <v>43.9</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="367">
@@ -19482,31 +19482,31 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14570</v>
+        <v>14850</v>
       </c>
       <c r="D367" t="n">
         <v>14173.87</v>
       </c>
       <c r="E367" t="n">
-        <v>396.13</v>
+        <v>676.13</v>
       </c>
       <c r="F367" t="n">
-        <v>15000</v>
+        <v>14924</v>
       </c>
       <c r="G367" t="n">
         <v>14825.24</v>
       </c>
       <c r="H367" t="n">
-        <v>174.76</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="I367" t="n">
-        <v>14484</v>
+        <v>14620</v>
       </c>
       <c r="J367" t="n">
         <v>14490.99</v>
       </c>
       <c r="K367" t="n">
-        <v>-6.99</v>
+        <v>129.01</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>2.79</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="368">
@@ -19534,31 +19534,31 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>870.45</v>
+        <v>876.9</v>
       </c>
       <c r="D368" t="n">
         <v>863.54</v>
       </c>
       <c r="E368" t="n">
-        <v>6.91</v>
+        <v>13.36</v>
       </c>
       <c r="F368" t="n">
-        <v>883.85</v>
+        <v>880.9</v>
       </c>
       <c r="G368" t="n">
         <v>863.9</v>
       </c>
       <c r="H368" t="n">
-        <v>19.95</v>
+        <v>17</v>
       </c>
       <c r="I368" t="n">
-        <v>862</v>
+        <v>870.5</v>
       </c>
       <c r="J368" t="n">
         <v>847.41</v>
       </c>
       <c r="K368" t="n">
-        <v>14.59</v>
+        <v>23.09</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>0.8</v>
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
@@ -21024,31 +21024,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24219.05</v>
+        <v>24252</v>
       </c>
       <c r="D28" t="n">
         <v>24219.05</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>32.95</v>
       </c>
       <c r="F28" t="n">
-        <v>24313</v>
+        <v>24284.05</v>
       </c>
       <c r="G28" t="n">
         <v>24306.6</v>
       </c>
       <c r="H28" t="n">
-        <v>6.4</v>
+        <v>-22.55</v>
       </c>
       <c r="I28" t="n">
-        <v>24144.3</v>
+        <v>24206.8</v>
       </c>
       <c r="J28" t="n">
         <v>24137.9</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="29">
@@ -21076,31 +21076,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>57525.95</v>
+        <v>57761.95</v>
       </c>
       <c r="D29" t="n">
         <v>57525.95</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="F29" t="n">
-        <v>57873.75</v>
+        <v>57772.45</v>
       </c>
       <c r="G29" t="n">
         <v>57851.15</v>
       </c>
       <c r="H29" t="n">
-        <v>22.6</v>
+        <v>-78.7</v>
       </c>
       <c r="I29" t="n">
-        <v>57245.95</v>
+        <v>57481.55</v>
       </c>
       <c r="J29" t="n">
         <v>57223.35</v>
       </c>
       <c r="K29" t="n">
-        <v>22.6</v>
+        <v>258.2</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -38842,31 +38842,31 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2145</v>
+        <v>2139</v>
       </c>
       <c r="D341" t="n">
         <v>2121.71</v>
       </c>
       <c r="E341" t="n">
-        <v>23.29</v>
+        <v>17.29</v>
       </c>
       <c r="F341" t="n">
-        <v>2172.8</v>
+        <v>2162.2</v>
       </c>
       <c r="G341" t="n">
         <v>2174.62</v>
       </c>
       <c r="H341" t="n">
-        <v>-1.82</v>
+        <v>-12.42</v>
       </c>
       <c r="I341" t="n">
-        <v>2131.8</v>
+        <v>2126.3</v>
       </c>
       <c r="J341" t="n">
         <v>2102.44</v>
       </c>
       <c r="K341" t="n">
-        <v>29.36</v>
+        <v>23.86</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="342">
@@ -38894,31 +38894,31 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3414.1</v>
+        <v>3412.2</v>
       </c>
       <c r="D342" t="n">
         <v>3262.68</v>
       </c>
       <c r="E342" t="n">
-        <v>151.42</v>
+        <v>149.52</v>
       </c>
       <c r="F342" t="n">
-        <v>3444.7</v>
+        <v>3453.9</v>
       </c>
       <c r="G342" t="n">
         <v>3439.56</v>
       </c>
       <c r="H342" t="n">
-        <v>5.14</v>
+        <v>14.34</v>
       </c>
       <c r="I342" t="n">
-        <v>3400</v>
+        <v>3412.2</v>
       </c>
       <c r="J342" t="n">
         <v>3362.82</v>
       </c>
       <c r="K342" t="n">
-        <v>37.18</v>
+        <v>49.38</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="343">
@@ -38946,31 +38946,31 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>689</v>
+        <v>678.1</v>
       </c>
       <c r="D343" t="n">
         <v>713.8</v>
       </c>
       <c r="E343" t="n">
-        <v>-24.8</v>
+        <v>-35.7</v>
       </c>
       <c r="F343" t="n">
-        <v>689</v>
+        <v>684.45</v>
       </c>
       <c r="G343" t="n">
         <v>700.5599999999999</v>
       </c>
       <c r="H343" t="n">
-        <v>-11.56</v>
+        <v>-16.11</v>
       </c>
       <c r="I343" t="n">
-        <v>678.1</v>
+        <v>675.25</v>
       </c>
       <c r="J343" t="n">
         <v>673.78</v>
       </c>
       <c r="K343" t="n">
-        <v>4.32</v>
+        <v>1.47</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>3.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344">
@@ -38998,31 +38998,31 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D344" t="n">
         <v>487.29</v>
       </c>
       <c r="E344" t="n">
-        <v>-10.29</v>
+        <v>-12.29</v>
       </c>
       <c r="F344" t="n">
-        <v>479.25</v>
+        <v>482</v>
       </c>
       <c r="G344" t="n">
         <v>487.14</v>
       </c>
       <c r="H344" t="n">
-        <v>-7.89</v>
+        <v>-5.14</v>
       </c>
       <c r="I344" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="J344" t="n">
         <v>464.85</v>
       </c>
       <c r="K344" t="n">
-        <v>7.15</v>
+        <v>10.15</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -39031,11 +39031,11 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N344" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="345">
@@ -39050,31 +39050,31 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>295.95</v>
+        <v>293</v>
       </c>
       <c r="D345" t="n">
         <v>299.07</v>
       </c>
       <c r="E345" t="n">
-        <v>-3.12</v>
+        <v>-6.07</v>
       </c>
       <c r="F345" t="n">
-        <v>296.8</v>
+        <v>293.5</v>
       </c>
       <c r="G345" t="n">
         <v>299.79</v>
       </c>
       <c r="H345" t="n">
-        <v>-2.99</v>
+        <v>-6.29</v>
       </c>
       <c r="I345" t="n">
-        <v>291.4</v>
+        <v>289.75</v>
       </c>
       <c r="J345" t="n">
         <v>290.26</v>
       </c>
       <c r="K345" t="n">
-        <v>1.14</v>
+        <v>-0.51</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>1.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="346">
@@ -39102,31 +39102,31 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>115.86</v>
+        <v>116.55</v>
       </c>
       <c r="D346" t="n">
         <v>121.77</v>
       </c>
       <c r="E346" t="n">
-        <v>-5.91</v>
+        <v>-5.22</v>
       </c>
       <c r="F346" t="n">
-        <v>117.03</v>
+        <v>117.52</v>
       </c>
       <c r="G346" t="n">
         <v>117.01</v>
       </c>
       <c r="H346" t="n">
-        <v>0.02</v>
+        <v>0.51</v>
       </c>
       <c r="I346" t="n">
-        <v>115</v>
+        <v>115.41</v>
       </c>
       <c r="J346" t="n">
         <v>113.9</v>
       </c>
       <c r="K346" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>4.85</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="347">
@@ -39154,31 +39154,31 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>5694</v>
+        <v>5667.5</v>
       </c>
       <c r="D347" t="n">
         <v>5678.44</v>
       </c>
       <c r="E347" t="n">
-        <v>15.56</v>
+        <v>-10.94</v>
       </c>
       <c r="F347" t="n">
-        <v>5725</v>
+        <v>5722</v>
       </c>
       <c r="G347" t="n">
         <v>5780.4</v>
       </c>
       <c r="H347" t="n">
-        <v>-55.4</v>
+        <v>-58.4</v>
       </c>
       <c r="I347" t="n">
-        <v>5646</v>
+        <v>5602</v>
       </c>
       <c r="J347" t="n">
         <v>5575.15</v>
       </c>
       <c r="K347" t="n">
-        <v>70.84999999999999</v>
+        <v>26.85</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="348">
@@ -39206,31 +39206,31 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>403.3</v>
+        <v>393.45</v>
       </c>
       <c r="D348" t="n">
         <v>468.64</v>
       </c>
       <c r="E348" t="n">
-        <v>-65.34</v>
+        <v>-75.19</v>
       </c>
       <c r="F348" t="n">
-        <v>405</v>
+        <v>396.49</v>
       </c>
       <c r="G348" t="n">
         <v>414.41</v>
       </c>
       <c r="H348" t="n">
-        <v>-9.41</v>
+        <v>-17.92</v>
       </c>
       <c r="I348" t="n">
-        <v>397.5</v>
+        <v>383.62</v>
       </c>
       <c r="J348" t="n">
         <v>391.09</v>
       </c>
       <c r="K348" t="n">
-        <v>6.41</v>
+        <v>-7.47</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>13.94</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="349">
@@ -39258,31 +39258,31 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>3268</v>
+        <v>3185</v>
       </c>
       <c r="D349" t="n">
         <v>3429.43</v>
       </c>
       <c r="E349" t="n">
-        <v>-161.43</v>
+        <v>-244.43</v>
       </c>
       <c r="F349" t="n">
-        <v>3289.7</v>
+        <v>3211.4</v>
       </c>
       <c r="G349" t="n">
         <v>3355.87</v>
       </c>
       <c r="H349" t="n">
-        <v>-66.17</v>
+        <v>-144.47</v>
       </c>
       <c r="I349" t="n">
-        <v>3180.1</v>
+        <v>3132</v>
       </c>
       <c r="J349" t="n">
         <v>3170.74</v>
       </c>
       <c r="K349" t="n">
-        <v>9.359999999999999</v>
+        <v>-38.74</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>4.71</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="350">
@@ -39310,31 +39310,31 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>183.6</v>
+        <v>183.45</v>
       </c>
       <c r="D350" t="n">
         <v>198.44</v>
       </c>
       <c r="E350" t="n">
-        <v>-14.84</v>
+        <v>-14.99</v>
       </c>
       <c r="F350" t="n">
-        <v>184.7</v>
+        <v>185.3</v>
       </c>
       <c r="G350" t="n">
         <v>186.78</v>
       </c>
       <c r="H350" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="I350" t="n">
-        <v>182.02</v>
+        <v>182.5</v>
       </c>
       <c r="J350" t="n">
         <v>179.46</v>
       </c>
       <c r="K350" t="n">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>7.48</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="351">
@@ -39362,31 +39362,31 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>173.29</v>
+        <v>173</v>
       </c>
       <c r="D351" t="n">
         <v>176.3</v>
       </c>
       <c r="E351" t="n">
-        <v>-3.01</v>
+        <v>-3.3</v>
       </c>
       <c r="F351" t="n">
-        <v>173.66</v>
+        <v>173.69</v>
       </c>
       <c r="G351" t="n">
         <v>176.39</v>
       </c>
       <c r="H351" t="n">
-        <v>-2.73</v>
+        <v>-2.7</v>
       </c>
       <c r="I351" t="n">
-        <v>171.65</v>
+        <v>172.3</v>
       </c>
       <c r="J351" t="n">
         <v>169.32</v>
       </c>
       <c r="K351" t="n">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="352">
@@ -39414,31 +39414,31 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>1058.5</v>
+        <v>1034</v>
       </c>
       <c r="D352" t="n">
         <v>1076.15</v>
       </c>
       <c r="E352" t="n">
-        <v>-17.65</v>
+        <v>-42.15</v>
       </c>
       <c r="F352" t="n">
-        <v>1058.5</v>
+        <v>1040.45</v>
       </c>
       <c r="G352" t="n">
         <v>1078.51</v>
       </c>
       <c r="H352" t="n">
-        <v>-20.01</v>
+        <v>-38.06</v>
       </c>
       <c r="I352" t="n">
-        <v>1043.3</v>
+        <v>1024.6</v>
       </c>
       <c r="J352" t="n">
         <v>1033.42</v>
       </c>
       <c r="K352" t="n">
-        <v>9.880000000000001</v>
+        <v>-8.82</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -39447,11 +39447,11 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N352" t="n">
-        <v>1.64</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="353">
@@ -39466,31 +39466,31 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1251.3</v>
+        <v>1265</v>
       </c>
       <c r="D353" t="n">
         <v>1268.07</v>
       </c>
       <c r="E353" t="n">
-        <v>-16.77</v>
+        <v>-3.07</v>
       </c>
       <c r="F353" t="n">
-        <v>1261.6</v>
+        <v>1267</v>
       </c>
       <c r="G353" t="n">
         <v>1271.01</v>
       </c>
       <c r="H353" t="n">
-        <v>-9.41</v>
+        <v>-4.01</v>
       </c>
       <c r="I353" t="n">
-        <v>1245.1</v>
+        <v>1252</v>
       </c>
       <c r="J353" t="n">
         <v>1224.65</v>
       </c>
       <c r="K353" t="n">
-        <v>20.45</v>
+        <v>27.35</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>1.32</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="354">
@@ -39518,31 +39518,31 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>327.15</v>
+        <v>328</v>
       </c>
       <c r="D354" t="n">
         <v>311.5</v>
       </c>
       <c r="E354" t="n">
-        <v>15.65</v>
+        <v>16.5</v>
       </c>
       <c r="F354" t="n">
-        <v>329.5</v>
+        <v>331.7</v>
       </c>
       <c r="G354" t="n">
         <v>331.41</v>
       </c>
       <c r="H354" t="n">
-        <v>-1.91</v>
+        <v>0.29</v>
       </c>
       <c r="I354" t="n">
-        <v>323</v>
+        <v>324.1</v>
       </c>
       <c r="J354" t="n">
         <v>320.87</v>
       </c>
       <c r="K354" t="n">
-        <v>2.13</v>
+        <v>3.23</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         </is>
       </c>
       <c r="N354" t="n">
-        <v>5.02</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="355">
@@ -39570,31 +39570,31 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>5685</v>
+        <v>5735</v>
       </c>
       <c r="D355" t="n">
         <v>5761.02</v>
       </c>
       <c r="E355" t="n">
-        <v>-76.02</v>
+        <v>-26.02</v>
       </c>
       <c r="F355" t="n">
-        <v>5728</v>
+        <v>5735</v>
       </c>
       <c r="G355" t="n">
         <v>5774.36</v>
       </c>
       <c r="H355" t="n">
-        <v>-46.36</v>
+        <v>-39.36</v>
       </c>
       <c r="I355" t="n">
-        <v>5650</v>
+        <v>5642</v>
       </c>
       <c r="J355" t="n">
         <v>5564</v>
       </c>
       <c r="K355" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>1.32</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="356">
@@ -39622,31 +39622,31 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>2001.7</v>
+        <v>2032.5</v>
       </c>
       <c r="D356" t="n">
         <v>2070.03</v>
       </c>
       <c r="E356" t="n">
-        <v>-68.33</v>
+        <v>-37.53</v>
       </c>
       <c r="F356" t="n">
-        <v>2028.6</v>
+        <v>2032.5</v>
       </c>
       <c r="G356" t="n">
         <v>2019.9</v>
       </c>
       <c r="H356" t="n">
-        <v>8.699999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="I356" t="n">
-        <v>1995.3</v>
+        <v>2005</v>
       </c>
       <c r="J356" t="n">
         <v>1969.17</v>
       </c>
       <c r="K356" t="n">
-        <v>26.13</v>
+        <v>35.83</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -39655,11 +39655,11 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N356" t="n">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="357">
@@ -39674,31 +39674,31 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1635.8</v>
+        <v>1631</v>
       </c>
       <c r="D357" t="n">
         <v>1725.82</v>
       </c>
       <c r="E357" t="n">
-        <v>-90.02</v>
+        <v>-94.81999999999999</v>
       </c>
       <c r="F357" t="n">
-        <v>1641.6</v>
+        <v>1651.3</v>
       </c>
       <c r="G357" t="n">
         <v>1672.94</v>
       </c>
       <c r="H357" t="n">
-        <v>-31.34</v>
+        <v>-21.64</v>
       </c>
       <c r="I357" t="n">
-        <v>1618.1</v>
+        <v>1590</v>
       </c>
       <c r="J357" t="n">
         <v>1592.31</v>
       </c>
       <c r="K357" t="n">
-        <v>25.79</v>
+        <v>-2.31</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>5.22</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="358">
@@ -39726,31 +39726,31 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>11120</v>
+        <v>11320</v>
       </c>
       <c r="D358" t="n">
         <v>11182.72</v>
       </c>
       <c r="E358" t="n">
-        <v>-62.72</v>
+        <v>137.28</v>
       </c>
       <c r="F358" t="n">
-        <v>11360</v>
+        <v>11410</v>
       </c>
       <c r="G358" t="n">
         <v>11211.97</v>
       </c>
       <c r="H358" t="n">
-        <v>148.03</v>
+        <v>198.03</v>
       </c>
       <c r="I358" t="n">
-        <v>11050</v>
+        <v>11280</v>
       </c>
       <c r="J358" t="n">
         <v>10946.16</v>
       </c>
       <c r="K358" t="n">
-        <v>103.84</v>
+        <v>333.84</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="359">
@@ -39778,31 +39778,31 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1785</v>
+        <v>1795.2</v>
       </c>
       <c r="D359" t="n">
         <v>1822.47</v>
       </c>
       <c r="E359" t="n">
-        <v>-37.47</v>
+        <v>-27.27</v>
       </c>
       <c r="F359" t="n">
-        <v>1811.8</v>
+        <v>1799</v>
       </c>
       <c r="G359" t="n">
         <v>1826.16</v>
       </c>
       <c r="H359" t="n">
-        <v>-14.36</v>
+        <v>-27.16</v>
       </c>
       <c r="I359" t="n">
-        <v>1773.5</v>
+        <v>1757</v>
       </c>
       <c r="J359" t="n">
         <v>1737.07</v>
       </c>
       <c r="K359" t="n">
-        <v>36.43</v>
+        <v>19.93</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="360">
@@ -39830,31 +39830,31 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>516.4</v>
+        <v>515.05</v>
       </c>
       <c r="D360" t="n">
         <v>488.91</v>
       </c>
       <c r="E360" t="n">
-        <v>27.49</v>
+        <v>26.14</v>
       </c>
       <c r="F360" t="n">
-        <v>524.2</v>
+        <v>523</v>
       </c>
       <c r="G360" t="n">
         <v>524.6900000000001</v>
       </c>
       <c r="H360" t="n">
-        <v>-0.49</v>
+        <v>-1.69</v>
       </c>
       <c r="I360" t="n">
-        <v>513.05</v>
+        <v>512.15</v>
       </c>
       <c r="J360" t="n">
         <v>505.27</v>
       </c>
       <c r="K360" t="n">
-        <v>7.78</v>
+        <v>6.88</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>5.62</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="361">
@@ -39882,31 +39882,31 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>4090</v>
+        <v>4093</v>
       </c>
       <c r="D361" t="n">
         <v>4102.28</v>
       </c>
       <c r="E361" t="n">
-        <v>-12.28</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="F361" t="n">
-        <v>4107.1</v>
+        <v>4100</v>
       </c>
       <c r="G361" t="n">
         <v>4100.23</v>
       </c>
       <c r="H361" t="n">
-        <v>6.87</v>
+        <v>-0.23</v>
       </c>
       <c r="I361" t="n">
-        <v>4077.7</v>
+        <v>4061.4</v>
       </c>
       <c r="J361" t="n">
         <v>4043.97</v>
       </c>
       <c r="K361" t="n">
-        <v>33.73</v>
+        <v>17.43</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="362">
@@ -39943,22 +39943,22 @@
         <v>-18.22</v>
       </c>
       <c r="F362" t="n">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="G362" t="n">
         <v>1010.37</v>
       </c>
       <c r="H362" t="n">
-        <v>4.63</v>
+        <v>-6.37</v>
       </c>
       <c r="I362" t="n">
-        <v>988.3</v>
+        <v>968.55</v>
       </c>
       <c r="J362" t="n">
         <v>965.28</v>
       </c>
       <c r="K362" t="n">
-        <v>23.02</v>
+        <v>3.27</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -39986,31 +39986,31 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>2207</v>
+        <v>2218.8</v>
       </c>
       <c r="D363" t="n">
         <v>2230.21</v>
       </c>
       <c r="E363" t="n">
-        <v>-23.21</v>
+        <v>-11.41</v>
       </c>
       <c r="F363" t="n">
-        <v>2235.4</v>
+        <v>2251.7</v>
       </c>
       <c r="G363" t="n">
         <v>2235.63</v>
       </c>
       <c r="H363" t="n">
-        <v>-0.23</v>
+        <v>16.07</v>
       </c>
       <c r="I363" t="n">
-        <v>2206.1</v>
+        <v>2211.1</v>
       </c>
       <c r="J363" t="n">
         <v>2164.63</v>
       </c>
       <c r="K363" t="n">
-        <v>41.47</v>
+        <v>46.47</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>1.04</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="364">
@@ -40038,31 +40038,31 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>1873</v>
+        <v>1891.7</v>
       </c>
       <c r="D364" t="n">
         <v>1943.39</v>
       </c>
       <c r="E364" t="n">
-        <v>-70.39</v>
+        <v>-51.69</v>
       </c>
       <c r="F364" t="n">
-        <v>1900.8</v>
+        <v>1891.7</v>
       </c>
       <c r="G364" t="n">
         <v>1901.03</v>
       </c>
       <c r="H364" t="n">
-        <v>-0.23</v>
+        <v>-9.33</v>
       </c>
       <c r="I364" t="n">
-        <v>1869.6</v>
+        <v>1851</v>
       </c>
       <c r="J364" t="n">
         <v>1834.21</v>
       </c>
       <c r="K364" t="n">
-        <v>35.39</v>
+        <v>16.79</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         </is>
       </c>
       <c r="N364" t="n">
-        <v>3.62</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="365">
@@ -40090,31 +40090,31 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2540</v>
+        <v>2552</v>
       </c>
       <c r="D365" t="n">
         <v>2626.09</v>
       </c>
       <c r="E365" t="n">
-        <v>-86.09</v>
+        <v>-74.09</v>
       </c>
       <c r="F365" t="n">
-        <v>2572.6</v>
+        <v>2596</v>
       </c>
       <c r="G365" t="n">
         <v>2589.6</v>
       </c>
       <c r="H365" t="n">
-        <v>-17</v>
+        <v>6.4</v>
       </c>
       <c r="I365" t="n">
-        <v>2523.4</v>
+        <v>2542</v>
       </c>
       <c r="J365" t="n">
         <v>2478.6</v>
       </c>
       <c r="K365" t="n">
-        <v>44.8</v>
+        <v>63.4</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>3.28</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="366">
@@ -40142,31 +40142,31 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1349</v>
+        <v>1350.1</v>
       </c>
       <c r="D366" t="n">
         <v>1377.16</v>
       </c>
       <c r="E366" t="n">
-        <v>-28.16</v>
+        <v>-27.06</v>
       </c>
       <c r="F366" t="n">
-        <v>1360</v>
+        <v>1367.8</v>
       </c>
       <c r="G366" t="n">
         <v>1379.96</v>
       </c>
       <c r="H366" t="n">
-        <v>-19.96</v>
+        <v>-12.16</v>
       </c>
       <c r="I366" t="n">
-        <v>1336.7</v>
+        <v>1345.2</v>
       </c>
       <c r="J366" t="n">
         <v>1312.88</v>
       </c>
       <c r="K366" t="n">
-        <v>23.82</v>
+        <v>32.32</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="367">
@@ -40194,31 +40194,31 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14570</v>
+        <v>14850</v>
       </c>
       <c r="D367" t="n">
         <v>14441.11</v>
       </c>
       <c r="E367" t="n">
-        <v>128.89</v>
+        <v>408.89</v>
       </c>
       <c r="F367" t="n">
-        <v>15000</v>
+        <v>14924</v>
       </c>
       <c r="G367" t="n">
         <v>14794.91</v>
       </c>
       <c r="H367" t="n">
-        <v>205.09</v>
+        <v>129.09</v>
       </c>
       <c r="I367" t="n">
-        <v>14484</v>
+        <v>14620</v>
       </c>
       <c r="J367" t="n">
         <v>14263</v>
       </c>
       <c r="K367" t="n">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.89</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="368">
@@ -40246,31 +40246,31 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>870.45</v>
+        <v>876.9</v>
       </c>
       <c r="D368" t="n">
         <v>880.0599999999999</v>
       </c>
       <c r="E368" t="n">
-        <v>-9.609999999999999</v>
+        <v>-3.16</v>
       </c>
       <c r="F368" t="n">
-        <v>883.85</v>
+        <v>880.9</v>
       </c>
       <c r="G368" t="n">
         <v>882.1799999999999</v>
       </c>
       <c r="H368" t="n">
-        <v>1.67</v>
+        <v>-1.28</v>
       </c>
       <c r="I368" t="n">
-        <v>862</v>
+        <v>870.5</v>
       </c>
       <c r="J368" t="n">
         <v>853.4</v>
       </c>
       <c r="K368" t="n">
-        <v>8.6</v>
+        <v>17.1</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N368"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19572,6 +19572,1618 @@
       </c>
       <c r="N368" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D369" t="n">
+        <v>2012.25</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="F369" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="G369" t="n">
+        <v>2012.25</v>
+      </c>
+      <c r="H369" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="I369" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J369" t="n">
+        <v>1979.81</v>
+      </c>
+      <c r="K369" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N369" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D370" t="n">
+        <v>1048.91</v>
+      </c>
+      <c r="E370" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F370" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1056.46</v>
+      </c>
+      <c r="H370" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="I370" t="n">
+        <v>1031.3</v>
+      </c>
+      <c r="J370" t="n">
+        <v>1033.1</v>
+      </c>
+      <c r="K370" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N370" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>115.93</v>
+      </c>
+      <c r="D371" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="E371" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F371" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="G371" t="n">
+        <v>117.64</v>
+      </c>
+      <c r="H371" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I371" t="n">
+        <v>115.01</v>
+      </c>
+      <c r="J371" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="K371" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N371" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>3443</v>
+      </c>
+      <c r="D372" t="n">
+        <v>3676.17</v>
+      </c>
+      <c r="E372" t="n">
+        <v>-233.17</v>
+      </c>
+      <c r="F372" t="n">
+        <v>3443</v>
+      </c>
+      <c r="G372" t="n">
+        <v>3676.17</v>
+      </c>
+      <c r="H372" t="n">
+        <v>-233.17</v>
+      </c>
+      <c r="I372" t="n">
+        <v>3396.8</v>
+      </c>
+      <c r="J372" t="n">
+        <v>3423.64</v>
+      </c>
+      <c r="K372" t="n">
+        <v>-26.84</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N372" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>11729</v>
+      </c>
+      <c r="D373" t="n">
+        <v>11739.24</v>
+      </c>
+      <c r="E373" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="F373" t="n">
+        <v>11729</v>
+      </c>
+      <c r="G373" t="n">
+        <v>11951.36</v>
+      </c>
+      <c r="H373" t="n">
+        <v>-222.36</v>
+      </c>
+      <c r="I373" t="n">
+        <v>11355</v>
+      </c>
+      <c r="J373" t="n">
+        <v>11691.57</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-336.57</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N373" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>2139.3</v>
+      </c>
+      <c r="D374" t="n">
+        <v>2216.34</v>
+      </c>
+      <c r="E374" t="n">
+        <v>-77.04000000000001</v>
+      </c>
+      <c r="F374" t="n">
+        <v>2151.8</v>
+      </c>
+      <c r="G374" t="n">
+        <v>2216.34</v>
+      </c>
+      <c r="H374" t="n">
+        <v>-64.54000000000001</v>
+      </c>
+      <c r="I374" t="n">
+        <v>2124</v>
+      </c>
+      <c r="J374" t="n">
+        <v>2102.97</v>
+      </c>
+      <c r="K374" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N374" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="D375" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="E375" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F375" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="G375" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="H375" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="I375" t="n">
+        <v>171.58</v>
+      </c>
+      <c r="J375" t="n">
+        <v>172.04</v>
+      </c>
+      <c r="K375" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N375" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1948.7</v>
+      </c>
+      <c r="E376" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="F376" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G376" t="n">
+        <v>1974.82</v>
+      </c>
+      <c r="H376" t="n">
+        <v>-27.82</v>
+      </c>
+      <c r="I376" t="n">
+        <v>1923.4</v>
+      </c>
+      <c r="J376" t="n">
+        <v>1931.58</v>
+      </c>
+      <c r="K376" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N376" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>1011.5</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="E377" t="n">
+        <v>-16.25</v>
+      </c>
+      <c r="F377" t="n">
+        <v>1019.9</v>
+      </c>
+      <c r="G377" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="H377" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="I377" t="n">
+        <v>992</v>
+      </c>
+      <c r="J377" t="n">
+        <v>1003.04</v>
+      </c>
+      <c r="K377" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N377" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>1798.3</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1837.63</v>
+      </c>
+      <c r="E378" t="n">
+        <v>-39.33</v>
+      </c>
+      <c r="F378" t="n">
+        <v>1815</v>
+      </c>
+      <c r="G378" t="n">
+        <v>1837.63</v>
+      </c>
+      <c r="H378" t="n">
+        <v>-22.63</v>
+      </c>
+      <c r="I378" t="n">
+        <v>1775</v>
+      </c>
+      <c r="J378" t="n">
+        <v>1760.02</v>
+      </c>
+      <c r="K378" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N378" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>3280</v>
+      </c>
+      <c r="D379" t="n">
+        <v>3158.38</v>
+      </c>
+      <c r="E379" t="n">
+        <v>121.62</v>
+      </c>
+      <c r="F379" t="n">
+        <v>3308.7</v>
+      </c>
+      <c r="G379" t="n">
+        <v>3343.9</v>
+      </c>
+      <c r="H379" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="I379" t="n">
+        <v>3254.3</v>
+      </c>
+      <c r="J379" t="n">
+        <v>3271.27</v>
+      </c>
+      <c r="K379" t="n">
+        <v>-16.97</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N379" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>4119</v>
+      </c>
+      <c r="D380" t="n">
+        <v>4174.25</v>
+      </c>
+      <c r="E380" t="n">
+        <v>-55.25</v>
+      </c>
+      <c r="F380" t="n">
+        <v>4125.3</v>
+      </c>
+      <c r="G380" t="n">
+        <v>4179.37</v>
+      </c>
+      <c r="H380" t="n">
+        <v>-54.07</v>
+      </c>
+      <c r="I380" t="n">
+        <v>4066.6</v>
+      </c>
+      <c r="J380" t="n">
+        <v>4106.99</v>
+      </c>
+      <c r="K380" t="n">
+        <v>-40.39</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N380" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>11290</v>
+      </c>
+      <c r="D381" t="n">
+        <v>11708.14</v>
+      </c>
+      <c r="E381" t="n">
+        <v>-418.14</v>
+      </c>
+      <c r="F381" t="n">
+        <v>11290</v>
+      </c>
+      <c r="G381" t="n">
+        <v>11708.14</v>
+      </c>
+      <c r="H381" t="n">
+        <v>-418.14</v>
+      </c>
+      <c r="I381" t="n">
+        <v>10811</v>
+      </c>
+      <c r="J381" t="n">
+        <v>11290</v>
+      </c>
+      <c r="K381" t="n">
+        <v>-479</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="D382" t="n">
+        <v>471.88</v>
+      </c>
+      <c r="E382" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="F382" t="n">
+        <v>479</v>
+      </c>
+      <c r="G382" t="n">
+        <v>471.88</v>
+      </c>
+      <c r="H382" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="I382" t="n">
+        <v>466.05</v>
+      </c>
+      <c r="J382" t="n">
+        <v>455.69</v>
+      </c>
+      <c r="K382" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>2232.5</v>
+      </c>
+      <c r="D383" t="n">
+        <v>2288.38</v>
+      </c>
+      <c r="E383" t="n">
+        <v>-55.88</v>
+      </c>
+      <c r="F383" t="n">
+        <v>2243.8</v>
+      </c>
+      <c r="G383" t="n">
+        <v>2292.81</v>
+      </c>
+      <c r="H383" t="n">
+        <v>-49.01</v>
+      </c>
+      <c r="I383" t="n">
+        <v>2190</v>
+      </c>
+      <c r="J383" t="n">
+        <v>2232.5</v>
+      </c>
+      <c r="K383" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="D384" t="n">
+        <v>178.29</v>
+      </c>
+      <c r="E384" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="F384" t="n">
+        <v>187.33</v>
+      </c>
+      <c r="G384" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="H384" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="I384" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="J384" t="n">
+        <v>183.96</v>
+      </c>
+      <c r="K384" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>331</v>
+      </c>
+      <c r="D385" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="E385" t="n">
+        <v>-27.33</v>
+      </c>
+      <c r="F385" t="n">
+        <v>331</v>
+      </c>
+      <c r="G385" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="H385" t="n">
+        <v>-27.33</v>
+      </c>
+      <c r="I385" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="J385" t="n">
+        <v>331</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D386" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="E386" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="F386" t="n">
+        <v>402</v>
+      </c>
+      <c r="G386" t="n">
+        <v>404.41</v>
+      </c>
+      <c r="H386" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="I386" t="n">
+        <v>392.05</v>
+      </c>
+      <c r="J386" t="n">
+        <v>395.59</v>
+      </c>
+      <c r="K386" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1892.8</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1895.63</v>
+      </c>
+      <c r="E387" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="F387" t="n">
+        <v>1899.9</v>
+      </c>
+      <c r="G387" t="n">
+        <v>1903.48</v>
+      </c>
+      <c r="H387" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I387" t="n">
+        <v>1870</v>
+      </c>
+      <c r="J387" t="n">
+        <v>1861.23</v>
+      </c>
+      <c r="K387" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="D388" t="n">
+        <v>294.24</v>
+      </c>
+      <c r="E388" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="F388" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="G388" t="n">
+        <v>294.24</v>
+      </c>
+      <c r="H388" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I388" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="J388" t="n">
+        <v>287.9</v>
+      </c>
+      <c r="K388" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>1253.4</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1287.49</v>
+      </c>
+      <c r="E389" t="n">
+        <v>-34.09</v>
+      </c>
+      <c r="F389" t="n">
+        <v>1256.5</v>
+      </c>
+      <c r="G389" t="n">
+        <v>1287.49</v>
+      </c>
+      <c r="H389" t="n">
+        <v>-30.99</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1240.5</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1234.86</v>
+      </c>
+      <c r="K389" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>5624.5</v>
+      </c>
+      <c r="D390" t="n">
+        <v>5765.14</v>
+      </c>
+      <c r="E390" t="n">
+        <v>-140.64</v>
+      </c>
+      <c r="F390" t="n">
+        <v>5682</v>
+      </c>
+      <c r="G390" t="n">
+        <v>5765.14</v>
+      </c>
+      <c r="H390" t="n">
+        <v>-83.14</v>
+      </c>
+      <c r="I390" t="n">
+        <v>5590</v>
+      </c>
+      <c r="J390" t="n">
+        <v>5516.7</v>
+      </c>
+      <c r="K390" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>5655</v>
+      </c>
+      <c r="D391" t="n">
+        <v>5808.2</v>
+      </c>
+      <c r="E391" t="n">
+        <v>-153.2</v>
+      </c>
+      <c r="F391" t="n">
+        <v>5687</v>
+      </c>
+      <c r="G391" t="n">
+        <v>5808.2</v>
+      </c>
+      <c r="H391" t="n">
+        <v>-121.2</v>
+      </c>
+      <c r="I391" t="n">
+        <v>5570.5</v>
+      </c>
+      <c r="J391" t="n">
+        <v>5555.36</v>
+      </c>
+      <c r="K391" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>2610</v>
+      </c>
+      <c r="D392" t="n">
+        <v>2621.75</v>
+      </c>
+      <c r="E392" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="F392" t="n">
+        <v>2621.7</v>
+      </c>
+      <c r="G392" t="n">
+        <v>2621.75</v>
+      </c>
+      <c r="H392" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I392" t="n">
+        <v>2520</v>
+      </c>
+      <c r="J392" t="n">
+        <v>2552.86</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-32.86</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1211.06</v>
+      </c>
+      <c r="E393" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F393" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G393" t="n">
+        <v>1223.84</v>
+      </c>
+      <c r="H393" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="I393" t="n">
+        <v>1186.4</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1196.92</v>
+      </c>
+      <c r="K393" t="n">
+        <v>-10.52</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>1051.05</v>
+      </c>
+      <c r="D394" t="n">
+        <v>1043.22</v>
+      </c>
+      <c r="E394" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F394" t="n">
+        <v>1057</v>
+      </c>
+      <c r="G394" t="n">
+        <v>1069.88</v>
+      </c>
+      <c r="H394" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="I394" t="n">
+        <v>1040.45</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1046.59</v>
+      </c>
+      <c r="K394" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>682.95</v>
+      </c>
+      <c r="D395" t="n">
+        <v>668.76</v>
+      </c>
+      <c r="E395" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="F395" t="n">
+        <v>688.2</v>
+      </c>
+      <c r="G395" t="n">
+        <v>694.11</v>
+      </c>
+      <c r="H395" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="I395" t="n">
+        <v>678.3</v>
+      </c>
+      <c r="J395" t="n">
+        <v>678.96</v>
+      </c>
+      <c r="K395" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>14990</v>
+      </c>
+      <c r="D396" t="n">
+        <v>15955.71</v>
+      </c>
+      <c r="E396" t="n">
+        <v>-965.71</v>
+      </c>
+      <c r="F396" t="n">
+        <v>14990</v>
+      </c>
+      <c r="G396" t="n">
+        <v>15955.71</v>
+      </c>
+      <c r="H396" t="n">
+        <v>-965.71</v>
+      </c>
+      <c r="I396" t="n">
+        <v>14400</v>
+      </c>
+      <c r="J396" t="n">
+        <v>14990</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-590</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D397" t="n">
+        <v>1372.8</v>
+      </c>
+      <c r="E397" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="F397" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G397" t="n">
+        <v>1372.8</v>
+      </c>
+      <c r="H397" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1328.1</v>
+      </c>
+      <c r="J397" t="n">
+        <v>1315.92</v>
+      </c>
+      <c r="K397" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>878</v>
+      </c>
+      <c r="D398" t="n">
+        <v>898.71</v>
+      </c>
+      <c r="E398" t="n">
+        <v>-20.71</v>
+      </c>
+      <c r="F398" t="n">
+        <v>881.75</v>
+      </c>
+      <c r="G398" t="n">
+        <v>898.71</v>
+      </c>
+      <c r="H398" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="I398" t="n">
+        <v>869</v>
+      </c>
+      <c r="J398" t="n">
+        <v>863.09</v>
+      </c>
+      <c r="K398" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>516</v>
+      </c>
+      <c r="D399" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="E399" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="F399" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="G399" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="H399" t="n">
+        <v>-41.49</v>
+      </c>
+      <c r="I399" t="n">
+        <v>511.3</v>
+      </c>
+      <c r="J399" t="n">
+        <v>506.16</v>
+      </c>
+      <c r="K399" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>7.84</v>
       </c>
     </row>
   </sheetData>
@@ -19585,7 +21197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21114,6 +22726,110 @@
       </c>
       <c r="N29" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24407.59</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-73.04000000000001</v>
+      </c>
+      <c r="I30" t="n">
+        <v>24115.45</v>
+      </c>
+      <c r="J30" t="n">
+        <v>24188.49</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-73.04000000000001</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>57653.85</v>
+      </c>
+      <c r="G31" t="n">
+        <v>57701.61</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-47.76</v>
+      </c>
+      <c r="I31" t="n">
+        <v>57231.25</v>
+      </c>
+      <c r="J31" t="n">
+        <v>57279.01</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-47.76</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21127,7 +22843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N368"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40286,6 +42002,1618 @@
         <v>0.36</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>3443</v>
+      </c>
+      <c r="D369" t="n">
+        <v>3721.73</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-278.73</v>
+      </c>
+      <c r="F369" t="n">
+        <v>3443</v>
+      </c>
+      <c r="G369" t="n">
+        <v>3498.62</v>
+      </c>
+      <c r="H369" t="n">
+        <v>-55.62</v>
+      </c>
+      <c r="I369" t="n">
+        <v>3396.8</v>
+      </c>
+      <c r="J369" t="n">
+        <v>3426</v>
+      </c>
+      <c r="K369" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N369" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>2139.3</v>
+      </c>
+      <c r="D370" t="n">
+        <v>2259.34</v>
+      </c>
+      <c r="E370" t="n">
+        <v>-120.04</v>
+      </c>
+      <c r="F370" t="n">
+        <v>2151.8</v>
+      </c>
+      <c r="G370" t="n">
+        <v>2188.32</v>
+      </c>
+      <c r="H370" t="n">
+        <v>-36.52</v>
+      </c>
+      <c r="I370" t="n">
+        <v>2124</v>
+      </c>
+      <c r="J370" t="n">
+        <v>2117.73</v>
+      </c>
+      <c r="K370" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N370" t="n">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>MCX (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>3280</v>
+      </c>
+      <c r="D371" t="n">
+        <v>3266.25</v>
+      </c>
+      <c r="E371" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F371" t="n">
+        <v>3308.7</v>
+      </c>
+      <c r="G371" t="n">
+        <v>3401.82</v>
+      </c>
+      <c r="H371" t="n">
+        <v>-93.12</v>
+      </c>
+      <c r="I371" t="n">
+        <v>3254.3</v>
+      </c>
+      <c r="J371" t="n">
+        <v>3211.51</v>
+      </c>
+      <c r="K371" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N371" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D372" t="n">
+        <v>2041.17</v>
+      </c>
+      <c r="E372" t="n">
+        <v>-37.17</v>
+      </c>
+      <c r="F372" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="G372" t="n">
+        <v>2040.2</v>
+      </c>
+      <c r="H372" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="I372" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J372" t="n">
+        <v>1991.19</v>
+      </c>
+      <c r="K372" t="n">
+        <v>-6.19</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N372" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>OFSS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>11729</v>
+      </c>
+      <c r="D373" t="n">
+        <v>12016.89</v>
+      </c>
+      <c r="E373" t="n">
+        <v>-287.89</v>
+      </c>
+      <c r="F373" t="n">
+        <v>11729</v>
+      </c>
+      <c r="G373" t="n">
+        <v>12045.84</v>
+      </c>
+      <c r="H373" t="n">
+        <v>-316.84</v>
+      </c>
+      <c r="I373" t="n">
+        <v>11355</v>
+      </c>
+      <c r="J373" t="n">
+        <v>11574.33</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-219.33</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N373" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>115.93</v>
+      </c>
+      <c r="D374" t="n">
+        <v>115.36</v>
+      </c>
+      <c r="E374" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F374" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="G374" t="n">
+        <v>118.18</v>
+      </c>
+      <c r="H374" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="I374" t="n">
+        <v>115.01</v>
+      </c>
+      <c r="J374" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="K374" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N374" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D375" t="n">
+        <v>1066.49</v>
+      </c>
+      <c r="E375" t="n">
+        <v>-18.49</v>
+      </c>
+      <c r="F375" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G375" t="n">
+        <v>1069.34</v>
+      </c>
+      <c r="H375" t="n">
+        <v>-21.34</v>
+      </c>
+      <c r="I375" t="n">
+        <v>1031.3</v>
+      </c>
+      <c r="J375" t="n">
+        <v>1039.48</v>
+      </c>
+      <c r="K375" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N375" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="D376" t="n">
+        <v>180.93</v>
+      </c>
+      <c r="E376" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="F376" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="G376" t="n">
+        <v>179.27</v>
+      </c>
+      <c r="H376" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="I376" t="n">
+        <v>171.58</v>
+      </c>
+      <c r="J376" t="n">
+        <v>172.49</v>
+      </c>
+      <c r="K376" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N376" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>POLICYBZR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>1798.3</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1890.44</v>
+      </c>
+      <c r="E377" t="n">
+        <v>-92.14</v>
+      </c>
+      <c r="F377" t="n">
+        <v>1815</v>
+      </c>
+      <c r="G377" t="n">
+        <v>1855.7</v>
+      </c>
+      <c r="H377" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="I377" t="n">
+        <v>1775</v>
+      </c>
+      <c r="J377" t="n">
+        <v>1767.89</v>
+      </c>
+      <c r="K377" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N377" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>11290</v>
+      </c>
+      <c r="D378" t="n">
+        <v>11838.88</v>
+      </c>
+      <c r="E378" t="n">
+        <v>-548.88</v>
+      </c>
+      <c r="F378" t="n">
+        <v>11290</v>
+      </c>
+      <c r="G378" t="n">
+        <v>11487.76</v>
+      </c>
+      <c r="H378" t="n">
+        <v>-197.76</v>
+      </c>
+      <c r="I378" t="n">
+        <v>10811</v>
+      </c>
+      <c r="J378" t="n">
+        <v>11222.55</v>
+      </c>
+      <c r="K378" t="n">
+        <v>-411.55</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N378" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>BHARTIARTL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D379" t="n">
+        <v>1978.19</v>
+      </c>
+      <c r="E379" t="n">
+        <v>-31.19</v>
+      </c>
+      <c r="F379" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G379" t="n">
+        <v>1983.6</v>
+      </c>
+      <c r="H379" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="I379" t="n">
+        <v>1923.4</v>
+      </c>
+      <c r="J379" t="n">
+        <v>1933.47</v>
+      </c>
+      <c r="K379" t="n">
+        <v>-10.07</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N379" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="D380" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="E380" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F380" t="n">
+        <v>187.33</v>
+      </c>
+      <c r="G380" t="n">
+        <v>191.81</v>
+      </c>
+      <c r="H380" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="I380" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="J380" t="n">
+        <v>184.69</v>
+      </c>
+      <c r="K380" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N380" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>331</v>
+      </c>
+      <c r="D381" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="E381" t="n">
+        <v>-33.63</v>
+      </c>
+      <c r="F381" t="n">
+        <v>331</v>
+      </c>
+      <c r="G381" t="n">
+        <v>338.43</v>
+      </c>
+      <c r="H381" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="I381" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="J381" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="K381" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>9.220000000000001</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1011.5</v>
+      </c>
+      <c r="D382" t="n">
+        <v>1054.61</v>
+      </c>
+      <c r="E382" t="n">
+        <v>-43.11</v>
+      </c>
+      <c r="F382" t="n">
+        <v>1019.9</v>
+      </c>
+      <c r="G382" t="n">
+        <v>1041.24</v>
+      </c>
+      <c r="H382" t="n">
+        <v>-21.34</v>
+      </c>
+      <c r="I382" t="n">
+        <v>992</v>
+      </c>
+      <c r="J382" t="n">
+        <v>996.3099999999999</v>
+      </c>
+      <c r="K382" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D383" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="E383" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F383" t="n">
+        <v>402</v>
+      </c>
+      <c r="G383" t="n">
+        <v>412.32</v>
+      </c>
+      <c r="H383" t="n">
+        <v>-10.32</v>
+      </c>
+      <c r="I383" t="n">
+        <v>392.05</v>
+      </c>
+      <c r="J383" t="n">
+        <v>389.69</v>
+      </c>
+      <c r="K383" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>4119</v>
+      </c>
+      <c r="D384" t="n">
+        <v>4205.1</v>
+      </c>
+      <c r="E384" t="n">
+        <v>-86.09999999999999</v>
+      </c>
+      <c r="F384" t="n">
+        <v>4125.3</v>
+      </c>
+      <c r="G384" t="n">
+        <v>4165.68</v>
+      </c>
+      <c r="H384" t="n">
+        <v>-40.38</v>
+      </c>
+      <c r="I384" t="n">
+        <v>4066.6</v>
+      </c>
+      <c r="J384" t="n">
+        <v>4113.74</v>
+      </c>
+      <c r="K384" t="n">
+        <v>-47.14</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>2232.5</v>
+      </c>
+      <c r="D385" t="n">
+        <v>2320.45</v>
+      </c>
+      <c r="E385" t="n">
+        <v>-87.95</v>
+      </c>
+      <c r="F385" t="n">
+        <v>2243.8</v>
+      </c>
+      <c r="G385" t="n">
+        <v>2279.86</v>
+      </c>
+      <c r="H385" t="n">
+        <v>-36.06</v>
+      </c>
+      <c r="I385" t="n">
+        <v>2190</v>
+      </c>
+      <c r="J385" t="n">
+        <v>2212.88</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-22.88</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>OIL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="D386" t="n">
+        <v>485.03</v>
+      </c>
+      <c r="E386" t="n">
+        <v>-17.53</v>
+      </c>
+      <c r="F386" t="n">
+        <v>479</v>
+      </c>
+      <c r="G386" t="n">
+        <v>482.04</v>
+      </c>
+      <c r="H386" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="I386" t="n">
+        <v>466.05</v>
+      </c>
+      <c r="J386" t="n">
+        <v>459.89</v>
+      </c>
+      <c r="K386" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1253.4</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1314.93</v>
+      </c>
+      <c r="E387" t="n">
+        <v>-61.53</v>
+      </c>
+      <c r="F387" t="n">
+        <v>1256.5</v>
+      </c>
+      <c r="G387" t="n">
+        <v>1284.43</v>
+      </c>
+      <c r="H387" t="n">
+        <v>-27.93</v>
+      </c>
+      <c r="I387" t="n">
+        <v>1240.5</v>
+      </c>
+      <c r="J387" t="n">
+        <v>1239.02</v>
+      </c>
+      <c r="K387" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>1892.8</v>
+      </c>
+      <c r="D388" t="n">
+        <v>1933.09</v>
+      </c>
+      <c r="E388" t="n">
+        <v>-40.29</v>
+      </c>
+      <c r="F388" t="n">
+        <v>1899.9</v>
+      </c>
+      <c r="G388" t="n">
+        <v>1936.83</v>
+      </c>
+      <c r="H388" t="n">
+        <v>-36.93</v>
+      </c>
+      <c r="I388" t="n">
+        <v>1870</v>
+      </c>
+      <c r="J388" t="n">
+        <v>1873.23</v>
+      </c>
+      <c r="K388" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>5624.5</v>
+      </c>
+      <c r="D389" t="n">
+        <v>5889.9</v>
+      </c>
+      <c r="E389" t="n">
+        <v>-265.4</v>
+      </c>
+      <c r="F389" t="n">
+        <v>5682</v>
+      </c>
+      <c r="G389" t="n">
+        <v>5765.53</v>
+      </c>
+      <c r="H389" t="n">
+        <v>-83.53</v>
+      </c>
+      <c r="I389" t="n">
+        <v>5590</v>
+      </c>
+      <c r="J389" t="n">
+        <v>5558.62</v>
+      </c>
+      <c r="K389" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>5655</v>
+      </c>
+      <c r="D390" t="n">
+        <v>5924.69</v>
+      </c>
+      <c r="E390" t="n">
+        <v>-269.69</v>
+      </c>
+      <c r="F390" t="n">
+        <v>5687</v>
+      </c>
+      <c r="G390" t="n">
+        <v>5788.15</v>
+      </c>
+      <c r="H390" t="n">
+        <v>-101.15</v>
+      </c>
+      <c r="I390" t="n">
+        <v>5570.5</v>
+      </c>
+      <c r="J390" t="n">
+        <v>5595.31</v>
+      </c>
+      <c r="K390" t="n">
+        <v>-24.81</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="D391" t="n">
+        <v>299.58</v>
+      </c>
+      <c r="E391" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="F391" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="G391" t="n">
+        <v>298.85</v>
+      </c>
+      <c r="H391" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="I391" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="J391" t="n">
+        <v>289.83</v>
+      </c>
+      <c r="K391" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>14990</v>
+      </c>
+      <c r="D392" t="n">
+        <v>16173.54</v>
+      </c>
+      <c r="E392" t="n">
+        <v>-1183.54</v>
+      </c>
+      <c r="F392" t="n">
+        <v>14990</v>
+      </c>
+      <c r="G392" t="n">
+        <v>15366.14</v>
+      </c>
+      <c r="H392" t="n">
+        <v>-376.14</v>
+      </c>
+      <c r="I392" t="n">
+        <v>14400</v>
+      </c>
+      <c r="J392" t="n">
+        <v>14814.18</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-414.18</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1051.05</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1068.98</v>
+      </c>
+      <c r="E393" t="n">
+        <v>-17.93</v>
+      </c>
+      <c r="F393" t="n">
+        <v>1057</v>
+      </c>
+      <c r="G393" t="n">
+        <v>1080.5</v>
+      </c>
+      <c r="H393" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="I393" t="n">
+        <v>1040.45</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1036.39</v>
+      </c>
+      <c r="K393" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DLF (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>682.95</v>
+      </c>
+      <c r="D394" t="n">
+        <v>682.71</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F394" t="n">
+        <v>688.2</v>
+      </c>
+      <c r="G394" t="n">
+        <v>699.5599999999999</v>
+      </c>
+      <c r="H394" t="n">
+        <v>-11.36</v>
+      </c>
+      <c r="I394" t="n">
+        <v>678.3</v>
+      </c>
+      <c r="J394" t="n">
+        <v>675.35</v>
+      </c>
+      <c r="K394" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>MAZDOCK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>2610</v>
+      </c>
+      <c r="D395" t="n">
+        <v>2685.8</v>
+      </c>
+      <c r="E395" t="n">
+        <v>-75.8</v>
+      </c>
+      <c r="F395" t="n">
+        <v>2621.7</v>
+      </c>
+      <c r="G395" t="n">
+        <v>2682.47</v>
+      </c>
+      <c r="H395" t="n">
+        <v>-60.77</v>
+      </c>
+      <c r="I395" t="n">
+        <v>2520</v>
+      </c>
+      <c r="J395" t="n">
+        <v>2574.1</v>
+      </c>
+      <c r="K395" t="n">
+        <v>-54.1</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D396" t="n">
+        <v>1239.31</v>
+      </c>
+      <c r="E396" t="n">
+        <v>-29.31</v>
+      </c>
+      <c r="F396" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G396" t="n">
+        <v>1242.31</v>
+      </c>
+      <c r="H396" t="n">
+        <v>-32.31</v>
+      </c>
+      <c r="I396" t="n">
+        <v>1186.4</v>
+      </c>
+      <c r="J396" t="n">
+        <v>1194.32</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>878</v>
+      </c>
+      <c r="D397" t="n">
+        <v>916.14</v>
+      </c>
+      <c r="E397" t="n">
+        <v>-38.14</v>
+      </c>
+      <c r="F397" t="n">
+        <v>881.75</v>
+      </c>
+      <c r="G397" t="n">
+        <v>898.11</v>
+      </c>
+      <c r="H397" t="n">
+        <v>-16.36</v>
+      </c>
+      <c r="I397" t="n">
+        <v>869</v>
+      </c>
+      <c r="J397" t="n">
+        <v>869.15</v>
+      </c>
+      <c r="K397" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D398" t="n">
+        <v>1412.44</v>
+      </c>
+      <c r="E398" t="n">
+        <v>-62.44</v>
+      </c>
+      <c r="F398" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G398" t="n">
+        <v>1393.26</v>
+      </c>
+      <c r="H398" t="n">
+        <v>-43.26</v>
+      </c>
+      <c r="I398" t="n">
+        <v>1328.1</v>
+      </c>
+      <c r="J398" t="n">
+        <v>1327.04</v>
+      </c>
+      <c r="K398" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>516</v>
+      </c>
+      <c r="D399" t="n">
+        <v>571.95</v>
+      </c>
+      <c r="E399" t="n">
+        <v>-55.95</v>
+      </c>
+      <c r="F399" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="G399" t="n">
+        <v>528.89</v>
+      </c>
+      <c r="H399" t="n">
+        <v>-10.49</v>
+      </c>
+      <c r="I399" t="n">
+        <v>511.3</v>
+      </c>
+      <c r="J399" t="n">
+        <v>509.99</v>
+      </c>
+      <c r="K399" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -19586,31 +19586,31 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>2004</v>
+        <v>2001.7</v>
       </c>
       <c r="D369" t="n">
         <v>2012.25</v>
       </c>
       <c r="E369" t="n">
-        <v>-8.25</v>
+        <v>-10.55</v>
       </c>
       <c r="F369" t="n">
-        <v>2011.7</v>
+        <v>2028.6</v>
       </c>
       <c r="G369" t="n">
         <v>2012.25</v>
       </c>
       <c r="H369" t="n">
-        <v>-0.55</v>
+        <v>16.35</v>
       </c>
       <c r="I369" t="n">
-        <v>1985</v>
+        <v>1995.3</v>
       </c>
       <c r="J369" t="n">
         <v>1979.81</v>
       </c>
       <c r="K369" t="n">
-        <v>5.19</v>
+        <v>15.49</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="370">
@@ -19638,31 +19638,31 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1048</v>
+        <v>1039.5</v>
       </c>
       <c r="D370" t="n">
         <v>1048.91</v>
       </c>
       <c r="E370" t="n">
-        <v>-0.91</v>
+        <v>-9.41</v>
       </c>
       <c r="F370" t="n">
-        <v>1048</v>
+        <v>1047.9</v>
       </c>
       <c r="G370" t="n">
         <v>1056.46</v>
       </c>
       <c r="H370" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="I370" t="n">
-        <v>1031.3</v>
+        <v>1032.1</v>
       </c>
       <c r="J370" t="n">
         <v>1033.1</v>
       </c>
       <c r="K370" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="371">
@@ -19690,31 +19690,31 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>115.93</v>
+        <v>115.86</v>
       </c>
       <c r="D371" t="n">
         <v>113.57</v>
       </c>
       <c r="E371" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="F371" t="n">
-        <v>116.9</v>
+        <v>117.03</v>
       </c>
       <c r="G371" t="n">
         <v>117.64</v>
       </c>
       <c r="H371" t="n">
-        <v>-0.74</v>
+        <v>-0.61</v>
       </c>
       <c r="I371" t="n">
-        <v>115.01</v>
+        <v>115</v>
       </c>
       <c r="J371" t="n">
         <v>115.06</v>
       </c>
       <c r="K371" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="372">
@@ -19742,31 +19742,31 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3443</v>
+        <v>3414.1</v>
       </c>
       <c r="D372" t="n">
         <v>3676.17</v>
       </c>
       <c r="E372" t="n">
-        <v>-233.17</v>
+        <v>-262.07</v>
       </c>
       <c r="F372" t="n">
-        <v>3443</v>
+        <v>3444.7</v>
       </c>
       <c r="G372" t="n">
         <v>3676.17</v>
       </c>
       <c r="H372" t="n">
-        <v>-233.17</v>
+        <v>-231.47</v>
       </c>
       <c r="I372" t="n">
-        <v>3396.8</v>
+        <v>3400</v>
       </c>
       <c r="J372" t="n">
         <v>3423.64</v>
       </c>
       <c r="K372" t="n">
-        <v>-26.84</v>
+        <v>-23.64</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>6.34</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="373">
@@ -19794,31 +19794,31 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>11729</v>
+        <v>11518</v>
       </c>
       <c r="D373" t="n">
         <v>11739.24</v>
       </c>
       <c r="E373" t="n">
-        <v>-10.24</v>
+        <v>-221.24</v>
       </c>
       <c r="F373" t="n">
-        <v>11729</v>
+        <v>11898</v>
       </c>
       <c r="G373" t="n">
         <v>11951.36</v>
       </c>
       <c r="H373" t="n">
-        <v>-222.36</v>
+        <v>-53.36</v>
       </c>
       <c r="I373" t="n">
-        <v>11355</v>
+        <v>11457</v>
       </c>
       <c r="J373" t="n">
         <v>11691.57</v>
       </c>
       <c r="K373" t="n">
-        <v>-336.57</v>
+        <v>-234.57</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>0.09</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="374">
@@ -19846,31 +19846,31 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>2139.3</v>
+        <v>2145</v>
       </c>
       <c r="D374" t="n">
         <v>2216.34</v>
       </c>
       <c r="E374" t="n">
-        <v>-77.04000000000001</v>
+        <v>-71.34</v>
       </c>
       <c r="F374" t="n">
-        <v>2151.8</v>
+        <v>2172.8</v>
       </c>
       <c r="G374" t="n">
         <v>2216.34</v>
       </c>
       <c r="H374" t="n">
-        <v>-64.54000000000001</v>
+        <v>-43.54</v>
       </c>
       <c r="I374" t="n">
-        <v>2124</v>
+        <v>2131.8</v>
       </c>
       <c r="J374" t="n">
         <v>2102.97</v>
       </c>
       <c r="K374" t="n">
-        <v>21.03</v>
+        <v>28.83</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="375">
@@ -19898,31 +19898,31 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>174.69</v>
+        <v>173.29</v>
       </c>
       <c r="D375" t="n">
         <v>176.9</v>
       </c>
       <c r="E375" t="n">
-        <v>-2.21</v>
+        <v>-3.61</v>
       </c>
       <c r="F375" t="n">
-        <v>174.69</v>
+        <v>173.66</v>
       </c>
       <c r="G375" t="n">
         <v>176.9</v>
       </c>
       <c r="H375" t="n">
-        <v>-2.21</v>
+        <v>-3.24</v>
       </c>
       <c r="I375" t="n">
-        <v>171.58</v>
+        <v>171.65</v>
       </c>
       <c r="J375" t="n">
         <v>172.04</v>
       </c>
       <c r="K375" t="n">
-        <v>-0.46</v>
+        <v>-0.39</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="376">
@@ -19950,31 +19950,31 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1947</v>
+        <v>1935</v>
       </c>
       <c r="D376" t="n">
         <v>1948.7</v>
       </c>
       <c r="E376" t="n">
-        <v>-1.7</v>
+        <v>-13.7</v>
       </c>
       <c r="F376" t="n">
-        <v>1947</v>
+        <v>1952.5</v>
       </c>
       <c r="G376" t="n">
         <v>1974.82</v>
       </c>
       <c r="H376" t="n">
-        <v>-27.82</v>
+        <v>-22.32</v>
       </c>
       <c r="I376" t="n">
-        <v>1923.4</v>
+        <v>1932.5</v>
       </c>
       <c r="J376" t="n">
         <v>1931.58</v>
       </c>
       <c r="K376" t="n">
-        <v>-8.18</v>
+        <v>0.92</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="377">
@@ -20002,31 +20002,31 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1011.5</v>
+        <v>990</v>
       </c>
       <c r="D377" t="n">
         <v>1027.75</v>
       </c>
       <c r="E377" t="n">
-        <v>-16.25</v>
+        <v>-37.75</v>
       </c>
       <c r="F377" t="n">
-        <v>1019.9</v>
+        <v>1015</v>
       </c>
       <c r="G377" t="n">
         <v>1027.75</v>
       </c>
       <c r="H377" t="n">
-        <v>-7.85</v>
+        <v>-12.75</v>
       </c>
       <c r="I377" t="n">
-        <v>992</v>
+        <v>988.3</v>
       </c>
       <c r="J377" t="n">
         <v>1003.04</v>
       </c>
       <c r="K377" t="n">
-        <v>-11.04</v>
+        <v>-14.74</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>1.58</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="378">
@@ -20054,31 +20054,31 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1798.3</v>
+        <v>1785</v>
       </c>
       <c r="D378" t="n">
         <v>1837.63</v>
       </c>
       <c r="E378" t="n">
-        <v>-39.33</v>
+        <v>-52.63</v>
       </c>
       <c r="F378" t="n">
-        <v>1815</v>
+        <v>1811.8</v>
       </c>
       <c r="G378" t="n">
         <v>1837.63</v>
       </c>
       <c r="H378" t="n">
-        <v>-22.63</v>
+        <v>-25.83</v>
       </c>
       <c r="I378" t="n">
-        <v>1775</v>
+        <v>1773.5</v>
       </c>
       <c r="J378" t="n">
         <v>1760.02</v>
       </c>
       <c r="K378" t="n">
-        <v>14.98</v>
+        <v>13.48</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="379">
@@ -20106,31 +20106,31 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3280</v>
+        <v>3268</v>
       </c>
       <c r="D379" t="n">
         <v>3158.38</v>
       </c>
       <c r="E379" t="n">
-        <v>121.62</v>
+        <v>109.62</v>
       </c>
       <c r="F379" t="n">
-        <v>3308.7</v>
+        <v>3289.7</v>
       </c>
       <c r="G379" t="n">
         <v>3343.9</v>
       </c>
       <c r="H379" t="n">
-        <v>-35.2</v>
+        <v>-54.2</v>
       </c>
       <c r="I379" t="n">
-        <v>3254.3</v>
+        <v>3180.1</v>
       </c>
       <c r="J379" t="n">
         <v>3271.27</v>
       </c>
       <c r="K379" t="n">
-        <v>-16.97</v>
+        <v>-91.17</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -20139,11 +20139,11 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N379" t="n">
-        <v>3.85</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="380">
@@ -20158,31 +20158,31 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>4119</v>
+        <v>4090</v>
       </c>
       <c r="D380" t="n">
         <v>4174.25</v>
       </c>
       <c r="E380" t="n">
-        <v>-55.25</v>
+        <v>-84.25</v>
       </c>
       <c r="F380" t="n">
-        <v>4125.3</v>
+        <v>4107.1</v>
       </c>
       <c r="G380" t="n">
         <v>4179.37</v>
       </c>
       <c r="H380" t="n">
-        <v>-54.07</v>
+        <v>-72.27</v>
       </c>
       <c r="I380" t="n">
-        <v>4066.6</v>
+        <v>4077.7</v>
       </c>
       <c r="J380" t="n">
         <v>4106.99</v>
       </c>
       <c r="K380" t="n">
-        <v>-40.39</v>
+        <v>-29.29</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="381">
@@ -20210,31 +20210,31 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>11290</v>
+        <v>11120</v>
       </c>
       <c r="D381" t="n">
         <v>11708.14</v>
       </c>
       <c r="E381" t="n">
-        <v>-418.14</v>
+        <v>-588.14</v>
       </c>
       <c r="F381" t="n">
-        <v>11290</v>
+        <v>11360</v>
       </c>
       <c r="G381" t="n">
         <v>11708.14</v>
       </c>
       <c r="H381" t="n">
-        <v>-418.14</v>
+        <v>-348.14</v>
       </c>
       <c r="I381" t="n">
-        <v>10811</v>
+        <v>11050</v>
       </c>
       <c r="J381" t="n">
         <v>11290</v>
       </c>
       <c r="K381" t="n">
-        <v>-479</v>
+        <v>-240</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>3.57</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="382">
@@ -20262,31 +20262,31 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>467.5</v>
+        <v>477</v>
       </c>
       <c r="D382" t="n">
         <v>471.88</v>
       </c>
       <c r="E382" t="n">
-        <v>-4.38</v>
+        <v>5.12</v>
       </c>
       <c r="F382" t="n">
-        <v>479</v>
+        <v>479.25</v>
       </c>
       <c r="G382" t="n">
         <v>471.88</v>
       </c>
       <c r="H382" t="n">
-        <v>7.12</v>
+        <v>7.37</v>
       </c>
       <c r="I382" t="n">
-        <v>466.05</v>
+        <v>472</v>
       </c>
       <c r="J382" t="n">
         <v>455.69</v>
       </c>
       <c r="K382" t="n">
-        <v>10.36</v>
+        <v>16.31</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="383">
@@ -20314,31 +20314,31 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2232.5</v>
+        <v>2207</v>
       </c>
       <c r="D383" t="n">
         <v>2288.38</v>
       </c>
       <c r="E383" t="n">
-        <v>-55.88</v>
+        <v>-81.38</v>
       </c>
       <c r="F383" t="n">
-        <v>2243.8</v>
+        <v>2235.4</v>
       </c>
       <c r="G383" t="n">
         <v>2292.81</v>
       </c>
       <c r="H383" t="n">
-        <v>-49.01</v>
+        <v>-57.41</v>
       </c>
       <c r="I383" t="n">
-        <v>2190</v>
+        <v>2206.1</v>
       </c>
       <c r="J383" t="n">
         <v>2232.5</v>
       </c>
       <c r="K383" t="n">
-        <v>-42.5</v>
+        <v>-26.4</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>2.44</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="384">
@@ -20366,31 +20366,31 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>186.98</v>
+        <v>183.6</v>
       </c>
       <c r="D384" t="n">
         <v>178.29</v>
       </c>
       <c r="E384" t="n">
-        <v>8.69</v>
+        <v>5.31</v>
       </c>
       <c r="F384" t="n">
-        <v>187.33</v>
+        <v>184.7</v>
       </c>
       <c r="G384" t="n">
         <v>188.14</v>
       </c>
       <c r="H384" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.44</v>
       </c>
       <c r="I384" t="n">
-        <v>181.4</v>
+        <v>182.02</v>
       </c>
       <c r="J384" t="n">
         <v>183.96</v>
       </c>
       <c r="K384" t="n">
-        <v>-2.56</v>
+        <v>-1.94</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>4.87</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="385">
@@ -20418,31 +20418,31 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>331</v>
+        <v>327.15</v>
       </c>
       <c r="D385" t="n">
         <v>358.33</v>
       </c>
       <c r="E385" t="n">
-        <v>-27.33</v>
+        <v>-31.18</v>
       </c>
       <c r="F385" t="n">
-        <v>331</v>
+        <v>329.5</v>
       </c>
       <c r="G385" t="n">
         <v>358.33</v>
       </c>
       <c r="H385" t="n">
-        <v>-27.33</v>
+        <v>-28.83</v>
       </c>
       <c r="I385" t="n">
-        <v>325.5</v>
+        <v>323</v>
       </c>
       <c r="J385" t="n">
         <v>331</v>
       </c>
       <c r="K385" t="n">
-        <v>-5.5</v>
+        <v>-8</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>7.63</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="386">
@@ -20470,31 +20470,31 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>397.8</v>
+        <v>403.3</v>
       </c>
       <c r="D386" t="n">
         <v>348.04</v>
       </c>
       <c r="E386" t="n">
-        <v>49.76</v>
+        <v>55.26</v>
       </c>
       <c r="F386" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G386" t="n">
         <v>404.41</v>
       </c>
       <c r="H386" t="n">
-        <v>-2.41</v>
+        <v>0.59</v>
       </c>
       <c r="I386" t="n">
-        <v>392.05</v>
+        <v>397.5</v>
       </c>
       <c r="J386" t="n">
         <v>395.59</v>
       </c>
       <c r="K386" t="n">
-        <v>-3.54</v>
+        <v>1.91</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>14.3</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="387">
@@ -20522,31 +20522,31 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1892.8</v>
+        <v>1873</v>
       </c>
       <c r="D387" t="n">
         <v>1895.63</v>
       </c>
       <c r="E387" t="n">
-        <v>-2.83</v>
+        <v>-22.63</v>
       </c>
       <c r="F387" t="n">
-        <v>1899.9</v>
+        <v>1900.8</v>
       </c>
       <c r="G387" t="n">
         <v>1903.48</v>
       </c>
       <c r="H387" t="n">
-        <v>-3.58</v>
+        <v>-2.68</v>
       </c>
       <c r="I387" t="n">
-        <v>1870</v>
+        <v>1869.6</v>
       </c>
       <c r="J387" t="n">
         <v>1861.23</v>
       </c>
       <c r="K387" t="n">
-        <v>8.77</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>0.15</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="388">
@@ -20574,31 +20574,31 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>292.5</v>
+        <v>295.95</v>
       </c>
       <c r="D388" t="n">
         <v>294.24</v>
       </c>
       <c r="E388" t="n">
-        <v>-1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F388" t="n">
-        <v>295.7</v>
+        <v>296.8</v>
       </c>
       <c r="G388" t="n">
         <v>294.24</v>
       </c>
       <c r="H388" t="n">
-        <v>1.46</v>
+        <v>2.56</v>
       </c>
       <c r="I388" t="n">
-        <v>291.6</v>
+        <v>291.4</v>
       </c>
       <c r="J388" t="n">
         <v>287.9</v>
       </c>
       <c r="K388" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="389">
@@ -20626,31 +20626,31 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1253.4</v>
+        <v>1251.3</v>
       </c>
       <c r="D389" t="n">
         <v>1287.49</v>
       </c>
       <c r="E389" t="n">
-        <v>-34.09</v>
+        <v>-36.19</v>
       </c>
       <c r="F389" t="n">
-        <v>1256.5</v>
+        <v>1261.6</v>
       </c>
       <c r="G389" t="n">
         <v>1287.49</v>
       </c>
       <c r="H389" t="n">
-        <v>-30.99</v>
+        <v>-25.89</v>
       </c>
       <c r="I389" t="n">
-        <v>1240.5</v>
+        <v>1245.1</v>
       </c>
       <c r="J389" t="n">
         <v>1234.86</v>
       </c>
       <c r="K389" t="n">
-        <v>5.64</v>
+        <v>10.24</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="390">
@@ -20678,31 +20678,31 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>5624.5</v>
+        <v>5685</v>
       </c>
       <c r="D390" t="n">
         <v>5765.14</v>
       </c>
       <c r="E390" t="n">
-        <v>-140.64</v>
+        <v>-80.14</v>
       </c>
       <c r="F390" t="n">
-        <v>5682</v>
+        <v>5728</v>
       </c>
       <c r="G390" t="n">
         <v>5765.14</v>
       </c>
       <c r="H390" t="n">
-        <v>-83.14</v>
+        <v>-37.14</v>
       </c>
       <c r="I390" t="n">
-        <v>5590</v>
+        <v>5650</v>
       </c>
       <c r="J390" t="n">
         <v>5516.7</v>
       </c>
       <c r="K390" t="n">
-        <v>73.3</v>
+        <v>133.3</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>2.44</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="391">
@@ -20730,31 +20730,31 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>5655</v>
+        <v>5694</v>
       </c>
       <c r="D391" t="n">
         <v>5808.2</v>
       </c>
       <c r="E391" t="n">
-        <v>-153.2</v>
+        <v>-114.2</v>
       </c>
       <c r="F391" t="n">
-        <v>5687</v>
+        <v>5725</v>
       </c>
       <c r="G391" t="n">
         <v>5808.2</v>
       </c>
       <c r="H391" t="n">
-        <v>-121.2</v>
+        <v>-83.2</v>
       </c>
       <c r="I391" t="n">
-        <v>5570.5</v>
+        <v>5646</v>
       </c>
       <c r="J391" t="n">
         <v>5555.36</v>
       </c>
       <c r="K391" t="n">
-        <v>15.14</v>
+        <v>90.64</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="392">
@@ -20782,31 +20782,31 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>2610</v>
+        <v>2540</v>
       </c>
       <c r="D392" t="n">
         <v>2621.75</v>
       </c>
       <c r="E392" t="n">
-        <v>-11.75</v>
+        <v>-81.75</v>
       </c>
       <c r="F392" t="n">
-        <v>2621.7</v>
+        <v>2572.6</v>
       </c>
       <c r="G392" t="n">
         <v>2621.75</v>
       </c>
       <c r="H392" t="n">
-        <v>-0.05</v>
+        <v>-49.15</v>
       </c>
       <c r="I392" t="n">
-        <v>2520</v>
+        <v>2523.4</v>
       </c>
       <c r="J392" t="n">
         <v>2552.86</v>
       </c>
       <c r="K392" t="n">
-        <v>-32.86</v>
+        <v>-29.46</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>0.45</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="393">
@@ -20834,31 +20834,31 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1210</v>
+        <v>1189.8</v>
       </c>
       <c r="D393" t="n">
         <v>1211.06</v>
       </c>
       <c r="E393" t="n">
-        <v>-1.06</v>
+        <v>-21.26</v>
       </c>
       <c r="F393" t="n">
-        <v>1210</v>
+        <v>1215.2</v>
       </c>
       <c r="G393" t="n">
         <v>1223.84</v>
       </c>
       <c r="H393" t="n">
-        <v>-13.84</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I393" t="n">
-        <v>1186.4</v>
+        <v>1189.8</v>
       </c>
       <c r="J393" t="n">
         <v>1196.92</v>
       </c>
       <c r="K393" t="n">
-        <v>-10.52</v>
+        <v>-7.12</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>0.09</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="394">
@@ -20886,31 +20886,31 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1051.05</v>
+        <v>1058.5</v>
       </c>
       <c r="D394" t="n">
         <v>1043.22</v>
       </c>
       <c r="E394" t="n">
-        <v>7.83</v>
+        <v>15.28</v>
       </c>
       <c r="F394" t="n">
-        <v>1057</v>
+        <v>1058.5</v>
       </c>
       <c r="G394" t="n">
         <v>1069.88</v>
       </c>
       <c r="H394" t="n">
-        <v>-12.88</v>
+        <v>-11.38</v>
       </c>
       <c r="I394" t="n">
-        <v>1040.45</v>
+        <v>1043.3</v>
       </c>
       <c r="J394" t="n">
         <v>1046.59</v>
       </c>
       <c r="K394" t="n">
-        <v>-6.14</v>
+        <v>-3.29</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>0.75</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="395">
@@ -20938,31 +20938,31 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>682.95</v>
+        <v>689</v>
       </c>
       <c r="D395" t="n">
         <v>668.76</v>
       </c>
       <c r="E395" t="n">
-        <v>14.19</v>
+        <v>20.24</v>
       </c>
       <c r="F395" t="n">
-        <v>688.2</v>
+        <v>689</v>
       </c>
       <c r="G395" t="n">
         <v>694.11</v>
       </c>
       <c r="H395" t="n">
-        <v>-5.91</v>
+        <v>-5.11</v>
       </c>
       <c r="I395" t="n">
-        <v>678.3</v>
+        <v>678.1</v>
       </c>
       <c r="J395" t="n">
         <v>678.96</v>
       </c>
       <c r="K395" t="n">
-        <v>-0.66</v>
+        <v>-0.86</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>2.12</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="396">
@@ -20990,31 +20990,31 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>14990</v>
+        <v>14570</v>
       </c>
       <c r="D396" t="n">
         <v>15955.71</v>
       </c>
       <c r="E396" t="n">
-        <v>-965.71</v>
+        <v>-1385.71</v>
       </c>
       <c r="F396" t="n">
-        <v>14990</v>
+        <v>15000</v>
       </c>
       <c r="G396" t="n">
         <v>15955.71</v>
       </c>
       <c r="H396" t="n">
-        <v>-965.71</v>
+        <v>-955.71</v>
       </c>
       <c r="I396" t="n">
-        <v>14400</v>
+        <v>14484</v>
       </c>
       <c r="J396" t="n">
         <v>14990</v>
       </c>
       <c r="K396" t="n">
-        <v>-590</v>
+        <v>-506</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>6.05</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="397">
@@ -21042,31 +21042,31 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D397" t="n">
         <v>1372.8</v>
       </c>
       <c r="E397" t="n">
-        <v>-22.8</v>
+        <v>-23.8</v>
       </c>
       <c r="F397" t="n">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="G397" t="n">
         <v>1372.8</v>
       </c>
       <c r="H397" t="n">
-        <v>-22.8</v>
+        <v>-12.8</v>
       </c>
       <c r="I397" t="n">
-        <v>1328.1</v>
+        <v>1336.7</v>
       </c>
       <c r="J397" t="n">
         <v>1315.92</v>
       </c>
       <c r="K397" t="n">
-        <v>12.18</v>
+        <v>20.78</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="398">
@@ -21094,31 +21094,31 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>878</v>
+        <v>870.45</v>
       </c>
       <c r="D398" t="n">
         <v>898.71</v>
       </c>
       <c r="E398" t="n">
-        <v>-20.71</v>
+        <v>-28.26</v>
       </c>
       <c r="F398" t="n">
-        <v>881.75</v>
+        <v>883.85</v>
       </c>
       <c r="G398" t="n">
         <v>898.71</v>
       </c>
       <c r="H398" t="n">
-        <v>-16.96</v>
+        <v>-14.86</v>
       </c>
       <c r="I398" t="n">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="J398" t="n">
         <v>863.09</v>
       </c>
       <c r="K398" t="n">
-        <v>5.91</v>
+        <v>-1.09</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="399">
@@ -21146,31 +21146,31 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>516</v>
+        <v>516.4</v>
       </c>
       <c r="D399" t="n">
         <v>559.89</v>
       </c>
       <c r="E399" t="n">
-        <v>-43.89</v>
+        <v>-43.49</v>
       </c>
       <c r="F399" t="n">
-        <v>518.4</v>
+        <v>524.2</v>
       </c>
       <c r="G399" t="n">
         <v>559.89</v>
       </c>
       <c r="H399" t="n">
-        <v>-41.49</v>
+        <v>-35.69</v>
       </c>
       <c r="I399" t="n">
-        <v>511.3</v>
+        <v>513.05</v>
       </c>
       <c r="J399" t="n">
         <v>506.16</v>
       </c>
       <c r="K399" t="n">
-        <v>5.14</v>
+        <v>6.89</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>7.84</v>
+        <v>7.77</v>
       </c>
     </row>
   </sheetData>
@@ -22740,31 +22740,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24334.55</v>
+        <v>24219.05</v>
       </c>
       <c r="D30" t="n">
         <v>24334.55</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-115.5</v>
       </c>
       <c r="F30" t="n">
-        <v>24334.55</v>
+        <v>24313</v>
       </c>
       <c r="G30" t="n">
         <v>24407.59</v>
       </c>
       <c r="H30" t="n">
-        <v>-73.04000000000001</v>
+        <v>-94.59</v>
       </c>
       <c r="I30" t="n">
-        <v>24115.45</v>
+        <v>24144.3</v>
       </c>
       <c r="J30" t="n">
         <v>24188.49</v>
       </c>
       <c r="K30" t="n">
-        <v>-73.04000000000001</v>
+        <v>-44.19</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="31">
@@ -22792,31 +22792,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>57514.2</v>
+        <v>57525.95</v>
       </c>
       <c r="D31" t="n">
         <v>57514.2</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="F31" t="n">
-        <v>57653.85</v>
+        <v>57873.75</v>
       </c>
       <c r="G31" t="n">
         <v>57701.61</v>
       </c>
       <c r="H31" t="n">
-        <v>-47.76</v>
+        <v>172.14</v>
       </c>
       <c r="I31" t="n">
-        <v>57231.25</v>
+        <v>57245.95</v>
       </c>
       <c r="J31" t="n">
         <v>57279.01</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.76</v>
+        <v>-33.06</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -42014,31 +42014,31 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3443</v>
+        <v>3414.1</v>
       </c>
       <c r="D369" t="n">
         <v>3721.73</v>
       </c>
       <c r="E369" t="n">
-        <v>-278.73</v>
+        <v>-307.63</v>
       </c>
       <c r="F369" t="n">
-        <v>3443</v>
+        <v>3444.7</v>
       </c>
       <c r="G369" t="n">
         <v>3498.62</v>
       </c>
       <c r="H369" t="n">
-        <v>-55.62</v>
+        <v>-53.92</v>
       </c>
       <c r="I369" t="n">
-        <v>3396.8</v>
+        <v>3400</v>
       </c>
       <c r="J369" t="n">
         <v>3426</v>
       </c>
       <c r="K369" t="n">
-        <v>-29.2</v>
+        <v>-26</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>7.49</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="370">
@@ -42066,31 +42066,31 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>2139.3</v>
+        <v>2145</v>
       </c>
       <c r="D370" t="n">
         <v>2259.34</v>
       </c>
       <c r="E370" t="n">
-        <v>-120.04</v>
+        <v>-114.34</v>
       </c>
       <c r="F370" t="n">
-        <v>2151.8</v>
+        <v>2172.8</v>
       </c>
       <c r="G370" t="n">
         <v>2188.32</v>
       </c>
       <c r="H370" t="n">
-        <v>-36.52</v>
+        <v>-15.52</v>
       </c>
       <c r="I370" t="n">
-        <v>2124</v>
+        <v>2131.8</v>
       </c>
       <c r="J370" t="n">
         <v>2117.73</v>
       </c>
       <c r="K370" t="n">
-        <v>6.27</v>
+        <v>14.07</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="371">
@@ -42118,31 +42118,31 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3280</v>
+        <v>3268</v>
       </c>
       <c r="D371" t="n">
         <v>3266.25</v>
       </c>
       <c r="E371" t="n">
-        <v>13.75</v>
+        <v>1.75</v>
       </c>
       <c r="F371" t="n">
-        <v>3308.7</v>
+        <v>3289.7</v>
       </c>
       <c r="G371" t="n">
         <v>3401.82</v>
       </c>
       <c r="H371" t="n">
-        <v>-93.12</v>
+        <v>-112.12</v>
       </c>
       <c r="I371" t="n">
-        <v>3254.3</v>
+        <v>3180.1</v>
       </c>
       <c r="J371" t="n">
         <v>3211.51</v>
       </c>
       <c r="K371" t="n">
-        <v>42.79</v>
+        <v>-31.41</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>0.42</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="372">
@@ -42170,31 +42170,31 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>2004</v>
+        <v>2001.7</v>
       </c>
       <c r="D372" t="n">
         <v>2041.17</v>
       </c>
       <c r="E372" t="n">
-        <v>-37.17</v>
+        <v>-39.47</v>
       </c>
       <c r="F372" t="n">
-        <v>2011.7</v>
+        <v>2028.6</v>
       </c>
       <c r="G372" t="n">
         <v>2040.2</v>
       </c>
       <c r="H372" t="n">
-        <v>-28.5</v>
+        <v>-11.6</v>
       </c>
       <c r="I372" t="n">
-        <v>1985</v>
+        <v>1995.3</v>
       </c>
       <c r="J372" t="n">
         <v>1991.19</v>
       </c>
       <c r="K372" t="n">
-        <v>-6.19</v>
+        <v>4.11</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="373">
@@ -42222,31 +42222,31 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>11729</v>
+        <v>11518</v>
       </c>
       <c r="D373" t="n">
         <v>12016.89</v>
       </c>
       <c r="E373" t="n">
-        <v>-287.89</v>
+        <v>-498.89</v>
       </c>
       <c r="F373" t="n">
-        <v>11729</v>
+        <v>11898</v>
       </c>
       <c r="G373" t="n">
         <v>12045.84</v>
       </c>
       <c r="H373" t="n">
-        <v>-316.84</v>
+        <v>-147.84</v>
       </c>
       <c r="I373" t="n">
-        <v>11355</v>
+        <v>11457</v>
       </c>
       <c r="J373" t="n">
         <v>11574.33</v>
       </c>
       <c r="K373" t="n">
-        <v>-219.33</v>
+        <v>-117.33</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>2.4</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="374">
@@ -42274,31 +42274,31 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>115.93</v>
+        <v>115.86</v>
       </c>
       <c r="D374" t="n">
         <v>115.36</v>
       </c>
       <c r="E374" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="F374" t="n">
-        <v>116.9</v>
+        <v>117.03</v>
       </c>
       <c r="G374" t="n">
         <v>118.18</v>
       </c>
       <c r="H374" t="n">
-        <v>-1.28</v>
+        <v>-1.15</v>
       </c>
       <c r="I374" t="n">
-        <v>115.01</v>
+        <v>115</v>
       </c>
       <c r="J374" t="n">
         <v>115.06</v>
       </c>
       <c r="K374" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="375">
@@ -42326,31 +42326,31 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1048</v>
+        <v>1039.5</v>
       </c>
       <c r="D375" t="n">
         <v>1066.49</v>
       </c>
       <c r="E375" t="n">
-        <v>-18.49</v>
+        <v>-26.99</v>
       </c>
       <c r="F375" t="n">
-        <v>1048</v>
+        <v>1047.9</v>
       </c>
       <c r="G375" t="n">
         <v>1069.34</v>
       </c>
       <c r="H375" t="n">
-        <v>-21.34</v>
+        <v>-21.44</v>
       </c>
       <c r="I375" t="n">
-        <v>1031.3</v>
+        <v>1032.1</v>
       </c>
       <c r="J375" t="n">
         <v>1039.48</v>
       </c>
       <c r="K375" t="n">
-        <v>-8.18</v>
+        <v>-7.38</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -42359,11 +42359,11 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N375" t="n">
-        <v>1.73</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="376">
@@ -42378,31 +42378,31 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>174.69</v>
+        <v>173.29</v>
       </c>
       <c r="D376" t="n">
         <v>180.93</v>
       </c>
       <c r="E376" t="n">
-        <v>-6.24</v>
+        <v>-7.64</v>
       </c>
       <c r="F376" t="n">
-        <v>174.69</v>
+        <v>173.66</v>
       </c>
       <c r="G376" t="n">
         <v>179.27</v>
       </c>
       <c r="H376" t="n">
-        <v>-4.58</v>
+        <v>-5.61</v>
       </c>
       <c r="I376" t="n">
-        <v>171.58</v>
+        <v>171.65</v>
       </c>
       <c r="J376" t="n">
         <v>172.49</v>
       </c>
       <c r="K376" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>3.45</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="377">
@@ -42430,31 +42430,31 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1798.3</v>
+        <v>1785</v>
       </c>
       <c r="D377" t="n">
         <v>1890.44</v>
       </c>
       <c r="E377" t="n">
-        <v>-92.14</v>
+        <v>-105.44</v>
       </c>
       <c r="F377" t="n">
-        <v>1815</v>
+        <v>1811.8</v>
       </c>
       <c r="G377" t="n">
         <v>1855.7</v>
       </c>
       <c r="H377" t="n">
-        <v>-40.7</v>
+        <v>-43.9</v>
       </c>
       <c r="I377" t="n">
-        <v>1775</v>
+        <v>1773.5</v>
       </c>
       <c r="J377" t="n">
         <v>1767.89</v>
       </c>
       <c r="K377" t="n">
-        <v>7.11</v>
+        <v>5.61</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>4.87</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="378">
@@ -42482,31 +42482,31 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>11290</v>
+        <v>11120</v>
       </c>
       <c r="D378" t="n">
         <v>11838.88</v>
       </c>
       <c r="E378" t="n">
-        <v>-548.88</v>
+        <v>-718.88</v>
       </c>
       <c r="F378" t="n">
-        <v>11290</v>
+        <v>11360</v>
       </c>
       <c r="G378" t="n">
         <v>11487.76</v>
       </c>
       <c r="H378" t="n">
-        <v>-197.76</v>
+        <v>-127.76</v>
       </c>
       <c r="I378" t="n">
-        <v>10811</v>
+        <v>11050</v>
       </c>
       <c r="J378" t="n">
         <v>11222.55</v>
       </c>
       <c r="K378" t="n">
-        <v>-411.55</v>
+        <v>-172.55</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>4.64</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="379">
@@ -42534,31 +42534,31 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1947</v>
+        <v>1935</v>
       </c>
       <c r="D379" t="n">
         <v>1978.19</v>
       </c>
       <c r="E379" t="n">
-        <v>-31.19</v>
+        <v>-43.19</v>
       </c>
       <c r="F379" t="n">
-        <v>1947</v>
+        <v>1952.5</v>
       </c>
       <c r="G379" t="n">
         <v>1983.6</v>
       </c>
       <c r="H379" t="n">
-        <v>-36.6</v>
+        <v>-31.1</v>
       </c>
       <c r="I379" t="n">
-        <v>1923.4</v>
+        <v>1932.5</v>
       </c>
       <c r="J379" t="n">
         <v>1933.47</v>
       </c>
       <c r="K379" t="n">
-        <v>-10.07</v>
+        <v>-0.97</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="380">
@@ -42586,31 +42586,31 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>186.98</v>
+        <v>183.6</v>
       </c>
       <c r="D380" t="n">
         <v>182.28</v>
       </c>
       <c r="E380" t="n">
-        <v>4.7</v>
+        <v>1.32</v>
       </c>
       <c r="F380" t="n">
-        <v>187.33</v>
+        <v>184.7</v>
       </c>
       <c r="G380" t="n">
         <v>191.81</v>
       </c>
       <c r="H380" t="n">
-        <v>-4.48</v>
+        <v>-7.11</v>
       </c>
       <c r="I380" t="n">
-        <v>181.4</v>
+        <v>182.02</v>
       </c>
       <c r="J380" t="n">
         <v>184.69</v>
       </c>
       <c r="K380" t="n">
-        <v>-3.29</v>
+        <v>-2.67</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>2.58</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="381">
@@ -42638,31 +42638,31 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>331</v>
+        <v>327.15</v>
       </c>
       <c r="D381" t="n">
         <v>364.63</v>
       </c>
       <c r="E381" t="n">
-        <v>-33.63</v>
+        <v>-37.48</v>
       </c>
       <c r="F381" t="n">
-        <v>331</v>
+        <v>329.5</v>
       </c>
       <c r="G381" t="n">
         <v>338.43</v>
       </c>
       <c r="H381" t="n">
-        <v>-7.43</v>
+        <v>-8.93</v>
       </c>
       <c r="I381" t="n">
-        <v>325.5</v>
+        <v>323</v>
       </c>
       <c r="J381" t="n">
         <v>327.78</v>
       </c>
       <c r="K381" t="n">
-        <v>-2.28</v>
+        <v>-4.78</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>9.220000000000001</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="382">
@@ -42690,31 +42690,31 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1011.5</v>
+        <v>990</v>
       </c>
       <c r="D382" t="n">
         <v>1054.61</v>
       </c>
       <c r="E382" t="n">
-        <v>-43.11</v>
+        <v>-64.61</v>
       </c>
       <c r="F382" t="n">
-        <v>1019.9</v>
+        <v>1015</v>
       </c>
       <c r="G382" t="n">
         <v>1041.24</v>
       </c>
       <c r="H382" t="n">
-        <v>-21.34</v>
+        <v>-26.24</v>
       </c>
       <c r="I382" t="n">
-        <v>992</v>
+        <v>988.3</v>
       </c>
       <c r="J382" t="n">
         <v>996.3099999999999</v>
       </c>
       <c r="K382" t="n">
-        <v>-4.31</v>
+        <v>-8.01</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>4.09</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="383">
@@ -42742,31 +42742,31 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>397.8</v>
+        <v>403.3</v>
       </c>
       <c r="D383" t="n">
         <v>359.7</v>
       </c>
       <c r="E383" t="n">
-        <v>38.1</v>
+        <v>43.6</v>
       </c>
       <c r="F383" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G383" t="n">
         <v>412.32</v>
       </c>
       <c r="H383" t="n">
-        <v>-10.32</v>
+        <v>-7.32</v>
       </c>
       <c r="I383" t="n">
-        <v>392.05</v>
+        <v>397.5</v>
       </c>
       <c r="J383" t="n">
         <v>389.69</v>
       </c>
       <c r="K383" t="n">
-        <v>2.36</v>
+        <v>7.81</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>10.59</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="384">
@@ -42794,31 +42794,31 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>4119</v>
+        <v>4090</v>
       </c>
       <c r="D384" t="n">
         <v>4205.1</v>
       </c>
       <c r="E384" t="n">
-        <v>-86.09999999999999</v>
+        <v>-115.1</v>
       </c>
       <c r="F384" t="n">
-        <v>4125.3</v>
+        <v>4107.1</v>
       </c>
       <c r="G384" t="n">
         <v>4165.68</v>
       </c>
       <c r="H384" t="n">
-        <v>-40.38</v>
+        <v>-58.58</v>
       </c>
       <c r="I384" t="n">
-        <v>4066.6</v>
+        <v>4077.7</v>
       </c>
       <c r="J384" t="n">
         <v>4113.74</v>
       </c>
       <c r="K384" t="n">
-        <v>-47.14</v>
+        <v>-36.04</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -42827,11 +42827,11 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N384" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="385">
@@ -42846,31 +42846,31 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>2232.5</v>
+        <v>2207</v>
       </c>
       <c r="D385" t="n">
         <v>2320.45</v>
       </c>
       <c r="E385" t="n">
-        <v>-87.95</v>
+        <v>-113.45</v>
       </c>
       <c r="F385" t="n">
-        <v>2243.8</v>
+        <v>2235.4</v>
       </c>
       <c r="G385" t="n">
         <v>2279.86</v>
       </c>
       <c r="H385" t="n">
-        <v>-36.06</v>
+        <v>-44.46</v>
       </c>
       <c r="I385" t="n">
-        <v>2190</v>
+        <v>2206.1</v>
       </c>
       <c r="J385" t="n">
         <v>2212.88</v>
       </c>
       <c r="K385" t="n">
-        <v>-22.88</v>
+        <v>-6.78</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>3.79</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="386">
@@ -42898,31 +42898,31 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>467.5</v>
+        <v>477</v>
       </c>
       <c r="D386" t="n">
         <v>485.03</v>
       </c>
       <c r="E386" t="n">
-        <v>-17.53</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="F386" t="n">
-        <v>479</v>
+        <v>479.25</v>
       </c>
       <c r="G386" t="n">
         <v>482.04</v>
       </c>
       <c r="H386" t="n">
-        <v>-3.04</v>
+        <v>-2.79</v>
       </c>
       <c r="I386" t="n">
-        <v>466.05</v>
+        <v>472</v>
       </c>
       <c r="J386" t="n">
         <v>459.89</v>
       </c>
       <c r="K386" t="n">
-        <v>6.16</v>
+        <v>12.11</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -42931,11 +42931,11 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N386" t="n">
-        <v>3.61</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="387">
@@ -42950,31 +42950,31 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1253.4</v>
+        <v>1251.3</v>
       </c>
       <c r="D387" t="n">
         <v>1314.93</v>
       </c>
       <c r="E387" t="n">
-        <v>-61.53</v>
+        <v>-63.63</v>
       </c>
       <c r="F387" t="n">
-        <v>1256.5</v>
+        <v>1261.6</v>
       </c>
       <c r="G387" t="n">
         <v>1284.43</v>
       </c>
       <c r="H387" t="n">
-        <v>-27.93</v>
+        <v>-22.83</v>
       </c>
       <c r="I387" t="n">
-        <v>1240.5</v>
+        <v>1245.1</v>
       </c>
       <c r="J387" t="n">
         <v>1239.02</v>
       </c>
       <c r="K387" t="n">
-        <v>1.48</v>
+        <v>6.08</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>4.68</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="388">
@@ -43002,31 +43002,31 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1892.8</v>
+        <v>1873</v>
       </c>
       <c r="D388" t="n">
         <v>1933.09</v>
       </c>
       <c r="E388" t="n">
-        <v>-40.29</v>
+        <v>-60.09</v>
       </c>
       <c r="F388" t="n">
-        <v>1899.9</v>
+        <v>1900.8</v>
       </c>
       <c r="G388" t="n">
         <v>1936.83</v>
       </c>
       <c r="H388" t="n">
-        <v>-36.93</v>
+        <v>-36.03</v>
       </c>
       <c r="I388" t="n">
-        <v>1870</v>
+        <v>1869.6</v>
       </c>
       <c r="J388" t="n">
         <v>1873.23</v>
       </c>
       <c r="K388" t="n">
-        <v>-3.23</v>
+        <v>-3.63</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -43035,11 +43035,11 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N388" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="389">
@@ -43054,31 +43054,31 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>5624.5</v>
+        <v>5685</v>
       </c>
       <c r="D389" t="n">
         <v>5889.9</v>
       </c>
       <c r="E389" t="n">
-        <v>-265.4</v>
+        <v>-204.9</v>
       </c>
       <c r="F389" t="n">
-        <v>5682</v>
+        <v>5728</v>
       </c>
       <c r="G389" t="n">
         <v>5765.53</v>
       </c>
       <c r="H389" t="n">
-        <v>-83.53</v>
+        <v>-37.53</v>
       </c>
       <c r="I389" t="n">
-        <v>5590</v>
+        <v>5650</v>
       </c>
       <c r="J389" t="n">
         <v>5558.62</v>
       </c>
       <c r="K389" t="n">
-        <v>31.38</v>
+        <v>91.38</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>4.51</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="390">
@@ -43106,31 +43106,31 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>5655</v>
+        <v>5694</v>
       </c>
       <c r="D390" t="n">
         <v>5924.69</v>
       </c>
       <c r="E390" t="n">
-        <v>-269.69</v>
+        <v>-230.69</v>
       </c>
       <c r="F390" t="n">
-        <v>5687</v>
+        <v>5725</v>
       </c>
       <c r="G390" t="n">
         <v>5788.15</v>
       </c>
       <c r="H390" t="n">
-        <v>-101.15</v>
+        <v>-63.15</v>
       </c>
       <c r="I390" t="n">
-        <v>5570.5</v>
+        <v>5646</v>
       </c>
       <c r="J390" t="n">
         <v>5595.31</v>
       </c>
       <c r="K390" t="n">
-        <v>-24.81</v>
+        <v>50.69</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>4.55</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="391">
@@ -43158,31 +43158,31 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>292.5</v>
+        <v>295.95</v>
       </c>
       <c r="D391" t="n">
         <v>299.58</v>
       </c>
       <c r="E391" t="n">
-        <v>-7.08</v>
+        <v>-3.63</v>
       </c>
       <c r="F391" t="n">
-        <v>295.7</v>
+        <v>296.8</v>
       </c>
       <c r="G391" t="n">
         <v>298.85</v>
       </c>
       <c r="H391" t="n">
-        <v>-3.15</v>
+        <v>-2.05</v>
       </c>
       <c r="I391" t="n">
-        <v>291.6</v>
+        <v>291.4</v>
       </c>
       <c r="J391" t="n">
         <v>289.83</v>
       </c>
       <c r="K391" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>2.36</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="392">
@@ -43210,31 +43210,31 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>14990</v>
+        <v>14570</v>
       </c>
       <c r="D392" t="n">
         <v>16173.54</v>
       </c>
       <c r="E392" t="n">
-        <v>-1183.54</v>
+        <v>-1603.54</v>
       </c>
       <c r="F392" t="n">
-        <v>14990</v>
+        <v>15000</v>
       </c>
       <c r="G392" t="n">
         <v>15366.14</v>
       </c>
       <c r="H392" t="n">
-        <v>-376.14</v>
+        <v>-366.14</v>
       </c>
       <c r="I392" t="n">
-        <v>14400</v>
+        <v>14484</v>
       </c>
       <c r="J392" t="n">
         <v>14814.18</v>
       </c>
       <c r="K392" t="n">
-        <v>-414.18</v>
+        <v>-330.18</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>7.32</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="393">
@@ -43262,31 +43262,31 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1051.05</v>
+        <v>1058.5</v>
       </c>
       <c r="D393" t="n">
         <v>1068.98</v>
       </c>
       <c r="E393" t="n">
-        <v>-17.93</v>
+        <v>-10.48</v>
       </c>
       <c r="F393" t="n">
-        <v>1057</v>
+        <v>1058.5</v>
       </c>
       <c r="G393" t="n">
         <v>1080.5</v>
       </c>
       <c r="H393" t="n">
-        <v>-23.5</v>
+        <v>-22</v>
       </c>
       <c r="I393" t="n">
-        <v>1040.45</v>
+        <v>1043.3</v>
       </c>
       <c r="J393" t="n">
         <v>1036.39</v>
       </c>
       <c r="K393" t="n">
-        <v>4.06</v>
+        <v>6.91</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>1.68</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="394">
@@ -43314,31 +43314,31 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>682.95</v>
+        <v>689</v>
       </c>
       <c r="D394" t="n">
         <v>682.71</v>
       </c>
       <c r="E394" t="n">
-        <v>0.24</v>
+        <v>6.29</v>
       </c>
       <c r="F394" t="n">
-        <v>688.2</v>
+        <v>689</v>
       </c>
       <c r="G394" t="n">
         <v>699.5599999999999</v>
       </c>
       <c r="H394" t="n">
-        <v>-11.36</v>
+        <v>-10.56</v>
       </c>
       <c r="I394" t="n">
-        <v>678.3</v>
+        <v>678.1</v>
       </c>
       <c r="J394" t="n">
         <v>675.35</v>
       </c>
       <c r="K394" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>0.04</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="395">
@@ -43366,31 +43366,31 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>2610</v>
+        <v>2540</v>
       </c>
       <c r="D395" t="n">
         <v>2685.8</v>
       </c>
       <c r="E395" t="n">
-        <v>-75.8</v>
+        <v>-145.8</v>
       </c>
       <c r="F395" t="n">
-        <v>2621.7</v>
+        <v>2572.6</v>
       </c>
       <c r="G395" t="n">
         <v>2682.47</v>
       </c>
       <c r="H395" t="n">
-        <v>-60.77</v>
+        <v>-109.87</v>
       </c>
       <c r="I395" t="n">
-        <v>2520</v>
+        <v>2523.4</v>
       </c>
       <c r="J395" t="n">
         <v>2574.1</v>
       </c>
       <c r="K395" t="n">
-        <v>-54.1</v>
+        <v>-50.7</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>2.82</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="396">
@@ -43418,31 +43418,31 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>1210</v>
+        <v>1189.8</v>
       </c>
       <c r="D396" t="n">
         <v>1239.31</v>
       </c>
       <c r="E396" t="n">
-        <v>-29.31</v>
+        <v>-49.51</v>
       </c>
       <c r="F396" t="n">
-        <v>1210</v>
+        <v>1215.2</v>
       </c>
       <c r="G396" t="n">
         <v>1242.31</v>
       </c>
       <c r="H396" t="n">
-        <v>-32.31</v>
+        <v>-27.11</v>
       </c>
       <c r="I396" t="n">
-        <v>1186.4</v>
+        <v>1189.8</v>
       </c>
       <c r="J396" t="n">
         <v>1194.32</v>
       </c>
       <c r="K396" t="n">
-        <v>-7.92</v>
+        <v>-4.52</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -43451,11 +43451,11 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N396" t="n">
-        <v>2.37</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="397">
@@ -43470,31 +43470,31 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>878</v>
+        <v>870.45</v>
       </c>
       <c r="D397" t="n">
         <v>916.14</v>
       </c>
       <c r="E397" t="n">
-        <v>-38.14</v>
+        <v>-45.69</v>
       </c>
       <c r="F397" t="n">
-        <v>881.75</v>
+        <v>883.85</v>
       </c>
       <c r="G397" t="n">
         <v>898.11</v>
       </c>
       <c r="H397" t="n">
-        <v>-16.36</v>
+        <v>-14.26</v>
       </c>
       <c r="I397" t="n">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="J397" t="n">
         <v>869.15</v>
       </c>
       <c r="K397" t="n">
-        <v>-0.15</v>
+        <v>-7.15</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>4.16</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="398">
@@ -43522,31 +43522,31 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D398" t="n">
         <v>1412.44</v>
       </c>
       <c r="E398" t="n">
-        <v>-62.44</v>
+        <v>-63.44</v>
       </c>
       <c r="F398" t="n">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="G398" t="n">
         <v>1393.26</v>
       </c>
       <c r="H398" t="n">
-        <v>-43.26</v>
+        <v>-33.26</v>
       </c>
       <c r="I398" t="n">
-        <v>1328.1</v>
+        <v>1336.7</v>
       </c>
       <c r="J398" t="n">
         <v>1327.04</v>
       </c>
       <c r="K398" t="n">
-        <v>1.06</v>
+        <v>9.66</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>4.42</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="399">
@@ -43574,31 +43574,31 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>516</v>
+        <v>516.4</v>
       </c>
       <c r="D399" t="n">
         <v>571.95</v>
       </c>
       <c r="E399" t="n">
-        <v>-55.95</v>
+        <v>-55.55</v>
       </c>
       <c r="F399" t="n">
-        <v>518.4</v>
+        <v>524.2</v>
       </c>
       <c r="G399" t="n">
         <v>528.89</v>
       </c>
       <c r="H399" t="n">
-        <v>-10.49</v>
+        <v>-4.69</v>
       </c>
       <c r="I399" t="n">
-        <v>511.3</v>
+        <v>513.05</v>
       </c>
       <c r="J399" t="n">
         <v>509.99</v>
       </c>
       <c r="K399" t="n">
-        <v>1.31</v>
+        <v>3.06</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>9.779999999999999</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N399"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21184,6 +21184,1618 @@
       </c>
       <c r="N399" t="n">
         <v>7.77</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D400" t="n">
+        <v>2015.46</v>
+      </c>
+      <c r="E400" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="F400" t="n">
+        <v>2024.9</v>
+      </c>
+      <c r="G400" t="n">
+        <v>2015.46</v>
+      </c>
+      <c r="H400" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="I400" t="n">
+        <v>2005.5</v>
+      </c>
+      <c r="J400" t="n">
+        <v>1964.76</v>
+      </c>
+      <c r="K400" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D401" t="n">
+        <v>1050.91</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F401" t="n">
+        <v>1062.3</v>
+      </c>
+      <c r="G401" t="n">
+        <v>1058.98</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="J401" t="n">
+        <v>1035.78</v>
+      </c>
+      <c r="K401" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N401" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D402" t="n">
+        <v>1234.38</v>
+      </c>
+      <c r="E402" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="F402" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="G402" t="n">
+        <v>1261.24</v>
+      </c>
+      <c r="H402" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1250.7</v>
+      </c>
+      <c r="J402" t="n">
+        <v>1233.35</v>
+      </c>
+      <c r="K402" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2159</v>
+      </c>
+      <c r="D403" t="n">
+        <v>2106.22</v>
+      </c>
+      <c r="E403" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="F403" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G403" t="n">
+        <v>2177.62</v>
+      </c>
+      <c r="H403" t="n">
+        <v>-18.62</v>
+      </c>
+      <c r="I403" t="n">
+        <v>2119.7</v>
+      </c>
+      <c r="J403" t="n">
+        <v>2130.04</v>
+      </c>
+      <c r="K403" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D404" t="n">
+        <v>120</v>
+      </c>
+      <c r="E404" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F404" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G404" t="n">
+        <v>120</v>
+      </c>
+      <c r="H404" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I404" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J404" t="n">
+        <v>115.09</v>
+      </c>
+      <c r="K404" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D405" t="n">
+        <v>3494.24</v>
+      </c>
+      <c r="E405" t="n">
+        <v>-144.24</v>
+      </c>
+      <c r="F405" t="n">
+        <v>3355</v>
+      </c>
+      <c r="G405" t="n">
+        <v>3494.24</v>
+      </c>
+      <c r="H405" t="n">
+        <v>-139.24</v>
+      </c>
+      <c r="I405" t="n">
+        <v>3243.3</v>
+      </c>
+      <c r="J405" t="n">
+        <v>3320.18</v>
+      </c>
+      <c r="K405" t="n">
+        <v>-76.88</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1801.6</v>
+      </c>
+      <c r="E406" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F406" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G406" t="n">
+        <v>1855.29</v>
+      </c>
+      <c r="H406" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1806.3</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1814.74</v>
+      </c>
+      <c r="K406" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="D407" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="E407" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F407" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G407" t="n">
+        <v>180.12</v>
+      </c>
+      <c r="H407" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I407" t="n">
+        <v>175.41</v>
+      </c>
+      <c r="J407" t="n">
+        <v>176.17</v>
+      </c>
+      <c r="K407" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>187.52</v>
+      </c>
+      <c r="D408" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="E408" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="F408" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="G408" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="H408" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I408" t="n">
+        <v>187.12</v>
+      </c>
+      <c r="J408" t="n">
+        <v>182.61</v>
+      </c>
+      <c r="K408" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>469.15</v>
+      </c>
+      <c r="D409" t="n">
+        <v>478.03</v>
+      </c>
+      <c r="E409" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="F409" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="G409" t="n">
+        <v>478.03</v>
+      </c>
+      <c r="H409" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="I409" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J409" t="n">
+        <v>452.42</v>
+      </c>
+      <c r="K409" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D410" t="n">
+        <v>11093.82</v>
+      </c>
+      <c r="E410" t="n">
+        <v>446.18</v>
+      </c>
+      <c r="F410" t="n">
+        <v>11540</v>
+      </c>
+      <c r="G410" t="n">
+        <v>11689.23</v>
+      </c>
+      <c r="H410" t="n">
+        <v>-149.23</v>
+      </c>
+      <c r="I410" t="n">
+        <v>11223</v>
+      </c>
+      <c r="J410" t="n">
+        <v>11484.65</v>
+      </c>
+      <c r="K410" t="n">
+        <v>-261.65</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1076.97</v>
+      </c>
+      <c r="E411" t="n">
+        <v>-23.97</v>
+      </c>
+      <c r="F411" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="G411" t="n">
+        <v>1076.97</v>
+      </c>
+      <c r="H411" t="n">
+        <v>-17.47</v>
+      </c>
+      <c r="I411" t="n">
+        <v>1039.15</v>
+      </c>
+      <c r="J411" t="n">
+        <v>1039.21</v>
+      </c>
+      <c r="K411" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1526.1</v>
+      </c>
+      <c r="D412" t="n">
+        <v>1504.36</v>
+      </c>
+      <c r="E412" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="F412" t="n">
+        <v>1544.6</v>
+      </c>
+      <c r="G412" t="n">
+        <v>1528.5</v>
+      </c>
+      <c r="H412" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I412" t="n">
+        <v>1525.9</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1494.74</v>
+      </c>
+      <c r="K412" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="D413" t="n">
+        <v>3181.19</v>
+      </c>
+      <c r="E413" t="n">
+        <v>217.01</v>
+      </c>
+      <c r="F413" t="n">
+        <v>3447.9</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3414.55</v>
+      </c>
+      <c r="H413" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="I413" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>3339.5</v>
+      </c>
+      <c r="K413" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D414" t="n">
+        <v>2188.49</v>
+      </c>
+      <c r="E414" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>2279</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2280.44</v>
+      </c>
+      <c r="H414" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2232.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>2231</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D415" t="n">
+        <v>466.39</v>
+      </c>
+      <c r="E415" t="n">
+        <v>-67.09</v>
+      </c>
+      <c r="F415" t="n">
+        <v>400.45</v>
+      </c>
+      <c r="G415" t="n">
+        <v>466.39</v>
+      </c>
+      <c r="H415" t="n">
+        <v>-65.94</v>
+      </c>
+      <c r="I415" t="n">
+        <v>393</v>
+      </c>
+      <c r="J415" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="K415" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>14.38</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D416" t="n">
+        <v>1012.2</v>
+      </c>
+      <c r="E416" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F416" t="n">
+        <v>1048.8</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1055.98</v>
+      </c>
+      <c r="H416" t="n">
+        <v>-7.18</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1010.65</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1033.15</v>
+      </c>
+      <c r="K416" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>289</v>
+      </c>
+      <c r="D417" t="n">
+        <v>293</v>
+      </c>
+      <c r="E417" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F417" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="G417" t="n">
+        <v>293</v>
+      </c>
+      <c r="H417" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I417" t="n">
+        <v>289</v>
+      </c>
+      <c r="J417" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="K417" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="D418" t="n">
+        <v>5524.43</v>
+      </c>
+      <c r="E418" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="F418" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G418" t="n">
+        <v>5524.43</v>
+      </c>
+      <c r="H418" t="n">
+        <v>180.57</v>
+      </c>
+      <c r="I418" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="J418" t="n">
+        <v>5424.98</v>
+      </c>
+      <c r="K418" t="n">
+        <v>165.52</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>5250.5</v>
+      </c>
+      <c r="D419" t="n">
+        <v>5175.69</v>
+      </c>
+      <c r="E419" t="n">
+        <v>74.81</v>
+      </c>
+      <c r="F419" t="n">
+        <v>5280</v>
+      </c>
+      <c r="G419" t="n">
+        <v>5279.51</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I419" t="n">
+        <v>5221.5</v>
+      </c>
+      <c r="J419" t="n">
+        <v>5163.61</v>
+      </c>
+      <c r="K419" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>5595</v>
+      </c>
+      <c r="D420" t="n">
+        <v>5561.37</v>
+      </c>
+      <c r="E420" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="F420" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G420" t="n">
+        <v>5561.37</v>
+      </c>
+      <c r="H420" t="n">
+        <v>158.63</v>
+      </c>
+      <c r="I420" t="n">
+        <v>5595</v>
+      </c>
+      <c r="J420" t="n">
+        <v>5438.41</v>
+      </c>
+      <c r="K420" t="n">
+        <v>156.59</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="D421" t="n">
+        <v>698.39</v>
+      </c>
+      <c r="E421" t="n">
+        <v>-25.89</v>
+      </c>
+      <c r="F421" t="n">
+        <v>690.4</v>
+      </c>
+      <c r="G421" t="n">
+        <v>698.39</v>
+      </c>
+      <c r="H421" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="I421" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="J421" t="n">
+        <v>664.92</v>
+      </c>
+      <c r="K421" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="D422" t="n">
+        <v>3988.26</v>
+      </c>
+      <c r="E422" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="F422" t="n">
+        <v>4124.9</v>
+      </c>
+      <c r="G422" t="n">
+        <v>4047.72</v>
+      </c>
+      <c r="H422" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="I422" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="J422" t="n">
+        <v>3989.84</v>
+      </c>
+      <c r="K422" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>889</v>
+      </c>
+      <c r="D423" t="n">
+        <v>867.9299999999999</v>
+      </c>
+      <c r="E423" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="F423" t="n">
+        <v>905</v>
+      </c>
+      <c r="G423" t="n">
+        <v>898.46</v>
+      </c>
+      <c r="H423" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I423" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="J423" t="n">
+        <v>878.9</v>
+      </c>
+      <c r="K423" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>1323.5</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1310.96</v>
+      </c>
+      <c r="E424" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F424" t="n">
+        <v>1350.9</v>
+      </c>
+      <c r="G424" t="n">
+        <v>1313.69</v>
+      </c>
+      <c r="H424" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="I424" t="n">
+        <v>1322</v>
+      </c>
+      <c r="J424" t="n">
+        <v>1284.25</v>
+      </c>
+      <c r="K424" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>517</v>
+      </c>
+      <c r="D425" t="n">
+        <v>480.66</v>
+      </c>
+      <c r="E425" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="F425" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="G425" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="H425" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="I425" t="n">
+        <v>514.75</v>
+      </c>
+      <c r="J425" t="n">
+        <v>501.99</v>
+      </c>
+      <c r="K425" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>327</v>
+      </c>
+      <c r="D426" t="n">
+        <v>300.94</v>
+      </c>
+      <c r="E426" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="F426" t="n">
+        <v>332</v>
+      </c>
+      <c r="G426" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I426" t="n">
+        <v>325</v>
+      </c>
+      <c r="J426" t="n">
+        <v>323.91</v>
+      </c>
+      <c r="K426" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D427" t="n">
+        <v>1185.6</v>
+      </c>
+      <c r="E427" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="G427" t="n">
+        <v>1189.57</v>
+      </c>
+      <c r="H427" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="I427" t="n">
+        <v>1195</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1162.96</v>
+      </c>
+      <c r="K427" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D428" t="n">
+        <v>2563.5</v>
+      </c>
+      <c r="E428" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F428" t="n">
+        <v>2656.8</v>
+      </c>
+      <c r="G428" t="n">
+        <v>2584.48</v>
+      </c>
+      <c r="H428" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="I428" t="n">
+        <v>2579.4</v>
+      </c>
+      <c r="J428" t="n">
+        <v>2533.54</v>
+      </c>
+      <c r="K428" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1878.53</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F429" t="n">
+        <v>1937.1</v>
+      </c>
+      <c r="G429" t="n">
+        <v>1910.56</v>
+      </c>
+      <c r="H429" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="I429" t="n">
+        <v>1878.6</v>
+      </c>
+      <c r="J429" t="n">
+        <v>1869.32</v>
+      </c>
+      <c r="K429" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D430" t="n">
+        <v>13562.91</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1172.09</v>
+      </c>
+      <c r="F430" t="n">
+        <v>14983</v>
+      </c>
+      <c r="G430" t="n">
+        <v>14809.22</v>
+      </c>
+      <c r="H430" t="n">
+        <v>173.78</v>
+      </c>
+      <c r="I430" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J430" t="n">
+        <v>14483.88</v>
+      </c>
+      <c r="K430" t="n">
+        <v>236.12</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>8.640000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21197,7 +22809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22830,6 +24442,110 @@
       </c>
       <c r="N31" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="D32" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>24378.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>24321.65</v>
+      </c>
+      <c r="H32" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="I32" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="J32" t="n">
+        <v>24150.8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>57996.05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>57982.59</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="I33" t="n">
+        <v>57611.85</v>
+      </c>
+      <c r="J33" t="n">
+        <v>57598.39</v>
+      </c>
+      <c r="K33" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22843,7 +24559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N399"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43614,6 +45330,1618 @@
         <v>9.710000000000001</v>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>UNOMINDA (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1255.73</v>
+      </c>
+      <c r="E400" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="F400" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="G400" t="n">
+        <v>1271.96</v>
+      </c>
+      <c r="H400" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1250.7</v>
+      </c>
+      <c r="J400" t="n">
+        <v>1234.8</v>
+      </c>
+      <c r="K400" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>MCX (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D401" t="n">
+        <v>3604.21</v>
+      </c>
+      <c r="E401" t="n">
+        <v>-254.21</v>
+      </c>
+      <c r="F401" t="n">
+        <v>3355</v>
+      </c>
+      <c r="G401" t="n">
+        <v>3427.28</v>
+      </c>
+      <c r="H401" t="n">
+        <v>-72.28</v>
+      </c>
+      <c r="I401" t="n">
+        <v>3243.3</v>
+      </c>
+      <c r="J401" t="n">
+        <v>3248.44</v>
+      </c>
+      <c r="K401" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N401" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D402" t="n">
+        <v>2042.6</v>
+      </c>
+      <c r="E402" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="F402" t="n">
+        <v>2024.9</v>
+      </c>
+      <c r="G402" t="n">
+        <v>2021.73</v>
+      </c>
+      <c r="H402" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I402" t="n">
+        <v>2005.5</v>
+      </c>
+      <c r="J402" t="n">
+        <v>1975.37</v>
+      </c>
+      <c r="K402" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SBIN (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D403" t="n">
+        <v>1068.43</v>
+      </c>
+      <c r="E403" t="n">
+        <v>-16.43</v>
+      </c>
+      <c r="F403" t="n">
+        <v>1062.3</v>
+      </c>
+      <c r="G403" t="n">
+        <v>1061.36</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I403" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="J403" t="n">
+        <v>1031.44</v>
+      </c>
+      <c r="K403" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>2159</v>
+      </c>
+      <c r="D404" t="n">
+        <v>2141.83</v>
+      </c>
+      <c r="E404" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="F404" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G404" t="n">
+        <v>2178.68</v>
+      </c>
+      <c r="H404" t="n">
+        <v>-19.68</v>
+      </c>
+      <c r="I404" t="n">
+        <v>2119.7</v>
+      </c>
+      <c r="J404" t="n">
+        <v>2116.44</v>
+      </c>
+      <c r="K404" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>PNB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D405" t="n">
+        <v>121.87</v>
+      </c>
+      <c r="E405" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="F405" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G405" t="n">
+        <v>117.61</v>
+      </c>
+      <c r="H405" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I405" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J405" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="K405" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>POLICYBZR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1849.63</v>
+      </c>
+      <c r="E406" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="F406" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G406" t="n">
+        <v>1873.88</v>
+      </c>
+      <c r="H406" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1806.3</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1790.73</v>
+      </c>
+      <c r="K406" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ASHOKLEY (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="D407" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="E407" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="F407" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G407" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="H407" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I407" t="n">
+        <v>175.41</v>
+      </c>
+      <c r="J407" t="n">
+        <v>175.06</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D408" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E408" t="n">
+        <v>323</v>
+      </c>
+      <c r="F408" t="n">
+        <v>11540</v>
+      </c>
+      <c r="G408" t="n">
+        <v>11627.45</v>
+      </c>
+      <c r="H408" t="n">
+        <v>-87.45</v>
+      </c>
+      <c r="I408" t="n">
+        <v>11223</v>
+      </c>
+      <c r="J408" t="n">
+        <v>11325.96</v>
+      </c>
+      <c r="K408" t="n">
+        <v>-102.96</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>UNIONBANK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>187.52</v>
+      </c>
+      <c r="D409" t="n">
+        <v>199.14</v>
+      </c>
+      <c r="E409" t="n">
+        <v>-11.62</v>
+      </c>
+      <c r="F409" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="G409" t="n">
+        <v>190.32</v>
+      </c>
+      <c r="H409" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I409" t="n">
+        <v>187.12</v>
+      </c>
+      <c r="J409" t="n">
+        <v>183</v>
+      </c>
+      <c r="K409" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>OIL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>469.15</v>
+      </c>
+      <c r="D410" t="n">
+        <v>491.09</v>
+      </c>
+      <c r="E410" t="n">
+        <v>-21.94</v>
+      </c>
+      <c r="F410" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="G410" t="n">
+        <v>478.09</v>
+      </c>
+      <c r="H410" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="I410" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J410" t="n">
+        <v>456.36</v>
+      </c>
+      <c r="K410" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>M&amp;M (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="D411" t="n">
+        <v>3220.43</v>
+      </c>
+      <c r="E411" t="n">
+        <v>177.77</v>
+      </c>
+      <c r="F411" t="n">
+        <v>3447.9</v>
+      </c>
+      <c r="G411" t="n">
+        <v>3414.36</v>
+      </c>
+      <c r="H411" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="I411" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="J411" t="n">
+        <v>3342.45</v>
+      </c>
+      <c r="K411" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>HYUNDAI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D412" t="n">
+        <v>2226.91</v>
+      </c>
+      <c r="E412" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="F412" t="n">
+        <v>2279</v>
+      </c>
+      <c r="G412" t="n">
+        <v>2273.04</v>
+      </c>
+      <c r="H412" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="I412" t="n">
+        <v>2232.3</v>
+      </c>
+      <c r="J412" t="n">
+        <v>2203.72</v>
+      </c>
+      <c r="K412" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>NATIONALUM (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D413" t="n">
+        <v>482.13</v>
+      </c>
+      <c r="E413" t="n">
+        <v>-82.83</v>
+      </c>
+      <c r="F413" t="n">
+        <v>400.45</v>
+      </c>
+      <c r="G413" t="n">
+        <v>409.34</v>
+      </c>
+      <c r="H413" t="n">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="I413" t="n">
+        <v>393</v>
+      </c>
+      <c r="J413" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="K413" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>17.18</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>HINDALCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D414" t="n">
+        <v>1102.38</v>
+      </c>
+      <c r="E414" t="n">
+        <v>-49.38</v>
+      </c>
+      <c r="F414" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1069.31</v>
+      </c>
+      <c r="H414" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1039.15</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1027.14</v>
+      </c>
+      <c r="K414" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D415" t="n">
+        <v>1035.94</v>
+      </c>
+      <c r="E415" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F415" t="n">
+        <v>1048.8</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1058.36</v>
+      </c>
+      <c r="H415" t="n">
+        <v>-9.56</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1010.65</v>
+      </c>
+      <c r="J415" t="n">
+        <v>1012.75</v>
+      </c>
+      <c r="K415" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ASTRAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>1526.1</v>
+      </c>
+      <c r="D416" t="n">
+        <v>1537.34</v>
+      </c>
+      <c r="E416" t="n">
+        <v>-11.24</v>
+      </c>
+      <c r="F416" t="n">
+        <v>1544.6</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1547.31</v>
+      </c>
+      <c r="H416" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1525.9</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1490.47</v>
+      </c>
+      <c r="K416" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>PERSISTENT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="D417" t="n">
+        <v>5639.45</v>
+      </c>
+      <c r="E417" t="n">
+        <v>-48.95</v>
+      </c>
+      <c r="F417" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G417" t="n">
+        <v>5662.31</v>
+      </c>
+      <c r="H417" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="I417" t="n">
+        <v>5590.5</v>
+      </c>
+      <c r="J417" t="n">
+        <v>5464.44</v>
+      </c>
+      <c r="K417" t="n">
+        <v>126.06</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>CONCOR (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>517</v>
+      </c>
+      <c r="D418" t="n">
+        <v>490.38</v>
+      </c>
+      <c r="E418" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="F418" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="G418" t="n">
+        <v>523.36</v>
+      </c>
+      <c r="H418" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I418" t="n">
+        <v>514.75</v>
+      </c>
+      <c r="J418" t="n">
+        <v>505.57</v>
+      </c>
+      <c r="K418" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ETERNAL (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>327</v>
+      </c>
+      <c r="D419" t="n">
+        <v>306.71</v>
+      </c>
+      <c r="E419" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="F419" t="n">
+        <v>332</v>
+      </c>
+      <c r="G419" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="H419" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I419" t="n">
+        <v>325</v>
+      </c>
+      <c r="J419" t="n">
+        <v>320.02</v>
+      </c>
+      <c r="K419" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>INDIGO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>5250.5</v>
+      </c>
+      <c r="D420" t="n">
+        <v>5251.52</v>
+      </c>
+      <c r="E420" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="F420" t="n">
+        <v>5280</v>
+      </c>
+      <c r="G420" t="n">
+        <v>5287.06</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="I420" t="n">
+        <v>5221.5</v>
+      </c>
+      <c r="J420" t="n">
+        <v>5155.56</v>
+      </c>
+      <c r="K420" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>PETRONET (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>289</v>
+      </c>
+      <c r="D421" t="n">
+        <v>298.34</v>
+      </c>
+      <c r="E421" t="n">
+        <v>-9.34</v>
+      </c>
+      <c r="F421" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="G421" t="n">
+        <v>291.99</v>
+      </c>
+      <c r="H421" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I421" t="n">
+        <v>289</v>
+      </c>
+      <c r="J421" t="n">
+        <v>283.03</v>
+      </c>
+      <c r="K421" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>5595</v>
+      </c>
+      <c r="D422" t="n">
+        <v>5667.83</v>
+      </c>
+      <c r="E422" t="n">
+        <v>-72.83</v>
+      </c>
+      <c r="F422" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G422" t="n">
+        <v>5657.93</v>
+      </c>
+      <c r="H422" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="I422" t="n">
+        <v>5595</v>
+      </c>
+      <c r="J422" t="n">
+        <v>5475.63</v>
+      </c>
+      <c r="K422" t="n">
+        <v>119.37</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>DLF (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="D423" t="n">
+        <v>712.1</v>
+      </c>
+      <c r="E423" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="F423" t="n">
+        <v>690.4</v>
+      </c>
+      <c r="G423" t="n">
+        <v>680.36</v>
+      </c>
+      <c r="H423" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="I423" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="J423" t="n">
+        <v>657.92</v>
+      </c>
+      <c r="K423" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>LT (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="D424" t="n">
+        <v>4013.97</v>
+      </c>
+      <c r="E424" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="F424" t="n">
+        <v>4124.9</v>
+      </c>
+      <c r="G424" t="n">
+        <v>4034.62</v>
+      </c>
+      <c r="H424" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="I424" t="n">
+        <v>4038.1</v>
+      </c>
+      <c r="J424" t="n">
+        <v>3989.09</v>
+      </c>
+      <c r="K424" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>INDIANB (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>889</v>
+      </c>
+      <c r="D425" t="n">
+        <v>883.76</v>
+      </c>
+      <c r="E425" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F425" t="n">
+        <v>905</v>
+      </c>
+      <c r="G425" t="n">
+        <v>898.23</v>
+      </c>
+      <c r="H425" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="I425" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="J425" t="n">
+        <v>870.61</v>
+      </c>
+      <c r="K425" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>NAUKRI (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>1323.5</v>
+      </c>
+      <c r="D426" t="n">
+        <v>1347.17</v>
+      </c>
+      <c r="E426" t="n">
+        <v>-23.67</v>
+      </c>
+      <c r="F426" t="n">
+        <v>1350.9</v>
+      </c>
+      <c r="G426" t="n">
+        <v>1349.09</v>
+      </c>
+      <c r="H426" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I426" t="n">
+        <v>1322</v>
+      </c>
+      <c r="J426" t="n">
+        <v>1287.14</v>
+      </c>
+      <c r="K426" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>360ONE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D427" t="n">
+        <v>1212.07</v>
+      </c>
+      <c r="E427" t="n">
+        <v>-14.87</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="G427" t="n">
+        <v>1214.29</v>
+      </c>
+      <c r="H427" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I427" t="n">
+        <v>1195</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1168.9</v>
+      </c>
+      <c r="K427" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MAZDOCK (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D428" t="n">
+        <v>2630.77</v>
+      </c>
+      <c r="E428" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="F428" t="n">
+        <v>2656.8</v>
+      </c>
+      <c r="G428" t="n">
+        <v>2672.3</v>
+      </c>
+      <c r="H428" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="I428" t="n">
+        <v>2579.4</v>
+      </c>
+      <c r="J428" t="n">
+        <v>2555.5</v>
+      </c>
+      <c r="K428" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>COFORGE (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1908.33</v>
+      </c>
+      <c r="E429" t="n">
+        <v>-28.33</v>
+      </c>
+      <c r="F429" t="n">
+        <v>1937.1</v>
+      </c>
+      <c r="G429" t="n">
+        <v>1901.22</v>
+      </c>
+      <c r="H429" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="I429" t="n">
+        <v>1878.6</v>
+      </c>
+      <c r="J429" t="n">
+        <v>1839.83</v>
+      </c>
+      <c r="K429" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>DIXON (AUG-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D430" t="n">
+        <v>13876.44</v>
+      </c>
+      <c r="E430" t="n">
+        <v>858.5599999999999</v>
+      </c>
+      <c r="F430" t="n">
+        <v>14983</v>
+      </c>
+      <c r="G430" t="n">
+        <v>14956.58</v>
+      </c>
+      <c r="H430" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="I430" t="n">
+        <v>14720</v>
+      </c>
+      <c r="J430" t="n">
+        <v>14378.2</v>
+      </c>
+      <c r="K430" t="n">
+        <v>341.8</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -21198,31 +21198,31 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="D400" t="n">
         <v>2015.46</v>
       </c>
       <c r="E400" t="n">
-        <v>-5.46</v>
+        <v>-11.46</v>
       </c>
       <c r="F400" t="n">
-        <v>2024.9</v>
+        <v>2011.7</v>
       </c>
       <c r="G400" t="n">
         <v>2015.46</v>
       </c>
       <c r="H400" t="n">
-        <v>9.44</v>
+        <v>-3.76</v>
       </c>
       <c r="I400" t="n">
-        <v>2005.5</v>
+        <v>1985</v>
       </c>
       <c r="J400" t="n">
         <v>1964.76</v>
       </c>
       <c r="K400" t="n">
-        <v>40.74</v>
+        <v>20.24</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>0.27</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="401">
@@ -21250,31 +21250,31 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="D401" t="n">
         <v>1050.91</v>
       </c>
       <c r="E401" t="n">
-        <v>1.09</v>
+        <v>-2.91</v>
       </c>
       <c r="F401" t="n">
-        <v>1062.3</v>
+        <v>1048</v>
       </c>
       <c r="G401" t="n">
         <v>1058.98</v>
       </c>
       <c r="H401" t="n">
-        <v>3.32</v>
+        <v>-10.98</v>
       </c>
       <c r="I401" t="n">
-        <v>1051.2</v>
+        <v>1031.3</v>
       </c>
       <c r="J401" t="n">
         <v>1035.78</v>
       </c>
       <c r="K401" t="n">
-        <v>15.42</v>
+        <v>-4.48</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="402">
@@ -21302,31 +21302,31 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1260</v>
+        <v>1253.4</v>
       </c>
       <c r="D402" t="n">
         <v>1234.38</v>
       </c>
       <c r="E402" t="n">
-        <v>25.62</v>
+        <v>19.02</v>
       </c>
       <c r="F402" t="n">
-        <v>1272.1</v>
+        <v>1256.5</v>
       </c>
       <c r="G402" t="n">
         <v>1261.24</v>
       </c>
       <c r="H402" t="n">
-        <v>10.86</v>
+        <v>-4.74</v>
       </c>
       <c r="I402" t="n">
-        <v>1250.7</v>
+        <v>1240.5</v>
       </c>
       <c r="J402" t="n">
         <v>1233.35</v>
       </c>
       <c r="K402" t="n">
-        <v>17.35</v>
+        <v>7.15</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="403">
@@ -21354,31 +21354,31 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2159</v>
+        <v>2139.3</v>
       </c>
       <c r="D403" t="n">
         <v>2106.22</v>
       </c>
       <c r="E403" t="n">
-        <v>52.78</v>
+        <v>33.08</v>
       </c>
       <c r="F403" t="n">
-        <v>2159</v>
+        <v>2151.8</v>
       </c>
       <c r="G403" t="n">
         <v>2177.62</v>
       </c>
       <c r="H403" t="n">
-        <v>-18.62</v>
+        <v>-25.82</v>
       </c>
       <c r="I403" t="n">
-        <v>2119.7</v>
+        <v>2124</v>
       </c>
       <c r="J403" t="n">
         <v>2130.04</v>
       </c>
       <c r="K403" t="n">
-        <v>-10.34</v>
+        <v>-6.04</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>2.51</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="404">
@@ -21406,31 +21406,31 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>116.7</v>
+        <v>115.93</v>
       </c>
       <c r="D404" t="n">
         <v>120</v>
       </c>
       <c r="E404" t="n">
-        <v>-3.3</v>
+        <v>-4.07</v>
       </c>
       <c r="F404" t="n">
-        <v>118.2</v>
+        <v>116.9</v>
       </c>
       <c r="G404" t="n">
         <v>120</v>
       </c>
       <c r="H404" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="I404" t="n">
-        <v>116.39</v>
+        <v>115.01</v>
       </c>
       <c r="J404" t="n">
         <v>115.09</v>
       </c>
       <c r="K404" t="n">
-        <v>1.3</v>
+        <v>-0.08</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>2.75</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="405">
@@ -21458,31 +21458,31 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3350</v>
+        <v>3280</v>
       </c>
       <c r="D405" t="n">
         <v>3494.24</v>
       </c>
       <c r="E405" t="n">
-        <v>-144.24</v>
+        <v>-214.24</v>
       </c>
       <c r="F405" t="n">
-        <v>3355</v>
+        <v>3308.7</v>
       </c>
       <c r="G405" t="n">
         <v>3494.24</v>
       </c>
       <c r="H405" t="n">
-        <v>-139.24</v>
+        <v>-185.54</v>
       </c>
       <c r="I405" t="n">
-        <v>3243.3</v>
+        <v>3254.3</v>
       </c>
       <c r="J405" t="n">
         <v>3320.18</v>
       </c>
       <c r="K405" t="n">
-        <v>-76.88</v>
+        <v>-65.88</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>4.13</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="406">
@@ -21510,31 +21510,31 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1840</v>
+        <v>1798.3</v>
       </c>
       <c r="D406" t="n">
         <v>1801.6</v>
       </c>
       <c r="E406" t="n">
-        <v>38.4</v>
+        <v>-3.3</v>
       </c>
       <c r="F406" t="n">
-        <v>1875</v>
+        <v>1815</v>
       </c>
       <c r="G406" t="n">
         <v>1855.29</v>
       </c>
       <c r="H406" t="n">
-        <v>19.71</v>
+        <v>-40.29</v>
       </c>
       <c r="I406" t="n">
-        <v>1806.3</v>
+        <v>1775</v>
       </c>
       <c r="J406" t="n">
         <v>1814.74</v>
       </c>
       <c r="K406" t="n">
-        <v>-8.44</v>
+        <v>-39.74</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>2.13</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="407">
@@ -21562,31 +21562,31 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>179.05</v>
+        <v>174.69</v>
       </c>
       <c r="D407" t="n">
         <v>176.8</v>
       </c>
       <c r="E407" t="n">
-        <v>2.25</v>
+        <v>-2.11</v>
       </c>
       <c r="F407" t="n">
-        <v>179.5</v>
+        <v>174.69</v>
       </c>
       <c r="G407" t="n">
         <v>180.12</v>
       </c>
       <c r="H407" t="n">
-        <v>-0.62</v>
+        <v>-5.43</v>
       </c>
       <c r="I407" t="n">
-        <v>175.41</v>
+        <v>171.58</v>
       </c>
       <c r="J407" t="n">
         <v>176.17</v>
       </c>
       <c r="K407" t="n">
-        <v>-0.76</v>
+        <v>-4.59</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="408">
@@ -21614,31 +21614,31 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>187.52</v>
+        <v>186.98</v>
       </c>
       <c r="D408" t="n">
         <v>194.65</v>
       </c>
       <c r="E408" t="n">
-        <v>-7.13</v>
+        <v>-7.67</v>
       </c>
       <c r="F408" t="n">
-        <v>192.33</v>
+        <v>187.33</v>
       </c>
       <c r="G408" t="n">
         <v>194.65</v>
       </c>
       <c r="H408" t="n">
-        <v>-2.32</v>
+        <v>-7.32</v>
       </c>
       <c r="I408" t="n">
-        <v>187.12</v>
+        <v>181.4</v>
       </c>
       <c r="J408" t="n">
         <v>182.61</v>
       </c>
       <c r="K408" t="n">
-        <v>4.51</v>
+        <v>-1.21</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="409">
@@ -21666,31 +21666,31 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>469.15</v>
+        <v>467.5</v>
       </c>
       <c r="D409" t="n">
         <v>478.03</v>
       </c>
       <c r="E409" t="n">
-        <v>-8.880000000000001</v>
+        <v>-10.53</v>
       </c>
       <c r="F409" t="n">
-        <v>471.6</v>
+        <v>479</v>
       </c>
       <c r="G409" t="n">
         <v>478.03</v>
       </c>
       <c r="H409" t="n">
-        <v>-6.43</v>
+        <v>0.97</v>
       </c>
       <c r="I409" t="n">
-        <v>458.7</v>
+        <v>466.05</v>
       </c>
       <c r="J409" t="n">
         <v>452.42</v>
       </c>
       <c r="K409" t="n">
-        <v>6.28</v>
+        <v>13.63</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="410">
@@ -21718,31 +21718,31 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>11540</v>
+        <v>11290</v>
       </c>
       <c r="D410" t="n">
         <v>11093.82</v>
       </c>
       <c r="E410" t="n">
-        <v>446.18</v>
+        <v>196.18</v>
       </c>
       <c r="F410" t="n">
-        <v>11540</v>
+        <v>11290</v>
       </c>
       <c r="G410" t="n">
         <v>11689.23</v>
       </c>
       <c r="H410" t="n">
-        <v>-149.23</v>
+        <v>-399.23</v>
       </c>
       <c r="I410" t="n">
-        <v>11223</v>
+        <v>10811</v>
       </c>
       <c r="J410" t="n">
         <v>11484.65</v>
       </c>
       <c r="K410" t="n">
-        <v>-261.65</v>
+        <v>-673.65</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -21751,11 +21751,11 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N410" t="n">
-        <v>4.02</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="411">
@@ -21770,31 +21770,31 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1053</v>
+        <v>1051.05</v>
       </c>
       <c r="D411" t="n">
         <v>1076.97</v>
       </c>
       <c r="E411" t="n">
-        <v>-23.97</v>
+        <v>-25.92</v>
       </c>
       <c r="F411" t="n">
-        <v>1059.5</v>
+        <v>1057</v>
       </c>
       <c r="G411" t="n">
         <v>1076.97</v>
       </c>
       <c r="H411" t="n">
-        <v>-17.47</v>
+        <v>-19.97</v>
       </c>
       <c r="I411" t="n">
-        <v>1039.15</v>
+        <v>1040.45</v>
       </c>
       <c r="J411" t="n">
         <v>1039.21</v>
       </c>
       <c r="K411" t="n">
-        <v>-0.06</v>
+        <v>1.24</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="412">
@@ -21822,31 +21822,31 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1526.1</v>
+        <v>1540</v>
       </c>
       <c r="D412" t="n">
         <v>1504.36</v>
       </c>
       <c r="E412" t="n">
-        <v>21.74</v>
+        <v>35.64</v>
       </c>
       <c r="F412" t="n">
-        <v>1544.6</v>
+        <v>1544.7</v>
       </c>
       <c r="G412" t="n">
         <v>1528.5</v>
       </c>
       <c r="H412" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="I412" t="n">
-        <v>1525.9</v>
+        <v>1519</v>
       </c>
       <c r="J412" t="n">
         <v>1494.74</v>
       </c>
       <c r="K412" t="n">
-        <v>31.16</v>
+        <v>24.26</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="413">
@@ -21874,31 +21874,31 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3398.2</v>
+        <v>3443</v>
       </c>
       <c r="D413" t="n">
         <v>3181.19</v>
       </c>
       <c r="E413" t="n">
-        <v>217.01</v>
+        <v>261.81</v>
       </c>
       <c r="F413" t="n">
-        <v>3447.9</v>
+        <v>3443</v>
       </c>
       <c r="G413" t="n">
         <v>3414.55</v>
       </c>
       <c r="H413" t="n">
-        <v>33.35</v>
+        <v>28.45</v>
       </c>
       <c r="I413" t="n">
-        <v>3398.2</v>
+        <v>3396.8</v>
       </c>
       <c r="J413" t="n">
         <v>3339.5</v>
       </c>
       <c r="K413" t="n">
-        <v>58.7</v>
+        <v>57.3</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>6.82</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="414">
@@ -21926,31 +21926,31 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2250</v>
+        <v>2232.5</v>
       </c>
       <c r="D414" t="n">
         <v>2188.49</v>
       </c>
       <c r="E414" t="n">
-        <v>61.51</v>
+        <v>44.01</v>
       </c>
       <c r="F414" t="n">
-        <v>2279</v>
+        <v>2243.8</v>
       </c>
       <c r="G414" t="n">
         <v>2280.44</v>
       </c>
       <c r="H414" t="n">
-        <v>-1.44</v>
+        <v>-36.64</v>
       </c>
       <c r="I414" t="n">
-        <v>2232.3</v>
+        <v>2190</v>
       </c>
       <c r="J414" t="n">
         <v>2231</v>
       </c>
       <c r="K414" t="n">
-        <v>1.3</v>
+        <v>-41</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="415">
@@ -21978,31 +21978,31 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>399.3</v>
+        <v>397.8</v>
       </c>
       <c r="D415" t="n">
         <v>466.39</v>
       </c>
       <c r="E415" t="n">
-        <v>-67.09</v>
+        <v>-68.59</v>
       </c>
       <c r="F415" t="n">
-        <v>400.45</v>
+        <v>402</v>
       </c>
       <c r="G415" t="n">
         <v>466.39</v>
       </c>
       <c r="H415" t="n">
-        <v>-65.94</v>
+        <v>-64.39</v>
       </c>
       <c r="I415" t="n">
-        <v>393</v>
+        <v>392.05</v>
       </c>
       <c r="J415" t="n">
         <v>388.7</v>
       </c>
       <c r="K415" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>14.38</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="416">
@@ -22030,31 +22030,31 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>1040</v>
+        <v>1011.5</v>
       </c>
       <c r="D416" t="n">
         <v>1012.2</v>
       </c>
       <c r="E416" t="n">
-        <v>27.8</v>
+        <v>-0.7</v>
       </c>
       <c r="F416" t="n">
-        <v>1048.8</v>
+        <v>1019.9</v>
       </c>
       <c r="G416" t="n">
         <v>1055.98</v>
       </c>
       <c r="H416" t="n">
-        <v>-7.18</v>
+        <v>-36.08</v>
       </c>
       <c r="I416" t="n">
-        <v>1010.65</v>
+        <v>992</v>
       </c>
       <c r="J416" t="n">
         <v>1033.15</v>
       </c>
       <c r="K416" t="n">
-        <v>-22.5</v>
+        <v>-41.15</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -22063,11 +22063,11 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N416" t="n">
-        <v>2.75</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="417">
@@ -22082,31 +22082,31 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>289</v>
+        <v>292.5</v>
       </c>
       <c r="D417" t="n">
         <v>293</v>
       </c>
       <c r="E417" t="n">
-        <v>-4</v>
+        <v>-0.5</v>
       </c>
       <c r="F417" t="n">
-        <v>295.95</v>
+        <v>295.7</v>
       </c>
       <c r="G417" t="n">
         <v>293</v>
       </c>
       <c r="H417" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="I417" t="n">
-        <v>289</v>
+        <v>291.6</v>
       </c>
       <c r="J417" t="n">
         <v>281.8</v>
       </c>
       <c r="K417" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>1.37</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="418">
@@ -22134,31 +22134,31 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>5590.5</v>
+        <v>5655</v>
       </c>
       <c r="D418" t="n">
         <v>5524.43</v>
       </c>
       <c r="E418" t="n">
-        <v>66.06999999999999</v>
+        <v>130.57</v>
       </c>
       <c r="F418" t="n">
-        <v>5705</v>
+        <v>5687</v>
       </c>
       <c r="G418" t="n">
         <v>5524.43</v>
       </c>
       <c r="H418" t="n">
-        <v>180.57</v>
+        <v>162.57</v>
       </c>
       <c r="I418" t="n">
-        <v>5590.5</v>
+        <v>5570.5</v>
       </c>
       <c r="J418" t="n">
         <v>5424.98</v>
       </c>
       <c r="K418" t="n">
-        <v>165.52</v>
+        <v>145.52</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>1.2</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="419">
@@ -22186,31 +22186,31 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>5250.5</v>
+        <v>5218</v>
       </c>
       <c r="D419" t="n">
         <v>5175.69</v>
       </c>
       <c r="E419" t="n">
-        <v>74.81</v>
+        <v>42.31</v>
       </c>
       <c r="F419" t="n">
-        <v>5280</v>
+        <v>5227.5</v>
       </c>
       <c r="G419" t="n">
         <v>5279.51</v>
       </c>
       <c r="H419" t="n">
-        <v>0.49</v>
+        <v>-52.01</v>
       </c>
       <c r="I419" t="n">
-        <v>5221.5</v>
+        <v>5080.5</v>
       </c>
       <c r="J419" t="n">
         <v>5163.61</v>
       </c>
       <c r="K419" t="n">
-        <v>57.89</v>
+        <v>-83.11</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>1.45</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="420">
@@ -22238,31 +22238,31 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>5595</v>
+        <v>5624.5</v>
       </c>
       <c r="D420" t="n">
         <v>5561.37</v>
       </c>
       <c r="E420" t="n">
-        <v>33.63</v>
+        <v>63.13</v>
       </c>
       <c r="F420" t="n">
-        <v>5720</v>
+        <v>5682</v>
       </c>
       <c r="G420" t="n">
         <v>5561.37</v>
       </c>
       <c r="H420" t="n">
-        <v>158.63</v>
+        <v>120.63</v>
       </c>
       <c r="I420" t="n">
-        <v>5595</v>
+        <v>5590</v>
       </c>
       <c r="J420" t="n">
         <v>5438.41</v>
       </c>
       <c r="K420" t="n">
-        <v>156.59</v>
+        <v>151.59</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="421">
@@ -22290,31 +22290,31 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>672.5</v>
+        <v>682.95</v>
       </c>
       <c r="D421" t="n">
         <v>698.39</v>
       </c>
       <c r="E421" t="n">
-        <v>-25.89</v>
+        <v>-15.44</v>
       </c>
       <c r="F421" t="n">
-        <v>690.4</v>
+        <v>688.2</v>
       </c>
       <c r="G421" t="n">
         <v>698.39</v>
       </c>
       <c r="H421" t="n">
-        <v>-7.99</v>
+        <v>-10.19</v>
       </c>
       <c r="I421" t="n">
-        <v>672.5</v>
+        <v>678.3</v>
       </c>
       <c r="J421" t="n">
         <v>664.92</v>
       </c>
       <c r="K421" t="n">
-        <v>7.58</v>
+        <v>13.38</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>3.71</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="422">
@@ -22342,31 +22342,31 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>4038.1</v>
+        <v>4119</v>
       </c>
       <c r="D422" t="n">
         <v>3988.26</v>
       </c>
       <c r="E422" t="n">
-        <v>49.84</v>
+        <v>130.74</v>
       </c>
       <c r="F422" t="n">
-        <v>4124.9</v>
+        <v>4125.3</v>
       </c>
       <c r="G422" t="n">
         <v>4047.72</v>
       </c>
       <c r="H422" t="n">
-        <v>77.18000000000001</v>
+        <v>77.58</v>
       </c>
       <c r="I422" t="n">
-        <v>4038.1</v>
+        <v>4066.6</v>
       </c>
       <c r="J422" t="n">
         <v>3989.84</v>
       </c>
       <c r="K422" t="n">
-        <v>48.26</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>1.25</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="423">
@@ -22394,31 +22394,31 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="D423" t="n">
         <v>867.9299999999999</v>
       </c>
       <c r="E423" t="n">
-        <v>21.07</v>
+        <v>10.07</v>
       </c>
       <c r="F423" t="n">
-        <v>905</v>
+        <v>881.75</v>
       </c>
       <c r="G423" t="n">
         <v>898.46</v>
       </c>
       <c r="H423" t="n">
-        <v>6.54</v>
+        <v>-16.71</v>
       </c>
       <c r="I423" t="n">
-        <v>882.5</v>
+        <v>869</v>
       </c>
       <c r="J423" t="n">
         <v>878.9</v>
       </c>
       <c r="K423" t="n">
-        <v>3.6</v>
+        <v>-9.9</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>2.43</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="424">
@@ -22446,31 +22446,31 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>1323.5</v>
+        <v>1350</v>
       </c>
       <c r="D424" t="n">
         <v>1310.96</v>
       </c>
       <c r="E424" t="n">
-        <v>12.54</v>
+        <v>39.04</v>
       </c>
       <c r="F424" t="n">
-        <v>1350.9</v>
+        <v>1350</v>
       </c>
       <c r="G424" t="n">
         <v>1313.69</v>
       </c>
       <c r="H424" t="n">
-        <v>37.21</v>
+        <v>36.31</v>
       </c>
       <c r="I424" t="n">
-        <v>1322</v>
+        <v>1328.1</v>
       </c>
       <c r="J424" t="n">
         <v>1284.25</v>
       </c>
       <c r="K424" t="n">
-        <v>37.75</v>
+        <v>43.85</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -22479,11 +22479,11 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N424" t="n">
-        <v>0.96</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="425">
@@ -22498,31 +22498,31 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D425" t="n">
         <v>480.66</v>
       </c>
       <c r="E425" t="n">
-        <v>36.34</v>
+        <v>35.34</v>
       </c>
       <c r="F425" t="n">
-        <v>524.25</v>
+        <v>518.4</v>
       </c>
       <c r="G425" t="n">
         <v>492.1</v>
       </c>
       <c r="H425" t="n">
-        <v>32.15</v>
+        <v>26.3</v>
       </c>
       <c r="I425" t="n">
-        <v>514.75</v>
+        <v>511.3</v>
       </c>
       <c r="J425" t="n">
         <v>501.99</v>
       </c>
       <c r="K425" t="n">
-        <v>12.76</v>
+        <v>9.31</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>7.56</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="426">
@@ -22550,31 +22550,31 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D426" t="n">
         <v>300.94</v>
       </c>
       <c r="E426" t="n">
-        <v>26.06</v>
+        <v>30.06</v>
       </c>
       <c r="F426" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G426" t="n">
         <v>331.1</v>
       </c>
       <c r="H426" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="I426" t="n">
-        <v>325</v>
+        <v>325.5</v>
       </c>
       <c r="J426" t="n">
         <v>323.91</v>
       </c>
       <c r="K426" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>8.66</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="427">
@@ -22602,31 +22602,31 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1197.2</v>
+        <v>1210</v>
       </c>
       <c r="D427" t="n">
         <v>1185.6</v>
       </c>
       <c r="E427" t="n">
-        <v>11.6</v>
+        <v>24.4</v>
       </c>
       <c r="F427" t="n">
-        <v>1219.8</v>
+        <v>1210</v>
       </c>
       <c r="G427" t="n">
         <v>1189.57</v>
       </c>
       <c r="H427" t="n">
-        <v>30.23</v>
+        <v>20.43</v>
       </c>
       <c r="I427" t="n">
-        <v>1195</v>
+        <v>1186.4</v>
       </c>
       <c r="J427" t="n">
         <v>1162.96</v>
       </c>
       <c r="K427" t="n">
-        <v>32.04</v>
+        <v>23.44</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>0.98</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="428">
@@ -22654,31 +22654,31 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="D428" t="n">
         <v>2563.5</v>
       </c>
       <c r="E428" t="n">
-        <v>61.5</v>
+        <v>46.5</v>
       </c>
       <c r="F428" t="n">
-        <v>2656.8</v>
+        <v>2621.7</v>
       </c>
       <c r="G428" t="n">
         <v>2584.48</v>
       </c>
       <c r="H428" t="n">
-        <v>72.31999999999999</v>
+        <v>37.22</v>
       </c>
       <c r="I428" t="n">
-        <v>2579.4</v>
+        <v>2520</v>
       </c>
       <c r="J428" t="n">
         <v>2533.54</v>
       </c>
       <c r="K428" t="n">
-        <v>45.86</v>
+        <v>-13.54</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="429">
@@ -22706,31 +22706,31 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>1880</v>
+        <v>1892.8</v>
       </c>
       <c r="D429" t="n">
         <v>1878.53</v>
       </c>
       <c r="E429" t="n">
-        <v>1.47</v>
+        <v>14.27</v>
       </c>
       <c r="F429" t="n">
-        <v>1937.1</v>
+        <v>1899.9</v>
       </c>
       <c r="G429" t="n">
         <v>1910.56</v>
       </c>
       <c r="H429" t="n">
-        <v>26.54</v>
+        <v>-10.66</v>
       </c>
       <c r="I429" t="n">
-        <v>1878.6</v>
+        <v>1870</v>
       </c>
       <c r="J429" t="n">
         <v>1869.32</v>
       </c>
       <c r="K429" t="n">
-        <v>9.279999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>0.08</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="430">
@@ -22758,31 +22758,31 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>14735</v>
+        <v>14990</v>
       </c>
       <c r="D430" t="n">
         <v>13562.91</v>
       </c>
       <c r="E430" t="n">
-        <v>1172.09</v>
+        <v>1427.09</v>
       </c>
       <c r="F430" t="n">
-        <v>14983</v>
+        <v>14990</v>
       </c>
       <c r="G430" t="n">
         <v>14809.22</v>
       </c>
       <c r="H430" t="n">
-        <v>173.78</v>
+        <v>180.78</v>
       </c>
       <c r="I430" t="n">
-        <v>14720</v>
+        <v>14400</v>
       </c>
       <c r="J430" t="n">
         <v>14483.88</v>
       </c>
       <c r="K430" t="n">
-        <v>236.12</v>
+        <v>-83.88</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>8.640000000000001</v>
+        <v>10.52</v>
       </c>
     </row>
   </sheetData>
@@ -24456,31 +24456,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>24207.75</v>
+        <v>24334.55</v>
       </c>
       <c r="D32" t="n">
         <v>24207.75</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>126.8</v>
       </c>
       <c r="F32" t="n">
-        <v>24378.6</v>
+        <v>24334.55</v>
       </c>
       <c r="G32" t="n">
         <v>24321.65</v>
       </c>
       <c r="H32" t="n">
-        <v>56.95</v>
+        <v>12.9</v>
       </c>
       <c r="I32" t="n">
-        <v>24207.75</v>
+        <v>24115.45</v>
       </c>
       <c r="J32" t="n">
         <v>24150.8</v>
       </c>
       <c r="K32" t="n">
-        <v>56.95</v>
+        <v>-35.35</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="33">
@@ -24508,31 +24508,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57783.75</v>
+        <v>57514.2</v>
       </c>
       <c r="D33" t="n">
         <v>57783.75</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-269.55</v>
       </c>
       <c r="F33" t="n">
-        <v>57996.05</v>
+        <v>57653.85</v>
       </c>
       <c r="G33" t="n">
         <v>57982.59</v>
       </c>
       <c r="H33" t="n">
-        <v>13.46</v>
+        <v>-328.74</v>
       </c>
       <c r="I33" t="n">
-        <v>57611.85</v>
+        <v>57231.25</v>
       </c>
       <c r="J33" t="n">
         <v>57598.39</v>
       </c>
       <c r="K33" t="n">
-        <v>13.46</v>
+        <v>-367.14</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -45342,31 +45342,31 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1260</v>
+        <v>1253.4</v>
       </c>
       <c r="D400" t="n">
         <v>1255.73</v>
       </c>
       <c r="E400" t="n">
-        <v>4.27</v>
+        <v>-2.33</v>
       </c>
       <c r="F400" t="n">
-        <v>1272.1</v>
+        <v>1256.5</v>
       </c>
       <c r="G400" t="n">
         <v>1271.96</v>
       </c>
       <c r="H400" t="n">
-        <v>0.14</v>
+        <v>-15.46</v>
       </c>
       <c r="I400" t="n">
-        <v>1250.7</v>
+        <v>1240.5</v>
       </c>
       <c r="J400" t="n">
         <v>1234.8</v>
       </c>
       <c r="K400" t="n">
-        <v>15.9</v>
+        <v>5.7</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="401">
@@ -45394,31 +45394,31 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>3350</v>
+        <v>3280</v>
       </c>
       <c r="D401" t="n">
         <v>3604.21</v>
       </c>
       <c r="E401" t="n">
-        <v>-254.21</v>
+        <v>-324.21</v>
       </c>
       <c r="F401" t="n">
-        <v>3355</v>
+        <v>3308.7</v>
       </c>
       <c r="G401" t="n">
         <v>3427.28</v>
       </c>
       <c r="H401" t="n">
-        <v>-72.28</v>
+        <v>-118.58</v>
       </c>
       <c r="I401" t="n">
-        <v>3243.3</v>
+        <v>3254.3</v>
       </c>
       <c r="J401" t="n">
         <v>3248.44</v>
       </c>
       <c r="K401" t="n">
-        <v>-5.14</v>
+        <v>5.86</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>7.05</v>
+        <v>9</v>
       </c>
     </row>
     <row r="402">
@@ -45446,31 +45446,31 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="D402" t="n">
         <v>2042.6</v>
       </c>
       <c r="E402" t="n">
-        <v>-32.6</v>
+        <v>-38.6</v>
       </c>
       <c r="F402" t="n">
-        <v>2024.9</v>
+        <v>2011.7</v>
       </c>
       <c r="G402" t="n">
         <v>2021.73</v>
       </c>
       <c r="H402" t="n">
-        <v>3.17</v>
+        <v>-10.03</v>
       </c>
       <c r="I402" t="n">
-        <v>2005.5</v>
+        <v>1985</v>
       </c>
       <c r="J402" t="n">
         <v>1975.37</v>
       </c>
       <c r="K402" t="n">
-        <v>30.13</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="403">
@@ -45498,31 +45498,31 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="D403" t="n">
         <v>1068.43</v>
       </c>
       <c r="E403" t="n">
-        <v>-16.43</v>
+        <v>-20.43</v>
       </c>
       <c r="F403" t="n">
-        <v>1062.3</v>
+        <v>1048</v>
       </c>
       <c r="G403" t="n">
         <v>1061.36</v>
       </c>
       <c r="H403" t="n">
-        <v>0.9399999999999999</v>
+        <v>-13.36</v>
       </c>
       <c r="I403" t="n">
-        <v>1051.2</v>
+        <v>1031.3</v>
       </c>
       <c r="J403" t="n">
         <v>1031.44</v>
       </c>
       <c r="K403" t="n">
-        <v>19.76</v>
+        <v>-0.14</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="404">
@@ -45550,31 +45550,31 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2159</v>
+        <v>2139.3</v>
       </c>
       <c r="D404" t="n">
         <v>2141.83</v>
       </c>
       <c r="E404" t="n">
-        <v>17.17</v>
+        <v>-2.53</v>
       </c>
       <c r="F404" t="n">
-        <v>2159</v>
+        <v>2151.8</v>
       </c>
       <c r="G404" t="n">
         <v>2178.68</v>
       </c>
       <c r="H404" t="n">
-        <v>-19.68</v>
+        <v>-26.88</v>
       </c>
       <c r="I404" t="n">
-        <v>2119.7</v>
+        <v>2124</v>
       </c>
       <c r="J404" t="n">
         <v>2116.44</v>
       </c>
       <c r="K404" t="n">
-        <v>3.26</v>
+        <v>7.56</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>0.8</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="405">
@@ -45602,31 +45602,31 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>116.7</v>
+        <v>115.93</v>
       </c>
       <c r="D405" t="n">
         <v>121.87</v>
       </c>
       <c r="E405" t="n">
-        <v>-5.17</v>
+        <v>-5.94</v>
       </c>
       <c r="F405" t="n">
-        <v>118.2</v>
+        <v>116.9</v>
       </c>
       <c r="G405" t="n">
         <v>117.61</v>
       </c>
       <c r="H405" t="n">
-        <v>0.59</v>
+        <v>-0.71</v>
       </c>
       <c r="I405" t="n">
-        <v>116.39</v>
+        <v>115.01</v>
       </c>
       <c r="J405" t="n">
         <v>114.52</v>
       </c>
       <c r="K405" t="n">
-        <v>1.87</v>
+        <v>0.49</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>4.24</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="406">
@@ -45654,31 +45654,31 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1840</v>
+        <v>1798.3</v>
       </c>
       <c r="D406" t="n">
         <v>1849.63</v>
       </c>
       <c r="E406" t="n">
-        <v>-9.630000000000001</v>
+        <v>-51.33</v>
       </c>
       <c r="F406" t="n">
-        <v>1875</v>
+        <v>1815</v>
       </c>
       <c r="G406" t="n">
         <v>1873.88</v>
       </c>
       <c r="H406" t="n">
-        <v>1.12</v>
+        <v>-58.88</v>
       </c>
       <c r="I406" t="n">
-        <v>1806.3</v>
+        <v>1775</v>
       </c>
       <c r="J406" t="n">
         <v>1790.73</v>
       </c>
       <c r="K406" t="n">
-        <v>15.57</v>
+        <v>-15.73</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -45687,11 +45687,11 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N406" t="n">
-        <v>0.52</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="407">
@@ -45706,31 +45706,31 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>179.05</v>
+        <v>174.69</v>
       </c>
       <c r="D407" t="n">
         <v>180.42</v>
       </c>
       <c r="E407" t="n">
-        <v>-1.37</v>
+        <v>-5.73</v>
       </c>
       <c r="F407" t="n">
-        <v>179.5</v>
+        <v>174.69</v>
       </c>
       <c r="G407" t="n">
         <v>181.3</v>
       </c>
       <c r="H407" t="n">
-        <v>-1.8</v>
+        <v>-6.61</v>
       </c>
       <c r="I407" t="n">
-        <v>175.41</v>
+        <v>171.58</v>
       </c>
       <c r="J407" t="n">
         <v>175.06</v>
       </c>
       <c r="K407" t="n">
-        <v>0.35</v>
+        <v>-3.48</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -45739,11 +45739,11 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N407" t="n">
-        <v>0.76</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="408">
@@ -45758,31 +45758,31 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>11540</v>
+        <v>11290</v>
       </c>
       <c r="D408" t="n">
         <v>11217</v>
       </c>
       <c r="E408" t="n">
-        <v>323</v>
+        <v>73</v>
       </c>
       <c r="F408" t="n">
-        <v>11540</v>
+        <v>11290</v>
       </c>
       <c r="G408" t="n">
         <v>11627.45</v>
       </c>
       <c r="H408" t="n">
-        <v>-87.45</v>
+        <v>-337.45</v>
       </c>
       <c r="I408" t="n">
-        <v>11223</v>
+        <v>10811</v>
       </c>
       <c r="J408" t="n">
         <v>11325.96</v>
       </c>
       <c r="K408" t="n">
-        <v>-102.96</v>
+        <v>-514.96</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>2.88</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="409">
@@ -45810,31 +45810,31 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>187.52</v>
+        <v>186.98</v>
       </c>
       <c r="D409" t="n">
         <v>199.14</v>
       </c>
       <c r="E409" t="n">
-        <v>-11.62</v>
+        <v>-12.16</v>
       </c>
       <c r="F409" t="n">
-        <v>192.33</v>
+        <v>187.33</v>
       </c>
       <c r="G409" t="n">
         <v>190.32</v>
       </c>
       <c r="H409" t="n">
-        <v>2.01</v>
+        <v>-2.99</v>
       </c>
       <c r="I409" t="n">
-        <v>187.12</v>
+        <v>181.4</v>
       </c>
       <c r="J409" t="n">
         <v>183</v>
       </c>
       <c r="K409" t="n">
-        <v>4.12</v>
+        <v>-1.6</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>5.84</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="410">
@@ -45862,31 +45862,31 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>469.15</v>
+        <v>467.5</v>
       </c>
       <c r="D410" t="n">
         <v>491.09</v>
       </c>
       <c r="E410" t="n">
-        <v>-21.94</v>
+        <v>-23.59</v>
       </c>
       <c r="F410" t="n">
-        <v>471.6</v>
+        <v>479</v>
       </c>
       <c r="G410" t="n">
         <v>478.09</v>
       </c>
       <c r="H410" t="n">
-        <v>-6.49</v>
+        <v>0.91</v>
       </c>
       <c r="I410" t="n">
-        <v>458.7</v>
+        <v>466.05</v>
       </c>
       <c r="J410" t="n">
         <v>456.36</v>
       </c>
       <c r="K410" t="n">
-        <v>2.34</v>
+        <v>9.69</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>4.47</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="411">
@@ -45914,31 +45914,31 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>3398.2</v>
+        <v>3443</v>
       </c>
       <c r="D411" t="n">
         <v>3220.43</v>
       </c>
       <c r="E411" t="n">
-        <v>177.77</v>
+        <v>222.57</v>
       </c>
       <c r="F411" t="n">
-        <v>3447.9</v>
+        <v>3443</v>
       </c>
       <c r="G411" t="n">
         <v>3414.36</v>
       </c>
       <c r="H411" t="n">
-        <v>33.54</v>
+        <v>28.64</v>
       </c>
       <c r="I411" t="n">
-        <v>3398.2</v>
+        <v>3396.8</v>
       </c>
       <c r="J411" t="n">
         <v>3342.45</v>
       </c>
       <c r="K411" t="n">
-        <v>55.75</v>
+        <v>54.35</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>5.52</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="412">
@@ -45966,31 +45966,31 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2250</v>
+        <v>2232.5</v>
       </c>
       <c r="D412" t="n">
         <v>2226.91</v>
       </c>
       <c r="E412" t="n">
-        <v>23.09</v>
+        <v>5.59</v>
       </c>
       <c r="F412" t="n">
-        <v>2279</v>
+        <v>2243.8</v>
       </c>
       <c r="G412" t="n">
         <v>2273.04</v>
       </c>
       <c r="H412" t="n">
-        <v>5.96</v>
+        <v>-29.24</v>
       </c>
       <c r="I412" t="n">
-        <v>2232.3</v>
+        <v>2190</v>
       </c>
       <c r="J412" t="n">
         <v>2203.72</v>
       </c>
       <c r="K412" t="n">
-        <v>28.58</v>
+        <v>-13.72</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>1.04</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="413">
@@ -46018,31 +46018,31 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>399.3</v>
+        <v>397.8</v>
       </c>
       <c r="D413" t="n">
         <v>482.13</v>
       </c>
       <c r="E413" t="n">
-        <v>-82.83</v>
+        <v>-84.33</v>
       </c>
       <c r="F413" t="n">
-        <v>400.45</v>
+        <v>402</v>
       </c>
       <c r="G413" t="n">
         <v>409.34</v>
       </c>
       <c r="H413" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.34</v>
       </c>
       <c r="I413" t="n">
-        <v>393</v>
+        <v>392.05</v>
       </c>
       <c r="J413" t="n">
         <v>386.56</v>
       </c>
       <c r="K413" t="n">
-        <v>6.44</v>
+        <v>5.49</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>17.18</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="414">
@@ -46070,31 +46070,31 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>1053</v>
+        <v>1051.05</v>
       </c>
       <c r="D414" t="n">
         <v>1102.38</v>
       </c>
       <c r="E414" t="n">
-        <v>-49.38</v>
+        <v>-51.33</v>
       </c>
       <c r="F414" t="n">
-        <v>1059.5</v>
+        <v>1057</v>
       </c>
       <c r="G414" t="n">
         <v>1069.31</v>
       </c>
       <c r="H414" t="n">
-        <v>-9.81</v>
+        <v>-12.31</v>
       </c>
       <c r="I414" t="n">
-        <v>1039.15</v>
+        <v>1040.45</v>
       </c>
       <c r="J414" t="n">
         <v>1027.14</v>
       </c>
       <c r="K414" t="n">
-        <v>12.01</v>
+        <v>13.31</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>4.48</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="415">
@@ -46122,31 +46122,31 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>1040</v>
+        <v>1011.5</v>
       </c>
       <c r="D415" t="n">
         <v>1035.94</v>
       </c>
       <c r="E415" t="n">
-        <v>4.06</v>
+        <v>-24.44</v>
       </c>
       <c r="F415" t="n">
-        <v>1048.8</v>
+        <v>1019.9</v>
       </c>
       <c r="G415" t="n">
         <v>1058.36</v>
       </c>
       <c r="H415" t="n">
-        <v>-9.56</v>
+        <v>-38.46</v>
       </c>
       <c r="I415" t="n">
-        <v>1010.65</v>
+        <v>992</v>
       </c>
       <c r="J415" t="n">
         <v>1012.75</v>
       </c>
       <c r="K415" t="n">
-        <v>-2.1</v>
+        <v>-20.75</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>0.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="416">
@@ -46174,31 +46174,31 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>1526.1</v>
+        <v>1540</v>
       </c>
       <c r="D416" t="n">
         <v>1537.34</v>
       </c>
       <c r="E416" t="n">
-        <v>-11.24</v>
+        <v>2.66</v>
       </c>
       <c r="F416" t="n">
-        <v>1544.6</v>
+        <v>1544.7</v>
       </c>
       <c r="G416" t="n">
         <v>1547.31</v>
       </c>
       <c r="H416" t="n">
-        <v>-2.71</v>
+        <v>-2.61</v>
       </c>
       <c r="I416" t="n">
-        <v>1525.9</v>
+        <v>1519</v>
       </c>
       <c r="J416" t="n">
         <v>1490.47</v>
       </c>
       <c r="K416" t="n">
-        <v>35.43</v>
+        <v>28.53</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>0.73</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="417">
@@ -46226,31 +46226,31 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>5590.5</v>
+        <v>5655</v>
       </c>
       <c r="D417" t="n">
         <v>5639.45</v>
       </c>
       <c r="E417" t="n">
-        <v>-48.95</v>
+        <v>15.55</v>
       </c>
       <c r="F417" t="n">
-        <v>5705</v>
+        <v>5687</v>
       </c>
       <c r="G417" t="n">
         <v>5662.31</v>
       </c>
       <c r="H417" t="n">
-        <v>42.69</v>
+        <v>24.69</v>
       </c>
       <c r="I417" t="n">
-        <v>5590.5</v>
+        <v>5570.5</v>
       </c>
       <c r="J417" t="n">
         <v>5464.44</v>
       </c>
       <c r="K417" t="n">
-        <v>126.06</v>
+        <v>106.06</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>0.87</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="418">
@@ -46278,31 +46278,31 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D418" t="n">
         <v>490.38</v>
       </c>
       <c r="E418" t="n">
-        <v>26.62</v>
+        <v>25.62</v>
       </c>
       <c r="F418" t="n">
-        <v>524.25</v>
+        <v>518.4</v>
       </c>
       <c r="G418" t="n">
         <v>523.36</v>
       </c>
       <c r="H418" t="n">
-        <v>0.89</v>
+        <v>-4.96</v>
       </c>
       <c r="I418" t="n">
-        <v>514.75</v>
+        <v>511.3</v>
       </c>
       <c r="J418" t="n">
         <v>505.57</v>
       </c>
       <c r="K418" t="n">
-        <v>9.18</v>
+        <v>5.73</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>5.43</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="419">
@@ -46330,31 +46330,31 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D419" t="n">
         <v>306.71</v>
       </c>
       <c r="E419" t="n">
-        <v>20.29</v>
+        <v>24.29</v>
       </c>
       <c r="F419" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G419" t="n">
         <v>330.69</v>
       </c>
       <c r="H419" t="n">
-        <v>1.31</v>
+        <v>0.31</v>
       </c>
       <c r="I419" t="n">
-        <v>325</v>
+        <v>325.5</v>
       </c>
       <c r="J419" t="n">
         <v>320.02</v>
       </c>
       <c r="K419" t="n">
-        <v>4.98</v>
+        <v>5.48</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>6.62</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="420">
@@ -46382,31 +46382,31 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>5250.5</v>
+        <v>5218</v>
       </c>
       <c r="D420" t="n">
         <v>5251.52</v>
       </c>
       <c r="E420" t="n">
-        <v>-1.02</v>
+        <v>-33.52</v>
       </c>
       <c r="F420" t="n">
-        <v>5280</v>
+        <v>5227.5</v>
       </c>
       <c r="G420" t="n">
         <v>5287.06</v>
       </c>
       <c r="H420" t="n">
-        <v>-7.06</v>
+        <v>-59.56</v>
       </c>
       <c r="I420" t="n">
-        <v>5221.5</v>
+        <v>5080.5</v>
       </c>
       <c r="J420" t="n">
         <v>5155.56</v>
       </c>
       <c r="K420" t="n">
-        <v>65.94</v>
+        <v>-75.06</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>0.02</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="421">
@@ -46434,31 +46434,31 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>289</v>
+        <v>292.5</v>
       </c>
       <c r="D421" t="n">
         <v>298.34</v>
       </c>
       <c r="E421" t="n">
-        <v>-9.34</v>
+        <v>-5.84</v>
       </c>
       <c r="F421" t="n">
-        <v>295.95</v>
+        <v>295.7</v>
       </c>
       <c r="G421" t="n">
         <v>291.99</v>
       </c>
       <c r="H421" t="n">
-        <v>3.96</v>
+        <v>3.71</v>
       </c>
       <c r="I421" t="n">
-        <v>289</v>
+        <v>291.6</v>
       </c>
       <c r="J421" t="n">
         <v>283.03</v>
       </c>
       <c r="K421" t="n">
-        <v>5.97</v>
+        <v>8.57</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>3.13</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="422">
@@ -46486,31 +46486,31 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>5595</v>
+        <v>5624.5</v>
       </c>
       <c r="D422" t="n">
         <v>5667.83</v>
       </c>
       <c r="E422" t="n">
-        <v>-72.83</v>
+        <v>-43.33</v>
       </c>
       <c r="F422" t="n">
-        <v>5720</v>
+        <v>5682</v>
       </c>
       <c r="G422" t="n">
         <v>5657.93</v>
       </c>
       <c r="H422" t="n">
-        <v>62.07</v>
+        <v>24.07</v>
       </c>
       <c r="I422" t="n">
-        <v>5595</v>
+        <v>5590</v>
       </c>
       <c r="J422" t="n">
         <v>5475.63</v>
       </c>
       <c r="K422" t="n">
-        <v>119.37</v>
+        <v>114.37</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>1.28</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="423">
@@ -46538,31 +46538,31 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>672.5</v>
+        <v>682.95</v>
       </c>
       <c r="D423" t="n">
         <v>712.1</v>
       </c>
       <c r="E423" t="n">
-        <v>-39.6</v>
+        <v>-29.15</v>
       </c>
       <c r="F423" t="n">
-        <v>690.4</v>
+        <v>688.2</v>
       </c>
       <c r="G423" t="n">
         <v>680.36</v>
       </c>
       <c r="H423" t="n">
-        <v>10.04</v>
+        <v>7.84</v>
       </c>
       <c r="I423" t="n">
-        <v>672.5</v>
+        <v>678.3</v>
       </c>
       <c r="J423" t="n">
         <v>657.92</v>
       </c>
       <c r="K423" t="n">
-        <v>14.58</v>
+        <v>20.38</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>5.56</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="424">
@@ -46590,31 +46590,31 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>4038.1</v>
+        <v>4119</v>
       </c>
       <c r="D424" t="n">
         <v>4013.97</v>
       </c>
       <c r="E424" t="n">
-        <v>24.13</v>
+        <v>105.03</v>
       </c>
       <c r="F424" t="n">
-        <v>4124.9</v>
+        <v>4125.3</v>
       </c>
       <c r="G424" t="n">
         <v>4034.62</v>
       </c>
       <c r="H424" t="n">
-        <v>90.28</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="I424" t="n">
-        <v>4038.1</v>
+        <v>4066.6</v>
       </c>
       <c r="J424" t="n">
         <v>3989.09</v>
       </c>
       <c r="K424" t="n">
-        <v>49.01</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>0.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="425">
@@ -46642,31 +46642,31 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="D425" t="n">
         <v>883.76</v>
       </c>
       <c r="E425" t="n">
-        <v>5.24</v>
+        <v>-5.76</v>
       </c>
       <c r="F425" t="n">
-        <v>905</v>
+        <v>881.75</v>
       </c>
       <c r="G425" t="n">
         <v>898.23</v>
       </c>
       <c r="H425" t="n">
-        <v>6.77</v>
+        <v>-16.48</v>
       </c>
       <c r="I425" t="n">
-        <v>882.5</v>
+        <v>869</v>
       </c>
       <c r="J425" t="n">
         <v>870.61</v>
       </c>
       <c r="K425" t="n">
-        <v>11.89</v>
+        <v>-1.61</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="426">
@@ -46694,31 +46694,31 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>1323.5</v>
+        <v>1350</v>
       </c>
       <c r="D426" t="n">
         <v>1347.17</v>
       </c>
       <c r="E426" t="n">
-        <v>-23.67</v>
+        <v>2.83</v>
       </c>
       <c r="F426" t="n">
-        <v>1350.9</v>
+        <v>1350</v>
       </c>
       <c r="G426" t="n">
         <v>1349.09</v>
       </c>
       <c r="H426" t="n">
-        <v>1.81</v>
+        <v>0.91</v>
       </c>
       <c r="I426" t="n">
-        <v>1322</v>
+        <v>1328.1</v>
       </c>
       <c r="J426" t="n">
         <v>1287.14</v>
       </c>
       <c r="K426" t="n">
-        <v>34.86</v>
+        <v>40.96</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>1.76</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="427">
@@ -46746,31 +46746,31 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1197.2</v>
+        <v>1210</v>
       </c>
       <c r="D427" t="n">
         <v>1212.07</v>
       </c>
       <c r="E427" t="n">
-        <v>-14.87</v>
+        <v>-2.07</v>
       </c>
       <c r="F427" t="n">
-        <v>1219.8</v>
+        <v>1210</v>
       </c>
       <c r="G427" t="n">
         <v>1214.29</v>
       </c>
       <c r="H427" t="n">
-        <v>5.51</v>
+        <v>-4.29</v>
       </c>
       <c r="I427" t="n">
-        <v>1195</v>
+        <v>1186.4</v>
       </c>
       <c r="J427" t="n">
         <v>1168.9</v>
       </c>
       <c r="K427" t="n">
-        <v>26.1</v>
+        <v>17.5</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>1.23</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="428">
@@ -46798,31 +46798,31 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="D428" t="n">
         <v>2630.77</v>
       </c>
       <c r="E428" t="n">
-        <v>-5.77</v>
+        <v>-20.77</v>
       </c>
       <c r="F428" t="n">
-        <v>2656.8</v>
+        <v>2621.7</v>
       </c>
       <c r="G428" t="n">
         <v>2672.3</v>
       </c>
       <c r="H428" t="n">
-        <v>-15.5</v>
+        <v>-50.6</v>
       </c>
       <c r="I428" t="n">
-        <v>2579.4</v>
+        <v>2520</v>
       </c>
       <c r="J428" t="n">
         <v>2555.5</v>
       </c>
       <c r="K428" t="n">
-        <v>23.9</v>
+        <v>-35.5</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>0.22</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="429">
@@ -46850,31 +46850,31 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>1880</v>
+        <v>1892.8</v>
       </c>
       <c r="D429" t="n">
         <v>1908.33</v>
       </c>
       <c r="E429" t="n">
-        <v>-28.33</v>
+        <v>-15.53</v>
       </c>
       <c r="F429" t="n">
-        <v>1937.1</v>
+        <v>1899.9</v>
       </c>
       <c r="G429" t="n">
         <v>1901.22</v>
       </c>
       <c r="H429" t="n">
-        <v>35.88</v>
+        <v>-1.32</v>
       </c>
       <c r="I429" t="n">
-        <v>1878.6</v>
+        <v>1870</v>
       </c>
       <c r="J429" t="n">
         <v>1839.83</v>
       </c>
       <c r="K429" t="n">
-        <v>38.77</v>
+        <v>30.17</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>1.48</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="430">
@@ -46902,31 +46902,31 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>14735</v>
+        <v>14990</v>
       </c>
       <c r="D430" t="n">
         <v>13876.44</v>
       </c>
       <c r="E430" t="n">
-        <v>858.5599999999999</v>
+        <v>1113.56</v>
       </c>
       <c r="F430" t="n">
-        <v>14983</v>
+        <v>14990</v>
       </c>
       <c r="G430" t="n">
         <v>14956.58</v>
       </c>
       <c r="H430" t="n">
-        <v>26.42</v>
+        <v>33.42</v>
       </c>
       <c r="I430" t="n">
-        <v>14720</v>
+        <v>14400</v>
       </c>
       <c r="J430" t="n">
         <v>14378.2</v>
       </c>
       <c r="K430" t="n">
-        <v>341.8</v>
+        <v>21.8</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>6.19</v>
+        <v>8.02</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22796,6 +22796,1618 @@
       </c>
       <c r="N430" t="n">
         <v>10.52</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D431" t="n">
+        <v>2015.56</v>
+      </c>
+      <c r="E431" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F431" t="n">
+        <v>2024.9</v>
+      </c>
+      <c r="G431" t="n">
+        <v>2015.56</v>
+      </c>
+      <c r="H431" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="I431" t="n">
+        <v>2005.5</v>
+      </c>
+      <c r="J431" t="n">
+        <v>1981.11</v>
+      </c>
+      <c r="K431" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1312.04</v>
+      </c>
+      <c r="E432" t="n">
+        <v>-52.04</v>
+      </c>
+      <c r="F432" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="G432" t="n">
+        <v>1312.04</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-39.94</v>
+      </c>
+      <c r="I432" t="n">
+        <v>1250.7</v>
+      </c>
+      <c r="J432" t="n">
+        <v>1279.57</v>
+      </c>
+      <c r="K432" t="n">
+        <v>-28.87</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N432" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>2159</v>
+      </c>
+      <c r="D433" t="n">
+        <v>2240.15</v>
+      </c>
+      <c r="E433" t="n">
+        <v>-81.15000000000001</v>
+      </c>
+      <c r="F433" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G433" t="n">
+        <v>2240.15</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-81.15000000000001</v>
+      </c>
+      <c r="I433" t="n">
+        <v>2119.7</v>
+      </c>
+      <c r="J433" t="n">
+        <v>2149.29</v>
+      </c>
+      <c r="K433" t="n">
+        <v>-29.59</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>469.15</v>
+      </c>
+      <c r="D434" t="n">
+        <v>463.18</v>
+      </c>
+      <c r="E434" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="F434" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="G434" t="n">
+        <v>470.72</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I434" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="K434" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>2035.1</v>
+      </c>
+      <c r="D435" t="n">
+        <v>2083.42</v>
+      </c>
+      <c r="E435" t="n">
+        <v>-48.32</v>
+      </c>
+      <c r="F435" t="n">
+        <v>2088.5</v>
+      </c>
+      <c r="G435" t="n">
+        <v>2083.42</v>
+      </c>
+      <c r="H435" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I435" t="n">
+        <v>2035.1</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2020.16</v>
+      </c>
+      <c r="K435" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1885.58</v>
+      </c>
+      <c r="E436" t="n">
+        <v>-15.58</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1905.5</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1885.58</v>
+      </c>
+      <c r="H436" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="I436" t="n">
+        <v>1867.8</v>
+      </c>
+      <c r="J436" t="n">
+        <v>1829.23</v>
+      </c>
+      <c r="K436" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="D437" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F437" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="G437" t="n">
+        <v>181.43</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="I437" t="n">
+        <v>175.41</v>
+      </c>
+      <c r="J437" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="K437" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>289</v>
+      </c>
+      <c r="D438" t="n">
+        <v>292.78</v>
+      </c>
+      <c r="E438" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="F438" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="G438" t="n">
+        <v>295.83</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I438" t="n">
+        <v>289</v>
+      </c>
+      <c r="J438" t="n">
+        <v>289.37</v>
+      </c>
+      <c r="K438" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="D439" t="n">
+        <v>667.5</v>
+      </c>
+      <c r="E439" t="n">
+        <v>5</v>
+      </c>
+      <c r="F439" t="n">
+        <v>690.4</v>
+      </c>
+      <c r="G439" t="n">
+        <v>690.92</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I439" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="J439" t="n">
+        <v>675.96</v>
+      </c>
+      <c r="K439" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D440" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="E440" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F440" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G440" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="H440" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I440" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="J440" t="n">
+        <v>113.31</v>
+      </c>
+      <c r="K440" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+         